--- a/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
+++ b/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Procomm\Documents\GitHub\Acumatica_Customizations_and_Packages\Istar_Development\Projects\BOL_Generation\Code\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C077439-9008-482F-9B8A-C0AC7C780BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1157327F-B2F9-41B3-BBF0-5010D1900D06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3705" yWindow="5430" windowWidth="28800" windowHeight="15345" xr2:uid="{888CA347-7849-4038-B8EE-FAC87BA1B844}"/>
   </bookViews>
@@ -1443,7 +1443,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="443">
+  <cellXfs count="447">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1473,7 +1473,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1496,90 +1495,25 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1744,33 +1678,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1780,21 +1687,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1846,24 +1738,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1891,9 +1765,6 @@
     <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1906,15 +1777,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1993,60 +1855,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2110,30 +1918,6 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2628,6 +2412,238 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="32" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="8" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4982,1165 +4998,1165 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="357" t="s">
         <v>237</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="145" t="s">
+      <c r="B1" s="358"/>
+      <c r="C1" s="109" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
-      <c r="L1" s="146" t="s">
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="110" t="s">
         <v>62</v>
       </c>
-      <c r="M1" s="147"/>
+      <c r="M1" s="111"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="140" t="s">
+      <c r="A2" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="141"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="142"/>
-      <c r="I2" s="148" t="s">
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
-      <c r="M2" s="150"/>
+      <c r="J2" s="360"/>
+      <c r="K2" s="360"/>
+      <c r="L2" s="360"/>
+      <c r="M2" s="361"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="128" t="s">
+      <c r="A3" s="92" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="129"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="151"/>
-      <c r="J3" s="152"/>
-      <c r="K3" s="152"/>
-      <c r="L3" s="152"/>
-      <c r="M3" s="153"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="365"/>
+      <c r="J3" s="366"/>
+      <c r="K3" s="366"/>
+      <c r="L3" s="366"/>
+      <c r="M3" s="367"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="128" t="s">
+      <c r="A4" s="92" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="129"/>
-      <c r="C4" s="129"/>
-      <c r="D4" s="129"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="129"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="131"/>
-      <c r="J4" s="132"/>
-      <c r="K4" s="132"/>
-      <c r="L4" s="132"/>
-      <c r="M4" s="133"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="95"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
+      <c r="M4" s="97"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="128" t="s">
+      <c r="A5" s="92" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="129"/>
-      <c r="C5" s="129"/>
-      <c r="D5" s="129"/>
-      <c r="E5" s="129"/>
-      <c r="F5" s="129"/>
-      <c r="G5" s="129"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="131"/>
-      <c r="J5" s="132"/>
-      <c r="K5" s="132"/>
-      <c r="L5" s="132"/>
-      <c r="M5" s="133"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="95"/>
+      <c r="J5" s="96"/>
+      <c r="K5" s="96"/>
+      <c r="L5" s="96"/>
+      <c r="M5" s="97"/>
     </row>
     <row r="6" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="137" t="s">
+      <c r="A6" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="138"/>
-      <c r="C6" s="138"/>
-      <c r="D6" s="138"/>
-      <c r="E6" s="138"/>
-      <c r="F6" s="139" t="s">
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="139"/>
+      <c r="G6" s="103"/>
       <c r="H6" s="12"/>
-      <c r="I6" s="134"/>
-      <c r="J6" s="135"/>
-      <c r="K6" s="135"/>
-      <c r="L6" s="135"/>
-      <c r="M6" s="136"/>
+      <c r="I6" s="98"/>
+      <c r="J6" s="99"/>
+      <c r="K6" s="99"/>
+      <c r="L6" s="99"/>
+      <c r="M6" s="100"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="140" t="s">
+      <c r="A7" s="104" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="141"/>
-      <c r="C7" s="141"/>
-      <c r="D7" s="141"/>
-      <c r="E7" s="141"/>
-      <c r="F7" s="141"/>
-      <c r="G7" s="141"/>
-      <c r="H7" s="142"/>
-      <c r="I7" s="53" t="s">
+      <c r="B7" s="105"/>
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="378" t="s">
         <v>233</v>
       </c>
-      <c r="J7" s="54"/>
-      <c r="K7" s="56" t="str">
+      <c r="J7" s="379"/>
+      <c r="K7" s="380" t="str">
         <f>ADDRESS!I1</f>
         <v>CH Robinson</v>
       </c>
-      <c r="L7" s="54"/>
-      <c r="M7" s="55"/>
+      <c r="L7" s="379"/>
+      <c r="M7" s="381"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="160" t="s">
+      <c r="A8" s="362" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="161"/>
-      <c r="C8" s="161"/>
-      <c r="D8" s="161"/>
-      <c r="E8" s="162" t="s">
+      <c r="B8" s="363"/>
+      <c r="C8" s="363"/>
+      <c r="D8" s="363"/>
+      <c r="E8" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="162"/>
-      <c r="G8" s="162"/>
-      <c r="H8" s="163"/>
-      <c r="I8" s="160" t="s">
+      <c r="F8" s="133"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="382"/>
+      <c r="I8" s="362" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="161"/>
-      <c r="K8" s="161"/>
-      <c r="L8" s="161"/>
-      <c r="M8" s="164"/>
+      <c r="J8" s="363"/>
+      <c r="K8" s="363"/>
+      <c r="L8" s="363"/>
+      <c r="M8" s="364"/>
     </row>
     <row r="9" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="160" t="s">
+      <c r="A9" s="362" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="161"/>
-      <c r="C9" s="161"/>
-      <c r="D9" s="161"/>
-      <c r="E9" s="161"/>
-      <c r="F9" s="161"/>
-      <c r="G9" s="161"/>
-      <c r="H9" s="164"/>
-      <c r="I9" s="57" t="s">
+      <c r="B9" s="363"/>
+      <c r="C9" s="363"/>
+      <c r="D9" s="363"/>
+      <c r="E9" s="363"/>
+      <c r="F9" s="363"/>
+      <c r="G9" s="363"/>
+      <c r="H9" s="364"/>
+      <c r="I9" s="383" t="s">
         <v>74</v>
       </c>
-      <c r="J9" s="58"/>
-      <c r="K9" s="58">
+      <c r="J9" s="384"/>
+      <c r="K9" s="384">
         <f>ADDRESS!I3</f>
         <v>10285609</v>
       </c>
-      <c r="L9" s="58"/>
-      <c r="M9" s="13"/>
+      <c r="L9" s="384"/>
+      <c r="M9" s="374"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="160" t="s">
+      <c r="A10" s="362" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="161"/>
-      <c r="C10" s="161"/>
-      <c r="D10" s="161"/>
-      <c r="E10" s="161"/>
-      <c r="F10" s="161"/>
-      <c r="G10" s="161"/>
-      <c r="H10" s="164"/>
-      <c r="I10" s="59" t="s">
+      <c r="B10" s="363"/>
+      <c r="C10" s="363"/>
+      <c r="D10" s="363"/>
+      <c r="E10" s="363"/>
+      <c r="F10" s="363"/>
+      <c r="G10" s="363"/>
+      <c r="H10" s="364"/>
+      <c r="I10" s="385" t="s">
         <v>234</v>
       </c>
-      <c r="J10" s="60" t="str">
+      <c r="J10" s="386" t="str">
         <f>ADDRESS!I2</f>
         <v>RBTW</v>
       </c>
-      <c r="K10" s="60"/>
-      <c r="L10" s="60"/>
-      <c r="M10" s="61"/>
+      <c r="K10" s="386"/>
+      <c r="L10" s="386"/>
+      <c r="M10" s="387"/>
     </row>
     <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="154" t="s">
+      <c r="A11" s="371" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="155"/>
-      <c r="C11" s="155"/>
-      <c r="D11" s="155"/>
-      <c r="E11" s="155"/>
-      <c r="F11" s="156" t="s">
+      <c r="B11" s="372"/>
+      <c r="C11" s="372"/>
+      <c r="D11" s="372"/>
+      <c r="E11" s="372"/>
+      <c r="F11" s="373" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="156"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="62" t="s">
+      <c r="G11" s="373"/>
+      <c r="H11" s="374"/>
+      <c r="I11" s="388" t="s">
         <v>235</v>
       </c>
-      <c r="J11" s="63"/>
-      <c r="K11" s="63">
+      <c r="J11" s="389"/>
+      <c r="K11" s="389">
         <f>ADDRESS!I4</f>
         <v>523953410</v>
       </c>
-      <c r="L11" s="63"/>
-      <c r="M11" s="64"/>
+      <c r="L11" s="389"/>
+      <c r="M11" s="390"/>
     </row>
     <row r="12" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="140" t="s">
+      <c r="A12" s="104" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="141"/>
-      <c r="C12" s="141"/>
-      <c r="D12" s="141"/>
-      <c r="E12" s="141"/>
-      <c r="F12" s="141"/>
-      <c r="G12" s="141"/>
-      <c r="H12" s="142"/>
-      <c r="I12" s="131"/>
-      <c r="J12" s="132"/>
-      <c r="K12" s="132"/>
-      <c r="L12" s="132"/>
-      <c r="M12" s="133"/>
+      <c r="B12" s="105"/>
+      <c r="C12" s="105"/>
+      <c r="D12" s="105"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="106"/>
+      <c r="I12" s="368"/>
+      <c r="J12" s="369"/>
+      <c r="K12" s="369"/>
+      <c r="L12" s="369"/>
+      <c r="M12" s="370"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="157" t="s">
+      <c r="A13" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="158"/>
-      <c r="C13" s="158"/>
-      <c r="D13" s="158"/>
-      <c r="E13" s="158"/>
-      <c r="F13" s="158"/>
-      <c r="G13" s="158"/>
-      <c r="H13" s="159"/>
-      <c r="I13" s="131"/>
-      <c r="J13" s="132"/>
-      <c r="K13" s="132"/>
-      <c r="L13" s="132"/>
-      <c r="M13" s="133"/>
+      <c r="B13" s="113"/>
+      <c r="C13" s="113"/>
+      <c r="D13" s="113"/>
+      <c r="E13" s="113"/>
+      <c r="F13" s="113"/>
+      <c r="G13" s="113"/>
+      <c r="H13" s="114"/>
+      <c r="I13" s="368"/>
+      <c r="J13" s="369"/>
+      <c r="K13" s="369"/>
+      <c r="L13" s="369"/>
+      <c r="M13" s="370"/>
     </row>
     <row r="14" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="128" t="s">
+      <c r="A14" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="129"/>
-      <c r="C14" s="129"/>
-      <c r="D14" s="129"/>
-      <c r="E14" s="129"/>
-      <c r="F14" s="129"/>
-      <c r="G14" s="129"/>
-      <c r="H14" s="130"/>
-      <c r="I14" s="134"/>
-      <c r="J14" s="135"/>
-      <c r="K14" s="135"/>
-      <c r="L14" s="135"/>
-      <c r="M14" s="136"/>
+      <c r="B14" s="93"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="93"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="93"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="94"/>
+      <c r="I14" s="375"/>
+      <c r="J14" s="376"/>
+      <c r="K14" s="376"/>
+      <c r="L14" s="376"/>
+      <c r="M14" s="377"/>
     </row>
     <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="180" t="s">
+      <c r="A15" s="130" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="181"/>
-      <c r="C15" s="181"/>
-      <c r="D15" s="181"/>
-      <c r="E15" s="181"/>
-      <c r="F15" s="181"/>
-      <c r="G15" s="181"/>
-      <c r="H15" s="181"/>
-      <c r="I15" s="182" t="s">
+      <c r="B15" s="131"/>
+      <c r="C15" s="131"/>
+      <c r="D15" s="131"/>
+      <c r="E15" s="131"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="131"/>
+      <c r="H15" s="131"/>
+      <c r="I15" s="391" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="183"/>
-      <c r="K15" s="183"/>
-      <c r="L15" s="183"/>
-      <c r="M15" s="184"/>
+      <c r="J15" s="392"/>
+      <c r="K15" s="392"/>
+      <c r="L15" s="392"/>
+      <c r="M15" s="393"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="65" t="s">
+      <c r="A16" s="394" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="236">
+      <c r="B16" s="395"/>
+      <c r="C16" s="395"/>
+      <c r="D16" s="395"/>
+      <c r="E16" s="395"/>
+      <c r="F16" s="396">
         <f>ADDRESS!I5</f>
         <v>59642884</v>
       </c>
-      <c r="G16" s="236"/>
-      <c r="H16" s="237"/>
-      <c r="I16" s="185" t="s">
+      <c r="G16" s="396"/>
+      <c r="H16" s="397"/>
+      <c r="I16" s="398" t="s">
         <v>61</v>
       </c>
-      <c r="J16" s="186"/>
-      <c r="K16" s="186"/>
-      <c r="L16" s="186"/>
-      <c r="M16" s="187"/>
+      <c r="J16" s="399"/>
+      <c r="K16" s="399"/>
+      <c r="L16" s="399"/>
+      <c r="M16" s="400"/>
     </row>
     <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="67"/>
-      <c r="B17" s="68"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="68"/>
-      <c r="G17" s="68"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="188"/>
-      <c r="J17" s="189"/>
-      <c r="K17" s="190" t="s">
+      <c r="A17" s="401"/>
+      <c r="B17" s="402"/>
+      <c r="C17" s="402"/>
+      <c r="D17" s="402"/>
+      <c r="E17" s="402"/>
+      <c r="F17" s="402"/>
+      <c r="G17" s="402"/>
+      <c r="H17" s="403"/>
+      <c r="I17" s="132"/>
+      <c r="J17" s="133"/>
+      <c r="K17" s="134" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="190"/>
-      <c r="M17" s="191"/>
+      <c r="L17" s="134"/>
+      <c r="M17" s="135"/>
     </row>
     <row r="18" spans="1:13" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="67"/>
-      <c r="B18" s="68"/>
-      <c r="C18" s="68"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="68"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="194" t="s">
+      <c r="A18" s="401"/>
+      <c r="B18" s="402"/>
+      <c r="C18" s="402"/>
+      <c r="D18" s="402"/>
+      <c r="E18" s="402"/>
+      <c r="F18" s="402"/>
+      <c r="G18" s="402"/>
+      <c r="H18" s="403"/>
+      <c r="I18" s="138" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="195"/>
-      <c r="K18" s="192"/>
-      <c r="L18" s="192"/>
-      <c r="M18" s="193"/>
+      <c r="J18" s="139"/>
+      <c r="K18" s="136"/>
+      <c r="L18" s="136"/>
+      <c r="M18" s="137"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="165" t="s">
+      <c r="A19" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="166"/>
-      <c r="C19" s="166"/>
-      <c r="D19" s="166"/>
-      <c r="E19" s="166"/>
-      <c r="F19" s="166"/>
-      <c r="G19" s="166"/>
-      <c r="H19" s="166"/>
-      <c r="I19" s="166"/>
-      <c r="J19" s="166"/>
-      <c r="K19" s="166"/>
-      <c r="L19" s="166"/>
-      <c r="M19" s="167"/>
+      <c r="B19" s="116"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="116"/>
+      <c r="G19" s="116"/>
+      <c r="H19" s="116"/>
+      <c r="I19" s="116"/>
+      <c r="J19" s="116"/>
+      <c r="K19" s="116"/>
+      <c r="L19" s="116"/>
+      <c r="M19" s="117"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="168" t="s">
+      <c r="A20" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="169"/>
-      <c r="C20" s="169"/>
-      <c r="D20" s="169"/>
-      <c r="E20" s="169" t="s">
+      <c r="B20" s="119"/>
+      <c r="C20" s="119"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="169" t="s">
+      <c r="F20" s="119" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="169"/>
-      <c r="H20" s="170" t="s">
+      <c r="G20" s="119"/>
+      <c r="H20" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="171"/>
-      <c r="J20" s="172" t="s">
+      <c r="I20" s="121"/>
+      <c r="J20" s="122" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="173"/>
-      <c r="L20" s="173"/>
-      <c r="M20" s="174"/>
+      <c r="K20" s="123"/>
+      <c r="L20" s="123"/>
+      <c r="M20" s="124"/>
     </row>
     <row r="21" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="168"/>
-      <c r="B21" s="169"/>
-      <c r="C21" s="169"/>
-      <c r="D21" s="169"/>
-      <c r="E21" s="169"/>
-      <c r="F21" s="169"/>
-      <c r="G21" s="169"/>
-      <c r="H21" s="178" t="s">
+      <c r="A21" s="118"/>
+      <c r="B21" s="119"/>
+      <c r="C21" s="119"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="119"/>
+      <c r="F21" s="119"/>
+      <c r="G21" s="119"/>
+      <c r="H21" s="128" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="179"/>
-      <c r="J21" s="175"/>
-      <c r="K21" s="176"/>
-      <c r="L21" s="176"/>
-      <c r="M21" s="177"/>
+      <c r="I21" s="129"/>
+      <c r="J21" s="125"/>
+      <c r="K21" s="126"/>
+      <c r="L21" s="126"/>
+      <c r="M21" s="127"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="196"/>
-      <c r="B22" s="196"/>
-      <c r="C22" s="196"/>
-      <c r="D22" s="197"/>
-      <c r="E22" s="10">
+      <c r="A22" s="404"/>
+      <c r="B22" s="404"/>
+      <c r="C22" s="404"/>
+      <c r="D22" s="405"/>
+      <c r="E22" s="406">
         <v>40</v>
       </c>
-      <c r="F22" s="198">
+      <c r="F22" s="407">
         <v>40</v>
       </c>
-      <c r="G22" s="198"/>
-      <c r="H22" s="14" t="s">
+      <c r="G22" s="407"/>
+      <c r="H22" s="408" t="s">
         <v>54</v>
       </c>
-      <c r="I22" s="14" t="s">
+      <c r="I22" s="408" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="199"/>
-      <c r="K22" s="199"/>
-      <c r="L22" s="199"/>
-      <c r="M22" s="200"/>
+      <c r="J22" s="142"/>
+      <c r="K22" s="142"/>
+      <c r="L22" s="142"/>
+      <c r="M22" s="143"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="196"/>
-      <c r="B23" s="196"/>
-      <c r="C23" s="196"/>
-      <c r="D23" s="197"/>
-      <c r="E23" s="10">
+      <c r="A23" s="404"/>
+      <c r="B23" s="404"/>
+      <c r="C23" s="404"/>
+      <c r="D23" s="405"/>
+      <c r="E23" s="406">
         <v>38</v>
       </c>
-      <c r="F23" s="198">
+      <c r="F23" s="407">
         <v>38</v>
       </c>
-      <c r="G23" s="198"/>
-      <c r="H23" s="14" t="s">
+      <c r="G23" s="407"/>
+      <c r="H23" s="408" t="s">
         <v>54</v>
       </c>
-      <c r="I23" s="14" t="s">
+      <c r="I23" s="408" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="199"/>
-      <c r="K23" s="199"/>
-      <c r="L23" s="199"/>
-      <c r="M23" s="200"/>
+      <c r="J23" s="142"/>
+      <c r="K23" s="142"/>
+      <c r="L23" s="142"/>
+      <c r="M23" s="143"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="196"/>
-      <c r="B24" s="196"/>
-      <c r="C24" s="196"/>
-      <c r="D24" s="197"/>
-      <c r="E24" s="10">
+      <c r="A24" s="404"/>
+      <c r="B24" s="404"/>
+      <c r="C24" s="404"/>
+      <c r="D24" s="405"/>
+      <c r="E24" s="406">
         <v>59</v>
       </c>
-      <c r="F24" s="198">
+      <c r="F24" s="407">
         <v>59</v>
       </c>
-      <c r="G24" s="198"/>
-      <c r="H24" s="14" t="s">
+      <c r="G24" s="407"/>
+      <c r="H24" s="408" t="s">
         <v>54</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="I24" s="408" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="199"/>
-      <c r="K24" s="199"/>
-      <c r="L24" s="199"/>
-      <c r="M24" s="200"/>
+      <c r="J24" s="142"/>
+      <c r="K24" s="142"/>
+      <c r="L24" s="142"/>
+      <c r="M24" s="143"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="196"/>
-      <c r="B25" s="196"/>
-      <c r="C25" s="196"/>
-      <c r="D25" s="197"/>
-      <c r="E25" s="10">
+      <c r="A25" s="404"/>
+      <c r="B25" s="404"/>
+      <c r="C25" s="404"/>
+      <c r="D25" s="405"/>
+      <c r="E25" s="406">
         <v>81</v>
       </c>
-      <c r="F25" s="198">
+      <c r="F25" s="407">
         <v>81</v>
       </c>
-      <c r="G25" s="198"/>
-      <c r="H25" s="14" t="s">
+      <c r="G25" s="407"/>
+      <c r="H25" s="408" t="s">
         <v>54</v>
       </c>
-      <c r="I25" s="14" t="s">
+      <c r="I25" s="408" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="199"/>
-      <c r="K25" s="199"/>
-      <c r="L25" s="199"/>
-      <c r="M25" s="200"/>
+      <c r="J25" s="142"/>
+      <c r="K25" s="142"/>
+      <c r="L25" s="142"/>
+      <c r="M25" s="143"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="196"/>
-      <c r="B26" s="196"/>
-      <c r="C26" s="196"/>
-      <c r="D26" s="197"/>
-      <c r="E26" s="10">
+      <c r="A26" s="404"/>
+      <c r="B26" s="404"/>
+      <c r="C26" s="404"/>
+      <c r="D26" s="405"/>
+      <c r="E26" s="406">
         <v>70</v>
       </c>
-      <c r="F26" s="198">
+      <c r="F26" s="407">
         <v>70</v>
       </c>
-      <c r="G26" s="198"/>
-      <c r="H26" s="14" t="s">
+      <c r="G26" s="407"/>
+      <c r="H26" s="408" t="s">
         <v>54</v>
       </c>
-      <c r="I26" s="14" t="s">
+      <c r="I26" s="408" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="199"/>
-      <c r="K26" s="199"/>
-      <c r="L26" s="199"/>
-      <c r="M26" s="200"/>
+      <c r="J26" s="142"/>
+      <c r="K26" s="142"/>
+      <c r="L26" s="142"/>
+      <c r="M26" s="143"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="196"/>
-      <c r="B27" s="196"/>
-      <c r="C27" s="196"/>
-      <c r="D27" s="197"/>
-      <c r="E27" s="10">
+      <c r="A27" s="404"/>
+      <c r="B27" s="404"/>
+      <c r="C27" s="404"/>
+      <c r="D27" s="405"/>
+      <c r="E27" s="406">
         <v>62</v>
       </c>
-      <c r="F27" s="198">
+      <c r="F27" s="407">
         <v>62</v>
       </c>
-      <c r="G27" s="198"/>
-      <c r="H27" s="14" t="s">
+      <c r="G27" s="407"/>
+      <c r="H27" s="408" t="s">
         <v>54</v>
       </c>
-      <c r="I27" s="14" t="s">
+      <c r="I27" s="408" t="s">
         <v>55</v>
       </c>
-      <c r="J27" s="199"/>
-      <c r="K27" s="199"/>
-      <c r="L27" s="199"/>
-      <c r="M27" s="200"/>
+      <c r="J27" s="142"/>
+      <c r="K27" s="142"/>
+      <c r="L27" s="142"/>
+      <c r="M27" s="143"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="196"/>
-      <c r="B28" s="196"/>
-      <c r="C28" s="196"/>
-      <c r="D28" s="197"/>
-      <c r="E28" s="10">
+      <c r="A28" s="404"/>
+      <c r="B28" s="404"/>
+      <c r="C28" s="404"/>
+      <c r="D28" s="405"/>
+      <c r="E28" s="406">
         <v>66</v>
       </c>
-      <c r="F28" s="198">
+      <c r="F28" s="407">
         <v>66</v>
       </c>
-      <c r="G28" s="198"/>
-      <c r="H28" s="14" t="s">
+      <c r="G28" s="407"/>
+      <c r="H28" s="408" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="14" t="s">
+      <c r="I28" s="408" t="s">
         <v>55</v>
       </c>
-      <c r="J28" s="199"/>
-      <c r="K28" s="199"/>
-      <c r="L28" s="199"/>
-      <c r="M28" s="200"/>
+      <c r="J28" s="142"/>
+      <c r="K28" s="142"/>
+      <c r="L28" s="142"/>
+      <c r="M28" s="143"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="196"/>
-      <c r="B29" s="196"/>
-      <c r="C29" s="196"/>
-      <c r="D29" s="197"/>
-      <c r="E29" s="10">
+      <c r="A29" s="404"/>
+      <c r="B29" s="404"/>
+      <c r="C29" s="404"/>
+      <c r="D29" s="405"/>
+      <c r="E29" s="406">
         <v>65</v>
       </c>
-      <c r="F29" s="198">
+      <c r="F29" s="407">
         <v>65</v>
       </c>
-      <c r="G29" s="198"/>
-      <c r="H29" s="14" t="s">
+      <c r="G29" s="407"/>
+      <c r="H29" s="408" t="s">
         <v>54</v>
       </c>
-      <c r="I29" s="14" t="s">
+      <c r="I29" s="408" t="s">
         <v>55</v>
       </c>
-      <c r="J29" s="199"/>
-      <c r="K29" s="199"/>
-      <c r="L29" s="199"/>
-      <c r="M29" s="200"/>
+      <c r="J29" s="142"/>
+      <c r="K29" s="142"/>
+      <c r="L29" s="142"/>
+      <c r="M29" s="143"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="206" t="s">
+      <c r="A30" s="146" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="207"/>
-      <c r="C30" s="207"/>
-      <c r="D30" s="207"/>
-      <c r="E30" s="16">
+      <c r="B30" s="147"/>
+      <c r="C30" s="147"/>
+      <c r="D30" s="147"/>
+      <c r="E30" s="15">
         <f>SUM(E22:E29,'Supplimental Master BOL'!E5:E25)</f>
         <v>1688</v>
       </c>
-      <c r="F30" s="208">
+      <c r="F30" s="148">
         <f>SUM(F22:G29,'Supplimental Master BOL'!F5:G25)</f>
         <v>1688</v>
       </c>
-      <c r="G30" s="199"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="209"/>
-      <c r="K30" s="209"/>
-      <c r="L30" s="209"/>
-      <c r="M30" s="210"/>
+      <c r="G30" s="142"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="149"/>
+      <c r="K30" s="149"/>
+      <c r="L30" s="149"/>
+      <c r="M30" s="150"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="165" t="s">
+      <c r="A31" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="166"/>
-      <c r="C31" s="166"/>
-      <c r="D31" s="166"/>
-      <c r="E31" s="166"/>
-      <c r="F31" s="166"/>
-      <c r="G31" s="166"/>
-      <c r="H31" s="166"/>
-      <c r="I31" s="166"/>
-      <c r="J31" s="166"/>
-      <c r="K31" s="166"/>
-      <c r="L31" s="166"/>
-      <c r="M31" s="167"/>
+      <c r="B31" s="116"/>
+      <c r="C31" s="116"/>
+      <c r="D31" s="116"/>
+      <c r="E31" s="116"/>
+      <c r="F31" s="116"/>
+      <c r="G31" s="116"/>
+      <c r="H31" s="116"/>
+      <c r="I31" s="116"/>
+      <c r="J31" s="116"/>
+      <c r="K31" s="116"/>
+      <c r="L31" s="116"/>
+      <c r="M31" s="117"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="211" t="s">
+      <c r="A32" s="151" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="212"/>
-      <c r="C32" s="212" t="s">
+      <c r="B32" s="152"/>
+      <c r="C32" s="152" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="212"/>
-      <c r="E32" s="213" t="s">
+      <c r="D32" s="152"/>
+      <c r="E32" s="153" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="214" t="s">
+      <c r="F32" s="154" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="215" t="s">
+      <c r="G32" s="155" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="215"/>
-      <c r="I32" s="215"/>
-      <c r="J32" s="215"/>
-      <c r="K32" s="215"/>
-      <c r="L32" s="212" t="s">
+      <c r="H32" s="155"/>
+      <c r="I32" s="155"/>
+      <c r="J32" s="155"/>
+      <c r="K32" s="155"/>
+      <c r="L32" s="152" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="216"/>
+      <c r="M32" s="156"/>
     </row>
     <row r="33" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="B33" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D33" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="213"/>
-      <c r="F33" s="214"/>
-      <c r="G33" s="201" t="s">
+      <c r="E33" s="153"/>
+      <c r="F33" s="154"/>
+      <c r="G33" s="144" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="201"/>
-      <c r="I33" s="201"/>
-      <c r="J33" s="201"/>
-      <c r="K33" s="201"/>
-      <c r="L33" s="20" t="s">
+      <c r="H33" s="144"/>
+      <c r="I33" s="144"/>
+      <c r="J33" s="144"/>
+      <c r="K33" s="144"/>
+      <c r="L33" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="M33" s="21" t="s">
+      <c r="M33" s="20" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="22">
+      <c r="A34" s="411">
         <v>6</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="408" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="23">
+      <c r="C34" s="409">
         <v>1688</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="408" t="s">
         <v>60</v>
       </c>
-      <c r="E34" s="23">
+      <c r="E34" s="409">
         <v>6698</v>
       </c>
-      <c r="F34" s="14"/>
-      <c r="G34" s="202" t="s">
+      <c r="F34" s="408"/>
+      <c r="G34" s="412" t="s">
         <v>70</v>
       </c>
-      <c r="H34" s="203"/>
-      <c r="I34" s="203"/>
-      <c r="J34" s="203"/>
-      <c r="K34" s="204"/>
-      <c r="L34" s="24"/>
-      <c r="M34" s="25"/>
+      <c r="H34" s="413"/>
+      <c r="I34" s="413"/>
+      <c r="J34" s="413"/>
+      <c r="K34" s="414"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="23"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" s="22"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="202"/>
-      <c r="H35" s="203"/>
-      <c r="I35" s="203"/>
-      <c r="J35" s="203"/>
-      <c r="K35" s="204"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="25"/>
+      <c r="A35" s="411"/>
+      <c r="B35" s="408"/>
+      <c r="C35" s="408"/>
+      <c r="D35" s="408"/>
+      <c r="E35" s="408"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="412"/>
+      <c r="H35" s="413"/>
+      <c r="I35" s="413"/>
+      <c r="J35" s="413"/>
+      <c r="K35" s="414"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="23"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" s="22"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="202"/>
-      <c r="H36" s="203"/>
-      <c r="I36" s="203"/>
-      <c r="J36" s="203"/>
-      <c r="K36" s="204"/>
-      <c r="L36" s="24"/>
-      <c r="M36" s="25"/>
+      <c r="A36" s="411"/>
+      <c r="B36" s="408"/>
+      <c r="C36" s="408"/>
+      <c r="D36" s="408"/>
+      <c r="E36" s="408"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="412"/>
+      <c r="H36" s="413"/>
+      <c r="I36" s="413"/>
+      <c r="J36" s="413"/>
+      <c r="K36" s="414"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="23"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A37" s="22"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="202"/>
-      <c r="H37" s="203"/>
-      <c r="I37" s="203"/>
-      <c r="J37" s="203"/>
-      <c r="K37" s="204"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="25"/>
-      <c r="Q37" s="205"/>
-      <c r="R37" s="205"/>
-      <c r="S37" s="27"/>
-      <c r="T37" s="229"/>
-      <c r="U37" s="229"/>
-      <c r="V37" s="229"/>
+      <c r="A37" s="411"/>
+      <c r="B37" s="408"/>
+      <c r="C37" s="408"/>
+      <c r="D37" s="408"/>
+      <c r="E37" s="408"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="412"/>
+      <c r="H37" s="413"/>
+      <c r="I37" s="413"/>
+      <c r="J37" s="413"/>
+      <c r="K37" s="414"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="23"/>
+      <c r="Q37" s="145"/>
+      <c r="R37" s="145"/>
+      <c r="S37" s="24"/>
+      <c r="T37" s="169"/>
+      <c r="U37" s="169"/>
+      <c r="V37" s="169"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A38" s="22"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="202"/>
-      <c r="H38" s="203"/>
-      <c r="I38" s="203"/>
-      <c r="J38" s="203"/>
-      <c r="K38" s="204"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="29"/>
-      <c r="Q38" s="205"/>
-      <c r="R38" s="205"/>
-      <c r="S38" s="27"/>
-      <c r="T38" s="229"/>
-      <c r="U38" s="229"/>
-      <c r="V38" s="229"/>
+      <c r="A38" s="411"/>
+      <c r="B38" s="408"/>
+      <c r="C38" s="408"/>
+      <c r="D38" s="408"/>
+      <c r="E38" s="408"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="412"/>
+      <c r="H38" s="413"/>
+      <c r="I38" s="413"/>
+      <c r="J38" s="413"/>
+      <c r="K38" s="414"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="26"/>
+      <c r="Q38" s="145"/>
+      <c r="R38" s="145"/>
+      <c r="S38" s="24"/>
+      <c r="T38" s="169"/>
+      <c r="U38" s="169"/>
+      <c r="V38" s="169"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A39" s="22"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="202"/>
-      <c r="H39" s="203"/>
-      <c r="I39" s="203"/>
-      <c r="J39" s="203"/>
-      <c r="K39" s="204"/>
-      <c r="L39" s="24"/>
-      <c r="M39" s="29"/>
-      <c r="Q39" s="30"/>
-      <c r="R39" s="30"/>
-      <c r="S39" s="230"/>
-      <c r="T39" s="229"/>
-      <c r="U39" s="229"/>
-      <c r="V39" s="229"/>
+      <c r="A39" s="411"/>
+      <c r="B39" s="408"/>
+      <c r="C39" s="408"/>
+      <c r="D39" s="408"/>
+      <c r="E39" s="408"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="412"/>
+      <c r="H39" s="413"/>
+      <c r="I39" s="413"/>
+      <c r="J39" s="413"/>
+      <c r="K39" s="414"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="26"/>
+      <c r="Q39" s="27"/>
+      <c r="R39" s="27"/>
+      <c r="S39" s="170"/>
+      <c r="T39" s="169"/>
+      <c r="U39" s="169"/>
+      <c r="V39" s="169"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A40" s="22"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="202"/>
-      <c r="H40" s="203"/>
-      <c r="I40" s="203"/>
-      <c r="J40" s="203"/>
-      <c r="K40" s="204"/>
-      <c r="L40" s="24"/>
-      <c r="M40" s="25"/>
-      <c r="Q40" s="30"/>
-      <c r="R40" s="30"/>
-      <c r="S40" s="230"/>
-      <c r="T40" s="229"/>
-      <c r="U40" s="229"/>
-      <c r="V40" s="229"/>
+      <c r="A40" s="411"/>
+      <c r="B40" s="408"/>
+      <c r="C40" s="408"/>
+      <c r="D40" s="408"/>
+      <c r="E40" s="408"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="412"/>
+      <c r="H40" s="413"/>
+      <c r="I40" s="413"/>
+      <c r="J40" s="413"/>
+      <c r="K40" s="414"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="23"/>
+      <c r="Q40" s="27"/>
+      <c r="R40" s="27"/>
+      <c r="S40" s="170"/>
+      <c r="T40" s="169"/>
+      <c r="U40" s="169"/>
+      <c r="V40" s="169"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A41" s="22"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="202"/>
-      <c r="H41" s="203"/>
-      <c r="I41" s="203"/>
-      <c r="J41" s="203"/>
-      <c r="K41" s="204"/>
-      <c r="L41" s="24"/>
-      <c r="M41" s="25"/>
+      <c r="A41" s="411"/>
+      <c r="B41" s="408"/>
+      <c r="C41" s="408"/>
+      <c r="D41" s="408"/>
+      <c r="E41" s="408"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="412"/>
+      <c r="H41" s="413"/>
+      <c r="I41" s="413"/>
+      <c r="J41" s="413"/>
+      <c r="K41" s="414"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="23"/>
     </row>
     <row r="42" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="31">
+      <c r="A42" s="415">
         <v>6</v>
       </c>
-      <c r="B42" s="32"/>
-      <c r="C42" s="33">
+      <c r="B42" s="416"/>
+      <c r="C42" s="417">
         <v>1688</v>
       </c>
-      <c r="D42" s="32"/>
-      <c r="E42" s="33">
+      <c r="D42" s="416"/>
+      <c r="E42" s="417">
         <v>1688</v>
       </c>
-      <c r="F42" s="34"/>
-      <c r="G42" s="275" t="s">
+      <c r="F42" s="28"/>
+      <c r="G42" s="418" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="276"/>
-      <c r="I42" s="276"/>
-      <c r="J42" s="276"/>
-      <c r="K42" s="277"/>
-      <c r="L42" s="35"/>
-      <c r="M42" s="36"/>
+      <c r="H42" s="419"/>
+      <c r="I42" s="419"/>
+      <c r="J42" s="419"/>
+      <c r="K42" s="420"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="29"/>
     </row>
     <row r="43" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="252" t="s">
+      <c r="A43" s="174" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="253"/>
-      <c r="C43" s="253"/>
-      <c r="D43" s="253"/>
-      <c r="E43" s="253"/>
-      <c r="F43" s="253"/>
-      <c r="G43" s="253"/>
-      <c r="H43" s="254"/>
-      <c r="I43" s="278" t="s">
+      <c r="B43" s="175"/>
+      <c r="C43" s="175"/>
+      <c r="D43" s="175"/>
+      <c r="E43" s="175"/>
+      <c r="F43" s="175"/>
+      <c r="G43" s="175"/>
+      <c r="H43" s="176"/>
+      <c r="I43" s="192" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="279"/>
-      <c r="K43" s="279"/>
-      <c r="L43" s="279"/>
-      <c r="M43" s="280"/>
+      <c r="J43" s="193"/>
+      <c r="K43" s="193"/>
+      <c r="L43" s="193"/>
+      <c r="M43" s="194"/>
     </row>
     <row r="44" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="255"/>
-      <c r="B44" s="256"/>
-      <c r="C44" s="256"/>
-      <c r="D44" s="256"/>
-      <c r="E44" s="256"/>
-      <c r="F44" s="256"/>
-      <c r="G44" s="256"/>
-      <c r="H44" s="257"/>
-      <c r="I44" s="281"/>
-      <c r="J44" s="282"/>
-      <c r="K44" s="282"/>
-      <c r="L44" s="282"/>
-      <c r="M44" s="283"/>
+      <c r="A44" s="177"/>
+      <c r="B44" s="178"/>
+      <c r="C44" s="178"/>
+      <c r="D44" s="178"/>
+      <c r="E44" s="178"/>
+      <c r="F44" s="178"/>
+      <c r="G44" s="178"/>
+      <c r="H44" s="179"/>
+      <c r="I44" s="195"/>
+      <c r="J44" s="196"/>
+      <c r="K44" s="196"/>
+      <c r="L44" s="196"/>
+      <c r="M44" s="197"/>
     </row>
     <row r="45" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="217" t="s">
+      <c r="A45" s="157" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="218"/>
-      <c r="C45" s="218"/>
-      <c r="D45" s="218"/>
-      <c r="E45" s="218"/>
-      <c r="F45" s="218"/>
-      <c r="G45" s="218"/>
-      <c r="H45" s="219"/>
-      <c r="I45" s="220" t="s">
+      <c r="B45" s="158"/>
+      <c r="C45" s="158"/>
+      <c r="D45" s="158"/>
+      <c r="E45" s="158"/>
+      <c r="F45" s="158"/>
+      <c r="G45" s="158"/>
+      <c r="H45" s="159"/>
+      <c r="I45" s="160" t="s">
         <v>36</v>
       </c>
-      <c r="J45" s="221"/>
-      <c r="K45" s="221"/>
-      <c r="L45" s="221"/>
-      <c r="M45" s="222"/>
+      <c r="J45" s="161"/>
+      <c r="K45" s="161"/>
+      <c r="L45" s="161"/>
+      <c r="M45" s="162"/>
     </row>
     <row r="46" spans="1:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="217" t="s">
+      <c r="A46" s="157" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="218"/>
-      <c r="C46" s="218"/>
-      <c r="D46" s="218"/>
-      <c r="E46" s="218"/>
-      <c r="F46" s="218"/>
-      <c r="G46" s="218"/>
-      <c r="H46" s="219"/>
-      <c r="I46" s="220"/>
-      <c r="J46" s="221"/>
-      <c r="K46" s="221"/>
-      <c r="L46" s="221"/>
-      <c r="M46" s="222"/>
+      <c r="B46" s="158"/>
+      <c r="C46" s="158"/>
+      <c r="D46" s="158"/>
+      <c r="E46" s="158"/>
+      <c r="F46" s="158"/>
+      <c r="G46" s="158"/>
+      <c r="H46" s="159"/>
+      <c r="I46" s="160"/>
+      <c r="J46" s="161"/>
+      <c r="K46" s="161"/>
+      <c r="L46" s="161"/>
+      <c r="M46" s="162"/>
     </row>
     <row r="47" spans="1:22" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="223"/>
-      <c r="B47" s="224"/>
-      <c r="C47" s="224"/>
-      <c r="D47" s="224"/>
-      <c r="E47" s="224"/>
-      <c r="F47" s="224"/>
-      <c r="G47" s="224"/>
-      <c r="H47" s="225"/>
-      <c r="I47" s="226" t="s">
+      <c r="A47" s="163"/>
+      <c r="B47" s="164"/>
+      <c r="C47" s="164"/>
+      <c r="D47" s="164"/>
+      <c r="E47" s="164"/>
+      <c r="F47" s="164"/>
+      <c r="G47" s="164"/>
+      <c r="H47" s="165"/>
+      <c r="I47" s="166" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="227"/>
-      <c r="K47" s="227"/>
-      <c r="L47" s="227"/>
-      <c r="M47" s="228"/>
+      <c r="J47" s="167"/>
+      <c r="K47" s="167"/>
+      <c r="L47" s="167"/>
+      <c r="M47" s="168"/>
     </row>
     <row r="48" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="249" t="s">
+      <c r="A48" s="171" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="250"/>
-      <c r="C48" s="250"/>
-      <c r="D48" s="250"/>
-      <c r="E48" s="250"/>
-      <c r="F48" s="250"/>
-      <c r="G48" s="250"/>
-      <c r="H48" s="250"/>
-      <c r="I48" s="250"/>
-      <c r="J48" s="250"/>
-      <c r="K48" s="250"/>
-      <c r="L48" s="250"/>
-      <c r="M48" s="251"/>
+      <c r="B48" s="172"/>
+      <c r="C48" s="172"/>
+      <c r="D48" s="172"/>
+      <c r="E48" s="172"/>
+      <c r="F48" s="172"/>
+      <c r="G48" s="172"/>
+      <c r="H48" s="172"/>
+      <c r="I48" s="172"/>
+      <c r="J48" s="172"/>
+      <c r="K48" s="172"/>
+      <c r="L48" s="172"/>
+      <c r="M48" s="173"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="252" t="s">
+      <c r="A49" s="174" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="253"/>
-      <c r="C49" s="253"/>
-      <c r="D49" s="253"/>
-      <c r="E49" s="253"/>
-      <c r="F49" s="253"/>
-      <c r="G49" s="253"/>
-      <c r="H49" s="254"/>
-      <c r="I49" s="260" t="s">
+      <c r="B49" s="175"/>
+      <c r="C49" s="175"/>
+      <c r="D49" s="175"/>
+      <c r="E49" s="175"/>
+      <c r="F49" s="175"/>
+      <c r="G49" s="175"/>
+      <c r="H49" s="176"/>
+      <c r="I49" s="182" t="s">
         <v>40</v>
       </c>
-      <c r="J49" s="261"/>
-      <c r="K49" s="261"/>
-      <c r="L49" s="261"/>
-      <c r="M49" s="262"/>
+      <c r="J49" s="183"/>
+      <c r="K49" s="183"/>
+      <c r="L49" s="183"/>
+      <c r="M49" s="184"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="255"/>
-      <c r="B50" s="256"/>
-      <c r="C50" s="256"/>
-      <c r="D50" s="256"/>
-      <c r="E50" s="256"/>
-      <c r="F50" s="256"/>
-      <c r="G50" s="256"/>
-      <c r="H50" s="257"/>
-      <c r="I50" s="263"/>
-      <c r="J50" s="264"/>
-      <c r="K50" s="264"/>
-      <c r="L50" s="264"/>
-      <c r="M50" s="265"/>
+      <c r="A50" s="177"/>
+      <c r="B50" s="178"/>
+      <c r="C50" s="178"/>
+      <c r="D50" s="178"/>
+      <c r="E50" s="178"/>
+      <c r="F50" s="178"/>
+      <c r="G50" s="178"/>
+      <c r="H50" s="179"/>
+      <c r="I50" s="185"/>
+      <c r="J50" s="186"/>
+      <c r="K50" s="186"/>
+      <c r="L50" s="186"/>
+      <c r="M50" s="187"/>
     </row>
     <row r="51" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="258"/>
-      <c r="B51" s="259"/>
-      <c r="C51" s="259"/>
-      <c r="D51" s="259"/>
-      <c r="E51" s="256"/>
-      <c r="F51" s="256"/>
-      <c r="G51" s="256"/>
-      <c r="H51" s="257"/>
-      <c r="I51" s="266" t="s">
+      <c r="A51" s="180"/>
+      <c r="B51" s="181"/>
+      <c r="C51" s="181"/>
+      <c r="D51" s="181"/>
+      <c r="E51" s="178"/>
+      <c r="F51" s="178"/>
+      <c r="G51" s="178"/>
+      <c r="H51" s="179"/>
+      <c r="I51" s="188" t="s">
         <v>41</v>
       </c>
-      <c r="J51" s="267"/>
-      <c r="K51" s="268"/>
-      <c r="L51" s="268"/>
-      <c r="M51" s="269"/>
+      <c r="J51" s="189"/>
+      <c r="K51" s="190"/>
+      <c r="L51" s="190"/>
+      <c r="M51" s="191"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="270" t="s">
+      <c r="A52" s="171" t="s">
         <v>42</v>
       </c>
-      <c r="B52" s="271"/>
-      <c r="C52" s="271"/>
-      <c r="D52" s="271"/>
-      <c r="E52" s="37" t="s">
+      <c r="B52" s="172"/>
+      <c r="C52" s="172"/>
+      <c r="D52" s="172"/>
+      <c r="E52" s="421" t="s">
         <v>44</v>
       </c>
-      <c r="F52" s="38"/>
-      <c r="G52" s="272" t="s">
+      <c r="F52" s="422"/>
+      <c r="G52" s="423" t="s">
         <v>45</v>
       </c>
-      <c r="H52" s="272"/>
-      <c r="I52" s="272"/>
-      <c r="J52" s="273"/>
-      <c r="K52" s="271" t="s">
+      <c r="H52" s="423"/>
+      <c r="I52" s="423"/>
+      <c r="J52" s="424"/>
+      <c r="K52" s="172" t="s">
         <v>50</v>
       </c>
-      <c r="L52" s="271"/>
-      <c r="M52" s="274"/>
+      <c r="L52" s="172"/>
+      <c r="M52" s="173"/>
     </row>
     <row r="53" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="238" t="s">
+      <c r="A53" s="425" t="s">
         <v>43</v>
       </c>
-      <c r="B53" s="239"/>
-      <c r="C53" s="239"/>
-      <c r="D53" s="239"/>
-      <c r="E53" s="39"/>
-      <c r="F53" s="40"/>
-      <c r="G53" s="40"/>
-      <c r="H53" s="40"/>
-      <c r="I53" s="40"/>
-      <c r="J53" s="41"/>
-      <c r="K53" s="239" t="s">
+      <c r="B53" s="426"/>
+      <c r="C53" s="426"/>
+      <c r="D53" s="426"/>
+      <c r="E53" s="427"/>
+      <c r="F53" s="410"/>
+      <c r="G53" s="410"/>
+      <c r="H53" s="410"/>
+      <c r="I53" s="410"/>
+      <c r="J53" s="428"/>
+      <c r="K53" s="426" t="s">
         <v>52</v>
       </c>
-      <c r="L53" s="239"/>
-      <c r="M53" s="240"/>
+      <c r="L53" s="426"/>
+      <c r="M53" s="429"/>
     </row>
     <row r="54" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="238"/>
-      <c r="B54" s="239"/>
-      <c r="C54" s="239"/>
-      <c r="D54" s="239"/>
-      <c r="E54" s="241" t="s">
+      <c r="A54" s="425"/>
+      <c r="B54" s="426"/>
+      <c r="C54" s="426"/>
+      <c r="D54" s="426"/>
+      <c r="E54" s="430" t="s">
         <v>46</v>
       </c>
-      <c r="F54" s="242"/>
-      <c r="G54" s="42"/>
-      <c r="H54" s="231" t="s">
+      <c r="F54" s="431"/>
+      <c r="G54" s="432"/>
+      <c r="H54" s="433" t="s">
         <v>46</v>
       </c>
-      <c r="I54" s="231"/>
-      <c r="J54" s="232"/>
-      <c r="K54" s="239"/>
-      <c r="L54" s="239"/>
-      <c r="M54" s="240"/>
+      <c r="I54" s="433"/>
+      <c r="J54" s="434"/>
+      <c r="K54" s="426"/>
+      <c r="L54" s="426"/>
+      <c r="M54" s="429"/>
     </row>
     <row r="55" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="238"/>
-      <c r="B55" s="239"/>
-      <c r="C55" s="239"/>
-      <c r="D55" s="239"/>
-      <c r="E55" s="241" t="s">
+      <c r="A55" s="425"/>
+      <c r="B55" s="426"/>
+      <c r="C55" s="426"/>
+      <c r="D55" s="426"/>
+      <c r="E55" s="430" t="s">
         <v>47</v>
       </c>
-      <c r="F55" s="242"/>
-      <c r="G55" s="242"/>
-      <c r="H55" s="231" t="s">
+      <c r="F55" s="431"/>
+      <c r="G55" s="431"/>
+      <c r="H55" s="433" t="s">
         <v>48</v>
       </c>
-      <c r="I55" s="231"/>
-      <c r="J55" s="232"/>
-      <c r="K55" s="239"/>
-      <c r="L55" s="239"/>
-      <c r="M55" s="240"/>
+      <c r="I55" s="433"/>
+      <c r="J55" s="434"/>
+      <c r="K55" s="426"/>
+      <c r="L55" s="426"/>
+      <c r="M55" s="429"/>
     </row>
     <row r="56" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="243"/>
-      <c r="B56" s="162"/>
-      <c r="C56" s="162"/>
-      <c r="D56" s="163"/>
-      <c r="E56" s="241"/>
-      <c r="F56" s="242"/>
-      <c r="G56" s="242"/>
-      <c r="H56" s="231"/>
-      <c r="I56" s="231"/>
-      <c r="J56" s="232"/>
-      <c r="K56" s="247" t="s">
+      <c r="A56" s="132"/>
+      <c r="B56" s="133"/>
+      <c r="C56" s="133"/>
+      <c r="D56" s="382"/>
+      <c r="E56" s="430"/>
+      <c r="F56" s="431"/>
+      <c r="G56" s="431"/>
+      <c r="H56" s="433"/>
+      <c r="I56" s="433"/>
+      <c r="J56" s="434"/>
+      <c r="K56" s="435" t="s">
         <v>51</v>
       </c>
-      <c r="L56" s="247"/>
-      <c r="M56" s="248"/>
+      <c r="L56" s="435"/>
+      <c r="M56" s="436"/>
     </row>
     <row r="57" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="243"/>
-      <c r="B57" s="162"/>
-      <c r="C57" s="162"/>
-      <c r="D57" s="163"/>
-      <c r="E57" s="241"/>
-      <c r="F57" s="242"/>
-      <c r="G57" s="42"/>
-      <c r="H57" s="231" t="s">
+      <c r="A57" s="132"/>
+      <c r="B57" s="133"/>
+      <c r="C57" s="133"/>
+      <c r="D57" s="382"/>
+      <c r="E57" s="430"/>
+      <c r="F57" s="431"/>
+      <c r="G57" s="432"/>
+      <c r="H57" s="433" t="s">
         <v>49</v>
       </c>
-      <c r="I57" s="231"/>
-      <c r="J57" s="232"/>
-      <c r="K57" s="43"/>
-      <c r="L57" s="44"/>
-      <c r="M57" s="45"/>
+      <c r="I57" s="433"/>
+      <c r="J57" s="434"/>
+      <c r="K57" s="437"/>
+      <c r="L57" s="438"/>
+      <c r="M57" s="439"/>
     </row>
     <row r="58" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="244"/>
-      <c r="B58" s="245"/>
-      <c r="C58" s="245"/>
-      <c r="D58" s="246"/>
-      <c r="E58" s="233"/>
-      <c r="F58" s="234"/>
-      <c r="G58" s="234"/>
-      <c r="H58" s="234"/>
-      <c r="I58" s="234"/>
-      <c r="J58" s="235"/>
-      <c r="K58" s="46"/>
-      <c r="L58" s="47"/>
-      <c r="M58" s="48"/>
+      <c r="A58" s="440"/>
+      <c r="B58" s="441"/>
+      <c r="C58" s="441"/>
+      <c r="D58" s="442"/>
+      <c r="E58" s="138"/>
+      <c r="F58" s="139"/>
+      <c r="G58" s="139"/>
+      <c r="H58" s="139"/>
+      <c r="I58" s="139"/>
+      <c r="J58" s="443"/>
+      <c r="K58" s="444"/>
+      <c r="L58" s="445"/>
+      <c r="M58" s="446"/>
     </row>
     <row r="59" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="49"/>
-      <c r="B59" s="49"/>
-      <c r="C59" s="49"/>
-      <c r="D59" s="49"/>
-      <c r="E59" s="30"/>
-      <c r="F59" s="30"/>
-      <c r="G59" s="30"/>
-      <c r="H59" s="28"/>
-      <c r="I59" s="28"/>
-      <c r="J59" s="28"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="30"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="25"/>
+      <c r="I59" s="25"/>
+      <c r="J59" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="112">
@@ -6976,1114 +6992,1114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="107" t="s">
         <v>237</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="145" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="109" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
-      <c r="L1" s="146" t="s">
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="110" t="s">
         <v>63</v>
       </c>
-      <c r="M1" s="147"/>
+      <c r="M1" s="111"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="165" t="s">
+      <c r="A2" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="166"/>
-      <c r="D2" s="166"/>
-      <c r="E2" s="166"/>
-      <c r="F2" s="166"/>
-      <c r="G2" s="166"/>
-      <c r="H2" s="166"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
-      <c r="L2" s="166"/>
-      <c r="M2" s="167"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="117"/>
     </row>
     <row r="3" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="168" t="s">
+      <c r="A3" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="169"/>
-      <c r="C3" s="169"/>
-      <c r="D3" s="169"/>
-      <c r="E3" s="169" t="s">
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="169" t="s">
+      <c r="F3" s="119" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="169"/>
-      <c r="H3" s="170" t="s">
+      <c r="G3" s="119"/>
+      <c r="H3" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="171"/>
-      <c r="J3" s="172" t="s">
+      <c r="I3" s="121"/>
+      <c r="J3" s="122" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="173"/>
-      <c r="L3" s="173"/>
-      <c r="M3" s="174"/>
+      <c r="K3" s="123"/>
+      <c r="L3" s="123"/>
+      <c r="M3" s="124"/>
     </row>
     <row r="4" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="168"/>
-      <c r="B4" s="169"/>
-      <c r="C4" s="169"/>
-      <c r="D4" s="169"/>
-      <c r="E4" s="169"/>
-      <c r="F4" s="169"/>
-      <c r="G4" s="169"/>
-      <c r="H4" s="178" t="s">
+      <c r="A4" s="118"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="128" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="179"/>
-      <c r="J4" s="175"/>
-      <c r="K4" s="176"/>
-      <c r="L4" s="176"/>
-      <c r="M4" s="177"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="126"/>
+      <c r="M4" s="127"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="284"/>
-      <c r="B5" s="196"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="196"/>
+      <c r="A5" s="198"/>
+      <c r="B5" s="140"/>
+      <c r="C5" s="140"/>
+      <c r="D5" s="140"/>
       <c r="E5" s="10">
         <v>61</v>
       </c>
-      <c r="F5" s="285">
+      <c r="F5" s="199">
         <v>61</v>
       </c>
-      <c r="G5" s="286"/>
-      <c r="H5" s="14" t="s">
+      <c r="G5" s="200"/>
+      <c r="H5" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J5" s="199"/>
-      <c r="K5" s="199"/>
-      <c r="L5" s="199"/>
-      <c r="M5" s="200"/>
+      <c r="J5" s="142"/>
+      <c r="K5" s="142"/>
+      <c r="L5" s="142"/>
+      <c r="M5" s="143"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="284"/>
-      <c r="B6" s="196"/>
-      <c r="C6" s="196"/>
-      <c r="D6" s="196"/>
+      <c r="A6" s="198"/>
+      <c r="B6" s="140"/>
+      <c r="C6" s="140"/>
+      <c r="D6" s="140"/>
       <c r="E6" s="10">
         <v>83</v>
       </c>
-      <c r="F6" s="285">
+      <c r="F6" s="199">
         <v>83</v>
       </c>
-      <c r="G6" s="286"/>
-      <c r="H6" s="14" t="s">
+      <c r="G6" s="200"/>
+      <c r="H6" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J6" s="199"/>
-      <c r="K6" s="199"/>
-      <c r="L6" s="199"/>
-      <c r="M6" s="200"/>
+      <c r="J6" s="142"/>
+      <c r="K6" s="142"/>
+      <c r="L6" s="142"/>
+      <c r="M6" s="143"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="284"/>
-      <c r="B7" s="196"/>
-      <c r="C7" s="196"/>
-      <c r="D7" s="196"/>
+      <c r="A7" s="198"/>
+      <c r="B7" s="140"/>
+      <c r="C7" s="140"/>
+      <c r="D7" s="140"/>
       <c r="E7" s="10">
         <v>70</v>
       </c>
-      <c r="F7" s="285">
+      <c r="F7" s="199">
         <v>70</v>
       </c>
-      <c r="G7" s="286"/>
-      <c r="H7" s="14" t="s">
+      <c r="G7" s="200"/>
+      <c r="H7" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J7" s="199"/>
-      <c r="K7" s="199"/>
-      <c r="L7" s="199"/>
-      <c r="M7" s="200"/>
+      <c r="J7" s="142"/>
+      <c r="K7" s="142"/>
+      <c r="L7" s="142"/>
+      <c r="M7" s="143"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="284"/>
-      <c r="B8" s="196"/>
-      <c r="C8" s="196"/>
-      <c r="D8" s="196"/>
+      <c r="A8" s="198"/>
+      <c r="B8" s="140"/>
+      <c r="C8" s="140"/>
+      <c r="D8" s="140"/>
       <c r="E8" s="10">
         <v>50</v>
       </c>
-      <c r="F8" s="285">
+      <c r="F8" s="199">
         <v>50</v>
       </c>
-      <c r="G8" s="286"/>
-      <c r="H8" s="14" t="s">
+      <c r="G8" s="200"/>
+      <c r="H8" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J8" s="199"/>
-      <c r="K8" s="199"/>
-      <c r="L8" s="199"/>
-      <c r="M8" s="200"/>
+      <c r="J8" s="142"/>
+      <c r="K8" s="142"/>
+      <c r="L8" s="142"/>
+      <c r="M8" s="143"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="284"/>
-      <c r="B9" s="196"/>
-      <c r="C9" s="196"/>
-      <c r="D9" s="196"/>
+      <c r="A9" s="198"/>
+      <c r="B9" s="140"/>
+      <c r="C9" s="140"/>
+      <c r="D9" s="140"/>
       <c r="E9" s="10">
         <v>70</v>
       </c>
-      <c r="F9" s="285">
+      <c r="F9" s="199">
         <v>70</v>
       </c>
-      <c r="G9" s="286"/>
-      <c r="H9" s="14" t="s">
+      <c r="G9" s="200"/>
+      <c r="H9" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J9" s="199"/>
-      <c r="K9" s="199"/>
-      <c r="L9" s="199"/>
-      <c r="M9" s="200"/>
+      <c r="J9" s="142"/>
+      <c r="K9" s="142"/>
+      <c r="L9" s="142"/>
+      <c r="M9" s="143"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="284"/>
-      <c r="B10" s="196"/>
-      <c r="C10" s="196"/>
-      <c r="D10" s="196"/>
+      <c r="A10" s="198"/>
+      <c r="B10" s="140"/>
+      <c r="C10" s="140"/>
+      <c r="D10" s="140"/>
       <c r="E10" s="10">
         <v>69</v>
       </c>
-      <c r="F10" s="285">
+      <c r="F10" s="199">
         <v>69</v>
       </c>
-      <c r="G10" s="286"/>
-      <c r="H10" s="14" t="s">
+      <c r="G10" s="200"/>
+      <c r="H10" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="199"/>
-      <c r="K10" s="199"/>
-      <c r="L10" s="199"/>
-      <c r="M10" s="200"/>
+      <c r="J10" s="142"/>
+      <c r="K10" s="142"/>
+      <c r="L10" s="142"/>
+      <c r="M10" s="143"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="284"/>
-      <c r="B11" s="196"/>
-      <c r="C11" s="196"/>
-      <c r="D11" s="196"/>
+      <c r="A11" s="198"/>
+      <c r="B11" s="140"/>
+      <c r="C11" s="140"/>
+      <c r="D11" s="140"/>
       <c r="E11" s="10">
         <v>54</v>
       </c>
-      <c r="F11" s="285">
+      <c r="F11" s="199">
         <v>54</v>
       </c>
-      <c r="G11" s="286"/>
-      <c r="H11" s="14" t="s">
+      <c r="G11" s="200"/>
+      <c r="H11" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J11" s="199"/>
-      <c r="K11" s="199"/>
-      <c r="L11" s="199"/>
-      <c r="M11" s="200"/>
+      <c r="J11" s="142"/>
+      <c r="K11" s="142"/>
+      <c r="L11" s="142"/>
+      <c r="M11" s="143"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="284"/>
-      <c r="B12" s="196"/>
-      <c r="C12" s="196"/>
-      <c r="D12" s="196"/>
+      <c r="A12" s="198"/>
+      <c r="B12" s="140"/>
+      <c r="C12" s="140"/>
+      <c r="D12" s="140"/>
       <c r="E12" s="10">
         <v>65</v>
       </c>
-      <c r="F12" s="285">
+      <c r="F12" s="199">
         <v>65</v>
       </c>
-      <c r="G12" s="286"/>
-      <c r="H12" s="14" t="s">
+      <c r="G12" s="200"/>
+      <c r="H12" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J12" s="199"/>
-      <c r="K12" s="199"/>
-      <c r="L12" s="199"/>
-      <c r="M12" s="200"/>
+      <c r="J12" s="142"/>
+      <c r="K12" s="142"/>
+      <c r="L12" s="142"/>
+      <c r="M12" s="143"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="284"/>
-      <c r="B13" s="196"/>
-      <c r="C13" s="196"/>
-      <c r="D13" s="196"/>
+      <c r="A13" s="198"/>
+      <c r="B13" s="140"/>
+      <c r="C13" s="140"/>
+      <c r="D13" s="140"/>
       <c r="E13" s="10">
         <v>65</v>
       </c>
-      <c r="F13" s="285">
+      <c r="F13" s="199">
         <v>65</v>
       </c>
-      <c r="G13" s="286"/>
-      <c r="H13" s="14" t="s">
+      <c r="G13" s="200"/>
+      <c r="H13" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J13" s="199"/>
-      <c r="K13" s="199"/>
-      <c r="L13" s="199"/>
-      <c r="M13" s="200"/>
+      <c r="J13" s="142"/>
+      <c r="K13" s="142"/>
+      <c r="L13" s="142"/>
+      <c r="M13" s="143"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="284"/>
-      <c r="B14" s="196"/>
-      <c r="C14" s="196"/>
-      <c r="D14" s="196"/>
+      <c r="A14" s="198"/>
+      <c r="B14" s="140"/>
+      <c r="C14" s="140"/>
+      <c r="D14" s="140"/>
       <c r="E14" s="10">
         <v>70</v>
       </c>
-      <c r="F14" s="285">
+      <c r="F14" s="199">
         <v>70</v>
       </c>
-      <c r="G14" s="286"/>
-      <c r="H14" s="14" t="s">
+      <c r="G14" s="200"/>
+      <c r="H14" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J14" s="199"/>
-      <c r="K14" s="199"/>
-      <c r="L14" s="199"/>
-      <c r="M14" s="200"/>
+      <c r="J14" s="142"/>
+      <c r="K14" s="142"/>
+      <c r="L14" s="142"/>
+      <c r="M14" s="143"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="284"/>
-      <c r="B15" s="196"/>
-      <c r="C15" s="196"/>
-      <c r="D15" s="196"/>
+      <c r="A15" s="198"/>
+      <c r="B15" s="140"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="140"/>
       <c r="E15" s="10">
         <v>55</v>
       </c>
-      <c r="F15" s="285">
+      <c r="F15" s="199">
         <v>55</v>
       </c>
-      <c r="G15" s="286"/>
-      <c r="H15" s="14" t="s">
+      <c r="G15" s="200"/>
+      <c r="H15" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J15" s="199"/>
-      <c r="K15" s="199"/>
-      <c r="L15" s="199"/>
-      <c r="M15" s="200"/>
+      <c r="J15" s="142"/>
+      <c r="K15" s="142"/>
+      <c r="L15" s="142"/>
+      <c r="M15" s="143"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="284"/>
-      <c r="B16" s="196"/>
-      <c r="C16" s="196"/>
-      <c r="D16" s="196"/>
+      <c r="A16" s="198"/>
+      <c r="B16" s="140"/>
+      <c r="C16" s="140"/>
+      <c r="D16" s="140"/>
       <c r="E16" s="10">
         <v>54</v>
       </c>
-      <c r="F16" s="285">
+      <c r="F16" s="199">
         <v>54</v>
       </c>
-      <c r="G16" s="286"/>
-      <c r="H16" s="14" t="s">
+      <c r="G16" s="200"/>
+      <c r="H16" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J16" s="199"/>
-      <c r="K16" s="199"/>
-      <c r="L16" s="199"/>
-      <c r="M16" s="200"/>
+      <c r="J16" s="142"/>
+      <c r="K16" s="142"/>
+      <c r="L16" s="142"/>
+      <c r="M16" s="143"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="284"/>
-      <c r="B17" s="196"/>
-      <c r="C17" s="196"/>
-      <c r="D17" s="196"/>
+      <c r="A17" s="198"/>
+      <c r="B17" s="140"/>
+      <c r="C17" s="140"/>
+      <c r="D17" s="140"/>
       <c r="E17" s="10">
         <v>76</v>
       </c>
-      <c r="F17" s="285">
+      <c r="F17" s="199">
         <v>76</v>
       </c>
-      <c r="G17" s="286"/>
-      <c r="H17" s="14" t="s">
+      <c r="G17" s="200"/>
+      <c r="H17" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I17" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J17" s="199"/>
-      <c r="K17" s="199"/>
-      <c r="L17" s="199"/>
-      <c r="M17" s="200"/>
+      <c r="J17" s="142"/>
+      <c r="K17" s="142"/>
+      <c r="L17" s="142"/>
+      <c r="M17" s="143"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="284"/>
-      <c r="B18" s="196"/>
-      <c r="C18" s="196"/>
-      <c r="D18" s="196"/>
+      <c r="A18" s="198"/>
+      <c r="B18" s="140"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="140"/>
       <c r="E18" s="10">
         <v>76</v>
       </c>
-      <c r="F18" s="285">
+      <c r="F18" s="199">
         <v>76</v>
       </c>
-      <c r="G18" s="286"/>
-      <c r="H18" s="14" t="s">
+      <c r="G18" s="200"/>
+      <c r="H18" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I18" s="14" t="s">
+      <c r="I18" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J18" s="199"/>
-      <c r="K18" s="199"/>
-      <c r="L18" s="199"/>
-      <c r="M18" s="200"/>
+      <c r="J18" s="142"/>
+      <c r="K18" s="142"/>
+      <c r="L18" s="142"/>
+      <c r="M18" s="143"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="284"/>
-      <c r="B19" s="196"/>
-      <c r="C19" s="196"/>
-      <c r="D19" s="196"/>
+      <c r="A19" s="198"/>
+      <c r="B19" s="140"/>
+      <c r="C19" s="140"/>
+      <c r="D19" s="140"/>
       <c r="E19" s="10">
         <v>65</v>
       </c>
-      <c r="F19" s="285">
+      <c r="F19" s="199">
         <v>65</v>
       </c>
-      <c r="G19" s="286"/>
-      <c r="H19" s="14" t="s">
+      <c r="G19" s="200"/>
+      <c r="H19" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I19" s="14" t="s">
+      <c r="I19" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J19" s="199"/>
-      <c r="K19" s="199"/>
-      <c r="L19" s="199"/>
-      <c r="M19" s="200"/>
+      <c r="J19" s="142"/>
+      <c r="K19" s="142"/>
+      <c r="L19" s="142"/>
+      <c r="M19" s="143"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="284"/>
-      <c r="B20" s="196"/>
-      <c r="C20" s="196"/>
-      <c r="D20" s="196"/>
+      <c r="A20" s="198"/>
+      <c r="B20" s="140"/>
+      <c r="C20" s="140"/>
+      <c r="D20" s="140"/>
       <c r="E20" s="10">
         <v>56</v>
       </c>
-      <c r="F20" s="285">
+      <c r="F20" s="199">
         <v>56</v>
       </c>
-      <c r="G20" s="286"/>
-      <c r="H20" s="14" t="s">
+      <c r="G20" s="200"/>
+      <c r="H20" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I20" s="14" t="s">
+      <c r="I20" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J20" s="199"/>
-      <c r="K20" s="199"/>
-      <c r="L20" s="199"/>
-      <c r="M20" s="200"/>
+      <c r="J20" s="142"/>
+      <c r="K20" s="142"/>
+      <c r="L20" s="142"/>
+      <c r="M20" s="143"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="284"/>
-      <c r="B21" s="196"/>
-      <c r="C21" s="196"/>
-      <c r="D21" s="196"/>
+      <c r="A21" s="198"/>
+      <c r="B21" s="140"/>
+      <c r="C21" s="140"/>
+      <c r="D21" s="140"/>
       <c r="E21" s="10">
         <v>83</v>
       </c>
-      <c r="F21" s="285">
+      <c r="F21" s="199">
         <v>83</v>
       </c>
-      <c r="G21" s="286"/>
-      <c r="H21" s="14" t="s">
+      <c r="G21" s="200"/>
+      <c r="H21" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I21" s="14" t="s">
+      <c r="I21" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J21" s="199"/>
-      <c r="K21" s="199"/>
-      <c r="L21" s="199"/>
-      <c r="M21" s="200"/>
+      <c r="J21" s="142"/>
+      <c r="K21" s="142"/>
+      <c r="L21" s="142"/>
+      <c r="M21" s="143"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="284"/>
-      <c r="B22" s="196"/>
-      <c r="C22" s="196"/>
-      <c r="D22" s="196"/>
+      <c r="A22" s="198"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="140"/>
+      <c r="D22" s="140"/>
       <c r="E22" s="10">
         <v>27</v>
       </c>
-      <c r="F22" s="285">
+      <c r="F22" s="199">
         <v>27</v>
       </c>
-      <c r="G22" s="286"/>
-      <c r="H22" s="14" t="s">
+      <c r="G22" s="200"/>
+      <c r="H22" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I22" s="14" t="s">
+      <c r="I22" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="199"/>
-      <c r="K22" s="199"/>
-      <c r="L22" s="199"/>
-      <c r="M22" s="200"/>
+      <c r="J22" s="142"/>
+      <c r="K22" s="142"/>
+      <c r="L22" s="142"/>
+      <c r="M22" s="143"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="284"/>
-      <c r="B23" s="196"/>
-      <c r="C23" s="196"/>
-      <c r="D23" s="196"/>
+      <c r="A23" s="198"/>
+      <c r="B23" s="140"/>
+      <c r="C23" s="140"/>
+      <c r="D23" s="140"/>
       <c r="E23" s="10">
         <v>16</v>
       </c>
-      <c r="F23" s="285">
+      <c r="F23" s="199">
         <v>16</v>
       </c>
-      <c r="G23" s="286"/>
-      <c r="H23" s="14" t="s">
+      <c r="G23" s="200"/>
+      <c r="H23" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I23" s="14" t="s">
+      <c r="I23" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="199"/>
-      <c r="K23" s="199"/>
-      <c r="L23" s="199"/>
-      <c r="M23" s="200"/>
+      <c r="J23" s="142"/>
+      <c r="K23" s="142"/>
+      <c r="L23" s="142"/>
+      <c r="M23" s="143"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="284"/>
-      <c r="B24" s="196"/>
-      <c r="C24" s="196"/>
-      <c r="D24" s="196"/>
+      <c r="A24" s="198"/>
+      <c r="B24" s="140"/>
+      <c r="C24" s="140"/>
+      <c r="D24" s="140"/>
       <c r="E24" s="10">
         <v>26</v>
       </c>
-      <c r="F24" s="285">
+      <c r="F24" s="199">
         <v>26</v>
       </c>
-      <c r="G24" s="286"/>
-      <c r="H24" s="14" t="s">
+      <c r="G24" s="200"/>
+      <c r="H24" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="I24" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="199"/>
-      <c r="K24" s="199"/>
-      <c r="L24" s="199"/>
-      <c r="M24" s="200"/>
+      <c r="J24" s="142"/>
+      <c r="K24" s="142"/>
+      <c r="L24" s="142"/>
+      <c r="M24" s="143"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="284"/>
-      <c r="B25" s="196"/>
-      <c r="C25" s="196"/>
-      <c r="D25" s="196"/>
+      <c r="A25" s="198"/>
+      <c r="B25" s="140"/>
+      <c r="C25" s="140"/>
+      <c r="D25" s="140"/>
       <c r="E25" s="10">
         <v>16</v>
       </c>
-      <c r="F25" s="285">
+      <c r="F25" s="199">
         <v>16</v>
       </c>
-      <c r="G25" s="286"/>
-      <c r="H25" s="14" t="s">
+      <c r="G25" s="200"/>
+      <c r="H25" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I25" s="14" t="s">
+      <c r="I25" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="199"/>
-      <c r="K25" s="199"/>
-      <c r="L25" s="199"/>
-      <c r="M25" s="200"/>
+      <c r="J25" s="142"/>
+      <c r="K25" s="142"/>
+      <c r="L25" s="142"/>
+      <c r="M25" s="143"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="287"/>
-      <c r="B26" s="288"/>
-      <c r="C26" s="288"/>
-      <c r="D26" s="288"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="199"/>
-      <c r="G26" s="199"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="199"/>
-      <c r="K26" s="199"/>
-      <c r="L26" s="199"/>
-      <c r="M26" s="200"/>
+      <c r="A26" s="201"/>
+      <c r="B26" s="202"/>
+      <c r="C26" s="202"/>
+      <c r="D26" s="202"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="142"/>
+      <c r="G26" s="142"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="142"/>
+      <c r="K26" s="142"/>
+      <c r="L26" s="142"/>
+      <c r="M26" s="143"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="287"/>
-      <c r="B27" s="288"/>
-      <c r="C27" s="288"/>
-      <c r="D27" s="288"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="199"/>
-      <c r="G27" s="199"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="199"/>
-      <c r="K27" s="199"/>
-      <c r="L27" s="199"/>
-      <c r="M27" s="200"/>
+      <c r="A27" s="201"/>
+      <c r="B27" s="202"/>
+      <c r="C27" s="202"/>
+      <c r="D27" s="202"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="142"/>
+      <c r="G27" s="142"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="142"/>
+      <c r="K27" s="142"/>
+      <c r="L27" s="142"/>
+      <c r="M27" s="143"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="287"/>
-      <c r="B28" s="288"/>
-      <c r="C28" s="288"/>
-      <c r="D28" s="288"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="199"/>
-      <c r="G28" s="199"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="199"/>
-      <c r="K28" s="199"/>
-      <c r="L28" s="199"/>
-      <c r="M28" s="200"/>
+      <c r="A28" s="201"/>
+      <c r="B28" s="202"/>
+      <c r="C28" s="202"/>
+      <c r="D28" s="202"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="142"/>
+      <c r="G28" s="142"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="142"/>
+      <c r="K28" s="142"/>
+      <c r="L28" s="142"/>
+      <c r="M28" s="143"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="287"/>
-      <c r="B29" s="288"/>
-      <c r="C29" s="288"/>
-      <c r="D29" s="288"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="199"/>
-      <c r="G29" s="199"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="199"/>
-      <c r="K29" s="199"/>
-      <c r="L29" s="199"/>
-      <c r="M29" s="200"/>
+      <c r="A29" s="201"/>
+      <c r="B29" s="202"/>
+      <c r="C29" s="202"/>
+      <c r="D29" s="202"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="142"/>
+      <c r="G29" s="142"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="142"/>
+      <c r="K29" s="142"/>
+      <c r="L29" s="142"/>
+      <c r="M29" s="143"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="287"/>
-      <c r="B30" s="288"/>
-      <c r="C30" s="288"/>
-      <c r="D30" s="288"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="199"/>
-      <c r="G30" s="199"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="199"/>
-      <c r="K30" s="199"/>
-      <c r="L30" s="199"/>
-      <c r="M30" s="200"/>
+      <c r="A30" s="201"/>
+      <c r="B30" s="202"/>
+      <c r="C30" s="202"/>
+      <c r="D30" s="202"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="142"/>
+      <c r="G30" s="142"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="142"/>
+      <c r="K30" s="142"/>
+      <c r="L30" s="142"/>
+      <c r="M30" s="143"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="287"/>
-      <c r="B31" s="288"/>
-      <c r="C31" s="288"/>
-      <c r="D31" s="288"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="199"/>
-      <c r="G31" s="199"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="199"/>
-      <c r="K31" s="199"/>
-      <c r="L31" s="199"/>
-      <c r="M31" s="200"/>
+      <c r="A31" s="201"/>
+      <c r="B31" s="202"/>
+      <c r="C31" s="202"/>
+      <c r="D31" s="202"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="142"/>
+      <c r="G31" s="142"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="142"/>
+      <c r="K31" s="142"/>
+      <c r="L31" s="142"/>
+      <c r="M31" s="143"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="287"/>
-      <c r="B32" s="288"/>
-      <c r="C32" s="288"/>
-      <c r="D32" s="288"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="199"/>
-      <c r="G32" s="199"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="199"/>
-      <c r="K32" s="199"/>
-      <c r="L32" s="199"/>
-      <c r="M32" s="200"/>
+      <c r="A32" s="201"/>
+      <c r="B32" s="202"/>
+      <c r="C32" s="202"/>
+      <c r="D32" s="202"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="142"/>
+      <c r="G32" s="142"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="142"/>
+      <c r="K32" s="142"/>
+      <c r="L32" s="142"/>
+      <c r="M32" s="143"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A33" s="287"/>
-      <c r="B33" s="288"/>
-      <c r="C33" s="288"/>
-      <c r="D33" s="288"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="199"/>
-      <c r="G33" s="199"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="199"/>
-      <c r="K33" s="199"/>
-      <c r="L33" s="199"/>
-      <c r="M33" s="200"/>
+      <c r="A33" s="201"/>
+      <c r="B33" s="202"/>
+      <c r="C33" s="202"/>
+      <c r="D33" s="202"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="142"/>
+      <c r="G33" s="142"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="142"/>
+      <c r="K33" s="142"/>
+      <c r="L33" s="142"/>
+      <c r="M33" s="143"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A34" s="287"/>
-      <c r="B34" s="288"/>
-      <c r="C34" s="288"/>
-      <c r="D34" s="288"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="199"/>
-      <c r="G34" s="199"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="199"/>
-      <c r="K34" s="199"/>
-      <c r="L34" s="199"/>
-      <c r="M34" s="200"/>
+      <c r="A34" s="201"/>
+      <c r="B34" s="202"/>
+      <c r="C34" s="202"/>
+      <c r="D34" s="202"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="142"/>
+      <c r="G34" s="142"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="142"/>
+      <c r="K34" s="142"/>
+      <c r="L34" s="142"/>
+      <c r="M34" s="143"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35" s="287"/>
-      <c r="B35" s="288"/>
-      <c r="C35" s="288"/>
-      <c r="D35" s="288"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="199"/>
-      <c r="G35" s="199"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="199"/>
-      <c r="K35" s="199"/>
-      <c r="L35" s="199"/>
-      <c r="M35" s="200"/>
+      <c r="A35" s="201"/>
+      <c r="B35" s="202"/>
+      <c r="C35" s="202"/>
+      <c r="D35" s="202"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="142"/>
+      <c r="G35" s="142"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="142"/>
+      <c r="K35" s="142"/>
+      <c r="L35" s="142"/>
+      <c r="M35" s="143"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A36" s="287"/>
-      <c r="B36" s="288"/>
-      <c r="C36" s="288"/>
-      <c r="D36" s="288"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="199"/>
-      <c r="G36" s="199"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="199"/>
-      <c r="K36" s="199"/>
-      <c r="L36" s="199"/>
-      <c r="M36" s="200"/>
+      <c r="A36" s="201"/>
+      <c r="B36" s="202"/>
+      <c r="C36" s="202"/>
+      <c r="D36" s="202"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="142"/>
+      <c r="G36" s="142"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="142"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="142"/>
+      <c r="M36" s="143"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A37" s="287"/>
-      <c r="B37" s="288"/>
-      <c r="C37" s="288"/>
-      <c r="D37" s="288"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="199"/>
-      <c r="G37" s="199"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="199"/>
-      <c r="K37" s="199"/>
-      <c r="L37" s="199"/>
-      <c r="M37" s="200"/>
+      <c r="A37" s="201"/>
+      <c r="B37" s="202"/>
+      <c r="C37" s="202"/>
+      <c r="D37" s="202"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="142"/>
+      <c r="G37" s="142"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="142"/>
+      <c r="K37" s="142"/>
+      <c r="L37" s="142"/>
+      <c r="M37" s="143"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A38" s="287"/>
-      <c r="B38" s="288"/>
-      <c r="C38" s="288"/>
-      <c r="D38" s="288"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="199"/>
-      <c r="G38" s="199"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="199"/>
-      <c r="K38" s="199"/>
-      <c r="L38" s="199"/>
-      <c r="M38" s="200"/>
+      <c r="A38" s="201"/>
+      <c r="B38" s="202"/>
+      <c r="C38" s="202"/>
+      <c r="D38" s="202"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="142"/>
+      <c r="G38" s="142"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="142"/>
+      <c r="K38" s="142"/>
+      <c r="L38" s="142"/>
+      <c r="M38" s="143"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A39" s="287"/>
-      <c r="B39" s="288"/>
-      <c r="C39" s="288"/>
-      <c r="D39" s="288"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="199"/>
-      <c r="G39" s="199"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="199"/>
-      <c r="K39" s="199"/>
-      <c r="L39" s="199"/>
-      <c r="M39" s="200"/>
+      <c r="A39" s="201"/>
+      <c r="B39" s="202"/>
+      <c r="C39" s="202"/>
+      <c r="D39" s="202"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="142"/>
+      <c r="G39" s="142"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="142"/>
+      <c r="K39" s="142"/>
+      <c r="L39" s="142"/>
+      <c r="M39" s="143"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A40" s="287"/>
-      <c r="B40" s="288"/>
-      <c r="C40" s="288"/>
-      <c r="D40" s="288"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="199"/>
-      <c r="G40" s="199"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="199"/>
-      <c r="K40" s="199"/>
-      <c r="L40" s="199"/>
-      <c r="M40" s="200"/>
+      <c r="A40" s="201"/>
+      <c r="B40" s="202"/>
+      <c r="C40" s="202"/>
+      <c r="D40" s="202"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="142"/>
+      <c r="G40" s="142"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="142"/>
+      <c r="K40" s="142"/>
+      <c r="L40" s="142"/>
+      <c r="M40" s="143"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A41" s="287"/>
-      <c r="B41" s="288"/>
-      <c r="C41" s="288"/>
-      <c r="D41" s="288"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="199"/>
-      <c r="G41" s="199"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="199"/>
-      <c r="K41" s="199"/>
-      <c r="L41" s="199"/>
-      <c r="M41" s="200"/>
+      <c r="A41" s="201"/>
+      <c r="B41" s="202"/>
+      <c r="C41" s="202"/>
+      <c r="D41" s="202"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="142"/>
+      <c r="G41" s="142"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="142"/>
+      <c r="K41" s="142"/>
+      <c r="L41" s="142"/>
+      <c r="M41" s="143"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A42" s="287"/>
-      <c r="B42" s="288"/>
-      <c r="C42" s="288"/>
-      <c r="D42" s="288"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="199"/>
-      <c r="G42" s="199"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="199"/>
-      <c r="K42" s="199"/>
-      <c r="L42" s="199"/>
-      <c r="M42" s="200"/>
+      <c r="A42" s="201"/>
+      <c r="B42" s="202"/>
+      <c r="C42" s="202"/>
+      <c r="D42" s="202"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="142"/>
+      <c r="G42" s="142"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="142"/>
+      <c r="K42" s="142"/>
+      <c r="L42" s="142"/>
+      <c r="M42" s="143"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A43" s="287"/>
-      <c r="B43" s="288"/>
-      <c r="C43" s="288"/>
-      <c r="D43" s="288"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="199"/>
-      <c r="G43" s="199"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="199"/>
-      <c r="K43" s="199"/>
-      <c r="L43" s="199"/>
-      <c r="M43" s="200"/>
+      <c r="A43" s="201"/>
+      <c r="B43" s="202"/>
+      <c r="C43" s="202"/>
+      <c r="D43" s="202"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="142"/>
+      <c r="G43" s="142"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="142"/>
+      <c r="K43" s="142"/>
+      <c r="L43" s="142"/>
+      <c r="M43" s="143"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A44" s="287"/>
-      <c r="B44" s="288"/>
-      <c r="C44" s="288"/>
-      <c r="D44" s="288"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="199"/>
-      <c r="G44" s="199"/>
-      <c r="H44" s="15"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="199"/>
-      <c r="K44" s="199"/>
-      <c r="L44" s="199"/>
-      <c r="M44" s="200"/>
+      <c r="A44" s="201"/>
+      <c r="B44" s="202"/>
+      <c r="C44" s="202"/>
+      <c r="D44" s="202"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="142"/>
+      <c r="G44" s="142"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="142"/>
+      <c r="K44" s="142"/>
+      <c r="L44" s="142"/>
+      <c r="M44" s="143"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A45" s="287"/>
-      <c r="B45" s="288"/>
-      <c r="C45" s="288"/>
-      <c r="D45" s="288"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="199"/>
-      <c r="G45" s="199"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="199"/>
-      <c r="K45" s="199"/>
-      <c r="L45" s="199"/>
-      <c r="M45" s="200"/>
+      <c r="A45" s="201"/>
+      <c r="B45" s="202"/>
+      <c r="C45" s="202"/>
+      <c r="D45" s="202"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="142"/>
+      <c r="G45" s="142"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="142"/>
+      <c r="K45" s="142"/>
+      <c r="L45" s="142"/>
+      <c r="M45" s="143"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A46" s="287"/>
-      <c r="B46" s="288"/>
-      <c r="C46" s="288"/>
-      <c r="D46" s="288"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="199"/>
-      <c r="G46" s="199"/>
-      <c r="H46" s="15"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="199"/>
-      <c r="K46" s="199"/>
-      <c r="L46" s="199"/>
-      <c r="M46" s="200"/>
+      <c r="A46" s="201"/>
+      <c r="B46" s="202"/>
+      <c r="C46" s="202"/>
+      <c r="D46" s="202"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="142"/>
+      <c r="G46" s="142"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="142"/>
+      <c r="K46" s="142"/>
+      <c r="L46" s="142"/>
+      <c r="M46" s="143"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A47" s="287"/>
-      <c r="B47" s="288"/>
-      <c r="C47" s="288"/>
-      <c r="D47" s="288"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="199"/>
-      <c r="G47" s="199"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="15"/>
-      <c r="J47" s="199"/>
-      <c r="K47" s="199"/>
-      <c r="L47" s="199"/>
-      <c r="M47" s="200"/>
+      <c r="A47" s="201"/>
+      <c r="B47" s="202"/>
+      <c r="C47" s="202"/>
+      <c r="D47" s="202"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="142"/>
+      <c r="G47" s="142"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="142"/>
+      <c r="K47" s="142"/>
+      <c r="L47" s="142"/>
+      <c r="M47" s="143"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A48" s="287"/>
-      <c r="B48" s="288"/>
-      <c r="C48" s="288"/>
-      <c r="D48" s="288"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="199"/>
-      <c r="G48" s="199"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="199"/>
-      <c r="K48" s="199"/>
-      <c r="L48" s="199"/>
-      <c r="M48" s="200"/>
+      <c r="A48" s="201"/>
+      <c r="B48" s="202"/>
+      <c r="C48" s="202"/>
+      <c r="D48" s="202"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="142"/>
+      <c r="G48" s="142"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="142"/>
+      <c r="K48" s="142"/>
+      <c r="L48" s="142"/>
+      <c r="M48" s="143"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A49" s="287"/>
-      <c r="B49" s="288"/>
-      <c r="C49" s="288"/>
-      <c r="D49" s="288"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="199"/>
-      <c r="G49" s="199"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="199"/>
-      <c r="K49" s="199"/>
-      <c r="L49" s="199"/>
-      <c r="M49" s="200"/>
+      <c r="A49" s="201"/>
+      <c r="B49" s="202"/>
+      <c r="C49" s="202"/>
+      <c r="D49" s="202"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="142"/>
+      <c r="G49" s="142"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="142"/>
+      <c r="K49" s="142"/>
+      <c r="L49" s="142"/>
+      <c r="M49" s="143"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="206" t="s">
+      <c r="A50" s="146" t="s">
         <v>22</v>
       </c>
-      <c r="B50" s="207"/>
-      <c r="C50" s="207"/>
-      <c r="D50" s="207"/>
-      <c r="E50" s="23">
+      <c r="B50" s="147"/>
+      <c r="C50" s="147"/>
+      <c r="D50" s="147"/>
+      <c r="E50" s="21">
         <f>SUM(E5:E25,BOL!E22:E29)</f>
         <v>1688</v>
       </c>
-      <c r="F50" s="301">
+      <c r="F50" s="215">
         <f>SUM(F5:F25,BOL!F22:F29)</f>
         <v>1688</v>
       </c>
-      <c r="G50" s="302"/>
-      <c r="H50" s="50"/>
-      <c r="I50" s="51"/>
-      <c r="J50" s="303"/>
-      <c r="K50" s="303"/>
-      <c r="L50" s="303"/>
-      <c r="M50" s="304"/>
+      <c r="G50" s="216"/>
+      <c r="H50" s="31"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="217"/>
+      <c r="K50" s="217"/>
+      <c r="L50" s="217"/>
+      <c r="M50" s="218"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A51" s="289" t="s">
+      <c r="A51" s="203" t="s">
         <v>58</v>
       </c>
-      <c r="B51" s="290"/>
-      <c r="C51" s="290"/>
-      <c r="D51" s="290"/>
-      <c r="E51" s="290"/>
-      <c r="F51" s="290"/>
-      <c r="G51" s="290"/>
-      <c r="H51" s="290"/>
-      <c r="I51" s="290"/>
-      <c r="J51" s="290"/>
-      <c r="K51" s="290"/>
-      <c r="L51" s="290"/>
-      <c r="M51" s="291"/>
+      <c r="B51" s="204"/>
+      <c r="C51" s="204"/>
+      <c r="D51" s="204"/>
+      <c r="E51" s="204"/>
+      <c r="F51" s="204"/>
+      <c r="G51" s="204"/>
+      <c r="H51" s="204"/>
+      <c r="I51" s="204"/>
+      <c r="J51" s="204"/>
+      <c r="K51" s="204"/>
+      <c r="L51" s="204"/>
+      <c r="M51" s="205"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="292"/>
-      <c r="B52" s="293"/>
-      <c r="C52" s="293"/>
-      <c r="D52" s="293"/>
-      <c r="E52" s="293"/>
-      <c r="F52" s="293"/>
-      <c r="G52" s="293"/>
-      <c r="H52" s="293"/>
-      <c r="I52" s="293"/>
-      <c r="J52" s="293"/>
-      <c r="K52" s="293"/>
-      <c r="L52" s="293"/>
-      <c r="M52" s="294"/>
+      <c r="A52" s="206"/>
+      <c r="B52" s="207"/>
+      <c r="C52" s="207"/>
+      <c r="D52" s="207"/>
+      <c r="E52" s="207"/>
+      <c r="F52" s="207"/>
+      <c r="G52" s="207"/>
+      <c r="H52" s="207"/>
+      <c r="I52" s="207"/>
+      <c r="J52" s="207"/>
+      <c r="K52" s="207"/>
+      <c r="L52" s="207"/>
+      <c r="M52" s="208"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A53" s="295"/>
-      <c r="B53" s="296"/>
-      <c r="C53" s="296"/>
-      <c r="D53" s="296"/>
-      <c r="E53" s="296"/>
-      <c r="F53" s="296"/>
-      <c r="G53" s="296"/>
-      <c r="H53" s="296"/>
-      <c r="I53" s="296"/>
-      <c r="J53" s="296"/>
-      <c r="K53" s="296"/>
-      <c r="L53" s="296"/>
-      <c r="M53" s="297"/>
+      <c r="A53" s="209"/>
+      <c r="B53" s="210"/>
+      <c r="C53" s="210"/>
+      <c r="D53" s="210"/>
+      <c r="E53" s="210"/>
+      <c r="F53" s="210"/>
+      <c r="G53" s="210"/>
+      <c r="H53" s="210"/>
+      <c r="I53" s="210"/>
+      <c r="J53" s="210"/>
+      <c r="K53" s="210"/>
+      <c r="L53" s="210"/>
+      <c r="M53" s="211"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A54" s="295"/>
-      <c r="B54" s="296"/>
-      <c r="C54" s="296"/>
-      <c r="D54" s="296"/>
-      <c r="E54" s="296"/>
-      <c r="F54" s="296"/>
-      <c r="G54" s="296"/>
-      <c r="H54" s="296"/>
-      <c r="I54" s="296"/>
-      <c r="J54" s="296"/>
-      <c r="K54" s="296"/>
-      <c r="L54" s="296"/>
-      <c r="M54" s="297"/>
+      <c r="A54" s="209"/>
+      <c r="B54" s="210"/>
+      <c r="C54" s="210"/>
+      <c r="D54" s="210"/>
+      <c r="E54" s="210"/>
+      <c r="F54" s="210"/>
+      <c r="G54" s="210"/>
+      <c r="H54" s="210"/>
+      <c r="I54" s="210"/>
+      <c r="J54" s="210"/>
+      <c r="K54" s="210"/>
+      <c r="L54" s="210"/>
+      <c r="M54" s="211"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A55" s="295"/>
-      <c r="B55" s="296"/>
-      <c r="C55" s="296"/>
-      <c r="D55" s="296"/>
-      <c r="E55" s="296"/>
-      <c r="F55" s="296"/>
-      <c r="G55" s="296"/>
-      <c r="H55" s="296"/>
-      <c r="I55" s="296"/>
-      <c r="J55" s="296"/>
-      <c r="K55" s="296"/>
-      <c r="L55" s="296"/>
-      <c r="M55" s="297"/>
+      <c r="A55" s="209"/>
+      <c r="B55" s="210"/>
+      <c r="C55" s="210"/>
+      <c r="D55" s="210"/>
+      <c r="E55" s="210"/>
+      <c r="F55" s="210"/>
+      <c r="G55" s="210"/>
+      <c r="H55" s="210"/>
+      <c r="I55" s="210"/>
+      <c r="J55" s="210"/>
+      <c r="K55" s="210"/>
+      <c r="L55" s="210"/>
+      <c r="M55" s="211"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A56" s="295"/>
-      <c r="B56" s="296"/>
-      <c r="C56" s="296"/>
-      <c r="D56" s="296"/>
-      <c r="E56" s="296"/>
-      <c r="F56" s="296"/>
-      <c r="G56" s="296"/>
-      <c r="H56" s="296"/>
-      <c r="I56" s="296"/>
-      <c r="J56" s="296"/>
-      <c r="K56" s="296"/>
-      <c r="L56" s="296"/>
-      <c r="M56" s="297"/>
+      <c r="A56" s="209"/>
+      <c r="B56" s="210"/>
+      <c r="C56" s="210"/>
+      <c r="D56" s="210"/>
+      <c r="E56" s="210"/>
+      <c r="F56" s="210"/>
+      <c r="G56" s="210"/>
+      <c r="H56" s="210"/>
+      <c r="I56" s="210"/>
+      <c r="J56" s="210"/>
+      <c r="K56" s="210"/>
+      <c r="L56" s="210"/>
+      <c r="M56" s="211"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A57" s="295"/>
-      <c r="B57" s="296"/>
-      <c r="C57" s="296"/>
-      <c r="D57" s="296"/>
-      <c r="E57" s="296"/>
-      <c r="F57" s="296"/>
-      <c r="G57" s="296"/>
-      <c r="H57" s="296"/>
-      <c r="I57" s="296"/>
-      <c r="J57" s="296"/>
-      <c r="K57" s="296"/>
-      <c r="L57" s="296"/>
-      <c r="M57" s="297"/>
+      <c r="A57" s="209"/>
+      <c r="B57" s="210"/>
+      <c r="C57" s="210"/>
+      <c r="D57" s="210"/>
+      <c r="E57" s="210"/>
+      <c r="F57" s="210"/>
+      <c r="G57" s="210"/>
+      <c r="H57" s="210"/>
+      <c r="I57" s="210"/>
+      <c r="J57" s="210"/>
+      <c r="K57" s="210"/>
+      <c r="L57" s="210"/>
+      <c r="M57" s="211"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A58" s="295"/>
-      <c r="B58" s="296"/>
-      <c r="C58" s="296"/>
-      <c r="D58" s="296"/>
-      <c r="E58" s="296"/>
-      <c r="F58" s="296"/>
-      <c r="G58" s="296"/>
-      <c r="H58" s="296"/>
-      <c r="I58" s="296"/>
-      <c r="J58" s="296"/>
-      <c r="K58" s="296"/>
-      <c r="L58" s="296"/>
-      <c r="M58" s="297"/>
+      <c r="A58" s="209"/>
+      <c r="B58" s="210"/>
+      <c r="C58" s="210"/>
+      <c r="D58" s="210"/>
+      <c r="E58" s="210"/>
+      <c r="F58" s="210"/>
+      <c r="G58" s="210"/>
+      <c r="H58" s="210"/>
+      <c r="I58" s="210"/>
+      <c r="J58" s="210"/>
+      <c r="K58" s="210"/>
+      <c r="L58" s="210"/>
+      <c r="M58" s="211"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A59" s="295"/>
-      <c r="B59" s="296"/>
-      <c r="C59" s="296"/>
-      <c r="D59" s="296"/>
-      <c r="E59" s="296"/>
-      <c r="F59" s="296"/>
-      <c r="G59" s="296"/>
-      <c r="H59" s="296"/>
-      <c r="I59" s="296"/>
-      <c r="J59" s="296"/>
-      <c r="K59" s="296"/>
-      <c r="L59" s="296"/>
-      <c r="M59" s="297"/>
+      <c r="A59" s="209"/>
+      <c r="B59" s="210"/>
+      <c r="C59" s="210"/>
+      <c r="D59" s="210"/>
+      <c r="E59" s="210"/>
+      <c r="F59" s="210"/>
+      <c r="G59" s="210"/>
+      <c r="H59" s="210"/>
+      <c r="I59" s="210"/>
+      <c r="J59" s="210"/>
+      <c r="K59" s="210"/>
+      <c r="L59" s="210"/>
+      <c r="M59" s="211"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A60" s="298"/>
-      <c r="B60" s="299"/>
-      <c r="C60" s="299"/>
-      <c r="D60" s="299"/>
-      <c r="E60" s="299"/>
-      <c r="F60" s="299"/>
-      <c r="G60" s="299"/>
-      <c r="H60" s="299"/>
-      <c r="I60" s="299"/>
-      <c r="J60" s="299"/>
-      <c r="K60" s="299"/>
-      <c r="L60" s="299"/>
-      <c r="M60" s="300"/>
+      <c r="A60" s="212"/>
+      <c r="B60" s="213"/>
+      <c r="C60" s="213"/>
+      <c r="D60" s="213"/>
+      <c r="E60" s="213"/>
+      <c r="F60" s="213"/>
+      <c r="G60" s="213"/>
+      <c r="H60" s="213"/>
+      <c r="I60" s="213"/>
+      <c r="J60" s="213"/>
+      <c r="K60" s="213"/>
+      <c r="L60" s="213"/>
+      <c r="M60" s="214"/>
     </row>
     <row r="61" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="49"/>
-      <c r="B61" s="49"/>
-      <c r="C61" s="49"/>
-      <c r="D61" s="49"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="30"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="28"/>
-      <c r="J61" s="28"/>
+      <c r="A61" s="30"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="25"/>
+      <c r="J61" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="150">
@@ -8260,640 +8276,640 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="421">
+      <c r="B1" s="335">
         <v>45877</v>
       </c>
-      <c r="C1" s="421"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79" t="s">
+      <c r="C1" s="335"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="426" t="s">
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="340" t="s">
         <v>72</v>
       </c>
-      <c r="M1" s="427"/>
+      <c r="M1" s="341"/>
     </row>
     <row r="2" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="423" t="s">
+      <c r="A2" s="337" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="424"/>
-      <c r="C2" s="424"/>
-      <c r="D2" s="424"/>
-      <c r="E2" s="424"/>
-      <c r="F2" s="424"/>
-      <c r="G2" s="424"/>
-      <c r="H2" s="425"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="83"/>
+      <c r="B2" s="338"/>
+      <c r="C2" s="338"/>
+      <c r="D2" s="338"/>
+      <c r="E2" s="338"/>
+      <c r="F2" s="338"/>
+      <c r="G2" s="338"/>
+      <c r="H2" s="339"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="47"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="388" t="s">
+      <c r="A3" s="302" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="389"/>
-      <c r="C3" s="389"/>
-      <c r="D3" s="389"/>
-      <c r="E3" s="389"/>
-      <c r="F3" s="389"/>
-      <c r="G3" s="389"/>
-      <c r="H3" s="390"/>
-      <c r="I3" s="84" t="s">
+      <c r="B3" s="303"/>
+      <c r="C3" s="303"/>
+      <c r="D3" s="303"/>
+      <c r="E3" s="303"/>
+      <c r="F3" s="303"/>
+      <c r="G3" s="303"/>
+      <c r="H3" s="304"/>
+      <c r="I3" s="48" t="s">
         <v>193</v>
       </c>
-      <c r="J3" s="82"/>
-      <c r="K3" s="85"/>
-      <c r="L3" s="82"/>
-      <c r="M3" s="86"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="50"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="388" t="s">
+      <c r="A4" s="302" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="389"/>
-      <c r="C4" s="389"/>
-      <c r="D4" s="389"/>
-      <c r="E4" s="389"/>
-      <c r="F4" s="389"/>
-      <c r="G4" s="389"/>
-      <c r="H4" s="390"/>
-      <c r="I4" s="433"/>
-      <c r="J4" s="417"/>
-      <c r="K4" s="417"/>
-      <c r="L4" s="417"/>
-      <c r="M4" s="418"/>
+      <c r="B4" s="303"/>
+      <c r="C4" s="303"/>
+      <c r="D4" s="303"/>
+      <c r="E4" s="303"/>
+      <c r="F4" s="303"/>
+      <c r="G4" s="303"/>
+      <c r="H4" s="304"/>
+      <c r="I4" s="347"/>
+      <c r="J4" s="331"/>
+      <c r="K4" s="331"/>
+      <c r="L4" s="331"/>
+      <c r="M4" s="332"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="388" t="s">
+      <c r="A5" s="302" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="389"/>
-      <c r="C5" s="389"/>
-      <c r="D5" s="389"/>
-      <c r="E5" s="389"/>
-      <c r="F5" s="389"/>
-      <c r="G5" s="389"/>
-      <c r="H5" s="390"/>
-      <c r="I5" s="433"/>
-      <c r="J5" s="417"/>
-      <c r="K5" s="417"/>
-      <c r="L5" s="417"/>
-      <c r="M5" s="418"/>
+      <c r="B5" s="303"/>
+      <c r="C5" s="303"/>
+      <c r="D5" s="303"/>
+      <c r="E5" s="303"/>
+      <c r="F5" s="303"/>
+      <c r="G5" s="303"/>
+      <c r="H5" s="304"/>
+      <c r="I5" s="347"/>
+      <c r="J5" s="331"/>
+      <c r="K5" s="331"/>
+      <c r="L5" s="331"/>
+      <c r="M5" s="332"/>
     </row>
     <row r="6" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="431" t="s">
+      <c r="A6" s="345" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="387"/>
-      <c r="C6" s="387"/>
-      <c r="D6" s="387"/>
-      <c r="E6" s="387"/>
-      <c r="F6" s="432" t="s">
+      <c r="B6" s="301"/>
+      <c r="C6" s="301"/>
+      <c r="D6" s="301"/>
+      <c r="E6" s="301"/>
+      <c r="F6" s="346" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="432"/>
-      <c r="H6" s="87"/>
-      <c r="I6" s="434"/>
-      <c r="J6" s="435"/>
-      <c r="K6" s="435"/>
-      <c r="L6" s="435"/>
-      <c r="M6" s="436"/>
+      <c r="G6" s="346"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="348"/>
+      <c r="J6" s="349"/>
+      <c r="K6" s="349"/>
+      <c r="L6" s="349"/>
+      <c r="M6" s="350"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="438" t="s">
+      <c r="A7" s="352" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="439"/>
-      <c r="C7" s="439"/>
-      <c r="D7" s="439"/>
-      <c r="E7" s="439"/>
-      <c r="F7" s="439"/>
-      <c r="G7" s="439"/>
-      <c r="H7" s="440"/>
-      <c r="I7" s="88" t="s">
+      <c r="B7" s="353"/>
+      <c r="C7" s="353"/>
+      <c r="D7" s="353"/>
+      <c r="E7" s="353"/>
+      <c r="F7" s="353"/>
+      <c r="G7" s="353"/>
+      <c r="H7" s="354"/>
+      <c r="I7" s="52" t="s">
         <v>233</v>
       </c>
-      <c r="J7" s="89"/>
-      <c r="K7" s="90" t="str">
+      <c r="J7" s="53"/>
+      <c r="K7" s="54" t="str">
         <f>ADDRESS!I1</f>
         <v>CH Robinson</v>
       </c>
-      <c r="L7" s="89"/>
-      <c r="M7" s="91"/>
+      <c r="L7" s="53"/>
+      <c r="M7" s="55"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="92" t="s">
+      <c r="A8" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="124" t="s">
+      <c r="B8" s="88" t="s">
         <v>113</v>
       </c>
-      <c r="C8" s="93"/>
-      <c r="D8" s="93"/>
-      <c r="E8" s="384" t="s">
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="298" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="384"/>
-      <c r="G8" s="384"/>
-      <c r="H8" s="385"/>
-      <c r="I8" s="437" t="s">
+      <c r="F8" s="298"/>
+      <c r="G8" s="298"/>
+      <c r="H8" s="299"/>
+      <c r="I8" s="351" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="389"/>
-      <c r="K8" s="389"/>
-      <c r="L8" s="389"/>
-      <c r="M8" s="390"/>
+      <c r="J8" s="303"/>
+      <c r="K8" s="303"/>
+      <c r="L8" s="303"/>
+      <c r="M8" s="304"/>
     </row>
     <row r="9" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="94" t="s">
+      <c r="A9" s="58" t="s">
         <v>2</v>
       </c>
       <c r="B9" t="str">
         <f>VLOOKUP(B8,ADDRESS!$A$2:$E$30,2,FALSE)</f>
         <v>13790 Harvey Road</v>
       </c>
-      <c r="H9" s="95"/>
-      <c r="I9" s="96" t="s">
+      <c r="H9" s="59"/>
+      <c r="I9" s="60" t="s">
         <v>74</v>
       </c>
-      <c r="J9" s="97"/>
-      <c r="K9" s="97">
+      <c r="J9" s="61"/>
+      <c r="K9" s="61">
         <f>ADDRESS!I3</f>
         <v>10285609</v>
       </c>
-      <c r="L9" s="97"/>
-      <c r="M9" s="87"/>
+      <c r="L9" s="61"/>
+      <c r="M9" s="51"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="98" t="s">
+      <c r="A10" s="62" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="416" t="str">
+      <c r="C10" s="330" t="str">
         <f>CONCATENATE(VLOOKUP(B8,ADDRESS!$A$2:$E$30,3,FALSE),", ",VLOOKUP(B8,ADDRESS!$A$2:$E$30,4,FALSE)," ",VLOOKUP(B8,ADDRESS!$A$2:$E$30,5,FALSE))</f>
         <v>TYLER, TX 75706</v>
       </c>
-      <c r="D10" s="416"/>
-      <c r="E10" s="416"/>
-      <c r="F10" s="416"/>
-      <c r="G10" s="416"/>
-      <c r="H10" s="95"/>
-      <c r="I10" s="99" t="s">
+      <c r="D10" s="330"/>
+      <c r="E10" s="330"/>
+      <c r="F10" s="330"/>
+      <c r="G10" s="330"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="63" t="s">
         <v>234</v>
       </c>
-      <c r="J10" s="100" t="str">
+      <c r="J10" s="64" t="str">
         <f>ADDRESS!I2</f>
         <v>RBTW</v>
       </c>
-      <c r="K10" s="100"/>
-      <c r="L10" s="100"/>
-      <c r="M10" s="101"/>
+      <c r="K10" s="64"/>
+      <c r="L10" s="64"/>
+      <c r="M10" s="65"/>
     </row>
     <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="386" t="s">
+      <c r="A11" s="300" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="387"/>
-      <c r="C11" s="387"/>
-      <c r="D11" s="387"/>
-      <c r="E11" s="387"/>
-      <c r="F11" s="432" t="s">
+      <c r="B11" s="301"/>
+      <c r="C11" s="301"/>
+      <c r="D11" s="301"/>
+      <c r="E11" s="301"/>
+      <c r="F11" s="346" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="432"/>
-      <c r="H11" s="87"/>
-      <c r="I11" s="419" t="s">
+      <c r="G11" s="346"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="333" t="s">
         <v>75</v>
       </c>
-      <c r="J11" s="420"/>
-      <c r="K11" s="102">
+      <c r="J11" s="334"/>
+      <c r="K11" s="66">
         <f>ADDRESS!I4</f>
         <v>523953410</v>
       </c>
-      <c r="L11" s="102"/>
-      <c r="M11" s="103"/>
+      <c r="L11" s="66"/>
+      <c r="M11" s="67"/>
     </row>
     <row r="12" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="355" t="s">
+      <c r="A12" s="269" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="356"/>
-      <c r="C12" s="356"/>
-      <c r="D12" s="356"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
-      <c r="G12" s="356"/>
-      <c r="H12" s="357"/>
-      <c r="I12" s="433"/>
-      <c r="J12" s="417"/>
-      <c r="K12" s="417"/>
-      <c r="L12" s="417"/>
-      <c r="M12" s="418"/>
+      <c r="B12" s="270"/>
+      <c r="C12" s="270"/>
+      <c r="D12" s="270"/>
+      <c r="E12" s="270"/>
+      <c r="F12" s="270"/>
+      <c r="G12" s="270"/>
+      <c r="H12" s="271"/>
+      <c r="I12" s="347"/>
+      <c r="J12" s="331"/>
+      <c r="K12" s="331"/>
+      <c r="L12" s="331"/>
+      <c r="M12" s="332"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="428" t="s">
+      <c r="A13" s="342" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="429"/>
-      <c r="C13" s="429"/>
-      <c r="D13" s="429"/>
-      <c r="E13" s="429"/>
-      <c r="F13" s="429"/>
-      <c r="G13" s="429"/>
-      <c r="H13" s="430"/>
-      <c r="I13" s="433"/>
-      <c r="J13" s="417"/>
-      <c r="K13" s="417"/>
-      <c r="L13" s="417"/>
-      <c r="M13" s="418"/>
+      <c r="B13" s="343"/>
+      <c r="C13" s="343"/>
+      <c r="D13" s="343"/>
+      <c r="E13" s="343"/>
+      <c r="F13" s="343"/>
+      <c r="G13" s="343"/>
+      <c r="H13" s="344"/>
+      <c r="I13" s="347"/>
+      <c r="J13" s="331"/>
+      <c r="K13" s="331"/>
+      <c r="L13" s="331"/>
+      <c r="M13" s="332"/>
     </row>
     <row r="14" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="388" t="s">
+      <c r="A14" s="302" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="389"/>
-      <c r="C14" s="389"/>
-      <c r="D14" s="389"/>
-      <c r="E14" s="389"/>
-      <c r="F14" s="389"/>
-      <c r="G14" s="389"/>
-      <c r="H14" s="390"/>
-      <c r="I14" s="434"/>
-      <c r="J14" s="435"/>
-      <c r="K14" s="435"/>
-      <c r="L14" s="435"/>
-      <c r="M14" s="436"/>
+      <c r="B14" s="303"/>
+      <c r="C14" s="303"/>
+      <c r="D14" s="303"/>
+      <c r="E14" s="303"/>
+      <c r="F14" s="303"/>
+      <c r="G14" s="303"/>
+      <c r="H14" s="304"/>
+      <c r="I14" s="348"/>
+      <c r="J14" s="349"/>
+      <c r="K14" s="349"/>
+      <c r="L14" s="349"/>
+      <c r="M14" s="350"/>
     </row>
     <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="398" t="s">
+      <c r="A15" s="312" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="399"/>
-      <c r="C15" s="399"/>
-      <c r="D15" s="399"/>
-      <c r="E15" s="399"/>
-      <c r="F15" s="400"/>
-      <c r="G15" s="400"/>
-      <c r="H15" s="400"/>
-      <c r="I15" s="395" t="s">
+      <c r="B15" s="313"/>
+      <c r="C15" s="313"/>
+      <c r="D15" s="313"/>
+      <c r="E15" s="313"/>
+      <c r="F15" s="314"/>
+      <c r="G15" s="314"/>
+      <c r="H15" s="314"/>
+      <c r="I15" s="309" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="396"/>
-      <c r="K15" s="396"/>
-      <c r="L15" s="396"/>
-      <c r="M15" s="397"/>
+      <c r="J15" s="310"/>
+      <c r="K15" s="310"/>
+      <c r="L15" s="310"/>
+      <c r="M15" s="311"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="70"/>
-      <c r="B16" s="70"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="72"/>
-      <c r="I16" s="410" t="s">
+      <c r="A16" s="34"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="324" t="s">
         <v>61</v>
       </c>
-      <c r="J16" s="411"/>
-      <c r="K16" s="411"/>
-      <c r="L16" s="411"/>
-      <c r="M16" s="412"/>
+      <c r="J16" s="325"/>
+      <c r="K16" s="325"/>
+      <c r="L16" s="325"/>
+      <c r="M16" s="326"/>
     </row>
     <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="73" t="s">
+      <c r="A17" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="74"/>
-      <c r="C17" s="74"/>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="417">
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="331">
         <f>ADDRESS!I5</f>
         <v>59642884</v>
       </c>
-      <c r="G17" s="417"/>
-      <c r="H17" s="418"/>
-      <c r="I17" s="409"/>
-      <c r="J17" s="384"/>
-      <c r="K17" s="391" t="s">
+      <c r="G17" s="331"/>
+      <c r="H17" s="332"/>
+      <c r="I17" s="323"/>
+      <c r="J17" s="298"/>
+      <c r="K17" s="305" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="391"/>
-      <c r="M17" s="392"/>
+      <c r="L17" s="305"/>
+      <c r="M17" s="306"/>
     </row>
     <row r="18" spans="1:13" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="75"/>
-      <c r="B18" s="76"/>
-      <c r="C18" s="76"/>
-      <c r="D18" s="76"/>
-      <c r="E18" s="76"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="76"/>
-      <c r="H18" s="77"/>
-      <c r="I18" s="305" t="s">
+      <c r="A18" s="39"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="219" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="306"/>
-      <c r="K18" s="393"/>
-      <c r="L18" s="393"/>
-      <c r="M18" s="394"/>
+      <c r="J18" s="220"/>
+      <c r="K18" s="307"/>
+      <c r="L18" s="307"/>
+      <c r="M18" s="308"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="358" t="s">
+      <c r="A19" s="272" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="359"/>
-      <c r="C19" s="359"/>
-      <c r="D19" s="359"/>
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
-      <c r="G19" s="359"/>
-      <c r="H19" s="359"/>
-      <c r="I19" s="359"/>
-      <c r="J19" s="359"/>
-      <c r="K19" s="359"/>
-      <c r="L19" s="359"/>
-      <c r="M19" s="360"/>
+      <c r="B19" s="273"/>
+      <c r="C19" s="273"/>
+      <c r="D19" s="273"/>
+      <c r="E19" s="273"/>
+      <c r="F19" s="273"/>
+      <c r="G19" s="273"/>
+      <c r="H19" s="273"/>
+      <c r="I19" s="273"/>
+      <c r="J19" s="273"/>
+      <c r="K19" s="273"/>
+      <c r="L19" s="273"/>
+      <c r="M19" s="274"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="413" t="s">
+      <c r="A20" s="327" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="414"/>
-      <c r="C20" s="414"/>
-      <c r="D20" s="414"/>
-      <c r="E20" s="414" t="s">
+      <c r="B20" s="328"/>
+      <c r="C20" s="328"/>
+      <c r="D20" s="328"/>
+      <c r="E20" s="328" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="414" t="s">
+      <c r="F20" s="328" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="414"/>
-      <c r="H20" s="407" t="s">
+      <c r="G20" s="328"/>
+      <c r="H20" s="321" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="408"/>
-      <c r="J20" s="401" t="s">
+      <c r="I20" s="322"/>
+      <c r="J20" s="315" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="402"/>
-      <c r="L20" s="402"/>
-      <c r="M20" s="403"/>
+      <c r="K20" s="316"/>
+      <c r="L20" s="316"/>
+      <c r="M20" s="317"/>
     </row>
     <row r="21" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="413"/>
-      <c r="B21" s="414"/>
-      <c r="C21" s="414"/>
-      <c r="D21" s="414"/>
-      <c r="E21" s="414"/>
-      <c r="F21" s="414"/>
-      <c r="G21" s="414"/>
-      <c r="H21" s="441" t="s">
+      <c r="A21" s="327"/>
+      <c r="B21" s="328"/>
+      <c r="C21" s="328"/>
+      <c r="D21" s="328"/>
+      <c r="E21" s="328"/>
+      <c r="F21" s="328"/>
+      <c r="G21" s="328"/>
+      <c r="H21" s="355" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="442"/>
-      <c r="J21" s="404"/>
-      <c r="K21" s="405"/>
-      <c r="L21" s="405"/>
-      <c r="M21" s="406"/>
+      <c r="I21" s="356"/>
+      <c r="J21" s="318"/>
+      <c r="K21" s="319"/>
+      <c r="L21" s="319"/>
+      <c r="M21" s="320"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="415" t="str">
+      <c r="A22" s="329" t="str">
         <f>VLOOKUP(B8,'Customer Order Info'!$A$3:$D$31,2,FALSE)</f>
         <v>0215-8880831-0578</v>
       </c>
-      <c r="B22" s="198"/>
-      <c r="C22" s="198"/>
-      <c r="D22" s="285"/>
+      <c r="B22" s="141"/>
+      <c r="C22" s="141"/>
+      <c r="D22" s="199"/>
       <c r="E22" s="10">
         <f>VLOOKUP(A22,'Customer Order Info'!B3:D31,2,FALSE)</f>
         <v>83</v>
       </c>
-      <c r="F22" s="198">
+      <c r="F22" s="141">
         <f>VLOOKUP(A22,'Customer Order Info'!B3:D31,3,FALSE)</f>
         <v>83</v>
       </c>
-      <c r="G22" s="198"/>
+      <c r="G22" s="141"/>
       <c r="H22" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="198"/>
-      <c r="K22" s="198"/>
-      <c r="L22" s="198"/>
-      <c r="M22" s="375"/>
+      <c r="J22" s="141"/>
+      <c r="K22" s="141"/>
+      <c r="L22" s="141"/>
+      <c r="M22" s="289"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="378"/>
-      <c r="B23" s="379"/>
-      <c r="C23" s="379"/>
-      <c r="D23" s="380"/>
+      <c r="A23" s="292"/>
+      <c r="B23" s="293"/>
+      <c r="C23" s="293"/>
+      <c r="D23" s="294"/>
       <c r="E23" s="10"/>
-      <c r="F23" s="198"/>
-      <c r="G23" s="198"/>
+      <c r="F23" s="141"/>
+      <c r="G23" s="141"/>
       <c r="H23" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="198"/>
-      <c r="K23" s="198"/>
-      <c r="L23" s="198"/>
-      <c r="M23" s="375"/>
+      <c r="J23" s="141"/>
+      <c r="K23" s="141"/>
+      <c r="L23" s="141"/>
+      <c r="M23" s="289"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="378"/>
-      <c r="B24" s="379"/>
-      <c r="C24" s="379"/>
-      <c r="D24" s="380"/>
+      <c r="A24" s="292"/>
+      <c r="B24" s="293"/>
+      <c r="C24" s="293"/>
+      <c r="D24" s="294"/>
       <c r="E24" s="10"/>
-      <c r="F24" s="198"/>
-      <c r="G24" s="198"/>
+      <c r="F24" s="141"/>
+      <c r="G24" s="141"/>
       <c r="H24" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="198"/>
-      <c r="K24" s="198"/>
-      <c r="L24" s="198"/>
-      <c r="M24" s="375"/>
+      <c r="J24" s="141"/>
+      <c r="K24" s="141"/>
+      <c r="L24" s="141"/>
+      <c r="M24" s="289"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="378"/>
-      <c r="B25" s="379"/>
-      <c r="C25" s="379"/>
-      <c r="D25" s="380"/>
+      <c r="A25" s="292"/>
+      <c r="B25" s="293"/>
+      <c r="C25" s="293"/>
+      <c r="D25" s="294"/>
       <c r="E25" s="10"/>
-      <c r="F25" s="198"/>
-      <c r="G25" s="198"/>
+      <c r="F25" s="141"/>
+      <c r="G25" s="141"/>
       <c r="H25" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="198"/>
-      <c r="K25" s="198"/>
-      <c r="L25" s="198"/>
-      <c r="M25" s="375"/>
+      <c r="J25" s="141"/>
+      <c r="K25" s="141"/>
+      <c r="L25" s="141"/>
+      <c r="M25" s="289"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="378"/>
-      <c r="B26" s="379"/>
-      <c r="C26" s="379"/>
-      <c r="D26" s="380"/>
+      <c r="A26" s="292"/>
+      <c r="B26" s="293"/>
+      <c r="C26" s="293"/>
+      <c r="D26" s="294"/>
       <c r="E26" s="10"/>
-      <c r="F26" s="198"/>
-      <c r="G26" s="198"/>
+      <c r="F26" s="141"/>
+      <c r="G26" s="141"/>
       <c r="H26" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="198"/>
-      <c r="K26" s="198"/>
-      <c r="L26" s="198"/>
-      <c r="M26" s="375"/>
+      <c r="J26" s="141"/>
+      <c r="K26" s="141"/>
+      <c r="L26" s="141"/>
+      <c r="M26" s="289"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="378"/>
-      <c r="B27" s="379"/>
-      <c r="C27" s="379"/>
-      <c r="D27" s="380"/>
+      <c r="A27" s="292"/>
+      <c r="B27" s="293"/>
+      <c r="C27" s="293"/>
+      <c r="D27" s="294"/>
       <c r="E27" s="10"/>
-      <c r="F27" s="198"/>
-      <c r="G27" s="198"/>
+      <c r="F27" s="141"/>
+      <c r="G27" s="141"/>
       <c r="H27" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J27" s="198"/>
-      <c r="K27" s="198"/>
-      <c r="L27" s="198"/>
-      <c r="M27" s="375"/>
+      <c r="J27" s="141"/>
+      <c r="K27" s="141"/>
+      <c r="L27" s="141"/>
+      <c r="M27" s="289"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="378"/>
-      <c r="B28" s="379"/>
-      <c r="C28" s="379"/>
-      <c r="D28" s="380"/>
+      <c r="A28" s="292"/>
+      <c r="B28" s="293"/>
+      <c r="C28" s="293"/>
+      <c r="D28" s="294"/>
       <c r="E28" s="10"/>
-      <c r="F28" s="198"/>
-      <c r="G28" s="198"/>
+      <c r="F28" s="141"/>
+      <c r="G28" s="141"/>
       <c r="H28" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J28" s="198"/>
-      <c r="K28" s="198"/>
-      <c r="L28" s="198"/>
-      <c r="M28" s="375"/>
+      <c r="J28" s="141"/>
+      <c r="K28" s="141"/>
+      <c r="L28" s="141"/>
+      <c r="M28" s="289"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="378"/>
-      <c r="B29" s="379"/>
-      <c r="C29" s="379"/>
-      <c r="D29" s="380"/>
+      <c r="A29" s="292"/>
+      <c r="B29" s="293"/>
+      <c r="C29" s="293"/>
+      <c r="D29" s="294"/>
       <c r="E29" s="10"/>
-      <c r="F29" s="198"/>
-      <c r="G29" s="198"/>
+      <c r="F29" s="141"/>
+      <c r="G29" s="141"/>
       <c r="H29" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J29" s="198"/>
-      <c r="K29" s="198"/>
-      <c r="L29" s="198"/>
-      <c r="M29" s="375"/>
+      <c r="J29" s="141"/>
+      <c r="K29" s="141"/>
+      <c r="L29" s="141"/>
+      <c r="M29" s="289"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="376" t="s">
+      <c r="A30" s="290" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="377"/>
-      <c r="C30" s="377"/>
-      <c r="D30" s="377"/>
+      <c r="B30" s="291"/>
+      <c r="C30" s="291"/>
+      <c r="D30" s="291"/>
       <c r="E30" s="9">
         <f>SUM(E22:E29)</f>
         <v>83</v>
       </c>
-      <c r="F30" s="364">
+      <c r="F30" s="278">
         <f>SUM(F22:G29)</f>
         <v>83</v>
       </c>
-      <c r="G30" s="198"/>
-      <c r="H30" s="381"/>
-      <c r="I30" s="383"/>
-      <c r="J30" s="381"/>
-      <c r="K30" s="382"/>
-      <c r="L30" s="382"/>
-      <c r="M30" s="383"/>
+      <c r="G30" s="141"/>
+      <c r="H30" s="295"/>
+      <c r="I30" s="297"/>
+      <c r="J30" s="295"/>
+      <c r="K30" s="296"/>
+      <c r="L30" s="296"/>
+      <c r="M30" s="297"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="365" t="s">
+      <c r="A31" s="279" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="366"/>
-      <c r="C31" s="366"/>
-      <c r="D31" s="366"/>
-      <c r="E31" s="366"/>
-      <c r="F31" s="366"/>
-      <c r="G31" s="366"/>
-      <c r="H31" s="366"/>
-      <c r="I31" s="366"/>
-      <c r="J31" s="366"/>
-      <c r="K31" s="366"/>
-      <c r="L31" s="366"/>
-      <c r="M31" s="367"/>
+      <c r="B31" s="280"/>
+      <c r="C31" s="280"/>
+      <c r="D31" s="280"/>
+      <c r="E31" s="280"/>
+      <c r="F31" s="280"/>
+      <c r="G31" s="280"/>
+      <c r="H31" s="280"/>
+      <c r="I31" s="280"/>
+      <c r="J31" s="280"/>
+      <c r="K31" s="280"/>
+      <c r="L31" s="280"/>
+      <c r="M31" s="281"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="372" t="s">
+      <c r="A32" s="286" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="370"/>
-      <c r="C32" s="370" t="s">
+      <c r="B32" s="284"/>
+      <c r="C32" s="284" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="370"/>
-      <c r="E32" s="373" t="s">
+      <c r="D32" s="284"/>
+      <c r="E32" s="287" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="374" t="s">
+      <c r="F32" s="288" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="368" t="s">
+      <c r="G32" s="282" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="368"/>
-      <c r="I32" s="368"/>
-      <c r="J32" s="368"/>
-      <c r="K32" s="368"/>
-      <c r="L32" s="370" t="s">
+      <c r="H32" s="282"/>
+      <c r="I32" s="282"/>
+      <c r="J32" s="282"/>
+      <c r="K32" s="282"/>
+      <c r="L32" s="284" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="371"/>
+      <c r="M32" s="285"/>
     </row>
     <row r="33" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
@@ -8908,15 +8924,15 @@
       <c r="D33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="373"/>
-      <c r="F33" s="374"/>
-      <c r="G33" s="369" t="s">
+      <c r="E33" s="287"/>
+      <c r="F33" s="288"/>
+      <c r="G33" s="283" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="369"/>
-      <c r="I33" s="369"/>
-      <c r="J33" s="369"/>
-      <c r="K33" s="369"/>
+      <c r="H33" s="283"/>
+      <c r="I33" s="283"/>
+      <c r="J33" s="283"/>
+      <c r="K33" s="283"/>
       <c r="L33" s="2" t="s">
         <v>14</v>
       </c>
@@ -8925,7 +8941,7 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="105">
+      <c r="A34" s="69">
         <f>E30</f>
         <v>83</v>
       </c>
@@ -8936,7 +8952,7 @@
         <f>F30</f>
         <v>83</v>
       </c>
-      <c r="D34" s="104" t="s">
+      <c r="D34" s="68" t="s">
         <v>60</v>
       </c>
       <c r="E34" s="9">
@@ -8944,449 +8960,449 @@
         <v>83</v>
       </c>
       <c r="F34" s="10"/>
-      <c r="G34" s="285" t="s">
+      <c r="G34" s="199" t="s">
         <v>77</v>
       </c>
-      <c r="H34" s="343"/>
-      <c r="I34" s="343"/>
-      <c r="J34" s="343"/>
-      <c r="K34" s="286"/>
-      <c r="L34" s="106"/>
-      <c r="M34" s="107"/>
+      <c r="H34" s="257"/>
+      <c r="I34" s="257"/>
+      <c r="J34" s="257"/>
+      <c r="K34" s="200"/>
+      <c r="L34" s="70"/>
+      <c r="M34" s="71"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" s="108"/>
+      <c r="A35" s="72"/>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
-      <c r="F35" s="106"/>
-      <c r="G35" s="285"/>
-      <c r="H35" s="343"/>
-      <c r="I35" s="343"/>
-      <c r="J35" s="343"/>
-      <c r="K35" s="286"/>
-      <c r="L35" s="106"/>
-      <c r="M35" s="107"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="199"/>
+      <c r="H35" s="257"/>
+      <c r="I35" s="257"/>
+      <c r="J35" s="257"/>
+      <c r="K35" s="200"/>
+      <c r="L35" s="70"/>
+      <c r="M35" s="71"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" s="108"/>
+      <c r="A36" s="72"/>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
-      <c r="F36" s="106"/>
-      <c r="G36" s="285"/>
-      <c r="H36" s="343"/>
-      <c r="I36" s="343"/>
-      <c r="J36" s="343"/>
-      <c r="K36" s="286"/>
-      <c r="L36" s="106"/>
-      <c r="M36" s="107"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="199"/>
+      <c r="H36" s="257"/>
+      <c r="I36" s="257"/>
+      <c r="J36" s="257"/>
+      <c r="K36" s="200"/>
+      <c r="L36" s="70"/>
+      <c r="M36" s="71"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A37" s="108"/>
+      <c r="A37" s="72"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
-      <c r="F37" s="106"/>
-      <c r="G37" s="285"/>
-      <c r="H37" s="343"/>
-      <c r="I37" s="343"/>
-      <c r="J37" s="343"/>
-      <c r="K37" s="286"/>
-      <c r="L37" s="106"/>
-      <c r="M37" s="107"/>
-      <c r="Q37" s="334"/>
-      <c r="R37" s="334"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="199"/>
+      <c r="H37" s="257"/>
+      <c r="I37" s="257"/>
+      <c r="J37" s="257"/>
+      <c r="K37" s="200"/>
+      <c r="L37" s="70"/>
+      <c r="M37" s="71"/>
+      <c r="Q37" s="248"/>
+      <c r="R37" s="248"/>
       <c r="S37" s="7"/>
-      <c r="T37" s="311"/>
-      <c r="U37" s="311"/>
-      <c r="V37" s="311"/>
+      <c r="T37" s="225"/>
+      <c r="U37" s="225"/>
+      <c r="V37" s="225"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A38" s="108"/>
+      <c r="A38" s="72"/>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
-      <c r="F38" s="106"/>
-      <c r="G38" s="285"/>
-      <c r="H38" s="343"/>
-      <c r="I38" s="343"/>
-      <c r="J38" s="343"/>
-      <c r="K38" s="286"/>
-      <c r="L38" s="106"/>
-      <c r="M38" s="109"/>
-      <c r="Q38" s="334"/>
-      <c r="R38" s="334"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="199"/>
+      <c r="H38" s="257"/>
+      <c r="I38" s="257"/>
+      <c r="J38" s="257"/>
+      <c r="K38" s="200"/>
+      <c r="L38" s="70"/>
+      <c r="M38" s="73"/>
+      <c r="Q38" s="248"/>
+      <c r="R38" s="248"/>
       <c r="S38" s="7"/>
-      <c r="T38" s="311"/>
-      <c r="U38" s="311"/>
-      <c r="V38" s="311"/>
+      <c r="T38" s="225"/>
+      <c r="U38" s="225"/>
+      <c r="V38" s="225"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A39" s="108"/>
+      <c r="A39" s="72"/>
       <c r="B39" s="10"/>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
-      <c r="F39" s="106"/>
-      <c r="G39" s="285"/>
-      <c r="H39" s="343"/>
-      <c r="I39" s="343"/>
-      <c r="J39" s="343"/>
-      <c r="K39" s="286"/>
-      <c r="L39" s="106"/>
-      <c r="M39" s="109"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="199"/>
+      <c r="H39" s="257"/>
+      <c r="I39" s="257"/>
+      <c r="J39" s="257"/>
+      <c r="K39" s="200"/>
+      <c r="L39" s="70"/>
+      <c r="M39" s="73"/>
       <c r="Q39" s="6"/>
       <c r="R39" s="6"/>
-      <c r="S39" s="337"/>
-      <c r="T39" s="311"/>
-      <c r="U39" s="311"/>
-      <c r="V39" s="311"/>
+      <c r="S39" s="251"/>
+      <c r="T39" s="225"/>
+      <c r="U39" s="225"/>
+      <c r="V39" s="225"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A40" s="108"/>
+      <c r="A40" s="72"/>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
       <c r="D40" s="10"/>
       <c r="E40" s="10"/>
-      <c r="F40" s="106"/>
-      <c r="G40" s="285"/>
-      <c r="H40" s="343"/>
-      <c r="I40" s="343"/>
-      <c r="J40" s="343"/>
-      <c r="K40" s="286"/>
-      <c r="L40" s="106"/>
-      <c r="M40" s="107"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="199"/>
+      <c r="H40" s="257"/>
+      <c r="I40" s="257"/>
+      <c r="J40" s="257"/>
+      <c r="K40" s="200"/>
+      <c r="L40" s="70"/>
+      <c r="M40" s="71"/>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
-      <c r="S40" s="337"/>
-      <c r="T40" s="311"/>
-      <c r="U40" s="311"/>
-      <c r="V40" s="311"/>
+      <c r="S40" s="251"/>
+      <c r="T40" s="225"/>
+      <c r="U40" s="225"/>
+      <c r="V40" s="225"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A41" s="108"/>
+      <c r="A41" s="72"/>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
       <c r="D41" s="10"/>
       <c r="E41" s="10"/>
-      <c r="F41" s="106"/>
-      <c r="G41" s="285"/>
-      <c r="H41" s="343"/>
-      <c r="I41" s="343"/>
-      <c r="J41" s="343"/>
-      <c r="K41" s="286"/>
-      <c r="L41" s="106"/>
-      <c r="M41" s="107"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="199"/>
+      <c r="H41" s="257"/>
+      <c r="I41" s="257"/>
+      <c r="J41" s="257"/>
+      <c r="K41" s="200"/>
+      <c r="L41" s="70"/>
+      <c r="M41" s="71"/>
     </row>
     <row r="42" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="110">
+      <c r="A42" s="74">
         <f>SUM(A34:A41)</f>
         <v>83</v>
       </c>
-      <c r="B42" s="111"/>
-      <c r="C42" s="112">
+      <c r="B42" s="75"/>
+      <c r="C42" s="76">
         <f>SUM(C34:C41)</f>
         <v>83</v>
       </c>
-      <c r="D42" s="111"/>
-      <c r="E42" s="112">
+      <c r="D42" s="75"/>
+      <c r="E42" s="76">
         <f>SUM(E34:E41)</f>
         <v>83</v>
       </c>
-      <c r="F42" s="113"/>
-      <c r="G42" s="344" t="s">
+      <c r="F42" s="77"/>
+      <c r="G42" s="258" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="345"/>
-      <c r="I42" s="345"/>
-      <c r="J42" s="345"/>
-      <c r="K42" s="346"/>
-      <c r="L42" s="113"/>
-      <c r="M42" s="114"/>
+      <c r="H42" s="259"/>
+      <c r="I42" s="259"/>
+      <c r="J42" s="259"/>
+      <c r="K42" s="260"/>
+      <c r="L42" s="77"/>
+      <c r="M42" s="78"/>
     </row>
     <row r="43" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="313" t="s">
+      <c r="A43" s="227" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="314"/>
-      <c r="C43" s="314"/>
-      <c r="D43" s="314"/>
-      <c r="E43" s="314"/>
-      <c r="F43" s="314"/>
-      <c r="G43" s="314"/>
-      <c r="H43" s="315"/>
-      <c r="I43" s="355" t="s">
+      <c r="B43" s="228"/>
+      <c r="C43" s="228"/>
+      <c r="D43" s="228"/>
+      <c r="E43" s="228"/>
+      <c r="F43" s="228"/>
+      <c r="G43" s="228"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="269" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="356"/>
-      <c r="K43" s="356"/>
-      <c r="L43" s="356"/>
-      <c r="M43" s="357"/>
+      <c r="J43" s="270"/>
+      <c r="K43" s="270"/>
+      <c r="L43" s="270"/>
+      <c r="M43" s="271"/>
     </row>
     <row r="44" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="316"/>
-      <c r="B44" s="317"/>
-      <c r="C44" s="317"/>
-      <c r="D44" s="317"/>
-      <c r="E44" s="317"/>
-      <c r="F44" s="317"/>
-      <c r="G44" s="317"/>
-      <c r="H44" s="318"/>
-      <c r="I44" s="358"/>
-      <c r="J44" s="359"/>
-      <c r="K44" s="359"/>
-      <c r="L44" s="359"/>
-      <c r="M44" s="360"/>
+      <c r="A44" s="230"/>
+      <c r="B44" s="231"/>
+      <c r="C44" s="231"/>
+      <c r="D44" s="231"/>
+      <c r="E44" s="231"/>
+      <c r="F44" s="231"/>
+      <c r="G44" s="231"/>
+      <c r="H44" s="232"/>
+      <c r="I44" s="272"/>
+      <c r="J44" s="273"/>
+      <c r="K44" s="273"/>
+      <c r="L44" s="273"/>
+      <c r="M44" s="274"/>
     </row>
     <row r="45" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="319" t="s">
+      <c r="A45" s="233" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="320"/>
-      <c r="C45" s="320"/>
-      <c r="D45" s="320"/>
-      <c r="E45" s="320"/>
-      <c r="F45" s="320"/>
-      <c r="G45" s="320"/>
-      <c r="H45" s="321"/>
-      <c r="I45" s="361" t="s">
+      <c r="B45" s="234"/>
+      <c r="C45" s="234"/>
+      <c r="D45" s="234"/>
+      <c r="E45" s="234"/>
+      <c r="F45" s="234"/>
+      <c r="G45" s="234"/>
+      <c r="H45" s="235"/>
+      <c r="I45" s="275" t="s">
         <v>36</v>
       </c>
-      <c r="J45" s="362"/>
-      <c r="K45" s="362"/>
-      <c r="L45" s="362"/>
-      <c r="M45" s="363"/>
+      <c r="J45" s="276"/>
+      <c r="K45" s="276"/>
+      <c r="L45" s="276"/>
+      <c r="M45" s="277"/>
     </row>
     <row r="46" spans="1:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="319" t="s">
+      <c r="A46" s="233" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="320"/>
-      <c r="C46" s="320"/>
-      <c r="D46" s="320"/>
-      <c r="E46" s="320"/>
-      <c r="F46" s="320"/>
-      <c r="G46" s="320"/>
-      <c r="H46" s="321"/>
-      <c r="I46" s="361"/>
-      <c r="J46" s="362"/>
-      <c r="K46" s="362"/>
-      <c r="L46" s="362"/>
-      <c r="M46" s="363"/>
+      <c r="B46" s="234"/>
+      <c r="C46" s="234"/>
+      <c r="D46" s="234"/>
+      <c r="E46" s="234"/>
+      <c r="F46" s="234"/>
+      <c r="G46" s="234"/>
+      <c r="H46" s="235"/>
+      <c r="I46" s="275"/>
+      <c r="J46" s="276"/>
+      <c r="K46" s="276"/>
+      <c r="L46" s="276"/>
+      <c r="M46" s="277"/>
     </row>
     <row r="47" spans="1:22" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="322"/>
-      <c r="B47" s="323"/>
-      <c r="C47" s="323"/>
-      <c r="D47" s="323"/>
-      <c r="E47" s="323"/>
-      <c r="F47" s="323"/>
-      <c r="G47" s="323"/>
-      <c r="H47" s="324"/>
-      <c r="I47" s="308" t="s">
+      <c r="A47" s="236"/>
+      <c r="B47" s="237"/>
+      <c r="C47" s="237"/>
+      <c r="D47" s="237"/>
+      <c r="E47" s="237"/>
+      <c r="F47" s="237"/>
+      <c r="G47" s="237"/>
+      <c r="H47" s="238"/>
+      <c r="I47" s="222" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="309"/>
-      <c r="K47" s="309"/>
-      <c r="L47" s="309"/>
-      <c r="M47" s="310"/>
+      <c r="J47" s="223"/>
+      <c r="K47" s="223"/>
+      <c r="L47" s="223"/>
+      <c r="M47" s="224"/>
     </row>
     <row r="48" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="329" t="s">
+      <c r="A48" s="243" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="330"/>
-      <c r="C48" s="330"/>
-      <c r="D48" s="330"/>
-      <c r="E48" s="330"/>
-      <c r="F48" s="330"/>
-      <c r="G48" s="330"/>
-      <c r="H48" s="330"/>
-      <c r="I48" s="330"/>
-      <c r="J48" s="330"/>
-      <c r="K48" s="330"/>
-      <c r="L48" s="330"/>
-      <c r="M48" s="338"/>
+      <c r="B48" s="244"/>
+      <c r="C48" s="244"/>
+      <c r="D48" s="244"/>
+      <c r="E48" s="244"/>
+      <c r="F48" s="244"/>
+      <c r="G48" s="244"/>
+      <c r="H48" s="244"/>
+      <c r="I48" s="244"/>
+      <c r="J48" s="244"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="244"/>
+      <c r="M48" s="252"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="313" t="s">
+      <c r="A49" s="227" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="314"/>
-      <c r="C49" s="314"/>
-      <c r="D49" s="314"/>
-      <c r="E49" s="314"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="315"/>
-      <c r="I49" s="347" t="s">
+      <c r="B49" s="228"/>
+      <c r="C49" s="228"/>
+      <c r="D49" s="228"/>
+      <c r="E49" s="228"/>
+      <c r="F49" s="228"/>
+      <c r="G49" s="228"/>
+      <c r="H49" s="229"/>
+      <c r="I49" s="261" t="s">
         <v>40</v>
       </c>
-      <c r="J49" s="348"/>
-      <c r="K49" s="348"/>
-      <c r="L49" s="348"/>
-      <c r="M49" s="349"/>
+      <c r="J49" s="262"/>
+      <c r="K49" s="262"/>
+      <c r="L49" s="262"/>
+      <c r="M49" s="263"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="316"/>
-      <c r="B50" s="317"/>
-      <c r="C50" s="317"/>
-      <c r="D50" s="317"/>
-      <c r="E50" s="317"/>
-      <c r="F50" s="317"/>
-      <c r="G50" s="317"/>
-      <c r="H50" s="318"/>
-      <c r="I50" s="350"/>
-      <c r="J50" s="351"/>
-      <c r="K50" s="351"/>
-      <c r="L50" s="351"/>
-      <c r="M50" s="352"/>
+      <c r="A50" s="230"/>
+      <c r="B50" s="231"/>
+      <c r="C50" s="231"/>
+      <c r="D50" s="231"/>
+      <c r="E50" s="231"/>
+      <c r="F50" s="231"/>
+      <c r="G50" s="231"/>
+      <c r="H50" s="232"/>
+      <c r="I50" s="264"/>
+      <c r="J50" s="265"/>
+      <c r="K50" s="265"/>
+      <c r="L50" s="265"/>
+      <c r="M50" s="266"/>
     </row>
     <row r="51" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="353"/>
-      <c r="B51" s="354"/>
-      <c r="C51" s="354"/>
-      <c r="D51" s="354"/>
-      <c r="E51" s="317"/>
-      <c r="F51" s="317"/>
-      <c r="G51" s="317"/>
-      <c r="H51" s="318"/>
-      <c r="I51" s="325" t="s">
+      <c r="A51" s="267"/>
+      <c r="B51" s="268"/>
+      <c r="C51" s="268"/>
+      <c r="D51" s="268"/>
+      <c r="E51" s="231"/>
+      <c r="F51" s="231"/>
+      <c r="G51" s="231"/>
+      <c r="H51" s="232"/>
+      <c r="I51" s="239" t="s">
         <v>41</v>
       </c>
-      <c r="J51" s="326"/>
-      <c r="K51" s="327"/>
-      <c r="L51" s="327"/>
-      <c r="M51" s="328"/>
+      <c r="J51" s="240"/>
+      <c r="K51" s="241"/>
+      <c r="L51" s="241"/>
+      <c r="M51" s="242"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="329" t="s">
+      <c r="A52" s="243" t="s">
         <v>42</v>
       </c>
-      <c r="B52" s="330"/>
-      <c r="C52" s="330"/>
-      <c r="D52" s="330"/>
-      <c r="E52" s="115" t="s">
+      <c r="B52" s="244"/>
+      <c r="C52" s="244"/>
+      <c r="D52" s="244"/>
+      <c r="E52" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="F52" s="116"/>
-      <c r="G52" s="335" t="s">
+      <c r="F52" s="80"/>
+      <c r="G52" s="249" t="s">
         <v>45</v>
       </c>
-      <c r="H52" s="335"/>
-      <c r="I52" s="335"/>
-      <c r="J52" s="336"/>
-      <c r="K52" s="330" t="s">
+      <c r="H52" s="249"/>
+      <c r="I52" s="249"/>
+      <c r="J52" s="250"/>
+      <c r="K52" s="244" t="s">
         <v>50</v>
       </c>
-      <c r="L52" s="330"/>
-      <c r="M52" s="338"/>
+      <c r="L52" s="244"/>
+      <c r="M52" s="252"/>
     </row>
     <row r="53" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="331" t="s">
+      <c r="A53" s="245" t="s">
         <v>43</v>
       </c>
-      <c r="B53" s="332"/>
-      <c r="C53" s="332"/>
-      <c r="D53" s="332"/>
-      <c r="E53" s="98"/>
-      <c r="J53" s="95"/>
-      <c r="K53" s="339" t="s">
+      <c r="B53" s="246"/>
+      <c r="C53" s="246"/>
+      <c r="D53" s="246"/>
+      <c r="E53" s="62"/>
+      <c r="J53" s="59"/>
+      <c r="K53" s="253" t="s">
         <v>52</v>
       </c>
-      <c r="L53" s="339"/>
-      <c r="M53" s="340"/>
+      <c r="L53" s="253"/>
+      <c r="M53" s="254"/>
     </row>
     <row r="54" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="331"/>
-      <c r="B54" s="332"/>
-      <c r="C54" s="332"/>
-      <c r="D54" s="332"/>
-      <c r="E54" s="333" t="s">
+      <c r="A54" s="245"/>
+      <c r="B54" s="246"/>
+      <c r="C54" s="246"/>
+      <c r="D54" s="246"/>
+      <c r="E54" s="247" t="s">
         <v>46</v>
       </c>
-      <c r="F54" s="334"/>
+      <c r="F54" s="248"/>
       <c r="G54" s="7"/>
-      <c r="H54" s="311" t="s">
+      <c r="H54" s="225" t="s">
         <v>46</v>
       </c>
-      <c r="I54" s="311"/>
-      <c r="J54" s="312"/>
-      <c r="K54" s="339"/>
-      <c r="L54" s="339"/>
-      <c r="M54" s="340"/>
+      <c r="I54" s="225"/>
+      <c r="J54" s="226"/>
+      <c r="K54" s="253"/>
+      <c r="L54" s="253"/>
+      <c r="M54" s="254"/>
     </row>
     <row r="55" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="331"/>
-      <c r="B55" s="332"/>
-      <c r="C55" s="332"/>
-      <c r="D55" s="332"/>
-      <c r="E55" s="333" t="s">
+      <c r="A55" s="245"/>
+      <c r="B55" s="246"/>
+      <c r="C55" s="246"/>
+      <c r="D55" s="246"/>
+      <c r="E55" s="247" t="s">
         <v>47</v>
       </c>
-      <c r="F55" s="334"/>
-      <c r="G55" s="334"/>
-      <c r="H55" s="311" t="s">
+      <c r="F55" s="248"/>
+      <c r="G55" s="248"/>
+      <c r="H55" s="225" t="s">
         <v>48</v>
       </c>
-      <c r="I55" s="311"/>
-      <c r="J55" s="312"/>
-      <c r="K55" s="339"/>
-      <c r="L55" s="339"/>
-      <c r="M55" s="340"/>
+      <c r="I55" s="225"/>
+      <c r="J55" s="226"/>
+      <c r="K55" s="253"/>
+      <c r="L55" s="253"/>
+      <c r="M55" s="254"/>
     </row>
     <row r="56" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="98"/>
-      <c r="D56" s="95"/>
-      <c r="E56" s="333"/>
-      <c r="F56" s="334"/>
-      <c r="G56" s="334"/>
-      <c r="H56" s="311"/>
-      <c r="I56" s="311"/>
-      <c r="J56" s="312"/>
-      <c r="K56" s="341" t="s">
+      <c r="A56" s="62"/>
+      <c r="D56" s="59"/>
+      <c r="E56" s="247"/>
+      <c r="F56" s="248"/>
+      <c r="G56" s="248"/>
+      <c r="H56" s="225"/>
+      <c r="I56" s="225"/>
+      <c r="J56" s="226"/>
+      <c r="K56" s="255" t="s">
         <v>51</v>
       </c>
-      <c r="L56" s="341"/>
-      <c r="M56" s="342"/>
+      <c r="L56" s="255"/>
+      <c r="M56" s="256"/>
     </row>
     <row r="57" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="98"/>
-      <c r="D57" s="95"/>
-      <c r="E57" s="333"/>
-      <c r="F57" s="334"/>
+      <c r="A57" s="62"/>
+      <c r="D57" s="59"/>
+      <c r="E57" s="247"/>
+      <c r="F57" s="248"/>
       <c r="G57" s="7"/>
-      <c r="H57" s="311" t="s">
+      <c r="H57" s="225" t="s">
         <v>49</v>
       </c>
-      <c r="I57" s="311"/>
-      <c r="J57" s="312"/>
-      <c r="K57" s="117"/>
-      <c r="L57" s="118"/>
-      <c r="M57" s="119"/>
+      <c r="I57" s="225"/>
+      <c r="J57" s="226"/>
+      <c r="K57" s="81"/>
+      <c r="L57" s="82"/>
+      <c r="M57" s="83"/>
     </row>
     <row r="58" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="120"/>
-      <c r="B58" s="422">
+      <c r="A58" s="84"/>
+      <c r="B58" s="336">
         <f>B1</f>
         <v>45877</v>
       </c>
-      <c r="C58" s="422"/>
-      <c r="D58" s="87"/>
-      <c r="E58" s="305"/>
-      <c r="F58" s="306"/>
-      <c r="G58" s="306"/>
-      <c r="H58" s="306"/>
-      <c r="I58" s="306"/>
-      <c r="J58" s="307"/>
-      <c r="K58" s="121"/>
-      <c r="L58" s="122"/>
-      <c r="M58" s="123"/>
+      <c r="C58" s="336"/>
+      <c r="D58" s="51"/>
+      <c r="E58" s="219"/>
+      <c r="F58" s="220"/>
+      <c r="G58" s="220"/>
+      <c r="H58" s="220"/>
+      <c r="I58" s="220"/>
+      <c r="J58" s="221"/>
+      <c r="K58" s="85"/>
+      <c r="L58" s="86"/>
+      <c r="M58" s="87"/>
     </row>
     <row r="59" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3"/>
@@ -9546,25 +9562,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="33" t="s">
         <v>191</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="E1" s="33" t="s">
         <v>192</v>
       </c>
-      <c r="H1" s="125" t="s">
+      <c r="H1" s="89" t="s">
         <v>226</v>
       </c>
-      <c r="I1" s="125" t="s">
+      <c r="I1" s="89" t="s">
         <v>227</v>
       </c>
     </row>
@@ -9584,10 +9600,10 @@
       <c r="E2">
         <v>92336</v>
       </c>
-      <c r="H2" s="125" t="s">
+      <c r="H2" s="89" t="s">
         <v>230</v>
       </c>
-      <c r="I2" s="125" t="s">
+      <c r="I2" s="89" t="s">
         <v>231</v>
       </c>
     </row>
@@ -9607,10 +9623,10 @@
       <c r="E3">
         <v>81001</v>
       </c>
-      <c r="H3" s="125" t="s">
+      <c r="H3" s="89" t="s">
         <v>228</v>
       </c>
-      <c r="I3" s="125">
+      <c r="I3" s="89">
         <v>10285609</v>
       </c>
     </row>
@@ -9630,15 +9646,15 @@
       <c r="E4">
         <v>24477</v>
       </c>
-      <c r="H4" s="125" t="s">
+      <c r="H4" s="89" t="s">
         <v>229</v>
       </c>
-      <c r="I4" s="126">
+      <c r="I4" s="90">
         <v>523953410</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="33" t="s">
         <v>90</v>
       </c>
       <c r="B5" t="s">
@@ -9653,10 +9669,10 @@
       <c r="E5">
         <v>55432</v>
       </c>
-      <c r="H5" s="125" t="s">
+      <c r="H5" s="89" t="s">
         <v>236</v>
       </c>
-      <c r="I5" s="127">
+      <c r="I5" s="91">
         <v>59642884</v>
       </c>
     </row>
@@ -10113,7 +10129,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="33" t="s">
         <v>90</v>
       </c>
       <c r="B3" t="s">
@@ -10519,7 +10535,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B32" s="52" t="s">
+      <c r="B32" s="33" t="s">
         <v>22</v>
       </c>
       <c r="C32">

--- a/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
+++ b/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Procomm\Documents\GitHub\Acumatica_Customizations_and_Packages\Istar_Development\Projects\BOL_Generation\Code\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1157327F-B2F9-41B3-BBF0-5010D1900D06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F3C4FF-F131-48B9-8BEB-8433480A7F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3705" yWindow="5430" windowWidth="28800" windowHeight="15345" xr2:uid="{888CA347-7849-4038-B8EE-FAC87BA1B844}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{888CA347-7849-4038-B8EE-FAC87BA1B844}"/>
   </bookViews>
   <sheets>
-    <sheet name="BOL" sheetId="3" r:id="rId1"/>
-    <sheet name="Supplimental Master BOL" sheetId="4" r:id="rId2"/>
-    <sheet name="Supplemental BOL" sheetId="1" r:id="rId3"/>
+    <sheet name="MasterBOL" sheetId="3" r:id="rId1"/>
+    <sheet name="Supplemental_Master_BOL" sheetId="4" r:id="rId2"/>
+    <sheet name="Supplemental_BOL" sheetId="1" r:id="rId3"/>
     <sheet name="ADDRESS" sheetId="5" r:id="rId4"/>
     <sheet name="Customer Order Info" sheetId="6" r:id="rId5"/>
   </sheets>
@@ -1443,7 +1443,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="447">
+  <cellXfs count="442">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1473,9 +1473,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1494,9 +1491,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
@@ -1608,7 +1602,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1618,869 +1611,11 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="32" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2489,6 +1624,378 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="8" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2498,153 +2005,631 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="32" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="8" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4998,1168 +4983,1256 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="357" t="s">
+      <c r="A1" s="270" t="s">
         <v>237</v>
       </c>
-      <c r="B1" s="358"/>
-      <c r="C1" s="109" t="s">
+      <c r="B1" s="271"/>
+      <c r="C1" s="272" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="110" t="s">
+      <c r="D1" s="272"/>
+      <c r="E1" s="272"/>
+      <c r="F1" s="272"/>
+      <c r="G1" s="272"/>
+      <c r="H1" s="272"/>
+      <c r="I1" s="272"/>
+      <c r="J1" s="272"/>
+      <c r="K1" s="272"/>
+      <c r="L1" s="273" t="s">
         <v>62</v>
       </c>
-      <c r="M1" s="111"/>
+      <c r="M1" s="274"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="243" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="105"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="106"/>
-      <c r="I2" s="359" t="s">
+      <c r="B2" s="244"/>
+      <c r="C2" s="244"/>
+      <c r="D2" s="244"/>
+      <c r="E2" s="244"/>
+      <c r="F2" s="244"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245"/>
+      <c r="I2" s="275" t="s">
         <v>232</v>
       </c>
-      <c r="J2" s="360"/>
-      <c r="K2" s="360"/>
-      <c r="L2" s="360"/>
-      <c r="M2" s="361"/>
+      <c r="J2" s="276"/>
+      <c r="K2" s="276"/>
+      <c r="L2" s="276"/>
+      <c r="M2" s="277"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="255" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="365"/>
-      <c r="J3" s="366"/>
-      <c r="K3" s="366"/>
-      <c r="L3" s="366"/>
-      <c r="M3" s="367"/>
+      <c r="B3" s="256"/>
+      <c r="C3" s="256"/>
+      <c r="D3" s="256"/>
+      <c r="E3" s="256"/>
+      <c r="F3" s="256"/>
+      <c r="G3" s="256"/>
+      <c r="H3" s="257"/>
+      <c r="I3" s="278"/>
+      <c r="J3" s="279"/>
+      <c r="K3" s="279"/>
+      <c r="L3" s="279"/>
+      <c r="M3" s="280"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="92" t="s">
+      <c r="A4" s="255" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="93"/>
-      <c r="C4" s="93"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="95"/>
-      <c r="J4" s="96"/>
-      <c r="K4" s="96"/>
-      <c r="L4" s="96"/>
-      <c r="M4" s="97"/>
+      <c r="B4" s="256"/>
+      <c r="C4" s="256"/>
+      <c r="D4" s="256"/>
+      <c r="E4" s="256"/>
+      <c r="F4" s="256"/>
+      <c r="G4" s="256"/>
+      <c r="H4" s="257"/>
+      <c r="I4" s="261"/>
+      <c r="J4" s="262"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
+      <c r="M4" s="263"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="255" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="93"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="95"/>
-      <c r="J5" s="96"/>
-      <c r="K5" s="96"/>
-      <c r="L5" s="96"/>
-      <c r="M5" s="97"/>
+      <c r="B5" s="256"/>
+      <c r="C5" s="256"/>
+      <c r="D5" s="256"/>
+      <c r="E5" s="256"/>
+      <c r="F5" s="256"/>
+      <c r="G5" s="256"/>
+      <c r="H5" s="257"/>
+      <c r="I5" s="261"/>
+      <c r="J5" s="262"/>
+      <c r="K5" s="262"/>
+      <c r="L5" s="262"/>
+      <c r="M5" s="263"/>
     </row>
     <row r="6" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="101" t="s">
+      <c r="A6" s="267" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="103" t="s">
+      <c r="B6" s="268"/>
+      <c r="C6" s="268"/>
+      <c r="D6" s="268"/>
+      <c r="E6" s="268"/>
+      <c r="F6" s="269" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="103"/>
+      <c r="G6" s="269"/>
       <c r="H6" s="12"/>
-      <c r="I6" s="98"/>
-      <c r="J6" s="99"/>
-      <c r="K6" s="99"/>
-      <c r="L6" s="99"/>
-      <c r="M6" s="100"/>
+      <c r="I6" s="264"/>
+      <c r="J6" s="265"/>
+      <c r="K6" s="265"/>
+      <c r="L6" s="265"/>
+      <c r="M6" s="266"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="104" t="s">
+      <c r="A7" s="243" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="105"/>
-      <c r="C7" s="105"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="378" t="s">
+      <c r="B7" s="244"/>
+      <c r="C7" s="244"/>
+      <c r="D7" s="244"/>
+      <c r="E7" s="244"/>
+      <c r="F7" s="244"/>
+      <c r="G7" s="244"/>
+      <c r="H7" s="245"/>
+      <c r="I7" s="90" t="s">
         <v>233</v>
       </c>
-      <c r="J7" s="379"/>
-      <c r="K7" s="380" t="str">
+      <c r="J7" s="91"/>
+      <c r="K7" s="92" t="str">
         <f>ADDRESS!I1</f>
         <v>CH Robinson</v>
       </c>
-      <c r="L7" s="379"/>
-      <c r="M7" s="381"/>
+      <c r="L7" s="91"/>
+      <c r="M7" s="93"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="362" t="s">
+      <c r="A8" s="258" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="363"/>
-      <c r="C8" s="363"/>
-      <c r="D8" s="363"/>
-      <c r="E8" s="133" t="s">
+      <c r="B8" s="259"/>
+      <c r="C8" s="259"/>
+      <c r="D8" s="259"/>
+      <c r="E8" s="139" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="133"/>
-      <c r="G8" s="133"/>
-      <c r="H8" s="382"/>
-      <c r="I8" s="362" t="s">
+      <c r="F8" s="139"/>
+      <c r="G8" s="139"/>
+      <c r="H8" s="140"/>
+      <c r="I8" s="258" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="363"/>
-      <c r="K8" s="363"/>
-      <c r="L8" s="363"/>
-      <c r="M8" s="364"/>
+      <c r="J8" s="259"/>
+      <c r="K8" s="259"/>
+      <c r="L8" s="259"/>
+      <c r="M8" s="260"/>
     </row>
     <row r="9" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="362" t="s">
+      <c r="A9" s="258" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="363"/>
-      <c r="C9" s="363"/>
-      <c r="D9" s="363"/>
-      <c r="E9" s="363"/>
-      <c r="F9" s="363"/>
-      <c r="G9" s="363"/>
-      <c r="H9" s="364"/>
-      <c r="I9" s="383" t="s">
+      <c r="B9" s="259"/>
+      <c r="C9" s="259"/>
+      <c r="D9" s="259"/>
+      <c r="E9" s="259"/>
+      <c r="F9" s="259"/>
+      <c r="G9" s="259"/>
+      <c r="H9" s="260"/>
+      <c r="I9" s="94" t="s">
         <v>74</v>
       </c>
-      <c r="J9" s="384"/>
-      <c r="K9" s="384">
+      <c r="J9" s="95"/>
+      <c r="K9" s="95">
         <f>ADDRESS!I3</f>
         <v>10285609</v>
       </c>
-      <c r="L9" s="384"/>
-      <c r="M9" s="374"/>
+      <c r="L9" s="95"/>
+      <c r="M9" s="89"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="362" t="s">
+      <c r="A10" s="258" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="363"/>
-      <c r="C10" s="363"/>
-      <c r="D10" s="363"/>
-      <c r="E10" s="363"/>
-      <c r="F10" s="363"/>
-      <c r="G10" s="363"/>
-      <c r="H10" s="364"/>
-      <c r="I10" s="385" t="s">
+      <c r="B10" s="259"/>
+      <c r="C10" s="259"/>
+      <c r="D10" s="259"/>
+      <c r="E10" s="259"/>
+      <c r="F10" s="259"/>
+      <c r="G10" s="259"/>
+      <c r="H10" s="260"/>
+      <c r="I10" s="96" t="s">
         <v>234</v>
       </c>
-      <c r="J10" s="386" t="str">
+      <c r="J10" s="97" t="str">
         <f>ADDRESS!I2</f>
         <v>RBTW</v>
       </c>
-      <c r="K10" s="386"/>
-      <c r="L10" s="386"/>
-      <c r="M10" s="387"/>
+      <c r="K10" s="97"/>
+      <c r="L10" s="97"/>
+      <c r="M10" s="98"/>
     </row>
     <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="371" t="s">
+      <c r="A11" s="240" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="372"/>
-      <c r="C11" s="372"/>
-      <c r="D11" s="372"/>
-      <c r="E11" s="372"/>
-      <c r="F11" s="373" t="s">
+      <c r="B11" s="241"/>
+      <c r="C11" s="241"/>
+      <c r="D11" s="241"/>
+      <c r="E11" s="241"/>
+      <c r="F11" s="242" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="373"/>
-      <c r="H11" s="374"/>
-      <c r="I11" s="388" t="s">
+      <c r="G11" s="242"/>
+      <c r="H11" s="89"/>
+      <c r="I11" s="99" t="s">
         <v>235</v>
       </c>
-      <c r="J11" s="389"/>
-      <c r="K11" s="389">
+      <c r="J11" s="100"/>
+      <c r="K11" s="100">
         <f>ADDRESS!I4</f>
         <v>523953410</v>
       </c>
-      <c r="L11" s="389"/>
-      <c r="M11" s="390"/>
+      <c r="L11" s="100"/>
+      <c r="M11" s="101"/>
     </row>
     <row r="12" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="104" t="s">
+      <c r="A12" s="243" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="105"/>
-      <c r="C12" s="105"/>
-      <c r="D12" s="105"/>
-      <c r="E12" s="105"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="106"/>
-      <c r="I12" s="368"/>
-      <c r="J12" s="369"/>
-      <c r="K12" s="369"/>
-      <c r="L12" s="369"/>
-      <c r="M12" s="370"/>
+      <c r="B12" s="244"/>
+      <c r="C12" s="244"/>
+      <c r="D12" s="244"/>
+      <c r="E12" s="244"/>
+      <c r="F12" s="244"/>
+      <c r="G12" s="244"/>
+      <c r="H12" s="245"/>
+      <c r="I12" s="246"/>
+      <c r="J12" s="247"/>
+      <c r="K12" s="247"/>
+      <c r="L12" s="247"/>
+      <c r="M12" s="248"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="112" t="s">
+      <c r="A13" s="252" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="113"/>
-      <c r="C13" s="113"/>
-      <c r="D13" s="113"/>
-      <c r="E13" s="113"/>
-      <c r="F13" s="113"/>
-      <c r="G13" s="113"/>
-      <c r="H13" s="114"/>
-      <c r="I13" s="368"/>
-      <c r="J13" s="369"/>
-      <c r="K13" s="369"/>
-      <c r="L13" s="369"/>
-      <c r="M13" s="370"/>
+      <c r="B13" s="253"/>
+      <c r="C13" s="253"/>
+      <c r="D13" s="253"/>
+      <c r="E13" s="253"/>
+      <c r="F13" s="253"/>
+      <c r="G13" s="253"/>
+      <c r="H13" s="254"/>
+      <c r="I13" s="246"/>
+      <c r="J13" s="247"/>
+      <c r="K13" s="247"/>
+      <c r="L13" s="247"/>
+      <c r="M13" s="248"/>
     </row>
     <row r="14" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="92" t="s">
+      <c r="A14" s="255" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="93"/>
-      <c r="C14" s="93"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="93"/>
-      <c r="F14" s="93"/>
-      <c r="G14" s="93"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="375"/>
-      <c r="J14" s="376"/>
-      <c r="K14" s="376"/>
-      <c r="L14" s="376"/>
-      <c r="M14" s="377"/>
+      <c r="B14" s="256"/>
+      <c r="C14" s="256"/>
+      <c r="D14" s="256"/>
+      <c r="E14" s="256"/>
+      <c r="F14" s="256"/>
+      <c r="G14" s="256"/>
+      <c r="H14" s="257"/>
+      <c r="I14" s="249"/>
+      <c r="J14" s="250"/>
+      <c r="K14" s="250"/>
+      <c r="L14" s="250"/>
+      <c r="M14" s="251"/>
     </row>
     <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="130" t="s">
+      <c r="A15" s="228" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="131"/>
-      <c r="C15" s="131"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="131"/>
-      <c r="F15" s="131"/>
-      <c r="G15" s="131"/>
-      <c r="H15" s="131"/>
-      <c r="I15" s="391" t="s">
+      <c r="B15" s="229"/>
+      <c r="C15" s="229"/>
+      <c r="D15" s="229"/>
+      <c r="E15" s="229"/>
+      <c r="F15" s="229"/>
+      <c r="G15" s="229"/>
+      <c r="H15" s="229"/>
+      <c r="I15" s="230" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="392"/>
-      <c r="K15" s="392"/>
-      <c r="L15" s="392"/>
-      <c r="M15" s="393"/>
+      <c r="J15" s="231"/>
+      <c r="K15" s="231"/>
+      <c r="L15" s="231"/>
+      <c r="M15" s="232"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="394" t="s">
+      <c r="A16" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="395"/>
-      <c r="C16" s="395"/>
-      <c r="D16" s="395"/>
-      <c r="E16" s="395"/>
-      <c r="F16" s="396">
+      <c r="B16" s="103"/>
+      <c r="C16" s="103"/>
+      <c r="D16" s="103"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="131">
         <f>ADDRESS!I5</f>
         <v>59642884</v>
       </c>
-      <c r="G16" s="396"/>
-      <c r="H16" s="397"/>
-      <c r="I16" s="398" t="s">
+      <c r="G16" s="131"/>
+      <c r="H16" s="132"/>
+      <c r="I16" s="233" t="s">
         <v>61</v>
       </c>
-      <c r="J16" s="399"/>
-      <c r="K16" s="399"/>
-      <c r="L16" s="399"/>
-      <c r="M16" s="400"/>
+      <c r="J16" s="234"/>
+      <c r="K16" s="234"/>
+      <c r="L16" s="234"/>
+      <c r="M16" s="235"/>
     </row>
     <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="401"/>
-      <c r="B17" s="402"/>
-      <c r="C17" s="402"/>
-      <c r="D17" s="402"/>
-      <c r="E17" s="402"/>
-      <c r="F17" s="402"/>
-      <c r="G17" s="402"/>
-      <c r="H17" s="403"/>
-      <c r="I17" s="132"/>
-      <c r="J17" s="133"/>
-      <c r="K17" s="134" t="s">
+      <c r="A17" s="104"/>
+      <c r="B17" s="105"/>
+      <c r="C17" s="105"/>
+      <c r="D17" s="105"/>
+      <c r="E17" s="105"/>
+      <c r="F17" s="105"/>
+      <c r="G17" s="105"/>
+      <c r="H17" s="106"/>
+      <c r="I17" s="138"/>
+      <c r="J17" s="139"/>
+      <c r="K17" s="236" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="134"/>
-      <c r="M17" s="135"/>
+      <c r="L17" s="236"/>
+      <c r="M17" s="237"/>
     </row>
     <row r="18" spans="1:13" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="401"/>
-      <c r="B18" s="402"/>
-      <c r="C18" s="402"/>
-      <c r="D18" s="402"/>
-      <c r="E18" s="402"/>
-      <c r="F18" s="402"/>
-      <c r="G18" s="402"/>
-      <c r="H18" s="403"/>
-      <c r="I18" s="138" t="s">
+      <c r="A18" s="104"/>
+      <c r="B18" s="105"/>
+      <c r="C18" s="105"/>
+      <c r="D18" s="105"/>
+      <c r="E18" s="105"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="105"/>
+      <c r="H18" s="106"/>
+      <c r="I18" s="128" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="139"/>
-      <c r="K18" s="136"/>
-      <c r="L18" s="136"/>
-      <c r="M18" s="137"/>
+      <c r="J18" s="129"/>
+      <c r="K18" s="238"/>
+      <c r="L18" s="238"/>
+      <c r="M18" s="239"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="115" t="s">
+      <c r="A19" s="203" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="116"/>
-      <c r="C19" s="116"/>
-      <c r="D19" s="116"/>
-      <c r="E19" s="116"/>
-      <c r="F19" s="116"/>
-      <c r="G19" s="116"/>
-      <c r="H19" s="116"/>
-      <c r="I19" s="116"/>
-      <c r="J19" s="116"/>
-      <c r="K19" s="116"/>
-      <c r="L19" s="116"/>
-      <c r="M19" s="117"/>
+      <c r="B19" s="204"/>
+      <c r="C19" s="204"/>
+      <c r="D19" s="204"/>
+      <c r="E19" s="204"/>
+      <c r="F19" s="204"/>
+      <c r="G19" s="204"/>
+      <c r="H19" s="204"/>
+      <c r="I19" s="204"/>
+      <c r="J19" s="204"/>
+      <c r="K19" s="204"/>
+      <c r="L19" s="204"/>
+      <c r="M19" s="205"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="118" t="s">
+      <c r="A20" s="216" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="119"/>
-      <c r="C20" s="119"/>
-      <c r="D20" s="119"/>
-      <c r="E20" s="119" t="s">
+      <c r="B20" s="217"/>
+      <c r="C20" s="217"/>
+      <c r="D20" s="217"/>
+      <c r="E20" s="217" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="119" t="s">
+      <c r="F20" s="217" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="119"/>
-      <c r="H20" s="120" t="s">
+      <c r="G20" s="217"/>
+      <c r="H20" s="218" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="121"/>
-      <c r="J20" s="122" t="s">
+      <c r="I20" s="219"/>
+      <c r="J20" s="220" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="123"/>
-      <c r="L20" s="123"/>
-      <c r="M20" s="124"/>
+      <c r="K20" s="221"/>
+      <c r="L20" s="221"/>
+      <c r="M20" s="222"/>
     </row>
     <row r="21" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="118"/>
-      <c r="B21" s="119"/>
-      <c r="C21" s="119"/>
-      <c r="D21" s="119"/>
-      <c r="E21" s="119"/>
-      <c r="F21" s="119"/>
-      <c r="G21" s="119"/>
-      <c r="H21" s="128" t="s">
+      <c r="A21" s="216"/>
+      <c r="B21" s="217"/>
+      <c r="C21" s="217"/>
+      <c r="D21" s="217"/>
+      <c r="E21" s="217"/>
+      <c r="F21" s="217"/>
+      <c r="G21" s="217"/>
+      <c r="H21" s="226" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="129"/>
-      <c r="J21" s="125"/>
-      <c r="K21" s="126"/>
-      <c r="L21" s="126"/>
-      <c r="M21" s="127"/>
+      <c r="I21" s="227"/>
+      <c r="J21" s="223"/>
+      <c r="K21" s="224"/>
+      <c r="L21" s="224"/>
+      <c r="M21" s="225"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="404"/>
-      <c r="B22" s="404"/>
-      <c r="C22" s="404"/>
-      <c r="D22" s="405"/>
-      <c r="E22" s="406">
+      <c r="A22" s="212"/>
+      <c r="B22" s="212"/>
+      <c r="C22" s="212"/>
+      <c r="D22" s="213"/>
+      <c r="E22" s="107">
         <v>40</v>
       </c>
-      <c r="F22" s="407">
+      <c r="F22" s="214">
         <v>40</v>
       </c>
-      <c r="G22" s="407"/>
-      <c r="H22" s="408" t="s">
+      <c r="G22" s="214"/>
+      <c r="H22" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I22" s="408" t="s">
+      <c r="I22" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="142"/>
-      <c r="K22" s="142"/>
-      <c r="L22" s="142"/>
-      <c r="M22" s="143"/>
+      <c r="J22" s="200"/>
+      <c r="K22" s="200"/>
+      <c r="L22" s="200"/>
+      <c r="M22" s="215"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="404"/>
-      <c r="B23" s="404"/>
-      <c r="C23" s="404"/>
-      <c r="D23" s="405"/>
-      <c r="E23" s="406">
+      <c r="A23" s="212"/>
+      <c r="B23" s="212"/>
+      <c r="C23" s="212"/>
+      <c r="D23" s="213"/>
+      <c r="E23" s="107">
         <v>38</v>
       </c>
-      <c r="F23" s="407">
+      <c r="F23" s="214">
         <v>38</v>
       </c>
-      <c r="G23" s="407"/>
-      <c r="H23" s="408" t="s">
+      <c r="G23" s="214"/>
+      <c r="H23" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I23" s="408" t="s">
+      <c r="I23" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="142"/>
-      <c r="K23" s="142"/>
-      <c r="L23" s="142"/>
-      <c r="M23" s="143"/>
+      <c r="J23" s="200"/>
+      <c r="K23" s="200"/>
+      <c r="L23" s="200"/>
+      <c r="M23" s="215"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="404"/>
-      <c r="B24" s="404"/>
-      <c r="C24" s="404"/>
-      <c r="D24" s="405"/>
-      <c r="E24" s="406">
+      <c r="A24" s="212"/>
+      <c r="B24" s="212"/>
+      <c r="C24" s="212"/>
+      <c r="D24" s="213"/>
+      <c r="E24" s="107">
         <v>59</v>
       </c>
-      <c r="F24" s="407">
+      <c r="F24" s="214">
         <v>59</v>
       </c>
-      <c r="G24" s="407"/>
-      <c r="H24" s="408" t="s">
+      <c r="G24" s="214"/>
+      <c r="H24" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I24" s="408" t="s">
+      <c r="I24" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="142"/>
-      <c r="K24" s="142"/>
-      <c r="L24" s="142"/>
-      <c r="M24" s="143"/>
+      <c r="J24" s="200"/>
+      <c r="K24" s="200"/>
+      <c r="L24" s="200"/>
+      <c r="M24" s="215"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="404"/>
-      <c r="B25" s="404"/>
-      <c r="C25" s="404"/>
-      <c r="D25" s="405"/>
-      <c r="E25" s="406">
+      <c r="A25" s="212"/>
+      <c r="B25" s="212"/>
+      <c r="C25" s="212"/>
+      <c r="D25" s="213"/>
+      <c r="E25" s="107">
         <v>81</v>
       </c>
-      <c r="F25" s="407">
+      <c r="F25" s="214">
         <v>81</v>
       </c>
-      <c r="G25" s="407"/>
-      <c r="H25" s="408" t="s">
+      <c r="G25" s="214"/>
+      <c r="H25" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I25" s="408" t="s">
+      <c r="I25" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="142"/>
-      <c r="K25" s="142"/>
-      <c r="L25" s="142"/>
-      <c r="M25" s="143"/>
+      <c r="J25" s="200"/>
+      <c r="K25" s="200"/>
+      <c r="L25" s="200"/>
+      <c r="M25" s="215"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="404"/>
-      <c r="B26" s="404"/>
-      <c r="C26" s="404"/>
-      <c r="D26" s="405"/>
-      <c r="E26" s="406">
+      <c r="A26" s="212"/>
+      <c r="B26" s="212"/>
+      <c r="C26" s="212"/>
+      <c r="D26" s="213"/>
+      <c r="E26" s="107">
         <v>70</v>
       </c>
-      <c r="F26" s="407">
+      <c r="F26" s="214">
         <v>70</v>
       </c>
-      <c r="G26" s="407"/>
-      <c r="H26" s="408" t="s">
+      <c r="G26" s="214"/>
+      <c r="H26" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I26" s="408" t="s">
+      <c r="I26" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="142"/>
-      <c r="K26" s="142"/>
-      <c r="L26" s="142"/>
-      <c r="M26" s="143"/>
+      <c r="J26" s="200"/>
+      <c r="K26" s="200"/>
+      <c r="L26" s="200"/>
+      <c r="M26" s="215"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="404"/>
-      <c r="B27" s="404"/>
-      <c r="C27" s="404"/>
-      <c r="D27" s="405"/>
-      <c r="E27" s="406">
+      <c r="A27" s="212"/>
+      <c r="B27" s="212"/>
+      <c r="C27" s="212"/>
+      <c r="D27" s="213"/>
+      <c r="E27" s="107">
         <v>62</v>
       </c>
-      <c r="F27" s="407">
+      <c r="F27" s="214">
         <v>62</v>
       </c>
-      <c r="G27" s="407"/>
-      <c r="H27" s="408" t="s">
+      <c r="G27" s="214"/>
+      <c r="H27" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I27" s="408" t="s">
+      <c r="I27" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J27" s="142"/>
-      <c r="K27" s="142"/>
-      <c r="L27" s="142"/>
-      <c r="M27" s="143"/>
+      <c r="J27" s="200"/>
+      <c r="K27" s="200"/>
+      <c r="L27" s="200"/>
+      <c r="M27" s="215"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="404"/>
-      <c r="B28" s="404"/>
-      <c r="C28" s="404"/>
-      <c r="D28" s="405"/>
-      <c r="E28" s="406">
+      <c r="A28" s="212"/>
+      <c r="B28" s="212"/>
+      <c r="C28" s="212"/>
+      <c r="D28" s="213"/>
+      <c r="E28" s="107">
         <v>66</v>
       </c>
-      <c r="F28" s="407">
+      <c r="F28" s="214">
         <v>66</v>
       </c>
-      <c r="G28" s="407"/>
-      <c r="H28" s="408" t="s">
+      <c r="G28" s="214"/>
+      <c r="H28" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="408" t="s">
+      <c r="I28" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J28" s="142"/>
-      <c r="K28" s="142"/>
-      <c r="L28" s="142"/>
-      <c r="M28" s="143"/>
+      <c r="J28" s="200"/>
+      <c r="K28" s="200"/>
+      <c r="L28" s="200"/>
+      <c r="M28" s="215"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="404"/>
-      <c r="B29" s="404"/>
-      <c r="C29" s="404"/>
-      <c r="D29" s="405"/>
-      <c r="E29" s="406">
+      <c r="A29" s="212"/>
+      <c r="B29" s="212"/>
+      <c r="C29" s="212"/>
+      <c r="D29" s="213"/>
+      <c r="E29" s="107">
         <v>65</v>
       </c>
-      <c r="F29" s="407">
+      <c r="F29" s="214">
         <v>65</v>
       </c>
-      <c r="G29" s="407"/>
-      <c r="H29" s="408" t="s">
+      <c r="G29" s="214"/>
+      <c r="H29" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I29" s="408" t="s">
+      <c r="I29" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J29" s="142"/>
-      <c r="K29" s="142"/>
-      <c r="L29" s="142"/>
-      <c r="M29" s="143"/>
+      <c r="J29" s="200"/>
+      <c r="K29" s="200"/>
+      <c r="L29" s="200"/>
+      <c r="M29" s="215"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="146" t="s">
+      <c r="A30" s="197" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="147"/>
-      <c r="C30" s="147"/>
-      <c r="D30" s="147"/>
-      <c r="E30" s="15">
-        <f>SUM(E22:E29,'Supplimental Master BOL'!E5:E25)</f>
+      <c r="B30" s="198"/>
+      <c r="C30" s="198"/>
+      <c r="D30" s="198"/>
+      <c r="E30" s="14">
+        <f>SUM(E22:E29,Supplemental_Master_BOL!E5:E25)</f>
         <v>1688</v>
       </c>
-      <c r="F30" s="148">
-        <f>SUM(F22:G29,'Supplimental Master BOL'!F5:G25)</f>
+      <c r="F30" s="199">
+        <f>SUM(F22:G29,Supplemental_Master_BOL!F5:G25)</f>
         <v>1688</v>
       </c>
-      <c r="G30" s="142"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="149"/>
-      <c r="K30" s="149"/>
-      <c r="L30" s="149"/>
-      <c r="M30" s="150"/>
+      <c r="G30" s="200"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="201"/>
+      <c r="K30" s="201"/>
+      <c r="L30" s="201"/>
+      <c r="M30" s="202"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="115" t="s">
+      <c r="A31" s="203" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="116"/>
-      <c r="C31" s="116"/>
-      <c r="D31" s="116"/>
-      <c r="E31" s="116"/>
-      <c r="F31" s="116"/>
-      <c r="G31" s="116"/>
-      <c r="H31" s="116"/>
-      <c r="I31" s="116"/>
-      <c r="J31" s="116"/>
-      <c r="K31" s="116"/>
-      <c r="L31" s="116"/>
-      <c r="M31" s="117"/>
+      <c r="B31" s="204"/>
+      <c r="C31" s="204"/>
+      <c r="D31" s="204"/>
+      <c r="E31" s="204"/>
+      <c r="F31" s="204"/>
+      <c r="G31" s="204"/>
+      <c r="H31" s="204"/>
+      <c r="I31" s="204"/>
+      <c r="J31" s="204"/>
+      <c r="K31" s="204"/>
+      <c r="L31" s="204"/>
+      <c r="M31" s="205"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="151" t="s">
+      <c r="A32" s="206" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="152"/>
-      <c r="C32" s="152" t="s">
+      <c r="B32" s="207"/>
+      <c r="C32" s="207" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="152"/>
-      <c r="E32" s="153" t="s">
+      <c r="D32" s="207"/>
+      <c r="E32" s="208" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="154" t="s">
+      <c r="F32" s="209" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="155" t="s">
+      <c r="G32" s="210" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="155"/>
-      <c r="I32" s="155"/>
-      <c r="J32" s="155"/>
-      <c r="K32" s="155"/>
-      <c r="L32" s="152" t="s">
+      <c r="H32" s="210"/>
+      <c r="I32" s="210"/>
+      <c r="J32" s="210"/>
+      <c r="K32" s="210"/>
+      <c r="L32" s="207" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="156"/>
+      <c r="M32" s="211"/>
     </row>
     <row r="33" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="D33" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="153"/>
-      <c r="F33" s="154"/>
-      <c r="G33" s="144" t="s">
+      <c r="E33" s="208"/>
+      <c r="F33" s="209"/>
+      <c r="G33" s="196" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="144"/>
-      <c r="I33" s="144"/>
-      <c r="J33" s="144"/>
-      <c r="K33" s="144"/>
-      <c r="L33" s="19" t="s">
+      <c r="H33" s="196"/>
+      <c r="I33" s="196"/>
+      <c r="J33" s="196"/>
+      <c r="K33" s="196"/>
+      <c r="L33" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="M33" s="20" t="s">
+      <c r="M33" s="19" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="411">
+      <c r="A34" s="111">
         <v>6</v>
       </c>
-      <c r="B34" s="408" t="s">
+      <c r="B34" s="108" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="409">
+      <c r="C34" s="109">
         <v>1688</v>
       </c>
-      <c r="D34" s="408" t="s">
+      <c r="D34" s="108" t="s">
         <v>60</v>
       </c>
-      <c r="E34" s="409">
+      <c r="E34" s="109">
         <v>6698</v>
       </c>
-      <c r="F34" s="408"/>
-      <c r="G34" s="412" t="s">
+      <c r="F34" s="108"/>
+      <c r="G34" s="169" t="s">
         <v>70</v>
       </c>
-      <c r="H34" s="413"/>
-      <c r="I34" s="413"/>
-      <c r="J34" s="413"/>
-      <c r="K34" s="414"/>
-      <c r="L34" s="22"/>
-      <c r="M34" s="23"/>
+      <c r="H34" s="170"/>
+      <c r="I34" s="170"/>
+      <c r="J34" s="170"/>
+      <c r="K34" s="171"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="21"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" s="411"/>
-      <c r="B35" s="408"/>
-      <c r="C35" s="408"/>
-      <c r="D35" s="408"/>
-      <c r="E35" s="408"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="412"/>
-      <c r="H35" s="413"/>
-      <c r="I35" s="413"/>
-      <c r="J35" s="413"/>
-      <c r="K35" s="414"/>
-      <c r="L35" s="22"/>
-      <c r="M35" s="23"/>
+      <c r="A35" s="111"/>
+      <c r="B35" s="108"/>
+      <c r="C35" s="108"/>
+      <c r="D35" s="108"/>
+      <c r="E35" s="108"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="169"/>
+      <c r="H35" s="170"/>
+      <c r="I35" s="170"/>
+      <c r="J35" s="170"/>
+      <c r="K35" s="171"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="21"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" s="411"/>
-      <c r="B36" s="408"/>
-      <c r="C36" s="408"/>
-      <c r="D36" s="408"/>
-      <c r="E36" s="408"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="412"/>
-      <c r="H36" s="413"/>
-      <c r="I36" s="413"/>
-      <c r="J36" s="413"/>
-      <c r="K36" s="414"/>
-      <c r="L36" s="22"/>
-      <c r="M36" s="23"/>
+      <c r="A36" s="111"/>
+      <c r="B36" s="108"/>
+      <c r="C36" s="108"/>
+      <c r="D36" s="108"/>
+      <c r="E36" s="108"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="169"/>
+      <c r="H36" s="170"/>
+      <c r="I36" s="170"/>
+      <c r="J36" s="170"/>
+      <c r="K36" s="171"/>
+      <c r="L36" s="20"/>
+      <c r="M36" s="21"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A37" s="411"/>
-      <c r="B37" s="408"/>
-      <c r="C37" s="408"/>
-      <c r="D37" s="408"/>
-      <c r="E37" s="408"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="412"/>
-      <c r="H37" s="413"/>
-      <c r="I37" s="413"/>
-      <c r="J37" s="413"/>
-      <c r="K37" s="414"/>
-      <c r="L37" s="22"/>
-      <c r="M37" s="23"/>
-      <c r="Q37" s="145"/>
-      <c r="R37" s="145"/>
-      <c r="S37" s="24"/>
-      <c r="T37" s="169"/>
-      <c r="U37" s="169"/>
-      <c r="V37" s="169"/>
+      <c r="A37" s="111"/>
+      <c r="B37" s="108"/>
+      <c r="C37" s="108"/>
+      <c r="D37" s="108"/>
+      <c r="E37" s="108"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="169"/>
+      <c r="H37" s="170"/>
+      <c r="I37" s="170"/>
+      <c r="J37" s="170"/>
+      <c r="K37" s="171"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="21"/>
+      <c r="Q37" s="194"/>
+      <c r="R37" s="194"/>
+      <c r="S37" s="22"/>
+      <c r="T37" s="193"/>
+      <c r="U37" s="193"/>
+      <c r="V37" s="193"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A38" s="411"/>
-      <c r="B38" s="408"/>
-      <c r="C38" s="408"/>
-      <c r="D38" s="408"/>
-      <c r="E38" s="408"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="412"/>
-      <c r="H38" s="413"/>
-      <c r="I38" s="413"/>
-      <c r="J38" s="413"/>
-      <c r="K38" s="414"/>
-      <c r="L38" s="22"/>
-      <c r="M38" s="26"/>
-      <c r="Q38" s="145"/>
-      <c r="R38" s="145"/>
-      <c r="S38" s="24"/>
-      <c r="T38" s="169"/>
-      <c r="U38" s="169"/>
-      <c r="V38" s="169"/>
+      <c r="A38" s="111"/>
+      <c r="B38" s="108"/>
+      <c r="C38" s="108"/>
+      <c r="D38" s="108"/>
+      <c r="E38" s="108"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="169"/>
+      <c r="H38" s="170"/>
+      <c r="I38" s="170"/>
+      <c r="J38" s="170"/>
+      <c r="K38" s="171"/>
+      <c r="L38" s="20"/>
+      <c r="M38" s="24"/>
+      <c r="Q38" s="194"/>
+      <c r="R38" s="194"/>
+      <c r="S38" s="22"/>
+      <c r="T38" s="193"/>
+      <c r="U38" s="193"/>
+      <c r="V38" s="193"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A39" s="411"/>
-      <c r="B39" s="408"/>
-      <c r="C39" s="408"/>
-      <c r="D39" s="408"/>
-      <c r="E39" s="408"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="412"/>
-      <c r="H39" s="413"/>
-      <c r="I39" s="413"/>
-      <c r="J39" s="413"/>
-      <c r="K39" s="414"/>
-      <c r="L39" s="22"/>
-      <c r="M39" s="26"/>
-      <c r="Q39" s="27"/>
-      <c r="R39" s="27"/>
-      <c r="S39" s="170"/>
-      <c r="T39" s="169"/>
-      <c r="U39" s="169"/>
-      <c r="V39" s="169"/>
+      <c r="A39" s="111"/>
+      <c r="B39" s="108"/>
+      <c r="C39" s="108"/>
+      <c r="D39" s="108"/>
+      <c r="E39" s="108"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="169"/>
+      <c r="H39" s="170"/>
+      <c r="I39" s="170"/>
+      <c r="J39" s="170"/>
+      <c r="K39" s="171"/>
+      <c r="L39" s="20"/>
+      <c r="M39" s="24"/>
+      <c r="Q39" s="25"/>
+      <c r="R39" s="25"/>
+      <c r="S39" s="195"/>
+      <c r="T39" s="193"/>
+      <c r="U39" s="193"/>
+      <c r="V39" s="193"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A40" s="411"/>
-      <c r="B40" s="408"/>
-      <c r="C40" s="408"/>
-      <c r="D40" s="408"/>
-      <c r="E40" s="408"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="412"/>
-      <c r="H40" s="413"/>
-      <c r="I40" s="413"/>
-      <c r="J40" s="413"/>
-      <c r="K40" s="414"/>
-      <c r="L40" s="22"/>
-      <c r="M40" s="23"/>
-      <c r="Q40" s="27"/>
-      <c r="R40" s="27"/>
-      <c r="S40" s="170"/>
-      <c r="T40" s="169"/>
-      <c r="U40" s="169"/>
-      <c r="V40" s="169"/>
+      <c r="A40" s="111"/>
+      <c r="B40" s="108"/>
+      <c r="C40" s="108"/>
+      <c r="D40" s="108"/>
+      <c r="E40" s="108"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="169"/>
+      <c r="H40" s="170"/>
+      <c r="I40" s="170"/>
+      <c r="J40" s="170"/>
+      <c r="K40" s="171"/>
+      <c r="L40" s="20"/>
+      <c r="M40" s="21"/>
+      <c r="Q40" s="25"/>
+      <c r="R40" s="25"/>
+      <c r="S40" s="195"/>
+      <c r="T40" s="193"/>
+      <c r="U40" s="193"/>
+      <c r="V40" s="193"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A41" s="411"/>
-      <c r="B41" s="408"/>
-      <c r="C41" s="408"/>
-      <c r="D41" s="408"/>
-      <c r="E41" s="408"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="412"/>
-      <c r="H41" s="413"/>
-      <c r="I41" s="413"/>
-      <c r="J41" s="413"/>
-      <c r="K41" s="414"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="23"/>
+      <c r="A41" s="111"/>
+      <c r="B41" s="108"/>
+      <c r="C41" s="108"/>
+      <c r="D41" s="108"/>
+      <c r="E41" s="108"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="169"/>
+      <c r="H41" s="170"/>
+      <c r="I41" s="170"/>
+      <c r="J41" s="170"/>
+      <c r="K41" s="171"/>
+      <c r="L41" s="20"/>
+      <c r="M41" s="21"/>
     </row>
     <row r="42" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="415">
+      <c r="A42" s="112">
         <v>6</v>
       </c>
-      <c r="B42" s="416"/>
-      <c r="C42" s="417">
+      <c r="B42" s="113"/>
+      <c r="C42" s="114">
         <v>1688</v>
       </c>
-      <c r="D42" s="416"/>
-      <c r="E42" s="417">
+      <c r="D42" s="113"/>
+      <c r="E42" s="114">
         <v>1688</v>
       </c>
-      <c r="F42" s="28"/>
-      <c r="G42" s="418" t="s">
+      <c r="F42" s="26"/>
+      <c r="G42" s="172" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="419"/>
-      <c r="I42" s="419"/>
-      <c r="J42" s="419"/>
-      <c r="K42" s="420"/>
-      <c r="L42" s="28"/>
-      <c r="M42" s="29"/>
+      <c r="H42" s="173"/>
+      <c r="I42" s="173"/>
+      <c r="J42" s="173"/>
+      <c r="K42" s="174"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="27"/>
     </row>
     <row r="43" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="174" t="s">
+      <c r="A43" s="149" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="175"/>
-      <c r="C43" s="175"/>
-      <c r="D43" s="175"/>
-      <c r="E43" s="175"/>
-      <c r="F43" s="175"/>
-      <c r="G43" s="175"/>
-      <c r="H43" s="176"/>
-      <c r="I43" s="192" t="s">
+      <c r="B43" s="150"/>
+      <c r="C43" s="150"/>
+      <c r="D43" s="150"/>
+      <c r="E43" s="150"/>
+      <c r="F43" s="150"/>
+      <c r="G43" s="150"/>
+      <c r="H43" s="151"/>
+      <c r="I43" s="175" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="193"/>
-      <c r="K43" s="193"/>
-      <c r="L43" s="193"/>
-      <c r="M43" s="194"/>
+      <c r="J43" s="176"/>
+      <c r="K43" s="176"/>
+      <c r="L43" s="176"/>
+      <c r="M43" s="177"/>
     </row>
     <row r="44" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="177"/>
-      <c r="B44" s="178"/>
-      <c r="C44" s="178"/>
-      <c r="D44" s="178"/>
-      <c r="E44" s="178"/>
-      <c r="F44" s="178"/>
-      <c r="G44" s="178"/>
-      <c r="H44" s="179"/>
-      <c r="I44" s="195"/>
-      <c r="J44" s="196"/>
-      <c r="K44" s="196"/>
-      <c r="L44" s="196"/>
-      <c r="M44" s="197"/>
+      <c r="A44" s="152"/>
+      <c r="B44" s="153"/>
+      <c r="C44" s="153"/>
+      <c r="D44" s="153"/>
+      <c r="E44" s="153"/>
+      <c r="F44" s="153"/>
+      <c r="G44" s="153"/>
+      <c r="H44" s="154"/>
+      <c r="I44" s="178"/>
+      <c r="J44" s="179"/>
+      <c r="K44" s="179"/>
+      <c r="L44" s="179"/>
+      <c r="M44" s="180"/>
     </row>
     <row r="45" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="157" t="s">
+      <c r="A45" s="181" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="158"/>
-      <c r="C45" s="158"/>
-      <c r="D45" s="158"/>
-      <c r="E45" s="158"/>
-      <c r="F45" s="158"/>
-      <c r="G45" s="158"/>
-      <c r="H45" s="159"/>
-      <c r="I45" s="160" t="s">
+      <c r="B45" s="182"/>
+      <c r="C45" s="182"/>
+      <c r="D45" s="182"/>
+      <c r="E45" s="182"/>
+      <c r="F45" s="182"/>
+      <c r="G45" s="182"/>
+      <c r="H45" s="183"/>
+      <c r="I45" s="184" t="s">
         <v>36</v>
       </c>
-      <c r="J45" s="161"/>
-      <c r="K45" s="161"/>
-      <c r="L45" s="161"/>
-      <c r="M45" s="162"/>
+      <c r="J45" s="185"/>
+      <c r="K45" s="185"/>
+      <c r="L45" s="185"/>
+      <c r="M45" s="186"/>
     </row>
     <row r="46" spans="1:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="157" t="s">
+      <c r="A46" s="181" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="158"/>
-      <c r="C46" s="158"/>
-      <c r="D46" s="158"/>
-      <c r="E46" s="158"/>
-      <c r="F46" s="158"/>
-      <c r="G46" s="158"/>
-      <c r="H46" s="159"/>
-      <c r="I46" s="160"/>
-      <c r="J46" s="161"/>
-      <c r="K46" s="161"/>
-      <c r="L46" s="161"/>
-      <c r="M46" s="162"/>
+      <c r="B46" s="182"/>
+      <c r="C46" s="182"/>
+      <c r="D46" s="182"/>
+      <c r="E46" s="182"/>
+      <c r="F46" s="182"/>
+      <c r="G46" s="182"/>
+      <c r="H46" s="183"/>
+      <c r="I46" s="184"/>
+      <c r="J46" s="185"/>
+      <c r="K46" s="185"/>
+      <c r="L46" s="185"/>
+      <c r="M46" s="186"/>
     </row>
     <row r="47" spans="1:22" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="163"/>
-      <c r="B47" s="164"/>
-      <c r="C47" s="164"/>
-      <c r="D47" s="164"/>
-      <c r="E47" s="164"/>
-      <c r="F47" s="164"/>
-      <c r="G47" s="164"/>
-      <c r="H47" s="165"/>
-      <c r="I47" s="166" t="s">
+      <c r="A47" s="187"/>
+      <c r="B47" s="188"/>
+      <c r="C47" s="188"/>
+      <c r="D47" s="188"/>
+      <c r="E47" s="188"/>
+      <c r="F47" s="188"/>
+      <c r="G47" s="188"/>
+      <c r="H47" s="189"/>
+      <c r="I47" s="190" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="167"/>
-      <c r="K47" s="167"/>
-      <c r="L47" s="167"/>
-      <c r="M47" s="168"/>
+      <c r="J47" s="191"/>
+      <c r="K47" s="191"/>
+      <c r="L47" s="191"/>
+      <c r="M47" s="192"/>
     </row>
     <row r="48" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="171" t="s">
+      <c r="A48" s="146" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="172"/>
-      <c r="C48" s="172"/>
-      <c r="D48" s="172"/>
-      <c r="E48" s="172"/>
-      <c r="F48" s="172"/>
-      <c r="G48" s="172"/>
-      <c r="H48" s="172"/>
-      <c r="I48" s="172"/>
-      <c r="J48" s="172"/>
-      <c r="K48" s="172"/>
-      <c r="L48" s="172"/>
-      <c r="M48" s="173"/>
+      <c r="B48" s="147"/>
+      <c r="C48" s="147"/>
+      <c r="D48" s="147"/>
+      <c r="E48" s="147"/>
+      <c r="F48" s="147"/>
+      <c r="G48" s="147"/>
+      <c r="H48" s="147"/>
+      <c r="I48" s="147"/>
+      <c r="J48" s="147"/>
+      <c r="K48" s="147"/>
+      <c r="L48" s="147"/>
+      <c r="M48" s="148"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="174" t="s">
+      <c r="A49" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="175"/>
-      <c r="C49" s="175"/>
-      <c r="D49" s="175"/>
-      <c r="E49" s="175"/>
-      <c r="F49" s="175"/>
-      <c r="G49" s="175"/>
-      <c r="H49" s="176"/>
-      <c r="I49" s="182" t="s">
+      <c r="B49" s="150"/>
+      <c r="C49" s="150"/>
+      <c r="D49" s="150"/>
+      <c r="E49" s="150"/>
+      <c r="F49" s="150"/>
+      <c r="G49" s="150"/>
+      <c r="H49" s="151"/>
+      <c r="I49" s="157" t="s">
         <v>40</v>
       </c>
-      <c r="J49" s="183"/>
-      <c r="K49" s="183"/>
-      <c r="L49" s="183"/>
-      <c r="M49" s="184"/>
+      <c r="J49" s="158"/>
+      <c r="K49" s="158"/>
+      <c r="L49" s="158"/>
+      <c r="M49" s="159"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="177"/>
-      <c r="B50" s="178"/>
-      <c r="C50" s="178"/>
-      <c r="D50" s="178"/>
-      <c r="E50" s="178"/>
-      <c r="F50" s="178"/>
-      <c r="G50" s="178"/>
-      <c r="H50" s="179"/>
-      <c r="I50" s="185"/>
-      <c r="J50" s="186"/>
-      <c r="K50" s="186"/>
-      <c r="L50" s="186"/>
-      <c r="M50" s="187"/>
+      <c r="A50" s="152"/>
+      <c r="B50" s="153"/>
+      <c r="C50" s="153"/>
+      <c r="D50" s="153"/>
+      <c r="E50" s="153"/>
+      <c r="F50" s="153"/>
+      <c r="G50" s="153"/>
+      <c r="H50" s="154"/>
+      <c r="I50" s="160"/>
+      <c r="J50" s="161"/>
+      <c r="K50" s="161"/>
+      <c r="L50" s="161"/>
+      <c r="M50" s="162"/>
     </row>
     <row r="51" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="180"/>
-      <c r="B51" s="181"/>
-      <c r="C51" s="181"/>
-      <c r="D51" s="181"/>
-      <c r="E51" s="178"/>
-      <c r="F51" s="178"/>
-      <c r="G51" s="178"/>
-      <c r="H51" s="179"/>
-      <c r="I51" s="188" t="s">
+      <c r="A51" s="155"/>
+      <c r="B51" s="156"/>
+      <c r="C51" s="156"/>
+      <c r="D51" s="156"/>
+      <c r="E51" s="153"/>
+      <c r="F51" s="153"/>
+      <c r="G51" s="153"/>
+      <c r="H51" s="154"/>
+      <c r="I51" s="163" t="s">
         <v>41</v>
       </c>
-      <c r="J51" s="189"/>
-      <c r="K51" s="190"/>
-      <c r="L51" s="190"/>
-      <c r="M51" s="191"/>
+      <c r="J51" s="164"/>
+      <c r="K51" s="165"/>
+      <c r="L51" s="165"/>
+      <c r="M51" s="166"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="171" t="s">
+      <c r="A52" s="146" t="s">
         <v>42</v>
       </c>
-      <c r="B52" s="172"/>
-      <c r="C52" s="172"/>
-      <c r="D52" s="172"/>
-      <c r="E52" s="421" t="s">
+      <c r="B52" s="147"/>
+      <c r="C52" s="147"/>
+      <c r="D52" s="147"/>
+      <c r="E52" s="115" t="s">
         <v>44</v>
       </c>
-      <c r="F52" s="422"/>
-      <c r="G52" s="423" t="s">
+      <c r="F52" s="116"/>
+      <c r="G52" s="167" t="s">
         <v>45</v>
       </c>
-      <c r="H52" s="423"/>
-      <c r="I52" s="423"/>
-      <c r="J52" s="424"/>
-      <c r="K52" s="172" t="s">
+      <c r="H52" s="167"/>
+      <c r="I52" s="167"/>
+      <c r="J52" s="168"/>
+      <c r="K52" s="147" t="s">
         <v>50</v>
       </c>
-      <c r="L52" s="172"/>
-      <c r="M52" s="173"/>
+      <c r="L52" s="147"/>
+      <c r="M52" s="148"/>
     </row>
     <row r="53" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="425" t="s">
+      <c r="A53" s="133" t="s">
         <v>43</v>
       </c>
-      <c r="B53" s="426"/>
-      <c r="C53" s="426"/>
-      <c r="D53" s="426"/>
-      <c r="E53" s="427"/>
-      <c r="F53" s="410"/>
-      <c r="G53" s="410"/>
-      <c r="H53" s="410"/>
-      <c r="I53" s="410"/>
-      <c r="J53" s="428"/>
-      <c r="K53" s="426" t="s">
+      <c r="B53" s="134"/>
+      <c r="C53" s="134"/>
+      <c r="D53" s="134"/>
+      <c r="E53" s="117"/>
+      <c r="F53" s="110"/>
+      <c r="G53" s="110"/>
+      <c r="H53" s="110"/>
+      <c r="I53" s="110"/>
+      <c r="J53" s="118"/>
+      <c r="K53" s="134" t="s">
         <v>52</v>
       </c>
-      <c r="L53" s="426"/>
-      <c r="M53" s="429"/>
+      <c r="L53" s="134"/>
+      <c r="M53" s="135"/>
     </row>
     <row r="54" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="425"/>
-      <c r="B54" s="426"/>
-      <c r="C54" s="426"/>
-      <c r="D54" s="426"/>
-      <c r="E54" s="430" t="s">
+      <c r="A54" s="133"/>
+      <c r="B54" s="134"/>
+      <c r="C54" s="134"/>
+      <c r="D54" s="134"/>
+      <c r="E54" s="136" t="s">
         <v>46</v>
       </c>
-      <c r="F54" s="431"/>
-      <c r="G54" s="432"/>
-      <c r="H54" s="433" t="s">
+      <c r="F54" s="137"/>
+      <c r="G54" s="119"/>
+      <c r="H54" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="I54" s="433"/>
-      <c r="J54" s="434"/>
-      <c r="K54" s="426"/>
-      <c r="L54" s="426"/>
-      <c r="M54" s="429"/>
+      <c r="I54" s="126"/>
+      <c r="J54" s="127"/>
+      <c r="K54" s="134"/>
+      <c r="L54" s="134"/>
+      <c r="M54" s="135"/>
     </row>
     <row r="55" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="425"/>
-      <c r="B55" s="426"/>
-      <c r="C55" s="426"/>
-      <c r="D55" s="426"/>
-      <c r="E55" s="430" t="s">
+      <c r="A55" s="133"/>
+      <c r="B55" s="134"/>
+      <c r="C55" s="134"/>
+      <c r="D55" s="134"/>
+      <c r="E55" s="136" t="s">
         <v>47</v>
       </c>
-      <c r="F55" s="431"/>
-      <c r="G55" s="431"/>
-      <c r="H55" s="433" t="s">
+      <c r="F55" s="137"/>
+      <c r="G55" s="137"/>
+      <c r="H55" s="126" t="s">
         <v>48</v>
       </c>
-      <c r="I55" s="433"/>
-      <c r="J55" s="434"/>
-      <c r="K55" s="426"/>
-      <c r="L55" s="426"/>
-      <c r="M55" s="429"/>
+      <c r="I55" s="126"/>
+      <c r="J55" s="127"/>
+      <c r="K55" s="134"/>
+      <c r="L55" s="134"/>
+      <c r="M55" s="135"/>
     </row>
     <row r="56" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="132"/>
-      <c r="B56" s="133"/>
-      <c r="C56" s="133"/>
-      <c r="D56" s="382"/>
-      <c r="E56" s="430"/>
-      <c r="F56" s="431"/>
-      <c r="G56" s="431"/>
-      <c r="H56" s="433"/>
-      <c r="I56" s="433"/>
-      <c r="J56" s="434"/>
-      <c r="K56" s="435" t="s">
+      <c r="A56" s="138"/>
+      <c r="B56" s="139"/>
+      <c r="C56" s="139"/>
+      <c r="D56" s="140"/>
+      <c r="E56" s="136"/>
+      <c r="F56" s="137"/>
+      <c r="G56" s="137"/>
+      <c r="H56" s="126"/>
+      <c r="I56" s="126"/>
+      <c r="J56" s="127"/>
+      <c r="K56" s="144" t="s">
         <v>51</v>
       </c>
-      <c r="L56" s="435"/>
-      <c r="M56" s="436"/>
+      <c r="L56" s="144"/>
+      <c r="M56" s="145"/>
     </row>
     <row r="57" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="132"/>
-      <c r="B57" s="133"/>
-      <c r="C57" s="133"/>
-      <c r="D57" s="382"/>
-      <c r="E57" s="430"/>
-      <c r="F57" s="431"/>
-      <c r="G57" s="432"/>
-      <c r="H57" s="433" t="s">
+      <c r="A57" s="138"/>
+      <c r="B57" s="139"/>
+      <c r="C57" s="139"/>
+      <c r="D57" s="140"/>
+      <c r="E57" s="136"/>
+      <c r="F57" s="137"/>
+      <c r="G57" s="119"/>
+      <c r="H57" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="I57" s="433"/>
-      <c r="J57" s="434"/>
-      <c r="K57" s="437"/>
-      <c r="L57" s="438"/>
-      <c r="M57" s="439"/>
+      <c r="I57" s="126"/>
+      <c r="J57" s="127"/>
+      <c r="K57" s="120"/>
+      <c r="L57" s="121"/>
+      <c r="M57" s="122"/>
     </row>
     <row r="58" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="440"/>
-      <c r="B58" s="441"/>
-      <c r="C58" s="441"/>
-      <c r="D58" s="442"/>
-      <c r="E58" s="138"/>
-      <c r="F58" s="139"/>
-      <c r="G58" s="139"/>
-      <c r="H58" s="139"/>
-      <c r="I58" s="139"/>
-      <c r="J58" s="443"/>
-      <c r="K58" s="444"/>
-      <c r="L58" s="445"/>
-      <c r="M58" s="446"/>
+      <c r="A58" s="141"/>
+      <c r="B58" s="142"/>
+      <c r="C58" s="142"/>
+      <c r="D58" s="143"/>
+      <c r="E58" s="128"/>
+      <c r="F58" s="129"/>
+      <c r="G58" s="129"/>
+      <c r="H58" s="129"/>
+      <c r="I58" s="129"/>
+      <c r="J58" s="130"/>
+      <c r="K58" s="123"/>
+      <c r="L58" s="124"/>
+      <c r="M58" s="125"/>
     </row>
     <row r="59" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="30"/>
-      <c r="B59" s="30"/>
-      <c r="C59" s="30"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="27"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
-      <c r="H59" s="25"/>
-      <c r="I59" s="25"/>
-      <c r="J59" s="25"/>
+      <c r="A59" s="28"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="28"/>
+      <c r="D59" s="28"/>
+      <c r="E59" s="25"/>
+      <c r="F59" s="25"/>
+      <c r="G59" s="25"/>
+      <c r="H59" s="23"/>
+      <c r="I59" s="23"/>
+      <c r="J59" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="112">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="I4:M6"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="I2:M3"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="I12:M14"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:G21"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J20:M21"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="I15:M15"/>
+    <mergeCell ref="I16:M16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:M18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="G34:K34"/>
+    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="G36:K36"/>
+    <mergeCell ref="G37:K37"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="A31:M31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="G32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="I45:M46"/>
+    <mergeCell ref="A46:H47"/>
+    <mergeCell ref="I47:M47"/>
+    <mergeCell ref="T37:V37"/>
+    <mergeCell ref="G38:K38"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="T38:V38"/>
+    <mergeCell ref="G39:K39"/>
+    <mergeCell ref="S39:S40"/>
+    <mergeCell ref="T39:V40"/>
+    <mergeCell ref="G40:K40"/>
     <mergeCell ref="H57:J57"/>
     <mergeCell ref="E58:J58"/>
     <mergeCell ref="F16:H16"/>
@@ -6184,94 +6257,6 @@
     <mergeCell ref="G42:K42"/>
     <mergeCell ref="A43:H44"/>
     <mergeCell ref="I43:M44"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="I45:M46"/>
-    <mergeCell ref="A46:H47"/>
-    <mergeCell ref="I47:M47"/>
-    <mergeCell ref="T37:V37"/>
-    <mergeCell ref="G38:K38"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="T38:V38"/>
-    <mergeCell ref="G39:K39"/>
-    <mergeCell ref="S39:S40"/>
-    <mergeCell ref="T39:V40"/>
-    <mergeCell ref="G40:K40"/>
-    <mergeCell ref="G33:K33"/>
-    <mergeCell ref="G34:K34"/>
-    <mergeCell ref="G35:K35"/>
-    <mergeCell ref="G36:K36"/>
-    <mergeCell ref="G37:K37"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="A31:M31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="G32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="A20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:G21"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="J20:M21"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="I16:M16"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:M18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="I12:M14"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="I8:M8"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="I4:M6"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:M3"/>
-    <mergeCell ref="A3:H3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.26" top="0.52" bottom="0.56000000000000005" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6992,1251 +6977,1117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="270" t="s">
         <v>237</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="109" t="s">
+      <c r="B1" s="271"/>
+      <c r="C1" s="272" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="110" t="s">
+      <c r="D1" s="272"/>
+      <c r="E1" s="272"/>
+      <c r="F1" s="272"/>
+      <c r="G1" s="272"/>
+      <c r="H1" s="272"/>
+      <c r="I1" s="272"/>
+      <c r="J1" s="272"/>
+      <c r="K1" s="272"/>
+      <c r="L1" s="273" t="s">
         <v>63</v>
       </c>
-      <c r="M1" s="111"/>
+      <c r="M1" s="274"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="115" t="s">
+      <c r="A2" s="203" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="117"/>
+      <c r="B2" s="204"/>
+      <c r="C2" s="204"/>
+      <c r="D2" s="204"/>
+      <c r="E2" s="204"/>
+      <c r="F2" s="204"/>
+      <c r="G2" s="204"/>
+      <c r="H2" s="204"/>
+      <c r="I2" s="204"/>
+      <c r="J2" s="204"/>
+      <c r="K2" s="204"/>
+      <c r="L2" s="204"/>
+      <c r="M2" s="205"/>
     </row>
     <row r="3" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="118" t="s">
+      <c r="A3" s="216" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119" t="s">
+      <c r="B3" s="217"/>
+      <c r="C3" s="217"/>
+      <c r="D3" s="217"/>
+      <c r="E3" s="217" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="119" t="s">
+      <c r="F3" s="217" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="119"/>
-      <c r="H3" s="120" t="s">
+      <c r="G3" s="217"/>
+      <c r="H3" s="218" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="121"/>
-      <c r="J3" s="122" t="s">
+      <c r="I3" s="219"/>
+      <c r="J3" s="220" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="123"/>
-      <c r="L3" s="123"/>
-      <c r="M3" s="124"/>
+      <c r="K3" s="221"/>
+      <c r="L3" s="221"/>
+      <c r="M3" s="222"/>
     </row>
     <row r="4" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="118"/>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="128" t="s">
+      <c r="A4" s="216"/>
+      <c r="B4" s="217"/>
+      <c r="C4" s="217"/>
+      <c r="D4" s="217"/>
+      <c r="E4" s="217"/>
+      <c r="F4" s="217"/>
+      <c r="G4" s="217"/>
+      <c r="H4" s="226" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="129"/>
-      <c r="J4" s="125"/>
-      <c r="K4" s="126"/>
-      <c r="L4" s="126"/>
-      <c r="M4" s="127"/>
+      <c r="I4" s="227"/>
+      <c r="J4" s="223"/>
+      <c r="K4" s="224"/>
+      <c r="L4" s="224"/>
+      <c r="M4" s="225"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="198"/>
-      <c r="B5" s="140"/>
-      <c r="C5" s="140"/>
-      <c r="D5" s="140"/>
+      <c r="A5" s="438"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="212"/>
       <c r="E5" s="10">
         <v>61</v>
       </c>
-      <c r="F5" s="199">
+      <c r="F5" s="297">
         <v>61</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="13" t="s">
+      <c r="G5" s="298"/>
+      <c r="H5" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J5" s="142"/>
-      <c r="K5" s="142"/>
-      <c r="L5" s="142"/>
-      <c r="M5" s="143"/>
+      <c r="J5" s="200"/>
+      <c r="K5" s="200"/>
+      <c r="L5" s="200"/>
+      <c r="M5" s="215"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="198"/>
-      <c r="B6" s="140"/>
-      <c r="C6" s="140"/>
-      <c r="D6" s="140"/>
+      <c r="A6" s="438"/>
+      <c r="B6" s="212"/>
+      <c r="C6" s="212"/>
+      <c r="D6" s="212"/>
       <c r="E6" s="10">
         <v>83</v>
       </c>
-      <c r="F6" s="199">
+      <c r="F6" s="297">
         <v>83</v>
       </c>
-      <c r="G6" s="200"/>
-      <c r="H6" s="13" t="s">
+      <c r="G6" s="298"/>
+      <c r="H6" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J6" s="142"/>
-      <c r="K6" s="142"/>
-      <c r="L6" s="142"/>
-      <c r="M6" s="143"/>
+      <c r="J6" s="200"/>
+      <c r="K6" s="200"/>
+      <c r="L6" s="200"/>
+      <c r="M6" s="215"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="198"/>
-      <c r="B7" s="140"/>
-      <c r="C7" s="140"/>
-      <c r="D7" s="140"/>
+      <c r="A7" s="438"/>
+      <c r="B7" s="212"/>
+      <c r="C7" s="212"/>
+      <c r="D7" s="212"/>
       <c r="E7" s="10">
         <v>70</v>
       </c>
-      <c r="F7" s="199">
+      <c r="F7" s="297">
         <v>70</v>
       </c>
-      <c r="G7" s="200"/>
-      <c r="H7" s="13" t="s">
+      <c r="G7" s="298"/>
+      <c r="H7" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J7" s="142"/>
-      <c r="K7" s="142"/>
-      <c r="L7" s="142"/>
-      <c r="M7" s="143"/>
+      <c r="J7" s="200"/>
+      <c r="K7" s="200"/>
+      <c r="L7" s="200"/>
+      <c r="M7" s="215"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="198"/>
-      <c r="B8" s="140"/>
-      <c r="C8" s="140"/>
-      <c r="D8" s="140"/>
+      <c r="A8" s="438"/>
+      <c r="B8" s="212"/>
+      <c r="C8" s="212"/>
+      <c r="D8" s="212"/>
       <c r="E8" s="10">
         <v>50</v>
       </c>
-      <c r="F8" s="199">
+      <c r="F8" s="297">
         <v>50</v>
       </c>
-      <c r="G8" s="200"/>
-      <c r="H8" s="13" t="s">
+      <c r="G8" s="298"/>
+      <c r="H8" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J8" s="142"/>
-      <c r="K8" s="142"/>
-      <c r="L8" s="142"/>
-      <c r="M8" s="143"/>
+      <c r="J8" s="200"/>
+      <c r="K8" s="200"/>
+      <c r="L8" s="200"/>
+      <c r="M8" s="215"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="198"/>
-      <c r="B9" s="140"/>
-      <c r="C9" s="140"/>
-      <c r="D9" s="140"/>
+      <c r="A9" s="438"/>
+      <c r="B9" s="212"/>
+      <c r="C9" s="212"/>
+      <c r="D9" s="212"/>
       <c r="E9" s="10">
         <v>70</v>
       </c>
-      <c r="F9" s="199">
+      <c r="F9" s="297">
         <v>70</v>
       </c>
-      <c r="G9" s="200"/>
-      <c r="H9" s="13" t="s">
+      <c r="G9" s="298"/>
+      <c r="H9" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J9" s="142"/>
-      <c r="K9" s="142"/>
-      <c r="L9" s="142"/>
-      <c r="M9" s="143"/>
+      <c r="J9" s="200"/>
+      <c r="K9" s="200"/>
+      <c r="L9" s="200"/>
+      <c r="M9" s="215"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="198"/>
-      <c r="B10" s="140"/>
-      <c r="C10" s="140"/>
-      <c r="D10" s="140"/>
+      <c r="A10" s="438"/>
+      <c r="B10" s="212"/>
+      <c r="C10" s="212"/>
+      <c r="D10" s="212"/>
       <c r="E10" s="10">
         <v>69</v>
       </c>
-      <c r="F10" s="199">
+      <c r="F10" s="297">
         <v>69</v>
       </c>
-      <c r="G10" s="200"/>
-      <c r="H10" s="13" t="s">
+      <c r="G10" s="298"/>
+      <c r="H10" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I10" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="142"/>
-      <c r="K10" s="142"/>
-      <c r="L10" s="142"/>
-      <c r="M10" s="143"/>
+      <c r="J10" s="200"/>
+      <c r="K10" s="200"/>
+      <c r="L10" s="200"/>
+      <c r="M10" s="215"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="198"/>
-      <c r="B11" s="140"/>
-      <c r="C11" s="140"/>
-      <c r="D11" s="140"/>
+      <c r="A11" s="438"/>
+      <c r="B11" s="212"/>
+      <c r="C11" s="212"/>
+      <c r="D11" s="212"/>
       <c r="E11" s="10">
         <v>54</v>
       </c>
-      <c r="F11" s="199">
+      <c r="F11" s="297">
         <v>54</v>
       </c>
-      <c r="G11" s="200"/>
-      <c r="H11" s="13" t="s">
+      <c r="G11" s="298"/>
+      <c r="H11" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J11" s="142"/>
-      <c r="K11" s="142"/>
-      <c r="L11" s="142"/>
-      <c r="M11" s="143"/>
+      <c r="J11" s="200"/>
+      <c r="K11" s="200"/>
+      <c r="L11" s="200"/>
+      <c r="M11" s="215"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="198"/>
-      <c r="B12" s="140"/>
-      <c r="C12" s="140"/>
-      <c r="D12" s="140"/>
+      <c r="A12" s="438"/>
+      <c r="B12" s="212"/>
+      <c r="C12" s="212"/>
+      <c r="D12" s="212"/>
       <c r="E12" s="10">
         <v>65</v>
       </c>
-      <c r="F12" s="199">
+      <c r="F12" s="297">
         <v>65</v>
       </c>
-      <c r="G12" s="200"/>
-      <c r="H12" s="13" t="s">
+      <c r="G12" s="298"/>
+      <c r="H12" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J12" s="142"/>
-      <c r="K12" s="142"/>
-      <c r="L12" s="142"/>
-      <c r="M12" s="143"/>
+      <c r="J12" s="200"/>
+      <c r="K12" s="200"/>
+      <c r="L12" s="200"/>
+      <c r="M12" s="215"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="198"/>
-      <c r="B13" s="140"/>
-      <c r="C13" s="140"/>
-      <c r="D13" s="140"/>
+      <c r="A13" s="438"/>
+      <c r="B13" s="212"/>
+      <c r="C13" s="212"/>
+      <c r="D13" s="212"/>
       <c r="E13" s="10">
         <v>65</v>
       </c>
-      <c r="F13" s="199">
+      <c r="F13" s="297">
         <v>65</v>
       </c>
-      <c r="G13" s="200"/>
-      <c r="H13" s="13" t="s">
+      <c r="G13" s="298"/>
+      <c r="H13" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="I13" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J13" s="142"/>
-      <c r="K13" s="142"/>
-      <c r="L13" s="142"/>
-      <c r="M13" s="143"/>
+      <c r="J13" s="200"/>
+      <c r="K13" s="200"/>
+      <c r="L13" s="200"/>
+      <c r="M13" s="215"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="198"/>
-      <c r="B14" s="140"/>
-      <c r="C14" s="140"/>
-      <c r="D14" s="140"/>
+      <c r="A14" s="438"/>
+      <c r="B14" s="212"/>
+      <c r="C14" s="212"/>
+      <c r="D14" s="212"/>
       <c r="E14" s="10">
         <v>70</v>
       </c>
-      <c r="F14" s="199">
+      <c r="F14" s="297">
         <v>70</v>
       </c>
-      <c r="G14" s="200"/>
-      <c r="H14" s="13" t="s">
+      <c r="G14" s="298"/>
+      <c r="H14" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="I14" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J14" s="142"/>
-      <c r="K14" s="142"/>
-      <c r="L14" s="142"/>
-      <c r="M14" s="143"/>
+      <c r="J14" s="200"/>
+      <c r="K14" s="200"/>
+      <c r="L14" s="200"/>
+      <c r="M14" s="215"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="198"/>
-      <c r="B15" s="140"/>
-      <c r="C15" s="140"/>
-      <c r="D15" s="140"/>
+      <c r="A15" s="438"/>
+      <c r="B15" s="212"/>
+      <c r="C15" s="212"/>
+      <c r="D15" s="212"/>
       <c r="E15" s="10">
         <v>55</v>
       </c>
-      <c r="F15" s="199">
+      <c r="F15" s="297">
         <v>55</v>
       </c>
-      <c r="G15" s="200"/>
-      <c r="H15" s="13" t="s">
+      <c r="G15" s="298"/>
+      <c r="H15" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I15" s="13" t="s">
+      <c r="I15" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J15" s="142"/>
-      <c r="K15" s="142"/>
-      <c r="L15" s="142"/>
-      <c r="M15" s="143"/>
+      <c r="J15" s="200"/>
+      <c r="K15" s="200"/>
+      <c r="L15" s="200"/>
+      <c r="M15" s="215"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="198"/>
-      <c r="B16" s="140"/>
-      <c r="C16" s="140"/>
-      <c r="D16" s="140"/>
+      <c r="A16" s="438"/>
+      <c r="B16" s="212"/>
+      <c r="C16" s="212"/>
+      <c r="D16" s="212"/>
       <c r="E16" s="10">
         <v>54</v>
       </c>
-      <c r="F16" s="199">
+      <c r="F16" s="297">
         <v>54</v>
       </c>
-      <c r="G16" s="200"/>
-      <c r="H16" s="13" t="s">
+      <c r="G16" s="298"/>
+      <c r="H16" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I16" s="13" t="s">
+      <c r="I16" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J16" s="142"/>
-      <c r="K16" s="142"/>
-      <c r="L16" s="142"/>
-      <c r="M16" s="143"/>
+      <c r="J16" s="200"/>
+      <c r="K16" s="200"/>
+      <c r="L16" s="200"/>
+      <c r="M16" s="215"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="198"/>
-      <c r="B17" s="140"/>
-      <c r="C17" s="140"/>
-      <c r="D17" s="140"/>
+      <c r="A17" s="438"/>
+      <c r="B17" s="212"/>
+      <c r="C17" s="212"/>
+      <c r="D17" s="212"/>
       <c r="E17" s="10">
         <v>76</v>
       </c>
-      <c r="F17" s="199">
+      <c r="F17" s="297">
         <v>76</v>
       </c>
-      <c r="G17" s="200"/>
-      <c r="H17" s="13" t="s">
+      <c r="G17" s="298"/>
+      <c r="H17" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I17" s="13" t="s">
+      <c r="I17" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J17" s="142"/>
-      <c r="K17" s="142"/>
-      <c r="L17" s="142"/>
-      <c r="M17" s="143"/>
+      <c r="J17" s="200"/>
+      <c r="K17" s="200"/>
+      <c r="L17" s="200"/>
+      <c r="M17" s="215"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="198"/>
-      <c r="B18" s="140"/>
-      <c r="C18" s="140"/>
-      <c r="D18" s="140"/>
+      <c r="A18" s="438"/>
+      <c r="B18" s="212"/>
+      <c r="C18" s="212"/>
+      <c r="D18" s="212"/>
       <c r="E18" s="10">
         <v>76</v>
       </c>
-      <c r="F18" s="199">
+      <c r="F18" s="297">
         <v>76</v>
       </c>
-      <c r="G18" s="200"/>
-      <c r="H18" s="13" t="s">
+      <c r="G18" s="298"/>
+      <c r="H18" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I18" s="13" t="s">
+      <c r="I18" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J18" s="142"/>
-      <c r="K18" s="142"/>
-      <c r="L18" s="142"/>
-      <c r="M18" s="143"/>
+      <c r="J18" s="200"/>
+      <c r="K18" s="200"/>
+      <c r="L18" s="200"/>
+      <c r="M18" s="215"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="198"/>
-      <c r="B19" s="140"/>
-      <c r="C19" s="140"/>
-      <c r="D19" s="140"/>
+      <c r="A19" s="438"/>
+      <c r="B19" s="212"/>
+      <c r="C19" s="212"/>
+      <c r="D19" s="212"/>
       <c r="E19" s="10">
         <v>65</v>
       </c>
-      <c r="F19" s="199">
+      <c r="F19" s="297">
         <v>65</v>
       </c>
-      <c r="G19" s="200"/>
-      <c r="H19" s="13" t="s">
+      <c r="G19" s="298"/>
+      <c r="H19" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I19" s="13" t="s">
+      <c r="I19" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J19" s="142"/>
-      <c r="K19" s="142"/>
-      <c r="L19" s="142"/>
-      <c r="M19" s="143"/>
+      <c r="J19" s="200"/>
+      <c r="K19" s="200"/>
+      <c r="L19" s="200"/>
+      <c r="M19" s="215"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="198"/>
-      <c r="B20" s="140"/>
-      <c r="C20" s="140"/>
-      <c r="D20" s="140"/>
+      <c r="A20" s="438"/>
+      <c r="B20" s="212"/>
+      <c r="C20" s="212"/>
+      <c r="D20" s="212"/>
       <c r="E20" s="10">
         <v>56</v>
       </c>
-      <c r="F20" s="199">
+      <c r="F20" s="297">
         <v>56</v>
       </c>
-      <c r="G20" s="200"/>
-      <c r="H20" s="13" t="s">
+      <c r="G20" s="298"/>
+      <c r="H20" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I20" s="13" t="s">
+      <c r="I20" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J20" s="142"/>
-      <c r="K20" s="142"/>
-      <c r="L20" s="142"/>
-      <c r="M20" s="143"/>
+      <c r="J20" s="200"/>
+      <c r="K20" s="200"/>
+      <c r="L20" s="200"/>
+      <c r="M20" s="215"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="198"/>
-      <c r="B21" s="140"/>
-      <c r="C21" s="140"/>
-      <c r="D21" s="140"/>
+      <c r="A21" s="438"/>
+      <c r="B21" s="212"/>
+      <c r="C21" s="212"/>
+      <c r="D21" s="212"/>
       <c r="E21" s="10">
         <v>83</v>
       </c>
-      <c r="F21" s="199">
+      <c r="F21" s="297">
         <v>83</v>
       </c>
-      <c r="G21" s="200"/>
-      <c r="H21" s="13" t="s">
+      <c r="G21" s="298"/>
+      <c r="H21" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I21" s="13" t="s">
+      <c r="I21" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J21" s="142"/>
-      <c r="K21" s="142"/>
-      <c r="L21" s="142"/>
-      <c r="M21" s="143"/>
+      <c r="J21" s="200"/>
+      <c r="K21" s="200"/>
+      <c r="L21" s="200"/>
+      <c r="M21" s="215"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="198"/>
-      <c r="B22" s="140"/>
-      <c r="C22" s="140"/>
-      <c r="D22" s="140"/>
+      <c r="A22" s="438"/>
+      <c r="B22" s="212"/>
+      <c r="C22" s="212"/>
+      <c r="D22" s="212"/>
       <c r="E22" s="10">
         <v>27</v>
       </c>
-      <c r="F22" s="199">
+      <c r="F22" s="297">
         <v>27</v>
       </c>
-      <c r="G22" s="200"/>
-      <c r="H22" s="13" t="s">
+      <c r="G22" s="298"/>
+      <c r="H22" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I22" s="13" t="s">
+      <c r="I22" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="142"/>
-      <c r="K22" s="142"/>
-      <c r="L22" s="142"/>
-      <c r="M22" s="143"/>
+      <c r="J22" s="200"/>
+      <c r="K22" s="200"/>
+      <c r="L22" s="200"/>
+      <c r="M22" s="215"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="198"/>
-      <c r="B23" s="140"/>
-      <c r="C23" s="140"/>
-      <c r="D23" s="140"/>
+      <c r="A23" s="438"/>
+      <c r="B23" s="212"/>
+      <c r="C23" s="212"/>
+      <c r="D23" s="212"/>
       <c r="E23" s="10">
         <v>16</v>
       </c>
-      <c r="F23" s="199">
+      <c r="F23" s="297">
         <v>16</v>
       </c>
-      <c r="G23" s="200"/>
-      <c r="H23" s="13" t="s">
+      <c r="G23" s="298"/>
+      <c r="H23" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I23" s="13" t="s">
+      <c r="I23" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="142"/>
-      <c r="K23" s="142"/>
-      <c r="L23" s="142"/>
-      <c r="M23" s="143"/>
+      <c r="J23" s="200"/>
+      <c r="K23" s="200"/>
+      <c r="L23" s="200"/>
+      <c r="M23" s="215"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="198"/>
-      <c r="B24" s="140"/>
-      <c r="C24" s="140"/>
-      <c r="D24" s="140"/>
+      <c r="A24" s="438"/>
+      <c r="B24" s="212"/>
+      <c r="C24" s="212"/>
+      <c r="D24" s="212"/>
       <c r="E24" s="10">
         <v>26</v>
       </c>
-      <c r="F24" s="199">
+      <c r="F24" s="297">
         <v>26</v>
       </c>
-      <c r="G24" s="200"/>
-      <c r="H24" s="13" t="s">
+      <c r="G24" s="298"/>
+      <c r="H24" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I24" s="13" t="s">
+      <c r="I24" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="142"/>
-      <c r="K24" s="142"/>
-      <c r="L24" s="142"/>
-      <c r="M24" s="143"/>
+      <c r="J24" s="200"/>
+      <c r="K24" s="200"/>
+      <c r="L24" s="200"/>
+      <c r="M24" s="215"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="198"/>
-      <c r="B25" s="140"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="140"/>
+      <c r="A25" s="438"/>
+      <c r="B25" s="212"/>
+      <c r="C25" s="212"/>
+      <c r="D25" s="212"/>
       <c r="E25" s="10">
         <v>16</v>
       </c>
-      <c r="F25" s="199">
+      <c r="F25" s="297">
         <v>16</v>
       </c>
-      <c r="G25" s="200"/>
-      <c r="H25" s="13" t="s">
+      <c r="G25" s="298"/>
+      <c r="H25" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="I25" s="13" t="s">
+      <c r="I25" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="142"/>
-      <c r="K25" s="142"/>
-      <c r="L25" s="142"/>
-      <c r="M25" s="143"/>
+      <c r="J25" s="200"/>
+      <c r="K25" s="200"/>
+      <c r="L25" s="200"/>
+      <c r="M25" s="215"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="201"/>
-      <c r="B26" s="202"/>
-      <c r="C26" s="202"/>
-      <c r="D26" s="202"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="142"/>
-      <c r="G26" s="142"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="142"/>
-      <c r="K26" s="142"/>
-      <c r="L26" s="142"/>
-      <c r="M26" s="143"/>
+      <c r="A26" s="293"/>
+      <c r="B26" s="294"/>
+      <c r="C26" s="294"/>
+      <c r="D26" s="294"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="200"/>
+      <c r="G26" s="200"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="200"/>
+      <c r="K26" s="200"/>
+      <c r="L26" s="200"/>
+      <c r="M26" s="215"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="201"/>
-      <c r="B27" s="202"/>
-      <c r="C27" s="202"/>
-      <c r="D27" s="202"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="142"/>
-      <c r="G27" s="142"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="142"/>
-      <c r="K27" s="142"/>
-      <c r="L27" s="142"/>
-      <c r="M27" s="143"/>
+      <c r="A27" s="293"/>
+      <c r="B27" s="294"/>
+      <c r="C27" s="294"/>
+      <c r="D27" s="294"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="200"/>
+      <c r="G27" s="200"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="200"/>
+      <c r="K27" s="200"/>
+      <c r="L27" s="200"/>
+      <c r="M27" s="215"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="201"/>
-      <c r="B28" s="202"/>
-      <c r="C28" s="202"/>
-      <c r="D28" s="202"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="142"/>
-      <c r="G28" s="142"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="142"/>
-      <c r="K28" s="142"/>
-      <c r="L28" s="142"/>
-      <c r="M28" s="143"/>
+      <c r="A28" s="293"/>
+      <c r="B28" s="294"/>
+      <c r="C28" s="294"/>
+      <c r="D28" s="294"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="200"/>
+      <c r="G28" s="200"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="200"/>
+      <c r="K28" s="200"/>
+      <c r="L28" s="200"/>
+      <c r="M28" s="215"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="201"/>
-      <c r="B29" s="202"/>
-      <c r="C29" s="202"/>
-      <c r="D29" s="202"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="142"/>
-      <c r="G29" s="142"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="142"/>
-      <c r="K29" s="142"/>
-      <c r="L29" s="142"/>
-      <c r="M29" s="143"/>
+      <c r="A29" s="293"/>
+      <c r="B29" s="294"/>
+      <c r="C29" s="294"/>
+      <c r="D29" s="294"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="200"/>
+      <c r="G29" s="200"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="200"/>
+      <c r="K29" s="200"/>
+      <c r="L29" s="200"/>
+      <c r="M29" s="215"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="201"/>
-      <c r="B30" s="202"/>
-      <c r="C30" s="202"/>
-      <c r="D30" s="202"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="142"/>
-      <c r="G30" s="142"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="142"/>
-      <c r="K30" s="142"/>
-      <c r="L30" s="142"/>
-      <c r="M30" s="143"/>
+      <c r="A30" s="293"/>
+      <c r="B30" s="294"/>
+      <c r="C30" s="294"/>
+      <c r="D30" s="294"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="200"/>
+      <c r="G30" s="200"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="200"/>
+      <c r="K30" s="200"/>
+      <c r="L30" s="200"/>
+      <c r="M30" s="215"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="201"/>
-      <c r="B31" s="202"/>
-      <c r="C31" s="202"/>
-      <c r="D31" s="202"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="142"/>
-      <c r="G31" s="142"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="142"/>
-      <c r="K31" s="142"/>
-      <c r="L31" s="142"/>
-      <c r="M31" s="143"/>
+      <c r="A31" s="293"/>
+      <c r="B31" s="294"/>
+      <c r="C31" s="294"/>
+      <c r="D31" s="294"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="200"/>
+      <c r="G31" s="200"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="200"/>
+      <c r="K31" s="200"/>
+      <c r="L31" s="200"/>
+      <c r="M31" s="215"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="201"/>
-      <c r="B32" s="202"/>
-      <c r="C32" s="202"/>
-      <c r="D32" s="202"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="142"/>
-      <c r="G32" s="142"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="142"/>
-      <c r="K32" s="142"/>
-      <c r="L32" s="142"/>
-      <c r="M32" s="143"/>
+      <c r="A32" s="293"/>
+      <c r="B32" s="294"/>
+      <c r="C32" s="294"/>
+      <c r="D32" s="294"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="200"/>
+      <c r="G32" s="200"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="200"/>
+      <c r="K32" s="200"/>
+      <c r="L32" s="200"/>
+      <c r="M32" s="215"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A33" s="201"/>
-      <c r="B33" s="202"/>
-      <c r="C33" s="202"/>
-      <c r="D33" s="202"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="142"/>
-      <c r="G33" s="142"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="142"/>
-      <c r="K33" s="142"/>
-      <c r="L33" s="142"/>
-      <c r="M33" s="143"/>
+      <c r="A33" s="293"/>
+      <c r="B33" s="294"/>
+      <c r="C33" s="294"/>
+      <c r="D33" s="294"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="200"/>
+      <c r="G33" s="200"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="200"/>
+      <c r="K33" s="200"/>
+      <c r="L33" s="200"/>
+      <c r="M33" s="215"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A34" s="201"/>
-      <c r="B34" s="202"/>
-      <c r="C34" s="202"/>
-      <c r="D34" s="202"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="142"/>
-      <c r="G34" s="142"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="142"/>
-      <c r="K34" s="142"/>
-      <c r="L34" s="142"/>
-      <c r="M34" s="143"/>
+      <c r="A34" s="293"/>
+      <c r="B34" s="294"/>
+      <c r="C34" s="294"/>
+      <c r="D34" s="294"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="200"/>
+      <c r="G34" s="200"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="200"/>
+      <c r="K34" s="200"/>
+      <c r="L34" s="200"/>
+      <c r="M34" s="215"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35" s="201"/>
-      <c r="B35" s="202"/>
-      <c r="C35" s="202"/>
-      <c r="D35" s="202"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="142"/>
-      <c r="G35" s="142"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="142"/>
-      <c r="K35" s="142"/>
-      <c r="L35" s="142"/>
-      <c r="M35" s="143"/>
+      <c r="A35" s="293"/>
+      <c r="B35" s="294"/>
+      <c r="C35" s="294"/>
+      <c r="D35" s="294"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="200"/>
+      <c r="G35" s="200"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="200"/>
+      <c r="K35" s="200"/>
+      <c r="L35" s="200"/>
+      <c r="M35" s="215"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A36" s="201"/>
-      <c r="B36" s="202"/>
-      <c r="C36" s="202"/>
-      <c r="D36" s="202"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="142"/>
-      <c r="G36" s="142"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="142"/>
-      <c r="K36" s="142"/>
-      <c r="L36" s="142"/>
-      <c r="M36" s="143"/>
+      <c r="A36" s="293"/>
+      <c r="B36" s="294"/>
+      <c r="C36" s="294"/>
+      <c r="D36" s="294"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="200"/>
+      <c r="G36" s="200"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="200"/>
+      <c r="K36" s="200"/>
+      <c r="L36" s="200"/>
+      <c r="M36" s="215"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A37" s="201"/>
-      <c r="B37" s="202"/>
-      <c r="C37" s="202"/>
-      <c r="D37" s="202"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="142"/>
-      <c r="G37" s="142"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="142"/>
-      <c r="K37" s="142"/>
-      <c r="L37" s="142"/>
-      <c r="M37" s="143"/>
+      <c r="A37" s="293"/>
+      <c r="B37" s="294"/>
+      <c r="C37" s="294"/>
+      <c r="D37" s="294"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="200"/>
+      <c r="G37" s="200"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="200"/>
+      <c r="K37" s="200"/>
+      <c r="L37" s="200"/>
+      <c r="M37" s="215"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A38" s="201"/>
-      <c r="B38" s="202"/>
-      <c r="C38" s="202"/>
-      <c r="D38" s="202"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="142"/>
-      <c r="G38" s="142"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="142"/>
-      <c r="K38" s="142"/>
-      <c r="L38" s="142"/>
-      <c r="M38" s="143"/>
+      <c r="A38" s="293"/>
+      <c r="B38" s="294"/>
+      <c r="C38" s="294"/>
+      <c r="D38" s="294"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="200"/>
+      <c r="G38" s="200"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="200"/>
+      <c r="K38" s="200"/>
+      <c r="L38" s="200"/>
+      <c r="M38" s="215"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A39" s="201"/>
-      <c r="B39" s="202"/>
-      <c r="C39" s="202"/>
-      <c r="D39" s="202"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="142"/>
-      <c r="G39" s="142"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="142"/>
-      <c r="K39" s="142"/>
-      <c r="L39" s="142"/>
-      <c r="M39" s="143"/>
+      <c r="A39" s="293"/>
+      <c r="B39" s="294"/>
+      <c r="C39" s="294"/>
+      <c r="D39" s="294"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="200"/>
+      <c r="G39" s="200"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="200"/>
+      <c r="K39" s="200"/>
+      <c r="L39" s="200"/>
+      <c r="M39" s="215"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A40" s="201"/>
-      <c r="B40" s="202"/>
-      <c r="C40" s="202"/>
-      <c r="D40" s="202"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="142"/>
-      <c r="G40" s="142"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="142"/>
-      <c r="K40" s="142"/>
-      <c r="L40" s="142"/>
-      <c r="M40" s="143"/>
+      <c r="A40" s="293"/>
+      <c r="B40" s="294"/>
+      <c r="C40" s="294"/>
+      <c r="D40" s="294"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="200"/>
+      <c r="G40" s="200"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="200"/>
+      <c r="K40" s="200"/>
+      <c r="L40" s="200"/>
+      <c r="M40" s="215"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A41" s="201"/>
-      <c r="B41" s="202"/>
-      <c r="C41" s="202"/>
-      <c r="D41" s="202"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="142"/>
-      <c r="G41" s="142"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="14"/>
-      <c r="J41" s="142"/>
-      <c r="K41" s="142"/>
-      <c r="L41" s="142"/>
-      <c r="M41" s="143"/>
+      <c r="A41" s="293"/>
+      <c r="B41" s="294"/>
+      <c r="C41" s="294"/>
+      <c r="D41" s="294"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="200"/>
+      <c r="G41" s="200"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="200"/>
+      <c r="K41" s="200"/>
+      <c r="L41" s="200"/>
+      <c r="M41" s="215"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A42" s="201"/>
-      <c r="B42" s="202"/>
-      <c r="C42" s="202"/>
-      <c r="D42" s="202"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="142"/>
-      <c r="G42" s="142"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="142"/>
-      <c r="K42" s="142"/>
-      <c r="L42" s="142"/>
-      <c r="M42" s="143"/>
+      <c r="A42" s="293"/>
+      <c r="B42" s="294"/>
+      <c r="C42" s="294"/>
+      <c r="D42" s="294"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="200"/>
+      <c r="G42" s="200"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="200"/>
+      <c r="K42" s="200"/>
+      <c r="L42" s="200"/>
+      <c r="M42" s="215"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A43" s="201"/>
-      <c r="B43" s="202"/>
-      <c r="C43" s="202"/>
-      <c r="D43" s="202"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="142"/>
-      <c r="G43" s="142"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="14"/>
-      <c r="J43" s="142"/>
-      <c r="K43" s="142"/>
-      <c r="L43" s="142"/>
-      <c r="M43" s="143"/>
+      <c r="A43" s="293"/>
+      <c r="B43" s="294"/>
+      <c r="C43" s="294"/>
+      <c r="D43" s="294"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="200"/>
+      <c r="G43" s="200"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="200"/>
+      <c r="K43" s="200"/>
+      <c r="L43" s="200"/>
+      <c r="M43" s="215"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A44" s="201"/>
-      <c r="B44" s="202"/>
-      <c r="C44" s="202"/>
-      <c r="D44" s="202"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="142"/>
-      <c r="G44" s="142"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="14"/>
-      <c r="J44" s="142"/>
-      <c r="K44" s="142"/>
-      <c r="L44" s="142"/>
-      <c r="M44" s="143"/>
+      <c r="A44" s="293"/>
+      <c r="B44" s="294"/>
+      <c r="C44" s="294"/>
+      <c r="D44" s="294"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="200"/>
+      <c r="G44" s="200"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="200"/>
+      <c r="K44" s="200"/>
+      <c r="L44" s="200"/>
+      <c r="M44" s="215"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A45" s="201"/>
-      <c r="B45" s="202"/>
-      <c r="C45" s="202"/>
-      <c r="D45" s="202"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="142"/>
-      <c r="G45" s="142"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="14"/>
-      <c r="J45" s="142"/>
-      <c r="K45" s="142"/>
-      <c r="L45" s="142"/>
-      <c r="M45" s="143"/>
+      <c r="A45" s="293"/>
+      <c r="B45" s="294"/>
+      <c r="C45" s="294"/>
+      <c r="D45" s="294"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="200"/>
+      <c r="G45" s="200"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="200"/>
+      <c r="K45" s="200"/>
+      <c r="L45" s="200"/>
+      <c r="M45" s="215"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A46" s="201"/>
-      <c r="B46" s="202"/>
-      <c r="C46" s="202"/>
-      <c r="D46" s="202"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="142"/>
-      <c r="G46" s="142"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="14"/>
-      <c r="J46" s="142"/>
-      <c r="K46" s="142"/>
-      <c r="L46" s="142"/>
-      <c r="M46" s="143"/>
+      <c r="A46" s="293"/>
+      <c r="B46" s="294"/>
+      <c r="C46" s="294"/>
+      <c r="D46" s="294"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="200"/>
+      <c r="G46" s="200"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="200"/>
+      <c r="K46" s="200"/>
+      <c r="L46" s="200"/>
+      <c r="M46" s="215"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A47" s="201"/>
-      <c r="B47" s="202"/>
-      <c r="C47" s="202"/>
-      <c r="D47" s="202"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="142"/>
-      <c r="G47" s="142"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="14"/>
-      <c r="J47" s="142"/>
-      <c r="K47" s="142"/>
-      <c r="L47" s="142"/>
-      <c r="M47" s="143"/>
+      <c r="A47" s="293"/>
+      <c r="B47" s="294"/>
+      <c r="C47" s="294"/>
+      <c r="D47" s="294"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="200"/>
+      <c r="G47" s="200"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="200"/>
+      <c r="K47" s="200"/>
+      <c r="L47" s="200"/>
+      <c r="M47" s="215"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A48" s="201"/>
-      <c r="B48" s="202"/>
-      <c r="C48" s="202"/>
-      <c r="D48" s="202"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="142"/>
-      <c r="G48" s="142"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="142"/>
-      <c r="K48" s="142"/>
-      <c r="L48" s="142"/>
-      <c r="M48" s="143"/>
+      <c r="A48" s="293"/>
+      <c r="B48" s="294"/>
+      <c r="C48" s="294"/>
+      <c r="D48" s="294"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="200"/>
+      <c r="G48" s="200"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="200"/>
+      <c r="K48" s="200"/>
+      <c r="L48" s="200"/>
+      <c r="M48" s="215"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A49" s="201"/>
-      <c r="B49" s="202"/>
-      <c r="C49" s="202"/>
-      <c r="D49" s="202"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="142"/>
-      <c r="G49" s="142"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="14"/>
-      <c r="J49" s="142"/>
-      <c r="K49" s="142"/>
-      <c r="L49" s="142"/>
-      <c r="M49" s="143"/>
+      <c r="A49" s="293"/>
+      <c r="B49" s="294"/>
+      <c r="C49" s="294"/>
+      <c r="D49" s="294"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="200"/>
+      <c r="G49" s="200"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="200"/>
+      <c r="K49" s="200"/>
+      <c r="L49" s="200"/>
+      <c r="M49" s="215"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="146" t="s">
+      <c r="A50" s="197" t="s">
         <v>22</v>
       </c>
-      <c r="B50" s="147"/>
-      <c r="C50" s="147"/>
-      <c r="D50" s="147"/>
-      <c r="E50" s="21">
-        <f>SUM(E5:E25,BOL!E22:E29)</f>
+      <c r="B50" s="198"/>
+      <c r="C50" s="198"/>
+      <c r="D50" s="198"/>
+      <c r="E50" s="109">
+        <f>SUM(E5:E25,MasterBOL!E22:E29)</f>
         <v>1688</v>
       </c>
-      <c r="F50" s="215">
-        <f>SUM(F5:F25,BOL!F22:F29)</f>
+      <c r="F50" s="439">
+        <f>SUM(F5:F25,MasterBOL!F22:F29)</f>
         <v>1688</v>
       </c>
-      <c r="G50" s="216"/>
-      <c r="H50" s="31"/>
-      <c r="I50" s="32"/>
-      <c r="J50" s="217"/>
-      <c r="K50" s="217"/>
-      <c r="L50" s="217"/>
-      <c r="M50" s="218"/>
+      <c r="G50" s="440"/>
+      <c r="H50" s="29"/>
+      <c r="I50" s="30"/>
+      <c r="J50" s="295"/>
+      <c r="K50" s="295"/>
+      <c r="L50" s="295"/>
+      <c r="M50" s="296"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A51" s="203" t="s">
+      <c r="A51" s="281" t="s">
         <v>58</v>
       </c>
-      <c r="B51" s="204"/>
-      <c r="C51" s="204"/>
-      <c r="D51" s="204"/>
-      <c r="E51" s="204"/>
-      <c r="F51" s="204"/>
-      <c r="G51" s="204"/>
-      <c r="H51" s="204"/>
-      <c r="I51" s="204"/>
-      <c r="J51" s="204"/>
-      <c r="K51" s="204"/>
-      <c r="L51" s="204"/>
-      <c r="M51" s="205"/>
+      <c r="B51" s="282"/>
+      <c r="C51" s="282"/>
+      <c r="D51" s="282"/>
+      <c r="E51" s="282"/>
+      <c r="F51" s="282"/>
+      <c r="G51" s="282"/>
+      <c r="H51" s="282"/>
+      <c r="I51" s="282"/>
+      <c r="J51" s="282"/>
+      <c r="K51" s="282"/>
+      <c r="L51" s="282"/>
+      <c r="M51" s="283"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="206"/>
-      <c r="B52" s="207"/>
-      <c r="C52" s="207"/>
-      <c r="D52" s="207"/>
-      <c r="E52" s="207"/>
-      <c r="F52" s="207"/>
-      <c r="G52" s="207"/>
-      <c r="H52" s="207"/>
-      <c r="I52" s="207"/>
-      <c r="J52" s="207"/>
-      <c r="K52" s="207"/>
-      <c r="L52" s="207"/>
-      <c r="M52" s="208"/>
+      <c r="A52" s="284"/>
+      <c r="B52" s="285"/>
+      <c r="C52" s="285"/>
+      <c r="D52" s="285"/>
+      <c r="E52" s="285"/>
+      <c r="F52" s="285"/>
+      <c r="G52" s="285"/>
+      <c r="H52" s="285"/>
+      <c r="I52" s="285"/>
+      <c r="J52" s="285"/>
+      <c r="K52" s="285"/>
+      <c r="L52" s="285"/>
+      <c r="M52" s="286"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A53" s="209"/>
-      <c r="B53" s="210"/>
-      <c r="C53" s="210"/>
-      <c r="D53" s="210"/>
-      <c r="E53" s="210"/>
-      <c r="F53" s="210"/>
-      <c r="G53" s="210"/>
-      <c r="H53" s="210"/>
-      <c r="I53" s="210"/>
-      <c r="J53" s="210"/>
-      <c r="K53" s="210"/>
-      <c r="L53" s="210"/>
-      <c r="M53" s="211"/>
+      <c r="A53" s="287"/>
+      <c r="B53" s="288"/>
+      <c r="C53" s="288"/>
+      <c r="D53" s="288"/>
+      <c r="E53" s="288"/>
+      <c r="F53" s="288"/>
+      <c r="G53" s="288"/>
+      <c r="H53" s="288"/>
+      <c r="I53" s="288"/>
+      <c r="J53" s="288"/>
+      <c r="K53" s="288"/>
+      <c r="L53" s="288"/>
+      <c r="M53" s="289"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A54" s="209"/>
-      <c r="B54" s="210"/>
-      <c r="C54" s="210"/>
-      <c r="D54" s="210"/>
-      <c r="E54" s="210"/>
-      <c r="F54" s="210"/>
-      <c r="G54" s="210"/>
-      <c r="H54" s="210"/>
-      <c r="I54" s="210"/>
-      <c r="J54" s="210"/>
-      <c r="K54" s="210"/>
-      <c r="L54" s="210"/>
-      <c r="M54" s="211"/>
+      <c r="A54" s="287"/>
+      <c r="B54" s="288"/>
+      <c r="C54" s="288"/>
+      <c r="D54" s="288"/>
+      <c r="E54" s="288"/>
+      <c r="F54" s="288"/>
+      <c r="G54" s="288"/>
+      <c r="H54" s="288"/>
+      <c r="I54" s="288"/>
+      <c r="J54" s="288"/>
+      <c r="K54" s="288"/>
+      <c r="L54" s="288"/>
+      <c r="M54" s="289"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A55" s="209"/>
-      <c r="B55" s="210"/>
-      <c r="C55" s="210"/>
-      <c r="D55" s="210"/>
-      <c r="E55" s="210"/>
-      <c r="F55" s="210"/>
-      <c r="G55" s="210"/>
-      <c r="H55" s="210"/>
-      <c r="I55" s="210"/>
-      <c r="J55" s="210"/>
-      <c r="K55" s="210"/>
-      <c r="L55" s="210"/>
-      <c r="M55" s="211"/>
+      <c r="A55" s="287"/>
+      <c r="B55" s="288"/>
+      <c r="C55" s="288"/>
+      <c r="D55" s="288"/>
+      <c r="E55" s="288"/>
+      <c r="F55" s="288"/>
+      <c r="G55" s="288"/>
+      <c r="H55" s="288"/>
+      <c r="I55" s="288"/>
+      <c r="J55" s="288"/>
+      <c r="K55" s="288"/>
+      <c r="L55" s="288"/>
+      <c r="M55" s="289"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A56" s="209"/>
-      <c r="B56" s="210"/>
-      <c r="C56" s="210"/>
-      <c r="D56" s="210"/>
-      <c r="E56" s="210"/>
-      <c r="F56" s="210"/>
-      <c r="G56" s="210"/>
-      <c r="H56" s="210"/>
-      <c r="I56" s="210"/>
-      <c r="J56" s="210"/>
-      <c r="K56" s="210"/>
-      <c r="L56" s="210"/>
-      <c r="M56" s="211"/>
+      <c r="A56" s="287"/>
+      <c r="B56" s="288"/>
+      <c r="C56" s="288"/>
+      <c r="D56" s="288"/>
+      <c r="E56" s="288"/>
+      <c r="F56" s="288"/>
+      <c r="G56" s="288"/>
+      <c r="H56" s="288"/>
+      <c r="I56" s="288"/>
+      <c r="J56" s="288"/>
+      <c r="K56" s="288"/>
+      <c r="L56" s="288"/>
+      <c r="M56" s="289"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A57" s="209"/>
-      <c r="B57" s="210"/>
-      <c r="C57" s="210"/>
-      <c r="D57" s="210"/>
-      <c r="E57" s="210"/>
-      <c r="F57" s="210"/>
-      <c r="G57" s="210"/>
-      <c r="H57" s="210"/>
-      <c r="I57" s="210"/>
-      <c r="J57" s="210"/>
-      <c r="K57" s="210"/>
-      <c r="L57" s="210"/>
-      <c r="M57" s="211"/>
+      <c r="A57" s="287"/>
+      <c r="B57" s="288"/>
+      <c r="C57" s="288"/>
+      <c r="D57" s="288"/>
+      <c r="E57" s="288"/>
+      <c r="F57" s="288"/>
+      <c r="G57" s="288"/>
+      <c r="H57" s="288"/>
+      <c r="I57" s="288"/>
+      <c r="J57" s="288"/>
+      <c r="K57" s="288"/>
+      <c r="L57" s="288"/>
+      <c r="M57" s="289"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A58" s="209"/>
-      <c r="B58" s="210"/>
-      <c r="C58" s="210"/>
-      <c r="D58" s="210"/>
-      <c r="E58" s="210"/>
-      <c r="F58" s="210"/>
-      <c r="G58" s="210"/>
-      <c r="H58" s="210"/>
-      <c r="I58" s="210"/>
-      <c r="J58" s="210"/>
-      <c r="K58" s="210"/>
-      <c r="L58" s="210"/>
-      <c r="M58" s="211"/>
+      <c r="A58" s="287"/>
+      <c r="B58" s="288"/>
+      <c r="C58" s="288"/>
+      <c r="D58" s="288"/>
+      <c r="E58" s="288"/>
+      <c r="F58" s="288"/>
+      <c r="G58" s="288"/>
+      <c r="H58" s="288"/>
+      <c r="I58" s="288"/>
+      <c r="J58" s="288"/>
+      <c r="K58" s="288"/>
+      <c r="L58" s="288"/>
+      <c r="M58" s="289"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A59" s="209"/>
-      <c r="B59" s="210"/>
-      <c r="C59" s="210"/>
-      <c r="D59" s="210"/>
-      <c r="E59" s="210"/>
-      <c r="F59" s="210"/>
-      <c r="G59" s="210"/>
-      <c r="H59" s="210"/>
-      <c r="I59" s="210"/>
-      <c r="J59" s="210"/>
-      <c r="K59" s="210"/>
-      <c r="L59" s="210"/>
-      <c r="M59" s="211"/>
+      <c r="A59" s="287"/>
+      <c r="B59" s="288"/>
+      <c r="C59" s="288"/>
+      <c r="D59" s="288"/>
+      <c r="E59" s="288"/>
+      <c r="F59" s="288"/>
+      <c r="G59" s="288"/>
+      <c r="H59" s="288"/>
+      <c r="I59" s="288"/>
+      <c r="J59" s="288"/>
+      <c r="K59" s="288"/>
+      <c r="L59" s="288"/>
+      <c r="M59" s="289"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A60" s="212"/>
-      <c r="B60" s="213"/>
-      <c r="C60" s="213"/>
-      <c r="D60" s="213"/>
-      <c r="E60" s="213"/>
-      <c r="F60" s="213"/>
-      <c r="G60" s="213"/>
-      <c r="H60" s="213"/>
-      <c r="I60" s="213"/>
-      <c r="J60" s="213"/>
-      <c r="K60" s="213"/>
-      <c r="L60" s="213"/>
-      <c r="M60" s="214"/>
+      <c r="A60" s="290"/>
+      <c r="B60" s="291"/>
+      <c r="C60" s="291"/>
+      <c r="D60" s="291"/>
+      <c r="E60" s="291"/>
+      <c r="F60" s="291"/>
+      <c r="G60" s="291"/>
+      <c r="H60" s="291"/>
+      <c r="I60" s="291"/>
+      <c r="J60" s="291"/>
+      <c r="K60" s="291"/>
+      <c r="L60" s="291"/>
+      <c r="M60" s="292"/>
     </row>
     <row r="61" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="30"/>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="25"/>
-      <c r="I61" s="25"/>
-      <c r="J61" s="25"/>
+      <c r="A61" s="28"/>
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="23"/>
+      <c r="I61" s="23"/>
+      <c r="J61" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="150">
-    <mergeCell ref="A51:M51"/>
-    <mergeCell ref="A52:M60"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="J49:M49"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="J50:M50"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="J47:M47"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="J48:M48"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="J46:M46"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="J44:M44"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="J42:M42"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="J39:M39"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="J40:M40"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="J20:M20"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="J18:M18"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="J11:M11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="J12:M12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="J9:M9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="J10:M10"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="J8:M8"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="J5:M5"/>
@@ -8253,6 +8104,140 @@
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="J3:M4"/>
     <mergeCell ref="H4:I4"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="J10:M10"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="J42:M42"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="J40:M40"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="J46:M46"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="J44:M44"/>
+    <mergeCell ref="A51:M51"/>
+    <mergeCell ref="A52:M60"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="J49:M49"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="J50:M50"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="J48:M48"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.26" top="0.2" bottom="0.27" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8276,640 +8261,640 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="40" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="335">
+      <c r="B1" s="303">
         <v>45877</v>
       </c>
-      <c r="C1" s="335"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43" t="s">
+      <c r="C1" s="303"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="340" t="s">
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="310" t="s">
         <v>72</v>
       </c>
-      <c r="M1" s="341"/>
+      <c r="M1" s="311"/>
     </row>
     <row r="2" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="337" t="s">
+      <c r="A2" s="307" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="338"/>
-      <c r="C2" s="338"/>
-      <c r="D2" s="338"/>
-      <c r="E2" s="338"/>
-      <c r="F2" s="338"/>
-      <c r="G2" s="338"/>
-      <c r="H2" s="339"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="47"/>
+      <c r="B2" s="308"/>
+      <c r="C2" s="308"/>
+      <c r="D2" s="308"/>
+      <c r="E2" s="308"/>
+      <c r="F2" s="308"/>
+      <c r="G2" s="308"/>
+      <c r="H2" s="309"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="45"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="302" t="s">
+      <c r="A3" s="317" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="303"/>
-      <c r="C3" s="303"/>
-      <c r="D3" s="303"/>
-      <c r="E3" s="303"/>
-      <c r="F3" s="303"/>
-      <c r="G3" s="303"/>
-      <c r="H3" s="304"/>
-      <c r="I3" s="48" t="s">
+      <c r="B3" s="318"/>
+      <c r="C3" s="318"/>
+      <c r="D3" s="318"/>
+      <c r="E3" s="318"/>
+      <c r="F3" s="318"/>
+      <c r="G3" s="318"/>
+      <c r="H3" s="319"/>
+      <c r="I3" s="46" t="s">
         <v>193</v>
       </c>
-      <c r="J3" s="46"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="50"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="48"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="302" t="s">
+      <c r="A4" s="317" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="303"/>
-      <c r="C4" s="303"/>
-      <c r="D4" s="303"/>
-      <c r="E4" s="303"/>
-      <c r="F4" s="303"/>
-      <c r="G4" s="303"/>
-      <c r="H4" s="304"/>
-      <c r="I4" s="347"/>
-      <c r="J4" s="331"/>
-      <c r="K4" s="331"/>
-      <c r="L4" s="331"/>
-      <c r="M4" s="332"/>
+      <c r="B4" s="318"/>
+      <c r="C4" s="318"/>
+      <c r="D4" s="318"/>
+      <c r="E4" s="318"/>
+      <c r="F4" s="318"/>
+      <c r="G4" s="318"/>
+      <c r="H4" s="319"/>
+      <c r="I4" s="321"/>
+      <c r="J4" s="299"/>
+      <c r="K4" s="299"/>
+      <c r="L4" s="299"/>
+      <c r="M4" s="300"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="302" t="s">
+      <c r="A5" s="317" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="303"/>
-      <c r="C5" s="303"/>
-      <c r="D5" s="303"/>
-      <c r="E5" s="303"/>
-      <c r="F5" s="303"/>
-      <c r="G5" s="303"/>
-      <c r="H5" s="304"/>
-      <c r="I5" s="347"/>
-      <c r="J5" s="331"/>
-      <c r="K5" s="331"/>
-      <c r="L5" s="331"/>
-      <c r="M5" s="332"/>
+      <c r="B5" s="318"/>
+      <c r="C5" s="318"/>
+      <c r="D5" s="318"/>
+      <c r="E5" s="318"/>
+      <c r="F5" s="318"/>
+      <c r="G5" s="318"/>
+      <c r="H5" s="319"/>
+      <c r="I5" s="321"/>
+      <c r="J5" s="299"/>
+      <c r="K5" s="299"/>
+      <c r="L5" s="299"/>
+      <c r="M5" s="300"/>
     </row>
     <row r="6" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="345" t="s">
+      <c r="A6" s="315" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="301"/>
-      <c r="C6" s="301"/>
-      <c r="D6" s="301"/>
-      <c r="E6" s="301"/>
-      <c r="F6" s="346" t="s">
+      <c r="B6" s="316"/>
+      <c r="C6" s="316"/>
+      <c r="D6" s="316"/>
+      <c r="E6" s="316"/>
+      <c r="F6" s="320" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="346"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="348"/>
-      <c r="J6" s="349"/>
-      <c r="K6" s="349"/>
-      <c r="L6" s="349"/>
-      <c r="M6" s="350"/>
+      <c r="G6" s="320"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="322"/>
+      <c r="J6" s="323"/>
+      <c r="K6" s="323"/>
+      <c r="L6" s="323"/>
+      <c r="M6" s="324"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="352" t="s">
+      <c r="A7" s="333" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="353"/>
-      <c r="C7" s="353"/>
-      <c r="D7" s="353"/>
-      <c r="E7" s="353"/>
-      <c r="F7" s="353"/>
-      <c r="G7" s="353"/>
-      <c r="H7" s="354"/>
-      <c r="I7" s="52" t="s">
+      <c r="B7" s="334"/>
+      <c r="C7" s="334"/>
+      <c r="D7" s="334"/>
+      <c r="E7" s="334"/>
+      <c r="F7" s="334"/>
+      <c r="G7" s="334"/>
+      <c r="H7" s="335"/>
+      <c r="I7" s="50" t="s">
         <v>233</v>
       </c>
-      <c r="J7" s="53"/>
-      <c r="K7" s="54" t="str">
+      <c r="J7" s="51"/>
+      <c r="K7" s="52" t="str">
         <f>ADDRESS!I1</f>
         <v>CH Robinson</v>
       </c>
-      <c r="L7" s="53"/>
-      <c r="M7" s="55"/>
+      <c r="L7" s="51"/>
+      <c r="M7" s="53"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="88" t="s">
+      <c r="B8" s="441" t="s">
         <v>113</v>
       </c>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="298" t="s">
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="339" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="298"/>
-      <c r="G8" s="298"/>
-      <c r="H8" s="299"/>
-      <c r="I8" s="351" t="s">
+      <c r="F8" s="339"/>
+      <c r="G8" s="339"/>
+      <c r="H8" s="340"/>
+      <c r="I8" s="325" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="303"/>
-      <c r="K8" s="303"/>
-      <c r="L8" s="303"/>
-      <c r="M8" s="304"/>
+      <c r="J8" s="318"/>
+      <c r="K8" s="318"/>
+      <c r="L8" s="318"/>
+      <c r="M8" s="319"/>
     </row>
     <row r="9" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="58" t="s">
+      <c r="A9" s="56" t="s">
         <v>2</v>
       </c>
       <c r="B9" t="str">
         <f>VLOOKUP(B8,ADDRESS!$A$2:$E$30,2,FALSE)</f>
         <v>13790 Harvey Road</v>
       </c>
-      <c r="H9" s="59"/>
-      <c r="I9" s="60" t="s">
+      <c r="H9" s="57"/>
+      <c r="I9" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="J9" s="61"/>
-      <c r="K9" s="61">
+      <c r="J9" s="59"/>
+      <c r="K9" s="59">
         <f>ADDRESS!I3</f>
         <v>10285609</v>
       </c>
-      <c r="L9" s="61"/>
-      <c r="M9" s="51"/>
+      <c r="L9" s="59"/>
+      <c r="M9" s="49"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="62" t="s">
+      <c r="A10" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="330" t="str">
+      <c r="C10" s="372" t="str">
         <f>CONCATENATE(VLOOKUP(B8,ADDRESS!$A$2:$E$30,3,FALSE),", ",VLOOKUP(B8,ADDRESS!$A$2:$E$30,4,FALSE)," ",VLOOKUP(B8,ADDRESS!$A$2:$E$30,5,FALSE))</f>
         <v>TYLER, TX 75706</v>
       </c>
-      <c r="D10" s="330"/>
-      <c r="E10" s="330"/>
-      <c r="F10" s="330"/>
-      <c r="G10" s="330"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="63" t="s">
+      <c r="D10" s="372"/>
+      <c r="E10" s="372"/>
+      <c r="F10" s="372"/>
+      <c r="G10" s="372"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="61" t="s">
         <v>234</v>
       </c>
-      <c r="J10" s="64" t="str">
+      <c r="J10" s="62" t="str">
         <f>ADDRESS!I2</f>
         <v>RBTW</v>
       </c>
-      <c r="K10" s="64"/>
-      <c r="L10" s="64"/>
-      <c r="M10" s="65"/>
+      <c r="K10" s="62"/>
+      <c r="L10" s="62"/>
+      <c r="M10" s="63"/>
     </row>
     <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="300" t="s">
+      <c r="A11" s="341" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="301"/>
-      <c r="C11" s="301"/>
-      <c r="D11" s="301"/>
-      <c r="E11" s="301"/>
-      <c r="F11" s="346" t="s">
+      <c r="B11" s="316"/>
+      <c r="C11" s="316"/>
+      <c r="D11" s="316"/>
+      <c r="E11" s="316"/>
+      <c r="F11" s="320" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="346"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="333" t="s">
+      <c r="G11" s="320"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="301" t="s">
         <v>75</v>
       </c>
-      <c r="J11" s="334"/>
-      <c r="K11" s="66">
+      <c r="J11" s="302"/>
+      <c r="K11" s="64">
         <f>ADDRESS!I4</f>
         <v>523953410</v>
       </c>
-      <c r="L11" s="66"/>
-      <c r="M11" s="67"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="65"/>
     </row>
     <row r="12" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="269" t="s">
+      <c r="A12" s="326" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="270"/>
-      <c r="C12" s="270"/>
-      <c r="D12" s="270"/>
-      <c r="E12" s="270"/>
-      <c r="F12" s="270"/>
-      <c r="G12" s="270"/>
-      <c r="H12" s="271"/>
-      <c r="I12" s="347"/>
-      <c r="J12" s="331"/>
-      <c r="K12" s="331"/>
-      <c r="L12" s="331"/>
-      <c r="M12" s="332"/>
+      <c r="B12" s="327"/>
+      <c r="C12" s="327"/>
+      <c r="D12" s="327"/>
+      <c r="E12" s="327"/>
+      <c r="F12" s="327"/>
+      <c r="G12" s="327"/>
+      <c r="H12" s="328"/>
+      <c r="I12" s="321"/>
+      <c r="J12" s="299"/>
+      <c r="K12" s="299"/>
+      <c r="L12" s="299"/>
+      <c r="M12" s="300"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="342" t="s">
+      <c r="A13" s="312" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="343"/>
-      <c r="C13" s="343"/>
-      <c r="D13" s="343"/>
-      <c r="E13" s="343"/>
-      <c r="F13" s="343"/>
-      <c r="G13" s="343"/>
-      <c r="H13" s="344"/>
-      <c r="I13" s="347"/>
-      <c r="J13" s="331"/>
-      <c r="K13" s="331"/>
-      <c r="L13" s="331"/>
-      <c r="M13" s="332"/>
+      <c r="B13" s="313"/>
+      <c r="C13" s="313"/>
+      <c r="D13" s="313"/>
+      <c r="E13" s="313"/>
+      <c r="F13" s="313"/>
+      <c r="G13" s="313"/>
+      <c r="H13" s="314"/>
+      <c r="I13" s="321"/>
+      <c r="J13" s="299"/>
+      <c r="K13" s="299"/>
+      <c r="L13" s="299"/>
+      <c r="M13" s="300"/>
     </row>
     <row r="14" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="302" t="s">
+      <c r="A14" s="317" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="303"/>
-      <c r="C14" s="303"/>
-      <c r="D14" s="303"/>
-      <c r="E14" s="303"/>
-      <c r="F14" s="303"/>
-      <c r="G14" s="303"/>
-      <c r="H14" s="304"/>
-      <c r="I14" s="348"/>
-      <c r="J14" s="349"/>
-      <c r="K14" s="349"/>
-      <c r="L14" s="349"/>
-      <c r="M14" s="350"/>
+      <c r="B14" s="318"/>
+      <c r="C14" s="318"/>
+      <c r="D14" s="318"/>
+      <c r="E14" s="318"/>
+      <c r="F14" s="318"/>
+      <c r="G14" s="318"/>
+      <c r="H14" s="319"/>
+      <c r="I14" s="322"/>
+      <c r="J14" s="323"/>
+      <c r="K14" s="323"/>
+      <c r="L14" s="323"/>
+      <c r="M14" s="324"/>
     </row>
     <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="312" t="s">
+      <c r="A15" s="349" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="313"/>
-      <c r="C15" s="313"/>
-      <c r="D15" s="313"/>
-      <c r="E15" s="313"/>
-      <c r="F15" s="314"/>
-      <c r="G15" s="314"/>
-      <c r="H15" s="314"/>
-      <c r="I15" s="309" t="s">
+      <c r="B15" s="350"/>
+      <c r="C15" s="350"/>
+      <c r="D15" s="350"/>
+      <c r="E15" s="350"/>
+      <c r="F15" s="351"/>
+      <c r="G15" s="351"/>
+      <c r="H15" s="351"/>
+      <c r="I15" s="346" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="310"/>
-      <c r="K15" s="310"/>
-      <c r="L15" s="310"/>
-      <c r="M15" s="311"/>
+      <c r="J15" s="347"/>
+      <c r="K15" s="347"/>
+      <c r="L15" s="347"/>
+      <c r="M15" s="348"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="34"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="324" t="s">
+      <c r="A16" s="32"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="363" t="s">
         <v>61</v>
       </c>
-      <c r="J16" s="325"/>
-      <c r="K16" s="325"/>
-      <c r="L16" s="325"/>
-      <c r="M16" s="326"/>
+      <c r="J16" s="364"/>
+      <c r="K16" s="364"/>
+      <c r="L16" s="364"/>
+      <c r="M16" s="365"/>
     </row>
     <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="37" t="s">
+      <c r="A17" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="331">
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="299">
         <f>ADDRESS!I5</f>
         <v>59642884</v>
       </c>
-      <c r="G17" s="331"/>
-      <c r="H17" s="332"/>
-      <c r="I17" s="323"/>
-      <c r="J17" s="298"/>
-      <c r="K17" s="305" t="s">
+      <c r="G17" s="299"/>
+      <c r="H17" s="300"/>
+      <c r="I17" s="360"/>
+      <c r="J17" s="339"/>
+      <c r="K17" s="342" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="305"/>
-      <c r="M17" s="306"/>
+      <c r="L17" s="342"/>
+      <c r="M17" s="343"/>
     </row>
     <row r="18" spans="1:13" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="39"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="219" t="s">
+      <c r="A18" s="37"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="361" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="220"/>
-      <c r="K18" s="307"/>
-      <c r="L18" s="307"/>
-      <c r="M18" s="308"/>
+      <c r="J18" s="362"/>
+      <c r="K18" s="344"/>
+      <c r="L18" s="344"/>
+      <c r="M18" s="345"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="272" t="s">
+      <c r="A19" s="366" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="273"/>
-      <c r="C19" s="273"/>
-      <c r="D19" s="273"/>
-      <c r="E19" s="273"/>
-      <c r="F19" s="273"/>
-      <c r="G19" s="273"/>
-      <c r="H19" s="273"/>
-      <c r="I19" s="273"/>
-      <c r="J19" s="273"/>
-      <c r="K19" s="273"/>
-      <c r="L19" s="273"/>
-      <c r="M19" s="274"/>
+      <c r="B19" s="367"/>
+      <c r="C19" s="367"/>
+      <c r="D19" s="367"/>
+      <c r="E19" s="367"/>
+      <c r="F19" s="367"/>
+      <c r="G19" s="367"/>
+      <c r="H19" s="367"/>
+      <c r="I19" s="367"/>
+      <c r="J19" s="367"/>
+      <c r="K19" s="367"/>
+      <c r="L19" s="367"/>
+      <c r="M19" s="368"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="327" t="s">
+      <c r="A20" s="369" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="328"/>
-      <c r="C20" s="328"/>
-      <c r="D20" s="328"/>
-      <c r="E20" s="328" t="s">
+      <c r="B20" s="370"/>
+      <c r="C20" s="370"/>
+      <c r="D20" s="370"/>
+      <c r="E20" s="370" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="328" t="s">
+      <c r="F20" s="370" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="328"/>
-      <c r="H20" s="321" t="s">
+      <c r="G20" s="370"/>
+      <c r="H20" s="358" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="322"/>
-      <c r="J20" s="315" t="s">
+      <c r="I20" s="359"/>
+      <c r="J20" s="352" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="316"/>
-      <c r="L20" s="316"/>
-      <c r="M20" s="317"/>
+      <c r="K20" s="353"/>
+      <c r="L20" s="353"/>
+      <c r="M20" s="354"/>
     </row>
     <row r="21" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="327"/>
-      <c r="B21" s="328"/>
-      <c r="C21" s="328"/>
-      <c r="D21" s="328"/>
-      <c r="E21" s="328"/>
-      <c r="F21" s="328"/>
-      <c r="G21" s="328"/>
-      <c r="H21" s="355" t="s">
+      <c r="A21" s="369"/>
+      <c r="B21" s="370"/>
+      <c r="C21" s="370"/>
+      <c r="D21" s="370"/>
+      <c r="E21" s="370"/>
+      <c r="F21" s="370"/>
+      <c r="G21" s="370"/>
+      <c r="H21" s="336" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="356"/>
-      <c r="J21" s="318"/>
-      <c r="K21" s="319"/>
-      <c r="L21" s="319"/>
-      <c r="M21" s="320"/>
+      <c r="I21" s="337"/>
+      <c r="J21" s="355"/>
+      <c r="K21" s="356"/>
+      <c r="L21" s="356"/>
+      <c r="M21" s="357"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="329" t="str">
+      <c r="A22" s="371" t="str">
         <f>VLOOKUP(B8,'Customer Order Info'!$A$3:$D$31,2,FALSE)</f>
         <v>0215-8880831-0578</v>
       </c>
-      <c r="B22" s="141"/>
-      <c r="C22" s="141"/>
-      <c r="D22" s="199"/>
+      <c r="B22" s="332"/>
+      <c r="C22" s="332"/>
+      <c r="D22" s="297"/>
       <c r="E22" s="10">
         <f>VLOOKUP(A22,'Customer Order Info'!B3:D31,2,FALSE)</f>
         <v>83</v>
       </c>
-      <c r="F22" s="141">
+      <c r="F22" s="332">
         <f>VLOOKUP(A22,'Customer Order Info'!B3:D31,3,FALSE)</f>
         <v>83</v>
       </c>
-      <c r="G22" s="141"/>
+      <c r="G22" s="332"/>
       <c r="H22" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="141"/>
-      <c r="K22" s="141"/>
-      <c r="L22" s="141"/>
-      <c r="M22" s="289"/>
+      <c r="J22" s="332"/>
+      <c r="K22" s="332"/>
+      <c r="L22" s="332"/>
+      <c r="M22" s="338"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="292"/>
-      <c r="B23" s="293"/>
-      <c r="C23" s="293"/>
-      <c r="D23" s="294"/>
+      <c r="A23" s="329"/>
+      <c r="B23" s="330"/>
+      <c r="C23" s="330"/>
+      <c r="D23" s="331"/>
       <c r="E23" s="10"/>
-      <c r="F23" s="141"/>
-      <c r="G23" s="141"/>
+      <c r="F23" s="332"/>
+      <c r="G23" s="332"/>
       <c r="H23" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="141"/>
-      <c r="K23" s="141"/>
-      <c r="L23" s="141"/>
-      <c r="M23" s="289"/>
+      <c r="J23" s="332"/>
+      <c r="K23" s="332"/>
+      <c r="L23" s="332"/>
+      <c r="M23" s="338"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="292"/>
-      <c r="B24" s="293"/>
-      <c r="C24" s="293"/>
-      <c r="D24" s="294"/>
+      <c r="A24" s="329"/>
+      <c r="B24" s="330"/>
+      <c r="C24" s="330"/>
+      <c r="D24" s="331"/>
       <c r="E24" s="10"/>
-      <c r="F24" s="141"/>
-      <c r="G24" s="141"/>
+      <c r="F24" s="332"/>
+      <c r="G24" s="332"/>
       <c r="H24" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="141"/>
-      <c r="K24" s="141"/>
-      <c r="L24" s="141"/>
-      <c r="M24" s="289"/>
+      <c r="J24" s="332"/>
+      <c r="K24" s="332"/>
+      <c r="L24" s="332"/>
+      <c r="M24" s="338"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="292"/>
-      <c r="B25" s="293"/>
-      <c r="C25" s="293"/>
-      <c r="D25" s="294"/>
+      <c r="A25" s="329"/>
+      <c r="B25" s="330"/>
+      <c r="C25" s="330"/>
+      <c r="D25" s="331"/>
       <c r="E25" s="10"/>
-      <c r="F25" s="141"/>
-      <c r="G25" s="141"/>
+      <c r="F25" s="332"/>
+      <c r="G25" s="332"/>
       <c r="H25" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="141"/>
-      <c r="K25" s="141"/>
-      <c r="L25" s="141"/>
-      <c r="M25" s="289"/>
+      <c r="J25" s="332"/>
+      <c r="K25" s="332"/>
+      <c r="L25" s="332"/>
+      <c r="M25" s="338"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="292"/>
-      <c r="B26" s="293"/>
-      <c r="C26" s="293"/>
-      <c r="D26" s="294"/>
+      <c r="A26" s="329"/>
+      <c r="B26" s="330"/>
+      <c r="C26" s="330"/>
+      <c r="D26" s="331"/>
       <c r="E26" s="10"/>
-      <c r="F26" s="141"/>
-      <c r="G26" s="141"/>
+      <c r="F26" s="332"/>
+      <c r="G26" s="332"/>
       <c r="H26" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="141"/>
-      <c r="K26" s="141"/>
-      <c r="L26" s="141"/>
-      <c r="M26" s="289"/>
+      <c r="J26" s="332"/>
+      <c r="K26" s="332"/>
+      <c r="L26" s="332"/>
+      <c r="M26" s="338"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="292"/>
-      <c r="B27" s="293"/>
-      <c r="C27" s="293"/>
-      <c r="D27" s="294"/>
+      <c r="A27" s="329"/>
+      <c r="B27" s="330"/>
+      <c r="C27" s="330"/>
+      <c r="D27" s="331"/>
       <c r="E27" s="10"/>
-      <c r="F27" s="141"/>
-      <c r="G27" s="141"/>
+      <c r="F27" s="332"/>
+      <c r="G27" s="332"/>
       <c r="H27" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J27" s="141"/>
-      <c r="K27" s="141"/>
-      <c r="L27" s="141"/>
-      <c r="M27" s="289"/>
+      <c r="J27" s="332"/>
+      <c r="K27" s="332"/>
+      <c r="L27" s="332"/>
+      <c r="M27" s="338"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="292"/>
-      <c r="B28" s="293"/>
-      <c r="C28" s="293"/>
-      <c r="D28" s="294"/>
+      <c r="A28" s="329"/>
+      <c r="B28" s="330"/>
+      <c r="C28" s="330"/>
+      <c r="D28" s="331"/>
       <c r="E28" s="10"/>
-      <c r="F28" s="141"/>
-      <c r="G28" s="141"/>
+      <c r="F28" s="332"/>
+      <c r="G28" s="332"/>
       <c r="H28" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J28" s="141"/>
-      <c r="K28" s="141"/>
-      <c r="L28" s="141"/>
-      <c r="M28" s="289"/>
+      <c r="J28" s="332"/>
+      <c r="K28" s="332"/>
+      <c r="L28" s="332"/>
+      <c r="M28" s="338"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="292"/>
-      <c r="B29" s="293"/>
-      <c r="C29" s="293"/>
-      <c r="D29" s="294"/>
+      <c r="A29" s="329"/>
+      <c r="B29" s="330"/>
+      <c r="C29" s="330"/>
+      <c r="D29" s="331"/>
       <c r="E29" s="10"/>
-      <c r="F29" s="141"/>
-      <c r="G29" s="141"/>
+      <c r="F29" s="332"/>
+      <c r="G29" s="332"/>
       <c r="H29" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J29" s="141"/>
-      <c r="K29" s="141"/>
-      <c r="L29" s="141"/>
-      <c r="M29" s="289"/>
+      <c r="J29" s="332"/>
+      <c r="K29" s="332"/>
+      <c r="L29" s="332"/>
+      <c r="M29" s="338"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="290" t="s">
+      <c r="A30" s="386" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="291"/>
-      <c r="C30" s="291"/>
-      <c r="D30" s="291"/>
+      <c r="B30" s="387"/>
+      <c r="C30" s="387"/>
+      <c r="D30" s="387"/>
       <c r="E30" s="9">
         <f>SUM(E22:E29)</f>
         <v>83</v>
       </c>
-      <c r="F30" s="278">
+      <c r="F30" s="375">
         <f>SUM(F22:G29)</f>
         <v>83</v>
       </c>
-      <c r="G30" s="141"/>
-      <c r="H30" s="295"/>
-      <c r="I30" s="297"/>
-      <c r="J30" s="295"/>
-      <c r="K30" s="296"/>
-      <c r="L30" s="296"/>
-      <c r="M30" s="297"/>
+      <c r="G30" s="332"/>
+      <c r="H30" s="305"/>
+      <c r="I30" s="306"/>
+      <c r="J30" s="305"/>
+      <c r="K30" s="373"/>
+      <c r="L30" s="373"/>
+      <c r="M30" s="306"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="279" t="s">
+      <c r="A31" s="376" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="280"/>
-      <c r="C31" s="280"/>
-      <c r="D31" s="280"/>
-      <c r="E31" s="280"/>
-      <c r="F31" s="280"/>
-      <c r="G31" s="280"/>
-      <c r="H31" s="280"/>
-      <c r="I31" s="280"/>
-      <c r="J31" s="280"/>
-      <c r="K31" s="280"/>
-      <c r="L31" s="280"/>
-      <c r="M31" s="281"/>
+      <c r="B31" s="377"/>
+      <c r="C31" s="377"/>
+      <c r="D31" s="377"/>
+      <c r="E31" s="377"/>
+      <c r="F31" s="377"/>
+      <c r="G31" s="377"/>
+      <c r="H31" s="377"/>
+      <c r="I31" s="377"/>
+      <c r="J31" s="377"/>
+      <c r="K31" s="377"/>
+      <c r="L31" s="377"/>
+      <c r="M31" s="378"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="286" t="s">
+      <c r="A32" s="383" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="284"/>
-      <c r="C32" s="284" t="s">
+      <c r="B32" s="381"/>
+      <c r="C32" s="381" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="284"/>
-      <c r="E32" s="287" t="s">
+      <c r="D32" s="381"/>
+      <c r="E32" s="384" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="288" t="s">
+      <c r="F32" s="385" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="282" t="s">
+      <c r="G32" s="379" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="282"/>
-      <c r="I32" s="282"/>
-      <c r="J32" s="282"/>
-      <c r="K32" s="282"/>
-      <c r="L32" s="284" t="s">
+      <c r="H32" s="379"/>
+      <c r="I32" s="379"/>
+      <c r="J32" s="379"/>
+      <c r="K32" s="379"/>
+      <c r="L32" s="381" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="285"/>
+      <c r="M32" s="382"/>
     </row>
     <row r="33" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
@@ -8924,15 +8909,15 @@
       <c r="D33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="287"/>
-      <c r="F33" s="288"/>
-      <c r="G33" s="283" t="s">
+      <c r="E33" s="384"/>
+      <c r="F33" s="385"/>
+      <c r="G33" s="380" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="283"/>
-      <c r="I33" s="283"/>
-      <c r="J33" s="283"/>
-      <c r="K33" s="283"/>
+      <c r="H33" s="380"/>
+      <c r="I33" s="380"/>
+      <c r="J33" s="380"/>
+      <c r="K33" s="380"/>
       <c r="L33" s="2" t="s">
         <v>14</v>
       </c>
@@ -8941,7 +8926,7 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="69">
+      <c r="A34" s="67">
         <f>E30</f>
         <v>83</v>
       </c>
@@ -8952,7 +8937,7 @@
         <f>F30</f>
         <v>83</v>
       </c>
-      <c r="D34" s="68" t="s">
+      <c r="D34" s="66" t="s">
         <v>60</v>
       </c>
       <c r="E34" s="9">
@@ -8960,449 +8945,449 @@
         <v>83</v>
       </c>
       <c r="F34" s="10"/>
-      <c r="G34" s="199" t="s">
+      <c r="G34" s="297" t="s">
         <v>77</v>
       </c>
-      <c r="H34" s="257"/>
-      <c r="I34" s="257"/>
-      <c r="J34" s="257"/>
-      <c r="K34" s="200"/>
-      <c r="L34" s="70"/>
-      <c r="M34" s="71"/>
+      <c r="H34" s="374"/>
+      <c r="I34" s="374"/>
+      <c r="J34" s="374"/>
+      <c r="K34" s="298"/>
+      <c r="L34" s="68"/>
+      <c r="M34" s="69"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" s="72"/>
+      <c r="A35" s="70"/>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
-      <c r="F35" s="70"/>
-      <c r="G35" s="199"/>
-      <c r="H35" s="257"/>
-      <c r="I35" s="257"/>
-      <c r="J35" s="257"/>
-      <c r="K35" s="200"/>
-      <c r="L35" s="70"/>
-      <c r="M35" s="71"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="297"/>
+      <c r="H35" s="374"/>
+      <c r="I35" s="374"/>
+      <c r="J35" s="374"/>
+      <c r="K35" s="298"/>
+      <c r="L35" s="68"/>
+      <c r="M35" s="69"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" s="72"/>
+      <c r="A36" s="70"/>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
-      <c r="F36" s="70"/>
-      <c r="G36" s="199"/>
-      <c r="H36" s="257"/>
-      <c r="I36" s="257"/>
-      <c r="J36" s="257"/>
-      <c r="K36" s="200"/>
-      <c r="L36" s="70"/>
-      <c r="M36" s="71"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="297"/>
+      <c r="H36" s="374"/>
+      <c r="I36" s="374"/>
+      <c r="J36" s="374"/>
+      <c r="K36" s="298"/>
+      <c r="L36" s="68"/>
+      <c r="M36" s="69"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A37" s="72"/>
+      <c r="A37" s="70"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
-      <c r="F37" s="70"/>
-      <c r="G37" s="199"/>
-      <c r="H37" s="257"/>
-      <c r="I37" s="257"/>
-      <c r="J37" s="257"/>
-      <c r="K37" s="200"/>
-      <c r="L37" s="70"/>
-      <c r="M37" s="71"/>
-      <c r="Q37" s="248"/>
-      <c r="R37" s="248"/>
+      <c r="F37" s="68"/>
+      <c r="G37" s="297"/>
+      <c r="H37" s="374"/>
+      <c r="I37" s="374"/>
+      <c r="J37" s="374"/>
+      <c r="K37" s="298"/>
+      <c r="L37" s="68"/>
+      <c r="M37" s="69"/>
+      <c r="Q37" s="389"/>
+      <c r="R37" s="389"/>
       <c r="S37" s="7"/>
-      <c r="T37" s="225"/>
-      <c r="U37" s="225"/>
-      <c r="V37" s="225"/>
+      <c r="T37" s="388"/>
+      <c r="U37" s="388"/>
+      <c r="V37" s="388"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A38" s="72"/>
+      <c r="A38" s="70"/>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="199"/>
-      <c r="H38" s="257"/>
-      <c r="I38" s="257"/>
-      <c r="J38" s="257"/>
-      <c r="K38" s="200"/>
-      <c r="L38" s="70"/>
-      <c r="M38" s="73"/>
-      <c r="Q38" s="248"/>
-      <c r="R38" s="248"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="297"/>
+      <c r="H38" s="374"/>
+      <c r="I38" s="374"/>
+      <c r="J38" s="374"/>
+      <c r="K38" s="298"/>
+      <c r="L38" s="68"/>
+      <c r="M38" s="71"/>
+      <c r="Q38" s="389"/>
+      <c r="R38" s="389"/>
       <c r="S38" s="7"/>
-      <c r="T38" s="225"/>
-      <c r="U38" s="225"/>
-      <c r="V38" s="225"/>
+      <c r="T38" s="388"/>
+      <c r="U38" s="388"/>
+      <c r="V38" s="388"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A39" s="72"/>
+      <c r="A39" s="70"/>
       <c r="B39" s="10"/>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
-      <c r="F39" s="70"/>
-      <c r="G39" s="199"/>
-      <c r="H39" s="257"/>
-      <c r="I39" s="257"/>
-      <c r="J39" s="257"/>
-      <c r="K39" s="200"/>
-      <c r="L39" s="70"/>
-      <c r="M39" s="73"/>
+      <c r="F39" s="68"/>
+      <c r="G39" s="297"/>
+      <c r="H39" s="374"/>
+      <c r="I39" s="374"/>
+      <c r="J39" s="374"/>
+      <c r="K39" s="298"/>
+      <c r="L39" s="68"/>
+      <c r="M39" s="71"/>
       <c r="Q39" s="6"/>
       <c r="R39" s="6"/>
-      <c r="S39" s="251"/>
-      <c r="T39" s="225"/>
-      <c r="U39" s="225"/>
-      <c r="V39" s="225"/>
+      <c r="S39" s="390"/>
+      <c r="T39" s="388"/>
+      <c r="U39" s="388"/>
+      <c r="V39" s="388"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A40" s="72"/>
+      <c r="A40" s="70"/>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
       <c r="D40" s="10"/>
       <c r="E40" s="10"/>
-      <c r="F40" s="70"/>
-      <c r="G40" s="199"/>
-      <c r="H40" s="257"/>
-      <c r="I40" s="257"/>
-      <c r="J40" s="257"/>
-      <c r="K40" s="200"/>
-      <c r="L40" s="70"/>
-      <c r="M40" s="71"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="297"/>
+      <c r="H40" s="374"/>
+      <c r="I40" s="374"/>
+      <c r="J40" s="374"/>
+      <c r="K40" s="298"/>
+      <c r="L40" s="68"/>
+      <c r="M40" s="69"/>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
-      <c r="S40" s="251"/>
-      <c r="T40" s="225"/>
-      <c r="U40" s="225"/>
-      <c r="V40" s="225"/>
+      <c r="S40" s="390"/>
+      <c r="T40" s="388"/>
+      <c r="U40" s="388"/>
+      <c r="V40" s="388"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A41" s="72"/>
+      <c r="A41" s="70"/>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
       <c r="D41" s="10"/>
       <c r="E41" s="10"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="199"/>
-      <c r="H41" s="257"/>
-      <c r="I41" s="257"/>
-      <c r="J41" s="257"/>
-      <c r="K41" s="200"/>
-      <c r="L41" s="70"/>
-      <c r="M41" s="71"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="297"/>
+      <c r="H41" s="374"/>
+      <c r="I41" s="374"/>
+      <c r="J41" s="374"/>
+      <c r="K41" s="298"/>
+      <c r="L41" s="68"/>
+      <c r="M41" s="69"/>
     </row>
     <row r="42" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="74">
+      <c r="A42" s="72">
         <f>SUM(A34:A41)</f>
         <v>83</v>
       </c>
-      <c r="B42" s="75"/>
-      <c r="C42" s="76">
+      <c r="B42" s="73"/>
+      <c r="C42" s="74">
         <f>SUM(C34:C41)</f>
         <v>83</v>
       </c>
-      <c r="D42" s="75"/>
-      <c r="E42" s="76">
+      <c r="D42" s="73"/>
+      <c r="E42" s="74">
         <f>SUM(E34:E41)</f>
         <v>83</v>
       </c>
-      <c r="F42" s="77"/>
-      <c r="G42" s="258" t="s">
+      <c r="F42" s="75"/>
+      <c r="G42" s="397" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="259"/>
-      <c r="I42" s="259"/>
-      <c r="J42" s="259"/>
-      <c r="K42" s="260"/>
-      <c r="L42" s="77"/>
-      <c r="M42" s="78"/>
+      <c r="H42" s="398"/>
+      <c r="I42" s="398"/>
+      <c r="J42" s="398"/>
+      <c r="K42" s="399"/>
+      <c r="L42" s="75"/>
+      <c r="M42" s="76"/>
     </row>
     <row r="43" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="227" t="s">
+      <c r="A43" s="407" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="228"/>
-      <c r="C43" s="228"/>
-      <c r="D43" s="228"/>
-      <c r="E43" s="228"/>
-      <c r="F43" s="228"/>
-      <c r="G43" s="228"/>
-      <c r="H43" s="229"/>
-      <c r="I43" s="269" t="s">
+      <c r="B43" s="408"/>
+      <c r="C43" s="408"/>
+      <c r="D43" s="408"/>
+      <c r="E43" s="408"/>
+      <c r="F43" s="408"/>
+      <c r="G43" s="408"/>
+      <c r="H43" s="409"/>
+      <c r="I43" s="326" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="270"/>
-      <c r="K43" s="270"/>
-      <c r="L43" s="270"/>
-      <c r="M43" s="271"/>
+      <c r="J43" s="327"/>
+      <c r="K43" s="327"/>
+      <c r="L43" s="327"/>
+      <c r="M43" s="328"/>
     </row>
     <row r="44" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="230"/>
-      <c r="B44" s="231"/>
-      <c r="C44" s="231"/>
-      <c r="D44" s="231"/>
-      <c r="E44" s="231"/>
-      <c r="F44" s="231"/>
-      <c r="G44" s="231"/>
-      <c r="H44" s="232"/>
-      <c r="I44" s="272"/>
-      <c r="J44" s="273"/>
-      <c r="K44" s="273"/>
-      <c r="L44" s="273"/>
-      <c r="M44" s="274"/>
+      <c r="A44" s="410"/>
+      <c r="B44" s="411"/>
+      <c r="C44" s="411"/>
+      <c r="D44" s="411"/>
+      <c r="E44" s="411"/>
+      <c r="F44" s="411"/>
+      <c r="G44" s="411"/>
+      <c r="H44" s="412"/>
+      <c r="I44" s="366"/>
+      <c r="J44" s="367"/>
+      <c r="K44" s="367"/>
+      <c r="L44" s="367"/>
+      <c r="M44" s="368"/>
     </row>
     <row r="45" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="233" t="s">
+      <c r="A45" s="423" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="234"/>
-      <c r="C45" s="234"/>
-      <c r="D45" s="234"/>
-      <c r="E45" s="234"/>
-      <c r="F45" s="234"/>
-      <c r="G45" s="234"/>
-      <c r="H45" s="235"/>
-      <c r="I45" s="275" t="s">
+      <c r="B45" s="424"/>
+      <c r="C45" s="424"/>
+      <c r="D45" s="424"/>
+      <c r="E45" s="424"/>
+      <c r="F45" s="424"/>
+      <c r="G45" s="424"/>
+      <c r="H45" s="425"/>
+      <c r="I45" s="415" t="s">
         <v>36</v>
       </c>
-      <c r="J45" s="276"/>
-      <c r="K45" s="276"/>
-      <c r="L45" s="276"/>
-      <c r="M45" s="277"/>
+      <c r="J45" s="416"/>
+      <c r="K45" s="416"/>
+      <c r="L45" s="416"/>
+      <c r="M45" s="417"/>
     </row>
     <row r="46" spans="1:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="233" t="s">
+      <c r="A46" s="423" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="234"/>
-      <c r="C46" s="234"/>
-      <c r="D46" s="234"/>
-      <c r="E46" s="234"/>
-      <c r="F46" s="234"/>
-      <c r="G46" s="234"/>
-      <c r="H46" s="235"/>
-      <c r="I46" s="275"/>
-      <c r="J46" s="276"/>
-      <c r="K46" s="276"/>
-      <c r="L46" s="276"/>
-      <c r="M46" s="277"/>
+      <c r="B46" s="424"/>
+      <c r="C46" s="424"/>
+      <c r="D46" s="424"/>
+      <c r="E46" s="424"/>
+      <c r="F46" s="424"/>
+      <c r="G46" s="424"/>
+      <c r="H46" s="425"/>
+      <c r="I46" s="415"/>
+      <c r="J46" s="416"/>
+      <c r="K46" s="416"/>
+      <c r="L46" s="416"/>
+      <c r="M46" s="417"/>
     </row>
     <row r="47" spans="1:22" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="236"/>
-      <c r="B47" s="237"/>
-      <c r="C47" s="237"/>
-      <c r="D47" s="237"/>
-      <c r="E47" s="237"/>
-      <c r="F47" s="237"/>
-      <c r="G47" s="237"/>
-      <c r="H47" s="238"/>
-      <c r="I47" s="222" t="s">
+      <c r="A47" s="426"/>
+      <c r="B47" s="427"/>
+      <c r="C47" s="427"/>
+      <c r="D47" s="427"/>
+      <c r="E47" s="427"/>
+      <c r="F47" s="427"/>
+      <c r="G47" s="427"/>
+      <c r="H47" s="428"/>
+      <c r="I47" s="419" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="223"/>
-      <c r="K47" s="223"/>
-      <c r="L47" s="223"/>
-      <c r="M47" s="224"/>
+      <c r="J47" s="420"/>
+      <c r="K47" s="420"/>
+      <c r="L47" s="420"/>
+      <c r="M47" s="421"/>
     </row>
     <row r="48" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="243" t="s">
+      <c r="A48" s="400" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="244"/>
-      <c r="C48" s="244"/>
-      <c r="D48" s="244"/>
-      <c r="E48" s="244"/>
-      <c r="F48" s="244"/>
-      <c r="G48" s="244"/>
-      <c r="H48" s="244"/>
-      <c r="I48" s="244"/>
-      <c r="J48" s="244"/>
-      <c r="K48" s="244"/>
-      <c r="L48" s="244"/>
-      <c r="M48" s="252"/>
+      <c r="B48" s="391"/>
+      <c r="C48" s="391"/>
+      <c r="D48" s="391"/>
+      <c r="E48" s="391"/>
+      <c r="F48" s="391"/>
+      <c r="G48" s="391"/>
+      <c r="H48" s="391"/>
+      <c r="I48" s="391"/>
+      <c r="J48" s="391"/>
+      <c r="K48" s="391"/>
+      <c r="L48" s="391"/>
+      <c r="M48" s="392"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="227" t="s">
+      <c r="A49" s="407" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="228"/>
-      <c r="C49" s="228"/>
-      <c r="D49" s="228"/>
-      <c r="E49" s="228"/>
-      <c r="F49" s="228"/>
-      <c r="G49" s="228"/>
-      <c r="H49" s="229"/>
-      <c r="I49" s="261" t="s">
+      <c r="B49" s="408"/>
+      <c r="C49" s="408"/>
+      <c r="D49" s="408"/>
+      <c r="E49" s="408"/>
+      <c r="F49" s="408"/>
+      <c r="G49" s="408"/>
+      <c r="H49" s="409"/>
+      <c r="I49" s="401" t="s">
         <v>40</v>
       </c>
-      <c r="J49" s="262"/>
-      <c r="K49" s="262"/>
-      <c r="L49" s="262"/>
-      <c r="M49" s="263"/>
+      <c r="J49" s="402"/>
+      <c r="K49" s="402"/>
+      <c r="L49" s="402"/>
+      <c r="M49" s="403"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="230"/>
-      <c r="B50" s="231"/>
-      <c r="C50" s="231"/>
-      <c r="D50" s="231"/>
-      <c r="E50" s="231"/>
-      <c r="F50" s="231"/>
-      <c r="G50" s="231"/>
-      <c r="H50" s="232"/>
-      <c r="I50" s="264"/>
-      <c r="J50" s="265"/>
-      <c r="K50" s="265"/>
-      <c r="L50" s="265"/>
-      <c r="M50" s="266"/>
+      <c r="A50" s="410"/>
+      <c r="B50" s="411"/>
+      <c r="C50" s="411"/>
+      <c r="D50" s="411"/>
+      <c r="E50" s="411"/>
+      <c r="F50" s="411"/>
+      <c r="G50" s="411"/>
+      <c r="H50" s="412"/>
+      <c r="I50" s="404"/>
+      <c r="J50" s="405"/>
+      <c r="K50" s="405"/>
+      <c r="L50" s="405"/>
+      <c r="M50" s="406"/>
     </row>
     <row r="51" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="267"/>
-      <c r="B51" s="268"/>
-      <c r="C51" s="268"/>
-      <c r="D51" s="268"/>
-      <c r="E51" s="231"/>
-      <c r="F51" s="231"/>
-      <c r="G51" s="231"/>
-      <c r="H51" s="232"/>
-      <c r="I51" s="239" t="s">
+      <c r="A51" s="413"/>
+      <c r="B51" s="414"/>
+      <c r="C51" s="414"/>
+      <c r="D51" s="414"/>
+      <c r="E51" s="411"/>
+      <c r="F51" s="411"/>
+      <c r="G51" s="411"/>
+      <c r="H51" s="412"/>
+      <c r="I51" s="429" t="s">
         <v>41</v>
       </c>
-      <c r="J51" s="240"/>
-      <c r="K51" s="241"/>
-      <c r="L51" s="241"/>
-      <c r="M51" s="242"/>
+      <c r="J51" s="430"/>
+      <c r="K51" s="431"/>
+      <c r="L51" s="431"/>
+      <c r="M51" s="432"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="243" t="s">
+      <c r="A52" s="400" t="s">
         <v>42</v>
       </c>
-      <c r="B52" s="244"/>
-      <c r="C52" s="244"/>
-      <c r="D52" s="244"/>
-      <c r="E52" s="79" t="s">
+      <c r="B52" s="391"/>
+      <c r="C52" s="391"/>
+      <c r="D52" s="391"/>
+      <c r="E52" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="F52" s="80"/>
-      <c r="G52" s="249" t="s">
+      <c r="F52" s="78"/>
+      <c r="G52" s="436" t="s">
         <v>45</v>
       </c>
-      <c r="H52" s="249"/>
-      <c r="I52" s="249"/>
-      <c r="J52" s="250"/>
-      <c r="K52" s="244" t="s">
+      <c r="H52" s="436"/>
+      <c r="I52" s="436"/>
+      <c r="J52" s="437"/>
+      <c r="K52" s="391" t="s">
         <v>50</v>
       </c>
-      <c r="L52" s="244"/>
-      <c r="M52" s="252"/>
+      <c r="L52" s="391"/>
+      <c r="M52" s="392"/>
     </row>
     <row r="53" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="245" t="s">
+      <c r="A53" s="433" t="s">
         <v>43</v>
       </c>
-      <c r="B53" s="246"/>
-      <c r="C53" s="246"/>
-      <c r="D53" s="246"/>
-      <c r="E53" s="62"/>
-      <c r="J53" s="59"/>
-      <c r="K53" s="253" t="s">
+      <c r="B53" s="434"/>
+      <c r="C53" s="434"/>
+      <c r="D53" s="434"/>
+      <c r="E53" s="60"/>
+      <c r="J53" s="57"/>
+      <c r="K53" s="393" t="s">
         <v>52</v>
       </c>
-      <c r="L53" s="253"/>
-      <c r="M53" s="254"/>
+      <c r="L53" s="393"/>
+      <c r="M53" s="394"/>
     </row>
     <row r="54" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="245"/>
-      <c r="B54" s="246"/>
-      <c r="C54" s="246"/>
-      <c r="D54" s="246"/>
-      <c r="E54" s="247" t="s">
+      <c r="A54" s="433"/>
+      <c r="B54" s="434"/>
+      <c r="C54" s="434"/>
+      <c r="D54" s="434"/>
+      <c r="E54" s="435" t="s">
         <v>46</v>
       </c>
-      <c r="F54" s="248"/>
+      <c r="F54" s="389"/>
       <c r="G54" s="7"/>
-      <c r="H54" s="225" t="s">
+      <c r="H54" s="388" t="s">
         <v>46</v>
       </c>
-      <c r="I54" s="225"/>
-      <c r="J54" s="226"/>
-      <c r="K54" s="253"/>
-      <c r="L54" s="253"/>
-      <c r="M54" s="254"/>
+      <c r="I54" s="388"/>
+      <c r="J54" s="422"/>
+      <c r="K54" s="393"/>
+      <c r="L54" s="393"/>
+      <c r="M54" s="394"/>
     </row>
     <row r="55" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="245"/>
-      <c r="B55" s="246"/>
-      <c r="C55" s="246"/>
-      <c r="D55" s="246"/>
-      <c r="E55" s="247" t="s">
+      <c r="A55" s="433"/>
+      <c r="B55" s="434"/>
+      <c r="C55" s="434"/>
+      <c r="D55" s="434"/>
+      <c r="E55" s="435" t="s">
         <v>47</v>
       </c>
-      <c r="F55" s="248"/>
-      <c r="G55" s="248"/>
-      <c r="H55" s="225" t="s">
+      <c r="F55" s="389"/>
+      <c r="G55" s="389"/>
+      <c r="H55" s="388" t="s">
         <v>48</v>
       </c>
-      <c r="I55" s="225"/>
-      <c r="J55" s="226"/>
-      <c r="K55" s="253"/>
-      <c r="L55" s="253"/>
-      <c r="M55" s="254"/>
+      <c r="I55" s="388"/>
+      <c r="J55" s="422"/>
+      <c r="K55" s="393"/>
+      <c r="L55" s="393"/>
+      <c r="M55" s="394"/>
     </row>
     <row r="56" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="62"/>
-      <c r="D56" s="59"/>
-      <c r="E56" s="247"/>
-      <c r="F56" s="248"/>
-      <c r="G56" s="248"/>
-      <c r="H56" s="225"/>
-      <c r="I56" s="225"/>
-      <c r="J56" s="226"/>
-      <c r="K56" s="255" t="s">
+      <c r="A56" s="60"/>
+      <c r="D56" s="57"/>
+      <c r="E56" s="435"/>
+      <c r="F56" s="389"/>
+      <c r="G56" s="389"/>
+      <c r="H56" s="388"/>
+      <c r="I56" s="388"/>
+      <c r="J56" s="422"/>
+      <c r="K56" s="395" t="s">
         <v>51</v>
       </c>
-      <c r="L56" s="255"/>
-      <c r="M56" s="256"/>
+      <c r="L56" s="395"/>
+      <c r="M56" s="396"/>
     </row>
     <row r="57" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="62"/>
-      <c r="D57" s="59"/>
-      <c r="E57" s="247"/>
-      <c r="F57" s="248"/>
+      <c r="A57" s="60"/>
+      <c r="D57" s="57"/>
+      <c r="E57" s="435"/>
+      <c r="F57" s="389"/>
       <c r="G57" s="7"/>
-      <c r="H57" s="225" t="s">
+      <c r="H57" s="388" t="s">
         <v>49</v>
       </c>
-      <c r="I57" s="225"/>
-      <c r="J57" s="226"/>
-      <c r="K57" s="81"/>
-      <c r="L57" s="82"/>
-      <c r="M57" s="83"/>
+      <c r="I57" s="388"/>
+      <c r="J57" s="422"/>
+      <c r="K57" s="79"/>
+      <c r="L57" s="80"/>
+      <c r="M57" s="81"/>
     </row>
     <row r="58" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="84"/>
-      <c r="B58" s="336">
+      <c r="A58" s="82"/>
+      <c r="B58" s="304">
         <f>B1</f>
         <v>45877</v>
       </c>
-      <c r="C58" s="336"/>
-      <c r="D58" s="51"/>
-      <c r="E58" s="219"/>
-      <c r="F58" s="220"/>
-      <c r="G58" s="220"/>
-      <c r="H58" s="220"/>
-      <c r="I58" s="220"/>
-      <c r="J58" s="221"/>
-      <c r="K58" s="85"/>
-      <c r="L58" s="86"/>
-      <c r="M58" s="87"/>
+      <c r="C58" s="304"/>
+      <c r="D58" s="49"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="362"/>
+      <c r="G58" s="362"/>
+      <c r="H58" s="362"/>
+      <c r="I58" s="362"/>
+      <c r="J58" s="418"/>
+      <c r="K58" s="83"/>
+      <c r="L58" s="84"/>
+      <c r="M58" s="85"/>
     </row>
     <row r="59" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3"/>
@@ -9418,6 +9403,92 @@
     </row>
   </sheetData>
   <mergeCells count="110">
+    <mergeCell ref="E58:J58"/>
+    <mergeCell ref="I47:M47"/>
+    <mergeCell ref="H55:J56"/>
+    <mergeCell ref="A43:H44"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A46:H47"/>
+    <mergeCell ref="I51:M51"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A53:D55"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="H57:J57"/>
+    <mergeCell ref="H54:J54"/>
+    <mergeCell ref="E55:F56"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="G52:J52"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="T37:V37"/>
+    <mergeCell ref="T38:V38"/>
+    <mergeCell ref="T39:V40"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="S39:S40"/>
+    <mergeCell ref="K52:M52"/>
+    <mergeCell ref="K53:M55"/>
+    <mergeCell ref="K56:M56"/>
+    <mergeCell ref="G37:K37"/>
+    <mergeCell ref="G42:K42"/>
+    <mergeCell ref="G40:K40"/>
+    <mergeCell ref="A48:M48"/>
+    <mergeCell ref="I49:M50"/>
+    <mergeCell ref="G41:K41"/>
+    <mergeCell ref="G38:K38"/>
+    <mergeCell ref="A49:H51"/>
+    <mergeCell ref="I43:M44"/>
+    <mergeCell ref="I45:M46"/>
+    <mergeCell ref="G39:K39"/>
+    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="G36:K36"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A31:M31"/>
+    <mergeCell ref="G32:K32"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="G34:K34"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="K17:M18"/>
+    <mergeCell ref="I15:M15"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="J20:M21"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I16:M16"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="F25:G25"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="I11:J11"/>
     <mergeCell ref="B1:C1"/>
@@ -9442,92 +9513,6 @@
     <mergeCell ref="J28:M28"/>
     <mergeCell ref="J29:M29"/>
     <mergeCell ref="E8:H8"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="K17:M18"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="J20:M21"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I16:M16"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="A20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="G35:K35"/>
-    <mergeCell ref="G36:K36"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="A31:M31"/>
-    <mergeCell ref="G32:K32"/>
-    <mergeCell ref="G33:K33"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="G34:K34"/>
-    <mergeCell ref="T37:V37"/>
-    <mergeCell ref="T38:V38"/>
-    <mergeCell ref="T39:V40"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="S39:S40"/>
-    <mergeCell ref="K52:M52"/>
-    <mergeCell ref="K53:M55"/>
-    <mergeCell ref="K56:M56"/>
-    <mergeCell ref="G37:K37"/>
-    <mergeCell ref="G42:K42"/>
-    <mergeCell ref="G40:K40"/>
-    <mergeCell ref="A48:M48"/>
-    <mergeCell ref="I49:M50"/>
-    <mergeCell ref="G41:K41"/>
-    <mergeCell ref="G38:K38"/>
-    <mergeCell ref="A49:H51"/>
-    <mergeCell ref="I43:M44"/>
-    <mergeCell ref="I45:M46"/>
-    <mergeCell ref="G39:K39"/>
-    <mergeCell ref="E58:J58"/>
-    <mergeCell ref="I47:M47"/>
-    <mergeCell ref="H55:J56"/>
-    <mergeCell ref="A43:H44"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A46:H47"/>
-    <mergeCell ref="I51:M51"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A53:D55"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="H57:J57"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="E55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="G52:J52"/>
-    <mergeCell ref="E54:F54"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.26" top="0.52" bottom="0.56000000000000005" header="0.5" footer="0.5"/>
@@ -9562,25 +9547,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="31" t="s">
         <v>188</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="31" t="s">
         <v>191</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="H1" s="89" t="s">
+      <c r="H1" s="86" t="s">
         <v>226</v>
       </c>
-      <c r="I1" s="89" t="s">
+      <c r="I1" s="86" t="s">
         <v>227</v>
       </c>
     </row>
@@ -9600,10 +9585,10 @@
       <c r="E2">
         <v>92336</v>
       </c>
-      <c r="H2" s="89" t="s">
+      <c r="H2" s="86" t="s">
         <v>230</v>
       </c>
-      <c r="I2" s="89" t="s">
+      <c r="I2" s="86" t="s">
         <v>231</v>
       </c>
     </row>
@@ -9623,10 +9608,10 @@
       <c r="E3">
         <v>81001</v>
       </c>
-      <c r="H3" s="89" t="s">
+      <c r="H3" s="86" t="s">
         <v>228</v>
       </c>
-      <c r="I3" s="89">
+      <c r="I3" s="86">
         <v>10285609</v>
       </c>
     </row>
@@ -9646,15 +9631,15 @@
       <c r="E4">
         <v>24477</v>
       </c>
-      <c r="H4" s="89" t="s">
+      <c r="H4" s="86" t="s">
         <v>229</v>
       </c>
-      <c r="I4" s="90">
+      <c r="I4" s="87">
         <v>523953410</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="31" t="s">
         <v>90</v>
       </c>
       <c r="B5" t="s">
@@ -9669,10 +9654,10 @@
       <c r="E5">
         <v>55432</v>
       </c>
-      <c r="H5" s="89" t="s">
+      <c r="H5" s="86" t="s">
         <v>236</v>
       </c>
-      <c r="I5" s="91">
+      <c r="I5" s="88">
         <v>59642884</v>
       </c>
     </row>
@@ -10129,7 +10114,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="31" t="s">
         <v>90</v>
       </c>
       <c r="B3" t="s">
@@ -10535,7 +10520,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B32" s="33" t="s">
+      <c r="B32" s="31" t="s">
         <v>22</v>
       </c>
       <c r="C32">

--- a/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
+++ b/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Procomm\Documents\GitHub\Acumatica_Customizations_and_Packages\Istar_Development\Projects\BOL_Generation\Code\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F3C4FF-F131-48B9-8BEB-8433480A7F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B434921-1526-4102-894B-647902FE358A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{888CA347-7849-4038-B8EE-FAC87BA1B844}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="236">
   <si>
     <t>SHIP FROM</t>
   </si>
@@ -243,33 +243,6 @@
     <t>Address: 910 Nestle Way</t>
   </si>
   <si>
-    <t>BX</t>
-  </si>
-  <si>
-    <r>
-      <t>Prepaid______      Collect_</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_X__</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_      3rd Party______</t>
-    </r>
-  </si>
-  <si>
     <t>Page 1 of 2</t>
   </si>
   <si>
@@ -288,13 +261,7 @@
     <t>Name: Target/NFI Consolidation</t>
   </si>
   <si>
-    <t>Pallets</t>
-  </si>
-  <si>
     <t>City/State/Zip: Breinigville, PA 18031</t>
-  </si>
-  <si>
-    <t>Mix Pallets - Commodity as jewelry</t>
   </si>
   <si>
     <t>BILL OF LADING</t>
@@ -814,10 +781,34 @@
     <t>TARGET Load:</t>
   </si>
   <si>
-    <t>Date: 08/08/2025</t>
-  </si>
-  <si>
     <t xml:space="preserve">Date: </t>
+  </si>
+  <si>
+    <r>
+      <t>Prepaid______      Collect_</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>____</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_      3rd Party______</t>
+    </r>
+  </si>
+  <si>
+    <t>Date:</t>
   </si>
 </sst>
 </file>
@@ -1684,18 +1675,754 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1720,15 +2447,6 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1813,15 +2531,6 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1849,346 +2558,55 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="32" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2197,439 +2615,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="32" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4983,317 +4970,302 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="270" t="s">
-        <v>237</v>
-      </c>
-      <c r="B1" s="271"/>
-      <c r="C1" s="272" t="s">
+      <c r="A1" s="440" t="s">
+        <v>235</v>
+      </c>
+      <c r="B1" s="441"/>
+      <c r="C1" s="283" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="272"/>
-      <c r="E1" s="272"/>
-      <c r="F1" s="272"/>
-      <c r="G1" s="272"/>
-      <c r="H1" s="272"/>
-      <c r="I1" s="272"/>
-      <c r="J1" s="272"/>
-      <c r="K1" s="272"/>
-      <c r="L1" s="273" t="s">
+      <c r="D1" s="283"/>
+      <c r="E1" s="283"/>
+      <c r="F1" s="283"/>
+      <c r="G1" s="283"/>
+      <c r="H1" s="283"/>
+      <c r="I1" s="283"/>
+      <c r="J1" s="283"/>
+      <c r="K1" s="283"/>
+      <c r="L1" s="284" t="s">
+        <v>60</v>
+      </c>
+      <c r="M1" s="285"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="280" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="281"/>
+      <c r="C2" s="281"/>
+      <c r="D2" s="281"/>
+      <c r="E2" s="281"/>
+      <c r="F2" s="281"/>
+      <c r="G2" s="281"/>
+      <c r="H2" s="282"/>
+      <c r="I2" s="286" t="s">
+        <v>228</v>
+      </c>
+      <c r="J2" s="287"/>
+      <c r="K2" s="287"/>
+      <c r="L2" s="287"/>
+      <c r="M2" s="288"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="268" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" s="269"/>
+      <c r="C3" s="269"/>
+      <c r="D3" s="269"/>
+      <c r="E3" s="269"/>
+      <c r="F3" s="269"/>
+      <c r="G3" s="269"/>
+      <c r="H3" s="270"/>
+      <c r="I3" s="289"/>
+      <c r="J3" s="290"/>
+      <c r="K3" s="290"/>
+      <c r="L3" s="290"/>
+      <c r="M3" s="291"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="268" t="s">
         <v>62</v>
       </c>
-      <c r="M1" s="274"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="243" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="244"/>
-      <c r="C2" s="244"/>
-      <c r="D2" s="244"/>
-      <c r="E2" s="244"/>
-      <c r="F2" s="244"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245"/>
-      <c r="I2" s="275" t="s">
-        <v>232</v>
-      </c>
-      <c r="J2" s="276"/>
-      <c r="K2" s="276"/>
-      <c r="L2" s="276"/>
-      <c r="M2" s="277"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="255" t="s">
-        <v>66</v>
-      </c>
-      <c r="B3" s="256"/>
-      <c r="C3" s="256"/>
-      <c r="D3" s="256"/>
-      <c r="E3" s="256"/>
-      <c r="F3" s="256"/>
-      <c r="G3" s="256"/>
-      <c r="H3" s="257"/>
-      <c r="I3" s="278"/>
-      <c r="J3" s="279"/>
-      <c r="K3" s="279"/>
-      <c r="L3" s="279"/>
-      <c r="M3" s="280"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="255" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="256"/>
-      <c r="C4" s="256"/>
-      <c r="D4" s="256"/>
-      <c r="E4" s="256"/>
-      <c r="F4" s="256"/>
-      <c r="G4" s="256"/>
-      <c r="H4" s="257"/>
-      <c r="I4" s="261"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
-      <c r="M4" s="263"/>
+      <c r="B4" s="269"/>
+      <c r="C4" s="269"/>
+      <c r="D4" s="269"/>
+      <c r="E4" s="269"/>
+      <c r="F4" s="269"/>
+      <c r="G4" s="269"/>
+      <c r="H4" s="270"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="272"/>
+      <c r="K4" s="272"/>
+      <c r="L4" s="272"/>
+      <c r="M4" s="273"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="255" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" s="256"/>
-      <c r="C5" s="256"/>
-      <c r="D5" s="256"/>
-      <c r="E5" s="256"/>
-      <c r="F5" s="256"/>
-      <c r="G5" s="256"/>
-      <c r="H5" s="257"/>
-      <c r="I5" s="261"/>
-      <c r="J5" s="262"/>
-      <c r="K5" s="262"/>
-      <c r="L5" s="262"/>
-      <c r="M5" s="263"/>
+      <c r="A5" s="268" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="269"/>
+      <c r="C5" s="269"/>
+      <c r="D5" s="269"/>
+      <c r="E5" s="269"/>
+      <c r="F5" s="269"/>
+      <c r="G5" s="269"/>
+      <c r="H5" s="270"/>
+      <c r="I5" s="271"/>
+      <c r="J5" s="272"/>
+      <c r="K5" s="272"/>
+      <c r="L5" s="272"/>
+      <c r="M5" s="273"/>
     </row>
     <row r="6" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="267" t="s">
+      <c r="A6" s="277" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="268"/>
-      <c r="C6" s="268"/>
-      <c r="D6" s="268"/>
-      <c r="E6" s="268"/>
-      <c r="F6" s="269" t="s">
+      <c r="B6" s="278"/>
+      <c r="C6" s="278"/>
+      <c r="D6" s="278"/>
+      <c r="E6" s="278"/>
+      <c r="F6" s="279" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="269"/>
+      <c r="G6" s="279"/>
       <c r="H6" s="12"/>
-      <c r="I6" s="264"/>
-      <c r="J6" s="265"/>
-      <c r="K6" s="265"/>
-      <c r="L6" s="265"/>
-      <c r="M6" s="266"/>
+      <c r="I6" s="274"/>
+      <c r="J6" s="275"/>
+      <c r="K6" s="275"/>
+      <c r="L6" s="275"/>
+      <c r="M6" s="276"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="243" t="s">
+      <c r="A7" s="280" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="244"/>
-      <c r="C7" s="244"/>
-      <c r="D7" s="244"/>
-      <c r="E7" s="244"/>
-      <c r="F7" s="244"/>
-      <c r="G7" s="244"/>
-      <c r="H7" s="245"/>
+      <c r="B7" s="281"/>
+      <c r="C7" s="281"/>
+      <c r="D7" s="281"/>
+      <c r="E7" s="281"/>
+      <c r="F7" s="281"/>
+      <c r="G7" s="281"/>
+      <c r="H7" s="282"/>
       <c r="I7" s="90" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J7" s="91"/>
-      <c r="K7" s="92" t="str">
-        <f>ADDRESS!I1</f>
-        <v>CH Robinson</v>
-      </c>
+      <c r="K7" s="92"/>
       <c r="L7" s="91"/>
       <c r="M7" s="93"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="258" t="s">
-        <v>67</v>
-      </c>
-      <c r="B8" s="259"/>
-      <c r="C8" s="259"/>
-      <c r="D8" s="259"/>
-      <c r="E8" s="139" t="s">
+      <c r="A8" s="304" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="305"/>
+      <c r="C8" s="305"/>
+      <c r="D8" s="305"/>
+      <c r="E8" s="306" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="139"/>
-      <c r="G8" s="139"/>
-      <c r="H8" s="140"/>
-      <c r="I8" s="258" t="s">
+      <c r="F8" s="306"/>
+      <c r="G8" s="306"/>
+      <c r="H8" s="307"/>
+      <c r="I8" s="304" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="259"/>
-      <c r="K8" s="259"/>
-      <c r="L8" s="259"/>
-      <c r="M8" s="260"/>
+      <c r="J8" s="305"/>
+      <c r="K8" s="305"/>
+      <c r="L8" s="305"/>
+      <c r="M8" s="308"/>
     </row>
     <row r="9" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="258" t="s">
+      <c r="A9" s="304" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="259"/>
-      <c r="C9" s="259"/>
-      <c r="D9" s="259"/>
-      <c r="E9" s="259"/>
-      <c r="F9" s="259"/>
-      <c r="G9" s="259"/>
-      <c r="H9" s="260"/>
+      <c r="B9" s="305"/>
+      <c r="C9" s="305"/>
+      <c r="D9" s="305"/>
+      <c r="E9" s="305"/>
+      <c r="F9" s="305"/>
+      <c r="G9" s="305"/>
+      <c r="H9" s="308"/>
       <c r="I9" s="94" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="J9" s="95"/>
-      <c r="K9" s="95">
-        <f>ADDRESS!I3</f>
-        <v>10285609</v>
-      </c>
+      <c r="K9" s="95"/>
       <c r="L9" s="95"/>
       <c r="M9" s="89"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="258" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="259"/>
-      <c r="C10" s="259"/>
-      <c r="D10" s="259"/>
-      <c r="E10" s="259"/>
-      <c r="F10" s="259"/>
-      <c r="G10" s="259"/>
-      <c r="H10" s="260"/>
+      <c r="A10" s="304" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="305"/>
+      <c r="C10" s="305"/>
+      <c r="D10" s="305"/>
+      <c r="E10" s="305"/>
+      <c r="F10" s="305"/>
+      <c r="G10" s="305"/>
+      <c r="H10" s="308"/>
       <c r="I10" s="96" t="s">
-        <v>234</v>
-      </c>
-      <c r="J10" s="97" t="str">
-        <f>ADDRESS!I2</f>
-        <v>RBTW</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="J10" s="97"/>
       <c r="K10" s="97"/>
       <c r="L10" s="97"/>
       <c r="M10" s="98"/>
     </row>
     <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="240" t="s">
+      <c r="A11" s="292" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="241"/>
-      <c r="C11" s="241"/>
-      <c r="D11" s="241"/>
-      <c r="E11" s="241"/>
-      <c r="F11" s="242" t="s">
+      <c r="B11" s="293"/>
+      <c r="C11" s="293"/>
+      <c r="D11" s="293"/>
+      <c r="E11" s="293"/>
+      <c r="F11" s="294" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="242"/>
+      <c r="G11" s="294"/>
       <c r="H11" s="89"/>
       <c r="I11" s="99" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="J11" s="100"/>
-      <c r="K11" s="100">
-        <f>ADDRESS!I4</f>
-        <v>523953410</v>
-      </c>
+      <c r="K11" s="100"/>
       <c r="L11" s="100"/>
       <c r="M11" s="101"/>
     </row>
     <row r="12" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="243" t="s">
+      <c r="A12" s="280" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="244"/>
-      <c r="C12" s="244"/>
-      <c r="D12" s="244"/>
-      <c r="E12" s="244"/>
-      <c r="F12" s="244"/>
-      <c r="G12" s="244"/>
-      <c r="H12" s="245"/>
-      <c r="I12" s="246"/>
-      <c r="J12" s="247"/>
-      <c r="K12" s="247"/>
-      <c r="L12" s="247"/>
-      <c r="M12" s="248"/>
+      <c r="B12" s="281"/>
+      <c r="C12" s="281"/>
+      <c r="D12" s="281"/>
+      <c r="E12" s="281"/>
+      <c r="F12" s="281"/>
+      <c r="G12" s="281"/>
+      <c r="H12" s="282"/>
+      <c r="I12" s="295"/>
+      <c r="J12" s="296"/>
+      <c r="K12" s="296"/>
+      <c r="L12" s="296"/>
+      <c r="M12" s="297"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="252" t="s">
+      <c r="A13" s="301" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="253"/>
-      <c r="C13" s="253"/>
-      <c r="D13" s="253"/>
-      <c r="E13" s="253"/>
-      <c r="F13" s="253"/>
-      <c r="G13" s="253"/>
-      <c r="H13" s="254"/>
-      <c r="I13" s="246"/>
-      <c r="J13" s="247"/>
-      <c r="K13" s="247"/>
-      <c r="L13" s="247"/>
-      <c r="M13" s="248"/>
+      <c r="B13" s="302"/>
+      <c r="C13" s="302"/>
+      <c r="D13" s="302"/>
+      <c r="E13" s="302"/>
+      <c r="F13" s="302"/>
+      <c r="G13" s="302"/>
+      <c r="H13" s="303"/>
+      <c r="I13" s="295"/>
+      <c r="J13" s="296"/>
+      <c r="K13" s="296"/>
+      <c r="L13" s="296"/>
+      <c r="M13" s="297"/>
     </row>
     <row r="14" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="255" t="s">
+      <c r="A14" s="268" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="256"/>
-      <c r="C14" s="256"/>
-      <c r="D14" s="256"/>
-      <c r="E14" s="256"/>
-      <c r="F14" s="256"/>
-      <c r="G14" s="256"/>
-      <c r="H14" s="257"/>
-      <c r="I14" s="249"/>
-      <c r="J14" s="250"/>
-      <c r="K14" s="250"/>
-      <c r="L14" s="250"/>
-      <c r="M14" s="251"/>
+      <c r="B14" s="269"/>
+      <c r="C14" s="269"/>
+      <c r="D14" s="269"/>
+      <c r="E14" s="269"/>
+      <c r="F14" s="269"/>
+      <c r="G14" s="269"/>
+      <c r="H14" s="270"/>
+      <c r="I14" s="298"/>
+      <c r="J14" s="299"/>
+      <c r="K14" s="299"/>
+      <c r="L14" s="299"/>
+      <c r="M14" s="300"/>
     </row>
     <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="228" t="s">
+      <c r="A15" s="324" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="229"/>
-      <c r="C15" s="229"/>
-      <c r="D15" s="229"/>
-      <c r="E15" s="229"/>
-      <c r="F15" s="229"/>
-      <c r="G15" s="229"/>
-      <c r="H15" s="229"/>
-      <c r="I15" s="230" t="s">
+      <c r="B15" s="325"/>
+      <c r="C15" s="325"/>
+      <c r="D15" s="325"/>
+      <c r="E15" s="325"/>
+      <c r="F15" s="325"/>
+      <c r="G15" s="325"/>
+      <c r="H15" s="325"/>
+      <c r="I15" s="326" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="231"/>
-      <c r="K15" s="231"/>
-      <c r="L15" s="231"/>
-      <c r="M15" s="232"/>
+      <c r="J15" s="327"/>
+      <c r="K15" s="327"/>
+      <c r="L15" s="327"/>
+      <c r="M15" s="328"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="102" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B16" s="103"/>
       <c r="C16" s="103"/>
       <c r="D16" s="103"/>
       <c r="E16" s="103"/>
-      <c r="F16" s="131">
-        <f>ADDRESS!I5</f>
-        <v>59642884</v>
-      </c>
-      <c r="G16" s="131"/>
-      <c r="H16" s="132"/>
-      <c r="I16" s="233" t="s">
-        <v>61</v>
-      </c>
-      <c r="J16" s="234"/>
-      <c r="K16" s="234"/>
-      <c r="L16" s="234"/>
-      <c r="M16" s="235"/>
+      <c r="F16" s="377"/>
+      <c r="G16" s="377"/>
+      <c r="H16" s="378"/>
+      <c r="I16" s="329" t="s">
+        <v>234</v>
+      </c>
+      <c r="J16" s="330"/>
+      <c r="K16" s="330"/>
+      <c r="L16" s="330"/>
+      <c r="M16" s="331"/>
     </row>
     <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="104"/>
@@ -5304,13 +5276,13 @@
       <c r="F17" s="105"/>
       <c r="G17" s="105"/>
       <c r="H17" s="106"/>
-      <c r="I17" s="138"/>
-      <c r="J17" s="139"/>
-      <c r="K17" s="236" t="s">
+      <c r="I17" s="332"/>
+      <c r="J17" s="306"/>
+      <c r="K17" s="333" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="236"/>
-      <c r="M17" s="237"/>
+      <c r="L17" s="333"/>
+      <c r="M17" s="334"/>
     </row>
     <row r="18" spans="1:13" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="104"/>
@@ -5321,323 +5293,285 @@
       <c r="F18" s="105"/>
       <c r="G18" s="105"/>
       <c r="H18" s="106"/>
-      <c r="I18" s="128" t="s">
+      <c r="I18" s="337" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="129"/>
-      <c r="K18" s="238"/>
-      <c r="L18" s="238"/>
-      <c r="M18" s="239"/>
+      <c r="J18" s="338"/>
+      <c r="K18" s="335"/>
+      <c r="L18" s="335"/>
+      <c r="M18" s="336"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="203" t="s">
+      <c r="A19" s="309" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="204"/>
-      <c r="C19" s="204"/>
-      <c r="D19" s="204"/>
-      <c r="E19" s="204"/>
-      <c r="F19" s="204"/>
-      <c r="G19" s="204"/>
-      <c r="H19" s="204"/>
-      <c r="I19" s="204"/>
-      <c r="J19" s="204"/>
-      <c r="K19" s="204"/>
-      <c r="L19" s="204"/>
-      <c r="M19" s="205"/>
+      <c r="B19" s="310"/>
+      <c r="C19" s="310"/>
+      <c r="D19" s="310"/>
+      <c r="E19" s="310"/>
+      <c r="F19" s="310"/>
+      <c r="G19" s="310"/>
+      <c r="H19" s="310"/>
+      <c r="I19" s="310"/>
+      <c r="J19" s="310"/>
+      <c r="K19" s="310"/>
+      <c r="L19" s="310"/>
+      <c r="M19" s="311"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="216" t="s">
+      <c r="A20" s="312" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="217"/>
-      <c r="C20" s="217"/>
-      <c r="D20" s="217"/>
-      <c r="E20" s="217" t="s">
+      <c r="B20" s="313"/>
+      <c r="C20" s="313"/>
+      <c r="D20" s="313"/>
+      <c r="E20" s="313" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="217" t="s">
+      <c r="F20" s="313" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="217"/>
-      <c r="H20" s="218" t="s">
+      <c r="G20" s="313"/>
+      <c r="H20" s="314" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="219"/>
-      <c r="J20" s="220" t="s">
+      <c r="I20" s="315"/>
+      <c r="J20" s="316" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="221"/>
-      <c r="L20" s="221"/>
-      <c r="M20" s="222"/>
+      <c r="K20" s="317"/>
+      <c r="L20" s="317"/>
+      <c r="M20" s="318"/>
     </row>
     <row r="21" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="216"/>
-      <c r="B21" s="217"/>
-      <c r="C21" s="217"/>
-      <c r="D21" s="217"/>
-      <c r="E21" s="217"/>
-      <c r="F21" s="217"/>
-      <c r="G21" s="217"/>
-      <c r="H21" s="226" t="s">
+      <c r="A21" s="312"/>
+      <c r="B21" s="313"/>
+      <c r="C21" s="313"/>
+      <c r="D21" s="313"/>
+      <c r="E21" s="313"/>
+      <c r="F21" s="313"/>
+      <c r="G21" s="313"/>
+      <c r="H21" s="322" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="227"/>
-      <c r="J21" s="223"/>
-      <c r="K21" s="224"/>
-      <c r="L21" s="224"/>
-      <c r="M21" s="225"/>
+      <c r="I21" s="323"/>
+      <c r="J21" s="319"/>
+      <c r="K21" s="320"/>
+      <c r="L21" s="320"/>
+      <c r="M21" s="321"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="212"/>
-      <c r="B22" s="212"/>
-      <c r="C22" s="212"/>
-      <c r="D22" s="213"/>
-      <c r="E22" s="107">
-        <v>40</v>
-      </c>
-      <c r="F22" s="214">
-        <v>40</v>
-      </c>
-      <c r="G22" s="214"/>
+      <c r="A22" s="339"/>
+      <c r="B22" s="339"/>
+      <c r="C22" s="339"/>
+      <c r="D22" s="340"/>
+      <c r="E22" s="107"/>
+      <c r="F22" s="341"/>
+      <c r="G22" s="341"/>
       <c r="H22" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I22" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="200"/>
-      <c r="K22" s="200"/>
-      <c r="L22" s="200"/>
-      <c r="M22" s="215"/>
+      <c r="J22" s="342"/>
+      <c r="K22" s="342"/>
+      <c r="L22" s="342"/>
+      <c r="M22" s="343"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="212"/>
-      <c r="B23" s="212"/>
-      <c r="C23" s="212"/>
-      <c r="D23" s="213"/>
-      <c r="E23" s="107">
-        <v>38</v>
-      </c>
-      <c r="F23" s="214">
-        <v>38</v>
-      </c>
-      <c r="G23" s="214"/>
+      <c r="A23" s="339"/>
+      <c r="B23" s="339"/>
+      <c r="C23" s="339"/>
+      <c r="D23" s="340"/>
+      <c r="E23" s="107"/>
+      <c r="F23" s="341"/>
+      <c r="G23" s="341"/>
       <c r="H23" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I23" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="200"/>
-      <c r="K23" s="200"/>
-      <c r="L23" s="200"/>
-      <c r="M23" s="215"/>
+      <c r="J23" s="342"/>
+      <c r="K23" s="342"/>
+      <c r="L23" s="342"/>
+      <c r="M23" s="343"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="212"/>
-      <c r="B24" s="212"/>
-      <c r="C24" s="212"/>
-      <c r="D24" s="213"/>
-      <c r="E24" s="107">
-        <v>59</v>
-      </c>
-      <c r="F24" s="214">
-        <v>59</v>
-      </c>
-      <c r="G24" s="214"/>
+      <c r="A24" s="339"/>
+      <c r="B24" s="339"/>
+      <c r="C24" s="339"/>
+      <c r="D24" s="340"/>
+      <c r="E24" s="107"/>
+      <c r="F24" s="341"/>
+      <c r="G24" s="341"/>
       <c r="H24" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I24" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="200"/>
-      <c r="K24" s="200"/>
-      <c r="L24" s="200"/>
-      <c r="M24" s="215"/>
+      <c r="J24" s="342"/>
+      <c r="K24" s="342"/>
+      <c r="L24" s="342"/>
+      <c r="M24" s="343"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="212"/>
-      <c r="B25" s="212"/>
-      <c r="C25" s="212"/>
-      <c r="D25" s="213"/>
-      <c r="E25" s="107">
-        <v>81</v>
-      </c>
-      <c r="F25" s="214">
-        <v>81</v>
-      </c>
-      <c r="G25" s="214"/>
+      <c r="A25" s="339"/>
+      <c r="B25" s="339"/>
+      <c r="C25" s="339"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="107"/>
+      <c r="F25" s="341"/>
+      <c r="G25" s="341"/>
       <c r="H25" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I25" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="200"/>
-      <c r="K25" s="200"/>
-      <c r="L25" s="200"/>
-      <c r="M25" s="215"/>
+      <c r="J25" s="342"/>
+      <c r="K25" s="342"/>
+      <c r="L25" s="342"/>
+      <c r="M25" s="343"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="212"/>
-      <c r="B26" s="212"/>
-      <c r="C26" s="212"/>
-      <c r="D26" s="213"/>
-      <c r="E26" s="107">
-        <v>70</v>
-      </c>
-      <c r="F26" s="214">
-        <v>70</v>
-      </c>
-      <c r="G26" s="214"/>
+      <c r="A26" s="339"/>
+      <c r="B26" s="339"/>
+      <c r="C26" s="339"/>
+      <c r="D26" s="340"/>
+      <c r="E26" s="107"/>
+      <c r="F26" s="341"/>
+      <c r="G26" s="341"/>
       <c r="H26" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I26" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="200"/>
-      <c r="K26" s="200"/>
-      <c r="L26" s="200"/>
-      <c r="M26" s="215"/>
+      <c r="J26" s="342"/>
+      <c r="K26" s="342"/>
+      <c r="L26" s="342"/>
+      <c r="M26" s="343"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="212"/>
-      <c r="B27" s="212"/>
-      <c r="C27" s="212"/>
-      <c r="D27" s="213"/>
-      <c r="E27" s="107">
-        <v>62</v>
-      </c>
-      <c r="F27" s="214">
-        <v>62</v>
-      </c>
-      <c r="G27" s="214"/>
+      <c r="A27" s="339"/>
+      <c r="B27" s="339"/>
+      <c r="C27" s="339"/>
+      <c r="D27" s="340"/>
+      <c r="E27" s="107"/>
+      <c r="F27" s="341"/>
+      <c r="G27" s="341"/>
       <c r="H27" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I27" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J27" s="200"/>
-      <c r="K27" s="200"/>
-      <c r="L27" s="200"/>
-      <c r="M27" s="215"/>
+      <c r="J27" s="342"/>
+      <c r="K27" s="342"/>
+      <c r="L27" s="342"/>
+      <c r="M27" s="343"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="212"/>
-      <c r="B28" s="212"/>
-      <c r="C28" s="212"/>
-      <c r="D28" s="213"/>
-      <c r="E28" s="107">
-        <v>66</v>
-      </c>
-      <c r="F28" s="214">
-        <v>66</v>
-      </c>
-      <c r="G28" s="214"/>
+      <c r="A28" s="339"/>
+      <c r="B28" s="339"/>
+      <c r="C28" s="339"/>
+      <c r="D28" s="340"/>
+      <c r="E28" s="107"/>
+      <c r="F28" s="341"/>
+      <c r="G28" s="341"/>
       <c r="H28" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J28" s="200"/>
-      <c r="K28" s="200"/>
-      <c r="L28" s="200"/>
-      <c r="M28" s="215"/>
+      <c r="J28" s="342"/>
+      <c r="K28" s="342"/>
+      <c r="L28" s="342"/>
+      <c r="M28" s="343"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="212"/>
-      <c r="B29" s="212"/>
-      <c r="C29" s="212"/>
-      <c r="D29" s="213"/>
-      <c r="E29" s="107">
-        <v>65</v>
-      </c>
-      <c r="F29" s="214">
-        <v>65</v>
-      </c>
-      <c r="G29" s="214"/>
+      <c r="A29" s="339"/>
+      <c r="B29" s="339"/>
+      <c r="C29" s="339"/>
+      <c r="D29" s="340"/>
+      <c r="E29" s="107"/>
+      <c r="F29" s="341"/>
+      <c r="G29" s="341"/>
       <c r="H29" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I29" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J29" s="200"/>
-      <c r="K29" s="200"/>
-      <c r="L29" s="200"/>
-      <c r="M29" s="215"/>
+      <c r="J29" s="342"/>
+      <c r="K29" s="342"/>
+      <c r="L29" s="342"/>
+      <c r="M29" s="343"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="197" t="s">
+      <c r="A30" s="349" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="198"/>
-      <c r="C30" s="198"/>
-      <c r="D30" s="198"/>
-      <c r="E30" s="14">
-        <f>SUM(E22:E29,Supplemental_Master_BOL!E5:E25)</f>
-        <v>1688</v>
-      </c>
-      <c r="F30" s="199">
-        <f>SUM(F22:G29,Supplemental_Master_BOL!F5:G25)</f>
-        <v>1688</v>
-      </c>
-      <c r="G30" s="200"/>
+      <c r="B30" s="350"/>
+      <c r="C30" s="350"/>
+      <c r="D30" s="350"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="351"/>
+      <c r="G30" s="342"/>
       <c r="H30" s="15"/>
       <c r="I30" s="15"/>
-      <c r="J30" s="201"/>
-      <c r="K30" s="201"/>
-      <c r="L30" s="201"/>
-      <c r="M30" s="202"/>
+      <c r="J30" s="352"/>
+      <c r="K30" s="352"/>
+      <c r="L30" s="352"/>
+      <c r="M30" s="353"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="203" t="s">
+      <c r="A31" s="309" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="204"/>
-      <c r="C31" s="204"/>
-      <c r="D31" s="204"/>
-      <c r="E31" s="204"/>
-      <c r="F31" s="204"/>
-      <c r="G31" s="204"/>
-      <c r="H31" s="204"/>
-      <c r="I31" s="204"/>
-      <c r="J31" s="204"/>
-      <c r="K31" s="204"/>
-      <c r="L31" s="204"/>
-      <c r="M31" s="205"/>
+      <c r="B31" s="310"/>
+      <c r="C31" s="310"/>
+      <c r="D31" s="310"/>
+      <c r="E31" s="310"/>
+      <c r="F31" s="310"/>
+      <c r="G31" s="310"/>
+      <c r="H31" s="310"/>
+      <c r="I31" s="310"/>
+      <c r="J31" s="310"/>
+      <c r="K31" s="310"/>
+      <c r="L31" s="310"/>
+      <c r="M31" s="311"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="206" t="s">
+      <c r="A32" s="354" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="207"/>
-      <c r="C32" s="207" t="s">
+      <c r="B32" s="355"/>
+      <c r="C32" s="355" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="207"/>
-      <c r="E32" s="208" t="s">
+      <c r="D32" s="355"/>
+      <c r="E32" s="356" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="209" t="s">
+      <c r="F32" s="357" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="210" t="s">
+      <c r="G32" s="358" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="210"/>
-      <c r="I32" s="210"/>
-      <c r="J32" s="210"/>
-      <c r="K32" s="210"/>
-      <c r="L32" s="207" t="s">
+      <c r="H32" s="358"/>
+      <c r="I32" s="358"/>
+      <c r="J32" s="358"/>
+      <c r="K32" s="358"/>
+      <c r="L32" s="355" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="211"/>
+      <c r="M32" s="359"/>
     </row>
     <row r="33" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="16" t="s">
@@ -5652,15 +5586,15 @@
       <c r="D33" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="208"/>
-      <c r="F33" s="209"/>
-      <c r="G33" s="196" t="s">
+      <c r="E33" s="356"/>
+      <c r="F33" s="357"/>
+      <c r="G33" s="344" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="196"/>
-      <c r="I33" s="196"/>
-      <c r="J33" s="196"/>
-      <c r="K33" s="196"/>
+      <c r="H33" s="344"/>
+      <c r="I33" s="344"/>
+      <c r="J33" s="344"/>
+      <c r="K33" s="344"/>
       <c r="L33" s="18" t="s">
         <v>14</v>
       </c>
@@ -5669,29 +5603,17 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="111">
-        <v>6</v>
-      </c>
-      <c r="B34" s="108" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" s="109">
-        <v>1688</v>
-      </c>
-      <c r="D34" s="108" t="s">
-        <v>60</v>
-      </c>
-      <c r="E34" s="109">
-        <v>6698</v>
-      </c>
+      <c r="A34" s="111"/>
+      <c r="B34" s="108"/>
+      <c r="C34" s="109"/>
+      <c r="D34" s="108"/>
+      <c r="E34" s="109"/>
       <c r="F34" s="108"/>
-      <c r="G34" s="169" t="s">
-        <v>70</v>
-      </c>
-      <c r="H34" s="170"/>
-      <c r="I34" s="170"/>
-      <c r="J34" s="170"/>
-      <c r="K34" s="171"/>
+      <c r="G34" s="345"/>
+      <c r="H34" s="346"/>
+      <c r="I34" s="346"/>
+      <c r="J34" s="346"/>
+      <c r="K34" s="347"/>
       <c r="L34" s="20"/>
       <c r="M34" s="21"/>
     </row>
@@ -5702,11 +5624,11 @@
       <c r="D35" s="108"/>
       <c r="E35" s="108"/>
       <c r="F35" s="20"/>
-      <c r="G35" s="169"/>
-      <c r="H35" s="170"/>
-      <c r="I35" s="170"/>
-      <c r="J35" s="170"/>
-      <c r="K35" s="171"/>
+      <c r="G35" s="345"/>
+      <c r="H35" s="346"/>
+      <c r="I35" s="346"/>
+      <c r="J35" s="346"/>
+      <c r="K35" s="347"/>
       <c r="L35" s="20"/>
       <c r="M35" s="21"/>
     </row>
@@ -5717,11 +5639,11 @@
       <c r="D36" s="108"/>
       <c r="E36" s="108"/>
       <c r="F36" s="20"/>
-      <c r="G36" s="169"/>
-      <c r="H36" s="170"/>
-      <c r="I36" s="170"/>
-      <c r="J36" s="170"/>
-      <c r="K36" s="171"/>
+      <c r="G36" s="345"/>
+      <c r="H36" s="346"/>
+      <c r="I36" s="346"/>
+      <c r="J36" s="346"/>
+      <c r="K36" s="347"/>
       <c r="L36" s="20"/>
       <c r="M36" s="21"/>
     </row>
@@ -5732,19 +5654,19 @@
       <c r="D37" s="108"/>
       <c r="E37" s="108"/>
       <c r="F37" s="20"/>
-      <c r="G37" s="169"/>
-      <c r="H37" s="170"/>
-      <c r="I37" s="170"/>
-      <c r="J37" s="170"/>
-      <c r="K37" s="171"/>
+      <c r="G37" s="345"/>
+      <c r="H37" s="346"/>
+      <c r="I37" s="346"/>
+      <c r="J37" s="346"/>
+      <c r="K37" s="347"/>
       <c r="L37" s="20"/>
       <c r="M37" s="21"/>
-      <c r="Q37" s="194"/>
-      <c r="R37" s="194"/>
+      <c r="Q37" s="348"/>
+      <c r="R37" s="348"/>
       <c r="S37" s="22"/>
-      <c r="T37" s="193"/>
-      <c r="U37" s="193"/>
-      <c r="V37" s="193"/>
+      <c r="T37" s="372"/>
+      <c r="U37" s="372"/>
+      <c r="V37" s="372"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A38" s="111"/>
@@ -5753,19 +5675,19 @@
       <c r="D38" s="108"/>
       <c r="E38" s="108"/>
       <c r="F38" s="20"/>
-      <c r="G38" s="169"/>
-      <c r="H38" s="170"/>
-      <c r="I38" s="170"/>
-      <c r="J38" s="170"/>
-      <c r="K38" s="171"/>
+      <c r="G38" s="345"/>
+      <c r="H38" s="346"/>
+      <c r="I38" s="346"/>
+      <c r="J38" s="346"/>
+      <c r="K38" s="347"/>
       <c r="L38" s="20"/>
       <c r="M38" s="24"/>
-      <c r="Q38" s="194"/>
-      <c r="R38" s="194"/>
+      <c r="Q38" s="348"/>
+      <c r="R38" s="348"/>
       <c r="S38" s="22"/>
-      <c r="T38" s="193"/>
-      <c r="U38" s="193"/>
-      <c r="V38" s="193"/>
+      <c r="T38" s="372"/>
+      <c r="U38" s="372"/>
+      <c r="V38" s="372"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A39" s="111"/>
@@ -5774,19 +5696,19 @@
       <c r="D39" s="108"/>
       <c r="E39" s="108"/>
       <c r="F39" s="20"/>
-      <c r="G39" s="169"/>
-      <c r="H39" s="170"/>
-      <c r="I39" s="170"/>
-      <c r="J39" s="170"/>
-      <c r="K39" s="171"/>
+      <c r="G39" s="345"/>
+      <c r="H39" s="346"/>
+      <c r="I39" s="346"/>
+      <c r="J39" s="346"/>
+      <c r="K39" s="347"/>
       <c r="L39" s="20"/>
       <c r="M39" s="24"/>
       <c r="Q39" s="25"/>
       <c r="R39" s="25"/>
-      <c r="S39" s="195"/>
-      <c r="T39" s="193"/>
-      <c r="U39" s="193"/>
-      <c r="V39" s="193"/>
+      <c r="S39" s="373"/>
+      <c r="T39" s="372"/>
+      <c r="U39" s="372"/>
+      <c r="V39" s="372"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A40" s="111"/>
@@ -5795,19 +5717,19 @@
       <c r="D40" s="108"/>
       <c r="E40" s="108"/>
       <c r="F40" s="20"/>
-      <c r="G40" s="169"/>
-      <c r="H40" s="170"/>
-      <c r="I40" s="170"/>
-      <c r="J40" s="170"/>
-      <c r="K40" s="171"/>
+      <c r="G40" s="345"/>
+      <c r="H40" s="346"/>
+      <c r="I40" s="346"/>
+      <c r="J40" s="346"/>
+      <c r="K40" s="347"/>
       <c r="L40" s="20"/>
       <c r="M40" s="21"/>
       <c r="Q40" s="25"/>
       <c r="R40" s="25"/>
-      <c r="S40" s="195"/>
-      <c r="T40" s="193"/>
-      <c r="U40" s="193"/>
-      <c r="V40" s="193"/>
+      <c r="S40" s="373"/>
+      <c r="T40" s="372"/>
+      <c r="U40" s="372"/>
+      <c r="V40" s="372"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A41" s="111"/>
@@ -5816,317 +5738,311 @@
       <c r="D41" s="108"/>
       <c r="E41" s="108"/>
       <c r="F41" s="20"/>
-      <c r="G41" s="169"/>
-      <c r="H41" s="170"/>
-      <c r="I41" s="170"/>
-      <c r="J41" s="170"/>
-      <c r="K41" s="171"/>
+      <c r="G41" s="345"/>
+      <c r="H41" s="346"/>
+      <c r="I41" s="346"/>
+      <c r="J41" s="346"/>
+      <c r="K41" s="347"/>
       <c r="L41" s="20"/>
       <c r="M41" s="21"/>
     </row>
     <row r="42" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="112">
-        <v>6</v>
-      </c>
+      <c r="A42" s="112"/>
       <c r="B42" s="113"/>
-      <c r="C42" s="114">
-        <v>1688</v>
-      </c>
+      <c r="C42" s="114"/>
       <c r="D42" s="113"/>
-      <c r="E42" s="114">
-        <v>1688</v>
-      </c>
+      <c r="E42" s="114"/>
       <c r="F42" s="26"/>
-      <c r="G42" s="172" t="s">
+      <c r="G42" s="412" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="173"/>
-      <c r="I42" s="173"/>
-      <c r="J42" s="173"/>
-      <c r="K42" s="174"/>
+      <c r="H42" s="413"/>
+      <c r="I42" s="413"/>
+      <c r="J42" s="413"/>
+      <c r="K42" s="414"/>
       <c r="L42" s="26"/>
       <c r="M42" s="27"/>
     </row>
     <row r="43" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="149" t="s">
+      <c r="A43" s="392" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="150"/>
-      <c r="C43" s="150"/>
-      <c r="D43" s="150"/>
-      <c r="E43" s="150"/>
-      <c r="F43" s="150"/>
-      <c r="G43" s="150"/>
-      <c r="H43" s="151"/>
-      <c r="I43" s="175" t="s">
+      <c r="B43" s="393"/>
+      <c r="C43" s="393"/>
+      <c r="D43" s="393"/>
+      <c r="E43" s="393"/>
+      <c r="F43" s="393"/>
+      <c r="G43" s="393"/>
+      <c r="H43" s="394"/>
+      <c r="I43" s="415" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="176"/>
-      <c r="K43" s="176"/>
-      <c r="L43" s="176"/>
-      <c r="M43" s="177"/>
+      <c r="J43" s="416"/>
+      <c r="K43" s="416"/>
+      <c r="L43" s="416"/>
+      <c r="M43" s="417"/>
     </row>
     <row r="44" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="152"/>
-      <c r="B44" s="153"/>
-      <c r="C44" s="153"/>
-      <c r="D44" s="153"/>
-      <c r="E44" s="153"/>
-      <c r="F44" s="153"/>
-      <c r="G44" s="153"/>
-      <c r="H44" s="154"/>
-      <c r="I44" s="178"/>
-      <c r="J44" s="179"/>
-      <c r="K44" s="179"/>
-      <c r="L44" s="179"/>
-      <c r="M44" s="180"/>
+      <c r="A44" s="395"/>
+      <c r="B44" s="396"/>
+      <c r="C44" s="396"/>
+      <c r="D44" s="396"/>
+      <c r="E44" s="396"/>
+      <c r="F44" s="396"/>
+      <c r="G44" s="396"/>
+      <c r="H44" s="397"/>
+      <c r="I44" s="418"/>
+      <c r="J44" s="419"/>
+      <c r="K44" s="419"/>
+      <c r="L44" s="419"/>
+      <c r="M44" s="420"/>
     </row>
     <row r="45" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="181" t="s">
+      <c r="A45" s="360" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="182"/>
-      <c r="C45" s="182"/>
-      <c r="D45" s="182"/>
-      <c r="E45" s="182"/>
-      <c r="F45" s="182"/>
-      <c r="G45" s="182"/>
-      <c r="H45" s="183"/>
-      <c r="I45" s="184" t="s">
+      <c r="B45" s="361"/>
+      <c r="C45" s="361"/>
+      <c r="D45" s="361"/>
+      <c r="E45" s="361"/>
+      <c r="F45" s="361"/>
+      <c r="G45" s="361"/>
+      <c r="H45" s="362"/>
+      <c r="I45" s="363" t="s">
         <v>36</v>
       </c>
-      <c r="J45" s="185"/>
-      <c r="K45" s="185"/>
-      <c r="L45" s="185"/>
-      <c r="M45" s="186"/>
+      <c r="J45" s="364"/>
+      <c r="K45" s="364"/>
+      <c r="L45" s="364"/>
+      <c r="M45" s="365"/>
     </row>
     <row r="46" spans="1:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="181" t="s">
+      <c r="A46" s="360" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="182"/>
-      <c r="C46" s="182"/>
-      <c r="D46" s="182"/>
-      <c r="E46" s="182"/>
-      <c r="F46" s="182"/>
-      <c r="G46" s="182"/>
-      <c r="H46" s="183"/>
-      <c r="I46" s="184"/>
-      <c r="J46" s="185"/>
-      <c r="K46" s="185"/>
-      <c r="L46" s="185"/>
-      <c r="M46" s="186"/>
+      <c r="B46" s="361"/>
+      <c r="C46" s="361"/>
+      <c r="D46" s="361"/>
+      <c r="E46" s="361"/>
+      <c r="F46" s="361"/>
+      <c r="G46" s="361"/>
+      <c r="H46" s="362"/>
+      <c r="I46" s="363"/>
+      <c r="J46" s="364"/>
+      <c r="K46" s="364"/>
+      <c r="L46" s="364"/>
+      <c r="M46" s="365"/>
     </row>
     <row r="47" spans="1:22" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="187"/>
-      <c r="B47" s="188"/>
-      <c r="C47" s="188"/>
-      <c r="D47" s="188"/>
-      <c r="E47" s="188"/>
-      <c r="F47" s="188"/>
-      <c r="G47" s="188"/>
-      <c r="H47" s="189"/>
-      <c r="I47" s="190" t="s">
+      <c r="A47" s="366"/>
+      <c r="B47" s="367"/>
+      <c r="C47" s="367"/>
+      <c r="D47" s="367"/>
+      <c r="E47" s="367"/>
+      <c r="F47" s="367"/>
+      <c r="G47" s="367"/>
+      <c r="H47" s="368"/>
+      <c r="I47" s="369" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="191"/>
-      <c r="K47" s="191"/>
-      <c r="L47" s="191"/>
-      <c r="M47" s="192"/>
+      <c r="J47" s="370"/>
+      <c r="K47" s="370"/>
+      <c r="L47" s="370"/>
+      <c r="M47" s="371"/>
     </row>
     <row r="48" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="146" t="s">
+      <c r="A48" s="389" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="147"/>
-      <c r="C48" s="147"/>
-      <c r="D48" s="147"/>
-      <c r="E48" s="147"/>
-      <c r="F48" s="147"/>
-      <c r="G48" s="147"/>
-      <c r="H48" s="147"/>
-      <c r="I48" s="147"/>
-      <c r="J48" s="147"/>
-      <c r="K48" s="147"/>
-      <c r="L48" s="147"/>
-      <c r="M48" s="148"/>
+      <c r="B48" s="390"/>
+      <c r="C48" s="390"/>
+      <c r="D48" s="390"/>
+      <c r="E48" s="390"/>
+      <c r="F48" s="390"/>
+      <c r="G48" s="390"/>
+      <c r="H48" s="390"/>
+      <c r="I48" s="390"/>
+      <c r="J48" s="390"/>
+      <c r="K48" s="390"/>
+      <c r="L48" s="390"/>
+      <c r="M48" s="391"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="149" t="s">
+      <c r="A49" s="392" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="150"/>
-      <c r="C49" s="150"/>
-      <c r="D49" s="150"/>
-      <c r="E49" s="150"/>
-      <c r="F49" s="150"/>
-      <c r="G49" s="150"/>
-      <c r="H49" s="151"/>
-      <c r="I49" s="157" t="s">
+      <c r="B49" s="393"/>
+      <c r="C49" s="393"/>
+      <c r="D49" s="393"/>
+      <c r="E49" s="393"/>
+      <c r="F49" s="393"/>
+      <c r="G49" s="393"/>
+      <c r="H49" s="394"/>
+      <c r="I49" s="400" t="s">
         <v>40</v>
       </c>
-      <c r="J49" s="158"/>
-      <c r="K49" s="158"/>
-      <c r="L49" s="158"/>
-      <c r="M49" s="159"/>
+      <c r="J49" s="401"/>
+      <c r="K49" s="401"/>
+      <c r="L49" s="401"/>
+      <c r="M49" s="402"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="152"/>
-      <c r="B50" s="153"/>
-      <c r="C50" s="153"/>
-      <c r="D50" s="153"/>
-      <c r="E50" s="153"/>
-      <c r="F50" s="153"/>
-      <c r="G50" s="153"/>
-      <c r="H50" s="154"/>
-      <c r="I50" s="160"/>
-      <c r="J50" s="161"/>
-      <c r="K50" s="161"/>
-      <c r="L50" s="161"/>
-      <c r="M50" s="162"/>
+      <c r="A50" s="395"/>
+      <c r="B50" s="396"/>
+      <c r="C50" s="396"/>
+      <c r="D50" s="396"/>
+      <c r="E50" s="396"/>
+      <c r="F50" s="396"/>
+      <c r="G50" s="396"/>
+      <c r="H50" s="397"/>
+      <c r="I50" s="403"/>
+      <c r="J50" s="404"/>
+      <c r="K50" s="404"/>
+      <c r="L50" s="404"/>
+      <c r="M50" s="405"/>
     </row>
     <row r="51" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="155"/>
-      <c r="B51" s="156"/>
-      <c r="C51" s="156"/>
-      <c r="D51" s="156"/>
-      <c r="E51" s="153"/>
-      <c r="F51" s="153"/>
-      <c r="G51" s="153"/>
-      <c r="H51" s="154"/>
-      <c r="I51" s="163" t="s">
+      <c r="A51" s="398"/>
+      <c r="B51" s="399"/>
+      <c r="C51" s="399"/>
+      <c r="D51" s="399"/>
+      <c r="E51" s="396"/>
+      <c r="F51" s="396"/>
+      <c r="G51" s="396"/>
+      <c r="H51" s="397"/>
+      <c r="I51" s="406" t="s">
         <v>41</v>
       </c>
-      <c r="J51" s="164"/>
-      <c r="K51" s="165"/>
-      <c r="L51" s="165"/>
-      <c r="M51" s="166"/>
+      <c r="J51" s="407"/>
+      <c r="K51" s="408"/>
+      <c r="L51" s="408"/>
+      <c r="M51" s="409"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="146" t="s">
+      <c r="A52" s="389" t="s">
         <v>42</v>
       </c>
-      <c r="B52" s="147"/>
-      <c r="C52" s="147"/>
-      <c r="D52" s="147"/>
+      <c r="B52" s="390"/>
+      <c r="C52" s="390"/>
+      <c r="D52" s="390"/>
       <c r="E52" s="115" t="s">
         <v>44</v>
       </c>
       <c r="F52" s="116"/>
-      <c r="G52" s="167" t="s">
+      <c r="G52" s="410" t="s">
         <v>45</v>
       </c>
-      <c r="H52" s="167"/>
-      <c r="I52" s="167"/>
-      <c r="J52" s="168"/>
-      <c r="K52" s="147" t="s">
+      <c r="H52" s="410"/>
+      <c r="I52" s="410"/>
+      <c r="J52" s="411"/>
+      <c r="K52" s="390" t="s">
         <v>50</v>
       </c>
-      <c r="L52" s="147"/>
-      <c r="M52" s="148"/>
+      <c r="L52" s="390"/>
+      <c r="M52" s="391"/>
     </row>
     <row r="53" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="133" t="s">
+      <c r="A53" s="379" t="s">
         <v>43</v>
       </c>
-      <c r="B53" s="134"/>
-      <c r="C53" s="134"/>
-      <c r="D53" s="134"/>
+      <c r="B53" s="380"/>
+      <c r="C53" s="380"/>
+      <c r="D53" s="380"/>
       <c r="E53" s="117"/>
       <c r="F53" s="110"/>
       <c r="G53" s="110"/>
       <c r="H53" s="110"/>
       <c r="I53" s="110"/>
       <c r="J53" s="118"/>
-      <c r="K53" s="134" t="s">
+      <c r="K53" s="380" t="s">
         <v>52</v>
       </c>
-      <c r="L53" s="134"/>
-      <c r="M53" s="135"/>
+      <c r="L53" s="380"/>
+      <c r="M53" s="381"/>
     </row>
     <row r="54" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="133"/>
-      <c r="B54" s="134"/>
-      <c r="C54" s="134"/>
-      <c r="D54" s="134"/>
-      <c r="E54" s="136" t="s">
+      <c r="A54" s="379"/>
+      <c r="B54" s="380"/>
+      <c r="C54" s="380"/>
+      <c r="D54" s="380"/>
+      <c r="E54" s="382" t="s">
         <v>46</v>
       </c>
-      <c r="F54" s="137"/>
+      <c r="F54" s="383"/>
       <c r="G54" s="119"/>
-      <c r="H54" s="126" t="s">
+      <c r="H54" s="374" t="s">
         <v>46</v>
       </c>
-      <c r="I54" s="126"/>
-      <c r="J54" s="127"/>
-      <c r="K54" s="134"/>
-      <c r="L54" s="134"/>
-      <c r="M54" s="135"/>
+      <c r="I54" s="374"/>
+      <c r="J54" s="375"/>
+      <c r="K54" s="380"/>
+      <c r="L54" s="380"/>
+      <c r="M54" s="381"/>
     </row>
     <row r="55" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="133"/>
-      <c r="B55" s="134"/>
-      <c r="C55" s="134"/>
-      <c r="D55" s="134"/>
-      <c r="E55" s="136" t="s">
+      <c r="A55" s="379"/>
+      <c r="B55" s="380"/>
+      <c r="C55" s="380"/>
+      <c r="D55" s="380"/>
+      <c r="E55" s="382" t="s">
         <v>47</v>
       </c>
-      <c r="F55" s="137"/>
-      <c r="G55" s="137"/>
-      <c r="H55" s="126" t="s">
+      <c r="F55" s="383"/>
+      <c r="G55" s="383"/>
+      <c r="H55" s="374" t="s">
         <v>48</v>
       </c>
-      <c r="I55" s="126"/>
-      <c r="J55" s="127"/>
-      <c r="K55" s="134"/>
-      <c r="L55" s="134"/>
-      <c r="M55" s="135"/>
+      <c r="I55" s="374"/>
+      <c r="J55" s="375"/>
+      <c r="K55" s="380"/>
+      <c r="L55" s="380"/>
+      <c r="M55" s="381"/>
     </row>
     <row r="56" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="138"/>
-      <c r="B56" s="139"/>
-      <c r="C56" s="139"/>
-      <c r="D56" s="140"/>
-      <c r="E56" s="136"/>
-      <c r="F56" s="137"/>
-      <c r="G56" s="137"/>
-      <c r="H56" s="126"/>
-      <c r="I56" s="126"/>
-      <c r="J56" s="127"/>
-      <c r="K56" s="144" t="s">
+      <c r="A56" s="332"/>
+      <c r="B56" s="306"/>
+      <c r="C56" s="306"/>
+      <c r="D56" s="307"/>
+      <c r="E56" s="382"/>
+      <c r="F56" s="383"/>
+      <c r="G56" s="383"/>
+      <c r="H56" s="374"/>
+      <c r="I56" s="374"/>
+      <c r="J56" s="375"/>
+      <c r="K56" s="387" t="s">
         <v>51</v>
       </c>
-      <c r="L56" s="144"/>
-      <c r="M56" s="145"/>
+      <c r="L56" s="387"/>
+      <c r="M56" s="388"/>
     </row>
     <row r="57" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="138"/>
-      <c r="B57" s="139"/>
-      <c r="C57" s="139"/>
-      <c r="D57" s="140"/>
-      <c r="E57" s="136"/>
-      <c r="F57" s="137"/>
+      <c r="A57" s="332"/>
+      <c r="B57" s="306"/>
+      <c r="C57" s="306"/>
+      <c r="D57" s="307"/>
+      <c r="E57" s="382"/>
+      <c r="F57" s="383"/>
       <c r="G57" s="119"/>
-      <c r="H57" s="126" t="s">
+      <c r="H57" s="374" t="s">
         <v>49</v>
       </c>
-      <c r="I57" s="126"/>
-      <c r="J57" s="127"/>
+      <c r="I57" s="374"/>
+      <c r="J57" s="375"/>
       <c r="K57" s="120"/>
       <c r="L57" s="121"/>
       <c r="M57" s="122"/>
     </row>
     <row r="58" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="141"/>
-      <c r="B58" s="142"/>
-      <c r="C58" s="142"/>
-      <c r="D58" s="143"/>
-      <c r="E58" s="128"/>
-      <c r="F58" s="129"/>
-      <c r="G58" s="129"/>
-      <c r="H58" s="129"/>
-      <c r="I58" s="129"/>
-      <c r="J58" s="130"/>
+      <c r="A58" s="384"/>
+      <c r="B58" s="385"/>
+      <c r="C58" s="385"/>
+      <c r="D58" s="386"/>
+      <c r="E58" s="337"/>
+      <c r="F58" s="338"/>
+      <c r="G58" s="338"/>
+      <c r="H58" s="338"/>
+      <c r="I58" s="338"/>
+      <c r="J58" s="376"/>
       <c r="K58" s="123"/>
       <c r="L58" s="124"/>
       <c r="M58" s="125"/>
@@ -6144,95 +6060,7 @@
       <c r="J59" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="112">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="I4:M6"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:M3"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="I12:M14"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="I8:M8"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="A20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:G21"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="J20:M21"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="I16:M16"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:M18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="G33:K33"/>
-    <mergeCell ref="G34:K34"/>
-    <mergeCell ref="G35:K35"/>
-    <mergeCell ref="G36:K36"/>
-    <mergeCell ref="G37:K37"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="A31:M31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="G32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="I45:M46"/>
-    <mergeCell ref="A46:H47"/>
-    <mergeCell ref="I47:M47"/>
-    <mergeCell ref="T37:V37"/>
-    <mergeCell ref="G38:K38"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="T38:V38"/>
-    <mergeCell ref="G39:K39"/>
-    <mergeCell ref="S39:S40"/>
-    <mergeCell ref="T39:V40"/>
-    <mergeCell ref="G40:K40"/>
+  <mergeCells count="111">
     <mergeCell ref="H57:J57"/>
     <mergeCell ref="E58:J58"/>
     <mergeCell ref="F16:H16"/>
@@ -6257,6 +6085,93 @@
     <mergeCell ref="G42:K42"/>
     <mergeCell ref="A43:H44"/>
     <mergeCell ref="I43:M44"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="I45:M46"/>
+    <mergeCell ref="A46:H47"/>
+    <mergeCell ref="I47:M47"/>
+    <mergeCell ref="T37:V37"/>
+    <mergeCell ref="G38:K38"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="T38:V38"/>
+    <mergeCell ref="G39:K39"/>
+    <mergeCell ref="S39:S40"/>
+    <mergeCell ref="T39:V40"/>
+    <mergeCell ref="G40:K40"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="G34:K34"/>
+    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="G36:K36"/>
+    <mergeCell ref="G37:K37"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="A31:M31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="G32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:G21"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J20:M21"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="I15:M15"/>
+    <mergeCell ref="I16:M16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:M18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="I12:M14"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="I4:M6"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="I2:M3"/>
+    <mergeCell ref="A3:H3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.26" top="0.52" bottom="0.56000000000000005" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6977,1102 +6892,1012 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="270" t="s">
-        <v>237</v>
-      </c>
-      <c r="B1" s="271"/>
-      <c r="C1" s="272" t="s">
+      <c r="A1" s="440" t="s">
+        <v>233</v>
+      </c>
+      <c r="B1" s="441"/>
+      <c r="C1" s="283" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="272"/>
-      <c r="E1" s="272"/>
-      <c r="F1" s="272"/>
-      <c r="G1" s="272"/>
-      <c r="H1" s="272"/>
-      <c r="I1" s="272"/>
-      <c r="J1" s="272"/>
-      <c r="K1" s="272"/>
-      <c r="L1" s="273" t="s">
-        <v>63</v>
-      </c>
-      <c r="M1" s="274"/>
+      <c r="D1" s="283"/>
+      <c r="E1" s="283"/>
+      <c r="F1" s="283"/>
+      <c r="G1" s="283"/>
+      <c r="H1" s="283"/>
+      <c r="I1" s="283"/>
+      <c r="J1" s="283"/>
+      <c r="K1" s="283"/>
+      <c r="L1" s="284" t="s">
+        <v>61</v>
+      </c>
+      <c r="M1" s="285"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="203" t="s">
+      <c r="A2" s="309" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="204"/>
-      <c r="C2" s="204"/>
-      <c r="D2" s="204"/>
-      <c r="E2" s="204"/>
-      <c r="F2" s="204"/>
-      <c r="G2" s="204"/>
-      <c r="H2" s="204"/>
-      <c r="I2" s="204"/>
-      <c r="J2" s="204"/>
-      <c r="K2" s="204"/>
-      <c r="L2" s="204"/>
-      <c r="M2" s="205"/>
+      <c r="B2" s="310"/>
+      <c r="C2" s="310"/>
+      <c r="D2" s="310"/>
+      <c r="E2" s="310"/>
+      <c r="F2" s="310"/>
+      <c r="G2" s="310"/>
+      <c r="H2" s="310"/>
+      <c r="I2" s="310"/>
+      <c r="J2" s="310"/>
+      <c r="K2" s="310"/>
+      <c r="L2" s="310"/>
+      <c r="M2" s="311"/>
     </row>
     <row r="3" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="216" t="s">
+      <c r="A3" s="312" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="217"/>
-      <c r="C3" s="217"/>
-      <c r="D3" s="217"/>
-      <c r="E3" s="217" t="s">
+      <c r="B3" s="313"/>
+      <c r="C3" s="313"/>
+      <c r="D3" s="313"/>
+      <c r="E3" s="313" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="217" t="s">
+      <c r="F3" s="313" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="217"/>
-      <c r="H3" s="218" t="s">
+      <c r="G3" s="313"/>
+      <c r="H3" s="314" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="219"/>
-      <c r="J3" s="220" t="s">
+      <c r="I3" s="315"/>
+      <c r="J3" s="316" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="221"/>
-      <c r="L3" s="221"/>
-      <c r="M3" s="222"/>
+      <c r="K3" s="317"/>
+      <c r="L3" s="317"/>
+      <c r="M3" s="318"/>
     </row>
     <row r="4" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="216"/>
-      <c r="B4" s="217"/>
-      <c r="C4" s="217"/>
-      <c r="D4" s="217"/>
-      <c r="E4" s="217"/>
-      <c r="F4" s="217"/>
-      <c r="G4" s="217"/>
-      <c r="H4" s="226" t="s">
+      <c r="A4" s="312"/>
+      <c r="B4" s="313"/>
+      <c r="C4" s="313"/>
+      <c r="D4" s="313"/>
+      <c r="E4" s="313"/>
+      <c r="F4" s="313"/>
+      <c r="G4" s="313"/>
+      <c r="H4" s="322" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="227"/>
-      <c r="J4" s="223"/>
-      <c r="K4" s="224"/>
-      <c r="L4" s="224"/>
-      <c r="M4" s="225"/>
+      <c r="I4" s="323"/>
+      <c r="J4" s="319"/>
+      <c r="K4" s="320"/>
+      <c r="L4" s="320"/>
+      <c r="M4" s="321"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="438"/>
-      <c r="B5" s="212"/>
-      <c r="C5" s="212"/>
-      <c r="D5" s="212"/>
-      <c r="E5" s="10">
-        <v>61</v>
-      </c>
-      <c r="F5" s="297">
-        <v>61</v>
-      </c>
-      <c r="G5" s="298"/>
+      <c r="A5" s="421"/>
+      <c r="B5" s="339"/>
+      <c r="C5" s="339"/>
+      <c r="D5" s="339"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="165"/>
+      <c r="G5" s="167"/>
       <c r="H5" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I5" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J5" s="200"/>
-      <c r="K5" s="200"/>
-      <c r="L5" s="200"/>
-      <c r="M5" s="215"/>
+      <c r="J5" s="342"/>
+      <c r="K5" s="342"/>
+      <c r="L5" s="342"/>
+      <c r="M5" s="343"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="438"/>
-      <c r="B6" s="212"/>
-      <c r="C6" s="212"/>
-      <c r="D6" s="212"/>
-      <c r="E6" s="10">
-        <v>83</v>
-      </c>
-      <c r="F6" s="297">
-        <v>83</v>
-      </c>
-      <c r="G6" s="298"/>
+      <c r="A6" s="421"/>
+      <c r="B6" s="339"/>
+      <c r="C6" s="339"/>
+      <c r="D6" s="339"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="165"/>
+      <c r="G6" s="167"/>
       <c r="H6" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I6" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J6" s="200"/>
-      <c r="K6" s="200"/>
-      <c r="L6" s="200"/>
-      <c r="M6" s="215"/>
+      <c r="J6" s="342"/>
+      <c r="K6" s="342"/>
+      <c r="L6" s="342"/>
+      <c r="M6" s="343"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="438"/>
-      <c r="B7" s="212"/>
-      <c r="C7" s="212"/>
-      <c r="D7" s="212"/>
-      <c r="E7" s="10">
-        <v>70</v>
-      </c>
-      <c r="F7" s="297">
-        <v>70</v>
-      </c>
-      <c r="G7" s="298"/>
+      <c r="A7" s="421"/>
+      <c r="B7" s="339"/>
+      <c r="C7" s="339"/>
+      <c r="D7" s="339"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="165"/>
+      <c r="G7" s="167"/>
       <c r="H7" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I7" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J7" s="200"/>
-      <c r="K7" s="200"/>
-      <c r="L7" s="200"/>
-      <c r="M7" s="215"/>
+      <c r="J7" s="342"/>
+      <c r="K7" s="342"/>
+      <c r="L7" s="342"/>
+      <c r="M7" s="343"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="438"/>
-      <c r="B8" s="212"/>
-      <c r="C8" s="212"/>
-      <c r="D8" s="212"/>
-      <c r="E8" s="10">
-        <v>50</v>
-      </c>
-      <c r="F8" s="297">
-        <v>50</v>
-      </c>
-      <c r="G8" s="298"/>
+      <c r="A8" s="421"/>
+      <c r="B8" s="339"/>
+      <c r="C8" s="339"/>
+      <c r="D8" s="339"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="165"/>
+      <c r="G8" s="167"/>
       <c r="H8" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I8" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J8" s="200"/>
-      <c r="K8" s="200"/>
-      <c r="L8" s="200"/>
-      <c r="M8" s="215"/>
+      <c r="J8" s="342"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="343"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="438"/>
-      <c r="B9" s="212"/>
-      <c r="C9" s="212"/>
-      <c r="D9" s="212"/>
-      <c r="E9" s="10">
-        <v>70</v>
-      </c>
-      <c r="F9" s="297">
-        <v>70</v>
-      </c>
-      <c r="G9" s="298"/>
+      <c r="A9" s="421"/>
+      <c r="B9" s="339"/>
+      <c r="C9" s="339"/>
+      <c r="D9" s="339"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="165"/>
+      <c r="G9" s="167"/>
       <c r="H9" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I9" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J9" s="200"/>
-      <c r="K9" s="200"/>
-      <c r="L9" s="200"/>
-      <c r="M9" s="215"/>
+      <c r="J9" s="342"/>
+      <c r="K9" s="342"/>
+      <c r="L9" s="342"/>
+      <c r="M9" s="343"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="438"/>
-      <c r="B10" s="212"/>
-      <c r="C10" s="212"/>
-      <c r="D10" s="212"/>
-      <c r="E10" s="10">
-        <v>69</v>
-      </c>
-      <c r="F10" s="297">
-        <v>69</v>
-      </c>
-      <c r="G10" s="298"/>
+      <c r="A10" s="421"/>
+      <c r="B10" s="339"/>
+      <c r="C10" s="339"/>
+      <c r="D10" s="339"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="165"/>
+      <c r="G10" s="167"/>
       <c r="H10" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I10" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="200"/>
-      <c r="K10" s="200"/>
-      <c r="L10" s="200"/>
-      <c r="M10" s="215"/>
+      <c r="J10" s="342"/>
+      <c r="K10" s="342"/>
+      <c r="L10" s="342"/>
+      <c r="M10" s="343"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="438"/>
-      <c r="B11" s="212"/>
-      <c r="C11" s="212"/>
-      <c r="D11" s="212"/>
-      <c r="E11" s="10">
-        <v>54</v>
-      </c>
-      <c r="F11" s="297">
-        <v>54</v>
-      </c>
-      <c r="G11" s="298"/>
+      <c r="A11" s="421"/>
+      <c r="B11" s="339"/>
+      <c r="C11" s="339"/>
+      <c r="D11" s="339"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="165"/>
+      <c r="G11" s="167"/>
       <c r="H11" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I11" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J11" s="200"/>
-      <c r="K11" s="200"/>
-      <c r="L11" s="200"/>
-      <c r="M11" s="215"/>
+      <c r="J11" s="342"/>
+      <c r="K11" s="342"/>
+      <c r="L11" s="342"/>
+      <c r="M11" s="343"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="438"/>
-      <c r="B12" s="212"/>
-      <c r="C12" s="212"/>
-      <c r="D12" s="212"/>
-      <c r="E12" s="10">
-        <v>65</v>
-      </c>
-      <c r="F12" s="297">
-        <v>65</v>
-      </c>
-      <c r="G12" s="298"/>
+      <c r="A12" s="421"/>
+      <c r="B12" s="339"/>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="165"/>
+      <c r="G12" s="167"/>
       <c r="H12" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I12" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J12" s="200"/>
-      <c r="K12" s="200"/>
-      <c r="L12" s="200"/>
-      <c r="M12" s="215"/>
+      <c r="J12" s="342"/>
+      <c r="K12" s="342"/>
+      <c r="L12" s="342"/>
+      <c r="M12" s="343"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="438"/>
-      <c r="B13" s="212"/>
-      <c r="C13" s="212"/>
-      <c r="D13" s="212"/>
-      <c r="E13" s="10">
-        <v>65</v>
-      </c>
-      <c r="F13" s="297">
-        <v>65</v>
-      </c>
-      <c r="G13" s="298"/>
+      <c r="A13" s="421"/>
+      <c r="B13" s="339"/>
+      <c r="C13" s="339"/>
+      <c r="D13" s="339"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="165"/>
+      <c r="G13" s="167"/>
       <c r="H13" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I13" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J13" s="200"/>
-      <c r="K13" s="200"/>
-      <c r="L13" s="200"/>
-      <c r="M13" s="215"/>
+      <c r="J13" s="342"/>
+      <c r="K13" s="342"/>
+      <c r="L13" s="342"/>
+      <c r="M13" s="343"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="438"/>
-      <c r="B14" s="212"/>
-      <c r="C14" s="212"/>
-      <c r="D14" s="212"/>
-      <c r="E14" s="10">
-        <v>70</v>
-      </c>
-      <c r="F14" s="297">
-        <v>70</v>
-      </c>
-      <c r="G14" s="298"/>
+      <c r="A14" s="421"/>
+      <c r="B14" s="339"/>
+      <c r="C14" s="339"/>
+      <c r="D14" s="339"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="165"/>
+      <c r="G14" s="167"/>
       <c r="H14" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I14" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J14" s="200"/>
-      <c r="K14" s="200"/>
-      <c r="L14" s="200"/>
-      <c r="M14" s="215"/>
+      <c r="J14" s="342"/>
+      <c r="K14" s="342"/>
+      <c r="L14" s="342"/>
+      <c r="M14" s="343"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="438"/>
-      <c r="B15" s="212"/>
-      <c r="C15" s="212"/>
-      <c r="D15" s="212"/>
-      <c r="E15" s="10">
-        <v>55</v>
-      </c>
-      <c r="F15" s="297">
-        <v>55</v>
-      </c>
-      <c r="G15" s="298"/>
+      <c r="A15" s="421"/>
+      <c r="B15" s="339"/>
+      <c r="C15" s="339"/>
+      <c r="D15" s="339"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="165"/>
+      <c r="G15" s="167"/>
       <c r="H15" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I15" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J15" s="200"/>
-      <c r="K15" s="200"/>
-      <c r="L15" s="200"/>
-      <c r="M15" s="215"/>
+      <c r="J15" s="342"/>
+      <c r="K15" s="342"/>
+      <c r="L15" s="342"/>
+      <c r="M15" s="343"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="438"/>
-      <c r="B16" s="212"/>
-      <c r="C16" s="212"/>
-      <c r="D16" s="212"/>
-      <c r="E16" s="10">
-        <v>54</v>
-      </c>
-      <c r="F16" s="297">
-        <v>54</v>
-      </c>
-      <c r="G16" s="298"/>
+      <c r="A16" s="421"/>
+      <c r="B16" s="339"/>
+      <c r="C16" s="339"/>
+      <c r="D16" s="339"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="165"/>
+      <c r="G16" s="167"/>
       <c r="H16" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I16" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J16" s="200"/>
-      <c r="K16" s="200"/>
-      <c r="L16" s="200"/>
-      <c r="M16" s="215"/>
+      <c r="J16" s="342"/>
+      <c r="K16" s="342"/>
+      <c r="L16" s="342"/>
+      <c r="M16" s="343"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="438"/>
-      <c r="B17" s="212"/>
-      <c r="C17" s="212"/>
-      <c r="D17" s="212"/>
-      <c r="E17" s="10">
-        <v>76</v>
-      </c>
-      <c r="F17" s="297">
-        <v>76</v>
-      </c>
-      <c r="G17" s="298"/>
+      <c r="A17" s="421"/>
+      <c r="B17" s="339"/>
+      <c r="C17" s="339"/>
+      <c r="D17" s="339"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="165"/>
+      <c r="G17" s="167"/>
       <c r="H17" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I17" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J17" s="200"/>
-      <c r="K17" s="200"/>
-      <c r="L17" s="200"/>
-      <c r="M17" s="215"/>
+      <c r="J17" s="342"/>
+      <c r="K17" s="342"/>
+      <c r="L17" s="342"/>
+      <c r="M17" s="343"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="438"/>
-      <c r="B18" s="212"/>
-      <c r="C18" s="212"/>
-      <c r="D18" s="212"/>
-      <c r="E18" s="10">
-        <v>76</v>
-      </c>
-      <c r="F18" s="297">
-        <v>76</v>
-      </c>
-      <c r="G18" s="298"/>
+      <c r="A18" s="421"/>
+      <c r="B18" s="339"/>
+      <c r="C18" s="339"/>
+      <c r="D18" s="339"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="165"/>
+      <c r="G18" s="167"/>
       <c r="H18" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I18" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J18" s="200"/>
-      <c r="K18" s="200"/>
-      <c r="L18" s="200"/>
-      <c r="M18" s="215"/>
+      <c r="J18" s="342"/>
+      <c r="K18" s="342"/>
+      <c r="L18" s="342"/>
+      <c r="M18" s="343"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="438"/>
-      <c r="B19" s="212"/>
-      <c r="C19" s="212"/>
-      <c r="D19" s="212"/>
-      <c r="E19" s="10">
-        <v>65</v>
-      </c>
-      <c r="F19" s="297">
-        <v>65</v>
-      </c>
-      <c r="G19" s="298"/>
+      <c r="A19" s="421"/>
+      <c r="B19" s="339"/>
+      <c r="C19" s="339"/>
+      <c r="D19" s="339"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="165"/>
+      <c r="G19" s="167"/>
       <c r="H19" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I19" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J19" s="200"/>
-      <c r="K19" s="200"/>
-      <c r="L19" s="200"/>
-      <c r="M19" s="215"/>
+      <c r="J19" s="342"/>
+      <c r="K19" s="342"/>
+      <c r="L19" s="342"/>
+      <c r="M19" s="343"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="438"/>
-      <c r="B20" s="212"/>
-      <c r="C20" s="212"/>
-      <c r="D20" s="212"/>
-      <c r="E20" s="10">
-        <v>56</v>
-      </c>
-      <c r="F20" s="297">
-        <v>56</v>
-      </c>
-      <c r="G20" s="298"/>
+      <c r="A20" s="421"/>
+      <c r="B20" s="339"/>
+      <c r="C20" s="339"/>
+      <c r="D20" s="339"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="165"/>
+      <c r="G20" s="167"/>
       <c r="H20" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I20" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J20" s="200"/>
-      <c r="K20" s="200"/>
-      <c r="L20" s="200"/>
-      <c r="M20" s="215"/>
+      <c r="J20" s="342"/>
+      <c r="K20" s="342"/>
+      <c r="L20" s="342"/>
+      <c r="M20" s="343"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="438"/>
-      <c r="B21" s="212"/>
-      <c r="C21" s="212"/>
-      <c r="D21" s="212"/>
-      <c r="E21" s="10">
-        <v>83</v>
-      </c>
-      <c r="F21" s="297">
-        <v>83</v>
-      </c>
-      <c r="G21" s="298"/>
+      <c r="A21" s="421"/>
+      <c r="B21" s="339"/>
+      <c r="C21" s="339"/>
+      <c r="D21" s="339"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="165"/>
+      <c r="G21" s="167"/>
       <c r="H21" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I21" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J21" s="200"/>
-      <c r="K21" s="200"/>
-      <c r="L21" s="200"/>
-      <c r="M21" s="215"/>
+      <c r="J21" s="342"/>
+      <c r="K21" s="342"/>
+      <c r="L21" s="342"/>
+      <c r="M21" s="343"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="438"/>
-      <c r="B22" s="212"/>
-      <c r="C22" s="212"/>
-      <c r="D22" s="212"/>
-      <c r="E22" s="10">
-        <v>27</v>
-      </c>
-      <c r="F22" s="297">
-        <v>27</v>
-      </c>
-      <c r="G22" s="298"/>
+      <c r="A22" s="421"/>
+      <c r="B22" s="339"/>
+      <c r="C22" s="339"/>
+      <c r="D22" s="339"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="165"/>
+      <c r="G22" s="167"/>
       <c r="H22" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I22" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="200"/>
-      <c r="K22" s="200"/>
-      <c r="L22" s="200"/>
-      <c r="M22" s="215"/>
+      <c r="J22" s="342"/>
+      <c r="K22" s="342"/>
+      <c r="L22" s="342"/>
+      <c r="M22" s="343"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="438"/>
-      <c r="B23" s="212"/>
-      <c r="C23" s="212"/>
-      <c r="D23" s="212"/>
-      <c r="E23" s="10">
-        <v>16</v>
-      </c>
-      <c r="F23" s="297">
-        <v>16</v>
-      </c>
-      <c r="G23" s="298"/>
+      <c r="A23" s="421"/>
+      <c r="B23" s="339"/>
+      <c r="C23" s="339"/>
+      <c r="D23" s="339"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="165"/>
+      <c r="G23" s="167"/>
       <c r="H23" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I23" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="200"/>
-      <c r="K23" s="200"/>
-      <c r="L23" s="200"/>
-      <c r="M23" s="215"/>
+      <c r="J23" s="342"/>
+      <c r="K23" s="342"/>
+      <c r="L23" s="342"/>
+      <c r="M23" s="343"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="438"/>
-      <c r="B24" s="212"/>
-      <c r="C24" s="212"/>
-      <c r="D24" s="212"/>
-      <c r="E24" s="10">
-        <v>26</v>
-      </c>
-      <c r="F24" s="297">
-        <v>26</v>
-      </c>
-      <c r="G24" s="298"/>
+      <c r="A24" s="421"/>
+      <c r="B24" s="339"/>
+      <c r="C24" s="339"/>
+      <c r="D24" s="339"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="165"/>
+      <c r="G24" s="167"/>
       <c r="H24" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I24" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="200"/>
-      <c r="K24" s="200"/>
-      <c r="L24" s="200"/>
-      <c r="M24" s="215"/>
+      <c r="J24" s="342"/>
+      <c r="K24" s="342"/>
+      <c r="L24" s="342"/>
+      <c r="M24" s="343"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="438"/>
-      <c r="B25" s="212"/>
-      <c r="C25" s="212"/>
-      <c r="D25" s="212"/>
-      <c r="E25" s="10">
-        <v>16</v>
-      </c>
-      <c r="F25" s="297">
-        <v>16</v>
-      </c>
-      <c r="G25" s="298"/>
+      <c r="A25" s="421"/>
+      <c r="B25" s="339"/>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="165"/>
+      <c r="G25" s="167"/>
       <c r="H25" s="108" t="s">
         <v>54</v>
       </c>
       <c r="I25" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="200"/>
-      <c r="K25" s="200"/>
-      <c r="L25" s="200"/>
-      <c r="M25" s="215"/>
+      <c r="J25" s="342"/>
+      <c r="K25" s="342"/>
+      <c r="L25" s="342"/>
+      <c r="M25" s="343"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="293"/>
-      <c r="B26" s="294"/>
-      <c r="C26" s="294"/>
-      <c r="D26" s="294"/>
+      <c r="A26" s="422"/>
+      <c r="B26" s="423"/>
+      <c r="C26" s="423"/>
+      <c r="D26" s="423"/>
       <c r="E26" s="13"/>
-      <c r="F26" s="200"/>
-      <c r="G26" s="200"/>
+      <c r="F26" s="342"/>
+      <c r="G26" s="342"/>
       <c r="H26" s="13"/>
       <c r="I26" s="13"/>
-      <c r="J26" s="200"/>
-      <c r="K26" s="200"/>
-      <c r="L26" s="200"/>
-      <c r="M26" s="215"/>
+      <c r="J26" s="342"/>
+      <c r="K26" s="342"/>
+      <c r="L26" s="342"/>
+      <c r="M26" s="343"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="293"/>
-      <c r="B27" s="294"/>
-      <c r="C27" s="294"/>
-      <c r="D27" s="294"/>
+      <c r="A27" s="422"/>
+      <c r="B27" s="423"/>
+      <c r="C27" s="423"/>
+      <c r="D27" s="423"/>
       <c r="E27" s="13"/>
-      <c r="F27" s="200"/>
-      <c r="G27" s="200"/>
+      <c r="F27" s="342"/>
+      <c r="G27" s="342"/>
       <c r="H27" s="13"/>
       <c r="I27" s="13"/>
-      <c r="J27" s="200"/>
-      <c r="K27" s="200"/>
-      <c r="L27" s="200"/>
-      <c r="M27" s="215"/>
+      <c r="J27" s="342"/>
+      <c r="K27" s="342"/>
+      <c r="L27" s="342"/>
+      <c r="M27" s="343"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="293"/>
-      <c r="B28" s="294"/>
-      <c r="C28" s="294"/>
-      <c r="D28" s="294"/>
+      <c r="A28" s="422"/>
+      <c r="B28" s="423"/>
+      <c r="C28" s="423"/>
+      <c r="D28" s="423"/>
       <c r="E28" s="13"/>
-      <c r="F28" s="200"/>
-      <c r="G28" s="200"/>
+      <c r="F28" s="342"/>
+      <c r="G28" s="342"/>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
-      <c r="J28" s="200"/>
-      <c r="K28" s="200"/>
-      <c r="L28" s="200"/>
-      <c r="M28" s="215"/>
+      <c r="J28" s="342"/>
+      <c r="K28" s="342"/>
+      <c r="L28" s="342"/>
+      <c r="M28" s="343"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="293"/>
-      <c r="B29" s="294"/>
-      <c r="C29" s="294"/>
-      <c r="D29" s="294"/>
+      <c r="A29" s="422"/>
+      <c r="B29" s="423"/>
+      <c r="C29" s="423"/>
+      <c r="D29" s="423"/>
       <c r="E29" s="13"/>
-      <c r="F29" s="200"/>
-      <c r="G29" s="200"/>
+      <c r="F29" s="342"/>
+      <c r="G29" s="342"/>
       <c r="H29" s="13"/>
       <c r="I29" s="13"/>
-      <c r="J29" s="200"/>
-      <c r="K29" s="200"/>
-      <c r="L29" s="200"/>
-      <c r="M29" s="215"/>
+      <c r="J29" s="342"/>
+      <c r="K29" s="342"/>
+      <c r="L29" s="342"/>
+      <c r="M29" s="343"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="293"/>
-      <c r="B30" s="294"/>
-      <c r="C30" s="294"/>
-      <c r="D30" s="294"/>
+      <c r="A30" s="422"/>
+      <c r="B30" s="423"/>
+      <c r="C30" s="423"/>
+      <c r="D30" s="423"/>
       <c r="E30" s="13"/>
-      <c r="F30" s="200"/>
-      <c r="G30" s="200"/>
+      <c r="F30" s="342"/>
+      <c r="G30" s="342"/>
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
-      <c r="J30" s="200"/>
-      <c r="K30" s="200"/>
-      <c r="L30" s="200"/>
-      <c r="M30" s="215"/>
+      <c r="J30" s="342"/>
+      <c r="K30" s="342"/>
+      <c r="L30" s="342"/>
+      <c r="M30" s="343"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="293"/>
-      <c r="B31" s="294"/>
-      <c r="C31" s="294"/>
-      <c r="D31" s="294"/>
+      <c r="A31" s="422"/>
+      <c r="B31" s="423"/>
+      <c r="C31" s="423"/>
+      <c r="D31" s="423"/>
       <c r="E31" s="13"/>
-      <c r="F31" s="200"/>
-      <c r="G31" s="200"/>
+      <c r="F31" s="342"/>
+      <c r="G31" s="342"/>
       <c r="H31" s="13"/>
       <c r="I31" s="13"/>
-      <c r="J31" s="200"/>
-      <c r="K31" s="200"/>
-      <c r="L31" s="200"/>
-      <c r="M31" s="215"/>
+      <c r="J31" s="342"/>
+      <c r="K31" s="342"/>
+      <c r="L31" s="342"/>
+      <c r="M31" s="343"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="293"/>
-      <c r="B32" s="294"/>
-      <c r="C32" s="294"/>
-      <c r="D32" s="294"/>
+      <c r="A32" s="422"/>
+      <c r="B32" s="423"/>
+      <c r="C32" s="423"/>
+      <c r="D32" s="423"/>
       <c r="E32" s="13"/>
-      <c r="F32" s="200"/>
-      <c r="G32" s="200"/>
+      <c r="F32" s="342"/>
+      <c r="G32" s="342"/>
       <c r="H32" s="13"/>
       <c r="I32" s="13"/>
-      <c r="J32" s="200"/>
-      <c r="K32" s="200"/>
-      <c r="L32" s="200"/>
-      <c r="M32" s="215"/>
+      <c r="J32" s="342"/>
+      <c r="K32" s="342"/>
+      <c r="L32" s="342"/>
+      <c r="M32" s="343"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A33" s="293"/>
-      <c r="B33" s="294"/>
-      <c r="C33" s="294"/>
-      <c r="D33" s="294"/>
+      <c r="A33" s="422"/>
+      <c r="B33" s="423"/>
+      <c r="C33" s="423"/>
+      <c r="D33" s="423"/>
       <c r="E33" s="13"/>
-      <c r="F33" s="200"/>
-      <c r="G33" s="200"/>
+      <c r="F33" s="342"/>
+      <c r="G33" s="342"/>
       <c r="H33" s="13"/>
       <c r="I33" s="13"/>
-      <c r="J33" s="200"/>
-      <c r="K33" s="200"/>
-      <c r="L33" s="200"/>
-      <c r="M33" s="215"/>
+      <c r="J33" s="342"/>
+      <c r="K33" s="342"/>
+      <c r="L33" s="342"/>
+      <c r="M33" s="343"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A34" s="293"/>
-      <c r="B34" s="294"/>
-      <c r="C34" s="294"/>
-      <c r="D34" s="294"/>
+      <c r="A34" s="422"/>
+      <c r="B34" s="423"/>
+      <c r="C34" s="423"/>
+      <c r="D34" s="423"/>
       <c r="E34" s="13"/>
-      <c r="F34" s="200"/>
-      <c r="G34" s="200"/>
+      <c r="F34" s="342"/>
+      <c r="G34" s="342"/>
       <c r="H34" s="13"/>
       <c r="I34" s="13"/>
-      <c r="J34" s="200"/>
-      <c r="K34" s="200"/>
-      <c r="L34" s="200"/>
-      <c r="M34" s="215"/>
+      <c r="J34" s="342"/>
+      <c r="K34" s="342"/>
+      <c r="L34" s="342"/>
+      <c r="M34" s="343"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35" s="293"/>
-      <c r="B35" s="294"/>
-      <c r="C35" s="294"/>
-      <c r="D35" s="294"/>
+      <c r="A35" s="422"/>
+      <c r="B35" s="423"/>
+      <c r="C35" s="423"/>
+      <c r="D35" s="423"/>
       <c r="E35" s="13"/>
-      <c r="F35" s="200"/>
-      <c r="G35" s="200"/>
+      <c r="F35" s="342"/>
+      <c r="G35" s="342"/>
       <c r="H35" s="13"/>
       <c r="I35" s="13"/>
-      <c r="J35" s="200"/>
-      <c r="K35" s="200"/>
-      <c r="L35" s="200"/>
-      <c r="M35" s="215"/>
+      <c r="J35" s="342"/>
+      <c r="K35" s="342"/>
+      <c r="L35" s="342"/>
+      <c r="M35" s="343"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A36" s="293"/>
-      <c r="B36" s="294"/>
-      <c r="C36" s="294"/>
-      <c r="D36" s="294"/>
+      <c r="A36" s="422"/>
+      <c r="B36" s="423"/>
+      <c r="C36" s="423"/>
+      <c r="D36" s="423"/>
       <c r="E36" s="13"/>
-      <c r="F36" s="200"/>
-      <c r="G36" s="200"/>
+      <c r="F36" s="342"/>
+      <c r="G36" s="342"/>
       <c r="H36" s="13"/>
       <c r="I36" s="13"/>
-      <c r="J36" s="200"/>
-      <c r="K36" s="200"/>
-      <c r="L36" s="200"/>
-      <c r="M36" s="215"/>
+      <c r="J36" s="342"/>
+      <c r="K36" s="342"/>
+      <c r="L36" s="342"/>
+      <c r="M36" s="343"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A37" s="293"/>
-      <c r="B37" s="294"/>
-      <c r="C37" s="294"/>
-      <c r="D37" s="294"/>
+      <c r="A37" s="422"/>
+      <c r="B37" s="423"/>
+      <c r="C37" s="423"/>
+      <c r="D37" s="423"/>
       <c r="E37" s="13"/>
-      <c r="F37" s="200"/>
-      <c r="G37" s="200"/>
+      <c r="F37" s="342"/>
+      <c r="G37" s="342"/>
       <c r="H37" s="13"/>
       <c r="I37" s="13"/>
-      <c r="J37" s="200"/>
-      <c r="K37" s="200"/>
-      <c r="L37" s="200"/>
-      <c r="M37" s="215"/>
+      <c r="J37" s="342"/>
+      <c r="K37" s="342"/>
+      <c r="L37" s="342"/>
+      <c r="M37" s="343"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A38" s="293"/>
-      <c r="B38" s="294"/>
-      <c r="C38" s="294"/>
-      <c r="D38" s="294"/>
+      <c r="A38" s="422"/>
+      <c r="B38" s="423"/>
+      <c r="C38" s="423"/>
+      <c r="D38" s="423"/>
       <c r="E38" s="13"/>
-      <c r="F38" s="200"/>
-      <c r="G38" s="200"/>
+      <c r="F38" s="342"/>
+      <c r="G38" s="342"/>
       <c r="H38" s="13"/>
       <c r="I38" s="13"/>
-      <c r="J38" s="200"/>
-      <c r="K38" s="200"/>
-      <c r="L38" s="200"/>
-      <c r="M38" s="215"/>
+      <c r="J38" s="342"/>
+      <c r="K38" s="342"/>
+      <c r="L38" s="342"/>
+      <c r="M38" s="343"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A39" s="293"/>
-      <c r="B39" s="294"/>
-      <c r="C39" s="294"/>
-      <c r="D39" s="294"/>
+      <c r="A39" s="422"/>
+      <c r="B39" s="423"/>
+      <c r="C39" s="423"/>
+      <c r="D39" s="423"/>
       <c r="E39" s="13"/>
-      <c r="F39" s="200"/>
-      <c r="G39" s="200"/>
+      <c r="F39" s="342"/>
+      <c r="G39" s="342"/>
       <c r="H39" s="13"/>
       <c r="I39" s="13"/>
-      <c r="J39" s="200"/>
-      <c r="K39" s="200"/>
-      <c r="L39" s="200"/>
-      <c r="M39" s="215"/>
+      <c r="J39" s="342"/>
+      <c r="K39" s="342"/>
+      <c r="L39" s="342"/>
+      <c r="M39" s="343"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A40" s="293"/>
-      <c r="B40" s="294"/>
-      <c r="C40" s="294"/>
-      <c r="D40" s="294"/>
+      <c r="A40" s="422"/>
+      <c r="B40" s="423"/>
+      <c r="C40" s="423"/>
+      <c r="D40" s="423"/>
       <c r="E40" s="13"/>
-      <c r="F40" s="200"/>
-      <c r="G40" s="200"/>
+      <c r="F40" s="342"/>
+      <c r="G40" s="342"/>
       <c r="H40" s="13"/>
       <c r="I40" s="13"/>
-      <c r="J40" s="200"/>
-      <c r="K40" s="200"/>
-      <c r="L40" s="200"/>
-      <c r="M40" s="215"/>
+      <c r="J40" s="342"/>
+      <c r="K40" s="342"/>
+      <c r="L40" s="342"/>
+      <c r="M40" s="343"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A41" s="293"/>
-      <c r="B41" s="294"/>
-      <c r="C41" s="294"/>
-      <c r="D41" s="294"/>
+      <c r="A41" s="422"/>
+      <c r="B41" s="423"/>
+      <c r="C41" s="423"/>
+      <c r="D41" s="423"/>
       <c r="E41" s="13"/>
-      <c r="F41" s="200"/>
-      <c r="G41" s="200"/>
+      <c r="F41" s="342"/>
+      <c r="G41" s="342"/>
       <c r="H41" s="13"/>
       <c r="I41" s="13"/>
-      <c r="J41" s="200"/>
-      <c r="K41" s="200"/>
-      <c r="L41" s="200"/>
-      <c r="M41" s="215"/>
+      <c r="J41" s="342"/>
+      <c r="K41" s="342"/>
+      <c r="L41" s="342"/>
+      <c r="M41" s="343"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A42" s="293"/>
-      <c r="B42" s="294"/>
-      <c r="C42" s="294"/>
-      <c r="D42" s="294"/>
+      <c r="A42" s="422"/>
+      <c r="B42" s="423"/>
+      <c r="C42" s="423"/>
+      <c r="D42" s="423"/>
       <c r="E42" s="13"/>
-      <c r="F42" s="200"/>
-      <c r="G42" s="200"/>
+      <c r="F42" s="342"/>
+      <c r="G42" s="342"/>
       <c r="H42" s="13"/>
       <c r="I42" s="13"/>
-      <c r="J42" s="200"/>
-      <c r="K42" s="200"/>
-      <c r="L42" s="200"/>
-      <c r="M42" s="215"/>
+      <c r="J42" s="342"/>
+      <c r="K42" s="342"/>
+      <c r="L42" s="342"/>
+      <c r="M42" s="343"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A43" s="293"/>
-      <c r="B43" s="294"/>
-      <c r="C43" s="294"/>
-      <c r="D43" s="294"/>
+      <c r="A43" s="422"/>
+      <c r="B43" s="423"/>
+      <c r="C43" s="423"/>
+      <c r="D43" s="423"/>
       <c r="E43" s="13"/>
-      <c r="F43" s="200"/>
-      <c r="G43" s="200"/>
+      <c r="F43" s="342"/>
+      <c r="G43" s="342"/>
       <c r="H43" s="13"/>
       <c r="I43" s="13"/>
-      <c r="J43" s="200"/>
-      <c r="K43" s="200"/>
-      <c r="L43" s="200"/>
-      <c r="M43" s="215"/>
+      <c r="J43" s="342"/>
+      <c r="K43" s="342"/>
+      <c r="L43" s="342"/>
+      <c r="M43" s="343"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A44" s="293"/>
-      <c r="B44" s="294"/>
-      <c r="C44" s="294"/>
-      <c r="D44" s="294"/>
+      <c r="A44" s="422"/>
+      <c r="B44" s="423"/>
+      <c r="C44" s="423"/>
+      <c r="D44" s="423"/>
       <c r="E44" s="13"/>
-      <c r="F44" s="200"/>
-      <c r="G44" s="200"/>
+      <c r="F44" s="342"/>
+      <c r="G44" s="342"/>
       <c r="H44" s="13"/>
       <c r="I44" s="13"/>
-      <c r="J44" s="200"/>
-      <c r="K44" s="200"/>
-      <c r="L44" s="200"/>
-      <c r="M44" s="215"/>
+      <c r="J44" s="342"/>
+      <c r="K44" s="342"/>
+      <c r="L44" s="342"/>
+      <c r="M44" s="343"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A45" s="293"/>
-      <c r="B45" s="294"/>
-      <c r="C45" s="294"/>
-      <c r="D45" s="294"/>
+      <c r="A45" s="422"/>
+      <c r="B45" s="423"/>
+      <c r="C45" s="423"/>
+      <c r="D45" s="423"/>
       <c r="E45" s="13"/>
-      <c r="F45" s="200"/>
-      <c r="G45" s="200"/>
+      <c r="F45" s="342"/>
+      <c r="G45" s="342"/>
       <c r="H45" s="13"/>
       <c r="I45" s="13"/>
-      <c r="J45" s="200"/>
-      <c r="K45" s="200"/>
-      <c r="L45" s="200"/>
-      <c r="M45" s="215"/>
+      <c r="J45" s="342"/>
+      <c r="K45" s="342"/>
+      <c r="L45" s="342"/>
+      <c r="M45" s="343"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A46" s="293"/>
-      <c r="B46" s="294"/>
-      <c r="C46" s="294"/>
-      <c r="D46" s="294"/>
+      <c r="A46" s="422"/>
+      <c r="B46" s="423"/>
+      <c r="C46" s="423"/>
+      <c r="D46" s="423"/>
       <c r="E46" s="13"/>
-      <c r="F46" s="200"/>
-      <c r="G46" s="200"/>
+      <c r="F46" s="342"/>
+      <c r="G46" s="342"/>
       <c r="H46" s="13"/>
       <c r="I46" s="13"/>
-      <c r="J46" s="200"/>
-      <c r="K46" s="200"/>
-      <c r="L46" s="200"/>
-      <c r="M46" s="215"/>
+      <c r="J46" s="342"/>
+      <c r="K46" s="342"/>
+      <c r="L46" s="342"/>
+      <c r="M46" s="343"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A47" s="293"/>
-      <c r="B47" s="294"/>
-      <c r="C47" s="294"/>
-      <c r="D47" s="294"/>
+      <c r="A47" s="422"/>
+      <c r="B47" s="423"/>
+      <c r="C47" s="423"/>
+      <c r="D47" s="423"/>
       <c r="E47" s="13"/>
-      <c r="F47" s="200"/>
-      <c r="G47" s="200"/>
+      <c r="F47" s="342"/>
+      <c r="G47" s="342"/>
       <c r="H47" s="13"/>
       <c r="I47" s="13"/>
-      <c r="J47" s="200"/>
-      <c r="K47" s="200"/>
-      <c r="L47" s="200"/>
-      <c r="M47" s="215"/>
+      <c r="J47" s="342"/>
+      <c r="K47" s="342"/>
+      <c r="L47" s="342"/>
+      <c r="M47" s="343"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A48" s="293"/>
-      <c r="B48" s="294"/>
-      <c r="C48" s="294"/>
-      <c r="D48" s="294"/>
+      <c r="A48" s="422"/>
+      <c r="B48" s="423"/>
+      <c r="C48" s="423"/>
+      <c r="D48" s="423"/>
       <c r="E48" s="13"/>
-      <c r="F48" s="200"/>
-      <c r="G48" s="200"/>
+      <c r="F48" s="342"/>
+      <c r="G48" s="342"/>
       <c r="H48" s="13"/>
       <c r="I48" s="13"/>
-      <c r="J48" s="200"/>
-      <c r="K48" s="200"/>
-      <c r="L48" s="200"/>
-      <c r="M48" s="215"/>
+      <c r="J48" s="342"/>
+      <c r="K48" s="342"/>
+      <c r="L48" s="342"/>
+      <c r="M48" s="343"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A49" s="293"/>
-      <c r="B49" s="294"/>
-      <c r="C49" s="294"/>
-      <c r="D49" s="294"/>
+      <c r="A49" s="422"/>
+      <c r="B49" s="423"/>
+      <c r="C49" s="423"/>
+      <c r="D49" s="423"/>
       <c r="E49" s="13"/>
-      <c r="F49" s="200"/>
-      <c r="G49" s="200"/>
+      <c r="F49" s="342"/>
+      <c r="G49" s="342"/>
       <c r="H49" s="13"/>
       <c r="I49" s="13"/>
-      <c r="J49" s="200"/>
-      <c r="K49" s="200"/>
-      <c r="L49" s="200"/>
-      <c r="M49" s="215"/>
+      <c r="J49" s="342"/>
+      <c r="K49" s="342"/>
+      <c r="L49" s="342"/>
+      <c r="M49" s="343"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="197" t="s">
+      <c r="A50" s="349" t="s">
         <v>22</v>
       </c>
-      <c r="B50" s="198"/>
-      <c r="C50" s="198"/>
-      <c r="D50" s="198"/>
-      <c r="E50" s="109">
-        <f>SUM(E5:E25,MasterBOL!E22:E29)</f>
-        <v>1688</v>
-      </c>
-      <c r="F50" s="439">
-        <f>SUM(F5:F25,MasterBOL!F22:F29)</f>
-        <v>1688</v>
-      </c>
-      <c r="G50" s="440"/>
+      <c r="B50" s="350"/>
+      <c r="C50" s="350"/>
+      <c r="D50" s="350"/>
+      <c r="E50" s="109"/>
+      <c r="F50" s="436"/>
+      <c r="G50" s="437"/>
       <c r="H50" s="29"/>
       <c r="I50" s="30"/>
-      <c r="J50" s="295"/>
-      <c r="K50" s="295"/>
-      <c r="L50" s="295"/>
-      <c r="M50" s="296"/>
+      <c r="J50" s="438"/>
+      <c r="K50" s="438"/>
+      <c r="L50" s="438"/>
+      <c r="M50" s="439"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A51" s="281" t="s">
+      <c r="A51" s="424" t="s">
         <v>58</v>
       </c>
-      <c r="B51" s="282"/>
-      <c r="C51" s="282"/>
-      <c r="D51" s="282"/>
-      <c r="E51" s="282"/>
-      <c r="F51" s="282"/>
-      <c r="G51" s="282"/>
-      <c r="H51" s="282"/>
-      <c r="I51" s="282"/>
-      <c r="J51" s="282"/>
-      <c r="K51" s="282"/>
-      <c r="L51" s="282"/>
-      <c r="M51" s="283"/>
+      <c r="B51" s="425"/>
+      <c r="C51" s="425"/>
+      <c r="D51" s="425"/>
+      <c r="E51" s="425"/>
+      <c r="F51" s="425"/>
+      <c r="G51" s="425"/>
+      <c r="H51" s="425"/>
+      <c r="I51" s="425"/>
+      <c r="J51" s="425"/>
+      <c r="K51" s="425"/>
+      <c r="L51" s="425"/>
+      <c r="M51" s="426"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="284"/>
-      <c r="B52" s="285"/>
-      <c r="C52" s="285"/>
-      <c r="D52" s="285"/>
-      <c r="E52" s="285"/>
-      <c r="F52" s="285"/>
-      <c r="G52" s="285"/>
-      <c r="H52" s="285"/>
-      <c r="I52" s="285"/>
-      <c r="J52" s="285"/>
-      <c r="K52" s="285"/>
-      <c r="L52" s="285"/>
-      <c r="M52" s="286"/>
+      <c r="A52" s="427"/>
+      <c r="B52" s="428"/>
+      <c r="C52" s="428"/>
+      <c r="D52" s="428"/>
+      <c r="E52" s="428"/>
+      <c r="F52" s="428"/>
+      <c r="G52" s="428"/>
+      <c r="H52" s="428"/>
+      <c r="I52" s="428"/>
+      <c r="J52" s="428"/>
+      <c r="K52" s="428"/>
+      <c r="L52" s="428"/>
+      <c r="M52" s="429"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A53" s="287"/>
-      <c r="B53" s="288"/>
-      <c r="C53" s="288"/>
-      <c r="D53" s="288"/>
-      <c r="E53" s="288"/>
-      <c r="F53" s="288"/>
-      <c r="G53" s="288"/>
-      <c r="H53" s="288"/>
-      <c r="I53" s="288"/>
-      <c r="J53" s="288"/>
-      <c r="K53" s="288"/>
-      <c r="L53" s="288"/>
-      <c r="M53" s="289"/>
+      <c r="A53" s="430"/>
+      <c r="B53" s="431"/>
+      <c r="C53" s="431"/>
+      <c r="D53" s="431"/>
+      <c r="E53" s="431"/>
+      <c r="F53" s="431"/>
+      <c r="G53" s="431"/>
+      <c r="H53" s="431"/>
+      <c r="I53" s="431"/>
+      <c r="J53" s="431"/>
+      <c r="K53" s="431"/>
+      <c r="L53" s="431"/>
+      <c r="M53" s="432"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A54" s="287"/>
-      <c r="B54" s="288"/>
-      <c r="C54" s="288"/>
-      <c r="D54" s="288"/>
-      <c r="E54" s="288"/>
-      <c r="F54" s="288"/>
-      <c r="G54" s="288"/>
-      <c r="H54" s="288"/>
-      <c r="I54" s="288"/>
-      <c r="J54" s="288"/>
-      <c r="K54" s="288"/>
-      <c r="L54" s="288"/>
-      <c r="M54" s="289"/>
+      <c r="A54" s="430"/>
+      <c r="B54" s="431"/>
+      <c r="C54" s="431"/>
+      <c r="D54" s="431"/>
+      <c r="E54" s="431"/>
+      <c r="F54" s="431"/>
+      <c r="G54" s="431"/>
+      <c r="H54" s="431"/>
+      <c r="I54" s="431"/>
+      <c r="J54" s="431"/>
+      <c r="K54" s="431"/>
+      <c r="L54" s="431"/>
+      <c r="M54" s="432"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A55" s="287"/>
-      <c r="B55" s="288"/>
-      <c r="C55" s="288"/>
-      <c r="D55" s="288"/>
-      <c r="E55" s="288"/>
-      <c r="F55" s="288"/>
-      <c r="G55" s="288"/>
-      <c r="H55" s="288"/>
-      <c r="I55" s="288"/>
-      <c r="J55" s="288"/>
-      <c r="K55" s="288"/>
-      <c r="L55" s="288"/>
-      <c r="M55" s="289"/>
+      <c r="A55" s="430"/>
+      <c r="B55" s="431"/>
+      <c r="C55" s="431"/>
+      <c r="D55" s="431"/>
+      <c r="E55" s="431"/>
+      <c r="F55" s="431"/>
+      <c r="G55" s="431"/>
+      <c r="H55" s="431"/>
+      <c r="I55" s="431"/>
+      <c r="J55" s="431"/>
+      <c r="K55" s="431"/>
+      <c r="L55" s="431"/>
+      <c r="M55" s="432"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A56" s="287"/>
-      <c r="B56" s="288"/>
-      <c r="C56" s="288"/>
-      <c r="D56" s="288"/>
-      <c r="E56" s="288"/>
-      <c r="F56" s="288"/>
-      <c r="G56" s="288"/>
-      <c r="H56" s="288"/>
-      <c r="I56" s="288"/>
-      <c r="J56" s="288"/>
-      <c r="K56" s="288"/>
-      <c r="L56" s="288"/>
-      <c r="M56" s="289"/>
+      <c r="A56" s="430"/>
+      <c r="B56" s="431"/>
+      <c r="C56" s="431"/>
+      <c r="D56" s="431"/>
+      <c r="E56" s="431"/>
+      <c r="F56" s="431"/>
+      <c r="G56" s="431"/>
+      <c r="H56" s="431"/>
+      <c r="I56" s="431"/>
+      <c r="J56" s="431"/>
+      <c r="K56" s="431"/>
+      <c r="L56" s="431"/>
+      <c r="M56" s="432"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A57" s="287"/>
-      <c r="B57" s="288"/>
-      <c r="C57" s="288"/>
-      <c r="D57" s="288"/>
-      <c r="E57" s="288"/>
-      <c r="F57" s="288"/>
-      <c r="G57" s="288"/>
-      <c r="H57" s="288"/>
-      <c r="I57" s="288"/>
-      <c r="J57" s="288"/>
-      <c r="K57" s="288"/>
-      <c r="L57" s="288"/>
-      <c r="M57" s="289"/>
+      <c r="A57" s="430"/>
+      <c r="B57" s="431"/>
+      <c r="C57" s="431"/>
+      <c r="D57" s="431"/>
+      <c r="E57" s="431"/>
+      <c r="F57" s="431"/>
+      <c r="G57" s="431"/>
+      <c r="H57" s="431"/>
+      <c r="I57" s="431"/>
+      <c r="J57" s="431"/>
+      <c r="K57" s="431"/>
+      <c r="L57" s="431"/>
+      <c r="M57" s="432"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A58" s="287"/>
-      <c r="B58" s="288"/>
-      <c r="C58" s="288"/>
-      <c r="D58" s="288"/>
-      <c r="E58" s="288"/>
-      <c r="F58" s="288"/>
-      <c r="G58" s="288"/>
-      <c r="H58" s="288"/>
-      <c r="I58" s="288"/>
-      <c r="J58" s="288"/>
-      <c r="K58" s="288"/>
-      <c r="L58" s="288"/>
-      <c r="M58" s="289"/>
+      <c r="A58" s="430"/>
+      <c r="B58" s="431"/>
+      <c r="C58" s="431"/>
+      <c r="D58" s="431"/>
+      <c r="E58" s="431"/>
+      <c r="F58" s="431"/>
+      <c r="G58" s="431"/>
+      <c r="H58" s="431"/>
+      <c r="I58" s="431"/>
+      <c r="J58" s="431"/>
+      <c r="K58" s="431"/>
+      <c r="L58" s="431"/>
+      <c r="M58" s="432"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A59" s="287"/>
-      <c r="B59" s="288"/>
-      <c r="C59" s="288"/>
-      <c r="D59" s="288"/>
-      <c r="E59" s="288"/>
-      <c r="F59" s="288"/>
-      <c r="G59" s="288"/>
-      <c r="H59" s="288"/>
-      <c r="I59" s="288"/>
-      <c r="J59" s="288"/>
-      <c r="K59" s="288"/>
-      <c r="L59" s="288"/>
-      <c r="M59" s="289"/>
+      <c r="A59" s="430"/>
+      <c r="B59" s="431"/>
+      <c r="C59" s="431"/>
+      <c r="D59" s="431"/>
+      <c r="E59" s="431"/>
+      <c r="F59" s="431"/>
+      <c r="G59" s="431"/>
+      <c r="H59" s="431"/>
+      <c r="I59" s="431"/>
+      <c r="J59" s="431"/>
+      <c r="K59" s="431"/>
+      <c r="L59" s="431"/>
+      <c r="M59" s="432"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A60" s="290"/>
-      <c r="B60" s="291"/>
-      <c r="C60" s="291"/>
-      <c r="D60" s="291"/>
-      <c r="E60" s="291"/>
-      <c r="F60" s="291"/>
-      <c r="G60" s="291"/>
-      <c r="H60" s="291"/>
-      <c r="I60" s="291"/>
-      <c r="J60" s="291"/>
-      <c r="K60" s="291"/>
-      <c r="L60" s="291"/>
-      <c r="M60" s="292"/>
+      <c r="A60" s="433"/>
+      <c r="B60" s="434"/>
+      <c r="C60" s="434"/>
+      <c r="D60" s="434"/>
+      <c r="E60" s="434"/>
+      <c r="F60" s="434"/>
+      <c r="G60" s="434"/>
+      <c r="H60" s="434"/>
+      <c r="I60" s="434"/>
+      <c r="J60" s="434"/>
+      <c r="K60" s="434"/>
+      <c r="L60" s="434"/>
+      <c r="M60" s="435"/>
     </row>
     <row r="61" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="28"/>
@@ -8087,143 +7912,7 @@
       <c r="J61" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="150">
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="J5:M5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="J6:M6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:G4"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:M4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="J9:M9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="J10:M10"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="J11:M11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="J12:M12"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="J18:M18"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="J20:M20"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="J42:M42"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="J39:M39"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="J40:M40"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="J45:M45"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="J46:M46"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="J44:M44"/>
+  <mergeCells count="149">
     <mergeCell ref="A51:M51"/>
     <mergeCell ref="A52:M60"/>
     <mergeCell ref="A49:D49"/>
@@ -8238,6 +7927,141 @@
     <mergeCell ref="A48:D48"/>
     <mergeCell ref="F48:G48"/>
     <mergeCell ref="J48:M48"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="J46:M46"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="J44:M44"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="J42:M42"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="J40:M40"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="J10:M10"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="J5:M5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:G4"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:M4"/>
+    <mergeCell ref="H4:I4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.26" top="0.2" bottom="0.27" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8262,36 +8086,34 @@
   <sheetData>
     <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="40" t="s">
-        <v>238</v>
-      </c>
-      <c r="B1" s="303">
-        <v>45877</v>
-      </c>
-      <c r="C1" s="303"/>
+        <v>233</v>
+      </c>
+      <c r="B1" s="245"/>
+      <c r="C1" s="245"/>
       <c r="F1" s="41"/>
       <c r="G1" s="41" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H1" s="41"/>
       <c r="I1" s="41"/>
       <c r="J1" s="42"/>
       <c r="K1" s="42"/>
-      <c r="L1" s="310" t="s">
-        <v>72</v>
-      </c>
-      <c r="M1" s="311"/>
+      <c r="L1" s="250" t="s">
+        <v>68</v>
+      </c>
+      <c r="M1" s="251"/>
     </row>
     <row r="2" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="307" t="s">
+      <c r="A2" s="247" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="308"/>
-      <c r="C2" s="308"/>
-      <c r="D2" s="308"/>
-      <c r="E2" s="308"/>
-      <c r="F2" s="308"/>
-      <c r="G2" s="308"/>
-      <c r="H2" s="309"/>
+      <c r="B2" s="248"/>
+      <c r="C2" s="248"/>
+      <c r="D2" s="248"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="248"/>
+      <c r="G2" s="248"/>
+      <c r="H2" s="249"/>
       <c r="I2" s="43"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44"/>
@@ -8299,18 +8121,18 @@
       <c r="M2" s="45"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="317" t="s">
-        <v>66</v>
-      </c>
-      <c r="B3" s="318"/>
-      <c r="C3" s="318"/>
-      <c r="D3" s="318"/>
-      <c r="E3" s="318"/>
-      <c r="F3" s="318"/>
-      <c r="G3" s="318"/>
-      <c r="H3" s="319"/>
+      <c r="A3" s="211" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" s="212"/>
+      <c r="C3" s="212"/>
+      <c r="D3" s="212"/>
+      <c r="E3" s="212"/>
+      <c r="F3" s="212"/>
+      <c r="G3" s="212"/>
+      <c r="H3" s="213"/>
       <c r="I3" s="46" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J3" s="44"/>
       <c r="K3" s="47"/>
@@ -8318,77 +8140,74 @@
       <c r="M3" s="48"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="317" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="318"/>
-      <c r="C4" s="318"/>
-      <c r="D4" s="318"/>
-      <c r="E4" s="318"/>
-      <c r="F4" s="318"/>
-      <c r="G4" s="318"/>
-      <c r="H4" s="319"/>
-      <c r="I4" s="321"/>
-      <c r="J4" s="299"/>
-      <c r="K4" s="299"/>
-      <c r="L4" s="299"/>
-      <c r="M4" s="300"/>
+      <c r="A4" s="211" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="212"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="212"/>
+      <c r="E4" s="212"/>
+      <c r="F4" s="212"/>
+      <c r="G4" s="212"/>
+      <c r="H4" s="213"/>
+      <c r="I4" s="257"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
+      <c r="M4" s="242"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="317" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" s="318"/>
-      <c r="C5" s="318"/>
-      <c r="D5" s="318"/>
-      <c r="E5" s="318"/>
-      <c r="F5" s="318"/>
-      <c r="G5" s="318"/>
-      <c r="H5" s="319"/>
-      <c r="I5" s="321"/>
-      <c r="J5" s="299"/>
-      <c r="K5" s="299"/>
-      <c r="L5" s="299"/>
-      <c r="M5" s="300"/>
+      <c r="A5" s="211" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="212"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="212"/>
+      <c r="E5" s="212"/>
+      <c r="F5" s="212"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="213"/>
+      <c r="I5" s="257"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
+      <c r="M5" s="242"/>
     </row>
     <row r="6" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="315" t="s">
+      <c r="A6" s="255" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="316"/>
-      <c r="C6" s="316"/>
-      <c r="D6" s="316"/>
-      <c r="E6" s="316"/>
-      <c r="F6" s="320" t="s">
+      <c r="B6" s="210"/>
+      <c r="C6" s="210"/>
+      <c r="D6" s="210"/>
+      <c r="E6" s="210"/>
+      <c r="F6" s="256" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="320"/>
+      <c r="G6" s="256"/>
       <c r="H6" s="49"/>
-      <c r="I6" s="322"/>
-      <c r="J6" s="323"/>
-      <c r="K6" s="323"/>
-      <c r="L6" s="323"/>
-      <c r="M6" s="324"/>
+      <c r="I6" s="258"/>
+      <c r="J6" s="259"/>
+      <c r="K6" s="259"/>
+      <c r="L6" s="259"/>
+      <c r="M6" s="260"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="333" t="s">
+      <c r="A7" s="262" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="334"/>
-      <c r="C7" s="334"/>
-      <c r="D7" s="334"/>
-      <c r="E7" s="334"/>
-      <c r="F7" s="334"/>
-      <c r="G7" s="334"/>
-      <c r="H7" s="335"/>
+      <c r="B7" s="263"/>
+      <c r="C7" s="263"/>
+      <c r="D7" s="263"/>
+      <c r="E7" s="263"/>
+      <c r="F7" s="263"/>
+      <c r="G7" s="263"/>
+      <c r="H7" s="264"/>
       <c r="I7" s="50" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J7" s="51"/>
-      <c r="K7" s="52" t="str">
-        <f>ADDRESS!I1</f>
-        <v>CH Robinson</v>
-      </c>
+      <c r="K7" s="52"/>
       <c r="L7" s="51"/>
       <c r="M7" s="53"/>
     </row>
@@ -8396,162 +8215,144 @@
       <c r="A8" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="441" t="s">
-        <v>113</v>
-      </c>
+      <c r="B8" s="126"/>
       <c r="C8" s="55"/>
       <c r="D8" s="55"/>
-      <c r="E8" s="339" t="s">
+      <c r="E8" s="233" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="339"/>
-      <c r="G8" s="339"/>
-      <c r="H8" s="340"/>
-      <c r="I8" s="325" t="s">
+      <c r="F8" s="233"/>
+      <c r="G8" s="233"/>
+      <c r="H8" s="267"/>
+      <c r="I8" s="261" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="318"/>
-      <c r="K8" s="318"/>
-      <c r="L8" s="318"/>
-      <c r="M8" s="319"/>
+      <c r="J8" s="212"/>
+      <c r="K8" s="212"/>
+      <c r="L8" s="212"/>
+      <c r="M8" s="213"/>
     </row>
     <row r="9" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="B9" t="str">
-        <f>VLOOKUP(B8,ADDRESS!$A$2:$E$30,2,FALSE)</f>
-        <v>13790 Harvey Road</v>
-      </c>
       <c r="H9" s="57"/>
       <c r="I9" s="58" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="J9" s="59"/>
-      <c r="K9" s="59">
-        <f>ADDRESS!I3</f>
-        <v>10285609</v>
-      </c>
+      <c r="K9" s="59"/>
       <c r="L9" s="59"/>
       <c r="M9" s="49"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="60" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="372" t="str">
-        <f>CONCATENATE(VLOOKUP(B8,ADDRESS!$A$2:$E$30,3,FALSE),", ",VLOOKUP(B8,ADDRESS!$A$2:$E$30,4,FALSE)," ",VLOOKUP(B8,ADDRESS!$A$2:$E$30,5,FALSE))</f>
-        <v>TYLER, TX 75706</v>
-      </c>
-      <c r="D10" s="372"/>
-      <c r="E10" s="372"/>
-      <c r="F10" s="372"/>
-      <c r="G10" s="372"/>
+        <v>69</v>
+      </c>
+      <c r="C10" s="240"/>
+      <c r="D10" s="240"/>
+      <c r="E10" s="240"/>
+      <c r="F10" s="240"/>
+      <c r="G10" s="240"/>
       <c r="H10" s="57"/>
       <c r="I10" s="61" t="s">
-        <v>234</v>
-      </c>
-      <c r="J10" s="62" t="str">
-        <f>ADDRESS!I2</f>
-        <v>RBTW</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="J10" s="62"/>
       <c r="K10" s="62"/>
       <c r="L10" s="62"/>
       <c r="M10" s="63"/>
     </row>
     <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="341" t="s">
+      <c r="A11" s="209" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="316"/>
-      <c r="C11" s="316"/>
-      <c r="D11" s="316"/>
-      <c r="E11" s="316"/>
-      <c r="F11" s="320" t="s">
+      <c r="B11" s="210"/>
+      <c r="C11" s="210"/>
+      <c r="D11" s="210"/>
+      <c r="E11" s="210"/>
+      <c r="F11" s="256" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="320"/>
+      <c r="G11" s="256"/>
       <c r="H11" s="49"/>
-      <c r="I11" s="301" t="s">
-        <v>75</v>
-      </c>
-      <c r="J11" s="302"/>
-      <c r="K11" s="64">
-        <f>ADDRESS!I4</f>
-        <v>523953410</v>
-      </c>
+      <c r="I11" s="243" t="s">
+        <v>71</v>
+      </c>
+      <c r="J11" s="244"/>
+      <c r="K11" s="64"/>
       <c r="L11" s="64"/>
       <c r="M11" s="65"/>
     </row>
     <row r="12" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="326" t="s">
+      <c r="A12" s="179" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="327"/>
-      <c r="C12" s="327"/>
-      <c r="D12" s="327"/>
-      <c r="E12" s="327"/>
-      <c r="F12" s="327"/>
-      <c r="G12" s="327"/>
-      <c r="H12" s="328"/>
-      <c r="I12" s="321"/>
-      <c r="J12" s="299"/>
-      <c r="K12" s="299"/>
-      <c r="L12" s="299"/>
-      <c r="M12" s="300"/>
+      <c r="B12" s="180"/>
+      <c r="C12" s="180"/>
+      <c r="D12" s="180"/>
+      <c r="E12" s="180"/>
+      <c r="F12" s="180"/>
+      <c r="G12" s="180"/>
+      <c r="H12" s="181"/>
+      <c r="I12" s="257"/>
+      <c r="J12" s="241"/>
+      <c r="K12" s="241"/>
+      <c r="L12" s="241"/>
+      <c r="M12" s="242"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="312" t="s">
+      <c r="A13" s="252" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="313"/>
-      <c r="C13" s="313"/>
-      <c r="D13" s="313"/>
-      <c r="E13" s="313"/>
-      <c r="F13" s="313"/>
-      <c r="G13" s="313"/>
-      <c r="H13" s="314"/>
-      <c r="I13" s="321"/>
-      <c r="J13" s="299"/>
-      <c r="K13" s="299"/>
-      <c r="L13" s="299"/>
-      <c r="M13" s="300"/>
+      <c r="B13" s="253"/>
+      <c r="C13" s="253"/>
+      <c r="D13" s="253"/>
+      <c r="E13" s="253"/>
+      <c r="F13" s="253"/>
+      <c r="G13" s="253"/>
+      <c r="H13" s="254"/>
+      <c r="I13" s="257"/>
+      <c r="J13" s="241"/>
+      <c r="K13" s="241"/>
+      <c r="L13" s="241"/>
+      <c r="M13" s="242"/>
     </row>
     <row r="14" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="317" t="s">
+      <c r="A14" s="211" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="318"/>
-      <c r="C14" s="318"/>
-      <c r="D14" s="318"/>
-      <c r="E14" s="318"/>
-      <c r="F14" s="318"/>
-      <c r="G14" s="318"/>
-      <c r="H14" s="319"/>
-      <c r="I14" s="322"/>
-      <c r="J14" s="323"/>
-      <c r="K14" s="323"/>
-      <c r="L14" s="323"/>
-      <c r="M14" s="324"/>
+      <c r="B14" s="212"/>
+      <c r="C14" s="212"/>
+      <c r="D14" s="212"/>
+      <c r="E14" s="212"/>
+      <c r="F14" s="212"/>
+      <c r="G14" s="212"/>
+      <c r="H14" s="213"/>
+      <c r="I14" s="258"/>
+      <c r="J14" s="259"/>
+      <c r="K14" s="259"/>
+      <c r="L14" s="259"/>
+      <c r="M14" s="260"/>
     </row>
     <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="349" t="s">
+      <c r="A15" s="221" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="350"/>
-      <c r="C15" s="350"/>
-      <c r="D15" s="350"/>
-      <c r="E15" s="350"/>
-      <c r="F15" s="351"/>
-      <c r="G15" s="351"/>
-      <c r="H15" s="351"/>
-      <c r="I15" s="346" t="s">
+      <c r="B15" s="222"/>
+      <c r="C15" s="222"/>
+      <c r="D15" s="222"/>
+      <c r="E15" s="222"/>
+      <c r="F15" s="223"/>
+      <c r="G15" s="223"/>
+      <c r="H15" s="223"/>
+      <c r="I15" s="218" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="347"/>
-      <c r="K15" s="347"/>
-      <c r="L15" s="347"/>
-      <c r="M15" s="348"/>
+      <c r="J15" s="219"/>
+      <c r="K15" s="219"/>
+      <c r="L15" s="219"/>
+      <c r="M15" s="220"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="32"/>
@@ -8562,35 +8363,32 @@
       <c r="F16" s="33"/>
       <c r="G16" s="33"/>
       <c r="H16" s="34"/>
-      <c r="I16" s="363" t="s">
-        <v>61</v>
-      </c>
-      <c r="J16" s="364"/>
-      <c r="K16" s="364"/>
-      <c r="L16" s="364"/>
-      <c r="M16" s="365"/>
+      <c r="I16" s="234" t="s">
+        <v>234</v>
+      </c>
+      <c r="J16" s="235"/>
+      <c r="K16" s="235"/>
+      <c r="L16" s="235"/>
+      <c r="M16" s="236"/>
     </row>
     <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="35" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B17" s="36"/>
       <c r="C17" s="36"/>
       <c r="D17" s="36"/>
       <c r="E17" s="36"/>
-      <c r="F17" s="299">
-        <f>ADDRESS!I5</f>
-        <v>59642884</v>
-      </c>
-      <c r="G17" s="299"/>
-      <c r="H17" s="300"/>
-      <c r="I17" s="360"/>
-      <c r="J17" s="339"/>
-      <c r="K17" s="342" t="s">
+      <c r="F17" s="241"/>
+      <c r="G17" s="241"/>
+      <c r="H17" s="242"/>
+      <c r="I17" s="232"/>
+      <c r="J17" s="233"/>
+      <c r="K17" s="214" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="342"/>
-      <c r="M17" s="343"/>
+      <c r="L17" s="214"/>
+      <c r="M17" s="215"/>
     </row>
     <row r="18" spans="1:13" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="37"/>
@@ -8601,300 +8399,285 @@
       <c r="F18" s="38"/>
       <c r="G18" s="38"/>
       <c r="H18" s="39"/>
-      <c r="I18" s="361" t="s">
+      <c r="I18" s="127" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="362"/>
-      <c r="K18" s="344"/>
-      <c r="L18" s="344"/>
-      <c r="M18" s="345"/>
+      <c r="J18" s="128"/>
+      <c r="K18" s="216"/>
+      <c r="L18" s="216"/>
+      <c r="M18" s="217"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="366" t="s">
+      <c r="A19" s="182" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="367"/>
-      <c r="C19" s="367"/>
-      <c r="D19" s="367"/>
-      <c r="E19" s="367"/>
-      <c r="F19" s="367"/>
-      <c r="G19" s="367"/>
-      <c r="H19" s="367"/>
-      <c r="I19" s="367"/>
-      <c r="J19" s="367"/>
-      <c r="K19" s="367"/>
-      <c r="L19" s="367"/>
-      <c r="M19" s="368"/>
+      <c r="B19" s="183"/>
+      <c r="C19" s="183"/>
+      <c r="D19" s="183"/>
+      <c r="E19" s="183"/>
+      <c r="F19" s="183"/>
+      <c r="G19" s="183"/>
+      <c r="H19" s="183"/>
+      <c r="I19" s="183"/>
+      <c r="J19" s="183"/>
+      <c r="K19" s="183"/>
+      <c r="L19" s="183"/>
+      <c r="M19" s="184"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="369" t="s">
+      <c r="A20" s="237" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="370"/>
-      <c r="C20" s="370"/>
-      <c r="D20" s="370"/>
-      <c r="E20" s="370" t="s">
+      <c r="B20" s="238"/>
+      <c r="C20" s="238"/>
+      <c r="D20" s="238"/>
+      <c r="E20" s="238" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="370" t="s">
+      <c r="F20" s="238" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="370"/>
-      <c r="H20" s="358" t="s">
+      <c r="G20" s="238"/>
+      <c r="H20" s="230" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="359"/>
-      <c r="J20" s="352" t="s">
+      <c r="I20" s="231"/>
+      <c r="J20" s="224" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="353"/>
-      <c r="L20" s="353"/>
-      <c r="M20" s="354"/>
+      <c r="K20" s="225"/>
+      <c r="L20" s="225"/>
+      <c r="M20" s="226"/>
     </row>
     <row r="21" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="369"/>
-      <c r="B21" s="370"/>
-      <c r="C21" s="370"/>
-      <c r="D21" s="370"/>
-      <c r="E21" s="370"/>
-      <c r="F21" s="370"/>
-      <c r="G21" s="370"/>
-      <c r="H21" s="336" t="s">
+      <c r="A21" s="237"/>
+      <c r="B21" s="238"/>
+      <c r="C21" s="238"/>
+      <c r="D21" s="238"/>
+      <c r="E21" s="238"/>
+      <c r="F21" s="238"/>
+      <c r="G21" s="238"/>
+      <c r="H21" s="265" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="337"/>
-      <c r="J21" s="355"/>
-      <c r="K21" s="356"/>
-      <c r="L21" s="356"/>
-      <c r="M21" s="357"/>
+      <c r="I21" s="266"/>
+      <c r="J21" s="227"/>
+      <c r="K21" s="228"/>
+      <c r="L21" s="228"/>
+      <c r="M21" s="229"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="371" t="str">
-        <f>VLOOKUP(B8,'Customer Order Info'!$A$3:$D$31,2,FALSE)</f>
-        <v>0215-8880831-0578</v>
-      </c>
-      <c r="B22" s="332"/>
-      <c r="C22" s="332"/>
-      <c r="D22" s="297"/>
-      <c r="E22" s="10">
-        <f>VLOOKUP(A22,'Customer Order Info'!B3:D31,2,FALSE)</f>
-        <v>83</v>
-      </c>
-      <c r="F22" s="332">
-        <f>VLOOKUP(A22,'Customer Order Info'!B3:D31,3,FALSE)</f>
-        <v>83</v>
-      </c>
-      <c r="G22" s="332"/>
+      <c r="A22" s="239"/>
+      <c r="B22" s="188"/>
+      <c r="C22" s="188"/>
+      <c r="D22" s="165"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="188"/>
+      <c r="G22" s="188"/>
       <c r="H22" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="332"/>
-      <c r="K22" s="332"/>
-      <c r="L22" s="332"/>
-      <c r="M22" s="338"/>
+      <c r="J22" s="188"/>
+      <c r="K22" s="188"/>
+      <c r="L22" s="188"/>
+      <c r="M22" s="200"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="329"/>
-      <c r="B23" s="330"/>
-      <c r="C23" s="330"/>
-      <c r="D23" s="331"/>
+      <c r="A23" s="203"/>
+      <c r="B23" s="204"/>
+      <c r="C23" s="204"/>
+      <c r="D23" s="205"/>
       <c r="E23" s="10"/>
-      <c r="F23" s="332"/>
-      <c r="G23" s="332"/>
+      <c r="F23" s="188"/>
+      <c r="G23" s="188"/>
       <c r="H23" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="332"/>
-      <c r="K23" s="332"/>
-      <c r="L23" s="332"/>
-      <c r="M23" s="338"/>
+      <c r="J23" s="188"/>
+      <c r="K23" s="188"/>
+      <c r="L23" s="188"/>
+      <c r="M23" s="200"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="329"/>
-      <c r="B24" s="330"/>
-      <c r="C24" s="330"/>
-      <c r="D24" s="331"/>
+      <c r="A24" s="203"/>
+      <c r="B24" s="204"/>
+      <c r="C24" s="204"/>
+      <c r="D24" s="205"/>
       <c r="E24" s="10"/>
-      <c r="F24" s="332"/>
-      <c r="G24" s="332"/>
+      <c r="F24" s="188"/>
+      <c r="G24" s="188"/>
       <c r="H24" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="332"/>
-      <c r="K24" s="332"/>
-      <c r="L24" s="332"/>
-      <c r="M24" s="338"/>
+      <c r="J24" s="188"/>
+      <c r="K24" s="188"/>
+      <c r="L24" s="188"/>
+      <c r="M24" s="200"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="329"/>
-      <c r="B25" s="330"/>
-      <c r="C25" s="330"/>
-      <c r="D25" s="331"/>
+      <c r="A25" s="203"/>
+      <c r="B25" s="204"/>
+      <c r="C25" s="204"/>
+      <c r="D25" s="205"/>
       <c r="E25" s="10"/>
-      <c r="F25" s="332"/>
-      <c r="G25" s="332"/>
+      <c r="F25" s="188"/>
+      <c r="G25" s="188"/>
       <c r="H25" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="332"/>
-      <c r="K25" s="332"/>
-      <c r="L25" s="332"/>
-      <c r="M25" s="338"/>
+      <c r="J25" s="188"/>
+      <c r="K25" s="188"/>
+      <c r="L25" s="188"/>
+      <c r="M25" s="200"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="329"/>
-      <c r="B26" s="330"/>
-      <c r="C26" s="330"/>
-      <c r="D26" s="331"/>
+      <c r="A26" s="203"/>
+      <c r="B26" s="204"/>
+      <c r="C26" s="204"/>
+      <c r="D26" s="205"/>
       <c r="E26" s="10"/>
-      <c r="F26" s="332"/>
-      <c r="G26" s="332"/>
+      <c r="F26" s="188"/>
+      <c r="G26" s="188"/>
       <c r="H26" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="332"/>
-      <c r="K26" s="332"/>
-      <c r="L26" s="332"/>
-      <c r="M26" s="338"/>
+      <c r="J26" s="188"/>
+      <c r="K26" s="188"/>
+      <c r="L26" s="188"/>
+      <c r="M26" s="200"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="329"/>
-      <c r="B27" s="330"/>
-      <c r="C27" s="330"/>
-      <c r="D27" s="331"/>
+      <c r="A27" s="203"/>
+      <c r="B27" s="204"/>
+      <c r="C27" s="204"/>
+      <c r="D27" s="205"/>
       <c r="E27" s="10"/>
-      <c r="F27" s="332"/>
-      <c r="G27" s="332"/>
+      <c r="F27" s="188"/>
+      <c r="G27" s="188"/>
       <c r="H27" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J27" s="332"/>
-      <c r="K27" s="332"/>
-      <c r="L27" s="332"/>
-      <c r="M27" s="338"/>
+      <c r="J27" s="188"/>
+      <c r="K27" s="188"/>
+      <c r="L27" s="188"/>
+      <c r="M27" s="200"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="329"/>
-      <c r="B28" s="330"/>
-      <c r="C28" s="330"/>
-      <c r="D28" s="331"/>
+      <c r="A28" s="203"/>
+      <c r="B28" s="204"/>
+      <c r="C28" s="204"/>
+      <c r="D28" s="205"/>
       <c r="E28" s="10"/>
-      <c r="F28" s="332"/>
-      <c r="G28" s="332"/>
+      <c r="F28" s="188"/>
+      <c r="G28" s="188"/>
       <c r="H28" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J28" s="332"/>
-      <c r="K28" s="332"/>
-      <c r="L28" s="332"/>
-      <c r="M28" s="338"/>
+      <c r="J28" s="188"/>
+      <c r="K28" s="188"/>
+      <c r="L28" s="188"/>
+      <c r="M28" s="200"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="329"/>
-      <c r="B29" s="330"/>
-      <c r="C29" s="330"/>
-      <c r="D29" s="331"/>
+      <c r="A29" s="203"/>
+      <c r="B29" s="204"/>
+      <c r="C29" s="204"/>
+      <c r="D29" s="205"/>
       <c r="E29" s="10"/>
-      <c r="F29" s="332"/>
-      <c r="G29" s="332"/>
+      <c r="F29" s="188"/>
+      <c r="G29" s="188"/>
       <c r="H29" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J29" s="332"/>
-      <c r="K29" s="332"/>
-      <c r="L29" s="332"/>
-      <c r="M29" s="338"/>
+      <c r="J29" s="188"/>
+      <c r="K29" s="188"/>
+      <c r="L29" s="188"/>
+      <c r="M29" s="200"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="386" t="s">
+      <c r="A30" s="201" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="387"/>
-      <c r="C30" s="387"/>
-      <c r="D30" s="387"/>
-      <c r="E30" s="9">
-        <f>SUM(E22:E29)</f>
-        <v>83</v>
-      </c>
-      <c r="F30" s="375">
-        <f>SUM(F22:G29)</f>
-        <v>83</v>
-      </c>
-      <c r="G30" s="332"/>
-      <c r="H30" s="305"/>
-      <c r="I30" s="306"/>
-      <c r="J30" s="305"/>
-      <c r="K30" s="373"/>
-      <c r="L30" s="373"/>
-      <c r="M30" s="306"/>
+      <c r="B30" s="202"/>
+      <c r="C30" s="202"/>
+      <c r="D30" s="202"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="189"/>
+      <c r="G30" s="188"/>
+      <c r="H30" s="206"/>
+      <c r="I30" s="208"/>
+      <c r="J30" s="206"/>
+      <c r="K30" s="207"/>
+      <c r="L30" s="207"/>
+      <c r="M30" s="208"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="376" t="s">
+      <c r="A31" s="190" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="377"/>
-      <c r="C31" s="377"/>
-      <c r="D31" s="377"/>
-      <c r="E31" s="377"/>
-      <c r="F31" s="377"/>
-      <c r="G31" s="377"/>
-      <c r="H31" s="377"/>
-      <c r="I31" s="377"/>
-      <c r="J31" s="377"/>
-      <c r="K31" s="377"/>
-      <c r="L31" s="377"/>
-      <c r="M31" s="378"/>
+      <c r="B31" s="191"/>
+      <c r="C31" s="191"/>
+      <c r="D31" s="191"/>
+      <c r="E31" s="191"/>
+      <c r="F31" s="191"/>
+      <c r="G31" s="191"/>
+      <c r="H31" s="191"/>
+      <c r="I31" s="191"/>
+      <c r="J31" s="191"/>
+      <c r="K31" s="191"/>
+      <c r="L31" s="191"/>
+      <c r="M31" s="192"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="383" t="s">
+      <c r="A32" s="197" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="381"/>
-      <c r="C32" s="381" t="s">
+      <c r="B32" s="195"/>
+      <c r="C32" s="195" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="381"/>
-      <c r="E32" s="384" t="s">
+      <c r="D32" s="195"/>
+      <c r="E32" s="198" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="385" t="s">
+      <c r="F32" s="199" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="379" t="s">
+      <c r="G32" s="193" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="379"/>
-      <c r="I32" s="379"/>
-      <c r="J32" s="379"/>
-      <c r="K32" s="379"/>
-      <c r="L32" s="381" t="s">
+      <c r="H32" s="193"/>
+      <c r="I32" s="193"/>
+      <c r="J32" s="193"/>
+      <c r="K32" s="193"/>
+      <c r="L32" s="195" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="382"/>
+      <c r="M32" s="196"/>
     </row>
     <row r="33" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
@@ -8909,15 +8692,15 @@
       <c r="D33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="384"/>
-      <c r="F33" s="385"/>
-      <c r="G33" s="380" t="s">
+      <c r="E33" s="198"/>
+      <c r="F33" s="199"/>
+      <c r="G33" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="380"/>
-      <c r="I33" s="380"/>
-      <c r="J33" s="380"/>
-      <c r="K33" s="380"/>
+      <c r="H33" s="194"/>
+      <c r="I33" s="194"/>
+      <c r="J33" s="194"/>
+      <c r="K33" s="194"/>
       <c r="L33" s="2" t="s">
         <v>14</v>
       </c>
@@ -8926,32 +8709,19 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="67">
-        <f>E30</f>
-        <v>83</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C34" s="9">
-        <f>F30</f>
-        <v>83</v>
-      </c>
-      <c r="D34" s="66" t="s">
-        <v>60</v>
-      </c>
-      <c r="E34" s="9">
-        <f>F30</f>
-        <v>83</v>
-      </c>
+      <c r="A34" s="67"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="66"/>
+      <c r="E34" s="9"/>
       <c r="F34" s="10"/>
-      <c r="G34" s="297" t="s">
-        <v>77</v>
-      </c>
-      <c r="H34" s="374"/>
-      <c r="I34" s="374"/>
-      <c r="J34" s="374"/>
-      <c r="K34" s="298"/>
+      <c r="G34" s="165" t="s">
+        <v>73</v>
+      </c>
+      <c r="H34" s="166"/>
+      <c r="I34" s="166"/>
+      <c r="J34" s="166"/>
+      <c r="K34" s="167"/>
       <c r="L34" s="68"/>
       <c r="M34" s="69"/>
     </row>
@@ -8962,11 +8732,11 @@
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
       <c r="F35" s="68"/>
-      <c r="G35" s="297"/>
-      <c r="H35" s="374"/>
-      <c r="I35" s="374"/>
-      <c r="J35" s="374"/>
-      <c r="K35" s="298"/>
+      <c r="G35" s="165"/>
+      <c r="H35" s="166"/>
+      <c r="I35" s="166"/>
+      <c r="J35" s="166"/>
+      <c r="K35" s="167"/>
       <c r="L35" s="68"/>
       <c r="M35" s="69"/>
     </row>
@@ -8977,11 +8747,11 @@
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
       <c r="F36" s="68"/>
-      <c r="G36" s="297"/>
-      <c r="H36" s="374"/>
-      <c r="I36" s="374"/>
-      <c r="J36" s="374"/>
-      <c r="K36" s="298"/>
+      <c r="G36" s="165"/>
+      <c r="H36" s="166"/>
+      <c r="I36" s="166"/>
+      <c r="J36" s="166"/>
+      <c r="K36" s="167"/>
       <c r="L36" s="68"/>
       <c r="M36" s="69"/>
     </row>
@@ -8992,19 +8762,19 @@
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
       <c r="F37" s="68"/>
-      <c r="G37" s="297"/>
-      <c r="H37" s="374"/>
-      <c r="I37" s="374"/>
-      <c r="J37" s="374"/>
-      <c r="K37" s="298"/>
+      <c r="G37" s="165"/>
+      <c r="H37" s="166"/>
+      <c r="I37" s="166"/>
+      <c r="J37" s="166"/>
+      <c r="K37" s="167"/>
       <c r="L37" s="68"/>
       <c r="M37" s="69"/>
-      <c r="Q37" s="389"/>
-      <c r="R37" s="389"/>
+      <c r="Q37" s="156"/>
+      <c r="R37" s="156"/>
       <c r="S37" s="7"/>
-      <c r="T37" s="388"/>
-      <c r="U37" s="388"/>
-      <c r="V37" s="388"/>
+      <c r="T37" s="133"/>
+      <c r="U37" s="133"/>
+      <c r="V37" s="133"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A38" s="70"/>
@@ -9013,19 +8783,19 @@
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
       <c r="F38" s="68"/>
-      <c r="G38" s="297"/>
-      <c r="H38" s="374"/>
-      <c r="I38" s="374"/>
-      <c r="J38" s="374"/>
-      <c r="K38" s="298"/>
+      <c r="G38" s="165"/>
+      <c r="H38" s="166"/>
+      <c r="I38" s="166"/>
+      <c r="J38" s="166"/>
+      <c r="K38" s="167"/>
       <c r="L38" s="68"/>
       <c r="M38" s="71"/>
-      <c r="Q38" s="389"/>
-      <c r="R38" s="389"/>
+      <c r="Q38" s="156"/>
+      <c r="R38" s="156"/>
       <c r="S38" s="7"/>
-      <c r="T38" s="388"/>
-      <c r="U38" s="388"/>
-      <c r="V38" s="388"/>
+      <c r="T38" s="133"/>
+      <c r="U38" s="133"/>
+      <c r="V38" s="133"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A39" s="70"/>
@@ -9034,19 +8804,19 @@
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
       <c r="F39" s="68"/>
-      <c r="G39" s="297"/>
-      <c r="H39" s="374"/>
-      <c r="I39" s="374"/>
-      <c r="J39" s="374"/>
-      <c r="K39" s="298"/>
+      <c r="G39" s="165"/>
+      <c r="H39" s="166"/>
+      <c r="I39" s="166"/>
+      <c r="J39" s="166"/>
+      <c r="K39" s="167"/>
       <c r="L39" s="68"/>
       <c r="M39" s="71"/>
       <c r="Q39" s="6"/>
       <c r="R39" s="6"/>
-      <c r="S39" s="390"/>
-      <c r="T39" s="388"/>
-      <c r="U39" s="388"/>
-      <c r="V39" s="388"/>
+      <c r="S39" s="159"/>
+      <c r="T39" s="133"/>
+      <c r="U39" s="133"/>
+      <c r="V39" s="133"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A40" s="70"/>
@@ -9055,19 +8825,19 @@
       <c r="D40" s="10"/>
       <c r="E40" s="10"/>
       <c r="F40" s="68"/>
-      <c r="G40" s="297"/>
-      <c r="H40" s="374"/>
-      <c r="I40" s="374"/>
-      <c r="J40" s="374"/>
-      <c r="K40" s="298"/>
+      <c r="G40" s="165"/>
+      <c r="H40" s="166"/>
+      <c r="I40" s="166"/>
+      <c r="J40" s="166"/>
+      <c r="K40" s="167"/>
       <c r="L40" s="68"/>
       <c r="M40" s="69"/>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
-      <c r="S40" s="390"/>
-      <c r="T40" s="388"/>
-      <c r="U40" s="388"/>
-      <c r="V40" s="388"/>
+      <c r="S40" s="159"/>
+      <c r="T40" s="133"/>
+      <c r="U40" s="133"/>
+      <c r="V40" s="133"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A41" s="70"/>
@@ -9076,315 +8846,303 @@
       <c r="D41" s="10"/>
       <c r="E41" s="10"/>
       <c r="F41" s="68"/>
-      <c r="G41" s="297"/>
-      <c r="H41" s="374"/>
-      <c r="I41" s="374"/>
-      <c r="J41" s="374"/>
-      <c r="K41" s="298"/>
+      <c r="G41" s="165"/>
+      <c r="H41" s="166"/>
+      <c r="I41" s="166"/>
+      <c r="J41" s="166"/>
+      <c r="K41" s="167"/>
       <c r="L41" s="68"/>
       <c r="M41" s="69"/>
     </row>
     <row r="42" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="72">
-        <f>SUM(A34:A41)</f>
-        <v>83</v>
-      </c>
+      <c r="A42" s="72"/>
       <c r="B42" s="73"/>
-      <c r="C42" s="74">
-        <f>SUM(C34:C41)</f>
-        <v>83</v>
-      </c>
+      <c r="C42" s="74"/>
       <c r="D42" s="73"/>
-      <c r="E42" s="74">
-        <f>SUM(E34:E41)</f>
-        <v>83</v>
-      </c>
+      <c r="E42" s="74"/>
       <c r="F42" s="75"/>
-      <c r="G42" s="397" t="s">
+      <c r="G42" s="168" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="398"/>
-      <c r="I42" s="398"/>
-      <c r="J42" s="398"/>
-      <c r="K42" s="399"/>
+      <c r="H42" s="169"/>
+      <c r="I42" s="169"/>
+      <c r="J42" s="169"/>
+      <c r="K42" s="170"/>
       <c r="L42" s="75"/>
       <c r="M42" s="76"/>
     </row>
     <row r="43" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="407" t="s">
+      <c r="A43" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="408"/>
-      <c r="C43" s="408"/>
-      <c r="D43" s="408"/>
-      <c r="E43" s="408"/>
-      <c r="F43" s="408"/>
-      <c r="G43" s="408"/>
-      <c r="H43" s="409"/>
-      <c r="I43" s="326" t="s">
+      <c r="B43" s="136"/>
+      <c r="C43" s="136"/>
+      <c r="D43" s="136"/>
+      <c r="E43" s="136"/>
+      <c r="F43" s="136"/>
+      <c r="G43" s="136"/>
+      <c r="H43" s="137"/>
+      <c r="I43" s="179" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="327"/>
-      <c r="K43" s="327"/>
-      <c r="L43" s="327"/>
-      <c r="M43" s="328"/>
+      <c r="J43" s="180"/>
+      <c r="K43" s="180"/>
+      <c r="L43" s="180"/>
+      <c r="M43" s="181"/>
     </row>
     <row r="44" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="410"/>
-      <c r="B44" s="411"/>
-      <c r="C44" s="411"/>
-      <c r="D44" s="411"/>
-      <c r="E44" s="411"/>
-      <c r="F44" s="411"/>
-      <c r="G44" s="411"/>
-      <c r="H44" s="412"/>
-      <c r="I44" s="366"/>
-      <c r="J44" s="367"/>
-      <c r="K44" s="367"/>
-      <c r="L44" s="367"/>
-      <c r="M44" s="368"/>
+      <c r="A44" s="138"/>
+      <c r="B44" s="139"/>
+      <c r="C44" s="139"/>
+      <c r="D44" s="139"/>
+      <c r="E44" s="139"/>
+      <c r="F44" s="139"/>
+      <c r="G44" s="139"/>
+      <c r="H44" s="140"/>
+      <c r="I44" s="182"/>
+      <c r="J44" s="183"/>
+      <c r="K44" s="183"/>
+      <c r="L44" s="183"/>
+      <c r="M44" s="184"/>
     </row>
     <row r="45" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="423" t="s">
+      <c r="A45" s="141" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="424"/>
-      <c r="C45" s="424"/>
-      <c r="D45" s="424"/>
-      <c r="E45" s="424"/>
-      <c r="F45" s="424"/>
-      <c r="G45" s="424"/>
-      <c r="H45" s="425"/>
-      <c r="I45" s="415" t="s">
+      <c r="B45" s="142"/>
+      <c r="C45" s="142"/>
+      <c r="D45" s="142"/>
+      <c r="E45" s="142"/>
+      <c r="F45" s="142"/>
+      <c r="G45" s="142"/>
+      <c r="H45" s="143"/>
+      <c r="I45" s="185" t="s">
         <v>36</v>
       </c>
-      <c r="J45" s="416"/>
-      <c r="K45" s="416"/>
-      <c r="L45" s="416"/>
-      <c r="M45" s="417"/>
+      <c r="J45" s="186"/>
+      <c r="K45" s="186"/>
+      <c r="L45" s="186"/>
+      <c r="M45" s="187"/>
     </row>
     <row r="46" spans="1:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="423" t="s">
+      <c r="A46" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="424"/>
-      <c r="C46" s="424"/>
-      <c r="D46" s="424"/>
-      <c r="E46" s="424"/>
-      <c r="F46" s="424"/>
-      <c r="G46" s="424"/>
-      <c r="H46" s="425"/>
-      <c r="I46" s="415"/>
-      <c r="J46" s="416"/>
-      <c r="K46" s="416"/>
-      <c r="L46" s="416"/>
-      <c r="M46" s="417"/>
+      <c r="B46" s="142"/>
+      <c r="C46" s="142"/>
+      <c r="D46" s="142"/>
+      <c r="E46" s="142"/>
+      <c r="F46" s="142"/>
+      <c r="G46" s="142"/>
+      <c r="H46" s="143"/>
+      <c r="I46" s="185"/>
+      <c r="J46" s="186"/>
+      <c r="K46" s="186"/>
+      <c r="L46" s="186"/>
+      <c r="M46" s="187"/>
     </row>
     <row r="47" spans="1:22" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="426"/>
-      <c r="B47" s="427"/>
-      <c r="C47" s="427"/>
-      <c r="D47" s="427"/>
-      <c r="E47" s="427"/>
-      <c r="F47" s="427"/>
-      <c r="G47" s="427"/>
-      <c r="H47" s="428"/>
-      <c r="I47" s="419" t="s">
+      <c r="A47" s="144"/>
+      <c r="B47" s="145"/>
+      <c r="C47" s="145"/>
+      <c r="D47" s="145"/>
+      <c r="E47" s="145"/>
+      <c r="F47" s="145"/>
+      <c r="G47" s="145"/>
+      <c r="H47" s="146"/>
+      <c r="I47" s="130" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="420"/>
-      <c r="K47" s="420"/>
-      <c r="L47" s="420"/>
-      <c r="M47" s="421"/>
+      <c r="J47" s="131"/>
+      <c r="K47" s="131"/>
+      <c r="L47" s="131"/>
+      <c r="M47" s="132"/>
     </row>
     <row r="48" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="400" t="s">
+      <c r="A48" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="391"/>
-      <c r="C48" s="391"/>
-      <c r="D48" s="391"/>
-      <c r="E48" s="391"/>
-      <c r="F48" s="391"/>
-      <c r="G48" s="391"/>
-      <c r="H48" s="391"/>
-      <c r="I48" s="391"/>
-      <c r="J48" s="391"/>
-      <c r="K48" s="391"/>
-      <c r="L48" s="391"/>
-      <c r="M48" s="392"/>
+      <c r="B48" s="152"/>
+      <c r="C48" s="152"/>
+      <c r="D48" s="152"/>
+      <c r="E48" s="152"/>
+      <c r="F48" s="152"/>
+      <c r="G48" s="152"/>
+      <c r="H48" s="152"/>
+      <c r="I48" s="152"/>
+      <c r="J48" s="152"/>
+      <c r="K48" s="152"/>
+      <c r="L48" s="152"/>
+      <c r="M48" s="160"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="407" t="s">
+      <c r="A49" s="135" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="408"/>
-      <c r="C49" s="408"/>
-      <c r="D49" s="408"/>
-      <c r="E49" s="408"/>
-      <c r="F49" s="408"/>
-      <c r="G49" s="408"/>
-      <c r="H49" s="409"/>
-      <c r="I49" s="401" t="s">
+      <c r="B49" s="136"/>
+      <c r="C49" s="136"/>
+      <c r="D49" s="136"/>
+      <c r="E49" s="136"/>
+      <c r="F49" s="136"/>
+      <c r="G49" s="136"/>
+      <c r="H49" s="137"/>
+      <c r="I49" s="171" t="s">
         <v>40</v>
       </c>
-      <c r="J49" s="402"/>
-      <c r="K49" s="402"/>
-      <c r="L49" s="402"/>
-      <c r="M49" s="403"/>
+      <c r="J49" s="172"/>
+      <c r="K49" s="172"/>
+      <c r="L49" s="172"/>
+      <c r="M49" s="173"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="410"/>
-      <c r="B50" s="411"/>
-      <c r="C50" s="411"/>
-      <c r="D50" s="411"/>
-      <c r="E50" s="411"/>
-      <c r="F50" s="411"/>
-      <c r="G50" s="411"/>
-      <c r="H50" s="412"/>
-      <c r="I50" s="404"/>
-      <c r="J50" s="405"/>
-      <c r="K50" s="405"/>
-      <c r="L50" s="405"/>
-      <c r="M50" s="406"/>
+      <c r="A50" s="138"/>
+      <c r="B50" s="139"/>
+      <c r="C50" s="139"/>
+      <c r="D50" s="139"/>
+      <c r="E50" s="139"/>
+      <c r="F50" s="139"/>
+      <c r="G50" s="139"/>
+      <c r="H50" s="140"/>
+      <c r="I50" s="174"/>
+      <c r="J50" s="175"/>
+      <c r="K50" s="175"/>
+      <c r="L50" s="175"/>
+      <c r="M50" s="176"/>
     </row>
     <row r="51" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="413"/>
-      <c r="B51" s="414"/>
-      <c r="C51" s="414"/>
-      <c r="D51" s="414"/>
-      <c r="E51" s="411"/>
-      <c r="F51" s="411"/>
-      <c r="G51" s="411"/>
-      <c r="H51" s="412"/>
-      <c r="I51" s="429" t="s">
+      <c r="A51" s="177"/>
+      <c r="B51" s="178"/>
+      <c r="C51" s="178"/>
+      <c r="D51" s="178"/>
+      <c r="E51" s="139"/>
+      <c r="F51" s="139"/>
+      <c r="G51" s="139"/>
+      <c r="H51" s="140"/>
+      <c r="I51" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="J51" s="430"/>
-      <c r="K51" s="431"/>
-      <c r="L51" s="431"/>
-      <c r="M51" s="432"/>
+      <c r="J51" s="148"/>
+      <c r="K51" s="149"/>
+      <c r="L51" s="149"/>
+      <c r="M51" s="150"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="400" t="s">
+      <c r="A52" s="151" t="s">
         <v>42</v>
       </c>
-      <c r="B52" s="391"/>
-      <c r="C52" s="391"/>
-      <c r="D52" s="391"/>
+      <c r="B52" s="152"/>
+      <c r="C52" s="152"/>
+      <c r="D52" s="152"/>
       <c r="E52" s="77" t="s">
         <v>44</v>
       </c>
       <c r="F52" s="78"/>
-      <c r="G52" s="436" t="s">
+      <c r="G52" s="157" t="s">
         <v>45</v>
       </c>
-      <c r="H52" s="436"/>
-      <c r="I52" s="436"/>
-      <c r="J52" s="437"/>
-      <c r="K52" s="391" t="s">
+      <c r="H52" s="157"/>
+      <c r="I52" s="157"/>
+      <c r="J52" s="158"/>
+      <c r="K52" s="152" t="s">
         <v>50</v>
       </c>
-      <c r="L52" s="391"/>
-      <c r="M52" s="392"/>
+      <c r="L52" s="152"/>
+      <c r="M52" s="160"/>
     </row>
     <row r="53" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="433" t="s">
+      <c r="A53" s="153" t="s">
         <v>43</v>
       </c>
-      <c r="B53" s="434"/>
-      <c r="C53" s="434"/>
-      <c r="D53" s="434"/>
+      <c r="B53" s="154"/>
+      <c r="C53" s="154"/>
+      <c r="D53" s="154"/>
       <c r="E53" s="60"/>
       <c r="J53" s="57"/>
-      <c r="K53" s="393" t="s">
+      <c r="K53" s="161" t="s">
         <v>52</v>
       </c>
-      <c r="L53" s="393"/>
-      <c r="M53" s="394"/>
+      <c r="L53" s="161"/>
+      <c r="M53" s="162"/>
     </row>
     <row r="54" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="433"/>
-      <c r="B54" s="434"/>
-      <c r="C54" s="434"/>
-      <c r="D54" s="434"/>
-      <c r="E54" s="435" t="s">
+      <c r="A54" s="153"/>
+      <c r="B54" s="154"/>
+      <c r="C54" s="154"/>
+      <c r="D54" s="154"/>
+      <c r="E54" s="155" t="s">
         <v>46</v>
       </c>
-      <c r="F54" s="389"/>
+      <c r="F54" s="156"/>
       <c r="G54" s="7"/>
-      <c r="H54" s="388" t="s">
+      <c r="H54" s="133" t="s">
         <v>46</v>
       </c>
-      <c r="I54" s="388"/>
-      <c r="J54" s="422"/>
-      <c r="K54" s="393"/>
-      <c r="L54" s="393"/>
-      <c r="M54" s="394"/>
+      <c r="I54" s="133"/>
+      <c r="J54" s="134"/>
+      <c r="K54" s="161"/>
+      <c r="L54" s="161"/>
+      <c r="M54" s="162"/>
     </row>
     <row r="55" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="433"/>
-      <c r="B55" s="434"/>
-      <c r="C55" s="434"/>
-      <c r="D55" s="434"/>
-      <c r="E55" s="435" t="s">
+      <c r="A55" s="153"/>
+      <c r="B55" s="154"/>
+      <c r="C55" s="154"/>
+      <c r="D55" s="154"/>
+      <c r="E55" s="155" t="s">
         <v>47</v>
       </c>
-      <c r="F55" s="389"/>
-      <c r="G55" s="389"/>
-      <c r="H55" s="388" t="s">
+      <c r="F55" s="156"/>
+      <c r="G55" s="156"/>
+      <c r="H55" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="I55" s="388"/>
-      <c r="J55" s="422"/>
-      <c r="K55" s="393"/>
-      <c r="L55" s="393"/>
-      <c r="M55" s="394"/>
+      <c r="I55" s="133"/>
+      <c r="J55" s="134"/>
+      <c r="K55" s="161"/>
+      <c r="L55" s="161"/>
+      <c r="M55" s="162"/>
     </row>
     <row r="56" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="60"/>
       <c r="D56" s="57"/>
-      <c r="E56" s="435"/>
-      <c r="F56" s="389"/>
-      <c r="G56" s="389"/>
-      <c r="H56" s="388"/>
-      <c r="I56" s="388"/>
-      <c r="J56" s="422"/>
-      <c r="K56" s="395" t="s">
+      <c r="E56" s="155"/>
+      <c r="F56" s="156"/>
+      <c r="G56" s="156"/>
+      <c r="H56" s="133"/>
+      <c r="I56" s="133"/>
+      <c r="J56" s="134"/>
+      <c r="K56" s="163" t="s">
         <v>51</v>
       </c>
-      <c r="L56" s="395"/>
-      <c r="M56" s="396"/>
+      <c r="L56" s="163"/>
+      <c r="M56" s="164"/>
     </row>
     <row r="57" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="60"/>
       <c r="D57" s="57"/>
-      <c r="E57" s="435"/>
-      <c r="F57" s="389"/>
+      <c r="E57" s="155"/>
+      <c r="F57" s="156"/>
       <c r="G57" s="7"/>
-      <c r="H57" s="388" t="s">
+      <c r="H57" s="133" t="s">
         <v>49</v>
       </c>
-      <c r="I57" s="388"/>
-      <c r="J57" s="422"/>
+      <c r="I57" s="133"/>
+      <c r="J57" s="134"/>
       <c r="K57" s="79"/>
       <c r="L57" s="80"/>
       <c r="M57" s="81"/>
     </row>
     <row r="58" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="82"/>
-      <c r="B58" s="304">
-        <f>B1</f>
-        <v>45877</v>
-      </c>
-      <c r="C58" s="304"/>
+      <c r="B58" s="246"/>
+      <c r="C58" s="246"/>
       <c r="D58" s="49"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="362"/>
-      <c r="G58" s="362"/>
-      <c r="H58" s="362"/>
-      <c r="I58" s="362"/>
-      <c r="J58" s="418"/>
+      <c r="E58" s="127"/>
+      <c r="F58" s="128"/>
+      <c r="G58" s="128"/>
+      <c r="H58" s="128"/>
+      <c r="I58" s="128"/>
+      <c r="J58" s="129"/>
       <c r="K58" s="83"/>
       <c r="L58" s="84"/>
       <c r="M58" s="85"/>
@@ -9403,68 +9161,30 @@
     </row>
   </sheetData>
   <mergeCells count="110">
-    <mergeCell ref="E58:J58"/>
-    <mergeCell ref="I47:M47"/>
-    <mergeCell ref="H55:J56"/>
-    <mergeCell ref="A43:H44"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A46:H47"/>
-    <mergeCell ref="I51:M51"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A53:D55"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="H57:J57"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="E55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="G52:J52"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="T37:V37"/>
-    <mergeCell ref="T38:V38"/>
-    <mergeCell ref="T39:V40"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="S39:S40"/>
-    <mergeCell ref="K52:M52"/>
-    <mergeCell ref="K53:M55"/>
-    <mergeCell ref="K56:M56"/>
-    <mergeCell ref="G37:K37"/>
-    <mergeCell ref="G42:K42"/>
-    <mergeCell ref="G40:K40"/>
-    <mergeCell ref="A48:M48"/>
-    <mergeCell ref="I49:M50"/>
-    <mergeCell ref="G41:K41"/>
-    <mergeCell ref="G38:K38"/>
-    <mergeCell ref="A49:H51"/>
-    <mergeCell ref="I43:M44"/>
-    <mergeCell ref="I45:M46"/>
-    <mergeCell ref="G39:K39"/>
-    <mergeCell ref="G35:K35"/>
-    <mergeCell ref="G36:K36"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="A31:M31"/>
-    <mergeCell ref="G32:K32"/>
-    <mergeCell ref="G33:K33"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="G34:K34"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="I4:M6"/>
+    <mergeCell ref="I12:M14"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="E8:H8"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A5:H5"/>
@@ -9489,30 +9209,68 @@
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="I4:M6"/>
-    <mergeCell ref="I12:M14"/>
-    <mergeCell ref="I8:M8"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="G36:K36"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A31:M31"/>
+    <mergeCell ref="G32:K32"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="G34:K34"/>
+    <mergeCell ref="T37:V37"/>
+    <mergeCell ref="T38:V38"/>
+    <mergeCell ref="T39:V40"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="S39:S40"/>
+    <mergeCell ref="K52:M52"/>
+    <mergeCell ref="K53:M55"/>
+    <mergeCell ref="K56:M56"/>
+    <mergeCell ref="G37:K37"/>
+    <mergeCell ref="G42:K42"/>
+    <mergeCell ref="G40:K40"/>
+    <mergeCell ref="A48:M48"/>
+    <mergeCell ref="I49:M50"/>
+    <mergeCell ref="G41:K41"/>
+    <mergeCell ref="G38:K38"/>
+    <mergeCell ref="A49:H51"/>
+    <mergeCell ref="I43:M44"/>
+    <mergeCell ref="I45:M46"/>
+    <mergeCell ref="G39:K39"/>
+    <mergeCell ref="E58:J58"/>
+    <mergeCell ref="I47:M47"/>
+    <mergeCell ref="H55:J56"/>
+    <mergeCell ref="A43:H44"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A46:H47"/>
+    <mergeCell ref="I51:M51"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A53:D55"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="H57:J57"/>
+    <mergeCell ref="H54:J54"/>
+    <mergeCell ref="E55:F56"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="G52:J52"/>
+    <mergeCell ref="E54:F54"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.26" top="0.52" bottom="0.56000000000000005" header="0.5" footer="0.5"/>
@@ -9548,68 +9306,68 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>187</v>
+      </c>
+      <c r="E1" s="31" t="s">
         <v>188</v>
       </c>
-      <c r="B1" s="31" t="s">
-        <v>189</v>
-      </c>
-      <c r="C1" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="D1" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E1" s="31" t="s">
-        <v>192</v>
-      </c>
       <c r="H1" s="86" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="I1" s="86" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E2">
         <v>92336</v>
       </c>
       <c r="H2" s="86" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I2" s="86" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E3">
         <v>81001</v>
       </c>
       <c r="H3" s="86" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I3" s="86">
         <v>10285609</v>
@@ -9617,22 +9375,22 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E4">
         <v>24477</v>
       </c>
       <c r="H4" s="86" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="I4" s="87">
         <v>523953410</v>
@@ -9640,22 +9398,22 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="31" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E5">
         <v>55432</v>
       </c>
       <c r="H5" s="86" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="I5" s="88">
         <v>59642884</v>
@@ -9663,16 +9421,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E6">
         <v>95776</v>
@@ -9680,16 +9438,16 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E7">
         <v>31793</v>
@@ -9697,16 +9455,16 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <v>53066</v>
@@ -9714,16 +9472,16 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E9">
         <v>97321</v>
@@ -9731,16 +9489,16 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E10">
         <v>46231</v>
@@ -9748,16 +9506,16 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E11">
         <v>75706</v>
@@ -9765,16 +9523,16 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E12">
         <v>12831</v>
@@ -9782,16 +9540,16 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E13">
         <v>35756</v>
@@ -9799,16 +9557,16 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B14" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E14">
         <v>49053</v>
@@ -9816,16 +9574,16 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C15" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D15" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E15">
         <v>85043</v>
@@ -9833,16 +9591,16 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B16" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C16" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E16">
         <v>17202</v>
@@ -9850,16 +9608,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C17" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D17" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E17">
         <v>50613</v>
@@ -9867,16 +9625,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B18" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C18" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E18">
         <v>93263</v>
@@ -9884,16 +9642,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C19" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D19" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E19">
         <v>29078</v>
@@ -9901,16 +9659,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B20" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C20" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D20" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E20">
         <v>76065</v>
@@ -9918,16 +9676,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C21" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E21">
         <v>12010</v>
@@ -9935,16 +9693,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B22" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C22" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D22" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E22">
         <v>66609</v>
@@ -9952,16 +9710,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B23" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C23" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D23" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E23">
         <v>43162</v>
@@ -9969,16 +9727,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B24" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C24" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E24">
         <v>92376</v>
@@ -9986,16 +9744,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B25" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C25" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D25" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E25">
         <v>31320</v>
@@ -10003,33 +9761,33 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>164</v>
+      </c>
+      <c r="B26" t="s">
+        <v>165</v>
+      </c>
+      <c r="C26" t="s">
+        <v>166</v>
+      </c>
+      <c r="D26" t="s">
+        <v>167</v>
+      </c>
+      <c r="E26" t="s">
         <v>168</v>
-      </c>
-      <c r="B26" t="s">
-        <v>169</v>
-      </c>
-      <c r="C26" t="s">
-        <v>170</v>
-      </c>
-      <c r="D26" t="s">
-        <v>171</v>
-      </c>
-      <c r="E26" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B27" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C27" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E27">
         <v>92518</v>
@@ -10037,33 +9795,33 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>172</v>
+      </c>
+      <c r="B28" t="s">
+        <v>173</v>
+      </c>
+      <c r="C28" t="s">
+        <v>174</v>
+      </c>
+      <c r="D28" t="s">
+        <v>175</v>
+      </c>
+      <c r="E28" t="s">
         <v>176</v>
-      </c>
-      <c r="B28" t="s">
-        <v>177</v>
-      </c>
-      <c r="C28" t="s">
-        <v>178</v>
-      </c>
-      <c r="D28" t="s">
-        <v>179</v>
-      </c>
-      <c r="E28" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B29" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C29" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D29" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E29">
         <v>60623</v>
@@ -10071,16 +9829,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B30" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C30" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D30" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E30">
         <v>30228</v>
@@ -10104,21 +9862,21 @@
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="31" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C3">
         <v>40</v>
@@ -10129,10 +9887,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C4">
         <v>38</v>
@@ -10143,10 +9901,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C5">
         <v>59</v>
@@ -10157,10 +9915,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C6">
         <v>81</v>
@@ -10171,10 +9929,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C7">
         <v>70</v>
@@ -10185,10 +9943,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C8">
         <v>62</v>
@@ -10199,10 +9957,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C9">
         <v>66</v>
@@ -10213,10 +9971,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B10" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C10">
         <v>65</v>
@@ -10227,10 +9985,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C11">
         <v>61</v>
@@ -10241,10 +9999,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B12" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C12">
         <v>83</v>
@@ -10255,10 +10013,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B13" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C13">
         <v>70</v>
@@ -10269,10 +10027,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B14" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C14">
         <v>50</v>
@@ -10283,10 +10041,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B15" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C15">
         <v>70</v>
@@ -10297,10 +10055,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B16" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C16">
         <v>69</v>
@@ -10311,10 +10069,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B17" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C17">
         <v>54</v>
@@ -10325,10 +10083,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C18">
         <v>65</v>
@@ -10339,10 +10097,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C19">
         <v>65</v>
@@ -10353,10 +10111,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B20" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C20">
         <v>70</v>
@@ -10367,10 +10125,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B21" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C21">
         <v>55</v>
@@ -10381,10 +10139,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C22">
         <v>54</v>
@@ -10395,10 +10153,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C23">
         <v>76</v>
@@ -10409,10 +10167,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C24">
         <v>76</v>
@@ -10423,10 +10181,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B25" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C25">
         <v>65</v>
@@ -10437,10 +10195,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B26" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C26">
         <v>56</v>
@@ -10451,10 +10209,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B27" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C27">
         <v>83</v>
@@ -10465,10 +10223,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B28" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C28">
         <v>27</v>
@@ -10479,10 +10237,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B29" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C29">
         <v>16</v>
@@ -10493,10 +10251,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B30" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C30">
         <v>26</v>
@@ -10507,10 +10265,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B31" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C31">
         <v>16</v>

--- a/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
+++ b/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Procomm\Documents\GitHub\Acumatica_Customizations_and_Packages\Istar_Development\Projects\BOL_Generation\Code\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B434921-1526-4102-894B-647902FE358A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E097467-11F9-48A5-9D0E-F74C65F0CAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{888CA347-7849-4038-B8EE-FAC87BA1B844}"/>
   </bookViews>
@@ -16,8 +16,6 @@
     <sheet name="MasterBOL" sheetId="3" r:id="rId1"/>
     <sheet name="Supplemental_Master_BOL" sheetId="4" r:id="rId2"/>
     <sheet name="Supplemental_BOL" sheetId="1" r:id="rId3"/>
-    <sheet name="ADDRESS" sheetId="5" r:id="rId4"/>
-    <sheet name="Customer Order Info" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="82">
   <si>
     <t>SHIP FROM</t>
   </si>
@@ -304,466 +302,7 @@
     <t>Commodity as jewelry</t>
   </si>
   <si>
-    <t>TARGET  DC 0553</t>
-  </si>
-  <si>
-    <t>7895 REDWOOD AVE</t>
-  </si>
-  <si>
-    <t>FONTANA</t>
-  </si>
-  <si>
-    <t>CA</t>
-  </si>
-  <si>
-    <t>TARGET  DC 0554</t>
-  </si>
-  <si>
-    <t>34800 UNITED AVE</t>
-  </si>
-  <si>
-    <t>PUEBLO</t>
-  </si>
-  <si>
-    <t>CO</t>
-  </si>
-  <si>
-    <t>TARGET  DC 0560</t>
-  </si>
-  <si>
-    <t>423 MOUNT VERNON RD</t>
-  </si>
-  <si>
-    <t>STUARTS DRAFT</t>
-  </si>
-  <si>
-    <t>VA</t>
-  </si>
-  <si>
-    <t>TARGET DC 0551</t>
-  </si>
-  <si>
-    <t>7120 HWY 65 NE</t>
-  </si>
-  <si>
-    <t>FRIDLEY</t>
-  </si>
-  <si>
-    <t>MN</t>
-  </si>
-  <si>
-    <t>TARGET DC 0555</t>
-  </si>
-  <si>
-    <t>2050 E BEAMER ST</t>
-  </si>
-  <si>
-    <t>WOODLAND</t>
-  </si>
-  <si>
-    <t>TARGET DC 0556</t>
-  </si>
-  <si>
-    <t>110 W JORDAN RD</t>
-  </si>
-  <si>
-    <t>TIFTON</t>
-  </si>
-  <si>
-    <t>GA</t>
-  </si>
-  <si>
-    <t>TARGET DC 0557</t>
-  </si>
-  <si>
-    <t>1100 E VALLEY RD</t>
-  </si>
-  <si>
-    <t>OCONOMOWOC</t>
-  </si>
-  <si>
-    <t>WI</t>
-  </si>
-  <si>
-    <t>TARGET DC 0558</t>
-  </si>
-  <si>
-    <t>875 BETA DRIVE SW</t>
-  </si>
-  <si>
-    <t>ALBANY</t>
-  </si>
-  <si>
-    <t>OR</t>
-  </si>
-  <si>
-    <t>TARGET DC 0559</t>
-  </si>
-  <si>
-    <t>1350 S GIRLS SCHOOL RD</t>
-  </si>
-  <si>
-    <t>INDIANAPOLIS</t>
-  </si>
-  <si>
-    <t>IN</t>
-  </si>
-  <si>
-    <t>TARGET DC 0578</t>
-  </si>
-  <si>
-    <t>13790 Harvey Road</t>
-  </si>
-  <si>
-    <t>TYLER</t>
-  </si>
-  <si>
-    <t>TX</t>
-  </si>
-  <si>
-    <t>TARGET DC 0579</t>
-  </si>
-  <si>
-    <t>131 NORTH RD</t>
-  </si>
-  <si>
-    <t>WILTON</t>
-  </si>
-  <si>
-    <t>NY</t>
-  </si>
-  <si>
-    <t>TARGET DC 0580</t>
-  </si>
-  <si>
-    <t>6305 GREENBRIER RD</t>
-  </si>
-  <si>
-    <t>MADISON</t>
-  </si>
-  <si>
-    <t>AL</t>
-  </si>
-  <si>
-    <t>TARGET DC 0587</t>
-  </si>
-  <si>
-    <t>12905 East L Avenue</t>
-  </si>
-  <si>
-    <t>GALESBURG</t>
-  </si>
-  <si>
-    <t>MI</t>
-  </si>
-  <si>
-    <t>TARGET DC 0588</t>
-  </si>
-  <si>
-    <t>7101 W VAN BUREN</t>
-  </si>
-  <si>
-    <t>PHOENIX</t>
-  </si>
-  <si>
-    <t>AZ</t>
-  </si>
-  <si>
-    <t>TARGET DC 0589</t>
-  </si>
-  <si>
-    <t>3325 ARCHER DR</t>
-  </si>
-  <si>
-    <t>CHAMBERSBURG</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>TARGET DC 0590</t>
-  </si>
-  <si>
-    <t>6601 HUDSON RD</t>
-  </si>
-  <si>
-    <t>CEDAR FALLS</t>
-  </si>
-  <si>
-    <t>IA</t>
-  </si>
-  <si>
-    <t>TARGET DC 0593</t>
-  </si>
-  <si>
-    <t>3700 Zachary Avenue</t>
-  </si>
-  <si>
-    <t>SHAFTER</t>
-  </si>
-  <si>
-    <t>TARGET DC 0594</t>
-  </si>
-  <si>
-    <t>166 CORPORATE DR</t>
-  </si>
-  <si>
-    <t>LUGOFF</t>
-  </si>
-  <si>
-    <t>SC</t>
-  </si>
-  <si>
-    <t>TARGET DC 3801</t>
-  </si>
-  <si>
-    <t>4055 RAILPORT PKWY</t>
-  </si>
-  <si>
-    <t>MIDLOTHIAN</t>
-  </si>
-  <si>
-    <t>TARGET DC 3802</t>
-  </si>
-  <si>
-    <t>1730 STATE HWY 5S</t>
-  </si>
-  <si>
-    <t>AMSTERDAM</t>
-  </si>
-  <si>
-    <t>TARGET DC 3803</t>
-  </si>
-  <si>
-    <t>5400 WENGER ST</t>
-  </si>
-  <si>
-    <t>TOPEKA</t>
-  </si>
-  <si>
-    <t>KS</t>
-  </si>
-  <si>
-    <t>TARGET DC 3804</t>
-  </si>
-  <si>
-    <t>3 WALKER WAY</t>
-  </si>
-  <si>
-    <t>WEST JEFFERSON</t>
-  </si>
-  <si>
-    <t>OH</t>
-  </si>
-  <si>
-    <t>TARGET DC 3806</t>
-  </si>
-  <si>
-    <t>2702 SUMMIT AVE</t>
-  </si>
-  <si>
-    <t>RIALTO</t>
-  </si>
-  <si>
-    <t>TARGET DC 3808</t>
-  </si>
-  <si>
-    <t>895 SUNBURY RD</t>
-  </si>
-  <si>
-    <t>MIDWAY</t>
-  </si>
-  <si>
-    <t>TARGET DC 3811</t>
-  </si>
-  <si>
-    <t>1900 Stover Court</t>
-  </si>
-  <si>
-    <t>NEWTON</t>
-  </si>
-  <si>
-    <t>NC</t>
-  </si>
-  <si>
-    <t>28658-8983</t>
-  </si>
-  <si>
-    <t>TARGET DC 3856</t>
-  </si>
-  <si>
-    <t>23000 Van Buren Boulevard</t>
-  </si>
-  <si>
-    <t>Riverside</t>
-  </si>
-  <si>
-    <t>TARGET DC 3857</t>
-  </si>
-  <si>
-    <t>300 CREEKVIEW AVE, BLDG H</t>
-  </si>
-  <si>
-    <t>LOGAN  TWP</t>
-  </si>
-  <si>
-    <t>NJ</t>
-  </si>
-  <si>
-    <t>08085</t>
-  </si>
-  <si>
-    <t>TARGET DC 3865</t>
-  </si>
-  <si>
-    <t>3501 S Pulaski Rd</t>
-  </si>
-  <si>
-    <t>Chicago</t>
-  </si>
-  <si>
-    <t>IL</t>
-  </si>
-  <si>
-    <t>TARGET DC 3868</t>
-  </si>
-  <si>
-    <t>1050 Site Pkwy</t>
-  </si>
-  <si>
-    <t>Hampton</t>
-  </si>
-  <si>
-    <t>DC</t>
-  </si>
-  <si>
-    <t>ADDRESS</t>
-  </si>
-  <si>
-    <t>TOWN</t>
-  </si>
-  <si>
-    <t>STATE</t>
-  </si>
-  <si>
-    <t>ZIP</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bill of Lading Number: </t>
-  </si>
-  <si>
-    <t>Row Labels</t>
-  </si>
-  <si>
-    <t>Count of Carton Number</t>
-  </si>
-  <si>
-    <t>Sum of Gross Weight</t>
-  </si>
-  <si>
-    <t>0215-8880831-0551</t>
-  </si>
-  <si>
-    <t>0215-8880831-0553</t>
-  </si>
-  <si>
-    <t>0215-8880831-0554</t>
-  </si>
-  <si>
-    <t>0215-8880831-0555</t>
-  </si>
-  <si>
-    <t>0215-8880831-0556</t>
-  </si>
-  <si>
-    <t>0215-8880831-0557</t>
-  </si>
-  <si>
-    <t>0215-8880831-0558</t>
-  </si>
-  <si>
-    <t>0215-8880831-0559</t>
-  </si>
-  <si>
-    <t>0215-8880831-0560</t>
-  </si>
-  <si>
-    <t>0215-8880831-0578</t>
-  </si>
-  <si>
-    <t>0215-8880831-0579</t>
-  </si>
-  <si>
-    <t>0215-8880831-0580</t>
-  </si>
-  <si>
-    <t>0215-8880831-0587</t>
-  </si>
-  <si>
-    <t>0215-8880831-0588</t>
-  </si>
-  <si>
-    <t>0215-8880831-0589</t>
-  </si>
-  <si>
-    <t>0215-8880831-0590</t>
-  </si>
-  <si>
-    <t>0215-8880831-0593</t>
-  </si>
-  <si>
-    <t>0215-8880831-0594</t>
-  </si>
-  <si>
-    <t>0215-8880831-3801</t>
-  </si>
-  <si>
-    <t>0215-8880831-3802</t>
-  </si>
-  <si>
-    <t>0215-8880831-3803</t>
-  </si>
-  <si>
-    <t>0215-8880831-3804</t>
-  </si>
-  <si>
-    <t>0215-8880831-3806</t>
-  </si>
-  <si>
-    <t>0215-8880831-3808</t>
-  </si>
-  <si>
-    <t>0215-8880831-3811</t>
-  </si>
-  <si>
-    <t>0215-8880831-3856</t>
-  </si>
-  <si>
-    <t>0215-8880831-3857</t>
-  </si>
-  <si>
-    <t>0215-8880831-3865</t>
-  </si>
-  <si>
-    <t>0215-8880831-3868</t>
-  </si>
-  <si>
-    <t>CARRIER</t>
-  </si>
-  <si>
-    <t>CH Robinson</t>
-  </si>
-  <si>
-    <t>SEAL:</t>
-  </si>
-  <si>
-    <t>PRO #:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCAC: </t>
-  </si>
-  <si>
-    <t>RBTW</t>
   </si>
   <si>
     <t xml:space="preserve">Master Bill of Lading Number: </t>
@@ -776,9 +315,6 @@
   </si>
   <si>
     <t xml:space="preserve">Pro number: </t>
-  </si>
-  <si>
-    <t>TARGET Load:</t>
   </si>
   <si>
     <t xml:space="preserve">Date: </t>
@@ -815,7 +351,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -928,13 +464,8 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF2B2D31"/>
-      <name val="Helvetica"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -959,12 +490,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="40">
     <border>
@@ -1434,7 +959,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="442">
+  <cellXfs count="438">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1498,7 +1023,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1592,15 +1116,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -4970,608 +4485,608 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="440" t="s">
-        <v>235</v>
-      </c>
-      <c r="B1" s="441"/>
-      <c r="C1" s="283" t="s">
+      <c r="A1" s="436" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="437"/>
+      <c r="C1" s="279" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="283"/>
-      <c r="E1" s="283"/>
-      <c r="F1" s="283"/>
-      <c r="G1" s="283"/>
-      <c r="H1" s="283"/>
-      <c r="I1" s="283"/>
-      <c r="J1" s="283"/>
-      <c r="K1" s="283"/>
-      <c r="L1" s="284" t="s">
+      <c r="D1" s="279"/>
+      <c r="E1" s="279"/>
+      <c r="F1" s="279"/>
+      <c r="G1" s="279"/>
+      <c r="H1" s="279"/>
+      <c r="I1" s="279"/>
+      <c r="J1" s="279"/>
+      <c r="K1" s="279"/>
+      <c r="L1" s="280" t="s">
         <v>60</v>
       </c>
-      <c r="M1" s="285"/>
+      <c r="M1" s="281"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="280" t="s">
+      <c r="A2" s="276" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="281"/>
-      <c r="C2" s="281"/>
-      <c r="D2" s="281"/>
-      <c r="E2" s="281"/>
-      <c r="F2" s="281"/>
-      <c r="G2" s="281"/>
-      <c r="H2" s="282"/>
-      <c r="I2" s="286" t="s">
-        <v>228</v>
-      </c>
-      <c r="J2" s="287"/>
-      <c r="K2" s="287"/>
-      <c r="L2" s="287"/>
-      <c r="M2" s="288"/>
+      <c r="B2" s="277"/>
+      <c r="C2" s="277"/>
+      <c r="D2" s="277"/>
+      <c r="E2" s="277"/>
+      <c r="F2" s="277"/>
+      <c r="G2" s="277"/>
+      <c r="H2" s="278"/>
+      <c r="I2" s="282" t="s">
+        <v>75</v>
+      </c>
+      <c r="J2" s="283"/>
+      <c r="K2" s="283"/>
+      <c r="L2" s="283"/>
+      <c r="M2" s="284"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="268" t="s">
+      <c r="A3" s="264" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="269"/>
-      <c r="C3" s="269"/>
-      <c r="D3" s="269"/>
-      <c r="E3" s="269"/>
-      <c r="F3" s="269"/>
-      <c r="G3" s="269"/>
-      <c r="H3" s="270"/>
-      <c r="I3" s="289"/>
-      <c r="J3" s="290"/>
-      <c r="K3" s="290"/>
-      <c r="L3" s="290"/>
-      <c r="M3" s="291"/>
+      <c r="B3" s="265"/>
+      <c r="C3" s="265"/>
+      <c r="D3" s="265"/>
+      <c r="E3" s="265"/>
+      <c r="F3" s="265"/>
+      <c r="G3" s="265"/>
+      <c r="H3" s="266"/>
+      <c r="I3" s="285"/>
+      <c r="J3" s="286"/>
+      <c r="K3" s="286"/>
+      <c r="L3" s="286"/>
+      <c r="M3" s="287"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="268" t="s">
+      <c r="A4" s="264" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="269"/>
-      <c r="C4" s="269"/>
-      <c r="D4" s="269"/>
-      <c r="E4" s="269"/>
-      <c r="F4" s="269"/>
-      <c r="G4" s="269"/>
-      <c r="H4" s="270"/>
-      <c r="I4" s="271"/>
-      <c r="J4" s="272"/>
-      <c r="K4" s="272"/>
-      <c r="L4" s="272"/>
-      <c r="M4" s="273"/>
+      <c r="B4" s="265"/>
+      <c r="C4" s="265"/>
+      <c r="D4" s="265"/>
+      <c r="E4" s="265"/>
+      <c r="F4" s="265"/>
+      <c r="G4" s="265"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="267"/>
+      <c r="J4" s="268"/>
+      <c r="K4" s="268"/>
+      <c r="L4" s="268"/>
+      <c r="M4" s="269"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="268" t="s">
+      <c r="A5" s="264" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="269"/>
-      <c r="C5" s="269"/>
-      <c r="D5" s="269"/>
-      <c r="E5" s="269"/>
-      <c r="F5" s="269"/>
-      <c r="G5" s="269"/>
-      <c r="H5" s="270"/>
-      <c r="I5" s="271"/>
-      <c r="J5" s="272"/>
-      <c r="K5" s="272"/>
-      <c r="L5" s="272"/>
-      <c r="M5" s="273"/>
+      <c r="B5" s="265"/>
+      <c r="C5" s="265"/>
+      <c r="D5" s="265"/>
+      <c r="E5" s="265"/>
+      <c r="F5" s="265"/>
+      <c r="G5" s="265"/>
+      <c r="H5" s="266"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="268"/>
+      <c r="K5" s="268"/>
+      <c r="L5" s="268"/>
+      <c r="M5" s="269"/>
     </row>
     <row r="6" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="277" t="s">
+      <c r="A6" s="273" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="278"/>
-      <c r="C6" s="278"/>
-      <c r="D6" s="278"/>
-      <c r="E6" s="278"/>
-      <c r="F6" s="279" t="s">
+      <c r="B6" s="274"/>
+      <c r="C6" s="274"/>
+      <c r="D6" s="274"/>
+      <c r="E6" s="274"/>
+      <c r="F6" s="275" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="279"/>
+      <c r="G6" s="275"/>
       <c r="H6" s="12"/>
-      <c r="I6" s="274"/>
-      <c r="J6" s="275"/>
-      <c r="K6" s="275"/>
-      <c r="L6" s="275"/>
-      <c r="M6" s="276"/>
+      <c r="I6" s="270"/>
+      <c r="J6" s="271"/>
+      <c r="K6" s="271"/>
+      <c r="L6" s="271"/>
+      <c r="M6" s="272"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="280" t="s">
+      <c r="A7" s="276" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="281"/>
-      <c r="C7" s="281"/>
-      <c r="D7" s="281"/>
-      <c r="E7" s="281"/>
-      <c r="F7" s="281"/>
-      <c r="G7" s="281"/>
-      <c r="H7" s="282"/>
-      <c r="I7" s="90" t="s">
-        <v>229</v>
-      </c>
-      <c r="J7" s="91"/>
-      <c r="K7" s="92"/>
-      <c r="L7" s="91"/>
-      <c r="M7" s="93"/>
+      <c r="B7" s="277"/>
+      <c r="C7" s="277"/>
+      <c r="D7" s="277"/>
+      <c r="E7" s="277"/>
+      <c r="F7" s="277"/>
+      <c r="G7" s="277"/>
+      <c r="H7" s="278"/>
+      <c r="I7" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="J7" s="87"/>
+      <c r="K7" s="88"/>
+      <c r="L7" s="87"/>
+      <c r="M7" s="89"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="304" t="s">
+      <c r="A8" s="300" t="s">
         <v>65</v>
       </c>
-      <c r="B8" s="305"/>
-      <c r="C8" s="305"/>
-      <c r="D8" s="305"/>
-      <c r="E8" s="306" t="s">
+      <c r="B8" s="301"/>
+      <c r="C8" s="301"/>
+      <c r="D8" s="301"/>
+      <c r="E8" s="302" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="306"/>
-      <c r="G8" s="306"/>
-      <c r="H8" s="307"/>
-      <c r="I8" s="304" t="s">
+      <c r="F8" s="302"/>
+      <c r="G8" s="302"/>
+      <c r="H8" s="303"/>
+      <c r="I8" s="300" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="305"/>
-      <c r="K8" s="305"/>
-      <c r="L8" s="305"/>
-      <c r="M8" s="308"/>
+      <c r="J8" s="301"/>
+      <c r="K8" s="301"/>
+      <c r="L8" s="301"/>
+      <c r="M8" s="304"/>
     </row>
     <row r="9" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="304" t="s">
+      <c r="A9" s="300" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="305"/>
-      <c r="C9" s="305"/>
-      <c r="D9" s="305"/>
-      <c r="E9" s="305"/>
-      <c r="F9" s="305"/>
-      <c r="G9" s="305"/>
-      <c r="H9" s="308"/>
-      <c r="I9" s="94" t="s">
+      <c r="B9" s="301"/>
+      <c r="C9" s="301"/>
+      <c r="D9" s="301"/>
+      <c r="E9" s="301"/>
+      <c r="F9" s="301"/>
+      <c r="G9" s="301"/>
+      <c r="H9" s="304"/>
+      <c r="I9" s="90" t="s">
         <v>70</v>
       </c>
-      <c r="J9" s="95"/>
-      <c r="K9" s="95"/>
-      <c r="L9" s="95"/>
-      <c r="M9" s="89"/>
+      <c r="J9" s="91"/>
+      <c r="K9" s="91"/>
+      <c r="L9" s="91"/>
+      <c r="M9" s="85"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="304" t="s">
+      <c r="A10" s="300" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="305"/>
-      <c r="C10" s="305"/>
-      <c r="D10" s="305"/>
-      <c r="E10" s="305"/>
-      <c r="F10" s="305"/>
-      <c r="G10" s="305"/>
-      <c r="H10" s="308"/>
-      <c r="I10" s="96" t="s">
-        <v>230</v>
-      </c>
-      <c r="J10" s="97"/>
-      <c r="K10" s="97"/>
-      <c r="L10" s="97"/>
-      <c r="M10" s="98"/>
+      <c r="B10" s="301"/>
+      <c r="C10" s="301"/>
+      <c r="D10" s="301"/>
+      <c r="E10" s="301"/>
+      <c r="F10" s="301"/>
+      <c r="G10" s="301"/>
+      <c r="H10" s="304"/>
+      <c r="I10" s="92" t="s">
+        <v>77</v>
+      </c>
+      <c r="J10" s="93"/>
+      <c r="K10" s="93"/>
+      <c r="L10" s="93"/>
+      <c r="M10" s="94"/>
     </row>
     <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="292" t="s">
+      <c r="A11" s="288" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="293"/>
-      <c r="C11" s="293"/>
-      <c r="D11" s="293"/>
-      <c r="E11" s="293"/>
-      <c r="F11" s="294" t="s">
+      <c r="B11" s="289"/>
+      <c r="C11" s="289"/>
+      <c r="D11" s="289"/>
+      <c r="E11" s="289"/>
+      <c r="F11" s="290" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="294"/>
-      <c r="H11" s="89"/>
-      <c r="I11" s="99" t="s">
-        <v>231</v>
-      </c>
-      <c r="J11" s="100"/>
-      <c r="K11" s="100"/>
-      <c r="L11" s="100"/>
-      <c r="M11" s="101"/>
+      <c r="G11" s="290"/>
+      <c r="H11" s="85"/>
+      <c r="I11" s="95" t="s">
+        <v>78</v>
+      </c>
+      <c r="J11" s="96"/>
+      <c r="K11" s="96"/>
+      <c r="L11" s="96"/>
+      <c r="M11" s="97"/>
     </row>
     <row r="12" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="280" t="s">
+      <c r="A12" s="276" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="281"/>
-      <c r="C12" s="281"/>
-      <c r="D12" s="281"/>
-      <c r="E12" s="281"/>
-      <c r="F12" s="281"/>
-      <c r="G12" s="281"/>
-      <c r="H12" s="282"/>
-      <c r="I12" s="295"/>
-      <c r="J12" s="296"/>
-      <c r="K12" s="296"/>
-      <c r="L12" s="296"/>
-      <c r="M12" s="297"/>
+      <c r="B12" s="277"/>
+      <c r="C12" s="277"/>
+      <c r="D12" s="277"/>
+      <c r="E12" s="277"/>
+      <c r="F12" s="277"/>
+      <c r="G12" s="277"/>
+      <c r="H12" s="278"/>
+      <c r="I12" s="291"/>
+      <c r="J12" s="292"/>
+      <c r="K12" s="292"/>
+      <c r="L12" s="292"/>
+      <c r="M12" s="293"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="301" t="s">
+      <c r="A13" s="297" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="302"/>
-      <c r="C13" s="302"/>
-      <c r="D13" s="302"/>
-      <c r="E13" s="302"/>
-      <c r="F13" s="302"/>
-      <c r="G13" s="302"/>
-      <c r="H13" s="303"/>
-      <c r="I13" s="295"/>
-      <c r="J13" s="296"/>
-      <c r="K13" s="296"/>
-      <c r="L13" s="296"/>
-      <c r="M13" s="297"/>
+      <c r="B13" s="298"/>
+      <c r="C13" s="298"/>
+      <c r="D13" s="298"/>
+      <c r="E13" s="298"/>
+      <c r="F13" s="298"/>
+      <c r="G13" s="298"/>
+      <c r="H13" s="299"/>
+      <c r="I13" s="291"/>
+      <c r="J13" s="292"/>
+      <c r="K13" s="292"/>
+      <c r="L13" s="292"/>
+      <c r="M13" s="293"/>
     </row>
     <row r="14" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="268" t="s">
+      <c r="A14" s="264" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="269"/>
-      <c r="C14" s="269"/>
-      <c r="D14" s="269"/>
-      <c r="E14" s="269"/>
-      <c r="F14" s="269"/>
-      <c r="G14" s="269"/>
-      <c r="H14" s="270"/>
-      <c r="I14" s="298"/>
-      <c r="J14" s="299"/>
-      <c r="K14" s="299"/>
-      <c r="L14" s="299"/>
-      <c r="M14" s="300"/>
+      <c r="B14" s="265"/>
+      <c r="C14" s="265"/>
+      <c r="D14" s="265"/>
+      <c r="E14" s="265"/>
+      <c r="F14" s="265"/>
+      <c r="G14" s="265"/>
+      <c r="H14" s="266"/>
+      <c r="I14" s="294"/>
+      <c r="J14" s="295"/>
+      <c r="K14" s="295"/>
+      <c r="L14" s="295"/>
+      <c r="M14" s="296"/>
     </row>
     <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="324" t="s">
+      <c r="A15" s="320" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="325"/>
-      <c r="C15" s="325"/>
-      <c r="D15" s="325"/>
-      <c r="E15" s="325"/>
-      <c r="F15" s="325"/>
-      <c r="G15" s="325"/>
-      <c r="H15" s="325"/>
-      <c r="I15" s="326" t="s">
+      <c r="B15" s="321"/>
+      <c r="C15" s="321"/>
+      <c r="D15" s="321"/>
+      <c r="E15" s="321"/>
+      <c r="F15" s="321"/>
+      <c r="G15" s="321"/>
+      <c r="H15" s="321"/>
+      <c r="I15" s="322" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="327"/>
-      <c r="K15" s="327"/>
-      <c r="L15" s="327"/>
-      <c r="M15" s="328"/>
+      <c r="J15" s="323"/>
+      <c r="K15" s="323"/>
+      <c r="L15" s="323"/>
+      <c r="M15" s="324"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="102" t="s">
+      <c r="A16" s="98" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="103"/>
-      <c r="C16" s="103"/>
-      <c r="D16" s="103"/>
-      <c r="E16" s="103"/>
-      <c r="F16" s="377"/>
-      <c r="G16" s="377"/>
-      <c r="H16" s="378"/>
-      <c r="I16" s="329" t="s">
-        <v>234</v>
-      </c>
-      <c r="J16" s="330"/>
-      <c r="K16" s="330"/>
-      <c r="L16" s="330"/>
-      <c r="M16" s="331"/>
+      <c r="B16" s="99"/>
+      <c r="C16" s="99"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="373"/>
+      <c r="G16" s="373"/>
+      <c r="H16" s="374"/>
+      <c r="I16" s="325" t="s">
+        <v>80</v>
+      </c>
+      <c r="J16" s="326"/>
+      <c r="K16" s="326"/>
+      <c r="L16" s="326"/>
+      <c r="M16" s="327"/>
     </row>
     <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="104"/>
-      <c r="B17" s="105"/>
-      <c r="C17" s="105"/>
-      <c r="D17" s="105"/>
-      <c r="E17" s="105"/>
-      <c r="F17" s="105"/>
-      <c r="G17" s="105"/>
-      <c r="H17" s="106"/>
-      <c r="I17" s="332"/>
-      <c r="J17" s="306"/>
-      <c r="K17" s="333" t="s">
+      <c r="A17" s="100"/>
+      <c r="B17" s="101"/>
+      <c r="C17" s="101"/>
+      <c r="D17" s="101"/>
+      <c r="E17" s="101"/>
+      <c r="F17" s="101"/>
+      <c r="G17" s="101"/>
+      <c r="H17" s="102"/>
+      <c r="I17" s="328"/>
+      <c r="J17" s="302"/>
+      <c r="K17" s="329" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="333"/>
-      <c r="M17" s="334"/>
+      <c r="L17" s="329"/>
+      <c r="M17" s="330"/>
     </row>
     <row r="18" spans="1:13" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="104"/>
-      <c r="B18" s="105"/>
-      <c r="C18" s="105"/>
-      <c r="D18" s="105"/>
-      <c r="E18" s="105"/>
-      <c r="F18" s="105"/>
-      <c r="G18" s="105"/>
-      <c r="H18" s="106"/>
-      <c r="I18" s="337" t="s">
+      <c r="A18" s="100"/>
+      <c r="B18" s="101"/>
+      <c r="C18" s="101"/>
+      <c r="D18" s="101"/>
+      <c r="E18" s="101"/>
+      <c r="F18" s="101"/>
+      <c r="G18" s="101"/>
+      <c r="H18" s="102"/>
+      <c r="I18" s="333" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="338"/>
-      <c r="K18" s="335"/>
-      <c r="L18" s="335"/>
-      <c r="M18" s="336"/>
+      <c r="J18" s="334"/>
+      <c r="K18" s="331"/>
+      <c r="L18" s="331"/>
+      <c r="M18" s="332"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="309" t="s">
+      <c r="A19" s="305" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="310"/>
-      <c r="C19" s="310"/>
-      <c r="D19" s="310"/>
-      <c r="E19" s="310"/>
-      <c r="F19" s="310"/>
-      <c r="G19" s="310"/>
-      <c r="H19" s="310"/>
-      <c r="I19" s="310"/>
-      <c r="J19" s="310"/>
-      <c r="K19" s="310"/>
-      <c r="L19" s="310"/>
-      <c r="M19" s="311"/>
+      <c r="B19" s="306"/>
+      <c r="C19" s="306"/>
+      <c r="D19" s="306"/>
+      <c r="E19" s="306"/>
+      <c r="F19" s="306"/>
+      <c r="G19" s="306"/>
+      <c r="H19" s="306"/>
+      <c r="I19" s="306"/>
+      <c r="J19" s="306"/>
+      <c r="K19" s="306"/>
+      <c r="L19" s="306"/>
+      <c r="M19" s="307"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="312" t="s">
+      <c r="A20" s="308" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="313"/>
-      <c r="C20" s="313"/>
-      <c r="D20" s="313"/>
-      <c r="E20" s="313" t="s">
+      <c r="B20" s="309"/>
+      <c r="C20" s="309"/>
+      <c r="D20" s="309"/>
+      <c r="E20" s="309" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="313" t="s">
+      <c r="F20" s="309" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="313"/>
-      <c r="H20" s="314" t="s">
+      <c r="G20" s="309"/>
+      <c r="H20" s="310" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="315"/>
-      <c r="J20" s="316" t="s">
+      <c r="I20" s="311"/>
+      <c r="J20" s="312" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="317"/>
-      <c r="L20" s="317"/>
-      <c r="M20" s="318"/>
+      <c r="K20" s="313"/>
+      <c r="L20" s="313"/>
+      <c r="M20" s="314"/>
     </row>
     <row r="21" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="312"/>
-      <c r="B21" s="313"/>
-      <c r="C21" s="313"/>
-      <c r="D21" s="313"/>
-      <c r="E21" s="313"/>
-      <c r="F21" s="313"/>
-      <c r="G21" s="313"/>
-      <c r="H21" s="322" t="s">
+      <c r="A21" s="308"/>
+      <c r="B21" s="309"/>
+      <c r="C21" s="309"/>
+      <c r="D21" s="309"/>
+      <c r="E21" s="309"/>
+      <c r="F21" s="309"/>
+      <c r="G21" s="309"/>
+      <c r="H21" s="318" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="323"/>
-      <c r="J21" s="319"/>
-      <c r="K21" s="320"/>
-      <c r="L21" s="320"/>
-      <c r="M21" s="321"/>
+      <c r="I21" s="319"/>
+      <c r="J21" s="315"/>
+      <c r="K21" s="316"/>
+      <c r="L21" s="316"/>
+      <c r="M21" s="317"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="339"/>
-      <c r="B22" s="339"/>
-      <c r="C22" s="339"/>
-      <c r="D22" s="340"/>
-      <c r="E22" s="107"/>
-      <c r="F22" s="341"/>
-      <c r="G22" s="341"/>
-      <c r="H22" s="108" t="s">
+      <c r="A22" s="335"/>
+      <c r="B22" s="335"/>
+      <c r="C22" s="335"/>
+      <c r="D22" s="336"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="337"/>
+      <c r="G22" s="337"/>
+      <c r="H22" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I22" s="108" t="s">
+      <c r="I22" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="342"/>
-      <c r="K22" s="342"/>
-      <c r="L22" s="342"/>
-      <c r="M22" s="343"/>
+      <c r="J22" s="338"/>
+      <c r="K22" s="338"/>
+      <c r="L22" s="338"/>
+      <c r="M22" s="339"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="339"/>
-      <c r="B23" s="339"/>
-      <c r="C23" s="339"/>
-      <c r="D23" s="340"/>
-      <c r="E23" s="107"/>
-      <c r="F23" s="341"/>
-      <c r="G23" s="341"/>
-      <c r="H23" s="108" t="s">
+      <c r="A23" s="335"/>
+      <c r="B23" s="335"/>
+      <c r="C23" s="335"/>
+      <c r="D23" s="336"/>
+      <c r="E23" s="103"/>
+      <c r="F23" s="337"/>
+      <c r="G23" s="337"/>
+      <c r="H23" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I23" s="108" t="s">
+      <c r="I23" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="342"/>
-      <c r="K23" s="342"/>
-      <c r="L23" s="342"/>
-      <c r="M23" s="343"/>
+      <c r="J23" s="338"/>
+      <c r="K23" s="338"/>
+      <c r="L23" s="338"/>
+      <c r="M23" s="339"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="339"/>
-      <c r="B24" s="339"/>
-      <c r="C24" s="339"/>
-      <c r="D24" s="340"/>
-      <c r="E24" s="107"/>
-      <c r="F24" s="341"/>
-      <c r="G24" s="341"/>
-      <c r="H24" s="108" t="s">
+      <c r="A24" s="335"/>
+      <c r="B24" s="335"/>
+      <c r="C24" s="335"/>
+      <c r="D24" s="336"/>
+      <c r="E24" s="103"/>
+      <c r="F24" s="337"/>
+      <c r="G24" s="337"/>
+      <c r="H24" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I24" s="108" t="s">
+      <c r="I24" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="342"/>
-      <c r="K24" s="342"/>
-      <c r="L24" s="342"/>
-      <c r="M24" s="343"/>
+      <c r="J24" s="338"/>
+      <c r="K24" s="338"/>
+      <c r="L24" s="338"/>
+      <c r="M24" s="339"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="339"/>
-      <c r="B25" s="339"/>
-      <c r="C25" s="339"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="107"/>
-      <c r="F25" s="341"/>
-      <c r="G25" s="341"/>
-      <c r="H25" s="108" t="s">
+      <c r="A25" s="335"/>
+      <c r="B25" s="335"/>
+      <c r="C25" s="335"/>
+      <c r="D25" s="336"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="337"/>
+      <c r="G25" s="337"/>
+      <c r="H25" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I25" s="108" t="s">
+      <c r="I25" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="342"/>
-      <c r="K25" s="342"/>
-      <c r="L25" s="342"/>
-      <c r="M25" s="343"/>
+      <c r="J25" s="338"/>
+      <c r="K25" s="338"/>
+      <c r="L25" s="338"/>
+      <c r="M25" s="339"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="339"/>
-      <c r="B26" s="339"/>
-      <c r="C26" s="339"/>
-      <c r="D26" s="340"/>
-      <c r="E26" s="107"/>
-      <c r="F26" s="341"/>
-      <c r="G26" s="341"/>
-      <c r="H26" s="108" t="s">
+      <c r="A26" s="335"/>
+      <c r="B26" s="335"/>
+      <c r="C26" s="335"/>
+      <c r="D26" s="336"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="337"/>
+      <c r="G26" s="337"/>
+      <c r="H26" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I26" s="108" t="s">
+      <c r="I26" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="342"/>
-      <c r="K26" s="342"/>
-      <c r="L26" s="342"/>
-      <c r="M26" s="343"/>
+      <c r="J26" s="338"/>
+      <c r="K26" s="338"/>
+      <c r="L26" s="338"/>
+      <c r="M26" s="339"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="339"/>
-      <c r="B27" s="339"/>
-      <c r="C27" s="339"/>
-      <c r="D27" s="340"/>
-      <c r="E27" s="107"/>
-      <c r="F27" s="341"/>
-      <c r="G27" s="341"/>
-      <c r="H27" s="108" t="s">
+      <c r="A27" s="335"/>
+      <c r="B27" s="335"/>
+      <c r="C27" s="335"/>
+      <c r="D27" s="336"/>
+      <c r="E27" s="103"/>
+      <c r="F27" s="337"/>
+      <c r="G27" s="337"/>
+      <c r="H27" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I27" s="108" t="s">
+      <c r="I27" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J27" s="342"/>
-      <c r="K27" s="342"/>
-      <c r="L27" s="342"/>
-      <c r="M27" s="343"/>
+      <c r="J27" s="338"/>
+      <c r="K27" s="338"/>
+      <c r="L27" s="338"/>
+      <c r="M27" s="339"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="339"/>
-      <c r="B28" s="339"/>
-      <c r="C28" s="339"/>
-      <c r="D28" s="340"/>
-      <c r="E28" s="107"/>
-      <c r="F28" s="341"/>
-      <c r="G28" s="341"/>
-      <c r="H28" s="108" t="s">
+      <c r="A28" s="335"/>
+      <c r="B28" s="335"/>
+      <c r="C28" s="335"/>
+      <c r="D28" s="336"/>
+      <c r="E28" s="103"/>
+      <c r="F28" s="337"/>
+      <c r="G28" s="337"/>
+      <c r="H28" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="108" t="s">
+      <c r="I28" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J28" s="342"/>
-      <c r="K28" s="342"/>
-      <c r="L28" s="342"/>
-      <c r="M28" s="343"/>
+      <c r="J28" s="338"/>
+      <c r="K28" s="338"/>
+      <c r="L28" s="338"/>
+      <c r="M28" s="339"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="339"/>
-      <c r="B29" s="339"/>
-      <c r="C29" s="339"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="107"/>
-      <c r="F29" s="341"/>
-      <c r="G29" s="341"/>
-      <c r="H29" s="108" t="s">
+      <c r="A29" s="335"/>
+      <c r="B29" s="335"/>
+      <c r="C29" s="335"/>
+      <c r="D29" s="336"/>
+      <c r="E29" s="103"/>
+      <c r="F29" s="337"/>
+      <c r="G29" s="337"/>
+      <c r="H29" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I29" s="108" t="s">
+      <c r="I29" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J29" s="342"/>
-      <c r="K29" s="342"/>
-      <c r="L29" s="342"/>
-      <c r="M29" s="343"/>
+      <c r="J29" s="338"/>
+      <c r="K29" s="338"/>
+      <c r="L29" s="338"/>
+      <c r="M29" s="339"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="349" t="s">
+      <c r="A30" s="345" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="350"/>
-      <c r="C30" s="350"/>
-      <c r="D30" s="350"/>
+      <c r="B30" s="346"/>
+      <c r="C30" s="346"/>
+      <c r="D30" s="346"/>
       <c r="E30" s="14"/>
-      <c r="F30" s="351"/>
-      <c r="G30" s="342"/>
+      <c r="F30" s="347"/>
+      <c r="G30" s="338"/>
       <c r="H30" s="15"/>
       <c r="I30" s="15"/>
-      <c r="J30" s="352"/>
-      <c r="K30" s="352"/>
-      <c r="L30" s="352"/>
-      <c r="M30" s="353"/>
+      <c r="J30" s="348"/>
+      <c r="K30" s="348"/>
+      <c r="L30" s="348"/>
+      <c r="M30" s="349"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="309" t="s">
+      <c r="A31" s="305" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="310"/>
-      <c r="C31" s="310"/>
-      <c r="D31" s="310"/>
-      <c r="E31" s="310"/>
-      <c r="F31" s="310"/>
-      <c r="G31" s="310"/>
-      <c r="H31" s="310"/>
-      <c r="I31" s="310"/>
-      <c r="J31" s="310"/>
-      <c r="K31" s="310"/>
-      <c r="L31" s="310"/>
-      <c r="M31" s="311"/>
+      <c r="B31" s="306"/>
+      <c r="C31" s="306"/>
+      <c r="D31" s="306"/>
+      <c r="E31" s="306"/>
+      <c r="F31" s="306"/>
+      <c r="G31" s="306"/>
+      <c r="H31" s="306"/>
+      <c r="I31" s="306"/>
+      <c r="J31" s="306"/>
+      <c r="K31" s="306"/>
+      <c r="L31" s="306"/>
+      <c r="M31" s="307"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="354" t="s">
+      <c r="A32" s="350" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="355"/>
-      <c r="C32" s="355" t="s">
+      <c r="B32" s="351"/>
+      <c r="C32" s="351" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="355"/>
-      <c r="E32" s="356" t="s">
+      <c r="D32" s="351"/>
+      <c r="E32" s="352" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="357" t="s">
+      <c r="F32" s="353" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="358" t="s">
+      <c r="G32" s="354" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="358"/>
-      <c r="I32" s="358"/>
-      <c r="J32" s="358"/>
-      <c r="K32" s="358"/>
-      <c r="L32" s="355" t="s">
+      <c r="H32" s="354"/>
+      <c r="I32" s="354"/>
+      <c r="J32" s="354"/>
+      <c r="K32" s="354"/>
+      <c r="L32" s="351" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="359"/>
+      <c r="M32" s="355"/>
     </row>
     <row r="33" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="16" t="s">
@@ -5586,15 +5101,15 @@
       <c r="D33" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="356"/>
-      <c r="F33" s="357"/>
-      <c r="G33" s="344" t="s">
+      <c r="E33" s="352"/>
+      <c r="F33" s="353"/>
+      <c r="G33" s="340" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="344"/>
-      <c r="I33" s="344"/>
-      <c r="J33" s="344"/>
-      <c r="K33" s="344"/>
+      <c r="H33" s="340"/>
+      <c r="I33" s="340"/>
+      <c r="J33" s="340"/>
+      <c r="K33" s="340"/>
       <c r="L33" s="18" t="s">
         <v>14</v>
       </c>
@@ -5603,449 +5118,449 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="111"/>
-      <c r="B34" s="108"/>
-      <c r="C34" s="109"/>
-      <c r="D34" s="108"/>
-      <c r="E34" s="109"/>
-      <c r="F34" s="108"/>
-      <c r="G34" s="345"/>
-      <c r="H34" s="346"/>
-      <c r="I34" s="346"/>
-      <c r="J34" s="346"/>
-      <c r="K34" s="347"/>
+      <c r="A34" s="107"/>
+      <c r="B34" s="104"/>
+      <c r="C34" s="105"/>
+      <c r="D34" s="104"/>
+      <c r="E34" s="105"/>
+      <c r="F34" s="104"/>
+      <c r="G34" s="341"/>
+      <c r="H34" s="342"/>
+      <c r="I34" s="342"/>
+      <c r="J34" s="342"/>
+      <c r="K34" s="343"/>
       <c r="L34" s="20"/>
       <c r="M34" s="21"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" s="111"/>
-      <c r="B35" s="108"/>
-      <c r="C35" s="108"/>
-      <c r="D35" s="108"/>
-      <c r="E35" s="108"/>
+      <c r="A35" s="107"/>
+      <c r="B35" s="104"/>
+      <c r="C35" s="104"/>
+      <c r="D35" s="104"/>
+      <c r="E35" s="104"/>
       <c r="F35" s="20"/>
-      <c r="G35" s="345"/>
-      <c r="H35" s="346"/>
-      <c r="I35" s="346"/>
-      <c r="J35" s="346"/>
-      <c r="K35" s="347"/>
+      <c r="G35" s="341"/>
+      <c r="H35" s="342"/>
+      <c r="I35" s="342"/>
+      <c r="J35" s="342"/>
+      <c r="K35" s="343"/>
       <c r="L35" s="20"/>
       <c r="M35" s="21"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" s="111"/>
-      <c r="B36" s="108"/>
-      <c r="C36" s="108"/>
-      <c r="D36" s="108"/>
-      <c r="E36" s="108"/>
+      <c r="A36" s="107"/>
+      <c r="B36" s="104"/>
+      <c r="C36" s="104"/>
+      <c r="D36" s="104"/>
+      <c r="E36" s="104"/>
       <c r="F36" s="20"/>
-      <c r="G36" s="345"/>
-      <c r="H36" s="346"/>
-      <c r="I36" s="346"/>
-      <c r="J36" s="346"/>
-      <c r="K36" s="347"/>
+      <c r="G36" s="341"/>
+      <c r="H36" s="342"/>
+      <c r="I36" s="342"/>
+      <c r="J36" s="342"/>
+      <c r="K36" s="343"/>
       <c r="L36" s="20"/>
       <c r="M36" s="21"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A37" s="111"/>
-      <c r="B37" s="108"/>
-      <c r="C37" s="108"/>
-      <c r="D37" s="108"/>
-      <c r="E37" s="108"/>
+      <c r="A37" s="107"/>
+      <c r="B37" s="104"/>
+      <c r="C37" s="104"/>
+      <c r="D37" s="104"/>
+      <c r="E37" s="104"/>
       <c r="F37" s="20"/>
-      <c r="G37" s="345"/>
-      <c r="H37" s="346"/>
-      <c r="I37" s="346"/>
-      <c r="J37" s="346"/>
-      <c r="K37" s="347"/>
+      <c r="G37" s="341"/>
+      <c r="H37" s="342"/>
+      <c r="I37" s="342"/>
+      <c r="J37" s="342"/>
+      <c r="K37" s="343"/>
       <c r="L37" s="20"/>
       <c r="M37" s="21"/>
-      <c r="Q37" s="348"/>
-      <c r="R37" s="348"/>
+      <c r="Q37" s="344"/>
+      <c r="R37" s="344"/>
       <c r="S37" s="22"/>
-      <c r="T37" s="372"/>
-      <c r="U37" s="372"/>
-      <c r="V37" s="372"/>
+      <c r="T37" s="368"/>
+      <c r="U37" s="368"/>
+      <c r="V37" s="368"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A38" s="111"/>
-      <c r="B38" s="108"/>
-      <c r="C38" s="108"/>
-      <c r="D38" s="108"/>
-      <c r="E38" s="108"/>
+      <c r="A38" s="107"/>
+      <c r="B38" s="104"/>
+      <c r="C38" s="104"/>
+      <c r="D38" s="104"/>
+      <c r="E38" s="104"/>
       <c r="F38" s="20"/>
-      <c r="G38" s="345"/>
-      <c r="H38" s="346"/>
-      <c r="I38" s="346"/>
-      <c r="J38" s="346"/>
-      <c r="K38" s="347"/>
+      <c r="G38" s="341"/>
+      <c r="H38" s="342"/>
+      <c r="I38" s="342"/>
+      <c r="J38" s="342"/>
+      <c r="K38" s="343"/>
       <c r="L38" s="20"/>
       <c r="M38" s="24"/>
-      <c r="Q38" s="348"/>
-      <c r="R38" s="348"/>
+      <c r="Q38" s="344"/>
+      <c r="R38" s="344"/>
       <c r="S38" s="22"/>
-      <c r="T38" s="372"/>
-      <c r="U38" s="372"/>
-      <c r="V38" s="372"/>
+      <c r="T38" s="368"/>
+      <c r="U38" s="368"/>
+      <c r="V38" s="368"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A39" s="111"/>
-      <c r="B39" s="108"/>
-      <c r="C39" s="108"/>
-      <c r="D39" s="108"/>
-      <c r="E39" s="108"/>
+      <c r="A39" s="107"/>
+      <c r="B39" s="104"/>
+      <c r="C39" s="104"/>
+      <c r="D39" s="104"/>
+      <c r="E39" s="104"/>
       <c r="F39" s="20"/>
-      <c r="G39" s="345"/>
-      <c r="H39" s="346"/>
-      <c r="I39" s="346"/>
-      <c r="J39" s="346"/>
-      <c r="K39" s="347"/>
+      <c r="G39" s="341"/>
+      <c r="H39" s="342"/>
+      <c r="I39" s="342"/>
+      <c r="J39" s="342"/>
+      <c r="K39" s="343"/>
       <c r="L39" s="20"/>
       <c r="M39" s="24"/>
       <c r="Q39" s="25"/>
       <c r="R39" s="25"/>
-      <c r="S39" s="373"/>
-      <c r="T39" s="372"/>
-      <c r="U39" s="372"/>
-      <c r="V39" s="372"/>
+      <c r="S39" s="369"/>
+      <c r="T39" s="368"/>
+      <c r="U39" s="368"/>
+      <c r="V39" s="368"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A40" s="111"/>
-      <c r="B40" s="108"/>
-      <c r="C40" s="108"/>
-      <c r="D40" s="108"/>
-      <c r="E40" s="108"/>
+      <c r="A40" s="107"/>
+      <c r="B40" s="104"/>
+      <c r="C40" s="104"/>
+      <c r="D40" s="104"/>
+      <c r="E40" s="104"/>
       <c r="F40" s="20"/>
-      <c r="G40" s="345"/>
-      <c r="H40" s="346"/>
-      <c r="I40" s="346"/>
-      <c r="J40" s="346"/>
-      <c r="K40" s="347"/>
+      <c r="G40" s="341"/>
+      <c r="H40" s="342"/>
+      <c r="I40" s="342"/>
+      <c r="J40" s="342"/>
+      <c r="K40" s="343"/>
       <c r="L40" s="20"/>
       <c r="M40" s="21"/>
       <c r="Q40" s="25"/>
       <c r="R40" s="25"/>
-      <c r="S40" s="373"/>
-      <c r="T40" s="372"/>
-      <c r="U40" s="372"/>
-      <c r="V40" s="372"/>
+      <c r="S40" s="369"/>
+      <c r="T40" s="368"/>
+      <c r="U40" s="368"/>
+      <c r="V40" s="368"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A41" s="111"/>
-      <c r="B41" s="108"/>
-      <c r="C41" s="108"/>
-      <c r="D41" s="108"/>
-      <c r="E41" s="108"/>
+      <c r="A41" s="107"/>
+      <c r="B41" s="104"/>
+      <c r="C41" s="104"/>
+      <c r="D41" s="104"/>
+      <c r="E41" s="104"/>
       <c r="F41" s="20"/>
-      <c r="G41" s="345"/>
-      <c r="H41" s="346"/>
-      <c r="I41" s="346"/>
-      <c r="J41" s="346"/>
-      <c r="K41" s="347"/>
+      <c r="G41" s="341"/>
+      <c r="H41" s="342"/>
+      <c r="I41" s="342"/>
+      <c r="J41" s="342"/>
+      <c r="K41" s="343"/>
       <c r="L41" s="20"/>
       <c r="M41" s="21"/>
     </row>
     <row r="42" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="112"/>
-      <c r="B42" s="113"/>
-      <c r="C42" s="114"/>
-      <c r="D42" s="113"/>
-      <c r="E42" s="114"/>
+      <c r="A42" s="108"/>
+      <c r="B42" s="109"/>
+      <c r="C42" s="110"/>
+      <c r="D42" s="109"/>
+      <c r="E42" s="110"/>
       <c r="F42" s="26"/>
-      <c r="G42" s="412" t="s">
+      <c r="G42" s="408" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="413"/>
-      <c r="I42" s="413"/>
-      <c r="J42" s="413"/>
-      <c r="K42" s="414"/>
+      <c r="H42" s="409"/>
+      <c r="I42" s="409"/>
+      <c r="J42" s="409"/>
+      <c r="K42" s="410"/>
       <c r="L42" s="26"/>
       <c r="M42" s="27"/>
     </row>
     <row r="43" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="392" t="s">
+      <c r="A43" s="388" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="393"/>
-      <c r="C43" s="393"/>
-      <c r="D43" s="393"/>
-      <c r="E43" s="393"/>
-      <c r="F43" s="393"/>
-      <c r="G43" s="393"/>
-      <c r="H43" s="394"/>
-      <c r="I43" s="415" t="s">
+      <c r="B43" s="389"/>
+      <c r="C43" s="389"/>
+      <c r="D43" s="389"/>
+      <c r="E43" s="389"/>
+      <c r="F43" s="389"/>
+      <c r="G43" s="389"/>
+      <c r="H43" s="390"/>
+      <c r="I43" s="411" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="416"/>
-      <c r="K43" s="416"/>
-      <c r="L43" s="416"/>
-      <c r="M43" s="417"/>
+      <c r="J43" s="412"/>
+      <c r="K43" s="412"/>
+      <c r="L43" s="412"/>
+      <c r="M43" s="413"/>
     </row>
     <row r="44" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="395"/>
-      <c r="B44" s="396"/>
-      <c r="C44" s="396"/>
-      <c r="D44" s="396"/>
-      <c r="E44" s="396"/>
-      <c r="F44" s="396"/>
-      <c r="G44" s="396"/>
-      <c r="H44" s="397"/>
-      <c r="I44" s="418"/>
-      <c r="J44" s="419"/>
-      <c r="K44" s="419"/>
-      <c r="L44" s="419"/>
-      <c r="M44" s="420"/>
+      <c r="A44" s="391"/>
+      <c r="B44" s="392"/>
+      <c r="C44" s="392"/>
+      <c r="D44" s="392"/>
+      <c r="E44" s="392"/>
+      <c r="F44" s="392"/>
+      <c r="G44" s="392"/>
+      <c r="H44" s="393"/>
+      <c r="I44" s="414"/>
+      <c r="J44" s="415"/>
+      <c r="K44" s="415"/>
+      <c r="L44" s="415"/>
+      <c r="M44" s="416"/>
     </row>
     <row r="45" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="360" t="s">
+      <c r="A45" s="356" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="361"/>
-      <c r="C45" s="361"/>
-      <c r="D45" s="361"/>
-      <c r="E45" s="361"/>
-      <c r="F45" s="361"/>
-      <c r="G45" s="361"/>
-      <c r="H45" s="362"/>
-      <c r="I45" s="363" t="s">
+      <c r="B45" s="357"/>
+      <c r="C45" s="357"/>
+      <c r="D45" s="357"/>
+      <c r="E45" s="357"/>
+      <c r="F45" s="357"/>
+      <c r="G45" s="357"/>
+      <c r="H45" s="358"/>
+      <c r="I45" s="359" t="s">
         <v>36</v>
       </c>
-      <c r="J45" s="364"/>
-      <c r="K45" s="364"/>
-      <c r="L45" s="364"/>
-      <c r="M45" s="365"/>
+      <c r="J45" s="360"/>
+      <c r="K45" s="360"/>
+      <c r="L45" s="360"/>
+      <c r="M45" s="361"/>
     </row>
     <row r="46" spans="1:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="360" t="s">
+      <c r="A46" s="356" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="361"/>
-      <c r="C46" s="361"/>
-      <c r="D46" s="361"/>
-      <c r="E46" s="361"/>
-      <c r="F46" s="361"/>
-      <c r="G46" s="361"/>
-      <c r="H46" s="362"/>
-      <c r="I46" s="363"/>
-      <c r="J46" s="364"/>
-      <c r="K46" s="364"/>
-      <c r="L46" s="364"/>
-      <c r="M46" s="365"/>
+      <c r="B46" s="357"/>
+      <c r="C46" s="357"/>
+      <c r="D46" s="357"/>
+      <c r="E46" s="357"/>
+      <c r="F46" s="357"/>
+      <c r="G46" s="357"/>
+      <c r="H46" s="358"/>
+      <c r="I46" s="359"/>
+      <c r="J46" s="360"/>
+      <c r="K46" s="360"/>
+      <c r="L46" s="360"/>
+      <c r="M46" s="361"/>
     </row>
     <row r="47" spans="1:22" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="366"/>
-      <c r="B47" s="367"/>
-      <c r="C47" s="367"/>
-      <c r="D47" s="367"/>
-      <c r="E47" s="367"/>
-      <c r="F47" s="367"/>
-      <c r="G47" s="367"/>
-      <c r="H47" s="368"/>
-      <c r="I47" s="369" t="s">
+      <c r="A47" s="362"/>
+      <c r="B47" s="363"/>
+      <c r="C47" s="363"/>
+      <c r="D47" s="363"/>
+      <c r="E47" s="363"/>
+      <c r="F47" s="363"/>
+      <c r="G47" s="363"/>
+      <c r="H47" s="364"/>
+      <c r="I47" s="365" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="370"/>
-      <c r="K47" s="370"/>
-      <c r="L47" s="370"/>
-      <c r="M47" s="371"/>
+      <c r="J47" s="366"/>
+      <c r="K47" s="366"/>
+      <c r="L47" s="366"/>
+      <c r="M47" s="367"/>
     </row>
     <row r="48" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="389" t="s">
+      <c r="A48" s="385" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="390"/>
-      <c r="C48" s="390"/>
-      <c r="D48" s="390"/>
-      <c r="E48" s="390"/>
-      <c r="F48" s="390"/>
-      <c r="G48" s="390"/>
-      <c r="H48" s="390"/>
-      <c r="I48" s="390"/>
-      <c r="J48" s="390"/>
-      <c r="K48" s="390"/>
-      <c r="L48" s="390"/>
-      <c r="M48" s="391"/>
+      <c r="B48" s="386"/>
+      <c r="C48" s="386"/>
+      <c r="D48" s="386"/>
+      <c r="E48" s="386"/>
+      <c r="F48" s="386"/>
+      <c r="G48" s="386"/>
+      <c r="H48" s="386"/>
+      <c r="I48" s="386"/>
+      <c r="J48" s="386"/>
+      <c r="K48" s="386"/>
+      <c r="L48" s="386"/>
+      <c r="M48" s="387"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="392" t="s">
+      <c r="A49" s="388" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="393"/>
-      <c r="C49" s="393"/>
-      <c r="D49" s="393"/>
-      <c r="E49" s="393"/>
-      <c r="F49" s="393"/>
-      <c r="G49" s="393"/>
-      <c r="H49" s="394"/>
-      <c r="I49" s="400" t="s">
+      <c r="B49" s="389"/>
+      <c r="C49" s="389"/>
+      <c r="D49" s="389"/>
+      <c r="E49" s="389"/>
+      <c r="F49" s="389"/>
+      <c r="G49" s="389"/>
+      <c r="H49" s="390"/>
+      <c r="I49" s="396" t="s">
         <v>40</v>
       </c>
-      <c r="J49" s="401"/>
-      <c r="K49" s="401"/>
-      <c r="L49" s="401"/>
-      <c r="M49" s="402"/>
+      <c r="J49" s="397"/>
+      <c r="K49" s="397"/>
+      <c r="L49" s="397"/>
+      <c r="M49" s="398"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="395"/>
-      <c r="B50" s="396"/>
-      <c r="C50" s="396"/>
-      <c r="D50" s="396"/>
-      <c r="E50" s="396"/>
-      <c r="F50" s="396"/>
-      <c r="G50" s="396"/>
-      <c r="H50" s="397"/>
-      <c r="I50" s="403"/>
-      <c r="J50" s="404"/>
-      <c r="K50" s="404"/>
-      <c r="L50" s="404"/>
-      <c r="M50" s="405"/>
+      <c r="A50" s="391"/>
+      <c r="B50" s="392"/>
+      <c r="C50" s="392"/>
+      <c r="D50" s="392"/>
+      <c r="E50" s="392"/>
+      <c r="F50" s="392"/>
+      <c r="G50" s="392"/>
+      <c r="H50" s="393"/>
+      <c r="I50" s="399"/>
+      <c r="J50" s="400"/>
+      <c r="K50" s="400"/>
+      <c r="L50" s="400"/>
+      <c r="M50" s="401"/>
     </row>
     <row r="51" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="398"/>
-      <c r="B51" s="399"/>
-      <c r="C51" s="399"/>
-      <c r="D51" s="399"/>
-      <c r="E51" s="396"/>
-      <c r="F51" s="396"/>
-      <c r="G51" s="396"/>
-      <c r="H51" s="397"/>
-      <c r="I51" s="406" t="s">
+      <c r="A51" s="394"/>
+      <c r="B51" s="395"/>
+      <c r="C51" s="395"/>
+      <c r="D51" s="395"/>
+      <c r="E51" s="392"/>
+      <c r="F51" s="392"/>
+      <c r="G51" s="392"/>
+      <c r="H51" s="393"/>
+      <c r="I51" s="402" t="s">
         <v>41</v>
       </c>
-      <c r="J51" s="407"/>
-      <c r="K51" s="408"/>
-      <c r="L51" s="408"/>
-      <c r="M51" s="409"/>
+      <c r="J51" s="403"/>
+      <c r="K51" s="404"/>
+      <c r="L51" s="404"/>
+      <c r="M51" s="405"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="389" t="s">
+      <c r="A52" s="385" t="s">
         <v>42</v>
       </c>
-      <c r="B52" s="390"/>
-      <c r="C52" s="390"/>
-      <c r="D52" s="390"/>
-      <c r="E52" s="115" t="s">
+      <c r="B52" s="386"/>
+      <c r="C52" s="386"/>
+      <c r="D52" s="386"/>
+      <c r="E52" s="111" t="s">
         <v>44</v>
       </c>
-      <c r="F52" s="116"/>
-      <c r="G52" s="410" t="s">
+      <c r="F52" s="112"/>
+      <c r="G52" s="406" t="s">
         <v>45</v>
       </c>
-      <c r="H52" s="410"/>
-      <c r="I52" s="410"/>
-      <c r="J52" s="411"/>
-      <c r="K52" s="390" t="s">
+      <c r="H52" s="406"/>
+      <c r="I52" s="406"/>
+      <c r="J52" s="407"/>
+      <c r="K52" s="386" t="s">
         <v>50</v>
       </c>
-      <c r="L52" s="390"/>
-      <c r="M52" s="391"/>
+      <c r="L52" s="386"/>
+      <c r="M52" s="387"/>
     </row>
     <row r="53" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="379" t="s">
+      <c r="A53" s="375" t="s">
         <v>43</v>
       </c>
-      <c r="B53" s="380"/>
-      <c r="C53" s="380"/>
-      <c r="D53" s="380"/>
-      <c r="E53" s="117"/>
-      <c r="F53" s="110"/>
-      <c r="G53" s="110"/>
-      <c r="H53" s="110"/>
-      <c r="I53" s="110"/>
-      <c r="J53" s="118"/>
-      <c r="K53" s="380" t="s">
+      <c r="B53" s="376"/>
+      <c r="C53" s="376"/>
+      <c r="D53" s="376"/>
+      <c r="E53" s="113"/>
+      <c r="F53" s="106"/>
+      <c r="G53" s="106"/>
+      <c r="H53" s="106"/>
+      <c r="I53" s="106"/>
+      <c r="J53" s="114"/>
+      <c r="K53" s="376" t="s">
         <v>52</v>
       </c>
-      <c r="L53" s="380"/>
-      <c r="M53" s="381"/>
+      <c r="L53" s="376"/>
+      <c r="M53" s="377"/>
     </row>
     <row r="54" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="379"/>
-      <c r="B54" s="380"/>
-      <c r="C54" s="380"/>
-      <c r="D54" s="380"/>
-      <c r="E54" s="382" t="s">
+      <c r="A54" s="375"/>
+      <c r="B54" s="376"/>
+      <c r="C54" s="376"/>
+      <c r="D54" s="376"/>
+      <c r="E54" s="378" t="s">
         <v>46</v>
       </c>
-      <c r="F54" s="383"/>
-      <c r="G54" s="119"/>
-      <c r="H54" s="374" t="s">
+      <c r="F54" s="379"/>
+      <c r="G54" s="115"/>
+      <c r="H54" s="370" t="s">
         <v>46</v>
       </c>
-      <c r="I54" s="374"/>
-      <c r="J54" s="375"/>
-      <c r="K54" s="380"/>
-      <c r="L54" s="380"/>
-      <c r="M54" s="381"/>
+      <c r="I54" s="370"/>
+      <c r="J54" s="371"/>
+      <c r="K54" s="376"/>
+      <c r="L54" s="376"/>
+      <c r="M54" s="377"/>
     </row>
     <row r="55" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="379"/>
-      <c r="B55" s="380"/>
-      <c r="C55" s="380"/>
-      <c r="D55" s="380"/>
-      <c r="E55" s="382" t="s">
+      <c r="A55" s="375"/>
+      <c r="B55" s="376"/>
+      <c r="C55" s="376"/>
+      <c r="D55" s="376"/>
+      <c r="E55" s="378" t="s">
         <v>47</v>
       </c>
-      <c r="F55" s="383"/>
-      <c r="G55" s="383"/>
-      <c r="H55" s="374" t="s">
+      <c r="F55" s="379"/>
+      <c r="G55" s="379"/>
+      <c r="H55" s="370" t="s">
         <v>48</v>
       </c>
-      <c r="I55" s="374"/>
-      <c r="J55" s="375"/>
-      <c r="K55" s="380"/>
-      <c r="L55" s="380"/>
-      <c r="M55" s="381"/>
+      <c r="I55" s="370"/>
+      <c r="J55" s="371"/>
+      <c r="K55" s="376"/>
+      <c r="L55" s="376"/>
+      <c r="M55" s="377"/>
     </row>
     <row r="56" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="332"/>
-      <c r="B56" s="306"/>
-      <c r="C56" s="306"/>
-      <c r="D56" s="307"/>
-      <c r="E56" s="382"/>
-      <c r="F56" s="383"/>
-      <c r="G56" s="383"/>
-      <c r="H56" s="374"/>
-      <c r="I56" s="374"/>
-      <c r="J56" s="375"/>
-      <c r="K56" s="387" t="s">
+      <c r="A56" s="328"/>
+      <c r="B56" s="302"/>
+      <c r="C56" s="302"/>
+      <c r="D56" s="303"/>
+      <c r="E56" s="378"/>
+      <c r="F56" s="379"/>
+      <c r="G56" s="379"/>
+      <c r="H56" s="370"/>
+      <c r="I56" s="370"/>
+      <c r="J56" s="371"/>
+      <c r="K56" s="383" t="s">
         <v>51</v>
       </c>
-      <c r="L56" s="387"/>
-      <c r="M56" s="388"/>
+      <c r="L56" s="383"/>
+      <c r="M56" s="384"/>
     </row>
     <row r="57" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="332"/>
-      <c r="B57" s="306"/>
-      <c r="C57" s="306"/>
-      <c r="D57" s="307"/>
-      <c r="E57" s="382"/>
-      <c r="F57" s="383"/>
-      <c r="G57" s="119"/>
-      <c r="H57" s="374" t="s">
+      <c r="A57" s="328"/>
+      <c r="B57" s="302"/>
+      <c r="C57" s="302"/>
+      <c r="D57" s="303"/>
+      <c r="E57" s="378"/>
+      <c r="F57" s="379"/>
+      <c r="G57" s="115"/>
+      <c r="H57" s="370" t="s">
         <v>49</v>
       </c>
-      <c r="I57" s="374"/>
-      <c r="J57" s="375"/>
-      <c r="K57" s="120"/>
-      <c r="L57" s="121"/>
-      <c r="M57" s="122"/>
+      <c r="I57" s="370"/>
+      <c r="J57" s="371"/>
+      <c r="K57" s="116"/>
+      <c r="L57" s="117"/>
+      <c r="M57" s="118"/>
     </row>
     <row r="58" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="384"/>
-      <c r="B58" s="385"/>
-      <c r="C58" s="385"/>
-      <c r="D58" s="386"/>
-      <c r="E58" s="337"/>
-      <c r="F58" s="338"/>
-      <c r="G58" s="338"/>
-      <c r="H58" s="338"/>
-      <c r="I58" s="338"/>
-      <c r="J58" s="376"/>
-      <c r="K58" s="123"/>
-      <c r="L58" s="124"/>
-      <c r="M58" s="125"/>
+      <c r="A58" s="380"/>
+      <c r="B58" s="381"/>
+      <c r="C58" s="381"/>
+      <c r="D58" s="382"/>
+      <c r="E58" s="333"/>
+      <c r="F58" s="334"/>
+      <c r="G58" s="334"/>
+      <c r="H58" s="334"/>
+      <c r="I58" s="334"/>
+      <c r="J58" s="372"/>
+      <c r="K58" s="119"/>
+      <c r="L58" s="120"/>
+      <c r="M58" s="121"/>
     </row>
     <row r="59" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="28"/>
@@ -6892,1012 +6407,1012 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="440" t="s">
-        <v>233</v>
-      </c>
-      <c r="B1" s="441"/>
-      <c r="C1" s="283" t="s">
+      <c r="A1" s="436" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="437"/>
+      <c r="C1" s="279" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="283"/>
-      <c r="E1" s="283"/>
-      <c r="F1" s="283"/>
-      <c r="G1" s="283"/>
-      <c r="H1" s="283"/>
-      <c r="I1" s="283"/>
-      <c r="J1" s="283"/>
-      <c r="K1" s="283"/>
-      <c r="L1" s="284" t="s">
+      <c r="D1" s="279"/>
+      <c r="E1" s="279"/>
+      <c r="F1" s="279"/>
+      <c r="G1" s="279"/>
+      <c r="H1" s="279"/>
+      <c r="I1" s="279"/>
+      <c r="J1" s="279"/>
+      <c r="K1" s="279"/>
+      <c r="L1" s="280" t="s">
         <v>61</v>
       </c>
-      <c r="M1" s="285"/>
+      <c r="M1" s="281"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="309" t="s">
+      <c r="A2" s="305" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="310"/>
-      <c r="C2" s="310"/>
-      <c r="D2" s="310"/>
-      <c r="E2" s="310"/>
-      <c r="F2" s="310"/>
-      <c r="G2" s="310"/>
-      <c r="H2" s="310"/>
-      <c r="I2" s="310"/>
-      <c r="J2" s="310"/>
-      <c r="K2" s="310"/>
-      <c r="L2" s="310"/>
-      <c r="M2" s="311"/>
+      <c r="B2" s="306"/>
+      <c r="C2" s="306"/>
+      <c r="D2" s="306"/>
+      <c r="E2" s="306"/>
+      <c r="F2" s="306"/>
+      <c r="G2" s="306"/>
+      <c r="H2" s="306"/>
+      <c r="I2" s="306"/>
+      <c r="J2" s="306"/>
+      <c r="K2" s="306"/>
+      <c r="L2" s="306"/>
+      <c r="M2" s="307"/>
     </row>
     <row r="3" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="312" t="s">
+      <c r="A3" s="308" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="313"/>
-      <c r="C3" s="313"/>
-      <c r="D3" s="313"/>
-      <c r="E3" s="313" t="s">
+      <c r="B3" s="309"/>
+      <c r="C3" s="309"/>
+      <c r="D3" s="309"/>
+      <c r="E3" s="309" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="313" t="s">
+      <c r="F3" s="309" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="313"/>
-      <c r="H3" s="314" t="s">
+      <c r="G3" s="309"/>
+      <c r="H3" s="310" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="315"/>
-      <c r="J3" s="316" t="s">
+      <c r="I3" s="311"/>
+      <c r="J3" s="312" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="317"/>
-      <c r="L3" s="317"/>
-      <c r="M3" s="318"/>
+      <c r="K3" s="313"/>
+      <c r="L3" s="313"/>
+      <c r="M3" s="314"/>
     </row>
     <row r="4" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="312"/>
-      <c r="B4" s="313"/>
-      <c r="C4" s="313"/>
-      <c r="D4" s="313"/>
-      <c r="E4" s="313"/>
-      <c r="F4" s="313"/>
-      <c r="G4" s="313"/>
-      <c r="H4" s="322" t="s">
+      <c r="A4" s="308"/>
+      <c r="B4" s="309"/>
+      <c r="C4" s="309"/>
+      <c r="D4" s="309"/>
+      <c r="E4" s="309"/>
+      <c r="F4" s="309"/>
+      <c r="G4" s="309"/>
+      <c r="H4" s="318" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="323"/>
-      <c r="J4" s="319"/>
-      <c r="K4" s="320"/>
-      <c r="L4" s="320"/>
-      <c r="M4" s="321"/>
+      <c r="I4" s="319"/>
+      <c r="J4" s="315"/>
+      <c r="K4" s="316"/>
+      <c r="L4" s="316"/>
+      <c r="M4" s="317"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="421"/>
-      <c r="B5" s="339"/>
-      <c r="C5" s="339"/>
-      <c r="D5" s="339"/>
+      <c r="A5" s="417"/>
+      <c r="B5" s="335"/>
+      <c r="C5" s="335"/>
+      <c r="D5" s="335"/>
       <c r="E5" s="10"/>
-      <c r="F5" s="165"/>
-      <c r="G5" s="167"/>
-      <c r="H5" s="108" t="s">
+      <c r="F5" s="161"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I5" s="108" t="s">
+      <c r="I5" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J5" s="342"/>
-      <c r="K5" s="342"/>
-      <c r="L5" s="342"/>
-      <c r="M5" s="343"/>
+      <c r="J5" s="338"/>
+      <c r="K5" s="338"/>
+      <c r="L5" s="338"/>
+      <c r="M5" s="339"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="421"/>
-      <c r="B6" s="339"/>
-      <c r="C6" s="339"/>
-      <c r="D6" s="339"/>
+      <c r="A6" s="417"/>
+      <c r="B6" s="335"/>
+      <c r="C6" s="335"/>
+      <c r="D6" s="335"/>
       <c r="E6" s="10"/>
-      <c r="F6" s="165"/>
-      <c r="G6" s="167"/>
-      <c r="H6" s="108" t="s">
+      <c r="F6" s="161"/>
+      <c r="G6" s="163"/>
+      <c r="H6" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I6" s="108" t="s">
+      <c r="I6" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J6" s="342"/>
-      <c r="K6" s="342"/>
-      <c r="L6" s="342"/>
-      <c r="M6" s="343"/>
+      <c r="J6" s="338"/>
+      <c r="K6" s="338"/>
+      <c r="L6" s="338"/>
+      <c r="M6" s="339"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="421"/>
-      <c r="B7" s="339"/>
-      <c r="C7" s="339"/>
-      <c r="D7" s="339"/>
+      <c r="A7" s="417"/>
+      <c r="B7" s="335"/>
+      <c r="C7" s="335"/>
+      <c r="D7" s="335"/>
       <c r="E7" s="10"/>
-      <c r="F7" s="165"/>
-      <c r="G7" s="167"/>
-      <c r="H7" s="108" t="s">
+      <c r="F7" s="161"/>
+      <c r="G7" s="163"/>
+      <c r="H7" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="108" t="s">
+      <c r="I7" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J7" s="342"/>
-      <c r="K7" s="342"/>
-      <c r="L7" s="342"/>
-      <c r="M7" s="343"/>
+      <c r="J7" s="338"/>
+      <c r="K7" s="338"/>
+      <c r="L7" s="338"/>
+      <c r="M7" s="339"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="421"/>
-      <c r="B8" s="339"/>
-      <c r="C8" s="339"/>
-      <c r="D8" s="339"/>
+      <c r="A8" s="417"/>
+      <c r="B8" s="335"/>
+      <c r="C8" s="335"/>
+      <c r="D8" s="335"/>
       <c r="E8" s="10"/>
-      <c r="F8" s="165"/>
-      <c r="G8" s="167"/>
-      <c r="H8" s="108" t="s">
+      <c r="F8" s="161"/>
+      <c r="G8" s="163"/>
+      <c r="H8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="108" t="s">
+      <c r="I8" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J8" s="342"/>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="343"/>
+      <c r="J8" s="338"/>
+      <c r="K8" s="338"/>
+      <c r="L8" s="338"/>
+      <c r="M8" s="339"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="421"/>
-      <c r="B9" s="339"/>
-      <c r="C9" s="339"/>
-      <c r="D9" s="339"/>
+      <c r="A9" s="417"/>
+      <c r="B9" s="335"/>
+      <c r="C9" s="335"/>
+      <c r="D9" s="335"/>
       <c r="E9" s="10"/>
-      <c r="F9" s="165"/>
-      <c r="G9" s="167"/>
-      <c r="H9" s="108" t="s">
+      <c r="F9" s="161"/>
+      <c r="G9" s="163"/>
+      <c r="H9" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="108" t="s">
+      <c r="I9" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J9" s="342"/>
-      <c r="K9" s="342"/>
-      <c r="L9" s="342"/>
-      <c r="M9" s="343"/>
+      <c r="J9" s="338"/>
+      <c r="K9" s="338"/>
+      <c r="L9" s="338"/>
+      <c r="M9" s="339"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="421"/>
-      <c r="B10" s="339"/>
-      <c r="C10" s="339"/>
-      <c r="D10" s="339"/>
+      <c r="A10" s="417"/>
+      <c r="B10" s="335"/>
+      <c r="C10" s="335"/>
+      <c r="D10" s="335"/>
       <c r="E10" s="10"/>
-      <c r="F10" s="165"/>
-      <c r="G10" s="167"/>
-      <c r="H10" s="108" t="s">
+      <c r="F10" s="161"/>
+      <c r="G10" s="163"/>
+      <c r="H10" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="108" t="s">
+      <c r="I10" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="342"/>
-      <c r="K10" s="342"/>
-      <c r="L10" s="342"/>
-      <c r="M10" s="343"/>
+      <c r="J10" s="338"/>
+      <c r="K10" s="338"/>
+      <c r="L10" s="338"/>
+      <c r="M10" s="339"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="421"/>
-      <c r="B11" s="339"/>
-      <c r="C11" s="339"/>
-      <c r="D11" s="339"/>
+      <c r="A11" s="417"/>
+      <c r="B11" s="335"/>
+      <c r="C11" s="335"/>
+      <c r="D11" s="335"/>
       <c r="E11" s="10"/>
-      <c r="F11" s="165"/>
-      <c r="G11" s="167"/>
-      <c r="H11" s="108" t="s">
+      <c r="F11" s="161"/>
+      <c r="G11" s="163"/>
+      <c r="H11" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="108" t="s">
+      <c r="I11" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J11" s="342"/>
-      <c r="K11" s="342"/>
-      <c r="L11" s="342"/>
-      <c r="M11" s="343"/>
+      <c r="J11" s="338"/>
+      <c r="K11" s="338"/>
+      <c r="L11" s="338"/>
+      <c r="M11" s="339"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="421"/>
-      <c r="B12" s="339"/>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
+      <c r="A12" s="417"/>
+      <c r="B12" s="335"/>
+      <c r="C12" s="335"/>
+      <c r="D12" s="335"/>
       <c r="E12" s="10"/>
-      <c r="F12" s="165"/>
-      <c r="G12" s="167"/>
-      <c r="H12" s="108" t="s">
+      <c r="F12" s="161"/>
+      <c r="G12" s="163"/>
+      <c r="H12" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I12" s="108" t="s">
+      <c r="I12" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J12" s="342"/>
-      <c r="K12" s="342"/>
-      <c r="L12" s="342"/>
-      <c r="M12" s="343"/>
+      <c r="J12" s="338"/>
+      <c r="K12" s="338"/>
+      <c r="L12" s="338"/>
+      <c r="M12" s="339"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="421"/>
-      <c r="B13" s="339"/>
-      <c r="C13" s="339"/>
-      <c r="D13" s="339"/>
+      <c r="A13" s="417"/>
+      <c r="B13" s="335"/>
+      <c r="C13" s="335"/>
+      <c r="D13" s="335"/>
       <c r="E13" s="10"/>
-      <c r="F13" s="165"/>
-      <c r="G13" s="167"/>
-      <c r="H13" s="108" t="s">
+      <c r="F13" s="161"/>
+      <c r="G13" s="163"/>
+      <c r="H13" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I13" s="108" t="s">
+      <c r="I13" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J13" s="342"/>
-      <c r="K13" s="342"/>
-      <c r="L13" s="342"/>
-      <c r="M13" s="343"/>
+      <c r="J13" s="338"/>
+      <c r="K13" s="338"/>
+      <c r="L13" s="338"/>
+      <c r="M13" s="339"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="421"/>
-      <c r="B14" s="339"/>
-      <c r="C14" s="339"/>
-      <c r="D14" s="339"/>
+      <c r="A14" s="417"/>
+      <c r="B14" s="335"/>
+      <c r="C14" s="335"/>
+      <c r="D14" s="335"/>
       <c r="E14" s="10"/>
-      <c r="F14" s="165"/>
-      <c r="G14" s="167"/>
-      <c r="H14" s="108" t="s">
+      <c r="F14" s="161"/>
+      <c r="G14" s="163"/>
+      <c r="H14" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I14" s="108" t="s">
+      <c r="I14" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J14" s="342"/>
-      <c r="K14" s="342"/>
-      <c r="L14" s="342"/>
-      <c r="M14" s="343"/>
+      <c r="J14" s="338"/>
+      <c r="K14" s="338"/>
+      <c r="L14" s="338"/>
+      <c r="M14" s="339"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="421"/>
-      <c r="B15" s="339"/>
-      <c r="C15" s="339"/>
-      <c r="D15" s="339"/>
+      <c r="A15" s="417"/>
+      <c r="B15" s="335"/>
+      <c r="C15" s="335"/>
+      <c r="D15" s="335"/>
       <c r="E15" s="10"/>
-      <c r="F15" s="165"/>
-      <c r="G15" s="167"/>
-      <c r="H15" s="108" t="s">
+      <c r="F15" s="161"/>
+      <c r="G15" s="163"/>
+      <c r="H15" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I15" s="108" t="s">
+      <c r="I15" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J15" s="342"/>
-      <c r="K15" s="342"/>
-      <c r="L15" s="342"/>
-      <c r="M15" s="343"/>
+      <c r="J15" s="338"/>
+      <c r="K15" s="338"/>
+      <c r="L15" s="338"/>
+      <c r="M15" s="339"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="421"/>
-      <c r="B16" s="339"/>
-      <c r="C16" s="339"/>
-      <c r="D16" s="339"/>
+      <c r="A16" s="417"/>
+      <c r="B16" s="335"/>
+      <c r="C16" s="335"/>
+      <c r="D16" s="335"/>
       <c r="E16" s="10"/>
-      <c r="F16" s="165"/>
-      <c r="G16" s="167"/>
-      <c r="H16" s="108" t="s">
+      <c r="F16" s="161"/>
+      <c r="G16" s="163"/>
+      <c r="H16" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I16" s="108" t="s">
+      <c r="I16" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J16" s="342"/>
-      <c r="K16" s="342"/>
-      <c r="L16" s="342"/>
-      <c r="M16" s="343"/>
+      <c r="J16" s="338"/>
+      <c r="K16" s="338"/>
+      <c r="L16" s="338"/>
+      <c r="M16" s="339"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="421"/>
-      <c r="B17" s="339"/>
-      <c r="C17" s="339"/>
-      <c r="D17" s="339"/>
+      <c r="A17" s="417"/>
+      <c r="B17" s="335"/>
+      <c r="C17" s="335"/>
+      <c r="D17" s="335"/>
       <c r="E17" s="10"/>
-      <c r="F17" s="165"/>
-      <c r="G17" s="167"/>
-      <c r="H17" s="108" t="s">
+      <c r="F17" s="161"/>
+      <c r="G17" s="163"/>
+      <c r="H17" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I17" s="108" t="s">
+      <c r="I17" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J17" s="342"/>
-      <c r="K17" s="342"/>
-      <c r="L17" s="342"/>
-      <c r="M17" s="343"/>
+      <c r="J17" s="338"/>
+      <c r="K17" s="338"/>
+      <c r="L17" s="338"/>
+      <c r="M17" s="339"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="421"/>
-      <c r="B18" s="339"/>
-      <c r="C18" s="339"/>
-      <c r="D18" s="339"/>
+      <c r="A18" s="417"/>
+      <c r="B18" s="335"/>
+      <c r="C18" s="335"/>
+      <c r="D18" s="335"/>
       <c r="E18" s="10"/>
-      <c r="F18" s="165"/>
-      <c r="G18" s="167"/>
-      <c r="H18" s="108" t="s">
+      <c r="F18" s="161"/>
+      <c r="G18" s="163"/>
+      <c r="H18" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I18" s="108" t="s">
+      <c r="I18" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J18" s="342"/>
-      <c r="K18" s="342"/>
-      <c r="L18" s="342"/>
-      <c r="M18" s="343"/>
+      <c r="J18" s="338"/>
+      <c r="K18" s="338"/>
+      <c r="L18" s="338"/>
+      <c r="M18" s="339"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="421"/>
-      <c r="B19" s="339"/>
-      <c r="C19" s="339"/>
-      <c r="D19" s="339"/>
+      <c r="A19" s="417"/>
+      <c r="B19" s="335"/>
+      <c r="C19" s="335"/>
+      <c r="D19" s="335"/>
       <c r="E19" s="10"/>
-      <c r="F19" s="165"/>
-      <c r="G19" s="167"/>
-      <c r="H19" s="108" t="s">
+      <c r="F19" s="161"/>
+      <c r="G19" s="163"/>
+      <c r="H19" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I19" s="108" t="s">
+      <c r="I19" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J19" s="342"/>
-      <c r="K19" s="342"/>
-      <c r="L19" s="342"/>
-      <c r="M19" s="343"/>
+      <c r="J19" s="338"/>
+      <c r="K19" s="338"/>
+      <c r="L19" s="338"/>
+      <c r="M19" s="339"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="421"/>
-      <c r="B20" s="339"/>
-      <c r="C20" s="339"/>
-      <c r="D20" s="339"/>
+      <c r="A20" s="417"/>
+      <c r="B20" s="335"/>
+      <c r="C20" s="335"/>
+      <c r="D20" s="335"/>
       <c r="E20" s="10"/>
-      <c r="F20" s="165"/>
-      <c r="G20" s="167"/>
-      <c r="H20" s="108" t="s">
+      <c r="F20" s="161"/>
+      <c r="G20" s="163"/>
+      <c r="H20" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I20" s="108" t="s">
+      <c r="I20" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J20" s="342"/>
-      <c r="K20" s="342"/>
-      <c r="L20" s="342"/>
-      <c r="M20" s="343"/>
+      <c r="J20" s="338"/>
+      <c r="K20" s="338"/>
+      <c r="L20" s="338"/>
+      <c r="M20" s="339"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="421"/>
-      <c r="B21" s="339"/>
-      <c r="C21" s="339"/>
-      <c r="D21" s="339"/>
+      <c r="A21" s="417"/>
+      <c r="B21" s="335"/>
+      <c r="C21" s="335"/>
+      <c r="D21" s="335"/>
       <c r="E21" s="10"/>
-      <c r="F21" s="165"/>
-      <c r="G21" s="167"/>
-      <c r="H21" s="108" t="s">
+      <c r="F21" s="161"/>
+      <c r="G21" s="163"/>
+      <c r="H21" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I21" s="108" t="s">
+      <c r="I21" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J21" s="342"/>
-      <c r="K21" s="342"/>
-      <c r="L21" s="342"/>
-      <c r="M21" s="343"/>
+      <c r="J21" s="338"/>
+      <c r="K21" s="338"/>
+      <c r="L21" s="338"/>
+      <c r="M21" s="339"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="421"/>
-      <c r="B22" s="339"/>
-      <c r="C22" s="339"/>
-      <c r="D22" s="339"/>
+      <c r="A22" s="417"/>
+      <c r="B22" s="335"/>
+      <c r="C22" s="335"/>
+      <c r="D22" s="335"/>
       <c r="E22" s="10"/>
-      <c r="F22" s="165"/>
-      <c r="G22" s="167"/>
-      <c r="H22" s="108" t="s">
+      <c r="F22" s="161"/>
+      <c r="G22" s="163"/>
+      <c r="H22" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I22" s="108" t="s">
+      <c r="I22" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="342"/>
-      <c r="K22" s="342"/>
-      <c r="L22" s="342"/>
-      <c r="M22" s="343"/>
+      <c r="J22" s="338"/>
+      <c r="K22" s="338"/>
+      <c r="L22" s="338"/>
+      <c r="M22" s="339"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="421"/>
-      <c r="B23" s="339"/>
-      <c r="C23" s="339"/>
-      <c r="D23" s="339"/>
+      <c r="A23" s="417"/>
+      <c r="B23" s="335"/>
+      <c r="C23" s="335"/>
+      <c r="D23" s="335"/>
       <c r="E23" s="10"/>
-      <c r="F23" s="165"/>
-      <c r="G23" s="167"/>
-      <c r="H23" s="108" t="s">
+      <c r="F23" s="161"/>
+      <c r="G23" s="163"/>
+      <c r="H23" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I23" s="108" t="s">
+      <c r="I23" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="342"/>
-      <c r="K23" s="342"/>
-      <c r="L23" s="342"/>
-      <c r="M23" s="343"/>
+      <c r="J23" s="338"/>
+      <c r="K23" s="338"/>
+      <c r="L23" s="338"/>
+      <c r="M23" s="339"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="421"/>
-      <c r="B24" s="339"/>
-      <c r="C24" s="339"/>
-      <c r="D24" s="339"/>
+      <c r="A24" s="417"/>
+      <c r="B24" s="335"/>
+      <c r="C24" s="335"/>
+      <c r="D24" s="335"/>
       <c r="E24" s="10"/>
-      <c r="F24" s="165"/>
-      <c r="G24" s="167"/>
-      <c r="H24" s="108" t="s">
+      <c r="F24" s="161"/>
+      <c r="G24" s="163"/>
+      <c r="H24" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I24" s="108" t="s">
+      <c r="I24" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="342"/>
-      <c r="K24" s="342"/>
-      <c r="L24" s="342"/>
-      <c r="M24" s="343"/>
+      <c r="J24" s="338"/>
+      <c r="K24" s="338"/>
+      <c r="L24" s="338"/>
+      <c r="M24" s="339"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="421"/>
-      <c r="B25" s="339"/>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
+      <c r="A25" s="417"/>
+      <c r="B25" s="335"/>
+      <c r="C25" s="335"/>
+      <c r="D25" s="335"/>
       <c r="E25" s="10"/>
-      <c r="F25" s="165"/>
-      <c r="G25" s="167"/>
-      <c r="H25" s="108" t="s">
+      <c r="F25" s="161"/>
+      <c r="G25" s="163"/>
+      <c r="H25" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="I25" s="108" t="s">
+      <c r="I25" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="342"/>
-      <c r="K25" s="342"/>
-      <c r="L25" s="342"/>
-      <c r="M25" s="343"/>
+      <c r="J25" s="338"/>
+      <c r="K25" s="338"/>
+      <c r="L25" s="338"/>
+      <c r="M25" s="339"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="422"/>
-      <c r="B26" s="423"/>
-      <c r="C26" s="423"/>
-      <c r="D26" s="423"/>
+      <c r="A26" s="418"/>
+      <c r="B26" s="419"/>
+      <c r="C26" s="419"/>
+      <c r="D26" s="419"/>
       <c r="E26" s="13"/>
-      <c r="F26" s="342"/>
-      <c r="G26" s="342"/>
+      <c r="F26" s="338"/>
+      <c r="G26" s="338"/>
       <c r="H26" s="13"/>
       <c r="I26" s="13"/>
-      <c r="J26" s="342"/>
-      <c r="K26" s="342"/>
-      <c r="L26" s="342"/>
-      <c r="M26" s="343"/>
+      <c r="J26" s="338"/>
+      <c r="K26" s="338"/>
+      <c r="L26" s="338"/>
+      <c r="M26" s="339"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="422"/>
-      <c r="B27" s="423"/>
-      <c r="C27" s="423"/>
-      <c r="D27" s="423"/>
+      <c r="A27" s="418"/>
+      <c r="B27" s="419"/>
+      <c r="C27" s="419"/>
+      <c r="D27" s="419"/>
       <c r="E27" s="13"/>
-      <c r="F27" s="342"/>
-      <c r="G27" s="342"/>
+      <c r="F27" s="338"/>
+      <c r="G27" s="338"/>
       <c r="H27" s="13"/>
       <c r="I27" s="13"/>
-      <c r="J27" s="342"/>
-      <c r="K27" s="342"/>
-      <c r="L27" s="342"/>
-      <c r="M27" s="343"/>
+      <c r="J27" s="338"/>
+      <c r="K27" s="338"/>
+      <c r="L27" s="338"/>
+      <c r="M27" s="339"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="422"/>
-      <c r="B28" s="423"/>
-      <c r="C28" s="423"/>
-      <c r="D28" s="423"/>
+      <c r="A28" s="418"/>
+      <c r="B28" s="419"/>
+      <c r="C28" s="419"/>
+      <c r="D28" s="419"/>
       <c r="E28" s="13"/>
-      <c r="F28" s="342"/>
-      <c r="G28" s="342"/>
+      <c r="F28" s="338"/>
+      <c r="G28" s="338"/>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
-      <c r="J28" s="342"/>
-      <c r="K28" s="342"/>
-      <c r="L28" s="342"/>
-      <c r="M28" s="343"/>
+      <c r="J28" s="338"/>
+      <c r="K28" s="338"/>
+      <c r="L28" s="338"/>
+      <c r="M28" s="339"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="422"/>
-      <c r="B29" s="423"/>
-      <c r="C29" s="423"/>
-      <c r="D29" s="423"/>
+      <c r="A29" s="418"/>
+      <c r="B29" s="419"/>
+      <c r="C29" s="419"/>
+      <c r="D29" s="419"/>
       <c r="E29" s="13"/>
-      <c r="F29" s="342"/>
-      <c r="G29" s="342"/>
+      <c r="F29" s="338"/>
+      <c r="G29" s="338"/>
       <c r="H29" s="13"/>
       <c r="I29" s="13"/>
-      <c r="J29" s="342"/>
-      <c r="K29" s="342"/>
-      <c r="L29" s="342"/>
-      <c r="M29" s="343"/>
+      <c r="J29" s="338"/>
+      <c r="K29" s="338"/>
+      <c r="L29" s="338"/>
+      <c r="M29" s="339"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="422"/>
-      <c r="B30" s="423"/>
-      <c r="C30" s="423"/>
-      <c r="D30" s="423"/>
+      <c r="A30" s="418"/>
+      <c r="B30" s="419"/>
+      <c r="C30" s="419"/>
+      <c r="D30" s="419"/>
       <c r="E30" s="13"/>
-      <c r="F30" s="342"/>
-      <c r="G30" s="342"/>
+      <c r="F30" s="338"/>
+      <c r="G30" s="338"/>
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
-      <c r="J30" s="342"/>
-      <c r="K30" s="342"/>
-      <c r="L30" s="342"/>
-      <c r="M30" s="343"/>
+      <c r="J30" s="338"/>
+      <c r="K30" s="338"/>
+      <c r="L30" s="338"/>
+      <c r="M30" s="339"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="422"/>
-      <c r="B31" s="423"/>
-      <c r="C31" s="423"/>
-      <c r="D31" s="423"/>
+      <c r="A31" s="418"/>
+      <c r="B31" s="419"/>
+      <c r="C31" s="419"/>
+      <c r="D31" s="419"/>
       <c r="E31" s="13"/>
-      <c r="F31" s="342"/>
-      <c r="G31" s="342"/>
+      <c r="F31" s="338"/>
+      <c r="G31" s="338"/>
       <c r="H31" s="13"/>
       <c r="I31" s="13"/>
-      <c r="J31" s="342"/>
-      <c r="K31" s="342"/>
-      <c r="L31" s="342"/>
-      <c r="M31" s="343"/>
+      <c r="J31" s="338"/>
+      <c r="K31" s="338"/>
+      <c r="L31" s="338"/>
+      <c r="M31" s="339"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="422"/>
-      <c r="B32" s="423"/>
-      <c r="C32" s="423"/>
-      <c r="D32" s="423"/>
+      <c r="A32" s="418"/>
+      <c r="B32" s="419"/>
+      <c r="C32" s="419"/>
+      <c r="D32" s="419"/>
       <c r="E32" s="13"/>
-      <c r="F32" s="342"/>
-      <c r="G32" s="342"/>
+      <c r="F32" s="338"/>
+      <c r="G32" s="338"/>
       <c r="H32" s="13"/>
       <c r="I32" s="13"/>
-      <c r="J32" s="342"/>
-      <c r="K32" s="342"/>
-      <c r="L32" s="342"/>
-      <c r="M32" s="343"/>
+      <c r="J32" s="338"/>
+      <c r="K32" s="338"/>
+      <c r="L32" s="338"/>
+      <c r="M32" s="339"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A33" s="422"/>
-      <c r="B33" s="423"/>
-      <c r="C33" s="423"/>
-      <c r="D33" s="423"/>
+      <c r="A33" s="418"/>
+      <c r="B33" s="419"/>
+      <c r="C33" s="419"/>
+      <c r="D33" s="419"/>
       <c r="E33" s="13"/>
-      <c r="F33" s="342"/>
-      <c r="G33" s="342"/>
+      <c r="F33" s="338"/>
+      <c r="G33" s="338"/>
       <c r="H33" s="13"/>
       <c r="I33" s="13"/>
-      <c r="J33" s="342"/>
-      <c r="K33" s="342"/>
-      <c r="L33" s="342"/>
-      <c r="M33" s="343"/>
+      <c r="J33" s="338"/>
+      <c r="K33" s="338"/>
+      <c r="L33" s="338"/>
+      <c r="M33" s="339"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A34" s="422"/>
-      <c r="B34" s="423"/>
-      <c r="C34" s="423"/>
-      <c r="D34" s="423"/>
+      <c r="A34" s="418"/>
+      <c r="B34" s="419"/>
+      <c r="C34" s="419"/>
+      <c r="D34" s="419"/>
       <c r="E34" s="13"/>
-      <c r="F34" s="342"/>
-      <c r="G34" s="342"/>
+      <c r="F34" s="338"/>
+      <c r="G34" s="338"/>
       <c r="H34" s="13"/>
       <c r="I34" s="13"/>
-      <c r="J34" s="342"/>
-      <c r="K34" s="342"/>
-      <c r="L34" s="342"/>
-      <c r="M34" s="343"/>
+      <c r="J34" s="338"/>
+      <c r="K34" s="338"/>
+      <c r="L34" s="338"/>
+      <c r="M34" s="339"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35" s="422"/>
-      <c r="B35" s="423"/>
-      <c r="C35" s="423"/>
-      <c r="D35" s="423"/>
+      <c r="A35" s="418"/>
+      <c r="B35" s="419"/>
+      <c r="C35" s="419"/>
+      <c r="D35" s="419"/>
       <c r="E35" s="13"/>
-      <c r="F35" s="342"/>
-      <c r="G35" s="342"/>
+      <c r="F35" s="338"/>
+      <c r="G35" s="338"/>
       <c r="H35" s="13"/>
       <c r="I35" s="13"/>
-      <c r="J35" s="342"/>
-      <c r="K35" s="342"/>
-      <c r="L35" s="342"/>
-      <c r="M35" s="343"/>
+      <c r="J35" s="338"/>
+      <c r="K35" s="338"/>
+      <c r="L35" s="338"/>
+      <c r="M35" s="339"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A36" s="422"/>
-      <c r="B36" s="423"/>
-      <c r="C36" s="423"/>
-      <c r="D36" s="423"/>
+      <c r="A36" s="418"/>
+      <c r="B36" s="419"/>
+      <c r="C36" s="419"/>
+      <c r="D36" s="419"/>
       <c r="E36" s="13"/>
-      <c r="F36" s="342"/>
-      <c r="G36" s="342"/>
+      <c r="F36" s="338"/>
+      <c r="G36" s="338"/>
       <c r="H36" s="13"/>
       <c r="I36" s="13"/>
-      <c r="J36" s="342"/>
-      <c r="K36" s="342"/>
-      <c r="L36" s="342"/>
-      <c r="M36" s="343"/>
+      <c r="J36" s="338"/>
+      <c r="K36" s="338"/>
+      <c r="L36" s="338"/>
+      <c r="M36" s="339"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A37" s="422"/>
-      <c r="B37" s="423"/>
-      <c r="C37" s="423"/>
-      <c r="D37" s="423"/>
+      <c r="A37" s="418"/>
+      <c r="B37" s="419"/>
+      <c r="C37" s="419"/>
+      <c r="D37" s="419"/>
       <c r="E37" s="13"/>
-      <c r="F37" s="342"/>
-      <c r="G37" s="342"/>
+      <c r="F37" s="338"/>
+      <c r="G37" s="338"/>
       <c r="H37" s="13"/>
       <c r="I37" s="13"/>
-      <c r="J37" s="342"/>
-      <c r="K37" s="342"/>
-      <c r="L37" s="342"/>
-      <c r="M37" s="343"/>
+      <c r="J37" s="338"/>
+      <c r="K37" s="338"/>
+      <c r="L37" s="338"/>
+      <c r="M37" s="339"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A38" s="422"/>
-      <c r="B38" s="423"/>
-      <c r="C38" s="423"/>
-      <c r="D38" s="423"/>
+      <c r="A38" s="418"/>
+      <c r="B38" s="419"/>
+      <c r="C38" s="419"/>
+      <c r="D38" s="419"/>
       <c r="E38" s="13"/>
-      <c r="F38" s="342"/>
-      <c r="G38" s="342"/>
+      <c r="F38" s="338"/>
+      <c r="G38" s="338"/>
       <c r="H38" s="13"/>
       <c r="I38" s="13"/>
-      <c r="J38" s="342"/>
-      <c r="K38" s="342"/>
-      <c r="L38" s="342"/>
-      <c r="M38" s="343"/>
+      <c r="J38" s="338"/>
+      <c r="K38" s="338"/>
+      <c r="L38" s="338"/>
+      <c r="M38" s="339"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A39" s="422"/>
-      <c r="B39" s="423"/>
-      <c r="C39" s="423"/>
-      <c r="D39" s="423"/>
+      <c r="A39" s="418"/>
+      <c r="B39" s="419"/>
+      <c r="C39" s="419"/>
+      <c r="D39" s="419"/>
       <c r="E39" s="13"/>
-      <c r="F39" s="342"/>
-      <c r="G39" s="342"/>
+      <c r="F39" s="338"/>
+      <c r="G39" s="338"/>
       <c r="H39" s="13"/>
       <c r="I39" s="13"/>
-      <c r="J39" s="342"/>
-      <c r="K39" s="342"/>
-      <c r="L39" s="342"/>
-      <c r="M39" s="343"/>
+      <c r="J39" s="338"/>
+      <c r="K39" s="338"/>
+      <c r="L39" s="338"/>
+      <c r="M39" s="339"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A40" s="422"/>
-      <c r="B40" s="423"/>
-      <c r="C40" s="423"/>
-      <c r="D40" s="423"/>
+      <c r="A40" s="418"/>
+      <c r="B40" s="419"/>
+      <c r="C40" s="419"/>
+      <c r="D40" s="419"/>
       <c r="E40" s="13"/>
-      <c r="F40" s="342"/>
-      <c r="G40" s="342"/>
+      <c r="F40" s="338"/>
+      <c r="G40" s="338"/>
       <c r="H40" s="13"/>
       <c r="I40" s="13"/>
-      <c r="J40" s="342"/>
-      <c r="K40" s="342"/>
-      <c r="L40" s="342"/>
-      <c r="M40" s="343"/>
+      <c r="J40" s="338"/>
+      <c r="K40" s="338"/>
+      <c r="L40" s="338"/>
+      <c r="M40" s="339"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A41" s="422"/>
-      <c r="B41" s="423"/>
-      <c r="C41" s="423"/>
-      <c r="D41" s="423"/>
+      <c r="A41" s="418"/>
+      <c r="B41" s="419"/>
+      <c r="C41" s="419"/>
+      <c r="D41" s="419"/>
       <c r="E41" s="13"/>
-      <c r="F41" s="342"/>
-      <c r="G41" s="342"/>
+      <c r="F41" s="338"/>
+      <c r="G41" s="338"/>
       <c r="H41" s="13"/>
       <c r="I41" s="13"/>
-      <c r="J41" s="342"/>
-      <c r="K41" s="342"/>
-      <c r="L41" s="342"/>
-      <c r="M41" s="343"/>
+      <c r="J41" s="338"/>
+      <c r="K41" s="338"/>
+      <c r="L41" s="338"/>
+      <c r="M41" s="339"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A42" s="422"/>
-      <c r="B42" s="423"/>
-      <c r="C42" s="423"/>
-      <c r="D42" s="423"/>
+      <c r="A42" s="418"/>
+      <c r="B42" s="419"/>
+      <c r="C42" s="419"/>
+      <c r="D42" s="419"/>
       <c r="E42" s="13"/>
-      <c r="F42" s="342"/>
-      <c r="G42" s="342"/>
+      <c r="F42" s="338"/>
+      <c r="G42" s="338"/>
       <c r="H42" s="13"/>
       <c r="I42" s="13"/>
-      <c r="J42" s="342"/>
-      <c r="K42" s="342"/>
-      <c r="L42" s="342"/>
-      <c r="M42" s="343"/>
+      <c r="J42" s="338"/>
+      <c r="K42" s="338"/>
+      <c r="L42" s="338"/>
+      <c r="M42" s="339"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A43" s="422"/>
-      <c r="B43" s="423"/>
-      <c r="C43" s="423"/>
-      <c r="D43" s="423"/>
+      <c r="A43" s="418"/>
+      <c r="B43" s="419"/>
+      <c r="C43" s="419"/>
+      <c r="D43" s="419"/>
       <c r="E43" s="13"/>
-      <c r="F43" s="342"/>
-      <c r="G43" s="342"/>
+      <c r="F43" s="338"/>
+      <c r="G43" s="338"/>
       <c r="H43" s="13"/>
       <c r="I43" s="13"/>
-      <c r="J43" s="342"/>
-      <c r="K43" s="342"/>
-      <c r="L43" s="342"/>
-      <c r="M43" s="343"/>
+      <c r="J43" s="338"/>
+      <c r="K43" s="338"/>
+      <c r="L43" s="338"/>
+      <c r="M43" s="339"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A44" s="422"/>
-      <c r="B44" s="423"/>
-      <c r="C44" s="423"/>
-      <c r="D44" s="423"/>
+      <c r="A44" s="418"/>
+      <c r="B44" s="419"/>
+      <c r="C44" s="419"/>
+      <c r="D44" s="419"/>
       <c r="E44" s="13"/>
-      <c r="F44" s="342"/>
-      <c r="G44" s="342"/>
+      <c r="F44" s="338"/>
+      <c r="G44" s="338"/>
       <c r="H44" s="13"/>
       <c r="I44" s="13"/>
-      <c r="J44" s="342"/>
-      <c r="K44" s="342"/>
-      <c r="L44" s="342"/>
-      <c r="M44" s="343"/>
+      <c r="J44" s="338"/>
+      <c r="K44" s="338"/>
+      <c r="L44" s="338"/>
+      <c r="M44" s="339"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A45" s="422"/>
-      <c r="B45" s="423"/>
-      <c r="C45" s="423"/>
-      <c r="D45" s="423"/>
+      <c r="A45" s="418"/>
+      <c r="B45" s="419"/>
+      <c r="C45" s="419"/>
+      <c r="D45" s="419"/>
       <c r="E45" s="13"/>
-      <c r="F45" s="342"/>
-      <c r="G45" s="342"/>
+      <c r="F45" s="338"/>
+      <c r="G45" s="338"/>
       <c r="H45" s="13"/>
       <c r="I45" s="13"/>
-      <c r="J45" s="342"/>
-      <c r="K45" s="342"/>
-      <c r="L45" s="342"/>
-      <c r="M45" s="343"/>
+      <c r="J45" s="338"/>
+      <c r="K45" s="338"/>
+      <c r="L45" s="338"/>
+      <c r="M45" s="339"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A46" s="422"/>
-      <c r="B46" s="423"/>
-      <c r="C46" s="423"/>
-      <c r="D46" s="423"/>
+      <c r="A46" s="418"/>
+      <c r="B46" s="419"/>
+      <c r="C46" s="419"/>
+      <c r="D46" s="419"/>
       <c r="E46" s="13"/>
-      <c r="F46" s="342"/>
-      <c r="G46" s="342"/>
+      <c r="F46" s="338"/>
+      <c r="G46" s="338"/>
       <c r="H46" s="13"/>
       <c r="I46" s="13"/>
-      <c r="J46" s="342"/>
-      <c r="K46" s="342"/>
-      <c r="L46" s="342"/>
-      <c r="M46" s="343"/>
+      <c r="J46" s="338"/>
+      <c r="K46" s="338"/>
+      <c r="L46" s="338"/>
+      <c r="M46" s="339"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A47" s="422"/>
-      <c r="B47" s="423"/>
-      <c r="C47" s="423"/>
-      <c r="D47" s="423"/>
+      <c r="A47" s="418"/>
+      <c r="B47" s="419"/>
+      <c r="C47" s="419"/>
+      <c r="D47" s="419"/>
       <c r="E47" s="13"/>
-      <c r="F47" s="342"/>
-      <c r="G47" s="342"/>
+      <c r="F47" s="338"/>
+      <c r="G47" s="338"/>
       <c r="H47" s="13"/>
       <c r="I47" s="13"/>
-      <c r="J47" s="342"/>
-      <c r="K47" s="342"/>
-      <c r="L47" s="342"/>
-      <c r="M47" s="343"/>
+      <c r="J47" s="338"/>
+      <c r="K47" s="338"/>
+      <c r="L47" s="338"/>
+      <c r="M47" s="339"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A48" s="422"/>
-      <c r="B48" s="423"/>
-      <c r="C48" s="423"/>
-      <c r="D48" s="423"/>
+      <c r="A48" s="418"/>
+      <c r="B48" s="419"/>
+      <c r="C48" s="419"/>
+      <c r="D48" s="419"/>
       <c r="E48" s="13"/>
-      <c r="F48" s="342"/>
-      <c r="G48" s="342"/>
+      <c r="F48" s="338"/>
+      <c r="G48" s="338"/>
       <c r="H48" s="13"/>
       <c r="I48" s="13"/>
-      <c r="J48" s="342"/>
-      <c r="K48" s="342"/>
-      <c r="L48" s="342"/>
-      <c r="M48" s="343"/>
+      <c r="J48" s="338"/>
+      <c r="K48" s="338"/>
+      <c r="L48" s="338"/>
+      <c r="M48" s="339"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A49" s="422"/>
-      <c r="B49" s="423"/>
-      <c r="C49" s="423"/>
-      <c r="D49" s="423"/>
+      <c r="A49" s="418"/>
+      <c r="B49" s="419"/>
+      <c r="C49" s="419"/>
+      <c r="D49" s="419"/>
       <c r="E49" s="13"/>
-      <c r="F49" s="342"/>
-      <c r="G49" s="342"/>
+      <c r="F49" s="338"/>
+      <c r="G49" s="338"/>
       <c r="H49" s="13"/>
       <c r="I49" s="13"/>
-      <c r="J49" s="342"/>
-      <c r="K49" s="342"/>
-      <c r="L49" s="342"/>
-      <c r="M49" s="343"/>
+      <c r="J49" s="338"/>
+      <c r="K49" s="338"/>
+      <c r="L49" s="338"/>
+      <c r="M49" s="339"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="349" t="s">
+      <c r="A50" s="345" t="s">
         <v>22</v>
       </c>
-      <c r="B50" s="350"/>
-      <c r="C50" s="350"/>
-      <c r="D50" s="350"/>
-      <c r="E50" s="109"/>
-      <c r="F50" s="436"/>
-      <c r="G50" s="437"/>
+      <c r="B50" s="346"/>
+      <c r="C50" s="346"/>
+      <c r="D50" s="346"/>
+      <c r="E50" s="105"/>
+      <c r="F50" s="432"/>
+      <c r="G50" s="433"/>
       <c r="H50" s="29"/>
       <c r="I50" s="30"/>
-      <c r="J50" s="438"/>
-      <c r="K50" s="438"/>
-      <c r="L50" s="438"/>
-      <c r="M50" s="439"/>
+      <c r="J50" s="434"/>
+      <c r="K50" s="434"/>
+      <c r="L50" s="434"/>
+      <c r="M50" s="435"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A51" s="424" t="s">
+      <c r="A51" s="420" t="s">
         <v>58</v>
       </c>
-      <c r="B51" s="425"/>
-      <c r="C51" s="425"/>
-      <c r="D51" s="425"/>
-      <c r="E51" s="425"/>
-      <c r="F51" s="425"/>
-      <c r="G51" s="425"/>
-      <c r="H51" s="425"/>
-      <c r="I51" s="425"/>
-      <c r="J51" s="425"/>
-      <c r="K51" s="425"/>
-      <c r="L51" s="425"/>
-      <c r="M51" s="426"/>
+      <c r="B51" s="421"/>
+      <c r="C51" s="421"/>
+      <c r="D51" s="421"/>
+      <c r="E51" s="421"/>
+      <c r="F51" s="421"/>
+      <c r="G51" s="421"/>
+      <c r="H51" s="421"/>
+      <c r="I51" s="421"/>
+      <c r="J51" s="421"/>
+      <c r="K51" s="421"/>
+      <c r="L51" s="421"/>
+      <c r="M51" s="422"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="427"/>
-      <c r="B52" s="428"/>
-      <c r="C52" s="428"/>
-      <c r="D52" s="428"/>
-      <c r="E52" s="428"/>
-      <c r="F52" s="428"/>
-      <c r="G52" s="428"/>
-      <c r="H52" s="428"/>
-      <c r="I52" s="428"/>
-      <c r="J52" s="428"/>
-      <c r="K52" s="428"/>
-      <c r="L52" s="428"/>
-      <c r="M52" s="429"/>
+      <c r="A52" s="423"/>
+      <c r="B52" s="424"/>
+      <c r="C52" s="424"/>
+      <c r="D52" s="424"/>
+      <c r="E52" s="424"/>
+      <c r="F52" s="424"/>
+      <c r="G52" s="424"/>
+      <c r="H52" s="424"/>
+      <c r="I52" s="424"/>
+      <c r="J52" s="424"/>
+      <c r="K52" s="424"/>
+      <c r="L52" s="424"/>
+      <c r="M52" s="425"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A53" s="430"/>
-      <c r="B53" s="431"/>
-      <c r="C53" s="431"/>
-      <c r="D53" s="431"/>
-      <c r="E53" s="431"/>
-      <c r="F53" s="431"/>
-      <c r="G53" s="431"/>
-      <c r="H53" s="431"/>
-      <c r="I53" s="431"/>
-      <c r="J53" s="431"/>
-      <c r="K53" s="431"/>
-      <c r="L53" s="431"/>
-      <c r="M53" s="432"/>
+      <c r="A53" s="426"/>
+      <c r="B53" s="427"/>
+      <c r="C53" s="427"/>
+      <c r="D53" s="427"/>
+      <c r="E53" s="427"/>
+      <c r="F53" s="427"/>
+      <c r="G53" s="427"/>
+      <c r="H53" s="427"/>
+      <c r="I53" s="427"/>
+      <c r="J53" s="427"/>
+      <c r="K53" s="427"/>
+      <c r="L53" s="427"/>
+      <c r="M53" s="428"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A54" s="430"/>
-      <c r="B54" s="431"/>
-      <c r="C54" s="431"/>
-      <c r="D54" s="431"/>
-      <c r="E54" s="431"/>
-      <c r="F54" s="431"/>
-      <c r="G54" s="431"/>
-      <c r="H54" s="431"/>
-      <c r="I54" s="431"/>
-      <c r="J54" s="431"/>
-      <c r="K54" s="431"/>
-      <c r="L54" s="431"/>
-      <c r="M54" s="432"/>
+      <c r="A54" s="426"/>
+      <c r="B54" s="427"/>
+      <c r="C54" s="427"/>
+      <c r="D54" s="427"/>
+      <c r="E54" s="427"/>
+      <c r="F54" s="427"/>
+      <c r="G54" s="427"/>
+      <c r="H54" s="427"/>
+      <c r="I54" s="427"/>
+      <c r="J54" s="427"/>
+      <c r="K54" s="427"/>
+      <c r="L54" s="427"/>
+      <c r="M54" s="428"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A55" s="430"/>
-      <c r="B55" s="431"/>
-      <c r="C55" s="431"/>
-      <c r="D55" s="431"/>
-      <c r="E55" s="431"/>
-      <c r="F55" s="431"/>
-      <c r="G55" s="431"/>
-      <c r="H55" s="431"/>
-      <c r="I55" s="431"/>
-      <c r="J55" s="431"/>
-      <c r="K55" s="431"/>
-      <c r="L55" s="431"/>
-      <c r="M55" s="432"/>
+      <c r="A55" s="426"/>
+      <c r="B55" s="427"/>
+      <c r="C55" s="427"/>
+      <c r="D55" s="427"/>
+      <c r="E55" s="427"/>
+      <c r="F55" s="427"/>
+      <c r="G55" s="427"/>
+      <c r="H55" s="427"/>
+      <c r="I55" s="427"/>
+      <c r="J55" s="427"/>
+      <c r="K55" s="427"/>
+      <c r="L55" s="427"/>
+      <c r="M55" s="428"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A56" s="430"/>
-      <c r="B56" s="431"/>
-      <c r="C56" s="431"/>
-      <c r="D56" s="431"/>
-      <c r="E56" s="431"/>
-      <c r="F56" s="431"/>
-      <c r="G56" s="431"/>
-      <c r="H56" s="431"/>
-      <c r="I56" s="431"/>
-      <c r="J56" s="431"/>
-      <c r="K56" s="431"/>
-      <c r="L56" s="431"/>
-      <c r="M56" s="432"/>
+      <c r="A56" s="426"/>
+      <c r="B56" s="427"/>
+      <c r="C56" s="427"/>
+      <c r="D56" s="427"/>
+      <c r="E56" s="427"/>
+      <c r="F56" s="427"/>
+      <c r="G56" s="427"/>
+      <c r="H56" s="427"/>
+      <c r="I56" s="427"/>
+      <c r="J56" s="427"/>
+      <c r="K56" s="427"/>
+      <c r="L56" s="427"/>
+      <c r="M56" s="428"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A57" s="430"/>
-      <c r="B57" s="431"/>
-      <c r="C57" s="431"/>
-      <c r="D57" s="431"/>
-      <c r="E57" s="431"/>
-      <c r="F57" s="431"/>
-      <c r="G57" s="431"/>
-      <c r="H57" s="431"/>
-      <c r="I57" s="431"/>
-      <c r="J57" s="431"/>
-      <c r="K57" s="431"/>
-      <c r="L57" s="431"/>
-      <c r="M57" s="432"/>
+      <c r="A57" s="426"/>
+      <c r="B57" s="427"/>
+      <c r="C57" s="427"/>
+      <c r="D57" s="427"/>
+      <c r="E57" s="427"/>
+      <c r="F57" s="427"/>
+      <c r="G57" s="427"/>
+      <c r="H57" s="427"/>
+      <c r="I57" s="427"/>
+      <c r="J57" s="427"/>
+      <c r="K57" s="427"/>
+      <c r="L57" s="427"/>
+      <c r="M57" s="428"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A58" s="430"/>
-      <c r="B58" s="431"/>
-      <c r="C58" s="431"/>
-      <c r="D58" s="431"/>
-      <c r="E58" s="431"/>
-      <c r="F58" s="431"/>
-      <c r="G58" s="431"/>
-      <c r="H58" s="431"/>
-      <c r="I58" s="431"/>
-      <c r="J58" s="431"/>
-      <c r="K58" s="431"/>
-      <c r="L58" s="431"/>
-      <c r="M58" s="432"/>
+      <c r="A58" s="426"/>
+      <c r="B58" s="427"/>
+      <c r="C58" s="427"/>
+      <c r="D58" s="427"/>
+      <c r="E58" s="427"/>
+      <c r="F58" s="427"/>
+      <c r="G58" s="427"/>
+      <c r="H58" s="427"/>
+      <c r="I58" s="427"/>
+      <c r="J58" s="427"/>
+      <c r="K58" s="427"/>
+      <c r="L58" s="427"/>
+      <c r="M58" s="428"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A59" s="430"/>
-      <c r="B59" s="431"/>
-      <c r="C59" s="431"/>
-      <c r="D59" s="431"/>
-      <c r="E59" s="431"/>
-      <c r="F59" s="431"/>
-      <c r="G59" s="431"/>
-      <c r="H59" s="431"/>
-      <c r="I59" s="431"/>
-      <c r="J59" s="431"/>
-      <c r="K59" s="431"/>
-      <c r="L59" s="431"/>
-      <c r="M59" s="432"/>
+      <c r="A59" s="426"/>
+      <c r="B59" s="427"/>
+      <c r="C59" s="427"/>
+      <c r="D59" s="427"/>
+      <c r="E59" s="427"/>
+      <c r="F59" s="427"/>
+      <c r="G59" s="427"/>
+      <c r="H59" s="427"/>
+      <c r="I59" s="427"/>
+      <c r="J59" s="427"/>
+      <c r="K59" s="427"/>
+      <c r="L59" s="427"/>
+      <c r="M59" s="428"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A60" s="433"/>
-      <c r="B60" s="434"/>
-      <c r="C60" s="434"/>
-      <c r="D60" s="434"/>
-      <c r="E60" s="434"/>
-      <c r="F60" s="434"/>
-      <c r="G60" s="434"/>
-      <c r="H60" s="434"/>
-      <c r="I60" s="434"/>
-      <c r="J60" s="434"/>
-      <c r="K60" s="434"/>
-      <c r="L60" s="434"/>
-      <c r="M60" s="435"/>
+      <c r="A60" s="429"/>
+      <c r="B60" s="430"/>
+      <c r="C60" s="430"/>
+      <c r="D60" s="430"/>
+      <c r="E60" s="430"/>
+      <c r="F60" s="430"/>
+      <c r="G60" s="430"/>
+      <c r="H60" s="430"/>
+      <c r="I60" s="430"/>
+      <c r="J60" s="430"/>
+      <c r="K60" s="430"/>
+      <c r="L60" s="430"/>
+      <c r="M60" s="431"/>
     </row>
     <row r="61" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="28"/>
@@ -8085,599 +7600,599 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
-        <v>233</v>
-      </c>
-      <c r="B1" s="245"/>
-      <c r="C1" s="245"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41" t="s">
+      <c r="A1" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="250" t="s">
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="246" t="s">
         <v>68</v>
       </c>
-      <c r="M1" s="251"/>
+      <c r="M1" s="247"/>
     </row>
     <row r="2" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="243" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="248"/>
-      <c r="C2" s="248"/>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="248"/>
-      <c r="H2" s="249"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="45"/>
+      <c r="B2" s="244"/>
+      <c r="C2" s="244"/>
+      <c r="D2" s="244"/>
+      <c r="E2" s="244"/>
+      <c r="F2" s="244"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="44"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="211" t="s">
+      <c r="A3" s="207" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="212"/>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="212"/>
-      <c r="G3" s="212"/>
-      <c r="H3" s="213"/>
-      <c r="I3" s="46" t="s">
-        <v>189</v>
-      </c>
-      <c r="J3" s="44"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="48"/>
+      <c r="B3" s="208"/>
+      <c r="C3" s="208"/>
+      <c r="D3" s="208"/>
+      <c r="E3" s="208"/>
+      <c r="F3" s="208"/>
+      <c r="G3" s="208"/>
+      <c r="H3" s="209"/>
+      <c r="I3" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="J3" s="43"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="47"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="211" t="s">
+      <c r="A4" s="207" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="212"/>
-      <c r="C4" s="212"/>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
-      <c r="F4" s="212"/>
-      <c r="G4" s="212"/>
-      <c r="H4" s="213"/>
-      <c r="I4" s="257"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
-      <c r="M4" s="242"/>
+      <c r="B4" s="208"/>
+      <c r="C4" s="208"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="209"/>
+      <c r="I4" s="253"/>
+      <c r="J4" s="237"/>
+      <c r="K4" s="237"/>
+      <c r="L4" s="237"/>
+      <c r="M4" s="238"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="211" t="s">
+      <c r="A5" s="207" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="212"/>
-      <c r="C5" s="212"/>
-      <c r="D5" s="212"/>
-      <c r="E5" s="212"/>
-      <c r="F5" s="212"/>
-      <c r="G5" s="212"/>
-      <c r="H5" s="213"/>
-      <c r="I5" s="257"/>
-      <c r="J5" s="241"/>
-      <c r="K5" s="241"/>
-      <c r="L5" s="241"/>
-      <c r="M5" s="242"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="208"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="209"/>
+      <c r="I5" s="253"/>
+      <c r="J5" s="237"/>
+      <c r="K5" s="237"/>
+      <c r="L5" s="237"/>
+      <c r="M5" s="238"/>
     </row>
     <row r="6" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="255" t="s">
+      <c r="A6" s="251" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="210"/>
-      <c r="C6" s="210"/>
-      <c r="D6" s="210"/>
-      <c r="E6" s="210"/>
-      <c r="F6" s="256" t="s">
+      <c r="B6" s="206"/>
+      <c r="C6" s="206"/>
+      <c r="D6" s="206"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="252" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="256"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="258"/>
-      <c r="J6" s="259"/>
-      <c r="K6" s="259"/>
-      <c r="L6" s="259"/>
-      <c r="M6" s="260"/>
+      <c r="G6" s="252"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="254"/>
+      <c r="J6" s="255"/>
+      <c r="K6" s="255"/>
+      <c r="L6" s="255"/>
+      <c r="M6" s="256"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="262" t="s">
+      <c r="A7" s="258" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="263"/>
-      <c r="C7" s="263"/>
-      <c r="D7" s="263"/>
-      <c r="E7" s="263"/>
-      <c r="F7" s="263"/>
-      <c r="G7" s="263"/>
-      <c r="H7" s="264"/>
-      <c r="I7" s="50" t="s">
-        <v>229</v>
-      </c>
-      <c r="J7" s="51"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="53"/>
+      <c r="B7" s="259"/>
+      <c r="C7" s="259"/>
+      <c r="D7" s="259"/>
+      <c r="E7" s="259"/>
+      <c r="F7" s="259"/>
+      <c r="G7" s="259"/>
+      <c r="H7" s="260"/>
+      <c r="I7" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="J7" s="50"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="50"/>
+      <c r="M7" s="52"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="126"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="233" t="s">
+      <c r="B8" s="122"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="229" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="233"/>
-      <c r="G8" s="233"/>
-      <c r="H8" s="267"/>
-      <c r="I8" s="261" t="s">
+      <c r="F8" s="229"/>
+      <c r="G8" s="229"/>
+      <c r="H8" s="263"/>
+      <c r="I8" s="257" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="212"/>
-      <c r="K8" s="212"/>
-      <c r="L8" s="212"/>
-      <c r="M8" s="213"/>
+      <c r="J8" s="208"/>
+      <c r="K8" s="208"/>
+      <c r="L8" s="208"/>
+      <c r="M8" s="209"/>
     </row>
     <row r="9" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="56" t="s">
+      <c r="A9" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="H9" s="57"/>
-      <c r="I9" s="58" t="s">
+      <c r="H9" s="56"/>
+      <c r="I9" s="57" t="s">
         <v>70</v>
       </c>
-      <c r="J9" s="59"/>
-      <c r="K9" s="59"/>
-      <c r="L9" s="59"/>
-      <c r="M9" s="49"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="58"/>
+      <c r="L9" s="58"/>
+      <c r="M9" s="48"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="60" t="s">
+      <c r="A10" s="59" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="240"/>
-      <c r="D10" s="240"/>
-      <c r="E10" s="240"/>
-      <c r="F10" s="240"/>
-      <c r="G10" s="240"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="61" t="s">
-        <v>230</v>
-      </c>
-      <c r="J10" s="62"/>
-      <c r="K10" s="62"/>
-      <c r="L10" s="62"/>
-      <c r="M10" s="63"/>
+      <c r="C10" s="236"/>
+      <c r="D10" s="236"/>
+      <c r="E10" s="236"/>
+      <c r="F10" s="236"/>
+      <c r="G10" s="236"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="60" t="s">
+        <v>77</v>
+      </c>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+      <c r="L10" s="61"/>
+      <c r="M10" s="62"/>
     </row>
     <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="209" t="s">
+      <c r="A11" s="205" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="210"/>
-      <c r="C11" s="210"/>
-      <c r="D11" s="210"/>
-      <c r="E11" s="210"/>
-      <c r="F11" s="256" t="s">
+      <c r="B11" s="206"/>
+      <c r="C11" s="206"/>
+      <c r="D11" s="206"/>
+      <c r="E11" s="206"/>
+      <c r="F11" s="252" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="256"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="243" t="s">
+      <c r="G11" s="252"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="239" t="s">
         <v>71</v>
       </c>
-      <c r="J11" s="244"/>
-      <c r="K11" s="64"/>
-      <c r="L11" s="64"/>
-      <c r="M11" s="65"/>
+      <c r="J11" s="240"/>
+      <c r="K11" s="63"/>
+      <c r="L11" s="63"/>
+      <c r="M11" s="64"/>
     </row>
     <row r="12" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="179" t="s">
+      <c r="A12" s="175" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="180"/>
-      <c r="C12" s="180"/>
-      <c r="D12" s="180"/>
-      <c r="E12" s="180"/>
-      <c r="F12" s="180"/>
-      <c r="G12" s="180"/>
-      <c r="H12" s="181"/>
-      <c r="I12" s="257"/>
-      <c r="J12" s="241"/>
-      <c r="K12" s="241"/>
-      <c r="L12" s="241"/>
-      <c r="M12" s="242"/>
+      <c r="B12" s="176"/>
+      <c r="C12" s="176"/>
+      <c r="D12" s="176"/>
+      <c r="E12" s="176"/>
+      <c r="F12" s="176"/>
+      <c r="G12" s="176"/>
+      <c r="H12" s="177"/>
+      <c r="I12" s="253"/>
+      <c r="J12" s="237"/>
+      <c r="K12" s="237"/>
+      <c r="L12" s="237"/>
+      <c r="M12" s="238"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="252" t="s">
+      <c r="A13" s="248" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="253"/>
-      <c r="C13" s="253"/>
-      <c r="D13" s="253"/>
-      <c r="E13" s="253"/>
-      <c r="F13" s="253"/>
-      <c r="G13" s="253"/>
-      <c r="H13" s="254"/>
-      <c r="I13" s="257"/>
-      <c r="J13" s="241"/>
-      <c r="K13" s="241"/>
-      <c r="L13" s="241"/>
-      <c r="M13" s="242"/>
+      <c r="B13" s="249"/>
+      <c r="C13" s="249"/>
+      <c r="D13" s="249"/>
+      <c r="E13" s="249"/>
+      <c r="F13" s="249"/>
+      <c r="G13" s="249"/>
+      <c r="H13" s="250"/>
+      <c r="I13" s="253"/>
+      <c r="J13" s="237"/>
+      <c r="K13" s="237"/>
+      <c r="L13" s="237"/>
+      <c r="M13" s="238"/>
     </row>
     <row r="14" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="211" t="s">
+      <c r="A14" s="207" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="212"/>
-      <c r="C14" s="212"/>
-      <c r="D14" s="212"/>
-      <c r="E14" s="212"/>
-      <c r="F14" s="212"/>
-      <c r="G14" s="212"/>
-      <c r="H14" s="213"/>
-      <c r="I14" s="258"/>
-      <c r="J14" s="259"/>
-      <c r="K14" s="259"/>
-      <c r="L14" s="259"/>
-      <c r="M14" s="260"/>
+      <c r="B14" s="208"/>
+      <c r="C14" s="208"/>
+      <c r="D14" s="208"/>
+      <c r="E14" s="208"/>
+      <c r="F14" s="208"/>
+      <c r="G14" s="208"/>
+      <c r="H14" s="209"/>
+      <c r="I14" s="254"/>
+      <c r="J14" s="255"/>
+      <c r="K14" s="255"/>
+      <c r="L14" s="255"/>
+      <c r="M14" s="256"/>
     </row>
     <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="221" t="s">
+      <c r="A15" s="217" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="222"/>
-      <c r="C15" s="222"/>
-      <c r="D15" s="222"/>
-      <c r="E15" s="222"/>
-      <c r="F15" s="223"/>
-      <c r="G15" s="223"/>
-      <c r="H15" s="223"/>
-      <c r="I15" s="218" t="s">
+      <c r="B15" s="218"/>
+      <c r="C15" s="218"/>
+      <c r="D15" s="218"/>
+      <c r="E15" s="218"/>
+      <c r="F15" s="219"/>
+      <c r="G15" s="219"/>
+      <c r="H15" s="219"/>
+      <c r="I15" s="214" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="219"/>
-      <c r="K15" s="219"/>
-      <c r="L15" s="219"/>
-      <c r="M15" s="220"/>
+      <c r="J15" s="215"/>
+      <c r="K15" s="215"/>
+      <c r="L15" s="215"/>
+      <c r="M15" s="216"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="32"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="234" t="s">
-        <v>234</v>
-      </c>
-      <c r="J16" s="235"/>
-      <c r="K16" s="235"/>
-      <c r="L16" s="235"/>
-      <c r="M16" s="236"/>
+      <c r="A16" s="31"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="230" t="s">
+        <v>80</v>
+      </c>
+      <c r="J16" s="231"/>
+      <c r="K16" s="231"/>
+      <c r="L16" s="231"/>
+      <c r="M16" s="232"/>
     </row>
     <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="35" t="s">
+      <c r="A17" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="36"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="241"/>
-      <c r="G17" s="241"/>
-      <c r="H17" s="242"/>
-      <c r="I17" s="232"/>
-      <c r="J17" s="233"/>
-      <c r="K17" s="214" t="s">
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="237"/>
+      <c r="G17" s="237"/>
+      <c r="H17" s="238"/>
+      <c r="I17" s="228"/>
+      <c r="J17" s="229"/>
+      <c r="K17" s="210" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="214"/>
-      <c r="M17" s="215"/>
+      <c r="L17" s="210"/>
+      <c r="M17" s="211"/>
     </row>
     <row r="18" spans="1:13" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="37"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="127" t="s">
+      <c r="A18" s="36"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="123" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="128"/>
-      <c r="K18" s="216"/>
-      <c r="L18" s="216"/>
-      <c r="M18" s="217"/>
+      <c r="J18" s="124"/>
+      <c r="K18" s="212"/>
+      <c r="L18" s="212"/>
+      <c r="M18" s="213"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="182" t="s">
+      <c r="A19" s="178" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="183"/>
-      <c r="C19" s="183"/>
-      <c r="D19" s="183"/>
-      <c r="E19" s="183"/>
-      <c r="F19" s="183"/>
-      <c r="G19" s="183"/>
-      <c r="H19" s="183"/>
-      <c r="I19" s="183"/>
-      <c r="J19" s="183"/>
-      <c r="K19" s="183"/>
-      <c r="L19" s="183"/>
-      <c r="M19" s="184"/>
+      <c r="B19" s="179"/>
+      <c r="C19" s="179"/>
+      <c r="D19" s="179"/>
+      <c r="E19" s="179"/>
+      <c r="F19" s="179"/>
+      <c r="G19" s="179"/>
+      <c r="H19" s="179"/>
+      <c r="I19" s="179"/>
+      <c r="J19" s="179"/>
+      <c r="K19" s="179"/>
+      <c r="L19" s="179"/>
+      <c r="M19" s="180"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="237" t="s">
+      <c r="A20" s="233" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="238"/>
-      <c r="C20" s="238"/>
-      <c r="D20" s="238"/>
-      <c r="E20" s="238" t="s">
+      <c r="B20" s="234"/>
+      <c r="C20" s="234"/>
+      <c r="D20" s="234"/>
+      <c r="E20" s="234" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="238" t="s">
+      <c r="F20" s="234" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="238"/>
-      <c r="H20" s="230" t="s">
+      <c r="G20" s="234"/>
+      <c r="H20" s="226" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="231"/>
-      <c r="J20" s="224" t="s">
+      <c r="I20" s="227"/>
+      <c r="J20" s="220" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="225"/>
-      <c r="L20" s="225"/>
-      <c r="M20" s="226"/>
+      <c r="K20" s="221"/>
+      <c r="L20" s="221"/>
+      <c r="M20" s="222"/>
     </row>
     <row r="21" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="237"/>
-      <c r="B21" s="238"/>
-      <c r="C21" s="238"/>
-      <c r="D21" s="238"/>
-      <c r="E21" s="238"/>
-      <c r="F21" s="238"/>
-      <c r="G21" s="238"/>
-      <c r="H21" s="265" t="s">
+      <c r="A21" s="233"/>
+      <c r="B21" s="234"/>
+      <c r="C21" s="234"/>
+      <c r="D21" s="234"/>
+      <c r="E21" s="234"/>
+      <c r="F21" s="234"/>
+      <c r="G21" s="234"/>
+      <c r="H21" s="261" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="266"/>
-      <c r="J21" s="227"/>
-      <c r="K21" s="228"/>
-      <c r="L21" s="228"/>
-      <c r="M21" s="229"/>
+      <c r="I21" s="262"/>
+      <c r="J21" s="223"/>
+      <c r="K21" s="224"/>
+      <c r="L21" s="224"/>
+      <c r="M21" s="225"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="239"/>
-      <c r="B22" s="188"/>
-      <c r="C22" s="188"/>
-      <c r="D22" s="165"/>
+      <c r="A22" s="235"/>
+      <c r="B22" s="184"/>
+      <c r="C22" s="184"/>
+      <c r="D22" s="161"/>
       <c r="E22" s="10"/>
-      <c r="F22" s="188"/>
-      <c r="G22" s="188"/>
+      <c r="F22" s="184"/>
+      <c r="G22" s="184"/>
       <c r="H22" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="188"/>
-      <c r="K22" s="188"/>
-      <c r="L22" s="188"/>
-      <c r="M22" s="200"/>
+      <c r="J22" s="184"/>
+      <c r="K22" s="184"/>
+      <c r="L22" s="184"/>
+      <c r="M22" s="196"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="203"/>
-      <c r="B23" s="204"/>
-      <c r="C23" s="204"/>
-      <c r="D23" s="205"/>
+      <c r="A23" s="199"/>
+      <c r="B23" s="200"/>
+      <c r="C23" s="200"/>
+      <c r="D23" s="201"/>
       <c r="E23" s="10"/>
-      <c r="F23" s="188"/>
-      <c r="G23" s="188"/>
+      <c r="F23" s="184"/>
+      <c r="G23" s="184"/>
       <c r="H23" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="188"/>
-      <c r="K23" s="188"/>
-      <c r="L23" s="188"/>
-      <c r="M23" s="200"/>
+      <c r="J23" s="184"/>
+      <c r="K23" s="184"/>
+      <c r="L23" s="184"/>
+      <c r="M23" s="196"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="203"/>
-      <c r="B24" s="204"/>
-      <c r="C24" s="204"/>
-      <c r="D24" s="205"/>
+      <c r="A24" s="199"/>
+      <c r="B24" s="200"/>
+      <c r="C24" s="200"/>
+      <c r="D24" s="201"/>
       <c r="E24" s="10"/>
-      <c r="F24" s="188"/>
-      <c r="G24" s="188"/>
+      <c r="F24" s="184"/>
+      <c r="G24" s="184"/>
       <c r="H24" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="188"/>
-      <c r="K24" s="188"/>
-      <c r="L24" s="188"/>
-      <c r="M24" s="200"/>
+      <c r="J24" s="184"/>
+      <c r="K24" s="184"/>
+      <c r="L24" s="184"/>
+      <c r="M24" s="196"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="203"/>
-      <c r="B25" s="204"/>
-      <c r="C25" s="204"/>
-      <c r="D25" s="205"/>
+      <c r="A25" s="199"/>
+      <c r="B25" s="200"/>
+      <c r="C25" s="200"/>
+      <c r="D25" s="201"/>
       <c r="E25" s="10"/>
-      <c r="F25" s="188"/>
-      <c r="G25" s="188"/>
+      <c r="F25" s="184"/>
+      <c r="G25" s="184"/>
       <c r="H25" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="188"/>
-      <c r="K25" s="188"/>
-      <c r="L25" s="188"/>
-      <c r="M25" s="200"/>
+      <c r="J25" s="184"/>
+      <c r="K25" s="184"/>
+      <c r="L25" s="184"/>
+      <c r="M25" s="196"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="203"/>
-      <c r="B26" s="204"/>
-      <c r="C26" s="204"/>
-      <c r="D26" s="205"/>
+      <c r="A26" s="199"/>
+      <c r="B26" s="200"/>
+      <c r="C26" s="200"/>
+      <c r="D26" s="201"/>
       <c r="E26" s="10"/>
-      <c r="F26" s="188"/>
-      <c r="G26" s="188"/>
+      <c r="F26" s="184"/>
+      <c r="G26" s="184"/>
       <c r="H26" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="188"/>
-      <c r="K26" s="188"/>
-      <c r="L26" s="188"/>
-      <c r="M26" s="200"/>
+      <c r="J26" s="184"/>
+      <c r="K26" s="184"/>
+      <c r="L26" s="184"/>
+      <c r="M26" s="196"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="203"/>
-      <c r="B27" s="204"/>
-      <c r="C27" s="204"/>
-      <c r="D27" s="205"/>
+      <c r="A27" s="199"/>
+      <c r="B27" s="200"/>
+      <c r="C27" s="200"/>
+      <c r="D27" s="201"/>
       <c r="E27" s="10"/>
-      <c r="F27" s="188"/>
-      <c r="G27" s="188"/>
+      <c r="F27" s="184"/>
+      <c r="G27" s="184"/>
       <c r="H27" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J27" s="188"/>
-      <c r="K27" s="188"/>
-      <c r="L27" s="188"/>
-      <c r="M27" s="200"/>
+      <c r="J27" s="184"/>
+      <c r="K27" s="184"/>
+      <c r="L27" s="184"/>
+      <c r="M27" s="196"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="203"/>
-      <c r="B28" s="204"/>
-      <c r="C28" s="204"/>
-      <c r="D28" s="205"/>
+      <c r="A28" s="199"/>
+      <c r="B28" s="200"/>
+      <c r="C28" s="200"/>
+      <c r="D28" s="201"/>
       <c r="E28" s="10"/>
-      <c r="F28" s="188"/>
-      <c r="G28" s="188"/>
+      <c r="F28" s="184"/>
+      <c r="G28" s="184"/>
       <c r="H28" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J28" s="188"/>
-      <c r="K28" s="188"/>
-      <c r="L28" s="188"/>
-      <c r="M28" s="200"/>
+      <c r="J28" s="184"/>
+      <c r="K28" s="184"/>
+      <c r="L28" s="184"/>
+      <c r="M28" s="196"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="203"/>
-      <c r="B29" s="204"/>
-      <c r="C29" s="204"/>
-      <c r="D29" s="205"/>
+      <c r="A29" s="199"/>
+      <c r="B29" s="200"/>
+      <c r="C29" s="200"/>
+      <c r="D29" s="201"/>
       <c r="E29" s="10"/>
-      <c r="F29" s="188"/>
-      <c r="G29" s="188"/>
+      <c r="F29" s="184"/>
+      <c r="G29" s="184"/>
       <c r="H29" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J29" s="188"/>
-      <c r="K29" s="188"/>
-      <c r="L29" s="188"/>
-      <c r="M29" s="200"/>
+      <c r="J29" s="184"/>
+      <c r="K29" s="184"/>
+      <c r="L29" s="184"/>
+      <c r="M29" s="196"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="201" t="s">
+      <c r="A30" s="197" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="202"/>
-      <c r="C30" s="202"/>
-      <c r="D30" s="202"/>
+      <c r="B30" s="198"/>
+      <c r="C30" s="198"/>
+      <c r="D30" s="198"/>
       <c r="E30" s="9"/>
-      <c r="F30" s="189"/>
-      <c r="G30" s="188"/>
-      <c r="H30" s="206"/>
-      <c r="I30" s="208"/>
-      <c r="J30" s="206"/>
-      <c r="K30" s="207"/>
-      <c r="L30" s="207"/>
-      <c r="M30" s="208"/>
+      <c r="F30" s="185"/>
+      <c r="G30" s="184"/>
+      <c r="H30" s="202"/>
+      <c r="I30" s="204"/>
+      <c r="J30" s="202"/>
+      <c r="K30" s="203"/>
+      <c r="L30" s="203"/>
+      <c r="M30" s="204"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="190" t="s">
+      <c r="A31" s="186" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="191"/>
-      <c r="C31" s="191"/>
-      <c r="D31" s="191"/>
-      <c r="E31" s="191"/>
-      <c r="F31" s="191"/>
-      <c r="G31" s="191"/>
-      <c r="H31" s="191"/>
-      <c r="I31" s="191"/>
-      <c r="J31" s="191"/>
-      <c r="K31" s="191"/>
-      <c r="L31" s="191"/>
-      <c r="M31" s="192"/>
+      <c r="B31" s="187"/>
+      <c r="C31" s="187"/>
+      <c r="D31" s="187"/>
+      <c r="E31" s="187"/>
+      <c r="F31" s="187"/>
+      <c r="G31" s="187"/>
+      <c r="H31" s="187"/>
+      <c r="I31" s="187"/>
+      <c r="J31" s="187"/>
+      <c r="K31" s="187"/>
+      <c r="L31" s="187"/>
+      <c r="M31" s="188"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="197" t="s">
+      <c r="A32" s="193" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="195"/>
-      <c r="C32" s="195" t="s">
+      <c r="B32" s="191"/>
+      <c r="C32" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="195"/>
-      <c r="E32" s="198" t="s">
+      <c r="D32" s="191"/>
+      <c r="E32" s="194" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="199" t="s">
+      <c r="F32" s="195" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="193" t="s">
+      <c r="G32" s="189" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="193"/>
-      <c r="I32" s="193"/>
-      <c r="J32" s="193"/>
-      <c r="K32" s="193"/>
-      <c r="L32" s="195" t="s">
+      <c r="H32" s="189"/>
+      <c r="I32" s="189"/>
+      <c r="J32" s="189"/>
+      <c r="K32" s="189"/>
+      <c r="L32" s="191" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="196"/>
+      <c r="M32" s="192"/>
     </row>
     <row r="33" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
@@ -8692,15 +8207,15 @@
       <c r="D33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="198"/>
-      <c r="F33" s="199"/>
-      <c r="G33" s="194" t="s">
+      <c r="E33" s="194"/>
+      <c r="F33" s="195"/>
+      <c r="G33" s="190" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="194"/>
-      <c r="I33" s="194"/>
-      <c r="J33" s="194"/>
-      <c r="K33" s="194"/>
+      <c r="H33" s="190"/>
+      <c r="I33" s="190"/>
+      <c r="J33" s="190"/>
+      <c r="K33" s="190"/>
       <c r="L33" s="2" t="s">
         <v>14</v>
       </c>
@@ -8709,443 +8224,443 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="67"/>
+      <c r="A34" s="66"/>
       <c r="B34" s="10"/>
       <c r="C34" s="9"/>
-      <c r="D34" s="66"/>
+      <c r="D34" s="65"/>
       <c r="E34" s="9"/>
       <c r="F34" s="10"/>
-      <c r="G34" s="165" t="s">
+      <c r="G34" s="161" t="s">
         <v>73</v>
       </c>
-      <c r="H34" s="166"/>
-      <c r="I34" s="166"/>
-      <c r="J34" s="166"/>
-      <c r="K34" s="167"/>
-      <c r="L34" s="68"/>
-      <c r="M34" s="69"/>
+      <c r="H34" s="162"/>
+      <c r="I34" s="162"/>
+      <c r="J34" s="162"/>
+      <c r="K34" s="163"/>
+      <c r="L34" s="67"/>
+      <c r="M34" s="68"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" s="70"/>
+      <c r="A35" s="69"/>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
-      <c r="F35" s="68"/>
-      <c r="G35" s="165"/>
-      <c r="H35" s="166"/>
-      <c r="I35" s="166"/>
-      <c r="J35" s="166"/>
-      <c r="K35" s="167"/>
-      <c r="L35" s="68"/>
-      <c r="M35" s="69"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="161"/>
+      <c r="H35" s="162"/>
+      <c r="I35" s="162"/>
+      <c r="J35" s="162"/>
+      <c r="K35" s="163"/>
+      <c r="L35" s="67"/>
+      <c r="M35" s="68"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" s="70"/>
+      <c r="A36" s="69"/>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="165"/>
-      <c r="H36" s="166"/>
-      <c r="I36" s="166"/>
-      <c r="J36" s="166"/>
-      <c r="K36" s="167"/>
-      <c r="L36" s="68"/>
-      <c r="M36" s="69"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="161"/>
+      <c r="H36" s="162"/>
+      <c r="I36" s="162"/>
+      <c r="J36" s="162"/>
+      <c r="K36" s="163"/>
+      <c r="L36" s="67"/>
+      <c r="M36" s="68"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A37" s="70"/>
+      <c r="A37" s="69"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
-      <c r="F37" s="68"/>
-      <c r="G37" s="165"/>
-      <c r="H37" s="166"/>
-      <c r="I37" s="166"/>
-      <c r="J37" s="166"/>
-      <c r="K37" s="167"/>
-      <c r="L37" s="68"/>
-      <c r="M37" s="69"/>
-      <c r="Q37" s="156"/>
-      <c r="R37" s="156"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="161"/>
+      <c r="H37" s="162"/>
+      <c r="I37" s="162"/>
+      <c r="J37" s="162"/>
+      <c r="K37" s="163"/>
+      <c r="L37" s="67"/>
+      <c r="M37" s="68"/>
+      <c r="Q37" s="152"/>
+      <c r="R37" s="152"/>
       <c r="S37" s="7"/>
-      <c r="T37" s="133"/>
-      <c r="U37" s="133"/>
-      <c r="V37" s="133"/>
+      <c r="T37" s="129"/>
+      <c r="U37" s="129"/>
+      <c r="V37" s="129"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A38" s="70"/>
+      <c r="A38" s="69"/>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="165"/>
-      <c r="H38" s="166"/>
-      <c r="I38" s="166"/>
-      <c r="J38" s="166"/>
-      <c r="K38" s="167"/>
-      <c r="L38" s="68"/>
-      <c r="M38" s="71"/>
-      <c r="Q38" s="156"/>
-      <c r="R38" s="156"/>
+      <c r="F38" s="67"/>
+      <c r="G38" s="161"/>
+      <c r="H38" s="162"/>
+      <c r="I38" s="162"/>
+      <c r="J38" s="162"/>
+      <c r="K38" s="163"/>
+      <c r="L38" s="67"/>
+      <c r="M38" s="70"/>
+      <c r="Q38" s="152"/>
+      <c r="R38" s="152"/>
       <c r="S38" s="7"/>
-      <c r="T38" s="133"/>
-      <c r="U38" s="133"/>
-      <c r="V38" s="133"/>
+      <c r="T38" s="129"/>
+      <c r="U38" s="129"/>
+      <c r="V38" s="129"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A39" s="70"/>
+      <c r="A39" s="69"/>
       <c r="B39" s="10"/>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="165"/>
-      <c r="H39" s="166"/>
-      <c r="I39" s="166"/>
-      <c r="J39" s="166"/>
-      <c r="K39" s="167"/>
-      <c r="L39" s="68"/>
-      <c r="M39" s="71"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="161"/>
+      <c r="H39" s="162"/>
+      <c r="I39" s="162"/>
+      <c r="J39" s="162"/>
+      <c r="K39" s="163"/>
+      <c r="L39" s="67"/>
+      <c r="M39" s="70"/>
       <c r="Q39" s="6"/>
       <c r="R39" s="6"/>
-      <c r="S39" s="159"/>
-      <c r="T39" s="133"/>
-      <c r="U39" s="133"/>
-      <c r="V39" s="133"/>
+      <c r="S39" s="155"/>
+      <c r="T39" s="129"/>
+      <c r="U39" s="129"/>
+      <c r="V39" s="129"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A40" s="70"/>
+      <c r="A40" s="69"/>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
       <c r="D40" s="10"/>
       <c r="E40" s="10"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="165"/>
-      <c r="H40" s="166"/>
-      <c r="I40" s="166"/>
-      <c r="J40" s="166"/>
-      <c r="K40" s="167"/>
-      <c r="L40" s="68"/>
-      <c r="M40" s="69"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="161"/>
+      <c r="H40" s="162"/>
+      <c r="I40" s="162"/>
+      <c r="J40" s="162"/>
+      <c r="K40" s="163"/>
+      <c r="L40" s="67"/>
+      <c r="M40" s="68"/>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
-      <c r="S40" s="159"/>
-      <c r="T40" s="133"/>
-      <c r="U40" s="133"/>
-      <c r="V40" s="133"/>
+      <c r="S40" s="155"/>
+      <c r="T40" s="129"/>
+      <c r="U40" s="129"/>
+      <c r="V40" s="129"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A41" s="70"/>
+      <c r="A41" s="69"/>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
       <c r="D41" s="10"/>
       <c r="E41" s="10"/>
-      <c r="F41" s="68"/>
-      <c r="G41" s="165"/>
-      <c r="H41" s="166"/>
-      <c r="I41" s="166"/>
-      <c r="J41" s="166"/>
-      <c r="K41" s="167"/>
-      <c r="L41" s="68"/>
-      <c r="M41" s="69"/>
+      <c r="F41" s="67"/>
+      <c r="G41" s="161"/>
+      <c r="H41" s="162"/>
+      <c r="I41" s="162"/>
+      <c r="J41" s="162"/>
+      <c r="K41" s="163"/>
+      <c r="L41" s="67"/>
+      <c r="M41" s="68"/>
     </row>
     <row r="42" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="72"/>
-      <c r="B42" s="73"/>
-      <c r="C42" s="74"/>
-      <c r="D42" s="73"/>
-      <c r="E42" s="74"/>
-      <c r="F42" s="75"/>
-      <c r="G42" s="168" t="s">
+      <c r="A42" s="71"/>
+      <c r="B42" s="72"/>
+      <c r="C42" s="73"/>
+      <c r="D42" s="72"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="74"/>
+      <c r="G42" s="164" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="169"/>
-      <c r="I42" s="169"/>
-      <c r="J42" s="169"/>
-      <c r="K42" s="170"/>
-      <c r="L42" s="75"/>
-      <c r="M42" s="76"/>
+      <c r="H42" s="165"/>
+      <c r="I42" s="165"/>
+      <c r="J42" s="165"/>
+      <c r="K42" s="166"/>
+      <c r="L42" s="74"/>
+      <c r="M42" s="75"/>
     </row>
     <row r="43" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="135" t="s">
+      <c r="A43" s="131" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="136"/>
-      <c r="C43" s="136"/>
-      <c r="D43" s="136"/>
-      <c r="E43" s="136"/>
-      <c r="F43" s="136"/>
-      <c r="G43" s="136"/>
-      <c r="H43" s="137"/>
-      <c r="I43" s="179" t="s">
+      <c r="B43" s="132"/>
+      <c r="C43" s="132"/>
+      <c r="D43" s="132"/>
+      <c r="E43" s="132"/>
+      <c r="F43" s="132"/>
+      <c r="G43" s="132"/>
+      <c r="H43" s="133"/>
+      <c r="I43" s="175" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="180"/>
-      <c r="K43" s="180"/>
-      <c r="L43" s="180"/>
-      <c r="M43" s="181"/>
+      <c r="J43" s="176"/>
+      <c r="K43" s="176"/>
+      <c r="L43" s="176"/>
+      <c r="M43" s="177"/>
     </row>
     <row r="44" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="138"/>
-      <c r="B44" s="139"/>
-      <c r="C44" s="139"/>
-      <c r="D44" s="139"/>
-      <c r="E44" s="139"/>
-      <c r="F44" s="139"/>
-      <c r="G44" s="139"/>
-      <c r="H44" s="140"/>
-      <c r="I44" s="182"/>
-      <c r="J44" s="183"/>
-      <c r="K44" s="183"/>
-      <c r="L44" s="183"/>
-      <c r="M44" s="184"/>
+      <c r="A44" s="134"/>
+      <c r="B44" s="135"/>
+      <c r="C44" s="135"/>
+      <c r="D44" s="135"/>
+      <c r="E44" s="135"/>
+      <c r="F44" s="135"/>
+      <c r="G44" s="135"/>
+      <c r="H44" s="136"/>
+      <c r="I44" s="178"/>
+      <c r="J44" s="179"/>
+      <c r="K44" s="179"/>
+      <c r="L44" s="179"/>
+      <c r="M44" s="180"/>
     </row>
     <row r="45" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="141" t="s">
+      <c r="A45" s="137" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="142"/>
-      <c r="C45" s="142"/>
-      <c r="D45" s="142"/>
-      <c r="E45" s="142"/>
-      <c r="F45" s="142"/>
-      <c r="G45" s="142"/>
-      <c r="H45" s="143"/>
-      <c r="I45" s="185" t="s">
+      <c r="B45" s="138"/>
+      <c r="C45" s="138"/>
+      <c r="D45" s="138"/>
+      <c r="E45" s="138"/>
+      <c r="F45" s="138"/>
+      <c r="G45" s="138"/>
+      <c r="H45" s="139"/>
+      <c r="I45" s="181" t="s">
         <v>36</v>
       </c>
-      <c r="J45" s="186"/>
-      <c r="K45" s="186"/>
-      <c r="L45" s="186"/>
-      <c r="M45" s="187"/>
+      <c r="J45" s="182"/>
+      <c r="K45" s="182"/>
+      <c r="L45" s="182"/>
+      <c r="M45" s="183"/>
     </row>
     <row r="46" spans="1:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="141" t="s">
+      <c r="A46" s="137" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="142"/>
-      <c r="C46" s="142"/>
-      <c r="D46" s="142"/>
-      <c r="E46" s="142"/>
-      <c r="F46" s="142"/>
-      <c r="G46" s="142"/>
-      <c r="H46" s="143"/>
-      <c r="I46" s="185"/>
-      <c r="J46" s="186"/>
-      <c r="K46" s="186"/>
-      <c r="L46" s="186"/>
-      <c r="M46" s="187"/>
+      <c r="B46" s="138"/>
+      <c r="C46" s="138"/>
+      <c r="D46" s="138"/>
+      <c r="E46" s="138"/>
+      <c r="F46" s="138"/>
+      <c r="G46" s="138"/>
+      <c r="H46" s="139"/>
+      <c r="I46" s="181"/>
+      <c r="J46" s="182"/>
+      <c r="K46" s="182"/>
+      <c r="L46" s="182"/>
+      <c r="M46" s="183"/>
     </row>
     <row r="47" spans="1:22" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="144"/>
-      <c r="B47" s="145"/>
-      <c r="C47" s="145"/>
-      <c r="D47" s="145"/>
-      <c r="E47" s="145"/>
-      <c r="F47" s="145"/>
-      <c r="G47" s="145"/>
-      <c r="H47" s="146"/>
-      <c r="I47" s="130" t="s">
+      <c r="A47" s="140"/>
+      <c r="B47" s="141"/>
+      <c r="C47" s="141"/>
+      <c r="D47" s="141"/>
+      <c r="E47" s="141"/>
+      <c r="F47" s="141"/>
+      <c r="G47" s="141"/>
+      <c r="H47" s="142"/>
+      <c r="I47" s="126" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="131"/>
-      <c r="K47" s="131"/>
-      <c r="L47" s="131"/>
-      <c r="M47" s="132"/>
+      <c r="J47" s="127"/>
+      <c r="K47" s="127"/>
+      <c r="L47" s="127"/>
+      <c r="M47" s="128"/>
     </row>
     <row r="48" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="151" t="s">
+      <c r="A48" s="147" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="152"/>
-      <c r="C48" s="152"/>
-      <c r="D48" s="152"/>
-      <c r="E48" s="152"/>
-      <c r="F48" s="152"/>
-      <c r="G48" s="152"/>
-      <c r="H48" s="152"/>
-      <c r="I48" s="152"/>
-      <c r="J48" s="152"/>
-      <c r="K48" s="152"/>
-      <c r="L48" s="152"/>
-      <c r="M48" s="160"/>
+      <c r="B48" s="148"/>
+      <c r="C48" s="148"/>
+      <c r="D48" s="148"/>
+      <c r="E48" s="148"/>
+      <c r="F48" s="148"/>
+      <c r="G48" s="148"/>
+      <c r="H48" s="148"/>
+      <c r="I48" s="148"/>
+      <c r="J48" s="148"/>
+      <c r="K48" s="148"/>
+      <c r="L48" s="148"/>
+      <c r="M48" s="156"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="135" t="s">
+      <c r="A49" s="131" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="136"/>
-      <c r="C49" s="136"/>
-      <c r="D49" s="136"/>
-      <c r="E49" s="136"/>
-      <c r="F49" s="136"/>
-      <c r="G49" s="136"/>
-      <c r="H49" s="137"/>
-      <c r="I49" s="171" t="s">
+      <c r="B49" s="132"/>
+      <c r="C49" s="132"/>
+      <c r="D49" s="132"/>
+      <c r="E49" s="132"/>
+      <c r="F49" s="132"/>
+      <c r="G49" s="132"/>
+      <c r="H49" s="133"/>
+      <c r="I49" s="167" t="s">
         <v>40</v>
       </c>
-      <c r="J49" s="172"/>
-      <c r="K49" s="172"/>
-      <c r="L49" s="172"/>
-      <c r="M49" s="173"/>
+      <c r="J49" s="168"/>
+      <c r="K49" s="168"/>
+      <c r="L49" s="168"/>
+      <c r="M49" s="169"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="138"/>
-      <c r="B50" s="139"/>
-      <c r="C50" s="139"/>
-      <c r="D50" s="139"/>
-      <c r="E50" s="139"/>
-      <c r="F50" s="139"/>
-      <c r="G50" s="139"/>
-      <c r="H50" s="140"/>
-      <c r="I50" s="174"/>
-      <c r="J50" s="175"/>
-      <c r="K50" s="175"/>
-      <c r="L50" s="175"/>
-      <c r="M50" s="176"/>
+      <c r="A50" s="134"/>
+      <c r="B50" s="135"/>
+      <c r="C50" s="135"/>
+      <c r="D50" s="135"/>
+      <c r="E50" s="135"/>
+      <c r="F50" s="135"/>
+      <c r="G50" s="135"/>
+      <c r="H50" s="136"/>
+      <c r="I50" s="170"/>
+      <c r="J50" s="171"/>
+      <c r="K50" s="171"/>
+      <c r="L50" s="171"/>
+      <c r="M50" s="172"/>
     </row>
     <row r="51" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="177"/>
-      <c r="B51" s="178"/>
-      <c r="C51" s="178"/>
-      <c r="D51" s="178"/>
-      <c r="E51" s="139"/>
-      <c r="F51" s="139"/>
-      <c r="G51" s="139"/>
-      <c r="H51" s="140"/>
-      <c r="I51" s="147" t="s">
+      <c r="A51" s="173"/>
+      <c r="B51" s="174"/>
+      <c r="C51" s="174"/>
+      <c r="D51" s="174"/>
+      <c r="E51" s="135"/>
+      <c r="F51" s="135"/>
+      <c r="G51" s="135"/>
+      <c r="H51" s="136"/>
+      <c r="I51" s="143" t="s">
         <v>41</v>
       </c>
-      <c r="J51" s="148"/>
-      <c r="K51" s="149"/>
-      <c r="L51" s="149"/>
-      <c r="M51" s="150"/>
+      <c r="J51" s="144"/>
+      <c r="K51" s="145"/>
+      <c r="L51" s="145"/>
+      <c r="M51" s="146"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="151" t="s">
+      <c r="A52" s="147" t="s">
         <v>42</v>
       </c>
-      <c r="B52" s="152"/>
-      <c r="C52" s="152"/>
-      <c r="D52" s="152"/>
-      <c r="E52" s="77" t="s">
+      <c r="B52" s="148"/>
+      <c r="C52" s="148"/>
+      <c r="D52" s="148"/>
+      <c r="E52" s="76" t="s">
         <v>44</v>
       </c>
-      <c r="F52" s="78"/>
-      <c r="G52" s="157" t="s">
+      <c r="F52" s="77"/>
+      <c r="G52" s="153" t="s">
         <v>45</v>
       </c>
-      <c r="H52" s="157"/>
-      <c r="I52" s="157"/>
-      <c r="J52" s="158"/>
-      <c r="K52" s="152" t="s">
+      <c r="H52" s="153"/>
+      <c r="I52" s="153"/>
+      <c r="J52" s="154"/>
+      <c r="K52" s="148" t="s">
         <v>50</v>
       </c>
-      <c r="L52" s="152"/>
-      <c r="M52" s="160"/>
+      <c r="L52" s="148"/>
+      <c r="M52" s="156"/>
     </row>
     <row r="53" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="153" t="s">
+      <c r="A53" s="149" t="s">
         <v>43</v>
       </c>
-      <c r="B53" s="154"/>
-      <c r="C53" s="154"/>
-      <c r="D53" s="154"/>
-      <c r="E53" s="60"/>
-      <c r="J53" s="57"/>
-      <c r="K53" s="161" t="s">
+      <c r="B53" s="150"/>
+      <c r="C53" s="150"/>
+      <c r="D53" s="150"/>
+      <c r="E53" s="59"/>
+      <c r="J53" s="56"/>
+      <c r="K53" s="157" t="s">
         <v>52</v>
       </c>
-      <c r="L53" s="161"/>
-      <c r="M53" s="162"/>
+      <c r="L53" s="157"/>
+      <c r="M53" s="158"/>
     </row>
     <row r="54" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="153"/>
-      <c r="B54" s="154"/>
-      <c r="C54" s="154"/>
-      <c r="D54" s="154"/>
-      <c r="E54" s="155" t="s">
+      <c r="A54" s="149"/>
+      <c r="B54" s="150"/>
+      <c r="C54" s="150"/>
+      <c r="D54" s="150"/>
+      <c r="E54" s="151" t="s">
         <v>46</v>
       </c>
-      <c r="F54" s="156"/>
+      <c r="F54" s="152"/>
       <c r="G54" s="7"/>
-      <c r="H54" s="133" t="s">
+      <c r="H54" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="I54" s="133"/>
-      <c r="J54" s="134"/>
-      <c r="K54" s="161"/>
-      <c r="L54" s="161"/>
-      <c r="M54" s="162"/>
+      <c r="I54" s="129"/>
+      <c r="J54" s="130"/>
+      <c r="K54" s="157"/>
+      <c r="L54" s="157"/>
+      <c r="M54" s="158"/>
     </row>
     <row r="55" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="153"/>
-      <c r="B55" s="154"/>
-      <c r="C55" s="154"/>
-      <c r="D55" s="154"/>
-      <c r="E55" s="155" t="s">
+      <c r="A55" s="149"/>
+      <c r="B55" s="150"/>
+      <c r="C55" s="150"/>
+      <c r="D55" s="150"/>
+      <c r="E55" s="151" t="s">
         <v>47</v>
       </c>
-      <c r="F55" s="156"/>
-      <c r="G55" s="156"/>
-      <c r="H55" s="133" t="s">
+      <c r="F55" s="152"/>
+      <c r="G55" s="152"/>
+      <c r="H55" s="129" t="s">
         <v>48</v>
       </c>
-      <c r="I55" s="133"/>
-      <c r="J55" s="134"/>
-      <c r="K55" s="161"/>
-      <c r="L55" s="161"/>
-      <c r="M55" s="162"/>
+      <c r="I55" s="129"/>
+      <c r="J55" s="130"/>
+      <c r="K55" s="157"/>
+      <c r="L55" s="157"/>
+      <c r="M55" s="158"/>
     </row>
     <row r="56" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="60"/>
-      <c r="D56" s="57"/>
-      <c r="E56" s="155"/>
-      <c r="F56" s="156"/>
-      <c r="G56" s="156"/>
-      <c r="H56" s="133"/>
-      <c r="I56" s="133"/>
-      <c r="J56" s="134"/>
-      <c r="K56" s="163" t="s">
+      <c r="A56" s="59"/>
+      <c r="D56" s="56"/>
+      <c r="E56" s="151"/>
+      <c r="F56" s="152"/>
+      <c r="G56" s="152"/>
+      <c r="H56" s="129"/>
+      <c r="I56" s="129"/>
+      <c r="J56" s="130"/>
+      <c r="K56" s="159" t="s">
         <v>51</v>
       </c>
-      <c r="L56" s="163"/>
-      <c r="M56" s="164"/>
+      <c r="L56" s="159"/>
+      <c r="M56" s="160"/>
     </row>
     <row r="57" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="60"/>
-      <c r="D57" s="57"/>
-      <c r="E57" s="155"/>
-      <c r="F57" s="156"/>
+      <c r="A57" s="59"/>
+      <c r="D57" s="56"/>
+      <c r="E57" s="151"/>
+      <c r="F57" s="152"/>
       <c r="G57" s="7"/>
-      <c r="H57" s="133" t="s">
+      <c r="H57" s="129" t="s">
         <v>49</v>
       </c>
-      <c r="I57" s="133"/>
-      <c r="J57" s="134"/>
-      <c r="K57" s="79"/>
-      <c r="L57" s="80"/>
-      <c r="M57" s="81"/>
+      <c r="I57" s="129"/>
+      <c r="J57" s="130"/>
+      <c r="K57" s="78"/>
+      <c r="L57" s="79"/>
+      <c r="M57" s="80"/>
     </row>
     <row r="58" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="82"/>
-      <c r="B58" s="246"/>
-      <c r="C58" s="246"/>
-      <c r="D58" s="49"/>
-      <c r="E58" s="127"/>
-      <c r="F58" s="128"/>
-      <c r="G58" s="128"/>
-      <c r="H58" s="128"/>
-      <c r="I58" s="128"/>
-      <c r="J58" s="129"/>
-      <c r="K58" s="83"/>
-      <c r="L58" s="84"/>
-      <c r="M58" s="85"/>
+      <c r="A58" s="81"/>
+      <c r="B58" s="242"/>
+      <c r="C58" s="242"/>
+      <c r="D58" s="48"/>
+      <c r="E58" s="123"/>
+      <c r="F58" s="124"/>
+      <c r="G58" s="124"/>
+      <c r="H58" s="124"/>
+      <c r="I58" s="124"/>
+      <c r="J58" s="125"/>
+      <c r="K58" s="82"/>
+      <c r="L58" s="83"/>
+      <c r="M58" s="84"/>
     </row>
     <row r="59" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3"/>
@@ -9282,7 +8797,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6EF17896-8669-4AD8-94BE-BA18AA09DA67}">
           <x14:formula1>
-            <xm:f>ADDRESS!$A$2:$A$30</xm:f>
+            <xm:f>#REF!</xm:f>
           </x14:formula1>
           <xm:sqref>B8</xm:sqref>
         </x14:dataValidation>
@@ -9290,1007 +8805,4 @@
     </ext>
   </extLst>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{722D7E88-64F3-46D1-93E5-B41D536177D5}">
-  <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="C1" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="D1" s="31" t="s">
-        <v>187</v>
-      </c>
-      <c r="E1" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="H1" s="86" t="s">
-        <v>222</v>
-      </c>
-      <c r="I1" s="86" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2">
-        <v>92336</v>
-      </c>
-      <c r="H2" s="86" t="s">
-        <v>226</v>
-      </c>
-      <c r="I2" s="86" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E3">
-        <v>81001</v>
-      </c>
-      <c r="H3" s="86" t="s">
-        <v>224</v>
-      </c>
-      <c r="I3" s="86">
-        <v>10285609</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E4">
-        <v>24477</v>
-      </c>
-      <c r="H4" s="86" t="s">
-        <v>225</v>
-      </c>
-      <c r="I4" s="87">
-        <v>523953410</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="31" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5">
-        <v>55432</v>
-      </c>
-      <c r="H5" s="86" t="s">
-        <v>232</v>
-      </c>
-      <c r="I5" s="88">
-        <v>59642884</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6">
-        <v>95776</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7">
-        <v>31793</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" t="s">
-        <v>99</v>
-      </c>
-      <c r="D8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8">
-        <v>53066</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E9">
-        <v>97321</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>105</v>
-      </c>
-      <c r="B10" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E10">
-        <v>46231</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>109</v>
-      </c>
-      <c r="B11" t="s">
-        <v>110</v>
-      </c>
-      <c r="C11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D11" t="s">
-        <v>112</v>
-      </c>
-      <c r="E11">
-        <v>75706</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>113</v>
-      </c>
-      <c r="B12" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" t="s">
-        <v>115</v>
-      </c>
-      <c r="D12" t="s">
-        <v>116</v>
-      </c>
-      <c r="E12">
-        <v>12831</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>117</v>
-      </c>
-      <c r="B13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C13" t="s">
-        <v>119</v>
-      </c>
-      <c r="D13" t="s">
-        <v>120</v>
-      </c>
-      <c r="E13">
-        <v>35756</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>121</v>
-      </c>
-      <c r="B14" t="s">
-        <v>122</v>
-      </c>
-      <c r="C14" t="s">
-        <v>123</v>
-      </c>
-      <c r="D14" t="s">
-        <v>124</v>
-      </c>
-      <c r="E14">
-        <v>49053</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B15" t="s">
-        <v>126</v>
-      </c>
-      <c r="C15" t="s">
-        <v>127</v>
-      </c>
-      <c r="D15" t="s">
-        <v>128</v>
-      </c>
-      <c r="E15">
-        <v>85043</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>129</v>
-      </c>
-      <c r="B16" t="s">
-        <v>130</v>
-      </c>
-      <c r="C16" t="s">
-        <v>131</v>
-      </c>
-      <c r="D16" t="s">
-        <v>132</v>
-      </c>
-      <c r="E16">
-        <v>17202</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>133</v>
-      </c>
-      <c r="B17" t="s">
-        <v>134</v>
-      </c>
-      <c r="C17" t="s">
-        <v>135</v>
-      </c>
-      <c r="D17" t="s">
-        <v>136</v>
-      </c>
-      <c r="E17">
-        <v>50613</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>137</v>
-      </c>
-      <c r="B18" t="s">
-        <v>138</v>
-      </c>
-      <c r="C18" t="s">
-        <v>139</v>
-      </c>
-      <c r="D18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E18">
-        <v>93263</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>140</v>
-      </c>
-      <c r="B19" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" t="s">
-        <v>142</v>
-      </c>
-      <c r="D19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E19">
-        <v>29078</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>144</v>
-      </c>
-      <c r="B20" t="s">
-        <v>145</v>
-      </c>
-      <c r="C20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D20" t="s">
-        <v>112</v>
-      </c>
-      <c r="E20">
-        <v>76065</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>147</v>
-      </c>
-      <c r="B21" t="s">
-        <v>148</v>
-      </c>
-      <c r="C21" t="s">
-        <v>149</v>
-      </c>
-      <c r="D21" t="s">
-        <v>116</v>
-      </c>
-      <c r="E21">
-        <v>12010</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>150</v>
-      </c>
-      <c r="B22" t="s">
-        <v>151</v>
-      </c>
-      <c r="C22" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" t="s">
-        <v>153</v>
-      </c>
-      <c r="E22">
-        <v>66609</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>154</v>
-      </c>
-      <c r="B23" t="s">
-        <v>155</v>
-      </c>
-      <c r="C23" t="s">
-        <v>156</v>
-      </c>
-      <c r="D23" t="s">
-        <v>157</v>
-      </c>
-      <c r="E23">
-        <v>43162</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>158</v>
-      </c>
-      <c r="B24" t="s">
-        <v>159</v>
-      </c>
-      <c r="C24" t="s">
-        <v>160</v>
-      </c>
-      <c r="D24" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24">
-        <v>92376</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>161</v>
-      </c>
-      <c r="B25" t="s">
-        <v>162</v>
-      </c>
-      <c r="C25" t="s">
-        <v>163</v>
-      </c>
-      <c r="D25" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25">
-        <v>31320</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>164</v>
-      </c>
-      <c r="B26" t="s">
-        <v>165</v>
-      </c>
-      <c r="C26" t="s">
-        <v>166</v>
-      </c>
-      <c r="D26" t="s">
-        <v>167</v>
-      </c>
-      <c r="E26" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>169</v>
-      </c>
-      <c r="B27" t="s">
-        <v>170</v>
-      </c>
-      <c r="C27" t="s">
-        <v>171</v>
-      </c>
-      <c r="D27" t="s">
-        <v>77</v>
-      </c>
-      <c r="E27">
-        <v>92518</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>172</v>
-      </c>
-      <c r="B28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C28" t="s">
-        <v>174</v>
-      </c>
-      <c r="D28" t="s">
-        <v>175</v>
-      </c>
-      <c r="E28" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>177</v>
-      </c>
-      <c r="B29" t="s">
-        <v>178</v>
-      </c>
-      <c r="C29" t="s">
-        <v>179</v>
-      </c>
-      <c r="D29" t="s">
-        <v>180</v>
-      </c>
-      <c r="E29">
-        <v>60623</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>181</v>
-      </c>
-      <c r="B30" t="s">
-        <v>182</v>
-      </c>
-      <c r="C30" t="s">
-        <v>183</v>
-      </c>
-      <c r="D30" t="s">
-        <v>96</v>
-      </c>
-      <c r="E30">
-        <v>30228</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A09692DB-4271-4A63-8630-0427F5F0CBED}">
-  <dimension ref="A2:D32"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="31" t="s">
-        <v>86</v>
-      </c>
-      <c r="B3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C3">
-        <v>40</v>
-      </c>
-      <c r="D3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s">
-        <v>194</v>
-      </c>
-      <c r="C4">
-        <v>38</v>
-      </c>
-      <c r="D4">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C5">
-        <v>59</v>
-      </c>
-      <c r="D5">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B6" t="s">
-        <v>196</v>
-      </c>
-      <c r="C6">
-        <v>81</v>
-      </c>
-      <c r="D6">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B7" t="s">
-        <v>197</v>
-      </c>
-      <c r="C7">
-        <v>70</v>
-      </c>
-      <c r="D7">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C8">
-        <v>62</v>
-      </c>
-      <c r="D8">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B9" t="s">
-        <v>199</v>
-      </c>
-      <c r="C9">
-        <v>66</v>
-      </c>
-      <c r="D9">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>105</v>
-      </c>
-      <c r="B10" t="s">
-        <v>200</v>
-      </c>
-      <c r="C10">
-        <v>65</v>
-      </c>
-      <c r="D10">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B11" t="s">
-        <v>201</v>
-      </c>
-      <c r="C11">
-        <v>61</v>
-      </c>
-      <c r="D11">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>109</v>
-      </c>
-      <c r="B12" t="s">
-        <v>202</v>
-      </c>
-      <c r="C12">
-        <v>83</v>
-      </c>
-      <c r="D12">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B13" t="s">
-        <v>203</v>
-      </c>
-      <c r="C13">
-        <v>70</v>
-      </c>
-      <c r="D13">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>117</v>
-      </c>
-      <c r="B14" t="s">
-        <v>204</v>
-      </c>
-      <c r="C14">
-        <v>50</v>
-      </c>
-      <c r="D14">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>121</v>
-      </c>
-      <c r="B15" t="s">
-        <v>205</v>
-      </c>
-      <c r="C15">
-        <v>70</v>
-      </c>
-      <c r="D15">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B16" t="s">
-        <v>206</v>
-      </c>
-      <c r="C16">
-        <v>69</v>
-      </c>
-      <c r="D16">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>129</v>
-      </c>
-      <c r="B17" t="s">
-        <v>207</v>
-      </c>
-      <c r="C17">
-        <v>54</v>
-      </c>
-      <c r="D17">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>133</v>
-      </c>
-      <c r="B18" t="s">
-        <v>208</v>
-      </c>
-      <c r="C18">
-        <v>65</v>
-      </c>
-      <c r="D18">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>137</v>
-      </c>
-      <c r="B19" t="s">
-        <v>209</v>
-      </c>
-      <c r="C19">
-        <v>65</v>
-      </c>
-      <c r="D19">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>140</v>
-      </c>
-      <c r="B20" t="s">
-        <v>210</v>
-      </c>
-      <c r="C20">
-        <v>70</v>
-      </c>
-      <c r="D20">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>144</v>
-      </c>
-      <c r="B21" t="s">
-        <v>211</v>
-      </c>
-      <c r="C21">
-        <v>55</v>
-      </c>
-      <c r="D21">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>147</v>
-      </c>
-      <c r="B22" t="s">
-        <v>212</v>
-      </c>
-      <c r="C22">
-        <v>54</v>
-      </c>
-      <c r="D22">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>150</v>
-      </c>
-      <c r="B23" t="s">
-        <v>213</v>
-      </c>
-      <c r="C23">
-        <v>76</v>
-      </c>
-      <c r="D23">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>154</v>
-      </c>
-      <c r="B24" t="s">
-        <v>214</v>
-      </c>
-      <c r="C24">
-        <v>76</v>
-      </c>
-      <c r="D24">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>158</v>
-      </c>
-      <c r="B25" t="s">
-        <v>215</v>
-      </c>
-      <c r="C25">
-        <v>65</v>
-      </c>
-      <c r="D25">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>161</v>
-      </c>
-      <c r="B26" t="s">
-        <v>216</v>
-      </c>
-      <c r="C26">
-        <v>56</v>
-      </c>
-      <c r="D26">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>164</v>
-      </c>
-      <c r="B27" t="s">
-        <v>217</v>
-      </c>
-      <c r="C27">
-        <v>83</v>
-      </c>
-      <c r="D27">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>169</v>
-      </c>
-      <c r="B28" t="s">
-        <v>218</v>
-      </c>
-      <c r="C28">
-        <v>27</v>
-      </c>
-      <c r="D28">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>172</v>
-      </c>
-      <c r="B29" t="s">
-        <v>219</v>
-      </c>
-      <c r="C29">
-        <v>16</v>
-      </c>
-      <c r="D29">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>177</v>
-      </c>
-      <c r="B30" t="s">
-        <v>220</v>
-      </c>
-      <c r="C30">
-        <v>26</v>
-      </c>
-      <c r="D30">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>181</v>
-      </c>
-      <c r="B31" t="s">
-        <v>221</v>
-      </c>
-      <c r="C31">
-        <v>16</v>
-      </c>
-      <c r="D31">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B32" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32">
-        <f>SUM(C3:C31)</f>
-        <v>1688</v>
-      </c>
-      <c r="D32">
-        <f>SUM(D3:D31)</f>
-        <v>1688</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
+++ b/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Procomm\Documents\GitHub\Acumatica_Customizations_and_Packages\Istar_Development\Projects\BOL_Generation\Code\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E097467-11F9-48A5-9D0E-F74C65F0CAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D66ACD8-23A7-4AB8-8E70-7666E918D329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{888CA347-7849-4038-B8EE-FAC87BA1B844}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="83">
   <si>
     <t>SHIP FROM</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>Address: 910 Nestle Way</t>
+  </si>
+  <si>
+    <t>BX</t>
   </si>
   <si>
     <t>Page 1 of 2</t>
@@ -4486,7 +4489,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="436" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B1" s="437"/>
       <c r="C1" s="279" t="s">
@@ -4501,7 +4504,7 @@
       <c r="J1" s="279"/>
       <c r="K1" s="279"/>
       <c r="L1" s="280" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M1" s="281"/>
     </row>
@@ -4517,7 +4520,7 @@
       <c r="G2" s="277"/>
       <c r="H2" s="278"/>
       <c r="I2" s="282" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J2" s="283"/>
       <c r="K2" s="283"/>
@@ -4526,7 +4529,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="264" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B3" s="265"/>
       <c r="C3" s="265"/>
@@ -4543,7 +4546,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="264" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B4" s="265"/>
       <c r="C4" s="265"/>
@@ -4560,7 +4563,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="264" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B5" s="265"/>
       <c r="C5" s="265"/>
@@ -4606,7 +4609,7 @@
       <c r="G7" s="277"/>
       <c r="H7" s="278"/>
       <c r="I7" s="86" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="87"/>
       <c r="K7" s="88"/>
@@ -4615,7 +4618,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="300" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B8" s="301"/>
       <c r="C8" s="301"/>
@@ -4646,7 +4649,7 @@
       <c r="G9" s="301"/>
       <c r="H9" s="304"/>
       <c r="I9" s="90" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J9" s="91"/>
       <c r="K9" s="91"/>
@@ -4655,7 +4658,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="300" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B10" s="301"/>
       <c r="C10" s="301"/>
@@ -4665,7 +4668,7 @@
       <c r="G10" s="301"/>
       <c r="H10" s="304"/>
       <c r="I10" s="92" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J10" s="93"/>
       <c r="K10" s="93"/>
@@ -4686,7 +4689,7 @@
       <c r="G11" s="290"/>
       <c r="H11" s="85"/>
       <c r="I11" s="95" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J11" s="96"/>
       <c r="K11" s="96"/>
@@ -4765,7 +4768,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="98" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B16" s="99"/>
       <c r="C16" s="99"/>
@@ -4775,7 +4778,7 @@
       <c r="G16" s="373"/>
       <c r="H16" s="374"/>
       <c r="I16" s="325" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J16" s="326"/>
       <c r="K16" s="326"/>
@@ -6408,7 +6411,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="436" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B1" s="437"/>
       <c r="C1" s="279" t="s">
@@ -6423,7 +6426,7 @@
       <c r="J1" s="279"/>
       <c r="K1" s="279"/>
       <c r="L1" s="280" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M1" s="281"/>
     </row>
@@ -7601,20 +7604,20 @@
   <sheetData>
     <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="39" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B1" s="241"/>
       <c r="C1" s="241"/>
       <c r="F1" s="40"/>
       <c r="G1" s="40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H1" s="40"/>
       <c r="I1" s="40"/>
       <c r="J1" s="41"/>
       <c r="K1" s="41"/>
       <c r="L1" s="246" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M1" s="247"/>
     </row>
@@ -7637,7 +7640,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="207" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B3" s="208"/>
       <c r="C3" s="208"/>
@@ -7647,7 +7650,7 @@
       <c r="G3" s="208"/>
       <c r="H3" s="209"/>
       <c r="I3" s="45" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J3" s="43"/>
       <c r="K3" s="46"/>
@@ -7656,7 +7659,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="207" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B4" s="208"/>
       <c r="C4" s="208"/>
@@ -7673,7 +7676,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="207" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B5" s="208"/>
       <c r="C5" s="208"/>
@@ -7719,7 +7722,7 @@
       <c r="G7" s="259"/>
       <c r="H7" s="260"/>
       <c r="I7" s="49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="50"/>
       <c r="K7" s="51"/>
@@ -7753,7 +7756,7 @@
       </c>
       <c r="H9" s="56"/>
       <c r="I9" s="57" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J9" s="58"/>
       <c r="K9" s="58"/>
@@ -7762,7 +7765,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="59" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" s="236"/>
       <c r="D10" s="236"/>
@@ -7771,7 +7774,7 @@
       <c r="G10" s="236"/>
       <c r="H10" s="56"/>
       <c r="I10" s="60" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J10" s="61"/>
       <c r="K10" s="61"/>
@@ -7792,7 +7795,7 @@
       <c r="G11" s="252"/>
       <c r="H11" s="48"/>
       <c r="I11" s="239" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J11" s="240"/>
       <c r="K11" s="63"/>
@@ -7879,7 +7882,7 @@
       <c r="G16" s="32"/>
       <c r="H16" s="33"/>
       <c r="I16" s="230" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J16" s="231"/>
       <c r="K16" s="231"/>
@@ -7888,7 +7891,7 @@
     </row>
     <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B17" s="35"/>
       <c r="C17" s="35"/>
@@ -8225,13 +8228,17 @@
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A34" s="66"/>
-      <c r="B34" s="10"/>
+      <c r="B34" s="10" t="s">
+        <v>60</v>
+      </c>
       <c r="C34" s="9"/>
-      <c r="D34" s="65"/>
+      <c r="D34" s="65" t="s">
+        <v>60</v>
+      </c>
       <c r="E34" s="9"/>
       <c r="F34" s="10"/>
       <c r="G34" s="161" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H34" s="162"/>
       <c r="I34" s="162"/>

--- a/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
+++ b/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Procomm\Documents\GitHub\Acumatica_Customizations_and_Packages\Istar_Development\Projects\BOL_Generation\Code\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D66ACD8-23A7-4AB8-8E70-7666E918D329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC6B49A3-2085-4DF2-A6B3-2CB1712A114E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{888CA347-7849-4038-B8EE-FAC87BA1B844}"/>
   </bookViews>
@@ -494,7 +494,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="40">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -866,43 +866,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -944,19 +907,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1030,52 +980,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1452,9 +1366,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1467,21 +1378,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1509,13 +1405,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1536,47 +1426,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="18" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1584,37 +1435,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
@@ -1662,24 +1492,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2103,13 +1915,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyBorder="1" applyAlignment="1">
@@ -2133,8 +1945,140 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="32" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4487,609 +4431,609 @@
     <col min="16142" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="436" t="s">
+    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="383" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="437"/>
-      <c r="C1" s="279" t="s">
+      <c r="B1" s="384"/>
+      <c r="C1" s="380" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="279"/>
-      <c r="E1" s="279"/>
-      <c r="F1" s="279"/>
-      <c r="G1" s="279"/>
-      <c r="H1" s="279"/>
-      <c r="I1" s="279"/>
-      <c r="J1" s="279"/>
-      <c r="K1" s="279"/>
-      <c r="L1" s="280" t="s">
+      <c r="D1" s="381"/>
+      <c r="E1" s="381"/>
+      <c r="F1" s="381"/>
+      <c r="G1" s="381"/>
+      <c r="H1" s="381"/>
+      <c r="I1" s="381"/>
+      <c r="J1" s="381"/>
+      <c r="K1" s="382"/>
+      <c r="L1" s="385" t="s">
         <v>61</v>
       </c>
-      <c r="M1" s="281"/>
+      <c r="M1" s="386"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="276" t="s">
+      <c r="A2" s="247" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="277"/>
-      <c r="C2" s="277"/>
-      <c r="D2" s="277"/>
-      <c r="E2" s="277"/>
-      <c r="F2" s="277"/>
-      <c r="G2" s="277"/>
-      <c r="H2" s="278"/>
-      <c r="I2" s="282" t="s">
+      <c r="B2" s="378"/>
+      <c r="C2" s="378"/>
+      <c r="D2" s="378"/>
+      <c r="E2" s="378"/>
+      <c r="F2" s="378"/>
+      <c r="G2" s="378"/>
+      <c r="H2" s="249"/>
+      <c r="I2" s="227" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="283"/>
-      <c r="K2" s="283"/>
-      <c r="L2" s="283"/>
-      <c r="M2" s="284"/>
+      <c r="J2" s="379"/>
+      <c r="K2" s="379"/>
+      <c r="L2" s="379"/>
+      <c r="M2" s="229"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="264" t="s">
+      <c r="A3" s="212" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="265"/>
-      <c r="C3" s="265"/>
-      <c r="D3" s="265"/>
-      <c r="E3" s="265"/>
-      <c r="F3" s="265"/>
-      <c r="G3" s="265"/>
-      <c r="H3" s="266"/>
-      <c r="I3" s="285"/>
-      <c r="J3" s="286"/>
-      <c r="K3" s="286"/>
-      <c r="L3" s="286"/>
-      <c r="M3" s="287"/>
+      <c r="B3" s="213"/>
+      <c r="C3" s="213"/>
+      <c r="D3" s="213"/>
+      <c r="E3" s="213"/>
+      <c r="F3" s="213"/>
+      <c r="G3" s="213"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="227"/>
+      <c r="J3" s="228"/>
+      <c r="K3" s="228"/>
+      <c r="L3" s="228"/>
+      <c r="M3" s="229"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="264" t="s">
+      <c r="A4" s="212" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="265"/>
-      <c r="C4" s="265"/>
-      <c r="D4" s="265"/>
-      <c r="E4" s="265"/>
-      <c r="F4" s="265"/>
-      <c r="G4" s="265"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="267"/>
-      <c r="J4" s="268"/>
-      <c r="K4" s="268"/>
-      <c r="L4" s="268"/>
-      <c r="M4" s="269"/>
+      <c r="B4" s="213"/>
+      <c r="C4" s="213"/>
+      <c r="D4" s="213"/>
+      <c r="E4" s="213"/>
+      <c r="F4" s="213"/>
+      <c r="G4" s="213"/>
+      <c r="H4" s="214"/>
+      <c r="I4" s="215"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
+      <c r="M4" s="217"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="264" t="s">
+      <c r="A5" s="212" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="265"/>
-      <c r="C5" s="265"/>
-      <c r="D5" s="265"/>
-      <c r="E5" s="265"/>
-      <c r="F5" s="265"/>
-      <c r="G5" s="265"/>
-      <c r="H5" s="266"/>
-      <c r="I5" s="267"/>
-      <c r="J5" s="268"/>
-      <c r="K5" s="268"/>
-      <c r="L5" s="268"/>
-      <c r="M5" s="269"/>
+      <c r="B5" s="213"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="213"/>
+      <c r="E5" s="213"/>
+      <c r="F5" s="213"/>
+      <c r="G5" s="213"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="215"/>
+      <c r="J5" s="216"/>
+      <c r="K5" s="216"/>
+      <c r="L5" s="216"/>
+      <c r="M5" s="217"/>
     </row>
     <row r="6" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="273" t="s">
+      <c r="A6" s="221" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="274"/>
-      <c r="C6" s="274"/>
-      <c r="D6" s="274"/>
-      <c r="E6" s="274"/>
-      <c r="F6" s="275" t="s">
+      <c r="B6" s="222"/>
+      <c r="C6" s="222"/>
+      <c r="D6" s="222"/>
+      <c r="E6" s="222"/>
+      <c r="F6" s="223" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="275"/>
+      <c r="G6" s="223"/>
       <c r="H6" s="12"/>
-      <c r="I6" s="270"/>
-      <c r="J6" s="271"/>
-      <c r="K6" s="271"/>
-      <c r="L6" s="271"/>
-      <c r="M6" s="272"/>
+      <c r="I6" s="218"/>
+      <c r="J6" s="219"/>
+      <c r="K6" s="219"/>
+      <c r="L6" s="219"/>
+      <c r="M6" s="220"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="276" t="s">
+      <c r="A7" s="224" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="277"/>
-      <c r="C7" s="277"/>
-      <c r="D7" s="277"/>
-      <c r="E7" s="277"/>
-      <c r="F7" s="277"/>
-      <c r="G7" s="277"/>
-      <c r="H7" s="278"/>
-      <c r="I7" s="86" t="s">
+      <c r="B7" s="225"/>
+      <c r="C7" s="225"/>
+      <c r="D7" s="225"/>
+      <c r="E7" s="225"/>
+      <c r="F7" s="225"/>
+      <c r="G7" s="225"/>
+      <c r="H7" s="226"/>
+      <c r="I7" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="J7" s="87"/>
-      <c r="K7" s="88"/>
-      <c r="L7" s="87"/>
-      <c r="M7" s="89"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="63"/>
+      <c r="M7" s="65"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="300" t="s">
+      <c r="A8" s="242" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="301"/>
-      <c r="C8" s="301"/>
-      <c r="D8" s="301"/>
-      <c r="E8" s="302" t="s">
+      <c r="B8" s="243"/>
+      <c r="C8" s="243"/>
+      <c r="D8" s="243"/>
+      <c r="E8" s="244" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="302"/>
-      <c r="G8" s="302"/>
-      <c r="H8" s="303"/>
-      <c r="I8" s="300" t="s">
+      <c r="F8" s="244"/>
+      <c r="G8" s="244"/>
+      <c r="H8" s="245"/>
+      <c r="I8" s="242" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="301"/>
-      <c r="K8" s="301"/>
-      <c r="L8" s="301"/>
-      <c r="M8" s="304"/>
+      <c r="J8" s="243"/>
+      <c r="K8" s="243"/>
+      <c r="L8" s="243"/>
+      <c r="M8" s="246"/>
     </row>
     <row r="9" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="300" t="s">
+      <c r="A9" s="242" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="301"/>
-      <c r="C9" s="301"/>
-      <c r="D9" s="301"/>
-      <c r="E9" s="301"/>
-      <c r="F9" s="301"/>
-      <c r="G9" s="301"/>
-      <c r="H9" s="304"/>
-      <c r="I9" s="90" t="s">
+      <c r="B9" s="243"/>
+      <c r="C9" s="243"/>
+      <c r="D9" s="243"/>
+      <c r="E9" s="243"/>
+      <c r="F9" s="243"/>
+      <c r="G9" s="243"/>
+      <c r="H9" s="246"/>
+      <c r="I9" s="66" t="s">
         <v>71</v>
       </c>
-      <c r="J9" s="91"/>
-      <c r="K9" s="91"/>
-      <c r="L9" s="91"/>
-      <c r="M9" s="85"/>
+      <c r="J9" s="67"/>
+      <c r="K9" s="67"/>
+      <c r="L9" s="67"/>
+      <c r="M9" s="61"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="300" t="s">
+      <c r="A10" s="242" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="301"/>
-      <c r="C10" s="301"/>
-      <c r="D10" s="301"/>
-      <c r="E10" s="301"/>
-      <c r="F10" s="301"/>
-      <c r="G10" s="301"/>
-      <c r="H10" s="304"/>
-      <c r="I10" s="92" t="s">
+      <c r="B10" s="243"/>
+      <c r="C10" s="243"/>
+      <c r="D10" s="243"/>
+      <c r="E10" s="243"/>
+      <c r="F10" s="243"/>
+      <c r="G10" s="243"/>
+      <c r="H10" s="246"/>
+      <c r="I10" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="J10" s="93"/>
-      <c r="K10" s="93"/>
-      <c r="L10" s="93"/>
-      <c r="M10" s="94"/>
+      <c r="J10" s="69"/>
+      <c r="K10" s="69"/>
+      <c r="L10" s="69"/>
+      <c r="M10" s="70"/>
     </row>
     <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="288" t="s">
+      <c r="A11" s="230" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="289"/>
-      <c r="C11" s="289"/>
-      <c r="D11" s="289"/>
-      <c r="E11" s="289"/>
-      <c r="F11" s="290" t="s">
+      <c r="B11" s="231"/>
+      <c r="C11" s="231"/>
+      <c r="D11" s="231"/>
+      <c r="E11" s="231"/>
+      <c r="F11" s="232" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="290"/>
-      <c r="H11" s="85"/>
-      <c r="I11" s="95" t="s">
+      <c r="G11" s="232"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="71" t="s">
         <v>79</v>
       </c>
-      <c r="J11" s="96"/>
-      <c r="K11" s="96"/>
-      <c r="L11" s="96"/>
-      <c r="M11" s="97"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="72"/>
+      <c r="L11" s="72"/>
+      <c r="M11" s="73"/>
     </row>
     <row r="12" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="276" t="s">
+      <c r="A12" s="224" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="277"/>
-      <c r="C12" s="277"/>
-      <c r="D12" s="277"/>
-      <c r="E12" s="277"/>
-      <c r="F12" s="277"/>
-      <c r="G12" s="277"/>
-      <c r="H12" s="278"/>
-      <c r="I12" s="291"/>
-      <c r="J12" s="292"/>
-      <c r="K12" s="292"/>
-      <c r="L12" s="292"/>
-      <c r="M12" s="293"/>
+      <c r="B12" s="225"/>
+      <c r="C12" s="225"/>
+      <c r="D12" s="225"/>
+      <c r="E12" s="225"/>
+      <c r="F12" s="225"/>
+      <c r="G12" s="225"/>
+      <c r="H12" s="226"/>
+      <c r="I12" s="233"/>
+      <c r="J12" s="234"/>
+      <c r="K12" s="234"/>
+      <c r="L12" s="234"/>
+      <c r="M12" s="235"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="297" t="s">
+      <c r="A13" s="239" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="298"/>
-      <c r="C13" s="298"/>
-      <c r="D13" s="298"/>
-      <c r="E13" s="298"/>
-      <c r="F13" s="298"/>
-      <c r="G13" s="298"/>
-      <c r="H13" s="299"/>
-      <c r="I13" s="291"/>
-      <c r="J13" s="292"/>
-      <c r="K13" s="292"/>
-      <c r="L13" s="292"/>
-      <c r="M13" s="293"/>
+      <c r="B13" s="240"/>
+      <c r="C13" s="240"/>
+      <c r="D13" s="240"/>
+      <c r="E13" s="240"/>
+      <c r="F13" s="240"/>
+      <c r="G13" s="240"/>
+      <c r="H13" s="241"/>
+      <c r="I13" s="233"/>
+      <c r="J13" s="234"/>
+      <c r="K13" s="234"/>
+      <c r="L13" s="234"/>
+      <c r="M13" s="235"/>
     </row>
     <row r="14" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="264" t="s">
+      <c r="A14" s="212" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="265"/>
-      <c r="C14" s="265"/>
-      <c r="D14" s="265"/>
-      <c r="E14" s="265"/>
-      <c r="F14" s="265"/>
-      <c r="G14" s="265"/>
-      <c r="H14" s="266"/>
-      <c r="I14" s="294"/>
-      <c r="J14" s="295"/>
-      <c r="K14" s="295"/>
-      <c r="L14" s="295"/>
-      <c r="M14" s="296"/>
+      <c r="B14" s="213"/>
+      <c r="C14" s="213"/>
+      <c r="D14" s="213"/>
+      <c r="E14" s="213"/>
+      <c r="F14" s="213"/>
+      <c r="G14" s="213"/>
+      <c r="H14" s="214"/>
+      <c r="I14" s="236"/>
+      <c r="J14" s="237"/>
+      <c r="K14" s="237"/>
+      <c r="L14" s="237"/>
+      <c r="M14" s="238"/>
     </row>
     <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="320" t="s">
+      <c r="A15" s="262" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="321"/>
-      <c r="C15" s="321"/>
-      <c r="D15" s="321"/>
-      <c r="E15" s="321"/>
-      <c r="F15" s="321"/>
-      <c r="G15" s="321"/>
-      <c r="H15" s="321"/>
-      <c r="I15" s="322" t="s">
+      <c r="B15" s="263"/>
+      <c r="C15" s="263"/>
+      <c r="D15" s="263"/>
+      <c r="E15" s="263"/>
+      <c r="F15" s="263"/>
+      <c r="G15" s="263"/>
+      <c r="H15" s="263"/>
+      <c r="I15" s="264" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="323"/>
-      <c r="K15" s="323"/>
-      <c r="L15" s="323"/>
-      <c r="M15" s="324"/>
+      <c r="J15" s="265"/>
+      <c r="K15" s="265"/>
+      <c r="L15" s="265"/>
+      <c r="M15" s="266"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="98" t="s">
+      <c r="A16" s="74" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="99"/>
-      <c r="C16" s="99"/>
-      <c r="D16" s="99"/>
-      <c r="E16" s="99"/>
-      <c r="F16" s="373"/>
-      <c r="G16" s="373"/>
-      <c r="H16" s="374"/>
-      <c r="I16" s="325" t="s">
+      <c r="B16" s="75"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="315"/>
+      <c r="G16" s="315"/>
+      <c r="H16" s="316"/>
+      <c r="I16" s="267" t="s">
         <v>81</v>
       </c>
-      <c r="J16" s="326"/>
-      <c r="K16" s="326"/>
-      <c r="L16" s="326"/>
-      <c r="M16" s="327"/>
+      <c r="J16" s="268"/>
+      <c r="K16" s="268"/>
+      <c r="L16" s="268"/>
+      <c r="M16" s="269"/>
     </row>
     <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="100"/>
-      <c r="B17" s="101"/>
-      <c r="C17" s="101"/>
-      <c r="D17" s="101"/>
-      <c r="E17" s="101"/>
-      <c r="F17" s="101"/>
-      <c r="G17" s="101"/>
-      <c r="H17" s="102"/>
-      <c r="I17" s="328"/>
-      <c r="J17" s="302"/>
-      <c r="K17" s="329" t="s">
+      <c r="A17" s="76"/>
+      <c r="B17" s="77"/>
+      <c r="C17" s="77"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="77"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="78"/>
+      <c r="I17" s="270"/>
+      <c r="J17" s="244"/>
+      <c r="K17" s="271" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="329"/>
-      <c r="M17" s="330"/>
+      <c r="L17" s="271"/>
+      <c r="M17" s="272"/>
     </row>
     <row r="18" spans="1:13" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="100"/>
-      <c r="B18" s="101"/>
-      <c r="C18" s="101"/>
-      <c r="D18" s="101"/>
-      <c r="E18" s="101"/>
-      <c r="F18" s="101"/>
-      <c r="G18" s="101"/>
-      <c r="H18" s="102"/>
-      <c r="I18" s="333" t="s">
+      <c r="A18" s="76"/>
+      <c r="B18" s="77"/>
+      <c r="C18" s="77"/>
+      <c r="D18" s="77"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="77"/>
+      <c r="H18" s="78"/>
+      <c r="I18" s="275" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="334"/>
-      <c r="K18" s="331"/>
-      <c r="L18" s="331"/>
-      <c r="M18" s="332"/>
+      <c r="J18" s="276"/>
+      <c r="K18" s="273"/>
+      <c r="L18" s="273"/>
+      <c r="M18" s="274"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="305" t="s">
+      <c r="A19" s="247" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="306"/>
-      <c r="C19" s="306"/>
-      <c r="D19" s="306"/>
-      <c r="E19" s="306"/>
-      <c r="F19" s="306"/>
-      <c r="G19" s="306"/>
-      <c r="H19" s="306"/>
-      <c r="I19" s="306"/>
-      <c r="J19" s="306"/>
-      <c r="K19" s="306"/>
-      <c r="L19" s="306"/>
-      <c r="M19" s="307"/>
+      <c r="B19" s="248"/>
+      <c r="C19" s="248"/>
+      <c r="D19" s="248"/>
+      <c r="E19" s="248"/>
+      <c r="F19" s="248"/>
+      <c r="G19" s="248"/>
+      <c r="H19" s="248"/>
+      <c r="I19" s="248"/>
+      <c r="J19" s="248"/>
+      <c r="K19" s="248"/>
+      <c r="L19" s="248"/>
+      <c r="M19" s="249"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="308" t="s">
+      <c r="A20" s="250" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="309"/>
-      <c r="C20" s="309"/>
-      <c r="D20" s="309"/>
-      <c r="E20" s="309" t="s">
+      <c r="B20" s="251"/>
+      <c r="C20" s="251"/>
+      <c r="D20" s="251"/>
+      <c r="E20" s="251" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="309" t="s">
+      <c r="F20" s="251" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="309"/>
-      <c r="H20" s="310" t="s">
+      <c r="G20" s="251"/>
+      <c r="H20" s="252" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="311"/>
-      <c r="J20" s="312" t="s">
+      <c r="I20" s="253"/>
+      <c r="J20" s="254" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="313"/>
-      <c r="L20" s="313"/>
-      <c r="M20" s="314"/>
+      <c r="K20" s="255"/>
+      <c r="L20" s="255"/>
+      <c r="M20" s="256"/>
     </row>
     <row r="21" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="308"/>
-      <c r="B21" s="309"/>
-      <c r="C21" s="309"/>
-      <c r="D21" s="309"/>
-      <c r="E21" s="309"/>
-      <c r="F21" s="309"/>
-      <c r="G21" s="309"/>
-      <c r="H21" s="318" t="s">
+      <c r="A21" s="250"/>
+      <c r="B21" s="251"/>
+      <c r="C21" s="251"/>
+      <c r="D21" s="251"/>
+      <c r="E21" s="251"/>
+      <c r="F21" s="251"/>
+      <c r="G21" s="251"/>
+      <c r="H21" s="260" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="319"/>
-      <c r="J21" s="315"/>
-      <c r="K21" s="316"/>
-      <c r="L21" s="316"/>
-      <c r="M21" s="317"/>
+      <c r="I21" s="261"/>
+      <c r="J21" s="257"/>
+      <c r="K21" s="258"/>
+      <c r="L21" s="258"/>
+      <c r="M21" s="259"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="335"/>
-      <c r="B22" s="335"/>
-      <c r="C22" s="335"/>
-      <c r="D22" s="336"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="337"/>
-      <c r="G22" s="337"/>
-      <c r="H22" s="104" t="s">
+      <c r="A22" s="277"/>
+      <c r="B22" s="277"/>
+      <c r="C22" s="277"/>
+      <c r="D22" s="278"/>
+      <c r="E22" s="79"/>
+      <c r="F22" s="279"/>
+      <c r="G22" s="279"/>
+      <c r="H22" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I22" s="104" t="s">
+      <c r="I22" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="338"/>
-      <c r="K22" s="338"/>
-      <c r="L22" s="338"/>
-      <c r="M22" s="339"/>
+      <c r="J22" s="280"/>
+      <c r="K22" s="280"/>
+      <c r="L22" s="280"/>
+      <c r="M22" s="281"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="335"/>
-      <c r="B23" s="335"/>
-      <c r="C23" s="335"/>
-      <c r="D23" s="336"/>
-      <c r="E23" s="103"/>
-      <c r="F23" s="337"/>
-      <c r="G23" s="337"/>
-      <c r="H23" s="104" t="s">
+      <c r="A23" s="277"/>
+      <c r="B23" s="277"/>
+      <c r="C23" s="277"/>
+      <c r="D23" s="278"/>
+      <c r="E23" s="79"/>
+      <c r="F23" s="279"/>
+      <c r="G23" s="279"/>
+      <c r="H23" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I23" s="104" t="s">
+      <c r="I23" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="338"/>
-      <c r="K23" s="338"/>
-      <c r="L23" s="338"/>
-      <c r="M23" s="339"/>
+      <c r="J23" s="280"/>
+      <c r="K23" s="280"/>
+      <c r="L23" s="280"/>
+      <c r="M23" s="281"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="335"/>
-      <c r="B24" s="335"/>
-      <c r="C24" s="335"/>
-      <c r="D24" s="336"/>
-      <c r="E24" s="103"/>
-      <c r="F24" s="337"/>
-      <c r="G24" s="337"/>
-      <c r="H24" s="104" t="s">
+      <c r="A24" s="277"/>
+      <c r="B24" s="277"/>
+      <c r="C24" s="277"/>
+      <c r="D24" s="278"/>
+      <c r="E24" s="79"/>
+      <c r="F24" s="279"/>
+      <c r="G24" s="279"/>
+      <c r="H24" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I24" s="104" t="s">
+      <c r="I24" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="338"/>
-      <c r="K24" s="338"/>
-      <c r="L24" s="338"/>
-      <c r="M24" s="339"/>
+      <c r="J24" s="280"/>
+      <c r="K24" s="280"/>
+      <c r="L24" s="280"/>
+      <c r="M24" s="281"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="335"/>
-      <c r="B25" s="335"/>
-      <c r="C25" s="335"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="337"/>
-      <c r="G25" s="337"/>
-      <c r="H25" s="104" t="s">
+      <c r="A25" s="277"/>
+      <c r="B25" s="277"/>
+      <c r="C25" s="277"/>
+      <c r="D25" s="278"/>
+      <c r="E25" s="79"/>
+      <c r="F25" s="279"/>
+      <c r="G25" s="279"/>
+      <c r="H25" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I25" s="104" t="s">
+      <c r="I25" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="338"/>
-      <c r="K25" s="338"/>
-      <c r="L25" s="338"/>
-      <c r="M25" s="339"/>
+      <c r="J25" s="280"/>
+      <c r="K25" s="280"/>
+      <c r="L25" s="280"/>
+      <c r="M25" s="281"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="335"/>
-      <c r="B26" s="335"/>
-      <c r="C26" s="335"/>
-      <c r="D26" s="336"/>
-      <c r="E26" s="103"/>
-      <c r="F26" s="337"/>
-      <c r="G26" s="337"/>
-      <c r="H26" s="104" t="s">
+      <c r="A26" s="277"/>
+      <c r="B26" s="277"/>
+      <c r="C26" s="277"/>
+      <c r="D26" s="278"/>
+      <c r="E26" s="79"/>
+      <c r="F26" s="279"/>
+      <c r="G26" s="279"/>
+      <c r="H26" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I26" s="104" t="s">
+      <c r="I26" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="338"/>
-      <c r="K26" s="338"/>
-      <c r="L26" s="338"/>
-      <c r="M26" s="339"/>
+      <c r="J26" s="280"/>
+      <c r="K26" s="280"/>
+      <c r="L26" s="280"/>
+      <c r="M26" s="281"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="335"/>
-      <c r="B27" s="335"/>
-      <c r="C27" s="335"/>
-      <c r="D27" s="336"/>
-      <c r="E27" s="103"/>
-      <c r="F27" s="337"/>
-      <c r="G27" s="337"/>
-      <c r="H27" s="104" t="s">
+      <c r="A27" s="277"/>
+      <c r="B27" s="277"/>
+      <c r="C27" s="277"/>
+      <c r="D27" s="278"/>
+      <c r="E27" s="79"/>
+      <c r="F27" s="279"/>
+      <c r="G27" s="279"/>
+      <c r="H27" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I27" s="104" t="s">
+      <c r="I27" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J27" s="338"/>
-      <c r="K27" s="338"/>
-      <c r="L27" s="338"/>
-      <c r="M27" s="339"/>
+      <c r="J27" s="280"/>
+      <c r="K27" s="280"/>
+      <c r="L27" s="280"/>
+      <c r="M27" s="281"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="335"/>
-      <c r="B28" s="335"/>
-      <c r="C28" s="335"/>
-      <c r="D28" s="336"/>
-      <c r="E28" s="103"/>
-      <c r="F28" s="337"/>
-      <c r="G28" s="337"/>
-      <c r="H28" s="104" t="s">
+      <c r="A28" s="277"/>
+      <c r="B28" s="277"/>
+      <c r="C28" s="277"/>
+      <c r="D28" s="278"/>
+      <c r="E28" s="79"/>
+      <c r="F28" s="279"/>
+      <c r="G28" s="279"/>
+      <c r="H28" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="104" t="s">
+      <c r="I28" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J28" s="338"/>
-      <c r="K28" s="338"/>
-      <c r="L28" s="338"/>
-      <c r="M28" s="339"/>
+      <c r="J28" s="280"/>
+      <c r="K28" s="280"/>
+      <c r="L28" s="280"/>
+      <c r="M28" s="281"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="335"/>
-      <c r="B29" s="335"/>
-      <c r="C29" s="335"/>
-      <c r="D29" s="336"/>
-      <c r="E29" s="103"/>
-      <c r="F29" s="337"/>
-      <c r="G29" s="337"/>
-      <c r="H29" s="104" t="s">
+      <c r="A29" s="277"/>
+      <c r="B29" s="277"/>
+      <c r="C29" s="277"/>
+      <c r="D29" s="278"/>
+      <c r="E29" s="79"/>
+      <c r="F29" s="279"/>
+      <c r="G29" s="279"/>
+      <c r="H29" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I29" s="104" t="s">
+      <c r="I29" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J29" s="338"/>
-      <c r="K29" s="338"/>
-      <c r="L29" s="338"/>
-      <c r="M29" s="339"/>
+      <c r="J29" s="280"/>
+      <c r="K29" s="280"/>
+      <c r="L29" s="280"/>
+      <c r="M29" s="281"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="345" t="s">
+      <c r="A30" s="287" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="346"/>
-      <c r="C30" s="346"/>
-      <c r="D30" s="346"/>
+      <c r="B30" s="288"/>
+      <c r="C30" s="288"/>
+      <c r="D30" s="288"/>
       <c r="E30" s="14"/>
-      <c r="F30" s="347"/>
-      <c r="G30" s="338"/>
+      <c r="F30" s="289"/>
+      <c r="G30" s="280"/>
       <c r="H30" s="15"/>
       <c r="I30" s="15"/>
-      <c r="J30" s="348"/>
-      <c r="K30" s="348"/>
-      <c r="L30" s="348"/>
-      <c r="M30" s="349"/>
+      <c r="J30" s="290"/>
+      <c r="K30" s="290"/>
+      <c r="L30" s="290"/>
+      <c r="M30" s="291"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="305" t="s">
+      <c r="A31" s="247" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="306"/>
-      <c r="C31" s="306"/>
-      <c r="D31" s="306"/>
-      <c r="E31" s="306"/>
-      <c r="F31" s="306"/>
-      <c r="G31" s="306"/>
-      <c r="H31" s="306"/>
-      <c r="I31" s="306"/>
-      <c r="J31" s="306"/>
-      <c r="K31" s="306"/>
-      <c r="L31" s="306"/>
-      <c r="M31" s="307"/>
+      <c r="B31" s="248"/>
+      <c r="C31" s="248"/>
+      <c r="D31" s="248"/>
+      <c r="E31" s="248"/>
+      <c r="F31" s="248"/>
+      <c r="G31" s="248"/>
+      <c r="H31" s="248"/>
+      <c r="I31" s="248"/>
+      <c r="J31" s="248"/>
+      <c r="K31" s="248"/>
+      <c r="L31" s="248"/>
+      <c r="M31" s="249"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="350" t="s">
+      <c r="A32" s="292" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="351"/>
-      <c r="C32" s="351" t="s">
+      <c r="B32" s="293"/>
+      <c r="C32" s="293" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="351"/>
-      <c r="E32" s="352" t="s">
+      <c r="D32" s="293"/>
+      <c r="E32" s="294" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="353" t="s">
+      <c r="F32" s="295" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="354" t="s">
+      <c r="G32" s="296" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="354"/>
-      <c r="I32" s="354"/>
-      <c r="J32" s="354"/>
-      <c r="K32" s="354"/>
-      <c r="L32" s="351" t="s">
+      <c r="H32" s="296"/>
+      <c r="I32" s="296"/>
+      <c r="J32" s="296"/>
+      <c r="K32" s="296"/>
+      <c r="L32" s="293" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="355"/>
+      <c r="M32" s="297"/>
     </row>
     <row r="33" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="16" t="s">
@@ -5104,15 +5048,15 @@
       <c r="D33" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="352"/>
-      <c r="F33" s="353"/>
-      <c r="G33" s="340" t="s">
+      <c r="E33" s="294"/>
+      <c r="F33" s="295"/>
+      <c r="G33" s="282" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="340"/>
-      <c r="I33" s="340"/>
-      <c r="J33" s="340"/>
-      <c r="K33" s="340"/>
+      <c r="H33" s="282"/>
+      <c r="I33" s="282"/>
+      <c r="J33" s="282"/>
+      <c r="K33" s="282"/>
       <c r="L33" s="18" t="s">
         <v>14</v>
       </c>
@@ -5121,449 +5065,449 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="107"/>
-      <c r="B34" s="104"/>
-      <c r="C34" s="105"/>
-      <c r="D34" s="104"/>
-      <c r="E34" s="105"/>
-      <c r="F34" s="104"/>
-      <c r="G34" s="341"/>
-      <c r="H34" s="342"/>
-      <c r="I34" s="342"/>
-      <c r="J34" s="342"/>
-      <c r="K34" s="343"/>
+      <c r="A34" s="83"/>
+      <c r="B34" s="80"/>
+      <c r="C34" s="81"/>
+      <c r="D34" s="80"/>
+      <c r="E34" s="81"/>
+      <c r="F34" s="80"/>
+      <c r="G34" s="283"/>
+      <c r="H34" s="284"/>
+      <c r="I34" s="284"/>
+      <c r="J34" s="284"/>
+      <c r="K34" s="285"/>
       <c r="L34" s="20"/>
       <c r="M34" s="21"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" s="107"/>
-      <c r="B35" s="104"/>
-      <c r="C35" s="104"/>
-      <c r="D35" s="104"/>
-      <c r="E35" s="104"/>
+      <c r="A35" s="83"/>
+      <c r="B35" s="80"/>
+      <c r="C35" s="80"/>
+      <c r="D35" s="80"/>
+      <c r="E35" s="80"/>
       <c r="F35" s="20"/>
-      <c r="G35" s="341"/>
-      <c r="H35" s="342"/>
-      <c r="I35" s="342"/>
-      <c r="J35" s="342"/>
-      <c r="K35" s="343"/>
+      <c r="G35" s="283"/>
+      <c r="H35" s="284"/>
+      <c r="I35" s="284"/>
+      <c r="J35" s="284"/>
+      <c r="K35" s="285"/>
       <c r="L35" s="20"/>
       <c r="M35" s="21"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" s="107"/>
-      <c r="B36" s="104"/>
-      <c r="C36" s="104"/>
-      <c r="D36" s="104"/>
-      <c r="E36" s="104"/>
+      <c r="A36" s="83"/>
+      <c r="B36" s="80"/>
+      <c r="C36" s="80"/>
+      <c r="D36" s="80"/>
+      <c r="E36" s="80"/>
       <c r="F36" s="20"/>
-      <c r="G36" s="341"/>
-      <c r="H36" s="342"/>
-      <c r="I36" s="342"/>
-      <c r="J36" s="342"/>
-      <c r="K36" s="343"/>
+      <c r="G36" s="283"/>
+      <c r="H36" s="284"/>
+      <c r="I36" s="284"/>
+      <c r="J36" s="284"/>
+      <c r="K36" s="285"/>
       <c r="L36" s="20"/>
       <c r="M36" s="21"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A37" s="107"/>
-      <c r="B37" s="104"/>
-      <c r="C37" s="104"/>
-      <c r="D37" s="104"/>
-      <c r="E37" s="104"/>
+      <c r="A37" s="83"/>
+      <c r="B37" s="80"/>
+      <c r="C37" s="80"/>
+      <c r="D37" s="80"/>
+      <c r="E37" s="80"/>
       <c r="F37" s="20"/>
-      <c r="G37" s="341"/>
-      <c r="H37" s="342"/>
-      <c r="I37" s="342"/>
-      <c r="J37" s="342"/>
-      <c r="K37" s="343"/>
+      <c r="G37" s="283"/>
+      <c r="H37" s="284"/>
+      <c r="I37" s="284"/>
+      <c r="J37" s="284"/>
+      <c r="K37" s="285"/>
       <c r="L37" s="20"/>
       <c r="M37" s="21"/>
-      <c r="Q37" s="344"/>
-      <c r="R37" s="344"/>
+      <c r="Q37" s="286"/>
+      <c r="R37" s="286"/>
       <c r="S37" s="22"/>
-      <c r="T37" s="368"/>
-      <c r="U37" s="368"/>
-      <c r="V37" s="368"/>
+      <c r="T37" s="310"/>
+      <c r="U37" s="310"/>
+      <c r="V37" s="310"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A38" s="107"/>
-      <c r="B38" s="104"/>
-      <c r="C38" s="104"/>
-      <c r="D38" s="104"/>
-      <c r="E38" s="104"/>
+      <c r="A38" s="83"/>
+      <c r="B38" s="80"/>
+      <c r="C38" s="80"/>
+      <c r="D38" s="80"/>
+      <c r="E38" s="80"/>
       <c r="F38" s="20"/>
-      <c r="G38" s="341"/>
-      <c r="H38" s="342"/>
-      <c r="I38" s="342"/>
-      <c r="J38" s="342"/>
-      <c r="K38" s="343"/>
+      <c r="G38" s="283"/>
+      <c r="H38" s="284"/>
+      <c r="I38" s="284"/>
+      <c r="J38" s="284"/>
+      <c r="K38" s="285"/>
       <c r="L38" s="20"/>
       <c r="M38" s="24"/>
-      <c r="Q38" s="344"/>
-      <c r="R38" s="344"/>
+      <c r="Q38" s="286"/>
+      <c r="R38" s="286"/>
       <c r="S38" s="22"/>
-      <c r="T38" s="368"/>
-      <c r="U38" s="368"/>
-      <c r="V38" s="368"/>
+      <c r="T38" s="310"/>
+      <c r="U38" s="310"/>
+      <c r="V38" s="310"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A39" s="107"/>
-      <c r="B39" s="104"/>
-      <c r="C39" s="104"/>
-      <c r="D39" s="104"/>
-      <c r="E39" s="104"/>
+      <c r="A39" s="83"/>
+      <c r="B39" s="80"/>
+      <c r="C39" s="80"/>
+      <c r="D39" s="80"/>
+      <c r="E39" s="80"/>
       <c r="F39" s="20"/>
-      <c r="G39" s="341"/>
-      <c r="H39" s="342"/>
-      <c r="I39" s="342"/>
-      <c r="J39" s="342"/>
-      <c r="K39" s="343"/>
+      <c r="G39" s="283"/>
+      <c r="H39" s="284"/>
+      <c r="I39" s="284"/>
+      <c r="J39" s="284"/>
+      <c r="K39" s="285"/>
       <c r="L39" s="20"/>
       <c r="M39" s="24"/>
       <c r="Q39" s="25"/>
       <c r="R39" s="25"/>
-      <c r="S39" s="369"/>
-      <c r="T39" s="368"/>
-      <c r="U39" s="368"/>
-      <c r="V39" s="368"/>
+      <c r="S39" s="311"/>
+      <c r="T39" s="310"/>
+      <c r="U39" s="310"/>
+      <c r="V39" s="310"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A40" s="107"/>
-      <c r="B40" s="104"/>
-      <c r="C40" s="104"/>
-      <c r="D40" s="104"/>
-      <c r="E40" s="104"/>
+      <c r="A40" s="83"/>
+      <c r="B40" s="80"/>
+      <c r="C40" s="80"/>
+      <c r="D40" s="80"/>
+      <c r="E40" s="80"/>
       <c r="F40" s="20"/>
-      <c r="G40" s="341"/>
-      <c r="H40" s="342"/>
-      <c r="I40" s="342"/>
-      <c r="J40" s="342"/>
-      <c r="K40" s="343"/>
+      <c r="G40" s="283"/>
+      <c r="H40" s="284"/>
+      <c r="I40" s="284"/>
+      <c r="J40" s="284"/>
+      <c r="K40" s="285"/>
       <c r="L40" s="20"/>
       <c r="M40" s="21"/>
       <c r="Q40" s="25"/>
       <c r="R40" s="25"/>
-      <c r="S40" s="369"/>
-      <c r="T40" s="368"/>
-      <c r="U40" s="368"/>
-      <c r="V40" s="368"/>
+      <c r="S40" s="311"/>
+      <c r="T40" s="310"/>
+      <c r="U40" s="310"/>
+      <c r="V40" s="310"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A41" s="107"/>
-      <c r="B41" s="104"/>
-      <c r="C41" s="104"/>
-      <c r="D41" s="104"/>
-      <c r="E41" s="104"/>
+      <c r="A41" s="83"/>
+      <c r="B41" s="80"/>
+      <c r="C41" s="80"/>
+      <c r="D41" s="80"/>
+      <c r="E41" s="80"/>
       <c r="F41" s="20"/>
-      <c r="G41" s="341"/>
-      <c r="H41" s="342"/>
-      <c r="I41" s="342"/>
-      <c r="J41" s="342"/>
-      <c r="K41" s="343"/>
+      <c r="G41" s="283"/>
+      <c r="H41" s="284"/>
+      <c r="I41" s="284"/>
+      <c r="J41" s="284"/>
+      <c r="K41" s="285"/>
       <c r="L41" s="20"/>
       <c r="M41" s="21"/>
     </row>
     <row r="42" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="108"/>
-      <c r="B42" s="109"/>
-      <c r="C42" s="110"/>
-      <c r="D42" s="109"/>
-      <c r="E42" s="110"/>
+      <c r="A42" s="84"/>
+      <c r="B42" s="85"/>
+      <c r="C42" s="86"/>
+      <c r="D42" s="85"/>
+      <c r="E42" s="86"/>
       <c r="F42" s="26"/>
-      <c r="G42" s="408" t="s">
+      <c r="G42" s="350" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="409"/>
-      <c r="I42" s="409"/>
-      <c r="J42" s="409"/>
-      <c r="K42" s="410"/>
+      <c r="H42" s="351"/>
+      <c r="I42" s="351"/>
+      <c r="J42" s="351"/>
+      <c r="K42" s="352"/>
       <c r="L42" s="26"/>
       <c r="M42" s="27"/>
     </row>
     <row r="43" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="388" t="s">
+      <c r="A43" s="330" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="389"/>
-      <c r="C43" s="389"/>
-      <c r="D43" s="389"/>
-      <c r="E43" s="389"/>
-      <c r="F43" s="389"/>
-      <c r="G43" s="389"/>
-      <c r="H43" s="390"/>
-      <c r="I43" s="411" t="s">
+      <c r="B43" s="331"/>
+      <c r="C43" s="331"/>
+      <c r="D43" s="331"/>
+      <c r="E43" s="331"/>
+      <c r="F43" s="331"/>
+      <c r="G43" s="331"/>
+      <c r="H43" s="332"/>
+      <c r="I43" s="353" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="412"/>
-      <c r="K43" s="412"/>
-      <c r="L43" s="412"/>
-      <c r="M43" s="413"/>
+      <c r="J43" s="354"/>
+      <c r="K43" s="354"/>
+      <c r="L43" s="354"/>
+      <c r="M43" s="355"/>
     </row>
     <row r="44" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="391"/>
-      <c r="B44" s="392"/>
-      <c r="C44" s="392"/>
-      <c r="D44" s="392"/>
-      <c r="E44" s="392"/>
-      <c r="F44" s="392"/>
-      <c r="G44" s="392"/>
-      <c r="H44" s="393"/>
-      <c r="I44" s="414"/>
-      <c r="J44" s="415"/>
-      <c r="K44" s="415"/>
-      <c r="L44" s="415"/>
-      <c r="M44" s="416"/>
+      <c r="A44" s="333"/>
+      <c r="B44" s="334"/>
+      <c r="C44" s="334"/>
+      <c r="D44" s="334"/>
+      <c r="E44" s="334"/>
+      <c r="F44" s="334"/>
+      <c r="G44" s="334"/>
+      <c r="H44" s="335"/>
+      <c r="I44" s="356"/>
+      <c r="J44" s="357"/>
+      <c r="K44" s="357"/>
+      <c r="L44" s="357"/>
+      <c r="M44" s="358"/>
     </row>
     <row r="45" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="356" t="s">
+      <c r="A45" s="298" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="357"/>
-      <c r="C45" s="357"/>
-      <c r="D45" s="357"/>
-      <c r="E45" s="357"/>
-      <c r="F45" s="357"/>
-      <c r="G45" s="357"/>
-      <c r="H45" s="358"/>
-      <c r="I45" s="359" t="s">
+      <c r="B45" s="299"/>
+      <c r="C45" s="299"/>
+      <c r="D45" s="299"/>
+      <c r="E45" s="299"/>
+      <c r="F45" s="299"/>
+      <c r="G45" s="299"/>
+      <c r="H45" s="300"/>
+      <c r="I45" s="301" t="s">
         <v>36</v>
       </c>
-      <c r="J45" s="360"/>
-      <c r="K45" s="360"/>
-      <c r="L45" s="360"/>
-      <c r="M45" s="361"/>
+      <c r="J45" s="302"/>
+      <c r="K45" s="302"/>
+      <c r="L45" s="302"/>
+      <c r="M45" s="303"/>
     </row>
     <row r="46" spans="1:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="356" t="s">
+      <c r="A46" s="298" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="357"/>
-      <c r="C46" s="357"/>
-      <c r="D46" s="357"/>
-      <c r="E46" s="357"/>
-      <c r="F46" s="357"/>
-      <c r="G46" s="357"/>
-      <c r="H46" s="358"/>
-      <c r="I46" s="359"/>
-      <c r="J46" s="360"/>
-      <c r="K46" s="360"/>
-      <c r="L46" s="360"/>
-      <c r="M46" s="361"/>
+      <c r="B46" s="299"/>
+      <c r="C46" s="299"/>
+      <c r="D46" s="299"/>
+      <c r="E46" s="299"/>
+      <c r="F46" s="299"/>
+      <c r="G46" s="299"/>
+      <c r="H46" s="300"/>
+      <c r="I46" s="301"/>
+      <c r="J46" s="302"/>
+      <c r="K46" s="302"/>
+      <c r="L46" s="302"/>
+      <c r="M46" s="303"/>
     </row>
     <row r="47" spans="1:22" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="362"/>
-      <c r="B47" s="363"/>
-      <c r="C47" s="363"/>
-      <c r="D47" s="363"/>
-      <c r="E47" s="363"/>
-      <c r="F47" s="363"/>
-      <c r="G47" s="363"/>
-      <c r="H47" s="364"/>
-      <c r="I47" s="365" t="s">
+      <c r="A47" s="304"/>
+      <c r="B47" s="305"/>
+      <c r="C47" s="305"/>
+      <c r="D47" s="305"/>
+      <c r="E47" s="305"/>
+      <c r="F47" s="305"/>
+      <c r="G47" s="305"/>
+      <c r="H47" s="306"/>
+      <c r="I47" s="307" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="366"/>
-      <c r="K47" s="366"/>
-      <c r="L47" s="366"/>
-      <c r="M47" s="367"/>
+      <c r="J47" s="308"/>
+      <c r="K47" s="308"/>
+      <c r="L47" s="308"/>
+      <c r="M47" s="309"/>
     </row>
     <row r="48" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="385" t="s">
+      <c r="A48" s="327" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="386"/>
-      <c r="C48" s="386"/>
-      <c r="D48" s="386"/>
-      <c r="E48" s="386"/>
-      <c r="F48" s="386"/>
-      <c r="G48" s="386"/>
-      <c r="H48" s="386"/>
-      <c r="I48" s="386"/>
-      <c r="J48" s="386"/>
-      <c r="K48" s="386"/>
-      <c r="L48" s="386"/>
-      <c r="M48" s="387"/>
+      <c r="B48" s="328"/>
+      <c r="C48" s="328"/>
+      <c r="D48" s="328"/>
+      <c r="E48" s="328"/>
+      <c r="F48" s="328"/>
+      <c r="G48" s="328"/>
+      <c r="H48" s="328"/>
+      <c r="I48" s="328"/>
+      <c r="J48" s="328"/>
+      <c r="K48" s="328"/>
+      <c r="L48" s="328"/>
+      <c r="M48" s="329"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="388" t="s">
+      <c r="A49" s="330" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="389"/>
-      <c r="C49" s="389"/>
-      <c r="D49" s="389"/>
-      <c r="E49" s="389"/>
-      <c r="F49" s="389"/>
-      <c r="G49" s="389"/>
-      <c r="H49" s="390"/>
-      <c r="I49" s="396" t="s">
+      <c r="B49" s="331"/>
+      <c r="C49" s="331"/>
+      <c r="D49" s="331"/>
+      <c r="E49" s="331"/>
+      <c r="F49" s="331"/>
+      <c r="G49" s="331"/>
+      <c r="H49" s="332"/>
+      <c r="I49" s="338" t="s">
         <v>40</v>
       </c>
-      <c r="J49" s="397"/>
-      <c r="K49" s="397"/>
-      <c r="L49" s="397"/>
-      <c r="M49" s="398"/>
+      <c r="J49" s="339"/>
+      <c r="K49" s="339"/>
+      <c r="L49" s="339"/>
+      <c r="M49" s="340"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="391"/>
-      <c r="B50" s="392"/>
-      <c r="C50" s="392"/>
-      <c r="D50" s="392"/>
-      <c r="E50" s="392"/>
-      <c r="F50" s="392"/>
-      <c r="G50" s="392"/>
-      <c r="H50" s="393"/>
-      <c r="I50" s="399"/>
-      <c r="J50" s="400"/>
-      <c r="K50" s="400"/>
-      <c r="L50" s="400"/>
-      <c r="M50" s="401"/>
+      <c r="A50" s="333"/>
+      <c r="B50" s="334"/>
+      <c r="C50" s="334"/>
+      <c r="D50" s="334"/>
+      <c r="E50" s="334"/>
+      <c r="F50" s="334"/>
+      <c r="G50" s="334"/>
+      <c r="H50" s="335"/>
+      <c r="I50" s="341"/>
+      <c r="J50" s="342"/>
+      <c r="K50" s="342"/>
+      <c r="L50" s="342"/>
+      <c r="M50" s="343"/>
     </row>
     <row r="51" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="394"/>
-      <c r="B51" s="395"/>
-      <c r="C51" s="395"/>
-      <c r="D51" s="395"/>
-      <c r="E51" s="392"/>
-      <c r="F51" s="392"/>
-      <c r="G51" s="392"/>
-      <c r="H51" s="393"/>
-      <c r="I51" s="402" t="s">
+      <c r="A51" s="336"/>
+      <c r="B51" s="337"/>
+      <c r="C51" s="337"/>
+      <c r="D51" s="337"/>
+      <c r="E51" s="334"/>
+      <c r="F51" s="334"/>
+      <c r="G51" s="334"/>
+      <c r="H51" s="335"/>
+      <c r="I51" s="344" t="s">
         <v>41</v>
       </c>
-      <c r="J51" s="403"/>
-      <c r="K51" s="404"/>
-      <c r="L51" s="404"/>
-      <c r="M51" s="405"/>
+      <c r="J51" s="345"/>
+      <c r="K51" s="346"/>
+      <c r="L51" s="346"/>
+      <c r="M51" s="347"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="385" t="s">
+      <c r="A52" s="327" t="s">
         <v>42</v>
       </c>
-      <c r="B52" s="386"/>
-      <c r="C52" s="386"/>
-      <c r="D52" s="386"/>
-      <c r="E52" s="111" t="s">
+      <c r="B52" s="328"/>
+      <c r="C52" s="328"/>
+      <c r="D52" s="328"/>
+      <c r="E52" s="87" t="s">
         <v>44</v>
       </c>
-      <c r="F52" s="112"/>
-      <c r="G52" s="406" t="s">
+      <c r="F52" s="88"/>
+      <c r="G52" s="348" t="s">
         <v>45</v>
       </c>
-      <c r="H52" s="406"/>
-      <c r="I52" s="406"/>
-      <c r="J52" s="407"/>
-      <c r="K52" s="386" t="s">
+      <c r="H52" s="348"/>
+      <c r="I52" s="348"/>
+      <c r="J52" s="349"/>
+      <c r="K52" s="328" t="s">
         <v>50</v>
       </c>
-      <c r="L52" s="386"/>
-      <c r="M52" s="387"/>
+      <c r="L52" s="328"/>
+      <c r="M52" s="329"/>
     </row>
     <row r="53" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="375" t="s">
+      <c r="A53" s="317" t="s">
         <v>43</v>
       </c>
-      <c r="B53" s="376"/>
-      <c r="C53" s="376"/>
-      <c r="D53" s="376"/>
-      <c r="E53" s="113"/>
-      <c r="F53" s="106"/>
-      <c r="G53" s="106"/>
-      <c r="H53" s="106"/>
-      <c r="I53" s="106"/>
-      <c r="J53" s="114"/>
-      <c r="K53" s="376" t="s">
+      <c r="B53" s="318"/>
+      <c r="C53" s="318"/>
+      <c r="D53" s="318"/>
+      <c r="E53" s="89"/>
+      <c r="F53" s="82"/>
+      <c r="G53" s="82"/>
+      <c r="H53" s="82"/>
+      <c r="I53" s="82"/>
+      <c r="J53" s="90"/>
+      <c r="K53" s="318" t="s">
         <v>52</v>
       </c>
-      <c r="L53" s="376"/>
-      <c r="M53" s="377"/>
+      <c r="L53" s="318"/>
+      <c r="M53" s="319"/>
     </row>
     <row r="54" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="375"/>
-      <c r="B54" s="376"/>
-      <c r="C54" s="376"/>
-      <c r="D54" s="376"/>
-      <c r="E54" s="378" t="s">
+      <c r="A54" s="317"/>
+      <c r="B54" s="318"/>
+      <c r="C54" s="318"/>
+      <c r="D54" s="318"/>
+      <c r="E54" s="320" t="s">
         <v>46</v>
       </c>
-      <c r="F54" s="379"/>
-      <c r="G54" s="115"/>
-      <c r="H54" s="370" t="s">
+      <c r="F54" s="321"/>
+      <c r="G54" s="91"/>
+      <c r="H54" s="312" t="s">
         <v>46</v>
       </c>
-      <c r="I54" s="370"/>
-      <c r="J54" s="371"/>
-      <c r="K54" s="376"/>
-      <c r="L54" s="376"/>
-      <c r="M54" s="377"/>
+      <c r="I54" s="312"/>
+      <c r="J54" s="313"/>
+      <c r="K54" s="318"/>
+      <c r="L54" s="318"/>
+      <c r="M54" s="319"/>
     </row>
     <row r="55" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="375"/>
-      <c r="B55" s="376"/>
-      <c r="C55" s="376"/>
-      <c r="D55" s="376"/>
-      <c r="E55" s="378" t="s">
+      <c r="A55" s="317"/>
+      <c r="B55" s="318"/>
+      <c r="C55" s="318"/>
+      <c r="D55" s="318"/>
+      <c r="E55" s="320" t="s">
         <v>47</v>
       </c>
-      <c r="F55" s="379"/>
-      <c r="G55" s="379"/>
-      <c r="H55" s="370" t="s">
+      <c r="F55" s="321"/>
+      <c r="G55" s="321"/>
+      <c r="H55" s="312" t="s">
         <v>48</v>
       </c>
-      <c r="I55" s="370"/>
-      <c r="J55" s="371"/>
-      <c r="K55" s="376"/>
-      <c r="L55" s="376"/>
-      <c r="M55" s="377"/>
+      <c r="I55" s="312"/>
+      <c r="J55" s="313"/>
+      <c r="K55" s="318"/>
+      <c r="L55" s="318"/>
+      <c r="M55" s="319"/>
     </row>
     <row r="56" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="328"/>
-      <c r="B56" s="302"/>
-      <c r="C56" s="302"/>
-      <c r="D56" s="303"/>
-      <c r="E56" s="378"/>
-      <c r="F56" s="379"/>
-      <c r="G56" s="379"/>
-      <c r="H56" s="370"/>
-      <c r="I56" s="370"/>
-      <c r="J56" s="371"/>
-      <c r="K56" s="383" t="s">
+      <c r="A56" s="270"/>
+      <c r="B56" s="244"/>
+      <c r="C56" s="244"/>
+      <c r="D56" s="245"/>
+      <c r="E56" s="320"/>
+      <c r="F56" s="321"/>
+      <c r="G56" s="321"/>
+      <c r="H56" s="312"/>
+      <c r="I56" s="312"/>
+      <c r="J56" s="313"/>
+      <c r="K56" s="325" t="s">
         <v>51</v>
       </c>
-      <c r="L56" s="383"/>
-      <c r="M56" s="384"/>
+      <c r="L56" s="325"/>
+      <c r="M56" s="326"/>
     </row>
     <row r="57" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="328"/>
-      <c r="B57" s="302"/>
-      <c r="C57" s="302"/>
-      <c r="D57" s="303"/>
-      <c r="E57" s="378"/>
-      <c r="F57" s="379"/>
-      <c r="G57" s="115"/>
-      <c r="H57" s="370" t="s">
+      <c r="A57" s="270"/>
+      <c r="B57" s="244"/>
+      <c r="C57" s="244"/>
+      <c r="D57" s="245"/>
+      <c r="E57" s="320"/>
+      <c r="F57" s="321"/>
+      <c r="G57" s="91"/>
+      <c r="H57" s="312" t="s">
         <v>49</v>
       </c>
-      <c r="I57" s="370"/>
-      <c r="J57" s="371"/>
-      <c r="K57" s="116"/>
-      <c r="L57" s="117"/>
-      <c r="M57" s="118"/>
+      <c r="I57" s="312"/>
+      <c r="J57" s="313"/>
+      <c r="K57" s="92"/>
+      <c r="L57" s="93"/>
+      <c r="M57" s="94"/>
     </row>
     <row r="58" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="380"/>
-      <c r="B58" s="381"/>
-      <c r="C58" s="381"/>
-      <c r="D58" s="382"/>
-      <c r="E58" s="333"/>
-      <c r="F58" s="334"/>
-      <c r="G58" s="334"/>
-      <c r="H58" s="334"/>
-      <c r="I58" s="334"/>
-      <c r="J58" s="372"/>
-      <c r="K58" s="119"/>
-      <c r="L58" s="120"/>
-      <c r="M58" s="121"/>
+      <c r="A58" s="322"/>
+      <c r="B58" s="323"/>
+      <c r="C58" s="323"/>
+      <c r="D58" s="324"/>
+      <c r="E58" s="275"/>
+      <c r="F58" s="276"/>
+      <c r="G58" s="276"/>
+      <c r="H58" s="276"/>
+      <c r="I58" s="276"/>
+      <c r="J58" s="314"/>
+      <c r="K58" s="95"/>
+      <c r="L58" s="96"/>
+      <c r="M58" s="97"/>
     </row>
     <row r="59" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="28"/>
@@ -6409,1013 +6353,1013 @@
     <col min="16142" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="436" t="s">
+    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="383" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="437"/>
-      <c r="C1" s="279" t="s">
+      <c r="B1" s="384"/>
+      <c r="C1" s="381" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="279"/>
-      <c r="E1" s="279"/>
-      <c r="F1" s="279"/>
-      <c r="G1" s="279"/>
-      <c r="H1" s="279"/>
-      <c r="I1" s="279"/>
-      <c r="J1" s="279"/>
-      <c r="K1" s="279"/>
-      <c r="L1" s="280" t="s">
+      <c r="D1" s="381"/>
+      <c r="E1" s="381"/>
+      <c r="F1" s="381"/>
+      <c r="G1" s="381"/>
+      <c r="H1" s="381"/>
+      <c r="I1" s="381"/>
+      <c r="J1" s="381"/>
+      <c r="K1" s="381"/>
+      <c r="L1" s="385" t="s">
         <v>62</v>
       </c>
-      <c r="M1" s="281"/>
+      <c r="M1" s="386"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="305" t="s">
+      <c r="A2" s="247" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="306"/>
-      <c r="C2" s="306"/>
-      <c r="D2" s="306"/>
-      <c r="E2" s="306"/>
-      <c r="F2" s="306"/>
-      <c r="G2" s="306"/>
-      <c r="H2" s="306"/>
-      <c r="I2" s="306"/>
-      <c r="J2" s="306"/>
-      <c r="K2" s="306"/>
-      <c r="L2" s="306"/>
-      <c r="M2" s="307"/>
+      <c r="B2" s="248"/>
+      <c r="C2" s="248"/>
+      <c r="D2" s="248"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="248"/>
+      <c r="G2" s="248"/>
+      <c r="H2" s="248"/>
+      <c r="I2" s="248"/>
+      <c r="J2" s="248"/>
+      <c r="K2" s="248"/>
+      <c r="L2" s="248"/>
+      <c r="M2" s="249"/>
     </row>
     <row r="3" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="308" t="s">
+      <c r="A3" s="250" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="309"/>
-      <c r="C3" s="309"/>
-      <c r="D3" s="309"/>
-      <c r="E3" s="309" t="s">
+      <c r="B3" s="251"/>
+      <c r="C3" s="251"/>
+      <c r="D3" s="251"/>
+      <c r="E3" s="251" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="309" t="s">
+      <c r="F3" s="251" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="309"/>
-      <c r="H3" s="310" t="s">
+      <c r="G3" s="251"/>
+      <c r="H3" s="252" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="311"/>
-      <c r="J3" s="312" t="s">
+      <c r="I3" s="253"/>
+      <c r="J3" s="254" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="313"/>
-      <c r="L3" s="313"/>
-      <c r="M3" s="314"/>
+      <c r="K3" s="255"/>
+      <c r="L3" s="255"/>
+      <c r="M3" s="256"/>
     </row>
     <row r="4" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="308"/>
-      <c r="B4" s="309"/>
-      <c r="C4" s="309"/>
-      <c r="D4" s="309"/>
-      <c r="E4" s="309"/>
-      <c r="F4" s="309"/>
-      <c r="G4" s="309"/>
-      <c r="H4" s="318" t="s">
+      <c r="A4" s="250"/>
+      <c r="B4" s="251"/>
+      <c r="C4" s="251"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="260" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="319"/>
-      <c r="J4" s="315"/>
-      <c r="K4" s="316"/>
-      <c r="L4" s="316"/>
-      <c r="M4" s="317"/>
+      <c r="I4" s="261"/>
+      <c r="J4" s="257"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
+      <c r="M4" s="259"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="417"/>
-      <c r="B5" s="335"/>
-      <c r="C5" s="335"/>
-      <c r="D5" s="335"/>
+      <c r="A5" s="359"/>
+      <c r="B5" s="277"/>
+      <c r="C5" s="277"/>
+      <c r="D5" s="277"/>
       <c r="E5" s="10"/>
-      <c r="F5" s="161"/>
-      <c r="G5" s="163"/>
-      <c r="H5" s="104" t="s">
+      <c r="F5" s="137"/>
+      <c r="G5" s="139"/>
+      <c r="H5" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I5" s="104" t="s">
+      <c r="I5" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J5" s="338"/>
-      <c r="K5" s="338"/>
-      <c r="L5" s="338"/>
-      <c r="M5" s="339"/>
+      <c r="J5" s="280"/>
+      <c r="K5" s="280"/>
+      <c r="L5" s="280"/>
+      <c r="M5" s="281"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="417"/>
-      <c r="B6" s="335"/>
-      <c r="C6" s="335"/>
-      <c r="D6" s="335"/>
+      <c r="A6" s="359"/>
+      <c r="B6" s="277"/>
+      <c r="C6" s="277"/>
+      <c r="D6" s="277"/>
       <c r="E6" s="10"/>
-      <c r="F6" s="161"/>
-      <c r="G6" s="163"/>
-      <c r="H6" s="104" t="s">
+      <c r="F6" s="137"/>
+      <c r="G6" s="139"/>
+      <c r="H6" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I6" s="104" t="s">
+      <c r="I6" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J6" s="338"/>
-      <c r="K6" s="338"/>
-      <c r="L6" s="338"/>
-      <c r="M6" s="339"/>
+      <c r="J6" s="280"/>
+      <c r="K6" s="280"/>
+      <c r="L6" s="280"/>
+      <c r="M6" s="281"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="417"/>
-      <c r="B7" s="335"/>
-      <c r="C7" s="335"/>
-      <c r="D7" s="335"/>
+      <c r="A7" s="359"/>
+      <c r="B7" s="277"/>
+      <c r="C7" s="277"/>
+      <c r="D7" s="277"/>
       <c r="E7" s="10"/>
-      <c r="F7" s="161"/>
-      <c r="G7" s="163"/>
-      <c r="H7" s="104" t="s">
+      <c r="F7" s="137"/>
+      <c r="G7" s="139"/>
+      <c r="H7" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="104" t="s">
+      <c r="I7" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J7" s="338"/>
-      <c r="K7" s="338"/>
-      <c r="L7" s="338"/>
-      <c r="M7" s="339"/>
+      <c r="J7" s="280"/>
+      <c r="K7" s="280"/>
+      <c r="L7" s="280"/>
+      <c r="M7" s="281"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="417"/>
-      <c r="B8" s="335"/>
-      <c r="C8" s="335"/>
-      <c r="D8" s="335"/>
+      <c r="A8" s="359"/>
+      <c r="B8" s="277"/>
+      <c r="C8" s="277"/>
+      <c r="D8" s="277"/>
       <c r="E8" s="10"/>
-      <c r="F8" s="161"/>
-      <c r="G8" s="163"/>
-      <c r="H8" s="104" t="s">
+      <c r="F8" s="137"/>
+      <c r="G8" s="139"/>
+      <c r="H8" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="104" t="s">
+      <c r="I8" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J8" s="338"/>
-      <c r="K8" s="338"/>
-      <c r="L8" s="338"/>
-      <c r="M8" s="339"/>
+      <c r="J8" s="280"/>
+      <c r="K8" s="280"/>
+      <c r="L8" s="280"/>
+      <c r="M8" s="281"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="417"/>
-      <c r="B9" s="335"/>
-      <c r="C9" s="335"/>
-      <c r="D9" s="335"/>
+      <c r="A9" s="359"/>
+      <c r="B9" s="277"/>
+      <c r="C9" s="277"/>
+      <c r="D9" s="277"/>
       <c r="E9" s="10"/>
-      <c r="F9" s="161"/>
-      <c r="G9" s="163"/>
-      <c r="H9" s="104" t="s">
+      <c r="F9" s="137"/>
+      <c r="G9" s="139"/>
+      <c r="H9" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="104" t="s">
+      <c r="I9" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J9" s="338"/>
-      <c r="K9" s="338"/>
-      <c r="L9" s="338"/>
-      <c r="M9" s="339"/>
+      <c r="J9" s="280"/>
+      <c r="K9" s="280"/>
+      <c r="L9" s="280"/>
+      <c r="M9" s="281"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="417"/>
-      <c r="B10" s="335"/>
-      <c r="C10" s="335"/>
-      <c r="D10" s="335"/>
+      <c r="A10" s="359"/>
+      <c r="B10" s="277"/>
+      <c r="C10" s="277"/>
+      <c r="D10" s="277"/>
       <c r="E10" s="10"/>
-      <c r="F10" s="161"/>
-      <c r="G10" s="163"/>
-      <c r="H10" s="104" t="s">
+      <c r="F10" s="137"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="104" t="s">
+      <c r="I10" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="338"/>
-      <c r="K10" s="338"/>
-      <c r="L10" s="338"/>
-      <c r="M10" s="339"/>
+      <c r="J10" s="280"/>
+      <c r="K10" s="280"/>
+      <c r="L10" s="280"/>
+      <c r="M10" s="281"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="417"/>
-      <c r="B11" s="335"/>
-      <c r="C11" s="335"/>
-      <c r="D11" s="335"/>
+      <c r="A11" s="359"/>
+      <c r="B11" s="277"/>
+      <c r="C11" s="277"/>
+      <c r="D11" s="277"/>
       <c r="E11" s="10"/>
-      <c r="F11" s="161"/>
-      <c r="G11" s="163"/>
-      <c r="H11" s="104" t="s">
+      <c r="F11" s="137"/>
+      <c r="G11" s="139"/>
+      <c r="H11" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="104" t="s">
+      <c r="I11" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J11" s="338"/>
-      <c r="K11" s="338"/>
-      <c r="L11" s="338"/>
-      <c r="M11" s="339"/>
+      <c r="J11" s="280"/>
+      <c r="K11" s="280"/>
+      <c r="L11" s="280"/>
+      <c r="M11" s="281"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="417"/>
-      <c r="B12" s="335"/>
-      <c r="C12" s="335"/>
-      <c r="D12" s="335"/>
+      <c r="A12" s="359"/>
+      <c r="B12" s="277"/>
+      <c r="C12" s="277"/>
+      <c r="D12" s="277"/>
       <c r="E12" s="10"/>
-      <c r="F12" s="161"/>
-      <c r="G12" s="163"/>
-      <c r="H12" s="104" t="s">
+      <c r="F12" s="137"/>
+      <c r="G12" s="139"/>
+      <c r="H12" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I12" s="104" t="s">
+      <c r="I12" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J12" s="338"/>
-      <c r="K12" s="338"/>
-      <c r="L12" s="338"/>
-      <c r="M12" s="339"/>
+      <c r="J12" s="280"/>
+      <c r="K12" s="280"/>
+      <c r="L12" s="280"/>
+      <c r="M12" s="281"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="417"/>
-      <c r="B13" s="335"/>
-      <c r="C13" s="335"/>
-      <c r="D13" s="335"/>
+      <c r="A13" s="359"/>
+      <c r="B13" s="277"/>
+      <c r="C13" s="277"/>
+      <c r="D13" s="277"/>
       <c r="E13" s="10"/>
-      <c r="F13" s="161"/>
-      <c r="G13" s="163"/>
-      <c r="H13" s="104" t="s">
+      <c r="F13" s="137"/>
+      <c r="G13" s="139"/>
+      <c r="H13" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I13" s="104" t="s">
+      <c r="I13" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J13" s="338"/>
-      <c r="K13" s="338"/>
-      <c r="L13" s="338"/>
-      <c r="M13" s="339"/>
+      <c r="J13" s="280"/>
+      <c r="K13" s="280"/>
+      <c r="L13" s="280"/>
+      <c r="M13" s="281"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="417"/>
-      <c r="B14" s="335"/>
-      <c r="C14" s="335"/>
-      <c r="D14" s="335"/>
+      <c r="A14" s="359"/>
+      <c r="B14" s="277"/>
+      <c r="C14" s="277"/>
+      <c r="D14" s="277"/>
       <c r="E14" s="10"/>
-      <c r="F14" s="161"/>
-      <c r="G14" s="163"/>
-      <c r="H14" s="104" t="s">
+      <c r="F14" s="137"/>
+      <c r="G14" s="139"/>
+      <c r="H14" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I14" s="104" t="s">
+      <c r="I14" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J14" s="338"/>
-      <c r="K14" s="338"/>
-      <c r="L14" s="338"/>
-      <c r="M14" s="339"/>
+      <c r="J14" s="280"/>
+      <c r="K14" s="280"/>
+      <c r="L14" s="280"/>
+      <c r="M14" s="281"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="417"/>
-      <c r="B15" s="335"/>
-      <c r="C15" s="335"/>
-      <c r="D15" s="335"/>
+      <c r="A15" s="359"/>
+      <c r="B15" s="277"/>
+      <c r="C15" s="277"/>
+      <c r="D15" s="277"/>
       <c r="E15" s="10"/>
-      <c r="F15" s="161"/>
-      <c r="G15" s="163"/>
-      <c r="H15" s="104" t="s">
+      <c r="F15" s="137"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I15" s="104" t="s">
+      <c r="I15" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J15" s="338"/>
-      <c r="K15" s="338"/>
-      <c r="L15" s="338"/>
-      <c r="M15" s="339"/>
+      <c r="J15" s="280"/>
+      <c r="K15" s="280"/>
+      <c r="L15" s="280"/>
+      <c r="M15" s="281"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="417"/>
-      <c r="B16" s="335"/>
-      <c r="C16" s="335"/>
-      <c r="D16" s="335"/>
+      <c r="A16" s="359"/>
+      <c r="B16" s="277"/>
+      <c r="C16" s="277"/>
+      <c r="D16" s="277"/>
       <c r="E16" s="10"/>
-      <c r="F16" s="161"/>
-      <c r="G16" s="163"/>
-      <c r="H16" s="104" t="s">
+      <c r="F16" s="137"/>
+      <c r="G16" s="139"/>
+      <c r="H16" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I16" s="104" t="s">
+      <c r="I16" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J16" s="338"/>
-      <c r="K16" s="338"/>
-      <c r="L16" s="338"/>
-      <c r="M16" s="339"/>
+      <c r="J16" s="280"/>
+      <c r="K16" s="280"/>
+      <c r="L16" s="280"/>
+      <c r="M16" s="281"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="417"/>
-      <c r="B17" s="335"/>
-      <c r="C17" s="335"/>
-      <c r="D17" s="335"/>
+      <c r="A17" s="359"/>
+      <c r="B17" s="277"/>
+      <c r="C17" s="277"/>
+      <c r="D17" s="277"/>
       <c r="E17" s="10"/>
-      <c r="F17" s="161"/>
-      <c r="G17" s="163"/>
-      <c r="H17" s="104" t="s">
+      <c r="F17" s="137"/>
+      <c r="G17" s="139"/>
+      <c r="H17" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I17" s="104" t="s">
+      <c r="I17" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J17" s="338"/>
-      <c r="K17" s="338"/>
-      <c r="L17" s="338"/>
-      <c r="M17" s="339"/>
+      <c r="J17" s="280"/>
+      <c r="K17" s="280"/>
+      <c r="L17" s="280"/>
+      <c r="M17" s="281"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="417"/>
-      <c r="B18" s="335"/>
-      <c r="C18" s="335"/>
-      <c r="D18" s="335"/>
+      <c r="A18" s="359"/>
+      <c r="B18" s="277"/>
+      <c r="C18" s="277"/>
+      <c r="D18" s="277"/>
       <c r="E18" s="10"/>
-      <c r="F18" s="161"/>
-      <c r="G18" s="163"/>
-      <c r="H18" s="104" t="s">
+      <c r="F18" s="137"/>
+      <c r="G18" s="139"/>
+      <c r="H18" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I18" s="104" t="s">
+      <c r="I18" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J18" s="338"/>
-      <c r="K18" s="338"/>
-      <c r="L18" s="338"/>
-      <c r="M18" s="339"/>
+      <c r="J18" s="280"/>
+      <c r="K18" s="280"/>
+      <c r="L18" s="280"/>
+      <c r="M18" s="281"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="417"/>
-      <c r="B19" s="335"/>
-      <c r="C19" s="335"/>
-      <c r="D19" s="335"/>
+      <c r="A19" s="359"/>
+      <c r="B19" s="277"/>
+      <c r="C19" s="277"/>
+      <c r="D19" s="277"/>
       <c r="E19" s="10"/>
-      <c r="F19" s="161"/>
-      <c r="G19" s="163"/>
-      <c r="H19" s="104" t="s">
+      <c r="F19" s="137"/>
+      <c r="G19" s="139"/>
+      <c r="H19" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I19" s="104" t="s">
+      <c r="I19" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J19" s="338"/>
-      <c r="K19" s="338"/>
-      <c r="L19" s="338"/>
-      <c r="M19" s="339"/>
+      <c r="J19" s="280"/>
+      <c r="K19" s="280"/>
+      <c r="L19" s="280"/>
+      <c r="M19" s="281"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="417"/>
-      <c r="B20" s="335"/>
-      <c r="C20" s="335"/>
-      <c r="D20" s="335"/>
+      <c r="A20" s="359"/>
+      <c r="B20" s="277"/>
+      <c r="C20" s="277"/>
+      <c r="D20" s="277"/>
       <c r="E20" s="10"/>
-      <c r="F20" s="161"/>
-      <c r="G20" s="163"/>
-      <c r="H20" s="104" t="s">
+      <c r="F20" s="137"/>
+      <c r="G20" s="139"/>
+      <c r="H20" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I20" s="104" t="s">
+      <c r="I20" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J20" s="338"/>
-      <c r="K20" s="338"/>
-      <c r="L20" s="338"/>
-      <c r="M20" s="339"/>
+      <c r="J20" s="280"/>
+      <c r="K20" s="280"/>
+      <c r="L20" s="280"/>
+      <c r="M20" s="281"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="417"/>
-      <c r="B21" s="335"/>
-      <c r="C21" s="335"/>
-      <c r="D21" s="335"/>
+      <c r="A21" s="359"/>
+      <c r="B21" s="277"/>
+      <c r="C21" s="277"/>
+      <c r="D21" s="277"/>
       <c r="E21" s="10"/>
-      <c r="F21" s="161"/>
-      <c r="G21" s="163"/>
-      <c r="H21" s="104" t="s">
+      <c r="F21" s="137"/>
+      <c r="G21" s="139"/>
+      <c r="H21" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I21" s="104" t="s">
+      <c r="I21" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J21" s="338"/>
-      <c r="K21" s="338"/>
-      <c r="L21" s="338"/>
-      <c r="M21" s="339"/>
+      <c r="J21" s="280"/>
+      <c r="K21" s="280"/>
+      <c r="L21" s="280"/>
+      <c r="M21" s="281"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="417"/>
-      <c r="B22" s="335"/>
-      <c r="C22" s="335"/>
-      <c r="D22" s="335"/>
+      <c r="A22" s="359"/>
+      <c r="B22" s="277"/>
+      <c r="C22" s="277"/>
+      <c r="D22" s="277"/>
       <c r="E22" s="10"/>
-      <c r="F22" s="161"/>
-      <c r="G22" s="163"/>
-      <c r="H22" s="104" t="s">
+      <c r="F22" s="137"/>
+      <c r="G22" s="139"/>
+      <c r="H22" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I22" s="104" t="s">
+      <c r="I22" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="338"/>
-      <c r="K22" s="338"/>
-      <c r="L22" s="338"/>
-      <c r="M22" s="339"/>
+      <c r="J22" s="280"/>
+      <c r="K22" s="280"/>
+      <c r="L22" s="280"/>
+      <c r="M22" s="281"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="417"/>
-      <c r="B23" s="335"/>
-      <c r="C23" s="335"/>
-      <c r="D23" s="335"/>
+      <c r="A23" s="359"/>
+      <c r="B23" s="277"/>
+      <c r="C23" s="277"/>
+      <c r="D23" s="277"/>
       <c r="E23" s="10"/>
-      <c r="F23" s="161"/>
-      <c r="G23" s="163"/>
-      <c r="H23" s="104" t="s">
+      <c r="F23" s="137"/>
+      <c r="G23" s="139"/>
+      <c r="H23" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I23" s="104" t="s">
+      <c r="I23" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="338"/>
-      <c r="K23" s="338"/>
-      <c r="L23" s="338"/>
-      <c r="M23" s="339"/>
+      <c r="J23" s="280"/>
+      <c r="K23" s="280"/>
+      <c r="L23" s="280"/>
+      <c r="M23" s="281"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="417"/>
-      <c r="B24" s="335"/>
-      <c r="C24" s="335"/>
-      <c r="D24" s="335"/>
+      <c r="A24" s="359"/>
+      <c r="B24" s="277"/>
+      <c r="C24" s="277"/>
+      <c r="D24" s="277"/>
       <c r="E24" s="10"/>
-      <c r="F24" s="161"/>
-      <c r="G24" s="163"/>
-      <c r="H24" s="104" t="s">
+      <c r="F24" s="137"/>
+      <c r="G24" s="139"/>
+      <c r="H24" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I24" s="104" t="s">
+      <c r="I24" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="338"/>
-      <c r="K24" s="338"/>
-      <c r="L24" s="338"/>
-      <c r="M24" s="339"/>
+      <c r="J24" s="280"/>
+      <c r="K24" s="280"/>
+      <c r="L24" s="280"/>
+      <c r="M24" s="281"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="417"/>
-      <c r="B25" s="335"/>
-      <c r="C25" s="335"/>
-      <c r="D25" s="335"/>
+      <c r="A25" s="359"/>
+      <c r="B25" s="277"/>
+      <c r="C25" s="277"/>
+      <c r="D25" s="277"/>
       <c r="E25" s="10"/>
-      <c r="F25" s="161"/>
-      <c r="G25" s="163"/>
-      <c r="H25" s="104" t="s">
+      <c r="F25" s="137"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="I25" s="104" t="s">
+      <c r="I25" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="338"/>
-      <c r="K25" s="338"/>
-      <c r="L25" s="338"/>
-      <c r="M25" s="339"/>
+      <c r="J25" s="280"/>
+      <c r="K25" s="280"/>
+      <c r="L25" s="280"/>
+      <c r="M25" s="281"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="418"/>
-      <c r="B26" s="419"/>
-      <c r="C26" s="419"/>
-      <c r="D26" s="419"/>
+      <c r="A26" s="360"/>
+      <c r="B26" s="361"/>
+      <c r="C26" s="361"/>
+      <c r="D26" s="361"/>
       <c r="E26" s="13"/>
-      <c r="F26" s="338"/>
-      <c r="G26" s="338"/>
+      <c r="F26" s="280"/>
+      <c r="G26" s="280"/>
       <c r="H26" s="13"/>
       <c r="I26" s="13"/>
-      <c r="J26" s="338"/>
-      <c r="K26" s="338"/>
-      <c r="L26" s="338"/>
-      <c r="M26" s="339"/>
+      <c r="J26" s="280"/>
+      <c r="K26" s="280"/>
+      <c r="L26" s="280"/>
+      <c r="M26" s="281"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="418"/>
-      <c r="B27" s="419"/>
-      <c r="C27" s="419"/>
-      <c r="D27" s="419"/>
+      <c r="A27" s="360"/>
+      <c r="B27" s="361"/>
+      <c r="C27" s="361"/>
+      <c r="D27" s="361"/>
       <c r="E27" s="13"/>
-      <c r="F27" s="338"/>
-      <c r="G27" s="338"/>
+      <c r="F27" s="280"/>
+      <c r="G27" s="280"/>
       <c r="H27" s="13"/>
       <c r="I27" s="13"/>
-      <c r="J27" s="338"/>
-      <c r="K27" s="338"/>
-      <c r="L27" s="338"/>
-      <c r="M27" s="339"/>
+      <c r="J27" s="280"/>
+      <c r="K27" s="280"/>
+      <c r="L27" s="280"/>
+      <c r="M27" s="281"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="418"/>
-      <c r="B28" s="419"/>
-      <c r="C28" s="419"/>
-      <c r="D28" s="419"/>
+      <c r="A28" s="360"/>
+      <c r="B28" s="361"/>
+      <c r="C28" s="361"/>
+      <c r="D28" s="361"/>
       <c r="E28" s="13"/>
-      <c r="F28" s="338"/>
-      <c r="G28" s="338"/>
+      <c r="F28" s="280"/>
+      <c r="G28" s="280"/>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
-      <c r="J28" s="338"/>
-      <c r="K28" s="338"/>
-      <c r="L28" s="338"/>
-      <c r="M28" s="339"/>
+      <c r="J28" s="280"/>
+      <c r="K28" s="280"/>
+      <c r="L28" s="280"/>
+      <c r="M28" s="281"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="418"/>
-      <c r="B29" s="419"/>
-      <c r="C29" s="419"/>
-      <c r="D29" s="419"/>
+      <c r="A29" s="360"/>
+      <c r="B29" s="361"/>
+      <c r="C29" s="361"/>
+      <c r="D29" s="361"/>
       <c r="E29" s="13"/>
-      <c r="F29" s="338"/>
-      <c r="G29" s="338"/>
+      <c r="F29" s="280"/>
+      <c r="G29" s="280"/>
       <c r="H29" s="13"/>
       <c r="I29" s="13"/>
-      <c r="J29" s="338"/>
-      <c r="K29" s="338"/>
-      <c r="L29" s="338"/>
-      <c r="M29" s="339"/>
+      <c r="J29" s="280"/>
+      <c r="K29" s="280"/>
+      <c r="L29" s="280"/>
+      <c r="M29" s="281"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="418"/>
-      <c r="B30" s="419"/>
-      <c r="C30" s="419"/>
-      <c r="D30" s="419"/>
+      <c r="A30" s="360"/>
+      <c r="B30" s="361"/>
+      <c r="C30" s="361"/>
+      <c r="D30" s="361"/>
       <c r="E30" s="13"/>
-      <c r="F30" s="338"/>
-      <c r="G30" s="338"/>
+      <c r="F30" s="280"/>
+      <c r="G30" s="280"/>
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
-      <c r="J30" s="338"/>
-      <c r="K30" s="338"/>
-      <c r="L30" s="338"/>
-      <c r="M30" s="339"/>
+      <c r="J30" s="280"/>
+      <c r="K30" s="280"/>
+      <c r="L30" s="280"/>
+      <c r="M30" s="281"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="418"/>
-      <c r="B31" s="419"/>
-      <c r="C31" s="419"/>
-      <c r="D31" s="419"/>
+      <c r="A31" s="360"/>
+      <c r="B31" s="361"/>
+      <c r="C31" s="361"/>
+      <c r="D31" s="361"/>
       <c r="E31" s="13"/>
-      <c r="F31" s="338"/>
-      <c r="G31" s="338"/>
+      <c r="F31" s="280"/>
+      <c r="G31" s="280"/>
       <c r="H31" s="13"/>
       <c r="I31" s="13"/>
-      <c r="J31" s="338"/>
-      <c r="K31" s="338"/>
-      <c r="L31" s="338"/>
-      <c r="M31" s="339"/>
+      <c r="J31" s="280"/>
+      <c r="K31" s="280"/>
+      <c r="L31" s="280"/>
+      <c r="M31" s="281"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="418"/>
-      <c r="B32" s="419"/>
-      <c r="C32" s="419"/>
-      <c r="D32" s="419"/>
+      <c r="A32" s="360"/>
+      <c r="B32" s="361"/>
+      <c r="C32" s="361"/>
+      <c r="D32" s="361"/>
       <c r="E32" s="13"/>
-      <c r="F32" s="338"/>
-      <c r="G32" s="338"/>
+      <c r="F32" s="280"/>
+      <c r="G32" s="280"/>
       <c r="H32" s="13"/>
       <c r="I32" s="13"/>
-      <c r="J32" s="338"/>
-      <c r="K32" s="338"/>
-      <c r="L32" s="338"/>
-      <c r="M32" s="339"/>
+      <c r="J32" s="280"/>
+      <c r="K32" s="280"/>
+      <c r="L32" s="280"/>
+      <c r="M32" s="281"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A33" s="418"/>
-      <c r="B33" s="419"/>
-      <c r="C33" s="419"/>
-      <c r="D33" s="419"/>
+      <c r="A33" s="360"/>
+      <c r="B33" s="361"/>
+      <c r="C33" s="361"/>
+      <c r="D33" s="361"/>
       <c r="E33" s="13"/>
-      <c r="F33" s="338"/>
-      <c r="G33" s="338"/>
+      <c r="F33" s="280"/>
+      <c r="G33" s="280"/>
       <c r="H33" s="13"/>
       <c r="I33" s="13"/>
-      <c r="J33" s="338"/>
-      <c r="K33" s="338"/>
-      <c r="L33" s="338"/>
-      <c r="M33" s="339"/>
+      <c r="J33" s="280"/>
+      <c r="K33" s="280"/>
+      <c r="L33" s="280"/>
+      <c r="M33" s="281"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A34" s="418"/>
-      <c r="B34" s="419"/>
-      <c r="C34" s="419"/>
-      <c r="D34" s="419"/>
+      <c r="A34" s="360"/>
+      <c r="B34" s="361"/>
+      <c r="C34" s="361"/>
+      <c r="D34" s="361"/>
       <c r="E34" s="13"/>
-      <c r="F34" s="338"/>
-      <c r="G34" s="338"/>
+      <c r="F34" s="280"/>
+      <c r="G34" s="280"/>
       <c r="H34" s="13"/>
       <c r="I34" s="13"/>
-      <c r="J34" s="338"/>
-      <c r="K34" s="338"/>
-      <c r="L34" s="338"/>
-      <c r="M34" s="339"/>
+      <c r="J34" s="280"/>
+      <c r="K34" s="280"/>
+      <c r="L34" s="280"/>
+      <c r="M34" s="281"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35" s="418"/>
-      <c r="B35" s="419"/>
-      <c r="C35" s="419"/>
-      <c r="D35" s="419"/>
+      <c r="A35" s="360"/>
+      <c r="B35" s="361"/>
+      <c r="C35" s="361"/>
+      <c r="D35" s="361"/>
       <c r="E35" s="13"/>
-      <c r="F35" s="338"/>
-      <c r="G35" s="338"/>
+      <c r="F35" s="280"/>
+      <c r="G35" s="280"/>
       <c r="H35" s="13"/>
       <c r="I35" s="13"/>
-      <c r="J35" s="338"/>
-      <c r="K35" s="338"/>
-      <c r="L35" s="338"/>
-      <c r="M35" s="339"/>
+      <c r="J35" s="280"/>
+      <c r="K35" s="280"/>
+      <c r="L35" s="280"/>
+      <c r="M35" s="281"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A36" s="418"/>
-      <c r="B36" s="419"/>
-      <c r="C36" s="419"/>
-      <c r="D36" s="419"/>
+      <c r="A36" s="360"/>
+      <c r="B36" s="361"/>
+      <c r="C36" s="361"/>
+      <c r="D36" s="361"/>
       <c r="E36" s="13"/>
-      <c r="F36" s="338"/>
-      <c r="G36" s="338"/>
+      <c r="F36" s="280"/>
+      <c r="G36" s="280"/>
       <c r="H36" s="13"/>
       <c r="I36" s="13"/>
-      <c r="J36" s="338"/>
-      <c r="K36" s="338"/>
-      <c r="L36" s="338"/>
-      <c r="M36" s="339"/>
+      <c r="J36" s="280"/>
+      <c r="K36" s="280"/>
+      <c r="L36" s="280"/>
+      <c r="M36" s="281"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A37" s="418"/>
-      <c r="B37" s="419"/>
-      <c r="C37" s="419"/>
-      <c r="D37" s="419"/>
+      <c r="A37" s="360"/>
+      <c r="B37" s="361"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
       <c r="E37" s="13"/>
-      <c r="F37" s="338"/>
-      <c r="G37" s="338"/>
+      <c r="F37" s="280"/>
+      <c r="G37" s="280"/>
       <c r="H37" s="13"/>
       <c r="I37" s="13"/>
-      <c r="J37" s="338"/>
-      <c r="K37" s="338"/>
-      <c r="L37" s="338"/>
-      <c r="M37" s="339"/>
+      <c r="J37" s="280"/>
+      <c r="K37" s="280"/>
+      <c r="L37" s="280"/>
+      <c r="M37" s="281"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A38" s="418"/>
-      <c r="B38" s="419"/>
-      <c r="C38" s="419"/>
-      <c r="D38" s="419"/>
+      <c r="A38" s="360"/>
+      <c r="B38" s="361"/>
+      <c r="C38" s="361"/>
+      <c r="D38" s="361"/>
       <c r="E38" s="13"/>
-      <c r="F38" s="338"/>
-      <c r="G38" s="338"/>
+      <c r="F38" s="280"/>
+      <c r="G38" s="280"/>
       <c r="H38" s="13"/>
       <c r="I38" s="13"/>
-      <c r="J38" s="338"/>
-      <c r="K38" s="338"/>
-      <c r="L38" s="338"/>
-      <c r="M38" s="339"/>
+      <c r="J38" s="280"/>
+      <c r="K38" s="280"/>
+      <c r="L38" s="280"/>
+      <c r="M38" s="281"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A39" s="418"/>
-      <c r="B39" s="419"/>
-      <c r="C39" s="419"/>
-      <c r="D39" s="419"/>
+      <c r="A39" s="360"/>
+      <c r="B39" s="361"/>
+      <c r="C39" s="361"/>
+      <c r="D39" s="361"/>
       <c r="E39" s="13"/>
-      <c r="F39" s="338"/>
-      <c r="G39" s="338"/>
+      <c r="F39" s="280"/>
+      <c r="G39" s="280"/>
       <c r="H39" s="13"/>
       <c r="I39" s="13"/>
-      <c r="J39" s="338"/>
-      <c r="K39" s="338"/>
-      <c r="L39" s="338"/>
-      <c r="M39" s="339"/>
+      <c r="J39" s="280"/>
+      <c r="K39" s="280"/>
+      <c r="L39" s="280"/>
+      <c r="M39" s="281"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A40" s="418"/>
-      <c r="B40" s="419"/>
-      <c r="C40" s="419"/>
-      <c r="D40" s="419"/>
+      <c r="A40" s="360"/>
+      <c r="B40" s="361"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
       <c r="E40" s="13"/>
-      <c r="F40" s="338"/>
-      <c r="G40" s="338"/>
+      <c r="F40" s="280"/>
+      <c r="G40" s="280"/>
       <c r="H40" s="13"/>
       <c r="I40" s="13"/>
-      <c r="J40" s="338"/>
-      <c r="K40" s="338"/>
-      <c r="L40" s="338"/>
-      <c r="M40" s="339"/>
+      <c r="J40" s="280"/>
+      <c r="K40" s="280"/>
+      <c r="L40" s="280"/>
+      <c r="M40" s="281"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A41" s="418"/>
-      <c r="B41" s="419"/>
-      <c r="C41" s="419"/>
-      <c r="D41" s="419"/>
+      <c r="A41" s="360"/>
+      <c r="B41" s="361"/>
+      <c r="C41" s="361"/>
+      <c r="D41" s="361"/>
       <c r="E41" s="13"/>
-      <c r="F41" s="338"/>
-      <c r="G41" s="338"/>
+      <c r="F41" s="280"/>
+      <c r="G41" s="280"/>
       <c r="H41" s="13"/>
       <c r="I41" s="13"/>
-      <c r="J41" s="338"/>
-      <c r="K41" s="338"/>
-      <c r="L41" s="338"/>
-      <c r="M41" s="339"/>
+      <c r="J41" s="280"/>
+      <c r="K41" s="280"/>
+      <c r="L41" s="280"/>
+      <c r="M41" s="281"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A42" s="418"/>
-      <c r="B42" s="419"/>
-      <c r="C42" s="419"/>
-      <c r="D42" s="419"/>
+      <c r="A42" s="360"/>
+      <c r="B42" s="361"/>
+      <c r="C42" s="361"/>
+      <c r="D42" s="361"/>
       <c r="E42" s="13"/>
-      <c r="F42" s="338"/>
-      <c r="G42" s="338"/>
+      <c r="F42" s="280"/>
+      <c r="G42" s="280"/>
       <c r="H42" s="13"/>
       <c r="I42" s="13"/>
-      <c r="J42" s="338"/>
-      <c r="K42" s="338"/>
-      <c r="L42" s="338"/>
-      <c r="M42" s="339"/>
+      <c r="J42" s="280"/>
+      <c r="K42" s="280"/>
+      <c r="L42" s="280"/>
+      <c r="M42" s="281"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A43" s="418"/>
-      <c r="B43" s="419"/>
-      <c r="C43" s="419"/>
-      <c r="D43" s="419"/>
+      <c r="A43" s="360"/>
+      <c r="B43" s="361"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
       <c r="E43" s="13"/>
-      <c r="F43" s="338"/>
-      <c r="G43" s="338"/>
+      <c r="F43" s="280"/>
+      <c r="G43" s="280"/>
       <c r="H43" s="13"/>
       <c r="I43" s="13"/>
-      <c r="J43" s="338"/>
-      <c r="K43" s="338"/>
-      <c r="L43" s="338"/>
-      <c r="M43" s="339"/>
+      <c r="J43" s="280"/>
+      <c r="K43" s="280"/>
+      <c r="L43" s="280"/>
+      <c r="M43" s="281"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A44" s="418"/>
-      <c r="B44" s="419"/>
-      <c r="C44" s="419"/>
-      <c r="D44" s="419"/>
+      <c r="A44" s="360"/>
+      <c r="B44" s="361"/>
+      <c r="C44" s="361"/>
+      <c r="D44" s="361"/>
       <c r="E44" s="13"/>
-      <c r="F44" s="338"/>
-      <c r="G44" s="338"/>
+      <c r="F44" s="280"/>
+      <c r="G44" s="280"/>
       <c r="H44" s="13"/>
       <c r="I44" s="13"/>
-      <c r="J44" s="338"/>
-      <c r="K44" s="338"/>
-      <c r="L44" s="338"/>
-      <c r="M44" s="339"/>
+      <c r="J44" s="280"/>
+      <c r="K44" s="280"/>
+      <c r="L44" s="280"/>
+      <c r="M44" s="281"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A45" s="418"/>
-      <c r="B45" s="419"/>
-      <c r="C45" s="419"/>
-      <c r="D45" s="419"/>
+      <c r="A45" s="360"/>
+      <c r="B45" s="361"/>
+      <c r="C45" s="361"/>
+      <c r="D45" s="361"/>
       <c r="E45" s="13"/>
-      <c r="F45" s="338"/>
-      <c r="G45" s="338"/>
+      <c r="F45" s="280"/>
+      <c r="G45" s="280"/>
       <c r="H45" s="13"/>
       <c r="I45" s="13"/>
-      <c r="J45" s="338"/>
-      <c r="K45" s="338"/>
-      <c r="L45" s="338"/>
-      <c r="M45" s="339"/>
+      <c r="J45" s="280"/>
+      <c r="K45" s="280"/>
+      <c r="L45" s="280"/>
+      <c r="M45" s="281"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A46" s="418"/>
-      <c r="B46" s="419"/>
-      <c r="C46" s="419"/>
-      <c r="D46" s="419"/>
+      <c r="A46" s="360"/>
+      <c r="B46" s="361"/>
+      <c r="C46" s="361"/>
+      <c r="D46" s="361"/>
       <c r="E46" s="13"/>
-      <c r="F46" s="338"/>
-      <c r="G46" s="338"/>
+      <c r="F46" s="280"/>
+      <c r="G46" s="280"/>
       <c r="H46" s="13"/>
       <c r="I46" s="13"/>
-      <c r="J46" s="338"/>
-      <c r="K46" s="338"/>
-      <c r="L46" s="338"/>
-      <c r="M46" s="339"/>
+      <c r="J46" s="280"/>
+      <c r="K46" s="280"/>
+      <c r="L46" s="280"/>
+      <c r="M46" s="281"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A47" s="418"/>
-      <c r="B47" s="419"/>
-      <c r="C47" s="419"/>
-      <c r="D47" s="419"/>
+      <c r="A47" s="360"/>
+      <c r="B47" s="361"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
       <c r="E47" s="13"/>
-      <c r="F47" s="338"/>
-      <c r="G47" s="338"/>
+      <c r="F47" s="280"/>
+      <c r="G47" s="280"/>
       <c r="H47" s="13"/>
       <c r="I47" s="13"/>
-      <c r="J47" s="338"/>
-      <c r="K47" s="338"/>
-      <c r="L47" s="338"/>
-      <c r="M47" s="339"/>
+      <c r="J47" s="280"/>
+      <c r="K47" s="280"/>
+      <c r="L47" s="280"/>
+      <c r="M47" s="281"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A48" s="418"/>
-      <c r="B48" s="419"/>
-      <c r="C48" s="419"/>
-      <c r="D48" s="419"/>
+      <c r="A48" s="360"/>
+      <c r="B48" s="361"/>
+      <c r="C48" s="361"/>
+      <c r="D48" s="361"/>
       <c r="E48" s="13"/>
-      <c r="F48" s="338"/>
-      <c r="G48" s="338"/>
+      <c r="F48" s="280"/>
+      <c r="G48" s="280"/>
       <c r="H48" s="13"/>
       <c r="I48" s="13"/>
-      <c r="J48" s="338"/>
-      <c r="K48" s="338"/>
-      <c r="L48" s="338"/>
-      <c r="M48" s="339"/>
+      <c r="J48" s="280"/>
+      <c r="K48" s="280"/>
+      <c r="L48" s="280"/>
+      <c r="M48" s="281"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A49" s="418"/>
-      <c r="B49" s="419"/>
-      <c r="C49" s="419"/>
-      <c r="D49" s="419"/>
+      <c r="A49" s="360"/>
+      <c r="B49" s="361"/>
+      <c r="C49" s="361"/>
+      <c r="D49" s="361"/>
       <c r="E49" s="13"/>
-      <c r="F49" s="338"/>
-      <c r="G49" s="338"/>
+      <c r="F49" s="280"/>
+      <c r="G49" s="280"/>
       <c r="H49" s="13"/>
       <c r="I49" s="13"/>
-      <c r="J49" s="338"/>
-      <c r="K49" s="338"/>
-      <c r="L49" s="338"/>
-      <c r="M49" s="339"/>
+      <c r="J49" s="280"/>
+      <c r="K49" s="280"/>
+      <c r="L49" s="280"/>
+      <c r="M49" s="281"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="345" t="s">
+      <c r="A50" s="287" t="s">
         <v>22</v>
       </c>
-      <c r="B50" s="346"/>
-      <c r="C50" s="346"/>
-      <c r="D50" s="346"/>
-      <c r="E50" s="105"/>
-      <c r="F50" s="432"/>
-      <c r="G50" s="433"/>
+      <c r="B50" s="288"/>
+      <c r="C50" s="288"/>
+      <c r="D50" s="288"/>
+      <c r="E50" s="81"/>
+      <c r="F50" s="374"/>
+      <c r="G50" s="375"/>
       <c r="H50" s="29"/>
       <c r="I50" s="30"/>
-      <c r="J50" s="434"/>
-      <c r="K50" s="434"/>
-      <c r="L50" s="434"/>
-      <c r="M50" s="435"/>
+      <c r="J50" s="376"/>
+      <c r="K50" s="376"/>
+      <c r="L50" s="376"/>
+      <c r="M50" s="377"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A51" s="420" t="s">
+      <c r="A51" s="362" t="s">
         <v>58</v>
       </c>
-      <c r="B51" s="421"/>
-      <c r="C51" s="421"/>
-      <c r="D51" s="421"/>
-      <c r="E51" s="421"/>
-      <c r="F51" s="421"/>
-      <c r="G51" s="421"/>
-      <c r="H51" s="421"/>
-      <c r="I51" s="421"/>
-      <c r="J51" s="421"/>
-      <c r="K51" s="421"/>
-      <c r="L51" s="421"/>
-      <c r="M51" s="422"/>
+      <c r="B51" s="363"/>
+      <c r="C51" s="363"/>
+      <c r="D51" s="363"/>
+      <c r="E51" s="363"/>
+      <c r="F51" s="363"/>
+      <c r="G51" s="363"/>
+      <c r="H51" s="363"/>
+      <c r="I51" s="363"/>
+      <c r="J51" s="363"/>
+      <c r="K51" s="363"/>
+      <c r="L51" s="363"/>
+      <c r="M51" s="364"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="423"/>
-      <c r="B52" s="424"/>
-      <c r="C52" s="424"/>
-      <c r="D52" s="424"/>
-      <c r="E52" s="424"/>
-      <c r="F52" s="424"/>
-      <c r="G52" s="424"/>
-      <c r="H52" s="424"/>
-      <c r="I52" s="424"/>
-      <c r="J52" s="424"/>
-      <c r="K52" s="424"/>
-      <c r="L52" s="424"/>
-      <c r="M52" s="425"/>
+      <c r="A52" s="365"/>
+      <c r="B52" s="366"/>
+      <c r="C52" s="366"/>
+      <c r="D52" s="366"/>
+      <c r="E52" s="366"/>
+      <c r="F52" s="366"/>
+      <c r="G52" s="366"/>
+      <c r="H52" s="366"/>
+      <c r="I52" s="366"/>
+      <c r="J52" s="366"/>
+      <c r="K52" s="366"/>
+      <c r="L52" s="366"/>
+      <c r="M52" s="367"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A53" s="426"/>
-      <c r="B53" s="427"/>
-      <c r="C53" s="427"/>
-      <c r="D53" s="427"/>
-      <c r="E53" s="427"/>
-      <c r="F53" s="427"/>
-      <c r="G53" s="427"/>
-      <c r="H53" s="427"/>
-      <c r="I53" s="427"/>
-      <c r="J53" s="427"/>
-      <c r="K53" s="427"/>
-      <c r="L53" s="427"/>
-      <c r="M53" s="428"/>
+      <c r="A53" s="368"/>
+      <c r="B53" s="369"/>
+      <c r="C53" s="369"/>
+      <c r="D53" s="369"/>
+      <c r="E53" s="369"/>
+      <c r="F53" s="369"/>
+      <c r="G53" s="369"/>
+      <c r="H53" s="369"/>
+      <c r="I53" s="369"/>
+      <c r="J53" s="369"/>
+      <c r="K53" s="369"/>
+      <c r="L53" s="369"/>
+      <c r="M53" s="370"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A54" s="426"/>
-      <c r="B54" s="427"/>
-      <c r="C54" s="427"/>
-      <c r="D54" s="427"/>
-      <c r="E54" s="427"/>
-      <c r="F54" s="427"/>
-      <c r="G54" s="427"/>
-      <c r="H54" s="427"/>
-      <c r="I54" s="427"/>
-      <c r="J54" s="427"/>
-      <c r="K54" s="427"/>
-      <c r="L54" s="427"/>
-      <c r="M54" s="428"/>
+      <c r="A54" s="368"/>
+      <c r="B54" s="369"/>
+      <c r="C54" s="369"/>
+      <c r="D54" s="369"/>
+      <c r="E54" s="369"/>
+      <c r="F54" s="369"/>
+      <c r="G54" s="369"/>
+      <c r="H54" s="369"/>
+      <c r="I54" s="369"/>
+      <c r="J54" s="369"/>
+      <c r="K54" s="369"/>
+      <c r="L54" s="369"/>
+      <c r="M54" s="370"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A55" s="426"/>
-      <c r="B55" s="427"/>
-      <c r="C55" s="427"/>
-      <c r="D55" s="427"/>
-      <c r="E55" s="427"/>
-      <c r="F55" s="427"/>
-      <c r="G55" s="427"/>
-      <c r="H55" s="427"/>
-      <c r="I55" s="427"/>
-      <c r="J55" s="427"/>
-      <c r="K55" s="427"/>
-      <c r="L55" s="427"/>
-      <c r="M55" s="428"/>
+      <c r="A55" s="368"/>
+      <c r="B55" s="369"/>
+      <c r="C55" s="369"/>
+      <c r="D55" s="369"/>
+      <c r="E55" s="369"/>
+      <c r="F55" s="369"/>
+      <c r="G55" s="369"/>
+      <c r="H55" s="369"/>
+      <c r="I55" s="369"/>
+      <c r="J55" s="369"/>
+      <c r="K55" s="369"/>
+      <c r="L55" s="369"/>
+      <c r="M55" s="370"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A56" s="426"/>
-      <c r="B56" s="427"/>
-      <c r="C56" s="427"/>
-      <c r="D56" s="427"/>
-      <c r="E56" s="427"/>
-      <c r="F56" s="427"/>
-      <c r="G56" s="427"/>
-      <c r="H56" s="427"/>
-      <c r="I56" s="427"/>
-      <c r="J56" s="427"/>
-      <c r="K56" s="427"/>
-      <c r="L56" s="427"/>
-      <c r="M56" s="428"/>
+      <c r="A56" s="368"/>
+      <c r="B56" s="369"/>
+      <c r="C56" s="369"/>
+      <c r="D56" s="369"/>
+      <c r="E56" s="369"/>
+      <c r="F56" s="369"/>
+      <c r="G56" s="369"/>
+      <c r="H56" s="369"/>
+      <c r="I56" s="369"/>
+      <c r="J56" s="369"/>
+      <c r="K56" s="369"/>
+      <c r="L56" s="369"/>
+      <c r="M56" s="370"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A57" s="426"/>
-      <c r="B57" s="427"/>
-      <c r="C57" s="427"/>
-      <c r="D57" s="427"/>
-      <c r="E57" s="427"/>
-      <c r="F57" s="427"/>
-      <c r="G57" s="427"/>
-      <c r="H57" s="427"/>
-      <c r="I57" s="427"/>
-      <c r="J57" s="427"/>
-      <c r="K57" s="427"/>
-      <c r="L57" s="427"/>
-      <c r="M57" s="428"/>
+      <c r="A57" s="368"/>
+      <c r="B57" s="369"/>
+      <c r="C57" s="369"/>
+      <c r="D57" s="369"/>
+      <c r="E57" s="369"/>
+      <c r="F57" s="369"/>
+      <c r="G57" s="369"/>
+      <c r="H57" s="369"/>
+      <c r="I57" s="369"/>
+      <c r="J57" s="369"/>
+      <c r="K57" s="369"/>
+      <c r="L57" s="369"/>
+      <c r="M57" s="370"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A58" s="426"/>
-      <c r="B58" s="427"/>
-      <c r="C58" s="427"/>
-      <c r="D58" s="427"/>
-      <c r="E58" s="427"/>
-      <c r="F58" s="427"/>
-      <c r="G58" s="427"/>
-      <c r="H58" s="427"/>
-      <c r="I58" s="427"/>
-      <c r="J58" s="427"/>
-      <c r="K58" s="427"/>
-      <c r="L58" s="427"/>
-      <c r="M58" s="428"/>
+      <c r="A58" s="368"/>
+      <c r="B58" s="369"/>
+      <c r="C58" s="369"/>
+      <c r="D58" s="369"/>
+      <c r="E58" s="369"/>
+      <c r="F58" s="369"/>
+      <c r="G58" s="369"/>
+      <c r="H58" s="369"/>
+      <c r="I58" s="369"/>
+      <c r="J58" s="369"/>
+      <c r="K58" s="369"/>
+      <c r="L58" s="369"/>
+      <c r="M58" s="370"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A59" s="426"/>
-      <c r="B59" s="427"/>
-      <c r="C59" s="427"/>
-      <c r="D59" s="427"/>
-      <c r="E59" s="427"/>
-      <c r="F59" s="427"/>
-      <c r="G59" s="427"/>
-      <c r="H59" s="427"/>
-      <c r="I59" s="427"/>
-      <c r="J59" s="427"/>
-      <c r="K59" s="427"/>
-      <c r="L59" s="427"/>
-      <c r="M59" s="428"/>
+      <c r="A59" s="368"/>
+      <c r="B59" s="369"/>
+      <c r="C59" s="369"/>
+      <c r="D59" s="369"/>
+      <c r="E59" s="369"/>
+      <c r="F59" s="369"/>
+      <c r="G59" s="369"/>
+      <c r="H59" s="369"/>
+      <c r="I59" s="369"/>
+      <c r="J59" s="369"/>
+      <c r="K59" s="369"/>
+      <c r="L59" s="369"/>
+      <c r="M59" s="370"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A60" s="429"/>
-      <c r="B60" s="430"/>
-      <c r="C60" s="430"/>
-      <c r="D60" s="430"/>
-      <c r="E60" s="430"/>
-      <c r="F60" s="430"/>
-      <c r="G60" s="430"/>
-      <c r="H60" s="430"/>
-      <c r="I60" s="430"/>
-      <c r="J60" s="430"/>
-      <c r="K60" s="430"/>
-      <c r="L60" s="430"/>
-      <c r="M60" s="431"/>
+      <c r="A60" s="371"/>
+      <c r="B60" s="372"/>
+      <c r="C60" s="372"/>
+      <c r="D60" s="372"/>
+      <c r="E60" s="372"/>
+      <c r="F60" s="372"/>
+      <c r="G60" s="372"/>
+      <c r="H60" s="372"/>
+      <c r="I60" s="372"/>
+      <c r="J60" s="372"/>
+      <c r="K60" s="372"/>
+      <c r="L60" s="372"/>
+      <c r="M60" s="373"/>
     </row>
     <row r="61" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="28"/>
@@ -7602,600 +7546,602 @@
     <col min="13" max="13" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="390" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="241"/>
-      <c r="C1" s="241"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40" t="s">
+      <c r="B1" s="391"/>
+      <c r="C1" s="391"/>
+      <c r="D1" s="392"/>
+      <c r="E1" s="392"/>
+      <c r="F1" s="393"/>
+      <c r="G1" s="393" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="246" t="s">
+      <c r="H1" s="393"/>
+      <c r="I1" s="393"/>
+      <c r="J1" s="393"/>
+      <c r="K1" s="393"/>
+      <c r="L1" s="394" t="s">
         <v>69</v>
       </c>
-      <c r="M1" s="247"/>
+      <c r="M1" s="395"/>
     </row>
     <row r="2" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="243" t="s">
+      <c r="A2" s="387" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="244"/>
-      <c r="C2" s="244"/>
-      <c r="D2" s="244"/>
-      <c r="E2" s="244"/>
-      <c r="F2" s="244"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="44"/>
+      <c r="B2" s="388"/>
+      <c r="C2" s="388"/>
+      <c r="D2" s="388"/>
+      <c r="E2" s="388"/>
+      <c r="F2" s="388"/>
+      <c r="G2" s="388"/>
+      <c r="H2" s="388"/>
+      <c r="I2" s="412"/>
+      <c r="J2" s="413"/>
+      <c r="K2" s="413"/>
+      <c r="L2" s="413"/>
+      <c r="M2" s="414"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="207" t="s">
+      <c r="A3" s="183" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="208"/>
-      <c r="C3" s="208"/>
-      <c r="D3" s="208"/>
-      <c r="E3" s="208"/>
-      <c r="F3" s="208"/>
-      <c r="G3" s="208"/>
-      <c r="H3" s="209"/>
-      <c r="I3" s="45" t="s">
+      <c r="B3" s="184"/>
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="184"/>
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="400"/>
+      <c r="I3" s="415" t="s">
         <v>75</v>
       </c>
-      <c r="J3" s="43"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="47"/>
+      <c r="J3" s="389"/>
+      <c r="K3" s="416"/>
+      <c r="L3" s="389"/>
+      <c r="M3" s="417"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="207" t="s">
+      <c r="A4" s="183" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="208"/>
-      <c r="C4" s="208"/>
-      <c r="D4" s="208"/>
-      <c r="E4" s="208"/>
-      <c r="F4" s="208"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="209"/>
-      <c r="I4" s="253"/>
-      <c r="J4" s="237"/>
-      <c r="K4" s="237"/>
-      <c r="L4" s="237"/>
-      <c r="M4" s="238"/>
+      <c r="B4" s="184"/>
+      <c r="C4" s="184"/>
+      <c r="D4" s="184"/>
+      <c r="E4" s="184"/>
+      <c r="F4" s="184"/>
+      <c r="G4" s="184"/>
+      <c r="H4" s="400"/>
+      <c r="I4" s="418"/>
+      <c r="J4" s="396"/>
+      <c r="K4" s="396"/>
+      <c r="L4" s="396"/>
+      <c r="M4" s="409"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="207" t="s">
+      <c r="A5" s="183" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="208"/>
-      <c r="C5" s="208"/>
-      <c r="D5" s="208"/>
-      <c r="E5" s="208"/>
-      <c r="F5" s="208"/>
-      <c r="G5" s="208"/>
-      <c r="H5" s="209"/>
-      <c r="I5" s="253"/>
-      <c r="J5" s="237"/>
-      <c r="K5" s="237"/>
-      <c r="L5" s="237"/>
-      <c r="M5" s="238"/>
+      <c r="B5" s="184"/>
+      <c r="C5" s="184"/>
+      <c r="D5" s="184"/>
+      <c r="E5" s="184"/>
+      <c r="F5" s="184"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="400"/>
+      <c r="I5" s="418"/>
+      <c r="J5" s="396"/>
+      <c r="K5" s="396"/>
+      <c r="L5" s="396"/>
+      <c r="M5" s="409"/>
     </row>
     <row r="6" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="251" t="s">
+      <c r="A6" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="206"/>
-      <c r="C6" s="206"/>
-      <c r="D6" s="206"/>
-      <c r="E6" s="206"/>
-      <c r="F6" s="252" t="s">
+      <c r="B6" s="182"/>
+      <c r="C6" s="182"/>
+      <c r="D6" s="182"/>
+      <c r="E6" s="182"/>
+      <c r="F6" s="207" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="252"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="254"/>
-      <c r="J6" s="255"/>
-      <c r="K6" s="255"/>
-      <c r="L6" s="255"/>
-      <c r="M6" s="256"/>
+      <c r="G6" s="207"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="419"/>
+      <c r="J6" s="420"/>
+      <c r="K6" s="420"/>
+      <c r="L6" s="420"/>
+      <c r="M6" s="421"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="258" t="s">
+      <c r="A7" s="208" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="259"/>
-      <c r="C7" s="259"/>
-      <c r="D7" s="259"/>
-      <c r="E7" s="259"/>
-      <c r="F7" s="259"/>
-      <c r="G7" s="259"/>
-      <c r="H7" s="260"/>
-      <c r="I7" s="49" t="s">
+      <c r="B7" s="209"/>
+      <c r="C7" s="209"/>
+      <c r="D7" s="209"/>
+      <c r="E7" s="209"/>
+      <c r="F7" s="209"/>
+      <c r="G7" s="209"/>
+      <c r="H7" s="209"/>
+      <c r="I7" s="423" t="s">
         <v>77</v>
       </c>
-      <c r="J7" s="50"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="50"/>
-      <c r="M7" s="52"/>
+      <c r="J7" s="424"/>
+      <c r="K7" s="425"/>
+      <c r="L7" s="424"/>
+      <c r="M7" s="426"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="122"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="229" t="s">
+      <c r="B8" s="98"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="198" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="229"/>
-      <c r="G8" s="229"/>
-      <c r="H8" s="263"/>
-      <c r="I8" s="257" t="s">
+      <c r="F8" s="198"/>
+      <c r="G8" s="198"/>
+      <c r="H8" s="404"/>
+      <c r="I8" s="427" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="208"/>
-      <c r="K8" s="208"/>
-      <c r="L8" s="208"/>
-      <c r="M8" s="209"/>
-    </row>
-    <row r="9" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="55" t="s">
+      <c r="J8" s="400"/>
+      <c r="K8" s="400"/>
+      <c r="L8" s="400"/>
+      <c r="M8" s="401"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="H9" s="56"/>
-      <c r="I9" s="57" t="s">
+      <c r="H9" s="422"/>
+      <c r="I9" s="428" t="s">
         <v>71</v>
       </c>
-      <c r="J9" s="58"/>
-      <c r="K9" s="58"/>
-      <c r="L9" s="58"/>
-      <c r="M9" s="48"/>
+      <c r="J9" s="429"/>
+      <c r="K9" s="429"/>
+      <c r="L9" s="429"/>
+      <c r="M9" s="430"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="236"/>
-      <c r="D10" s="236"/>
-      <c r="E10" s="236"/>
-      <c r="F10" s="236"/>
-      <c r="G10" s="236"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="60" t="s">
+      <c r="C10" s="204"/>
+      <c r="D10" s="204"/>
+      <c r="E10" s="204"/>
+      <c r="F10" s="204"/>
+      <c r="G10" s="204"/>
+      <c r="H10" s="422"/>
+      <c r="I10" s="412" t="s">
         <v>78</v>
       </c>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="61"/>
-      <c r="M10" s="62"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="433"/>
     </row>
     <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="205" t="s">
+      <c r="A11" s="181" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="206"/>
-      <c r="C11" s="206"/>
-      <c r="D11" s="206"/>
-      <c r="E11" s="206"/>
-      <c r="F11" s="252" t="s">
+      <c r="B11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="207" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="252"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="239" t="s">
+      <c r="G11" s="207"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="434" t="s">
         <v>72</v>
       </c>
-      <c r="J11" s="240"/>
-      <c r="K11" s="63"/>
-      <c r="L11" s="63"/>
-      <c r="M11" s="64"/>
-    </row>
-    <row r="12" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="175" t="s">
+      <c r="J11" s="435"/>
+      <c r="K11" s="436"/>
+      <c r="L11" s="436"/>
+      <c r="M11" s="437"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" s="151" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="176"/>
-      <c r="C12" s="176"/>
-      <c r="D12" s="176"/>
-      <c r="E12" s="176"/>
-      <c r="F12" s="176"/>
-      <c r="G12" s="176"/>
-      <c r="H12" s="177"/>
-      <c r="I12" s="253"/>
-      <c r="J12" s="237"/>
-      <c r="K12" s="237"/>
-      <c r="L12" s="237"/>
-      <c r="M12" s="238"/>
+      <c r="B12" s="152"/>
+      <c r="C12" s="152"/>
+      <c r="D12" s="152"/>
+      <c r="E12" s="152"/>
+      <c r="F12" s="152"/>
+      <c r="G12" s="152"/>
+      <c r="H12" s="152"/>
+      <c r="I12" s="418"/>
+      <c r="J12" s="396"/>
+      <c r="K12" s="396"/>
+      <c r="L12" s="396"/>
+      <c r="M12" s="409"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="248" t="s">
+      <c r="A13" s="397" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="249"/>
-      <c r="C13" s="249"/>
-      <c r="D13" s="249"/>
-      <c r="E13" s="249"/>
-      <c r="F13" s="249"/>
-      <c r="G13" s="249"/>
-      <c r="H13" s="250"/>
-      <c r="I13" s="253"/>
-      <c r="J13" s="237"/>
-      <c r="K13" s="237"/>
-      <c r="L13" s="237"/>
-      <c r="M13" s="238"/>
-    </row>
-    <row r="14" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="207" t="s">
+      <c r="B13" s="398"/>
+      <c r="C13" s="398"/>
+      <c r="D13" s="398"/>
+      <c r="E13" s="398"/>
+      <c r="F13" s="398"/>
+      <c r="G13" s="398"/>
+      <c r="H13" s="398"/>
+      <c r="I13" s="418"/>
+      <c r="J13" s="396"/>
+      <c r="K13" s="396"/>
+      <c r="L13" s="396"/>
+      <c r="M13" s="409"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" s="399" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="208"/>
-      <c r="C14" s="208"/>
-      <c r="D14" s="208"/>
-      <c r="E14" s="208"/>
-      <c r="F14" s="208"/>
-      <c r="G14" s="208"/>
-      <c r="H14" s="209"/>
-      <c r="I14" s="254"/>
-      <c r="J14" s="255"/>
-      <c r="K14" s="255"/>
-      <c r="L14" s="255"/>
-      <c r="M14" s="256"/>
+      <c r="B14" s="400"/>
+      <c r="C14" s="400"/>
+      <c r="D14" s="400"/>
+      <c r="E14" s="400"/>
+      <c r="F14" s="400"/>
+      <c r="G14" s="400"/>
+      <c r="H14" s="400"/>
+      <c r="I14" s="419"/>
+      <c r="J14" s="420"/>
+      <c r="K14" s="420"/>
+      <c r="L14" s="420"/>
+      <c r="M14" s="421"/>
     </row>
     <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="217" t="s">
+      <c r="A15" s="402" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="218"/>
-      <c r="C15" s="218"/>
-      <c r="D15" s="218"/>
-      <c r="E15" s="218"/>
-      <c r="F15" s="219"/>
-      <c r="G15" s="219"/>
-      <c r="H15" s="219"/>
-      <c r="I15" s="214" t="s">
+      <c r="B15" s="189"/>
+      <c r="C15" s="189"/>
+      <c r="D15" s="189"/>
+      <c r="E15" s="189"/>
+      <c r="F15" s="189"/>
+      <c r="G15" s="189"/>
+      <c r="H15" s="403"/>
+      <c r="I15" s="431" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="215"/>
-      <c r="K15" s="215"/>
-      <c r="L15" s="215"/>
-      <c r="M15" s="216"/>
+      <c r="J15" s="431"/>
+      <c r="K15" s="431"/>
+      <c r="L15" s="431"/>
+      <c r="M15" s="432"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="31"/>
+      <c r="A16" s="405"/>
       <c r="B16" s="31"/>
       <c r="C16" s="31"/>
       <c r="D16" s="31"/>
       <c r="E16" s="31"/>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="230" t="s">
+      <c r="H16" s="406"/>
+      <c r="I16" s="199" t="s">
         <v>81</v>
       </c>
-      <c r="J16" s="231"/>
-      <c r="K16" s="231"/>
-      <c r="L16" s="231"/>
-      <c r="M16" s="232"/>
+      <c r="J16" s="199"/>
+      <c r="K16" s="199"/>
+      <c r="L16" s="199"/>
+      <c r="M16" s="200"/>
     </row>
     <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="407" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="237"/>
-      <c r="G17" s="237"/>
-      <c r="H17" s="238"/>
-      <c r="I17" s="228"/>
-      <c r="J17" s="229"/>
-      <c r="K17" s="210" t="s">
+      <c r="B17" s="408"/>
+      <c r="C17" s="408"/>
+      <c r="D17" s="408"/>
+      <c r="E17" s="408"/>
+      <c r="F17" s="396"/>
+      <c r="G17" s="396"/>
+      <c r="H17" s="409"/>
+      <c r="I17" s="404"/>
+      <c r="J17" s="198"/>
+      <c r="K17" s="185" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="210"/>
-      <c r="M17" s="211"/>
+      <c r="L17" s="185"/>
+      <c r="M17" s="186"/>
     </row>
     <row r="18" spans="1:13" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="36"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="123" t="s">
+      <c r="A18" s="410"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="411"/>
+      <c r="I18" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="124"/>
-      <c r="K18" s="212"/>
-      <c r="L18" s="212"/>
-      <c r="M18" s="213"/>
+      <c r="J18" s="100"/>
+      <c r="K18" s="187"/>
+      <c r="L18" s="187"/>
+      <c r="M18" s="188"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="178" t="s">
+      <c r="A19" s="154" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="179"/>
-      <c r="C19" s="179"/>
-      <c r="D19" s="179"/>
-      <c r="E19" s="179"/>
-      <c r="F19" s="179"/>
-      <c r="G19" s="179"/>
-      <c r="H19" s="179"/>
-      <c r="I19" s="179"/>
-      <c r="J19" s="179"/>
-      <c r="K19" s="179"/>
-      <c r="L19" s="179"/>
-      <c r="M19" s="180"/>
+      <c r="B19" s="155"/>
+      <c r="C19" s="155"/>
+      <c r="D19" s="155"/>
+      <c r="E19" s="155"/>
+      <c r="F19" s="155"/>
+      <c r="G19" s="155"/>
+      <c r="H19" s="155"/>
+      <c r="I19" s="155"/>
+      <c r="J19" s="155"/>
+      <c r="K19" s="155"/>
+      <c r="L19" s="155"/>
+      <c r="M19" s="156"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="233" t="s">
+      <c r="A20" s="201" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="234"/>
-      <c r="C20" s="234"/>
-      <c r="D20" s="234"/>
-      <c r="E20" s="234" t="s">
+      <c r="B20" s="202"/>
+      <c r="C20" s="202"/>
+      <c r="D20" s="202"/>
+      <c r="E20" s="202" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="234" t="s">
+      <c r="F20" s="202" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="234"/>
-      <c r="H20" s="226" t="s">
+      <c r="G20" s="202"/>
+      <c r="H20" s="196" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="227"/>
-      <c r="J20" s="220" t="s">
+      <c r="I20" s="197"/>
+      <c r="J20" s="190" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="221"/>
-      <c r="L20" s="221"/>
-      <c r="M20" s="222"/>
+      <c r="K20" s="191"/>
+      <c r="L20" s="191"/>
+      <c r="M20" s="192"/>
     </row>
     <row r="21" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="233"/>
-      <c r="B21" s="234"/>
-      <c r="C21" s="234"/>
-      <c r="D21" s="234"/>
-      <c r="E21" s="234"/>
-      <c r="F21" s="234"/>
-      <c r="G21" s="234"/>
-      <c r="H21" s="261" t="s">
+      <c r="A21" s="201"/>
+      <c r="B21" s="202"/>
+      <c r="C21" s="202"/>
+      <c r="D21" s="202"/>
+      <c r="E21" s="202"/>
+      <c r="F21" s="202"/>
+      <c r="G21" s="202"/>
+      <c r="H21" s="210" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="262"/>
-      <c r="J21" s="223"/>
-      <c r="K21" s="224"/>
-      <c r="L21" s="224"/>
-      <c r="M21" s="225"/>
+      <c r="I21" s="211"/>
+      <c r="J21" s="193"/>
+      <c r="K21" s="194"/>
+      <c r="L21" s="194"/>
+      <c r="M21" s="195"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="235"/>
-      <c r="B22" s="184"/>
-      <c r="C22" s="184"/>
-      <c r="D22" s="161"/>
+      <c r="A22" s="203"/>
+      <c r="B22" s="160"/>
+      <c r="C22" s="160"/>
+      <c r="D22" s="137"/>
       <c r="E22" s="10"/>
-      <c r="F22" s="184"/>
-      <c r="G22" s="184"/>
+      <c r="F22" s="160"/>
+      <c r="G22" s="160"/>
       <c r="H22" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="184"/>
-      <c r="K22" s="184"/>
-      <c r="L22" s="184"/>
-      <c r="M22" s="196"/>
+      <c r="J22" s="160"/>
+      <c r="K22" s="160"/>
+      <c r="L22" s="160"/>
+      <c r="M22" s="172"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="199"/>
-      <c r="B23" s="200"/>
-      <c r="C23" s="200"/>
-      <c r="D23" s="201"/>
+      <c r="A23" s="175"/>
+      <c r="B23" s="176"/>
+      <c r="C23" s="176"/>
+      <c r="D23" s="177"/>
       <c r="E23" s="10"/>
-      <c r="F23" s="184"/>
-      <c r="G23" s="184"/>
+      <c r="F23" s="160"/>
+      <c r="G23" s="160"/>
       <c r="H23" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="184"/>
-      <c r="K23" s="184"/>
-      <c r="L23" s="184"/>
-      <c r="M23" s="196"/>
+      <c r="J23" s="160"/>
+      <c r="K23" s="160"/>
+      <c r="L23" s="160"/>
+      <c r="M23" s="172"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="199"/>
-      <c r="B24" s="200"/>
-      <c r="C24" s="200"/>
-      <c r="D24" s="201"/>
+      <c r="A24" s="175"/>
+      <c r="B24" s="176"/>
+      <c r="C24" s="176"/>
+      <c r="D24" s="177"/>
       <c r="E24" s="10"/>
-      <c r="F24" s="184"/>
-      <c r="G24" s="184"/>
+      <c r="F24" s="160"/>
+      <c r="G24" s="160"/>
       <c r="H24" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="184"/>
-      <c r="K24" s="184"/>
-      <c r="L24" s="184"/>
-      <c r="M24" s="196"/>
+      <c r="J24" s="160"/>
+      <c r="K24" s="160"/>
+      <c r="L24" s="160"/>
+      <c r="M24" s="172"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="199"/>
-      <c r="B25" s="200"/>
-      <c r="C25" s="200"/>
-      <c r="D25" s="201"/>
+      <c r="A25" s="175"/>
+      <c r="B25" s="176"/>
+      <c r="C25" s="176"/>
+      <c r="D25" s="177"/>
       <c r="E25" s="10"/>
-      <c r="F25" s="184"/>
-      <c r="G25" s="184"/>
+      <c r="F25" s="160"/>
+      <c r="G25" s="160"/>
       <c r="H25" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="184"/>
-      <c r="K25" s="184"/>
-      <c r="L25" s="184"/>
-      <c r="M25" s="196"/>
+      <c r="J25" s="160"/>
+      <c r="K25" s="160"/>
+      <c r="L25" s="160"/>
+      <c r="M25" s="172"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="199"/>
-      <c r="B26" s="200"/>
-      <c r="C26" s="200"/>
-      <c r="D26" s="201"/>
+      <c r="A26" s="175"/>
+      <c r="B26" s="176"/>
+      <c r="C26" s="176"/>
+      <c r="D26" s="177"/>
       <c r="E26" s="10"/>
-      <c r="F26" s="184"/>
-      <c r="G26" s="184"/>
+      <c r="F26" s="160"/>
+      <c r="G26" s="160"/>
       <c r="H26" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="184"/>
-      <c r="K26" s="184"/>
-      <c r="L26" s="184"/>
-      <c r="M26" s="196"/>
+      <c r="J26" s="160"/>
+      <c r="K26" s="160"/>
+      <c r="L26" s="160"/>
+      <c r="M26" s="172"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="199"/>
-      <c r="B27" s="200"/>
-      <c r="C27" s="200"/>
-      <c r="D27" s="201"/>
+      <c r="A27" s="175"/>
+      <c r="B27" s="176"/>
+      <c r="C27" s="176"/>
+      <c r="D27" s="177"/>
       <c r="E27" s="10"/>
-      <c r="F27" s="184"/>
-      <c r="G27" s="184"/>
+      <c r="F27" s="160"/>
+      <c r="G27" s="160"/>
       <c r="H27" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J27" s="184"/>
-      <c r="K27" s="184"/>
-      <c r="L27" s="184"/>
-      <c r="M27" s="196"/>
+      <c r="J27" s="160"/>
+      <c r="K27" s="160"/>
+      <c r="L27" s="160"/>
+      <c r="M27" s="172"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="199"/>
-      <c r="B28" s="200"/>
-      <c r="C28" s="200"/>
-      <c r="D28" s="201"/>
+      <c r="A28" s="175"/>
+      <c r="B28" s="176"/>
+      <c r="C28" s="176"/>
+      <c r="D28" s="177"/>
       <c r="E28" s="10"/>
-      <c r="F28" s="184"/>
-      <c r="G28" s="184"/>
+      <c r="F28" s="160"/>
+      <c r="G28" s="160"/>
       <c r="H28" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J28" s="184"/>
-      <c r="K28" s="184"/>
-      <c r="L28" s="184"/>
-      <c r="M28" s="196"/>
+      <c r="J28" s="160"/>
+      <c r="K28" s="160"/>
+      <c r="L28" s="160"/>
+      <c r="M28" s="172"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="199"/>
-      <c r="B29" s="200"/>
-      <c r="C29" s="200"/>
-      <c r="D29" s="201"/>
+      <c r="A29" s="175"/>
+      <c r="B29" s="176"/>
+      <c r="C29" s="176"/>
+      <c r="D29" s="177"/>
       <c r="E29" s="10"/>
-      <c r="F29" s="184"/>
-      <c r="G29" s="184"/>
+      <c r="F29" s="160"/>
+      <c r="G29" s="160"/>
       <c r="H29" s="10" t="s">
         <v>54</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J29" s="184"/>
-      <c r="K29" s="184"/>
-      <c r="L29" s="184"/>
-      <c r="M29" s="196"/>
+      <c r="J29" s="160"/>
+      <c r="K29" s="160"/>
+      <c r="L29" s="160"/>
+      <c r="M29" s="172"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="197" t="s">
+      <c r="A30" s="173" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="198"/>
-      <c r="C30" s="198"/>
-      <c r="D30" s="198"/>
+      <c r="B30" s="174"/>
+      <c r="C30" s="174"/>
+      <c r="D30" s="174"/>
       <c r="E30" s="9"/>
-      <c r="F30" s="185"/>
-      <c r="G30" s="184"/>
-      <c r="H30" s="202"/>
-      <c r="I30" s="204"/>
-      <c r="J30" s="202"/>
-      <c r="K30" s="203"/>
-      <c r="L30" s="203"/>
-      <c r="M30" s="204"/>
+      <c r="F30" s="161"/>
+      <c r="G30" s="160"/>
+      <c r="H30" s="178"/>
+      <c r="I30" s="180"/>
+      <c r="J30" s="178"/>
+      <c r="K30" s="179"/>
+      <c r="L30" s="179"/>
+      <c r="M30" s="180"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="186" t="s">
+      <c r="A31" s="162" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="187"/>
-      <c r="C31" s="187"/>
-      <c r="D31" s="187"/>
-      <c r="E31" s="187"/>
-      <c r="F31" s="187"/>
-      <c r="G31" s="187"/>
-      <c r="H31" s="187"/>
-      <c r="I31" s="187"/>
-      <c r="J31" s="187"/>
-      <c r="K31" s="187"/>
-      <c r="L31" s="187"/>
-      <c r="M31" s="188"/>
+      <c r="B31" s="163"/>
+      <c r="C31" s="163"/>
+      <c r="D31" s="163"/>
+      <c r="E31" s="163"/>
+      <c r="F31" s="163"/>
+      <c r="G31" s="163"/>
+      <c r="H31" s="163"/>
+      <c r="I31" s="163"/>
+      <c r="J31" s="163"/>
+      <c r="K31" s="163"/>
+      <c r="L31" s="163"/>
+      <c r="M31" s="164"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="193" t="s">
+      <c r="A32" s="169" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="191"/>
-      <c r="C32" s="191" t="s">
+      <c r="B32" s="167"/>
+      <c r="C32" s="167" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="191"/>
-      <c r="E32" s="194" t="s">
+      <c r="D32" s="167"/>
+      <c r="E32" s="170" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="195" t="s">
+      <c r="F32" s="171" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="189" t="s">
+      <c r="G32" s="165" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="189"/>
-      <c r="I32" s="189"/>
-      <c r="J32" s="189"/>
-      <c r="K32" s="189"/>
-      <c r="L32" s="191" t="s">
+      <c r="H32" s="165"/>
+      <c r="I32" s="165"/>
+      <c r="J32" s="165"/>
+      <c r="K32" s="165"/>
+      <c r="L32" s="167" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="192"/>
+      <c r="M32" s="168"/>
     </row>
     <row r="33" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
@@ -8210,15 +8156,15 @@
       <c r="D33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="194"/>
-      <c r="F33" s="195"/>
-      <c r="G33" s="190" t="s">
+      <c r="E33" s="170"/>
+      <c r="F33" s="171"/>
+      <c r="G33" s="166" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="190"/>
-      <c r="I33" s="190"/>
-      <c r="J33" s="190"/>
-      <c r="K33" s="190"/>
+      <c r="H33" s="166"/>
+      <c r="I33" s="166"/>
+      <c r="J33" s="166"/>
+      <c r="K33" s="166"/>
       <c r="L33" s="2" t="s">
         <v>14</v>
       </c>
@@ -8227,447 +8173,447 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="66"/>
+      <c r="A34" s="42"/>
       <c r="B34" s="10" t="s">
         <v>60</v>
       </c>
       <c r="C34" s="9"/>
-      <c r="D34" s="65" t="s">
+      <c r="D34" s="41" t="s">
         <v>60</v>
       </c>
       <c r="E34" s="9"/>
       <c r="F34" s="10"/>
-      <c r="G34" s="161" t="s">
+      <c r="G34" s="137" t="s">
         <v>74</v>
       </c>
-      <c r="H34" s="162"/>
-      <c r="I34" s="162"/>
-      <c r="J34" s="162"/>
-      <c r="K34" s="163"/>
-      <c r="L34" s="67"/>
-      <c r="M34" s="68"/>
+      <c r="H34" s="138"/>
+      <c r="I34" s="138"/>
+      <c r="J34" s="138"/>
+      <c r="K34" s="139"/>
+      <c r="L34" s="43"/>
+      <c r="M34" s="44"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" s="69"/>
+      <c r="A35" s="45"/>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
-      <c r="F35" s="67"/>
-      <c r="G35" s="161"/>
-      <c r="H35" s="162"/>
-      <c r="I35" s="162"/>
-      <c r="J35" s="162"/>
-      <c r="K35" s="163"/>
-      <c r="L35" s="67"/>
-      <c r="M35" s="68"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="137"/>
+      <c r="H35" s="138"/>
+      <c r="I35" s="138"/>
+      <c r="J35" s="138"/>
+      <c r="K35" s="139"/>
+      <c r="L35" s="43"/>
+      <c r="M35" s="44"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" s="69"/>
+      <c r="A36" s="45"/>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="161"/>
-      <c r="H36" s="162"/>
-      <c r="I36" s="162"/>
-      <c r="J36" s="162"/>
-      <c r="K36" s="163"/>
-      <c r="L36" s="67"/>
-      <c r="M36" s="68"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="137"/>
+      <c r="H36" s="138"/>
+      <c r="I36" s="138"/>
+      <c r="J36" s="138"/>
+      <c r="K36" s="139"/>
+      <c r="L36" s="43"/>
+      <c r="M36" s="44"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A37" s="69"/>
+      <c r="A37" s="45"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
-      <c r="F37" s="67"/>
-      <c r="G37" s="161"/>
-      <c r="H37" s="162"/>
-      <c r="I37" s="162"/>
-      <c r="J37" s="162"/>
-      <c r="K37" s="163"/>
-      <c r="L37" s="67"/>
-      <c r="M37" s="68"/>
-      <c r="Q37" s="152"/>
-      <c r="R37" s="152"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="137"/>
+      <c r="H37" s="138"/>
+      <c r="I37" s="138"/>
+      <c r="J37" s="138"/>
+      <c r="K37" s="139"/>
+      <c r="L37" s="43"/>
+      <c r="M37" s="44"/>
+      <c r="Q37" s="128"/>
+      <c r="R37" s="128"/>
       <c r="S37" s="7"/>
-      <c r="T37" s="129"/>
-      <c r="U37" s="129"/>
-      <c r="V37" s="129"/>
+      <c r="T37" s="105"/>
+      <c r="U37" s="105"/>
+      <c r="V37" s="105"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A38" s="69"/>
+      <c r="A38" s="45"/>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="161"/>
-      <c r="H38" s="162"/>
-      <c r="I38" s="162"/>
-      <c r="J38" s="162"/>
-      <c r="K38" s="163"/>
-      <c r="L38" s="67"/>
-      <c r="M38" s="70"/>
-      <c r="Q38" s="152"/>
-      <c r="R38" s="152"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="137"/>
+      <c r="H38" s="138"/>
+      <c r="I38" s="138"/>
+      <c r="J38" s="138"/>
+      <c r="K38" s="139"/>
+      <c r="L38" s="43"/>
+      <c r="M38" s="46"/>
+      <c r="Q38" s="128"/>
+      <c r="R38" s="128"/>
       <c r="S38" s="7"/>
-      <c r="T38" s="129"/>
-      <c r="U38" s="129"/>
-      <c r="V38" s="129"/>
+      <c r="T38" s="105"/>
+      <c r="U38" s="105"/>
+      <c r="V38" s="105"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A39" s="69"/>
+      <c r="A39" s="45"/>
       <c r="B39" s="10"/>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="161"/>
-      <c r="H39" s="162"/>
-      <c r="I39" s="162"/>
-      <c r="J39" s="162"/>
-      <c r="K39" s="163"/>
-      <c r="L39" s="67"/>
-      <c r="M39" s="70"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="137"/>
+      <c r="H39" s="138"/>
+      <c r="I39" s="138"/>
+      <c r="J39" s="138"/>
+      <c r="K39" s="139"/>
+      <c r="L39" s="43"/>
+      <c r="M39" s="46"/>
       <c r="Q39" s="6"/>
       <c r="R39" s="6"/>
-      <c r="S39" s="155"/>
-      <c r="T39" s="129"/>
-      <c r="U39" s="129"/>
-      <c r="V39" s="129"/>
+      <c r="S39" s="131"/>
+      <c r="T39" s="105"/>
+      <c r="U39" s="105"/>
+      <c r="V39" s="105"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A40" s="69"/>
+      <c r="A40" s="45"/>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
       <c r="D40" s="10"/>
       <c r="E40" s="10"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="161"/>
-      <c r="H40" s="162"/>
-      <c r="I40" s="162"/>
-      <c r="J40" s="162"/>
-      <c r="K40" s="163"/>
-      <c r="L40" s="67"/>
-      <c r="M40" s="68"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="137"/>
+      <c r="H40" s="138"/>
+      <c r="I40" s="138"/>
+      <c r="J40" s="138"/>
+      <c r="K40" s="139"/>
+      <c r="L40" s="43"/>
+      <c r="M40" s="44"/>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
-      <c r="S40" s="155"/>
-      <c r="T40" s="129"/>
-      <c r="U40" s="129"/>
-      <c r="V40" s="129"/>
+      <c r="S40" s="131"/>
+      <c r="T40" s="105"/>
+      <c r="U40" s="105"/>
+      <c r="V40" s="105"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A41" s="69"/>
+      <c r="A41" s="45"/>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
       <c r="D41" s="10"/>
       <c r="E41" s="10"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="161"/>
-      <c r="H41" s="162"/>
-      <c r="I41" s="162"/>
-      <c r="J41" s="162"/>
-      <c r="K41" s="163"/>
-      <c r="L41" s="67"/>
-      <c r="M41" s="68"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="137"/>
+      <c r="H41" s="138"/>
+      <c r="I41" s="138"/>
+      <c r="J41" s="138"/>
+      <c r="K41" s="139"/>
+      <c r="L41" s="43"/>
+      <c r="M41" s="44"/>
     </row>
     <row r="42" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="71"/>
-      <c r="B42" s="72"/>
-      <c r="C42" s="73"/>
-      <c r="D42" s="72"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="74"/>
-      <c r="G42" s="164" t="s">
+      <c r="A42" s="47"/>
+      <c r="B42" s="48"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="48"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="50"/>
+      <c r="G42" s="140" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="165"/>
-      <c r="I42" s="165"/>
-      <c r="J42" s="165"/>
-      <c r="K42" s="166"/>
-      <c r="L42" s="74"/>
-      <c r="M42" s="75"/>
+      <c r="H42" s="141"/>
+      <c r="I42" s="141"/>
+      <c r="J42" s="141"/>
+      <c r="K42" s="142"/>
+      <c r="L42" s="50"/>
+      <c r="M42" s="51"/>
     </row>
     <row r="43" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="131" t="s">
+      <c r="A43" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="132"/>
-      <c r="C43" s="132"/>
-      <c r="D43" s="132"/>
-      <c r="E43" s="132"/>
-      <c r="F43" s="132"/>
-      <c r="G43" s="132"/>
-      <c r="H43" s="133"/>
-      <c r="I43" s="175" t="s">
+      <c r="B43" s="108"/>
+      <c r="C43" s="108"/>
+      <c r="D43" s="108"/>
+      <c r="E43" s="108"/>
+      <c r="F43" s="108"/>
+      <c r="G43" s="108"/>
+      <c r="H43" s="109"/>
+      <c r="I43" s="151" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="176"/>
-      <c r="K43" s="176"/>
-      <c r="L43" s="176"/>
-      <c r="M43" s="177"/>
+      <c r="J43" s="152"/>
+      <c r="K43" s="152"/>
+      <c r="L43" s="152"/>
+      <c r="M43" s="153"/>
     </row>
     <row r="44" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="134"/>
-      <c r="B44" s="135"/>
-      <c r="C44" s="135"/>
-      <c r="D44" s="135"/>
-      <c r="E44" s="135"/>
-      <c r="F44" s="135"/>
-      <c r="G44" s="135"/>
-      <c r="H44" s="136"/>
-      <c r="I44" s="178"/>
-      <c r="J44" s="179"/>
-      <c r="K44" s="179"/>
-      <c r="L44" s="179"/>
-      <c r="M44" s="180"/>
+      <c r="A44" s="110"/>
+      <c r="B44" s="111"/>
+      <c r="C44" s="111"/>
+      <c r="D44" s="111"/>
+      <c r="E44" s="111"/>
+      <c r="F44" s="111"/>
+      <c r="G44" s="111"/>
+      <c r="H44" s="112"/>
+      <c r="I44" s="154"/>
+      <c r="J44" s="155"/>
+      <c r="K44" s="155"/>
+      <c r="L44" s="155"/>
+      <c r="M44" s="156"/>
     </row>
     <row r="45" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="137" t="s">
+      <c r="A45" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="138"/>
-      <c r="C45" s="138"/>
-      <c r="D45" s="138"/>
-      <c r="E45" s="138"/>
-      <c r="F45" s="138"/>
-      <c r="G45" s="138"/>
-      <c r="H45" s="139"/>
-      <c r="I45" s="181" t="s">
+      <c r="B45" s="114"/>
+      <c r="C45" s="114"/>
+      <c r="D45" s="114"/>
+      <c r="E45" s="114"/>
+      <c r="F45" s="114"/>
+      <c r="G45" s="114"/>
+      <c r="H45" s="115"/>
+      <c r="I45" s="157" t="s">
         <v>36</v>
       </c>
-      <c r="J45" s="182"/>
-      <c r="K45" s="182"/>
-      <c r="L45" s="182"/>
-      <c r="M45" s="183"/>
+      <c r="J45" s="158"/>
+      <c r="K45" s="158"/>
+      <c r="L45" s="158"/>
+      <c r="M45" s="159"/>
     </row>
     <row r="46" spans="1:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="137" t="s">
+      <c r="A46" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="138"/>
-      <c r="C46" s="138"/>
-      <c r="D46" s="138"/>
-      <c r="E46" s="138"/>
-      <c r="F46" s="138"/>
-      <c r="G46" s="138"/>
-      <c r="H46" s="139"/>
-      <c r="I46" s="181"/>
-      <c r="J46" s="182"/>
-      <c r="K46" s="182"/>
-      <c r="L46" s="182"/>
-      <c r="M46" s="183"/>
+      <c r="B46" s="114"/>
+      <c r="C46" s="114"/>
+      <c r="D46" s="114"/>
+      <c r="E46" s="114"/>
+      <c r="F46" s="114"/>
+      <c r="G46" s="114"/>
+      <c r="H46" s="115"/>
+      <c r="I46" s="157"/>
+      <c r="J46" s="158"/>
+      <c r="K46" s="158"/>
+      <c r="L46" s="158"/>
+      <c r="M46" s="159"/>
     </row>
     <row r="47" spans="1:22" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="140"/>
-      <c r="B47" s="141"/>
-      <c r="C47" s="141"/>
-      <c r="D47" s="141"/>
-      <c r="E47" s="141"/>
-      <c r="F47" s="141"/>
-      <c r="G47" s="141"/>
-      <c r="H47" s="142"/>
-      <c r="I47" s="126" t="s">
+      <c r="A47" s="116"/>
+      <c r="B47" s="117"/>
+      <c r="C47" s="117"/>
+      <c r="D47" s="117"/>
+      <c r="E47" s="117"/>
+      <c r="F47" s="117"/>
+      <c r="G47" s="117"/>
+      <c r="H47" s="118"/>
+      <c r="I47" s="102" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="127"/>
-      <c r="K47" s="127"/>
-      <c r="L47" s="127"/>
-      <c r="M47" s="128"/>
+      <c r="J47" s="103"/>
+      <c r="K47" s="103"/>
+      <c r="L47" s="103"/>
+      <c r="M47" s="104"/>
     </row>
     <row r="48" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="147" t="s">
+      <c r="A48" s="123" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="148"/>
-      <c r="C48" s="148"/>
-      <c r="D48" s="148"/>
-      <c r="E48" s="148"/>
-      <c r="F48" s="148"/>
-      <c r="G48" s="148"/>
-      <c r="H48" s="148"/>
-      <c r="I48" s="148"/>
-      <c r="J48" s="148"/>
-      <c r="K48" s="148"/>
-      <c r="L48" s="148"/>
-      <c r="M48" s="156"/>
+      <c r="B48" s="124"/>
+      <c r="C48" s="124"/>
+      <c r="D48" s="124"/>
+      <c r="E48" s="124"/>
+      <c r="F48" s="124"/>
+      <c r="G48" s="124"/>
+      <c r="H48" s="124"/>
+      <c r="I48" s="124"/>
+      <c r="J48" s="124"/>
+      <c r="K48" s="124"/>
+      <c r="L48" s="124"/>
+      <c r="M48" s="132"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="131" t="s">
+      <c r="A49" s="107" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="132"/>
-      <c r="C49" s="132"/>
-      <c r="D49" s="132"/>
-      <c r="E49" s="132"/>
-      <c r="F49" s="132"/>
-      <c r="G49" s="132"/>
-      <c r="H49" s="133"/>
-      <c r="I49" s="167" t="s">
+      <c r="B49" s="108"/>
+      <c r="C49" s="108"/>
+      <c r="D49" s="108"/>
+      <c r="E49" s="108"/>
+      <c r="F49" s="108"/>
+      <c r="G49" s="108"/>
+      <c r="H49" s="109"/>
+      <c r="I49" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="J49" s="168"/>
-      <c r="K49" s="168"/>
-      <c r="L49" s="168"/>
-      <c r="M49" s="169"/>
+      <c r="J49" s="144"/>
+      <c r="K49" s="144"/>
+      <c r="L49" s="144"/>
+      <c r="M49" s="145"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="134"/>
-      <c r="B50" s="135"/>
-      <c r="C50" s="135"/>
-      <c r="D50" s="135"/>
-      <c r="E50" s="135"/>
-      <c r="F50" s="135"/>
-      <c r="G50" s="135"/>
-      <c r="H50" s="136"/>
-      <c r="I50" s="170"/>
-      <c r="J50" s="171"/>
-      <c r="K50" s="171"/>
-      <c r="L50" s="171"/>
-      <c r="M50" s="172"/>
+      <c r="A50" s="110"/>
+      <c r="B50" s="111"/>
+      <c r="C50" s="111"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="111"/>
+      <c r="F50" s="111"/>
+      <c r="G50" s="111"/>
+      <c r="H50" s="112"/>
+      <c r="I50" s="146"/>
+      <c r="J50" s="147"/>
+      <c r="K50" s="147"/>
+      <c r="L50" s="147"/>
+      <c r="M50" s="148"/>
     </row>
     <row r="51" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="173"/>
-      <c r="B51" s="174"/>
-      <c r="C51" s="174"/>
-      <c r="D51" s="174"/>
-      <c r="E51" s="135"/>
-      <c r="F51" s="135"/>
-      <c r="G51" s="135"/>
-      <c r="H51" s="136"/>
-      <c r="I51" s="143" t="s">
+      <c r="A51" s="149"/>
+      <c r="B51" s="150"/>
+      <c r="C51" s="150"/>
+      <c r="D51" s="150"/>
+      <c r="E51" s="111"/>
+      <c r="F51" s="111"/>
+      <c r="G51" s="111"/>
+      <c r="H51" s="112"/>
+      <c r="I51" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="J51" s="144"/>
-      <c r="K51" s="145"/>
-      <c r="L51" s="145"/>
-      <c r="M51" s="146"/>
+      <c r="J51" s="120"/>
+      <c r="K51" s="121"/>
+      <c r="L51" s="121"/>
+      <c r="M51" s="122"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="147" t="s">
+      <c r="A52" s="123" t="s">
         <v>42</v>
       </c>
-      <c r="B52" s="148"/>
-      <c r="C52" s="148"/>
-      <c r="D52" s="148"/>
-      <c r="E52" s="76" t="s">
+      <c r="B52" s="124"/>
+      <c r="C52" s="124"/>
+      <c r="D52" s="124"/>
+      <c r="E52" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="F52" s="77"/>
-      <c r="G52" s="153" t="s">
+      <c r="F52" s="53"/>
+      <c r="G52" s="129" t="s">
         <v>45</v>
       </c>
-      <c r="H52" s="153"/>
-      <c r="I52" s="153"/>
-      <c r="J52" s="154"/>
-      <c r="K52" s="148" t="s">
+      <c r="H52" s="129"/>
+      <c r="I52" s="129"/>
+      <c r="J52" s="130"/>
+      <c r="K52" s="124" t="s">
         <v>50</v>
       </c>
-      <c r="L52" s="148"/>
-      <c r="M52" s="156"/>
+      <c r="L52" s="124"/>
+      <c r="M52" s="132"/>
     </row>
     <row r="53" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="149" t="s">
+      <c r="A53" s="125" t="s">
         <v>43</v>
       </c>
-      <c r="B53" s="150"/>
-      <c r="C53" s="150"/>
-      <c r="D53" s="150"/>
-      <c r="E53" s="59"/>
-      <c r="J53" s="56"/>
-      <c r="K53" s="157" t="s">
+      <c r="B53" s="126"/>
+      <c r="C53" s="126"/>
+      <c r="D53" s="126"/>
+      <c r="E53" s="40"/>
+      <c r="J53" s="38"/>
+      <c r="K53" s="133" t="s">
         <v>52</v>
       </c>
-      <c r="L53" s="157"/>
-      <c r="M53" s="158"/>
+      <c r="L53" s="133"/>
+      <c r="M53" s="134"/>
     </row>
     <row r="54" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="149"/>
-      <c r="B54" s="150"/>
-      <c r="C54" s="150"/>
-      <c r="D54" s="150"/>
-      <c r="E54" s="151" t="s">
+      <c r="A54" s="125"/>
+      <c r="B54" s="126"/>
+      <c r="C54" s="126"/>
+      <c r="D54" s="126"/>
+      <c r="E54" s="127" t="s">
         <v>46</v>
       </c>
-      <c r="F54" s="152"/>
+      <c r="F54" s="128"/>
       <c r="G54" s="7"/>
-      <c r="H54" s="129" t="s">
+      <c r="H54" s="105" t="s">
         <v>46</v>
       </c>
-      <c r="I54" s="129"/>
-      <c r="J54" s="130"/>
-      <c r="K54" s="157"/>
-      <c r="L54" s="157"/>
-      <c r="M54" s="158"/>
+      <c r="I54" s="105"/>
+      <c r="J54" s="106"/>
+      <c r="K54" s="133"/>
+      <c r="L54" s="133"/>
+      <c r="M54" s="134"/>
     </row>
     <row r="55" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="149"/>
-      <c r="B55" s="150"/>
-      <c r="C55" s="150"/>
-      <c r="D55" s="150"/>
-      <c r="E55" s="151" t="s">
+      <c r="A55" s="125"/>
+      <c r="B55" s="126"/>
+      <c r="C55" s="126"/>
+      <c r="D55" s="126"/>
+      <c r="E55" s="127" t="s">
         <v>47</v>
       </c>
-      <c r="F55" s="152"/>
-      <c r="G55" s="152"/>
-      <c r="H55" s="129" t="s">
+      <c r="F55" s="128"/>
+      <c r="G55" s="128"/>
+      <c r="H55" s="105" t="s">
         <v>48</v>
       </c>
-      <c r="I55" s="129"/>
-      <c r="J55" s="130"/>
-      <c r="K55" s="157"/>
-      <c r="L55" s="157"/>
-      <c r="M55" s="158"/>
+      <c r="I55" s="105"/>
+      <c r="J55" s="106"/>
+      <c r="K55" s="133"/>
+      <c r="L55" s="133"/>
+      <c r="M55" s="134"/>
     </row>
     <row r="56" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="59"/>
-      <c r="D56" s="56"/>
-      <c r="E56" s="151"/>
-      <c r="F56" s="152"/>
-      <c r="G56" s="152"/>
-      <c r="H56" s="129"/>
-      <c r="I56" s="129"/>
-      <c r="J56" s="130"/>
-      <c r="K56" s="159" t="s">
+      <c r="A56" s="40"/>
+      <c r="D56" s="38"/>
+      <c r="E56" s="127"/>
+      <c r="F56" s="128"/>
+      <c r="G56" s="128"/>
+      <c r="H56" s="105"/>
+      <c r="I56" s="105"/>
+      <c r="J56" s="106"/>
+      <c r="K56" s="135" t="s">
         <v>51</v>
       </c>
-      <c r="L56" s="159"/>
-      <c r="M56" s="160"/>
+      <c r="L56" s="135"/>
+      <c r="M56" s="136"/>
     </row>
     <row r="57" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="59"/>
-      <c r="D57" s="56"/>
-      <c r="E57" s="151"/>
-      <c r="F57" s="152"/>
+      <c r="A57" s="40"/>
+      <c r="D57" s="38"/>
+      <c r="E57" s="127"/>
+      <c r="F57" s="128"/>
       <c r="G57" s="7"/>
-      <c r="H57" s="129" t="s">
+      <c r="H57" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="I57" s="129"/>
-      <c r="J57" s="130"/>
-      <c r="K57" s="78"/>
-      <c r="L57" s="79"/>
-      <c r="M57" s="80"/>
+      <c r="I57" s="105"/>
+      <c r="J57" s="106"/>
+      <c r="K57" s="54"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="56"/>
     </row>
     <row r="58" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="81"/>
-      <c r="B58" s="242"/>
-      <c r="C58" s="242"/>
-      <c r="D58" s="48"/>
-      <c r="E58" s="123"/>
-      <c r="F58" s="124"/>
-      <c r="G58" s="124"/>
-      <c r="H58" s="124"/>
-      <c r="I58" s="124"/>
-      <c r="J58" s="125"/>
-      <c r="K58" s="82"/>
-      <c r="L58" s="83"/>
-      <c r="M58" s="84"/>
+      <c r="A58" s="57"/>
+      <c r="B58" s="205"/>
+      <c r="C58" s="205"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="99"/>
+      <c r="F58" s="100"/>
+      <c r="G58" s="100"/>
+      <c r="H58" s="100"/>
+      <c r="I58" s="100"/>
+      <c r="J58" s="101"/>
+      <c r="K58" s="58"/>
+      <c r="L58" s="59"/>
+      <c r="M58" s="60"/>
     </row>
     <row r="59" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3"/>

--- a/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
+++ b/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Procomm\Documents\GitHub\Acumatica_Customizations_and_Packages\Istar_Development\Projects\BOL_Generation\Code\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC6B49A3-2085-4DF2-A6B3-2CB1712A114E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D1FD027-D5F0-4466-A1F9-03A693F9CFF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{888CA347-7849-4038-B8EE-FAC87BA1B844}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{888CA347-7849-4038-B8EE-FAC87BA1B844}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterBOL" sheetId="3" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="83">
   <si>
     <t>SHIP FROM</t>
   </si>
@@ -5068,7 +5068,9 @@
       <c r="A34" s="83"/>
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
-      <c r="D34" s="80"/>
+      <c r="D34" s="80" t="s">
+        <v>60</v>
+      </c>
       <c r="E34" s="81"/>
       <c r="F34" s="80"/>
       <c r="G34" s="283"/>

--- a/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
+++ b/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Procomm\Documents\GitHub\Acumatica_Customizations_and_Packages\Istar_Development\Projects\BOL_Generation\Code\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D1FD027-D5F0-4466-A1F9-03A693F9CFF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA7C347-158B-4B80-944E-214BB7ADA40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{888CA347-7849-4038-B8EE-FAC87BA1B844}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{888CA347-7849-4038-B8EE-FAC87BA1B844}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterBOL" sheetId="3" r:id="rId1"/>
@@ -494,7 +494,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -907,12 +907,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="438">
+  <cellXfs count="441">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -925,9 +947,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -997,11 +1016,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1012,26 +1029,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
@@ -1123,9 +1130,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1144,18 +1148,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1168,16 +1166,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1189,9 +1178,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1207,21 +1193,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1246,18 +1217,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1270,27 +1232,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1298,12 +1245,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1315,9 +1256,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1327,9 +1265,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1363,21 +1298,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1387,31 +1310,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1422,9 +1333,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="18" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2064,12 +1972,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2079,6 +1981,133 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3725,1803 +3754,1803 @@
   <dimension ref="A1:V59"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="4" width="7.42578125" style="11" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="11"/>
-    <col min="6" max="6" width="5.5703125" style="11" customWidth="1"/>
-    <col min="7" max="7" width="3.5703125" style="11" customWidth="1"/>
-    <col min="8" max="8" width="5.140625" style="11" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" style="11" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="11"/>
-    <col min="11" max="11" width="17.140625" style="11" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" style="11"/>
-    <col min="13" max="13" width="9" style="11" customWidth="1"/>
-    <col min="14" max="256" width="9.140625" style="11"/>
-    <col min="257" max="260" width="7.42578125" style="11" customWidth="1"/>
-    <col min="261" max="261" width="9.140625" style="11"/>
-    <col min="262" max="262" width="5.5703125" style="11" customWidth="1"/>
-    <col min="263" max="263" width="3.5703125" style="11" customWidth="1"/>
-    <col min="264" max="264" width="5.140625" style="11" customWidth="1"/>
-    <col min="265" max="265" width="5.42578125" style="11" customWidth="1"/>
-    <col min="266" max="266" width="9.140625" style="11"/>
-    <col min="267" max="267" width="17.140625" style="11" customWidth="1"/>
-    <col min="268" max="268" width="9.140625" style="11"/>
-    <col min="269" max="269" width="9" style="11" customWidth="1"/>
-    <col min="270" max="512" width="9.140625" style="11"/>
-    <col min="513" max="516" width="7.42578125" style="11" customWidth="1"/>
-    <col min="517" max="517" width="9.140625" style="11"/>
-    <col min="518" max="518" width="5.5703125" style="11" customWidth="1"/>
-    <col min="519" max="519" width="3.5703125" style="11" customWidth="1"/>
-    <col min="520" max="520" width="5.140625" style="11" customWidth="1"/>
-    <col min="521" max="521" width="5.42578125" style="11" customWidth="1"/>
-    <col min="522" max="522" width="9.140625" style="11"/>
-    <col min="523" max="523" width="17.140625" style="11" customWidth="1"/>
-    <col min="524" max="524" width="9.140625" style="11"/>
-    <col min="525" max="525" width="9" style="11" customWidth="1"/>
-    <col min="526" max="768" width="9.140625" style="11"/>
-    <col min="769" max="772" width="7.42578125" style="11" customWidth="1"/>
-    <col min="773" max="773" width="9.140625" style="11"/>
-    <col min="774" max="774" width="5.5703125" style="11" customWidth="1"/>
-    <col min="775" max="775" width="3.5703125" style="11" customWidth="1"/>
-    <col min="776" max="776" width="5.140625" style="11" customWidth="1"/>
-    <col min="777" max="777" width="5.42578125" style="11" customWidth="1"/>
-    <col min="778" max="778" width="9.140625" style="11"/>
-    <col min="779" max="779" width="17.140625" style="11" customWidth="1"/>
-    <col min="780" max="780" width="9.140625" style="11"/>
-    <col min="781" max="781" width="9" style="11" customWidth="1"/>
-    <col min="782" max="1024" width="9.140625" style="11"/>
-    <col min="1025" max="1028" width="7.42578125" style="11" customWidth="1"/>
-    <col min="1029" max="1029" width="9.140625" style="11"/>
-    <col min="1030" max="1030" width="5.5703125" style="11" customWidth="1"/>
-    <col min="1031" max="1031" width="3.5703125" style="11" customWidth="1"/>
-    <col min="1032" max="1032" width="5.140625" style="11" customWidth="1"/>
-    <col min="1033" max="1033" width="5.42578125" style="11" customWidth="1"/>
-    <col min="1034" max="1034" width="9.140625" style="11"/>
-    <col min="1035" max="1035" width="17.140625" style="11" customWidth="1"/>
-    <col min="1036" max="1036" width="9.140625" style="11"/>
-    <col min="1037" max="1037" width="9" style="11" customWidth="1"/>
-    <col min="1038" max="1280" width="9.140625" style="11"/>
-    <col min="1281" max="1284" width="7.42578125" style="11" customWidth="1"/>
-    <col min="1285" max="1285" width="9.140625" style="11"/>
-    <col min="1286" max="1286" width="5.5703125" style="11" customWidth="1"/>
-    <col min="1287" max="1287" width="3.5703125" style="11" customWidth="1"/>
-    <col min="1288" max="1288" width="5.140625" style="11" customWidth="1"/>
-    <col min="1289" max="1289" width="5.42578125" style="11" customWidth="1"/>
-    <col min="1290" max="1290" width="9.140625" style="11"/>
-    <col min="1291" max="1291" width="17.140625" style="11" customWidth="1"/>
-    <col min="1292" max="1292" width="9.140625" style="11"/>
-    <col min="1293" max="1293" width="9" style="11" customWidth="1"/>
-    <col min="1294" max="1536" width="9.140625" style="11"/>
-    <col min="1537" max="1540" width="7.42578125" style="11" customWidth="1"/>
-    <col min="1541" max="1541" width="9.140625" style="11"/>
-    <col min="1542" max="1542" width="5.5703125" style="11" customWidth="1"/>
-    <col min="1543" max="1543" width="3.5703125" style="11" customWidth="1"/>
-    <col min="1544" max="1544" width="5.140625" style="11" customWidth="1"/>
-    <col min="1545" max="1545" width="5.42578125" style="11" customWidth="1"/>
-    <col min="1546" max="1546" width="9.140625" style="11"/>
-    <col min="1547" max="1547" width="17.140625" style="11" customWidth="1"/>
-    <col min="1548" max="1548" width="9.140625" style="11"/>
-    <col min="1549" max="1549" width="9" style="11" customWidth="1"/>
-    <col min="1550" max="1792" width="9.140625" style="11"/>
-    <col min="1793" max="1796" width="7.42578125" style="11" customWidth="1"/>
-    <col min="1797" max="1797" width="9.140625" style="11"/>
-    <col min="1798" max="1798" width="5.5703125" style="11" customWidth="1"/>
-    <col min="1799" max="1799" width="3.5703125" style="11" customWidth="1"/>
-    <col min="1800" max="1800" width="5.140625" style="11" customWidth="1"/>
-    <col min="1801" max="1801" width="5.42578125" style="11" customWidth="1"/>
-    <col min="1802" max="1802" width="9.140625" style="11"/>
-    <col min="1803" max="1803" width="17.140625" style="11" customWidth="1"/>
-    <col min="1804" max="1804" width="9.140625" style="11"/>
-    <col min="1805" max="1805" width="9" style="11" customWidth="1"/>
-    <col min="1806" max="2048" width="9.140625" style="11"/>
-    <col min="2049" max="2052" width="7.42578125" style="11" customWidth="1"/>
-    <col min="2053" max="2053" width="9.140625" style="11"/>
-    <col min="2054" max="2054" width="5.5703125" style="11" customWidth="1"/>
-    <col min="2055" max="2055" width="3.5703125" style="11" customWidth="1"/>
-    <col min="2056" max="2056" width="5.140625" style="11" customWidth="1"/>
-    <col min="2057" max="2057" width="5.42578125" style="11" customWidth="1"/>
-    <col min="2058" max="2058" width="9.140625" style="11"/>
-    <col min="2059" max="2059" width="17.140625" style="11" customWidth="1"/>
-    <col min="2060" max="2060" width="9.140625" style="11"/>
-    <col min="2061" max="2061" width="9" style="11" customWidth="1"/>
-    <col min="2062" max="2304" width="9.140625" style="11"/>
-    <col min="2305" max="2308" width="7.42578125" style="11" customWidth="1"/>
-    <col min="2309" max="2309" width="9.140625" style="11"/>
-    <col min="2310" max="2310" width="5.5703125" style="11" customWidth="1"/>
-    <col min="2311" max="2311" width="3.5703125" style="11" customWidth="1"/>
-    <col min="2312" max="2312" width="5.140625" style="11" customWidth="1"/>
-    <col min="2313" max="2313" width="5.42578125" style="11" customWidth="1"/>
-    <col min="2314" max="2314" width="9.140625" style="11"/>
-    <col min="2315" max="2315" width="17.140625" style="11" customWidth="1"/>
-    <col min="2316" max="2316" width="9.140625" style="11"/>
-    <col min="2317" max="2317" width="9" style="11" customWidth="1"/>
-    <col min="2318" max="2560" width="9.140625" style="11"/>
-    <col min="2561" max="2564" width="7.42578125" style="11" customWidth="1"/>
-    <col min="2565" max="2565" width="9.140625" style="11"/>
-    <col min="2566" max="2566" width="5.5703125" style="11" customWidth="1"/>
-    <col min="2567" max="2567" width="3.5703125" style="11" customWidth="1"/>
-    <col min="2568" max="2568" width="5.140625" style="11" customWidth="1"/>
-    <col min="2569" max="2569" width="5.42578125" style="11" customWidth="1"/>
-    <col min="2570" max="2570" width="9.140625" style="11"/>
-    <col min="2571" max="2571" width="17.140625" style="11" customWidth="1"/>
-    <col min="2572" max="2572" width="9.140625" style="11"/>
-    <col min="2573" max="2573" width="9" style="11" customWidth="1"/>
-    <col min="2574" max="2816" width="9.140625" style="11"/>
-    <col min="2817" max="2820" width="7.42578125" style="11" customWidth="1"/>
-    <col min="2821" max="2821" width="9.140625" style="11"/>
-    <col min="2822" max="2822" width="5.5703125" style="11" customWidth="1"/>
-    <col min="2823" max="2823" width="3.5703125" style="11" customWidth="1"/>
-    <col min="2824" max="2824" width="5.140625" style="11" customWidth="1"/>
-    <col min="2825" max="2825" width="5.42578125" style="11" customWidth="1"/>
-    <col min="2826" max="2826" width="9.140625" style="11"/>
-    <col min="2827" max="2827" width="17.140625" style="11" customWidth="1"/>
-    <col min="2828" max="2828" width="9.140625" style="11"/>
-    <col min="2829" max="2829" width="9" style="11" customWidth="1"/>
-    <col min="2830" max="3072" width="9.140625" style="11"/>
-    <col min="3073" max="3076" width="7.42578125" style="11" customWidth="1"/>
-    <col min="3077" max="3077" width="9.140625" style="11"/>
-    <col min="3078" max="3078" width="5.5703125" style="11" customWidth="1"/>
-    <col min="3079" max="3079" width="3.5703125" style="11" customWidth="1"/>
-    <col min="3080" max="3080" width="5.140625" style="11" customWidth="1"/>
-    <col min="3081" max="3081" width="5.42578125" style="11" customWidth="1"/>
-    <col min="3082" max="3082" width="9.140625" style="11"/>
-    <col min="3083" max="3083" width="17.140625" style="11" customWidth="1"/>
-    <col min="3084" max="3084" width="9.140625" style="11"/>
-    <col min="3085" max="3085" width="9" style="11" customWidth="1"/>
-    <col min="3086" max="3328" width="9.140625" style="11"/>
-    <col min="3329" max="3332" width="7.42578125" style="11" customWidth="1"/>
-    <col min="3333" max="3333" width="9.140625" style="11"/>
-    <col min="3334" max="3334" width="5.5703125" style="11" customWidth="1"/>
-    <col min="3335" max="3335" width="3.5703125" style="11" customWidth="1"/>
-    <col min="3336" max="3336" width="5.140625" style="11" customWidth="1"/>
-    <col min="3337" max="3337" width="5.42578125" style="11" customWidth="1"/>
-    <col min="3338" max="3338" width="9.140625" style="11"/>
-    <col min="3339" max="3339" width="17.140625" style="11" customWidth="1"/>
-    <col min="3340" max="3340" width="9.140625" style="11"/>
-    <col min="3341" max="3341" width="9" style="11" customWidth="1"/>
-    <col min="3342" max="3584" width="9.140625" style="11"/>
-    <col min="3585" max="3588" width="7.42578125" style="11" customWidth="1"/>
-    <col min="3589" max="3589" width="9.140625" style="11"/>
-    <col min="3590" max="3590" width="5.5703125" style="11" customWidth="1"/>
-    <col min="3591" max="3591" width="3.5703125" style="11" customWidth="1"/>
-    <col min="3592" max="3592" width="5.140625" style="11" customWidth="1"/>
-    <col min="3593" max="3593" width="5.42578125" style="11" customWidth="1"/>
-    <col min="3594" max="3594" width="9.140625" style="11"/>
-    <col min="3595" max="3595" width="17.140625" style="11" customWidth="1"/>
-    <col min="3596" max="3596" width="9.140625" style="11"/>
-    <col min="3597" max="3597" width="9" style="11" customWidth="1"/>
-    <col min="3598" max="3840" width="9.140625" style="11"/>
-    <col min="3841" max="3844" width="7.42578125" style="11" customWidth="1"/>
-    <col min="3845" max="3845" width="9.140625" style="11"/>
-    <col min="3846" max="3846" width="5.5703125" style="11" customWidth="1"/>
-    <col min="3847" max="3847" width="3.5703125" style="11" customWidth="1"/>
-    <col min="3848" max="3848" width="5.140625" style="11" customWidth="1"/>
-    <col min="3849" max="3849" width="5.42578125" style="11" customWidth="1"/>
-    <col min="3850" max="3850" width="9.140625" style="11"/>
-    <col min="3851" max="3851" width="17.140625" style="11" customWidth="1"/>
-    <col min="3852" max="3852" width="9.140625" style="11"/>
-    <col min="3853" max="3853" width="9" style="11" customWidth="1"/>
-    <col min="3854" max="4096" width="9.140625" style="11"/>
-    <col min="4097" max="4100" width="7.42578125" style="11" customWidth="1"/>
-    <col min="4101" max="4101" width="9.140625" style="11"/>
-    <col min="4102" max="4102" width="5.5703125" style="11" customWidth="1"/>
-    <col min="4103" max="4103" width="3.5703125" style="11" customWidth="1"/>
-    <col min="4104" max="4104" width="5.140625" style="11" customWidth="1"/>
-    <col min="4105" max="4105" width="5.42578125" style="11" customWidth="1"/>
-    <col min="4106" max="4106" width="9.140625" style="11"/>
-    <col min="4107" max="4107" width="17.140625" style="11" customWidth="1"/>
-    <col min="4108" max="4108" width="9.140625" style="11"/>
-    <col min="4109" max="4109" width="9" style="11" customWidth="1"/>
-    <col min="4110" max="4352" width="9.140625" style="11"/>
-    <col min="4353" max="4356" width="7.42578125" style="11" customWidth="1"/>
-    <col min="4357" max="4357" width="9.140625" style="11"/>
-    <col min="4358" max="4358" width="5.5703125" style="11" customWidth="1"/>
-    <col min="4359" max="4359" width="3.5703125" style="11" customWidth="1"/>
-    <col min="4360" max="4360" width="5.140625" style="11" customWidth="1"/>
-    <col min="4361" max="4361" width="5.42578125" style="11" customWidth="1"/>
-    <col min="4362" max="4362" width="9.140625" style="11"/>
-    <col min="4363" max="4363" width="17.140625" style="11" customWidth="1"/>
-    <col min="4364" max="4364" width="9.140625" style="11"/>
-    <col min="4365" max="4365" width="9" style="11" customWidth="1"/>
-    <col min="4366" max="4608" width="9.140625" style="11"/>
-    <col min="4609" max="4612" width="7.42578125" style="11" customWidth="1"/>
-    <col min="4613" max="4613" width="9.140625" style="11"/>
-    <col min="4614" max="4614" width="5.5703125" style="11" customWidth="1"/>
-    <col min="4615" max="4615" width="3.5703125" style="11" customWidth="1"/>
-    <col min="4616" max="4616" width="5.140625" style="11" customWidth="1"/>
-    <col min="4617" max="4617" width="5.42578125" style="11" customWidth="1"/>
-    <col min="4618" max="4618" width="9.140625" style="11"/>
-    <col min="4619" max="4619" width="17.140625" style="11" customWidth="1"/>
-    <col min="4620" max="4620" width="9.140625" style="11"/>
-    <col min="4621" max="4621" width="9" style="11" customWidth="1"/>
-    <col min="4622" max="4864" width="9.140625" style="11"/>
-    <col min="4865" max="4868" width="7.42578125" style="11" customWidth="1"/>
-    <col min="4869" max="4869" width="9.140625" style="11"/>
-    <col min="4870" max="4870" width="5.5703125" style="11" customWidth="1"/>
-    <col min="4871" max="4871" width="3.5703125" style="11" customWidth="1"/>
-    <col min="4872" max="4872" width="5.140625" style="11" customWidth="1"/>
-    <col min="4873" max="4873" width="5.42578125" style="11" customWidth="1"/>
-    <col min="4874" max="4874" width="9.140625" style="11"/>
-    <col min="4875" max="4875" width="17.140625" style="11" customWidth="1"/>
-    <col min="4876" max="4876" width="9.140625" style="11"/>
-    <col min="4877" max="4877" width="9" style="11" customWidth="1"/>
-    <col min="4878" max="5120" width="9.140625" style="11"/>
-    <col min="5121" max="5124" width="7.42578125" style="11" customWidth="1"/>
-    <col min="5125" max="5125" width="9.140625" style="11"/>
-    <col min="5126" max="5126" width="5.5703125" style="11" customWidth="1"/>
-    <col min="5127" max="5127" width="3.5703125" style="11" customWidth="1"/>
-    <col min="5128" max="5128" width="5.140625" style="11" customWidth="1"/>
-    <col min="5129" max="5129" width="5.42578125" style="11" customWidth="1"/>
-    <col min="5130" max="5130" width="9.140625" style="11"/>
-    <col min="5131" max="5131" width="17.140625" style="11" customWidth="1"/>
-    <col min="5132" max="5132" width="9.140625" style="11"/>
-    <col min="5133" max="5133" width="9" style="11" customWidth="1"/>
-    <col min="5134" max="5376" width="9.140625" style="11"/>
-    <col min="5377" max="5380" width="7.42578125" style="11" customWidth="1"/>
-    <col min="5381" max="5381" width="9.140625" style="11"/>
-    <col min="5382" max="5382" width="5.5703125" style="11" customWidth="1"/>
-    <col min="5383" max="5383" width="3.5703125" style="11" customWidth="1"/>
-    <col min="5384" max="5384" width="5.140625" style="11" customWidth="1"/>
-    <col min="5385" max="5385" width="5.42578125" style="11" customWidth="1"/>
-    <col min="5386" max="5386" width="9.140625" style="11"/>
-    <col min="5387" max="5387" width="17.140625" style="11" customWidth="1"/>
-    <col min="5388" max="5388" width="9.140625" style="11"/>
-    <col min="5389" max="5389" width="9" style="11" customWidth="1"/>
-    <col min="5390" max="5632" width="9.140625" style="11"/>
-    <col min="5633" max="5636" width="7.42578125" style="11" customWidth="1"/>
-    <col min="5637" max="5637" width="9.140625" style="11"/>
-    <col min="5638" max="5638" width="5.5703125" style="11" customWidth="1"/>
-    <col min="5639" max="5639" width="3.5703125" style="11" customWidth="1"/>
-    <col min="5640" max="5640" width="5.140625" style="11" customWidth="1"/>
-    <col min="5641" max="5641" width="5.42578125" style="11" customWidth="1"/>
-    <col min="5642" max="5642" width="9.140625" style="11"/>
-    <col min="5643" max="5643" width="17.140625" style="11" customWidth="1"/>
-    <col min="5644" max="5644" width="9.140625" style="11"/>
-    <col min="5645" max="5645" width="9" style="11" customWidth="1"/>
-    <col min="5646" max="5888" width="9.140625" style="11"/>
-    <col min="5889" max="5892" width="7.42578125" style="11" customWidth="1"/>
-    <col min="5893" max="5893" width="9.140625" style="11"/>
-    <col min="5894" max="5894" width="5.5703125" style="11" customWidth="1"/>
-    <col min="5895" max="5895" width="3.5703125" style="11" customWidth="1"/>
-    <col min="5896" max="5896" width="5.140625" style="11" customWidth="1"/>
-    <col min="5897" max="5897" width="5.42578125" style="11" customWidth="1"/>
-    <col min="5898" max="5898" width="9.140625" style="11"/>
-    <col min="5899" max="5899" width="17.140625" style="11" customWidth="1"/>
-    <col min="5900" max="5900" width="9.140625" style="11"/>
-    <col min="5901" max="5901" width="9" style="11" customWidth="1"/>
-    <col min="5902" max="6144" width="9.140625" style="11"/>
-    <col min="6145" max="6148" width="7.42578125" style="11" customWidth="1"/>
-    <col min="6149" max="6149" width="9.140625" style="11"/>
-    <col min="6150" max="6150" width="5.5703125" style="11" customWidth="1"/>
-    <col min="6151" max="6151" width="3.5703125" style="11" customWidth="1"/>
-    <col min="6152" max="6152" width="5.140625" style="11" customWidth="1"/>
-    <col min="6153" max="6153" width="5.42578125" style="11" customWidth="1"/>
-    <col min="6154" max="6154" width="9.140625" style="11"/>
-    <col min="6155" max="6155" width="17.140625" style="11" customWidth="1"/>
-    <col min="6156" max="6156" width="9.140625" style="11"/>
-    <col min="6157" max="6157" width="9" style="11" customWidth="1"/>
-    <col min="6158" max="6400" width="9.140625" style="11"/>
-    <col min="6401" max="6404" width="7.42578125" style="11" customWidth="1"/>
-    <col min="6405" max="6405" width="9.140625" style="11"/>
-    <col min="6406" max="6406" width="5.5703125" style="11" customWidth="1"/>
-    <col min="6407" max="6407" width="3.5703125" style="11" customWidth="1"/>
-    <col min="6408" max="6408" width="5.140625" style="11" customWidth="1"/>
-    <col min="6409" max="6409" width="5.42578125" style="11" customWidth="1"/>
-    <col min="6410" max="6410" width="9.140625" style="11"/>
-    <col min="6411" max="6411" width="17.140625" style="11" customWidth="1"/>
-    <col min="6412" max="6412" width="9.140625" style="11"/>
-    <col min="6413" max="6413" width="9" style="11" customWidth="1"/>
-    <col min="6414" max="6656" width="9.140625" style="11"/>
-    <col min="6657" max="6660" width="7.42578125" style="11" customWidth="1"/>
-    <col min="6661" max="6661" width="9.140625" style="11"/>
-    <col min="6662" max="6662" width="5.5703125" style="11" customWidth="1"/>
-    <col min="6663" max="6663" width="3.5703125" style="11" customWidth="1"/>
-    <col min="6664" max="6664" width="5.140625" style="11" customWidth="1"/>
-    <col min="6665" max="6665" width="5.42578125" style="11" customWidth="1"/>
-    <col min="6666" max="6666" width="9.140625" style="11"/>
-    <col min="6667" max="6667" width="17.140625" style="11" customWidth="1"/>
-    <col min="6668" max="6668" width="9.140625" style="11"/>
-    <col min="6669" max="6669" width="9" style="11" customWidth="1"/>
-    <col min="6670" max="6912" width="9.140625" style="11"/>
-    <col min="6913" max="6916" width="7.42578125" style="11" customWidth="1"/>
-    <col min="6917" max="6917" width="9.140625" style="11"/>
-    <col min="6918" max="6918" width="5.5703125" style="11" customWidth="1"/>
-    <col min="6919" max="6919" width="3.5703125" style="11" customWidth="1"/>
-    <col min="6920" max="6920" width="5.140625" style="11" customWidth="1"/>
-    <col min="6921" max="6921" width="5.42578125" style="11" customWidth="1"/>
-    <col min="6922" max="6922" width="9.140625" style="11"/>
-    <col min="6923" max="6923" width="17.140625" style="11" customWidth="1"/>
-    <col min="6924" max="6924" width="9.140625" style="11"/>
-    <col min="6925" max="6925" width="9" style="11" customWidth="1"/>
-    <col min="6926" max="7168" width="9.140625" style="11"/>
-    <col min="7169" max="7172" width="7.42578125" style="11" customWidth="1"/>
-    <col min="7173" max="7173" width="9.140625" style="11"/>
-    <col min="7174" max="7174" width="5.5703125" style="11" customWidth="1"/>
-    <col min="7175" max="7175" width="3.5703125" style="11" customWidth="1"/>
-    <col min="7176" max="7176" width="5.140625" style="11" customWidth="1"/>
-    <col min="7177" max="7177" width="5.42578125" style="11" customWidth="1"/>
-    <col min="7178" max="7178" width="9.140625" style="11"/>
-    <col min="7179" max="7179" width="17.140625" style="11" customWidth="1"/>
-    <col min="7180" max="7180" width="9.140625" style="11"/>
-    <col min="7181" max="7181" width="9" style="11" customWidth="1"/>
-    <col min="7182" max="7424" width="9.140625" style="11"/>
-    <col min="7425" max="7428" width="7.42578125" style="11" customWidth="1"/>
-    <col min="7429" max="7429" width="9.140625" style="11"/>
-    <col min="7430" max="7430" width="5.5703125" style="11" customWidth="1"/>
-    <col min="7431" max="7431" width="3.5703125" style="11" customWidth="1"/>
-    <col min="7432" max="7432" width="5.140625" style="11" customWidth="1"/>
-    <col min="7433" max="7433" width="5.42578125" style="11" customWidth="1"/>
-    <col min="7434" max="7434" width="9.140625" style="11"/>
-    <col min="7435" max="7435" width="17.140625" style="11" customWidth="1"/>
-    <col min="7436" max="7436" width="9.140625" style="11"/>
-    <col min="7437" max="7437" width="9" style="11" customWidth="1"/>
-    <col min="7438" max="7680" width="9.140625" style="11"/>
-    <col min="7681" max="7684" width="7.42578125" style="11" customWidth="1"/>
-    <col min="7685" max="7685" width="9.140625" style="11"/>
-    <col min="7686" max="7686" width="5.5703125" style="11" customWidth="1"/>
-    <col min="7687" max="7687" width="3.5703125" style="11" customWidth="1"/>
-    <col min="7688" max="7688" width="5.140625" style="11" customWidth="1"/>
-    <col min="7689" max="7689" width="5.42578125" style="11" customWidth="1"/>
-    <col min="7690" max="7690" width="9.140625" style="11"/>
-    <col min="7691" max="7691" width="17.140625" style="11" customWidth="1"/>
-    <col min="7692" max="7692" width="9.140625" style="11"/>
-    <col min="7693" max="7693" width="9" style="11" customWidth="1"/>
-    <col min="7694" max="7936" width="9.140625" style="11"/>
-    <col min="7937" max="7940" width="7.42578125" style="11" customWidth="1"/>
-    <col min="7941" max="7941" width="9.140625" style="11"/>
-    <col min="7942" max="7942" width="5.5703125" style="11" customWidth="1"/>
-    <col min="7943" max="7943" width="3.5703125" style="11" customWidth="1"/>
-    <col min="7944" max="7944" width="5.140625" style="11" customWidth="1"/>
-    <col min="7945" max="7945" width="5.42578125" style="11" customWidth="1"/>
-    <col min="7946" max="7946" width="9.140625" style="11"/>
-    <col min="7947" max="7947" width="17.140625" style="11" customWidth="1"/>
-    <col min="7948" max="7948" width="9.140625" style="11"/>
-    <col min="7949" max="7949" width="9" style="11" customWidth="1"/>
-    <col min="7950" max="8192" width="9.140625" style="11"/>
-    <col min="8193" max="8196" width="7.42578125" style="11" customWidth="1"/>
-    <col min="8197" max="8197" width="9.140625" style="11"/>
-    <col min="8198" max="8198" width="5.5703125" style="11" customWidth="1"/>
-    <col min="8199" max="8199" width="3.5703125" style="11" customWidth="1"/>
-    <col min="8200" max="8200" width="5.140625" style="11" customWidth="1"/>
-    <col min="8201" max="8201" width="5.42578125" style="11" customWidth="1"/>
-    <col min="8202" max="8202" width="9.140625" style="11"/>
-    <col min="8203" max="8203" width="17.140625" style="11" customWidth="1"/>
-    <col min="8204" max="8204" width="9.140625" style="11"/>
-    <col min="8205" max="8205" width="9" style="11" customWidth="1"/>
-    <col min="8206" max="8448" width="9.140625" style="11"/>
-    <col min="8449" max="8452" width="7.42578125" style="11" customWidth="1"/>
-    <col min="8453" max="8453" width="9.140625" style="11"/>
-    <col min="8454" max="8454" width="5.5703125" style="11" customWidth="1"/>
-    <col min="8455" max="8455" width="3.5703125" style="11" customWidth="1"/>
-    <col min="8456" max="8456" width="5.140625" style="11" customWidth="1"/>
-    <col min="8457" max="8457" width="5.42578125" style="11" customWidth="1"/>
-    <col min="8458" max="8458" width="9.140625" style="11"/>
-    <col min="8459" max="8459" width="17.140625" style="11" customWidth="1"/>
-    <col min="8460" max="8460" width="9.140625" style="11"/>
-    <col min="8461" max="8461" width="9" style="11" customWidth="1"/>
-    <col min="8462" max="8704" width="9.140625" style="11"/>
-    <col min="8705" max="8708" width="7.42578125" style="11" customWidth="1"/>
-    <col min="8709" max="8709" width="9.140625" style="11"/>
-    <col min="8710" max="8710" width="5.5703125" style="11" customWidth="1"/>
-    <col min="8711" max="8711" width="3.5703125" style="11" customWidth="1"/>
-    <col min="8712" max="8712" width="5.140625" style="11" customWidth="1"/>
-    <col min="8713" max="8713" width="5.42578125" style="11" customWidth="1"/>
-    <col min="8714" max="8714" width="9.140625" style="11"/>
-    <col min="8715" max="8715" width="17.140625" style="11" customWidth="1"/>
-    <col min="8716" max="8716" width="9.140625" style="11"/>
-    <col min="8717" max="8717" width="9" style="11" customWidth="1"/>
-    <col min="8718" max="8960" width="9.140625" style="11"/>
-    <col min="8961" max="8964" width="7.42578125" style="11" customWidth="1"/>
-    <col min="8965" max="8965" width="9.140625" style="11"/>
-    <col min="8966" max="8966" width="5.5703125" style="11" customWidth="1"/>
-    <col min="8967" max="8967" width="3.5703125" style="11" customWidth="1"/>
-    <col min="8968" max="8968" width="5.140625" style="11" customWidth="1"/>
-    <col min="8969" max="8969" width="5.42578125" style="11" customWidth="1"/>
-    <col min="8970" max="8970" width="9.140625" style="11"/>
-    <col min="8971" max="8971" width="17.140625" style="11" customWidth="1"/>
-    <col min="8972" max="8972" width="9.140625" style="11"/>
-    <col min="8973" max="8973" width="9" style="11" customWidth="1"/>
-    <col min="8974" max="9216" width="9.140625" style="11"/>
-    <col min="9217" max="9220" width="7.42578125" style="11" customWidth="1"/>
-    <col min="9221" max="9221" width="9.140625" style="11"/>
-    <col min="9222" max="9222" width="5.5703125" style="11" customWidth="1"/>
-    <col min="9223" max="9223" width="3.5703125" style="11" customWidth="1"/>
-    <col min="9224" max="9224" width="5.140625" style="11" customWidth="1"/>
-    <col min="9225" max="9225" width="5.42578125" style="11" customWidth="1"/>
-    <col min="9226" max="9226" width="9.140625" style="11"/>
-    <col min="9227" max="9227" width="17.140625" style="11" customWidth="1"/>
-    <col min="9228" max="9228" width="9.140625" style="11"/>
-    <col min="9229" max="9229" width="9" style="11" customWidth="1"/>
-    <col min="9230" max="9472" width="9.140625" style="11"/>
-    <col min="9473" max="9476" width="7.42578125" style="11" customWidth="1"/>
-    <col min="9477" max="9477" width="9.140625" style="11"/>
-    <col min="9478" max="9478" width="5.5703125" style="11" customWidth="1"/>
-    <col min="9479" max="9479" width="3.5703125" style="11" customWidth="1"/>
-    <col min="9480" max="9480" width="5.140625" style="11" customWidth="1"/>
-    <col min="9481" max="9481" width="5.42578125" style="11" customWidth="1"/>
-    <col min="9482" max="9482" width="9.140625" style="11"/>
-    <col min="9483" max="9483" width="17.140625" style="11" customWidth="1"/>
-    <col min="9484" max="9484" width="9.140625" style="11"/>
-    <col min="9485" max="9485" width="9" style="11" customWidth="1"/>
-    <col min="9486" max="9728" width="9.140625" style="11"/>
-    <col min="9729" max="9732" width="7.42578125" style="11" customWidth="1"/>
-    <col min="9733" max="9733" width="9.140625" style="11"/>
-    <col min="9734" max="9734" width="5.5703125" style="11" customWidth="1"/>
-    <col min="9735" max="9735" width="3.5703125" style="11" customWidth="1"/>
-    <col min="9736" max="9736" width="5.140625" style="11" customWidth="1"/>
-    <col min="9737" max="9737" width="5.42578125" style="11" customWidth="1"/>
-    <col min="9738" max="9738" width="9.140625" style="11"/>
-    <col min="9739" max="9739" width="17.140625" style="11" customWidth="1"/>
-    <col min="9740" max="9740" width="9.140625" style="11"/>
-    <col min="9741" max="9741" width="9" style="11" customWidth="1"/>
-    <col min="9742" max="9984" width="9.140625" style="11"/>
-    <col min="9985" max="9988" width="7.42578125" style="11" customWidth="1"/>
-    <col min="9989" max="9989" width="9.140625" style="11"/>
-    <col min="9990" max="9990" width="5.5703125" style="11" customWidth="1"/>
-    <col min="9991" max="9991" width="3.5703125" style="11" customWidth="1"/>
-    <col min="9992" max="9992" width="5.140625" style="11" customWidth="1"/>
-    <col min="9993" max="9993" width="5.42578125" style="11" customWidth="1"/>
-    <col min="9994" max="9994" width="9.140625" style="11"/>
-    <col min="9995" max="9995" width="17.140625" style="11" customWidth="1"/>
-    <col min="9996" max="9996" width="9.140625" style="11"/>
-    <col min="9997" max="9997" width="9" style="11" customWidth="1"/>
-    <col min="9998" max="10240" width="9.140625" style="11"/>
-    <col min="10241" max="10244" width="7.42578125" style="11" customWidth="1"/>
-    <col min="10245" max="10245" width="9.140625" style="11"/>
-    <col min="10246" max="10246" width="5.5703125" style="11" customWidth="1"/>
-    <col min="10247" max="10247" width="3.5703125" style="11" customWidth="1"/>
-    <col min="10248" max="10248" width="5.140625" style="11" customWidth="1"/>
-    <col min="10249" max="10249" width="5.42578125" style="11" customWidth="1"/>
-    <col min="10250" max="10250" width="9.140625" style="11"/>
-    <col min="10251" max="10251" width="17.140625" style="11" customWidth="1"/>
-    <col min="10252" max="10252" width="9.140625" style="11"/>
-    <col min="10253" max="10253" width="9" style="11" customWidth="1"/>
-    <col min="10254" max="10496" width="9.140625" style="11"/>
-    <col min="10497" max="10500" width="7.42578125" style="11" customWidth="1"/>
-    <col min="10501" max="10501" width="9.140625" style="11"/>
-    <col min="10502" max="10502" width="5.5703125" style="11" customWidth="1"/>
-    <col min="10503" max="10503" width="3.5703125" style="11" customWidth="1"/>
-    <col min="10504" max="10504" width="5.140625" style="11" customWidth="1"/>
-    <col min="10505" max="10505" width="5.42578125" style="11" customWidth="1"/>
-    <col min="10506" max="10506" width="9.140625" style="11"/>
-    <col min="10507" max="10507" width="17.140625" style="11" customWidth="1"/>
-    <col min="10508" max="10508" width="9.140625" style="11"/>
-    <col min="10509" max="10509" width="9" style="11" customWidth="1"/>
-    <col min="10510" max="10752" width="9.140625" style="11"/>
-    <col min="10753" max="10756" width="7.42578125" style="11" customWidth="1"/>
-    <col min="10757" max="10757" width="9.140625" style="11"/>
-    <col min="10758" max="10758" width="5.5703125" style="11" customWidth="1"/>
-    <col min="10759" max="10759" width="3.5703125" style="11" customWidth="1"/>
-    <col min="10760" max="10760" width="5.140625" style="11" customWidth="1"/>
-    <col min="10761" max="10761" width="5.42578125" style="11" customWidth="1"/>
-    <col min="10762" max="10762" width="9.140625" style="11"/>
-    <col min="10763" max="10763" width="17.140625" style="11" customWidth="1"/>
-    <col min="10764" max="10764" width="9.140625" style="11"/>
-    <col min="10765" max="10765" width="9" style="11" customWidth="1"/>
-    <col min="10766" max="11008" width="9.140625" style="11"/>
-    <col min="11009" max="11012" width="7.42578125" style="11" customWidth="1"/>
-    <col min="11013" max="11013" width="9.140625" style="11"/>
-    <col min="11014" max="11014" width="5.5703125" style="11" customWidth="1"/>
-    <col min="11015" max="11015" width="3.5703125" style="11" customWidth="1"/>
-    <col min="11016" max="11016" width="5.140625" style="11" customWidth="1"/>
-    <col min="11017" max="11017" width="5.42578125" style="11" customWidth="1"/>
-    <col min="11018" max="11018" width="9.140625" style="11"/>
-    <col min="11019" max="11019" width="17.140625" style="11" customWidth="1"/>
-    <col min="11020" max="11020" width="9.140625" style="11"/>
-    <col min="11021" max="11021" width="9" style="11" customWidth="1"/>
-    <col min="11022" max="11264" width="9.140625" style="11"/>
-    <col min="11265" max="11268" width="7.42578125" style="11" customWidth="1"/>
-    <col min="11269" max="11269" width="9.140625" style="11"/>
-    <col min="11270" max="11270" width="5.5703125" style="11" customWidth="1"/>
-    <col min="11271" max="11271" width="3.5703125" style="11" customWidth="1"/>
-    <col min="11272" max="11272" width="5.140625" style="11" customWidth="1"/>
-    <col min="11273" max="11273" width="5.42578125" style="11" customWidth="1"/>
-    <col min="11274" max="11274" width="9.140625" style="11"/>
-    <col min="11275" max="11275" width="17.140625" style="11" customWidth="1"/>
-    <col min="11276" max="11276" width="9.140625" style="11"/>
-    <col min="11277" max="11277" width="9" style="11" customWidth="1"/>
-    <col min="11278" max="11520" width="9.140625" style="11"/>
-    <col min="11521" max="11524" width="7.42578125" style="11" customWidth="1"/>
-    <col min="11525" max="11525" width="9.140625" style="11"/>
-    <col min="11526" max="11526" width="5.5703125" style="11" customWidth="1"/>
-    <col min="11527" max="11527" width="3.5703125" style="11" customWidth="1"/>
-    <col min="11528" max="11528" width="5.140625" style="11" customWidth="1"/>
-    <col min="11529" max="11529" width="5.42578125" style="11" customWidth="1"/>
-    <col min="11530" max="11530" width="9.140625" style="11"/>
-    <col min="11531" max="11531" width="17.140625" style="11" customWidth="1"/>
-    <col min="11532" max="11532" width="9.140625" style="11"/>
-    <col min="11533" max="11533" width="9" style="11" customWidth="1"/>
-    <col min="11534" max="11776" width="9.140625" style="11"/>
-    <col min="11777" max="11780" width="7.42578125" style="11" customWidth="1"/>
-    <col min="11781" max="11781" width="9.140625" style="11"/>
-    <col min="11782" max="11782" width="5.5703125" style="11" customWidth="1"/>
-    <col min="11783" max="11783" width="3.5703125" style="11" customWidth="1"/>
-    <col min="11784" max="11784" width="5.140625" style="11" customWidth="1"/>
-    <col min="11785" max="11785" width="5.42578125" style="11" customWidth="1"/>
-    <col min="11786" max="11786" width="9.140625" style="11"/>
-    <col min="11787" max="11787" width="17.140625" style="11" customWidth="1"/>
-    <col min="11788" max="11788" width="9.140625" style="11"/>
-    <col min="11789" max="11789" width="9" style="11" customWidth="1"/>
-    <col min="11790" max="12032" width="9.140625" style="11"/>
-    <col min="12033" max="12036" width="7.42578125" style="11" customWidth="1"/>
-    <col min="12037" max="12037" width="9.140625" style="11"/>
-    <col min="12038" max="12038" width="5.5703125" style="11" customWidth="1"/>
-    <col min="12039" max="12039" width="3.5703125" style="11" customWidth="1"/>
-    <col min="12040" max="12040" width="5.140625" style="11" customWidth="1"/>
-    <col min="12041" max="12041" width="5.42578125" style="11" customWidth="1"/>
-    <col min="12042" max="12042" width="9.140625" style="11"/>
-    <col min="12043" max="12043" width="17.140625" style="11" customWidth="1"/>
-    <col min="12044" max="12044" width="9.140625" style="11"/>
-    <col min="12045" max="12045" width="9" style="11" customWidth="1"/>
-    <col min="12046" max="12288" width="9.140625" style="11"/>
-    <col min="12289" max="12292" width="7.42578125" style="11" customWidth="1"/>
-    <col min="12293" max="12293" width="9.140625" style="11"/>
-    <col min="12294" max="12294" width="5.5703125" style="11" customWidth="1"/>
-    <col min="12295" max="12295" width="3.5703125" style="11" customWidth="1"/>
-    <col min="12296" max="12296" width="5.140625" style="11" customWidth="1"/>
-    <col min="12297" max="12297" width="5.42578125" style="11" customWidth="1"/>
-    <col min="12298" max="12298" width="9.140625" style="11"/>
-    <col min="12299" max="12299" width="17.140625" style="11" customWidth="1"/>
-    <col min="12300" max="12300" width="9.140625" style="11"/>
-    <col min="12301" max="12301" width="9" style="11" customWidth="1"/>
-    <col min="12302" max="12544" width="9.140625" style="11"/>
-    <col min="12545" max="12548" width="7.42578125" style="11" customWidth="1"/>
-    <col min="12549" max="12549" width="9.140625" style="11"/>
-    <col min="12550" max="12550" width="5.5703125" style="11" customWidth="1"/>
-    <col min="12551" max="12551" width="3.5703125" style="11" customWidth="1"/>
-    <col min="12552" max="12552" width="5.140625" style="11" customWidth="1"/>
-    <col min="12553" max="12553" width="5.42578125" style="11" customWidth="1"/>
-    <col min="12554" max="12554" width="9.140625" style="11"/>
-    <col min="12555" max="12555" width="17.140625" style="11" customWidth="1"/>
-    <col min="12556" max="12556" width="9.140625" style="11"/>
-    <col min="12557" max="12557" width="9" style="11" customWidth="1"/>
-    <col min="12558" max="12800" width="9.140625" style="11"/>
-    <col min="12801" max="12804" width="7.42578125" style="11" customWidth="1"/>
-    <col min="12805" max="12805" width="9.140625" style="11"/>
-    <col min="12806" max="12806" width="5.5703125" style="11" customWidth="1"/>
-    <col min="12807" max="12807" width="3.5703125" style="11" customWidth="1"/>
-    <col min="12808" max="12808" width="5.140625" style="11" customWidth="1"/>
-    <col min="12809" max="12809" width="5.42578125" style="11" customWidth="1"/>
-    <col min="12810" max="12810" width="9.140625" style="11"/>
-    <col min="12811" max="12811" width="17.140625" style="11" customWidth="1"/>
-    <col min="12812" max="12812" width="9.140625" style="11"/>
-    <col min="12813" max="12813" width="9" style="11" customWidth="1"/>
-    <col min="12814" max="13056" width="9.140625" style="11"/>
-    <col min="13057" max="13060" width="7.42578125" style="11" customWidth="1"/>
-    <col min="13061" max="13061" width="9.140625" style="11"/>
-    <col min="13062" max="13062" width="5.5703125" style="11" customWidth="1"/>
-    <col min="13063" max="13063" width="3.5703125" style="11" customWidth="1"/>
-    <col min="13064" max="13064" width="5.140625" style="11" customWidth="1"/>
-    <col min="13065" max="13065" width="5.42578125" style="11" customWidth="1"/>
-    <col min="13066" max="13066" width="9.140625" style="11"/>
-    <col min="13067" max="13067" width="17.140625" style="11" customWidth="1"/>
-    <col min="13068" max="13068" width="9.140625" style="11"/>
-    <col min="13069" max="13069" width="9" style="11" customWidth="1"/>
-    <col min="13070" max="13312" width="9.140625" style="11"/>
-    <col min="13313" max="13316" width="7.42578125" style="11" customWidth="1"/>
-    <col min="13317" max="13317" width="9.140625" style="11"/>
-    <col min="13318" max="13318" width="5.5703125" style="11" customWidth="1"/>
-    <col min="13319" max="13319" width="3.5703125" style="11" customWidth="1"/>
-    <col min="13320" max="13320" width="5.140625" style="11" customWidth="1"/>
-    <col min="13321" max="13321" width="5.42578125" style="11" customWidth="1"/>
-    <col min="13322" max="13322" width="9.140625" style="11"/>
-    <col min="13323" max="13323" width="17.140625" style="11" customWidth="1"/>
-    <col min="13324" max="13324" width="9.140625" style="11"/>
-    <col min="13325" max="13325" width="9" style="11" customWidth="1"/>
-    <col min="13326" max="13568" width="9.140625" style="11"/>
-    <col min="13569" max="13572" width="7.42578125" style="11" customWidth="1"/>
-    <col min="13573" max="13573" width="9.140625" style="11"/>
-    <col min="13574" max="13574" width="5.5703125" style="11" customWidth="1"/>
-    <col min="13575" max="13575" width="3.5703125" style="11" customWidth="1"/>
-    <col min="13576" max="13576" width="5.140625" style="11" customWidth="1"/>
-    <col min="13577" max="13577" width="5.42578125" style="11" customWidth="1"/>
-    <col min="13578" max="13578" width="9.140625" style="11"/>
-    <col min="13579" max="13579" width="17.140625" style="11" customWidth="1"/>
-    <col min="13580" max="13580" width="9.140625" style="11"/>
-    <col min="13581" max="13581" width="9" style="11" customWidth="1"/>
-    <col min="13582" max="13824" width="9.140625" style="11"/>
-    <col min="13825" max="13828" width="7.42578125" style="11" customWidth="1"/>
-    <col min="13829" max="13829" width="9.140625" style="11"/>
-    <col min="13830" max="13830" width="5.5703125" style="11" customWidth="1"/>
-    <col min="13831" max="13831" width="3.5703125" style="11" customWidth="1"/>
-    <col min="13832" max="13832" width="5.140625" style="11" customWidth="1"/>
-    <col min="13833" max="13833" width="5.42578125" style="11" customWidth="1"/>
-    <col min="13834" max="13834" width="9.140625" style="11"/>
-    <col min="13835" max="13835" width="17.140625" style="11" customWidth="1"/>
-    <col min="13836" max="13836" width="9.140625" style="11"/>
-    <col min="13837" max="13837" width="9" style="11" customWidth="1"/>
-    <col min="13838" max="14080" width="9.140625" style="11"/>
-    <col min="14081" max="14084" width="7.42578125" style="11" customWidth="1"/>
-    <col min="14085" max="14085" width="9.140625" style="11"/>
-    <col min="14086" max="14086" width="5.5703125" style="11" customWidth="1"/>
-    <col min="14087" max="14087" width="3.5703125" style="11" customWidth="1"/>
-    <col min="14088" max="14088" width="5.140625" style="11" customWidth="1"/>
-    <col min="14089" max="14089" width="5.42578125" style="11" customWidth="1"/>
-    <col min="14090" max="14090" width="9.140625" style="11"/>
-    <col min="14091" max="14091" width="17.140625" style="11" customWidth="1"/>
-    <col min="14092" max="14092" width="9.140625" style="11"/>
-    <col min="14093" max="14093" width="9" style="11" customWidth="1"/>
-    <col min="14094" max="14336" width="9.140625" style="11"/>
-    <col min="14337" max="14340" width="7.42578125" style="11" customWidth="1"/>
-    <col min="14341" max="14341" width="9.140625" style="11"/>
-    <col min="14342" max="14342" width="5.5703125" style="11" customWidth="1"/>
-    <col min="14343" max="14343" width="3.5703125" style="11" customWidth="1"/>
-    <col min="14344" max="14344" width="5.140625" style="11" customWidth="1"/>
-    <col min="14345" max="14345" width="5.42578125" style="11" customWidth="1"/>
-    <col min="14346" max="14346" width="9.140625" style="11"/>
-    <col min="14347" max="14347" width="17.140625" style="11" customWidth="1"/>
-    <col min="14348" max="14348" width="9.140625" style="11"/>
-    <col min="14349" max="14349" width="9" style="11" customWidth="1"/>
-    <col min="14350" max="14592" width="9.140625" style="11"/>
-    <col min="14593" max="14596" width="7.42578125" style="11" customWidth="1"/>
-    <col min="14597" max="14597" width="9.140625" style="11"/>
-    <col min="14598" max="14598" width="5.5703125" style="11" customWidth="1"/>
-    <col min="14599" max="14599" width="3.5703125" style="11" customWidth="1"/>
-    <col min="14600" max="14600" width="5.140625" style="11" customWidth="1"/>
-    <col min="14601" max="14601" width="5.42578125" style="11" customWidth="1"/>
-    <col min="14602" max="14602" width="9.140625" style="11"/>
-    <col min="14603" max="14603" width="17.140625" style="11" customWidth="1"/>
-    <col min="14604" max="14604" width="9.140625" style="11"/>
-    <col min="14605" max="14605" width="9" style="11" customWidth="1"/>
-    <col min="14606" max="14848" width="9.140625" style="11"/>
-    <col min="14849" max="14852" width="7.42578125" style="11" customWidth="1"/>
-    <col min="14853" max="14853" width="9.140625" style="11"/>
-    <col min="14854" max="14854" width="5.5703125" style="11" customWidth="1"/>
-    <col min="14855" max="14855" width="3.5703125" style="11" customWidth="1"/>
-    <col min="14856" max="14856" width="5.140625" style="11" customWidth="1"/>
-    <col min="14857" max="14857" width="5.42578125" style="11" customWidth="1"/>
-    <col min="14858" max="14858" width="9.140625" style="11"/>
-    <col min="14859" max="14859" width="17.140625" style="11" customWidth="1"/>
-    <col min="14860" max="14860" width="9.140625" style="11"/>
-    <col min="14861" max="14861" width="9" style="11" customWidth="1"/>
-    <col min="14862" max="15104" width="9.140625" style="11"/>
-    <col min="15105" max="15108" width="7.42578125" style="11" customWidth="1"/>
-    <col min="15109" max="15109" width="9.140625" style="11"/>
-    <col min="15110" max="15110" width="5.5703125" style="11" customWidth="1"/>
-    <col min="15111" max="15111" width="3.5703125" style="11" customWidth="1"/>
-    <col min="15112" max="15112" width="5.140625" style="11" customWidth="1"/>
-    <col min="15113" max="15113" width="5.42578125" style="11" customWidth="1"/>
-    <col min="15114" max="15114" width="9.140625" style="11"/>
-    <col min="15115" max="15115" width="17.140625" style="11" customWidth="1"/>
-    <col min="15116" max="15116" width="9.140625" style="11"/>
-    <col min="15117" max="15117" width="9" style="11" customWidth="1"/>
-    <col min="15118" max="15360" width="9.140625" style="11"/>
-    <col min="15361" max="15364" width="7.42578125" style="11" customWidth="1"/>
-    <col min="15365" max="15365" width="9.140625" style="11"/>
-    <col min="15366" max="15366" width="5.5703125" style="11" customWidth="1"/>
-    <col min="15367" max="15367" width="3.5703125" style="11" customWidth="1"/>
-    <col min="15368" max="15368" width="5.140625" style="11" customWidth="1"/>
-    <col min="15369" max="15369" width="5.42578125" style="11" customWidth="1"/>
-    <col min="15370" max="15370" width="9.140625" style="11"/>
-    <col min="15371" max="15371" width="17.140625" style="11" customWidth="1"/>
-    <col min="15372" max="15372" width="9.140625" style="11"/>
-    <col min="15373" max="15373" width="9" style="11" customWidth="1"/>
-    <col min="15374" max="15616" width="9.140625" style="11"/>
-    <col min="15617" max="15620" width="7.42578125" style="11" customWidth="1"/>
-    <col min="15621" max="15621" width="9.140625" style="11"/>
-    <col min="15622" max="15622" width="5.5703125" style="11" customWidth="1"/>
-    <col min="15623" max="15623" width="3.5703125" style="11" customWidth="1"/>
-    <col min="15624" max="15624" width="5.140625" style="11" customWidth="1"/>
-    <col min="15625" max="15625" width="5.42578125" style="11" customWidth="1"/>
-    <col min="15626" max="15626" width="9.140625" style="11"/>
-    <col min="15627" max="15627" width="17.140625" style="11" customWidth="1"/>
-    <col min="15628" max="15628" width="9.140625" style="11"/>
-    <col min="15629" max="15629" width="9" style="11" customWidth="1"/>
-    <col min="15630" max="15872" width="9.140625" style="11"/>
-    <col min="15873" max="15876" width="7.42578125" style="11" customWidth="1"/>
-    <col min="15877" max="15877" width="9.140625" style="11"/>
-    <col min="15878" max="15878" width="5.5703125" style="11" customWidth="1"/>
-    <col min="15879" max="15879" width="3.5703125" style="11" customWidth="1"/>
-    <col min="15880" max="15880" width="5.140625" style="11" customWidth="1"/>
-    <col min="15881" max="15881" width="5.42578125" style="11" customWidth="1"/>
-    <col min="15882" max="15882" width="9.140625" style="11"/>
-    <col min="15883" max="15883" width="17.140625" style="11" customWidth="1"/>
-    <col min="15884" max="15884" width="9.140625" style="11"/>
-    <col min="15885" max="15885" width="9" style="11" customWidth="1"/>
-    <col min="15886" max="16128" width="9.140625" style="11"/>
-    <col min="16129" max="16132" width="7.42578125" style="11" customWidth="1"/>
-    <col min="16133" max="16133" width="9.140625" style="11"/>
-    <col min="16134" max="16134" width="5.5703125" style="11" customWidth="1"/>
-    <col min="16135" max="16135" width="3.5703125" style="11" customWidth="1"/>
-    <col min="16136" max="16136" width="5.140625" style="11" customWidth="1"/>
-    <col min="16137" max="16137" width="5.42578125" style="11" customWidth="1"/>
-    <col min="16138" max="16138" width="9.140625" style="11"/>
-    <col min="16139" max="16139" width="17.140625" style="11" customWidth="1"/>
-    <col min="16140" max="16140" width="9.140625" style="11"/>
-    <col min="16141" max="16141" width="9" style="11" customWidth="1"/>
-    <col min="16142" max="16384" width="9.140625" style="11"/>
+    <col min="1" max="4" width="7.42578125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="10"/>
+    <col min="6" max="6" width="5.5703125" style="10" customWidth="1"/>
+    <col min="7" max="7" width="3.5703125" style="10" customWidth="1"/>
+    <col min="8" max="8" width="5.140625" style="10" customWidth="1"/>
+    <col min="9" max="9" width="6.140625" style="10" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="10"/>
+    <col min="11" max="11" width="17.140625" style="10" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="10"/>
+    <col min="13" max="13" width="9" style="10" customWidth="1"/>
+    <col min="14" max="256" width="9.140625" style="10"/>
+    <col min="257" max="260" width="7.42578125" style="10" customWidth="1"/>
+    <col min="261" max="261" width="9.140625" style="10"/>
+    <col min="262" max="262" width="5.5703125" style="10" customWidth="1"/>
+    <col min="263" max="263" width="3.5703125" style="10" customWidth="1"/>
+    <col min="264" max="264" width="5.140625" style="10" customWidth="1"/>
+    <col min="265" max="265" width="5.42578125" style="10" customWidth="1"/>
+    <col min="266" max="266" width="9.140625" style="10"/>
+    <col min="267" max="267" width="17.140625" style="10" customWidth="1"/>
+    <col min="268" max="268" width="9.140625" style="10"/>
+    <col min="269" max="269" width="9" style="10" customWidth="1"/>
+    <col min="270" max="512" width="9.140625" style="10"/>
+    <col min="513" max="516" width="7.42578125" style="10" customWidth="1"/>
+    <col min="517" max="517" width="9.140625" style="10"/>
+    <col min="518" max="518" width="5.5703125" style="10" customWidth="1"/>
+    <col min="519" max="519" width="3.5703125" style="10" customWidth="1"/>
+    <col min="520" max="520" width="5.140625" style="10" customWidth="1"/>
+    <col min="521" max="521" width="5.42578125" style="10" customWidth="1"/>
+    <col min="522" max="522" width="9.140625" style="10"/>
+    <col min="523" max="523" width="17.140625" style="10" customWidth="1"/>
+    <col min="524" max="524" width="9.140625" style="10"/>
+    <col min="525" max="525" width="9" style="10" customWidth="1"/>
+    <col min="526" max="768" width="9.140625" style="10"/>
+    <col min="769" max="772" width="7.42578125" style="10" customWidth="1"/>
+    <col min="773" max="773" width="9.140625" style="10"/>
+    <col min="774" max="774" width="5.5703125" style="10" customWidth="1"/>
+    <col min="775" max="775" width="3.5703125" style="10" customWidth="1"/>
+    <col min="776" max="776" width="5.140625" style="10" customWidth="1"/>
+    <col min="777" max="777" width="5.42578125" style="10" customWidth="1"/>
+    <col min="778" max="778" width="9.140625" style="10"/>
+    <col min="779" max="779" width="17.140625" style="10" customWidth="1"/>
+    <col min="780" max="780" width="9.140625" style="10"/>
+    <col min="781" max="781" width="9" style="10" customWidth="1"/>
+    <col min="782" max="1024" width="9.140625" style="10"/>
+    <col min="1025" max="1028" width="7.42578125" style="10" customWidth="1"/>
+    <col min="1029" max="1029" width="9.140625" style="10"/>
+    <col min="1030" max="1030" width="5.5703125" style="10" customWidth="1"/>
+    <col min="1031" max="1031" width="3.5703125" style="10" customWidth="1"/>
+    <col min="1032" max="1032" width="5.140625" style="10" customWidth="1"/>
+    <col min="1033" max="1033" width="5.42578125" style="10" customWidth="1"/>
+    <col min="1034" max="1034" width="9.140625" style="10"/>
+    <col min="1035" max="1035" width="17.140625" style="10" customWidth="1"/>
+    <col min="1036" max="1036" width="9.140625" style="10"/>
+    <col min="1037" max="1037" width="9" style="10" customWidth="1"/>
+    <col min="1038" max="1280" width="9.140625" style="10"/>
+    <col min="1281" max="1284" width="7.42578125" style="10" customWidth="1"/>
+    <col min="1285" max="1285" width="9.140625" style="10"/>
+    <col min="1286" max="1286" width="5.5703125" style="10" customWidth="1"/>
+    <col min="1287" max="1287" width="3.5703125" style="10" customWidth="1"/>
+    <col min="1288" max="1288" width="5.140625" style="10" customWidth="1"/>
+    <col min="1289" max="1289" width="5.42578125" style="10" customWidth="1"/>
+    <col min="1290" max="1290" width="9.140625" style="10"/>
+    <col min="1291" max="1291" width="17.140625" style="10" customWidth="1"/>
+    <col min="1292" max="1292" width="9.140625" style="10"/>
+    <col min="1293" max="1293" width="9" style="10" customWidth="1"/>
+    <col min="1294" max="1536" width="9.140625" style="10"/>
+    <col min="1537" max="1540" width="7.42578125" style="10" customWidth="1"/>
+    <col min="1541" max="1541" width="9.140625" style="10"/>
+    <col min="1542" max="1542" width="5.5703125" style="10" customWidth="1"/>
+    <col min="1543" max="1543" width="3.5703125" style="10" customWidth="1"/>
+    <col min="1544" max="1544" width="5.140625" style="10" customWidth="1"/>
+    <col min="1545" max="1545" width="5.42578125" style="10" customWidth="1"/>
+    <col min="1546" max="1546" width="9.140625" style="10"/>
+    <col min="1547" max="1547" width="17.140625" style="10" customWidth="1"/>
+    <col min="1548" max="1548" width="9.140625" style="10"/>
+    <col min="1549" max="1549" width="9" style="10" customWidth="1"/>
+    <col min="1550" max="1792" width="9.140625" style="10"/>
+    <col min="1793" max="1796" width="7.42578125" style="10" customWidth="1"/>
+    <col min="1797" max="1797" width="9.140625" style="10"/>
+    <col min="1798" max="1798" width="5.5703125" style="10" customWidth="1"/>
+    <col min="1799" max="1799" width="3.5703125" style="10" customWidth="1"/>
+    <col min="1800" max="1800" width="5.140625" style="10" customWidth="1"/>
+    <col min="1801" max="1801" width="5.42578125" style="10" customWidth="1"/>
+    <col min="1802" max="1802" width="9.140625" style="10"/>
+    <col min="1803" max="1803" width="17.140625" style="10" customWidth="1"/>
+    <col min="1804" max="1804" width="9.140625" style="10"/>
+    <col min="1805" max="1805" width="9" style="10" customWidth="1"/>
+    <col min="1806" max="2048" width="9.140625" style="10"/>
+    <col min="2049" max="2052" width="7.42578125" style="10" customWidth="1"/>
+    <col min="2053" max="2053" width="9.140625" style="10"/>
+    <col min="2054" max="2054" width="5.5703125" style="10" customWidth="1"/>
+    <col min="2055" max="2055" width="3.5703125" style="10" customWidth="1"/>
+    <col min="2056" max="2056" width="5.140625" style="10" customWidth="1"/>
+    <col min="2057" max="2057" width="5.42578125" style="10" customWidth="1"/>
+    <col min="2058" max="2058" width="9.140625" style="10"/>
+    <col min="2059" max="2059" width="17.140625" style="10" customWidth="1"/>
+    <col min="2060" max="2060" width="9.140625" style="10"/>
+    <col min="2061" max="2061" width="9" style="10" customWidth="1"/>
+    <col min="2062" max="2304" width="9.140625" style="10"/>
+    <col min="2305" max="2308" width="7.42578125" style="10" customWidth="1"/>
+    <col min="2309" max="2309" width="9.140625" style="10"/>
+    <col min="2310" max="2310" width="5.5703125" style="10" customWidth="1"/>
+    <col min="2311" max="2311" width="3.5703125" style="10" customWidth="1"/>
+    <col min="2312" max="2312" width="5.140625" style="10" customWidth="1"/>
+    <col min="2313" max="2313" width="5.42578125" style="10" customWidth="1"/>
+    <col min="2314" max="2314" width="9.140625" style="10"/>
+    <col min="2315" max="2315" width="17.140625" style="10" customWidth="1"/>
+    <col min="2316" max="2316" width="9.140625" style="10"/>
+    <col min="2317" max="2317" width="9" style="10" customWidth="1"/>
+    <col min="2318" max="2560" width="9.140625" style="10"/>
+    <col min="2561" max="2564" width="7.42578125" style="10" customWidth="1"/>
+    <col min="2565" max="2565" width="9.140625" style="10"/>
+    <col min="2566" max="2566" width="5.5703125" style="10" customWidth="1"/>
+    <col min="2567" max="2567" width="3.5703125" style="10" customWidth="1"/>
+    <col min="2568" max="2568" width="5.140625" style="10" customWidth="1"/>
+    <col min="2569" max="2569" width="5.42578125" style="10" customWidth="1"/>
+    <col min="2570" max="2570" width="9.140625" style="10"/>
+    <col min="2571" max="2571" width="17.140625" style="10" customWidth="1"/>
+    <col min="2572" max="2572" width="9.140625" style="10"/>
+    <col min="2573" max="2573" width="9" style="10" customWidth="1"/>
+    <col min="2574" max="2816" width="9.140625" style="10"/>
+    <col min="2817" max="2820" width="7.42578125" style="10" customWidth="1"/>
+    <col min="2821" max="2821" width="9.140625" style="10"/>
+    <col min="2822" max="2822" width="5.5703125" style="10" customWidth="1"/>
+    <col min="2823" max="2823" width="3.5703125" style="10" customWidth="1"/>
+    <col min="2824" max="2824" width="5.140625" style="10" customWidth="1"/>
+    <col min="2825" max="2825" width="5.42578125" style="10" customWidth="1"/>
+    <col min="2826" max="2826" width="9.140625" style="10"/>
+    <col min="2827" max="2827" width="17.140625" style="10" customWidth="1"/>
+    <col min="2828" max="2828" width="9.140625" style="10"/>
+    <col min="2829" max="2829" width="9" style="10" customWidth="1"/>
+    <col min="2830" max="3072" width="9.140625" style="10"/>
+    <col min="3073" max="3076" width="7.42578125" style="10" customWidth="1"/>
+    <col min="3077" max="3077" width="9.140625" style="10"/>
+    <col min="3078" max="3078" width="5.5703125" style="10" customWidth="1"/>
+    <col min="3079" max="3079" width="3.5703125" style="10" customWidth="1"/>
+    <col min="3080" max="3080" width="5.140625" style="10" customWidth="1"/>
+    <col min="3081" max="3081" width="5.42578125" style="10" customWidth="1"/>
+    <col min="3082" max="3082" width="9.140625" style="10"/>
+    <col min="3083" max="3083" width="17.140625" style="10" customWidth="1"/>
+    <col min="3084" max="3084" width="9.140625" style="10"/>
+    <col min="3085" max="3085" width="9" style="10" customWidth="1"/>
+    <col min="3086" max="3328" width="9.140625" style="10"/>
+    <col min="3329" max="3332" width="7.42578125" style="10" customWidth="1"/>
+    <col min="3333" max="3333" width="9.140625" style="10"/>
+    <col min="3334" max="3334" width="5.5703125" style="10" customWidth="1"/>
+    <col min="3335" max="3335" width="3.5703125" style="10" customWidth="1"/>
+    <col min="3336" max="3336" width="5.140625" style="10" customWidth="1"/>
+    <col min="3337" max="3337" width="5.42578125" style="10" customWidth="1"/>
+    <col min="3338" max="3338" width="9.140625" style="10"/>
+    <col min="3339" max="3339" width="17.140625" style="10" customWidth="1"/>
+    <col min="3340" max="3340" width="9.140625" style="10"/>
+    <col min="3341" max="3341" width="9" style="10" customWidth="1"/>
+    <col min="3342" max="3584" width="9.140625" style="10"/>
+    <col min="3585" max="3588" width="7.42578125" style="10" customWidth="1"/>
+    <col min="3589" max="3589" width="9.140625" style="10"/>
+    <col min="3590" max="3590" width="5.5703125" style="10" customWidth="1"/>
+    <col min="3591" max="3591" width="3.5703125" style="10" customWidth="1"/>
+    <col min="3592" max="3592" width="5.140625" style="10" customWidth="1"/>
+    <col min="3593" max="3593" width="5.42578125" style="10" customWidth="1"/>
+    <col min="3594" max="3594" width="9.140625" style="10"/>
+    <col min="3595" max="3595" width="17.140625" style="10" customWidth="1"/>
+    <col min="3596" max="3596" width="9.140625" style="10"/>
+    <col min="3597" max="3597" width="9" style="10" customWidth="1"/>
+    <col min="3598" max="3840" width="9.140625" style="10"/>
+    <col min="3841" max="3844" width="7.42578125" style="10" customWidth="1"/>
+    <col min="3845" max="3845" width="9.140625" style="10"/>
+    <col min="3846" max="3846" width="5.5703125" style="10" customWidth="1"/>
+    <col min="3847" max="3847" width="3.5703125" style="10" customWidth="1"/>
+    <col min="3848" max="3848" width="5.140625" style="10" customWidth="1"/>
+    <col min="3849" max="3849" width="5.42578125" style="10" customWidth="1"/>
+    <col min="3850" max="3850" width="9.140625" style="10"/>
+    <col min="3851" max="3851" width="17.140625" style="10" customWidth="1"/>
+    <col min="3852" max="3852" width="9.140625" style="10"/>
+    <col min="3853" max="3853" width="9" style="10" customWidth="1"/>
+    <col min="3854" max="4096" width="9.140625" style="10"/>
+    <col min="4097" max="4100" width="7.42578125" style="10" customWidth="1"/>
+    <col min="4101" max="4101" width="9.140625" style="10"/>
+    <col min="4102" max="4102" width="5.5703125" style="10" customWidth="1"/>
+    <col min="4103" max="4103" width="3.5703125" style="10" customWidth="1"/>
+    <col min="4104" max="4104" width="5.140625" style="10" customWidth="1"/>
+    <col min="4105" max="4105" width="5.42578125" style="10" customWidth="1"/>
+    <col min="4106" max="4106" width="9.140625" style="10"/>
+    <col min="4107" max="4107" width="17.140625" style="10" customWidth="1"/>
+    <col min="4108" max="4108" width="9.140625" style="10"/>
+    <col min="4109" max="4109" width="9" style="10" customWidth="1"/>
+    <col min="4110" max="4352" width="9.140625" style="10"/>
+    <col min="4353" max="4356" width="7.42578125" style="10" customWidth="1"/>
+    <col min="4357" max="4357" width="9.140625" style="10"/>
+    <col min="4358" max="4358" width="5.5703125" style="10" customWidth="1"/>
+    <col min="4359" max="4359" width="3.5703125" style="10" customWidth="1"/>
+    <col min="4360" max="4360" width="5.140625" style="10" customWidth="1"/>
+    <col min="4361" max="4361" width="5.42578125" style="10" customWidth="1"/>
+    <col min="4362" max="4362" width="9.140625" style="10"/>
+    <col min="4363" max="4363" width="17.140625" style="10" customWidth="1"/>
+    <col min="4364" max="4364" width="9.140625" style="10"/>
+    <col min="4365" max="4365" width="9" style="10" customWidth="1"/>
+    <col min="4366" max="4608" width="9.140625" style="10"/>
+    <col min="4609" max="4612" width="7.42578125" style="10" customWidth="1"/>
+    <col min="4613" max="4613" width="9.140625" style="10"/>
+    <col min="4614" max="4614" width="5.5703125" style="10" customWidth="1"/>
+    <col min="4615" max="4615" width="3.5703125" style="10" customWidth="1"/>
+    <col min="4616" max="4616" width="5.140625" style="10" customWidth="1"/>
+    <col min="4617" max="4617" width="5.42578125" style="10" customWidth="1"/>
+    <col min="4618" max="4618" width="9.140625" style="10"/>
+    <col min="4619" max="4619" width="17.140625" style="10" customWidth="1"/>
+    <col min="4620" max="4620" width="9.140625" style="10"/>
+    <col min="4621" max="4621" width="9" style="10" customWidth="1"/>
+    <col min="4622" max="4864" width="9.140625" style="10"/>
+    <col min="4865" max="4868" width="7.42578125" style="10" customWidth="1"/>
+    <col min="4869" max="4869" width="9.140625" style="10"/>
+    <col min="4870" max="4870" width="5.5703125" style="10" customWidth="1"/>
+    <col min="4871" max="4871" width="3.5703125" style="10" customWidth="1"/>
+    <col min="4872" max="4872" width="5.140625" style="10" customWidth="1"/>
+    <col min="4873" max="4873" width="5.42578125" style="10" customWidth="1"/>
+    <col min="4874" max="4874" width="9.140625" style="10"/>
+    <col min="4875" max="4875" width="17.140625" style="10" customWidth="1"/>
+    <col min="4876" max="4876" width="9.140625" style="10"/>
+    <col min="4877" max="4877" width="9" style="10" customWidth="1"/>
+    <col min="4878" max="5120" width="9.140625" style="10"/>
+    <col min="5121" max="5124" width="7.42578125" style="10" customWidth="1"/>
+    <col min="5125" max="5125" width="9.140625" style="10"/>
+    <col min="5126" max="5126" width="5.5703125" style="10" customWidth="1"/>
+    <col min="5127" max="5127" width="3.5703125" style="10" customWidth="1"/>
+    <col min="5128" max="5128" width="5.140625" style="10" customWidth="1"/>
+    <col min="5129" max="5129" width="5.42578125" style="10" customWidth="1"/>
+    <col min="5130" max="5130" width="9.140625" style="10"/>
+    <col min="5131" max="5131" width="17.140625" style="10" customWidth="1"/>
+    <col min="5132" max="5132" width="9.140625" style="10"/>
+    <col min="5133" max="5133" width="9" style="10" customWidth="1"/>
+    <col min="5134" max="5376" width="9.140625" style="10"/>
+    <col min="5377" max="5380" width="7.42578125" style="10" customWidth="1"/>
+    <col min="5381" max="5381" width="9.140625" style="10"/>
+    <col min="5382" max="5382" width="5.5703125" style="10" customWidth="1"/>
+    <col min="5383" max="5383" width="3.5703125" style="10" customWidth="1"/>
+    <col min="5384" max="5384" width="5.140625" style="10" customWidth="1"/>
+    <col min="5385" max="5385" width="5.42578125" style="10" customWidth="1"/>
+    <col min="5386" max="5386" width="9.140625" style="10"/>
+    <col min="5387" max="5387" width="17.140625" style="10" customWidth="1"/>
+    <col min="5388" max="5388" width="9.140625" style="10"/>
+    <col min="5389" max="5389" width="9" style="10" customWidth="1"/>
+    <col min="5390" max="5632" width="9.140625" style="10"/>
+    <col min="5633" max="5636" width="7.42578125" style="10" customWidth="1"/>
+    <col min="5637" max="5637" width="9.140625" style="10"/>
+    <col min="5638" max="5638" width="5.5703125" style="10" customWidth="1"/>
+    <col min="5639" max="5639" width="3.5703125" style="10" customWidth="1"/>
+    <col min="5640" max="5640" width="5.140625" style="10" customWidth="1"/>
+    <col min="5641" max="5641" width="5.42578125" style="10" customWidth="1"/>
+    <col min="5642" max="5642" width="9.140625" style="10"/>
+    <col min="5643" max="5643" width="17.140625" style="10" customWidth="1"/>
+    <col min="5644" max="5644" width="9.140625" style="10"/>
+    <col min="5645" max="5645" width="9" style="10" customWidth="1"/>
+    <col min="5646" max="5888" width="9.140625" style="10"/>
+    <col min="5889" max="5892" width="7.42578125" style="10" customWidth="1"/>
+    <col min="5893" max="5893" width="9.140625" style="10"/>
+    <col min="5894" max="5894" width="5.5703125" style="10" customWidth="1"/>
+    <col min="5895" max="5895" width="3.5703125" style="10" customWidth="1"/>
+    <col min="5896" max="5896" width="5.140625" style="10" customWidth="1"/>
+    <col min="5897" max="5897" width="5.42578125" style="10" customWidth="1"/>
+    <col min="5898" max="5898" width="9.140625" style="10"/>
+    <col min="5899" max="5899" width="17.140625" style="10" customWidth="1"/>
+    <col min="5900" max="5900" width="9.140625" style="10"/>
+    <col min="5901" max="5901" width="9" style="10" customWidth="1"/>
+    <col min="5902" max="6144" width="9.140625" style="10"/>
+    <col min="6145" max="6148" width="7.42578125" style="10" customWidth="1"/>
+    <col min="6149" max="6149" width="9.140625" style="10"/>
+    <col min="6150" max="6150" width="5.5703125" style="10" customWidth="1"/>
+    <col min="6151" max="6151" width="3.5703125" style="10" customWidth="1"/>
+    <col min="6152" max="6152" width="5.140625" style="10" customWidth="1"/>
+    <col min="6153" max="6153" width="5.42578125" style="10" customWidth="1"/>
+    <col min="6154" max="6154" width="9.140625" style="10"/>
+    <col min="6155" max="6155" width="17.140625" style="10" customWidth="1"/>
+    <col min="6156" max="6156" width="9.140625" style="10"/>
+    <col min="6157" max="6157" width="9" style="10" customWidth="1"/>
+    <col min="6158" max="6400" width="9.140625" style="10"/>
+    <col min="6401" max="6404" width="7.42578125" style="10" customWidth="1"/>
+    <col min="6405" max="6405" width="9.140625" style="10"/>
+    <col min="6406" max="6406" width="5.5703125" style="10" customWidth="1"/>
+    <col min="6407" max="6407" width="3.5703125" style="10" customWidth="1"/>
+    <col min="6408" max="6408" width="5.140625" style="10" customWidth="1"/>
+    <col min="6409" max="6409" width="5.42578125" style="10" customWidth="1"/>
+    <col min="6410" max="6410" width="9.140625" style="10"/>
+    <col min="6411" max="6411" width="17.140625" style="10" customWidth="1"/>
+    <col min="6412" max="6412" width="9.140625" style="10"/>
+    <col min="6413" max="6413" width="9" style="10" customWidth="1"/>
+    <col min="6414" max="6656" width="9.140625" style="10"/>
+    <col min="6657" max="6660" width="7.42578125" style="10" customWidth="1"/>
+    <col min="6661" max="6661" width="9.140625" style="10"/>
+    <col min="6662" max="6662" width="5.5703125" style="10" customWidth="1"/>
+    <col min="6663" max="6663" width="3.5703125" style="10" customWidth="1"/>
+    <col min="6664" max="6664" width="5.140625" style="10" customWidth="1"/>
+    <col min="6665" max="6665" width="5.42578125" style="10" customWidth="1"/>
+    <col min="6666" max="6666" width="9.140625" style="10"/>
+    <col min="6667" max="6667" width="17.140625" style="10" customWidth="1"/>
+    <col min="6668" max="6668" width="9.140625" style="10"/>
+    <col min="6669" max="6669" width="9" style="10" customWidth="1"/>
+    <col min="6670" max="6912" width="9.140625" style="10"/>
+    <col min="6913" max="6916" width="7.42578125" style="10" customWidth="1"/>
+    <col min="6917" max="6917" width="9.140625" style="10"/>
+    <col min="6918" max="6918" width="5.5703125" style="10" customWidth="1"/>
+    <col min="6919" max="6919" width="3.5703125" style="10" customWidth="1"/>
+    <col min="6920" max="6920" width="5.140625" style="10" customWidth="1"/>
+    <col min="6921" max="6921" width="5.42578125" style="10" customWidth="1"/>
+    <col min="6922" max="6922" width="9.140625" style="10"/>
+    <col min="6923" max="6923" width="17.140625" style="10" customWidth="1"/>
+    <col min="6924" max="6924" width="9.140625" style="10"/>
+    <col min="6925" max="6925" width="9" style="10" customWidth="1"/>
+    <col min="6926" max="7168" width="9.140625" style="10"/>
+    <col min="7169" max="7172" width="7.42578125" style="10" customWidth="1"/>
+    <col min="7173" max="7173" width="9.140625" style="10"/>
+    <col min="7174" max="7174" width="5.5703125" style="10" customWidth="1"/>
+    <col min="7175" max="7175" width="3.5703125" style="10" customWidth="1"/>
+    <col min="7176" max="7176" width="5.140625" style="10" customWidth="1"/>
+    <col min="7177" max="7177" width="5.42578125" style="10" customWidth="1"/>
+    <col min="7178" max="7178" width="9.140625" style="10"/>
+    <col min="7179" max="7179" width="17.140625" style="10" customWidth="1"/>
+    <col min="7180" max="7180" width="9.140625" style="10"/>
+    <col min="7181" max="7181" width="9" style="10" customWidth="1"/>
+    <col min="7182" max="7424" width="9.140625" style="10"/>
+    <col min="7425" max="7428" width="7.42578125" style="10" customWidth="1"/>
+    <col min="7429" max="7429" width="9.140625" style="10"/>
+    <col min="7430" max="7430" width="5.5703125" style="10" customWidth="1"/>
+    <col min="7431" max="7431" width="3.5703125" style="10" customWidth="1"/>
+    <col min="7432" max="7432" width="5.140625" style="10" customWidth="1"/>
+    <col min="7433" max="7433" width="5.42578125" style="10" customWidth="1"/>
+    <col min="7434" max="7434" width="9.140625" style="10"/>
+    <col min="7435" max="7435" width="17.140625" style="10" customWidth="1"/>
+    <col min="7436" max="7436" width="9.140625" style="10"/>
+    <col min="7437" max="7437" width="9" style="10" customWidth="1"/>
+    <col min="7438" max="7680" width="9.140625" style="10"/>
+    <col min="7681" max="7684" width="7.42578125" style="10" customWidth="1"/>
+    <col min="7685" max="7685" width="9.140625" style="10"/>
+    <col min="7686" max="7686" width="5.5703125" style="10" customWidth="1"/>
+    <col min="7687" max="7687" width="3.5703125" style="10" customWidth="1"/>
+    <col min="7688" max="7688" width="5.140625" style="10" customWidth="1"/>
+    <col min="7689" max="7689" width="5.42578125" style="10" customWidth="1"/>
+    <col min="7690" max="7690" width="9.140625" style="10"/>
+    <col min="7691" max="7691" width="17.140625" style="10" customWidth="1"/>
+    <col min="7692" max="7692" width="9.140625" style="10"/>
+    <col min="7693" max="7693" width="9" style="10" customWidth="1"/>
+    <col min="7694" max="7936" width="9.140625" style="10"/>
+    <col min="7937" max="7940" width="7.42578125" style="10" customWidth="1"/>
+    <col min="7941" max="7941" width="9.140625" style="10"/>
+    <col min="7942" max="7942" width="5.5703125" style="10" customWidth="1"/>
+    <col min="7943" max="7943" width="3.5703125" style="10" customWidth="1"/>
+    <col min="7944" max="7944" width="5.140625" style="10" customWidth="1"/>
+    <col min="7945" max="7945" width="5.42578125" style="10" customWidth="1"/>
+    <col min="7946" max="7946" width="9.140625" style="10"/>
+    <col min="7947" max="7947" width="17.140625" style="10" customWidth="1"/>
+    <col min="7948" max="7948" width="9.140625" style="10"/>
+    <col min="7949" max="7949" width="9" style="10" customWidth="1"/>
+    <col min="7950" max="8192" width="9.140625" style="10"/>
+    <col min="8193" max="8196" width="7.42578125" style="10" customWidth="1"/>
+    <col min="8197" max="8197" width="9.140625" style="10"/>
+    <col min="8198" max="8198" width="5.5703125" style="10" customWidth="1"/>
+    <col min="8199" max="8199" width="3.5703125" style="10" customWidth="1"/>
+    <col min="8200" max="8200" width="5.140625" style="10" customWidth="1"/>
+    <col min="8201" max="8201" width="5.42578125" style="10" customWidth="1"/>
+    <col min="8202" max="8202" width="9.140625" style="10"/>
+    <col min="8203" max="8203" width="17.140625" style="10" customWidth="1"/>
+    <col min="8204" max="8204" width="9.140625" style="10"/>
+    <col min="8205" max="8205" width="9" style="10" customWidth="1"/>
+    <col min="8206" max="8448" width="9.140625" style="10"/>
+    <col min="8449" max="8452" width="7.42578125" style="10" customWidth="1"/>
+    <col min="8453" max="8453" width="9.140625" style="10"/>
+    <col min="8454" max="8454" width="5.5703125" style="10" customWidth="1"/>
+    <col min="8455" max="8455" width="3.5703125" style="10" customWidth="1"/>
+    <col min="8456" max="8456" width="5.140625" style="10" customWidth="1"/>
+    <col min="8457" max="8457" width="5.42578125" style="10" customWidth="1"/>
+    <col min="8458" max="8458" width="9.140625" style="10"/>
+    <col min="8459" max="8459" width="17.140625" style="10" customWidth="1"/>
+    <col min="8460" max="8460" width="9.140625" style="10"/>
+    <col min="8461" max="8461" width="9" style="10" customWidth="1"/>
+    <col min="8462" max="8704" width="9.140625" style="10"/>
+    <col min="8705" max="8708" width="7.42578125" style="10" customWidth="1"/>
+    <col min="8709" max="8709" width="9.140625" style="10"/>
+    <col min="8710" max="8710" width="5.5703125" style="10" customWidth="1"/>
+    <col min="8711" max="8711" width="3.5703125" style="10" customWidth="1"/>
+    <col min="8712" max="8712" width="5.140625" style="10" customWidth="1"/>
+    <col min="8713" max="8713" width="5.42578125" style="10" customWidth="1"/>
+    <col min="8714" max="8714" width="9.140625" style="10"/>
+    <col min="8715" max="8715" width="17.140625" style="10" customWidth="1"/>
+    <col min="8716" max="8716" width="9.140625" style="10"/>
+    <col min="8717" max="8717" width="9" style="10" customWidth="1"/>
+    <col min="8718" max="8960" width="9.140625" style="10"/>
+    <col min="8961" max="8964" width="7.42578125" style="10" customWidth="1"/>
+    <col min="8965" max="8965" width="9.140625" style="10"/>
+    <col min="8966" max="8966" width="5.5703125" style="10" customWidth="1"/>
+    <col min="8967" max="8967" width="3.5703125" style="10" customWidth="1"/>
+    <col min="8968" max="8968" width="5.140625" style="10" customWidth="1"/>
+    <col min="8969" max="8969" width="5.42578125" style="10" customWidth="1"/>
+    <col min="8970" max="8970" width="9.140625" style="10"/>
+    <col min="8971" max="8971" width="17.140625" style="10" customWidth="1"/>
+    <col min="8972" max="8972" width="9.140625" style="10"/>
+    <col min="8973" max="8973" width="9" style="10" customWidth="1"/>
+    <col min="8974" max="9216" width="9.140625" style="10"/>
+    <col min="9217" max="9220" width="7.42578125" style="10" customWidth="1"/>
+    <col min="9221" max="9221" width="9.140625" style="10"/>
+    <col min="9222" max="9222" width="5.5703125" style="10" customWidth="1"/>
+    <col min="9223" max="9223" width="3.5703125" style="10" customWidth="1"/>
+    <col min="9224" max="9224" width="5.140625" style="10" customWidth="1"/>
+    <col min="9225" max="9225" width="5.42578125" style="10" customWidth="1"/>
+    <col min="9226" max="9226" width="9.140625" style="10"/>
+    <col min="9227" max="9227" width="17.140625" style="10" customWidth="1"/>
+    <col min="9228" max="9228" width="9.140625" style="10"/>
+    <col min="9229" max="9229" width="9" style="10" customWidth="1"/>
+    <col min="9230" max="9472" width="9.140625" style="10"/>
+    <col min="9473" max="9476" width="7.42578125" style="10" customWidth="1"/>
+    <col min="9477" max="9477" width="9.140625" style="10"/>
+    <col min="9478" max="9478" width="5.5703125" style="10" customWidth="1"/>
+    <col min="9479" max="9479" width="3.5703125" style="10" customWidth="1"/>
+    <col min="9480" max="9480" width="5.140625" style="10" customWidth="1"/>
+    <col min="9481" max="9481" width="5.42578125" style="10" customWidth="1"/>
+    <col min="9482" max="9482" width="9.140625" style="10"/>
+    <col min="9483" max="9483" width="17.140625" style="10" customWidth="1"/>
+    <col min="9484" max="9484" width="9.140625" style="10"/>
+    <col min="9485" max="9485" width="9" style="10" customWidth="1"/>
+    <col min="9486" max="9728" width="9.140625" style="10"/>
+    <col min="9729" max="9732" width="7.42578125" style="10" customWidth="1"/>
+    <col min="9733" max="9733" width="9.140625" style="10"/>
+    <col min="9734" max="9734" width="5.5703125" style="10" customWidth="1"/>
+    <col min="9735" max="9735" width="3.5703125" style="10" customWidth="1"/>
+    <col min="9736" max="9736" width="5.140625" style="10" customWidth="1"/>
+    <col min="9737" max="9737" width="5.42578125" style="10" customWidth="1"/>
+    <col min="9738" max="9738" width="9.140625" style="10"/>
+    <col min="9739" max="9739" width="17.140625" style="10" customWidth="1"/>
+    <col min="9740" max="9740" width="9.140625" style="10"/>
+    <col min="9741" max="9741" width="9" style="10" customWidth="1"/>
+    <col min="9742" max="9984" width="9.140625" style="10"/>
+    <col min="9985" max="9988" width="7.42578125" style="10" customWidth="1"/>
+    <col min="9989" max="9989" width="9.140625" style="10"/>
+    <col min="9990" max="9990" width="5.5703125" style="10" customWidth="1"/>
+    <col min="9991" max="9991" width="3.5703125" style="10" customWidth="1"/>
+    <col min="9992" max="9992" width="5.140625" style="10" customWidth="1"/>
+    <col min="9993" max="9993" width="5.42578125" style="10" customWidth="1"/>
+    <col min="9994" max="9994" width="9.140625" style="10"/>
+    <col min="9995" max="9995" width="17.140625" style="10" customWidth="1"/>
+    <col min="9996" max="9996" width="9.140625" style="10"/>
+    <col min="9997" max="9997" width="9" style="10" customWidth="1"/>
+    <col min="9998" max="10240" width="9.140625" style="10"/>
+    <col min="10241" max="10244" width="7.42578125" style="10" customWidth="1"/>
+    <col min="10245" max="10245" width="9.140625" style="10"/>
+    <col min="10246" max="10246" width="5.5703125" style="10" customWidth="1"/>
+    <col min="10247" max="10247" width="3.5703125" style="10" customWidth="1"/>
+    <col min="10248" max="10248" width="5.140625" style="10" customWidth="1"/>
+    <col min="10249" max="10249" width="5.42578125" style="10" customWidth="1"/>
+    <col min="10250" max="10250" width="9.140625" style="10"/>
+    <col min="10251" max="10251" width="17.140625" style="10" customWidth="1"/>
+    <col min="10252" max="10252" width="9.140625" style="10"/>
+    <col min="10253" max="10253" width="9" style="10" customWidth="1"/>
+    <col min="10254" max="10496" width="9.140625" style="10"/>
+    <col min="10497" max="10500" width="7.42578125" style="10" customWidth="1"/>
+    <col min="10501" max="10501" width="9.140625" style="10"/>
+    <col min="10502" max="10502" width="5.5703125" style="10" customWidth="1"/>
+    <col min="10503" max="10503" width="3.5703125" style="10" customWidth="1"/>
+    <col min="10504" max="10504" width="5.140625" style="10" customWidth="1"/>
+    <col min="10505" max="10505" width="5.42578125" style="10" customWidth="1"/>
+    <col min="10506" max="10506" width="9.140625" style="10"/>
+    <col min="10507" max="10507" width="17.140625" style="10" customWidth="1"/>
+    <col min="10508" max="10508" width="9.140625" style="10"/>
+    <col min="10509" max="10509" width="9" style="10" customWidth="1"/>
+    <col min="10510" max="10752" width="9.140625" style="10"/>
+    <col min="10753" max="10756" width="7.42578125" style="10" customWidth="1"/>
+    <col min="10757" max="10757" width="9.140625" style="10"/>
+    <col min="10758" max="10758" width="5.5703125" style="10" customWidth="1"/>
+    <col min="10759" max="10759" width="3.5703125" style="10" customWidth="1"/>
+    <col min="10760" max="10760" width="5.140625" style="10" customWidth="1"/>
+    <col min="10761" max="10761" width="5.42578125" style="10" customWidth="1"/>
+    <col min="10762" max="10762" width="9.140625" style="10"/>
+    <col min="10763" max="10763" width="17.140625" style="10" customWidth="1"/>
+    <col min="10764" max="10764" width="9.140625" style="10"/>
+    <col min="10765" max="10765" width="9" style="10" customWidth="1"/>
+    <col min="10766" max="11008" width="9.140625" style="10"/>
+    <col min="11009" max="11012" width="7.42578125" style="10" customWidth="1"/>
+    <col min="11013" max="11013" width="9.140625" style="10"/>
+    <col min="11014" max="11014" width="5.5703125" style="10" customWidth="1"/>
+    <col min="11015" max="11015" width="3.5703125" style="10" customWidth="1"/>
+    <col min="11016" max="11016" width="5.140625" style="10" customWidth="1"/>
+    <col min="11017" max="11017" width="5.42578125" style="10" customWidth="1"/>
+    <col min="11018" max="11018" width="9.140625" style="10"/>
+    <col min="11019" max="11019" width="17.140625" style="10" customWidth="1"/>
+    <col min="11020" max="11020" width="9.140625" style="10"/>
+    <col min="11021" max="11021" width="9" style="10" customWidth="1"/>
+    <col min="11022" max="11264" width="9.140625" style="10"/>
+    <col min="11265" max="11268" width="7.42578125" style="10" customWidth="1"/>
+    <col min="11269" max="11269" width="9.140625" style="10"/>
+    <col min="11270" max="11270" width="5.5703125" style="10" customWidth="1"/>
+    <col min="11271" max="11271" width="3.5703125" style="10" customWidth="1"/>
+    <col min="11272" max="11272" width="5.140625" style="10" customWidth="1"/>
+    <col min="11273" max="11273" width="5.42578125" style="10" customWidth="1"/>
+    <col min="11274" max="11274" width="9.140625" style="10"/>
+    <col min="11275" max="11275" width="17.140625" style="10" customWidth="1"/>
+    <col min="11276" max="11276" width="9.140625" style="10"/>
+    <col min="11277" max="11277" width="9" style="10" customWidth="1"/>
+    <col min="11278" max="11520" width="9.140625" style="10"/>
+    <col min="11521" max="11524" width="7.42578125" style="10" customWidth="1"/>
+    <col min="11525" max="11525" width="9.140625" style="10"/>
+    <col min="11526" max="11526" width="5.5703125" style="10" customWidth="1"/>
+    <col min="11527" max="11527" width="3.5703125" style="10" customWidth="1"/>
+    <col min="11528" max="11528" width="5.140625" style="10" customWidth="1"/>
+    <col min="11529" max="11529" width="5.42578125" style="10" customWidth="1"/>
+    <col min="11530" max="11530" width="9.140625" style="10"/>
+    <col min="11531" max="11531" width="17.140625" style="10" customWidth="1"/>
+    <col min="11532" max="11532" width="9.140625" style="10"/>
+    <col min="11533" max="11533" width="9" style="10" customWidth="1"/>
+    <col min="11534" max="11776" width="9.140625" style="10"/>
+    <col min="11777" max="11780" width="7.42578125" style="10" customWidth="1"/>
+    <col min="11781" max="11781" width="9.140625" style="10"/>
+    <col min="11782" max="11782" width="5.5703125" style="10" customWidth="1"/>
+    <col min="11783" max="11783" width="3.5703125" style="10" customWidth="1"/>
+    <col min="11784" max="11784" width="5.140625" style="10" customWidth="1"/>
+    <col min="11785" max="11785" width="5.42578125" style="10" customWidth="1"/>
+    <col min="11786" max="11786" width="9.140625" style="10"/>
+    <col min="11787" max="11787" width="17.140625" style="10" customWidth="1"/>
+    <col min="11788" max="11788" width="9.140625" style="10"/>
+    <col min="11789" max="11789" width="9" style="10" customWidth="1"/>
+    <col min="11790" max="12032" width="9.140625" style="10"/>
+    <col min="12033" max="12036" width="7.42578125" style="10" customWidth="1"/>
+    <col min="12037" max="12037" width="9.140625" style="10"/>
+    <col min="12038" max="12038" width="5.5703125" style="10" customWidth="1"/>
+    <col min="12039" max="12039" width="3.5703125" style="10" customWidth="1"/>
+    <col min="12040" max="12040" width="5.140625" style="10" customWidth="1"/>
+    <col min="12041" max="12041" width="5.42578125" style="10" customWidth="1"/>
+    <col min="12042" max="12042" width="9.140625" style="10"/>
+    <col min="12043" max="12043" width="17.140625" style="10" customWidth="1"/>
+    <col min="12044" max="12044" width="9.140625" style="10"/>
+    <col min="12045" max="12045" width="9" style="10" customWidth="1"/>
+    <col min="12046" max="12288" width="9.140625" style="10"/>
+    <col min="12289" max="12292" width="7.42578125" style="10" customWidth="1"/>
+    <col min="12293" max="12293" width="9.140625" style="10"/>
+    <col min="12294" max="12294" width="5.5703125" style="10" customWidth="1"/>
+    <col min="12295" max="12295" width="3.5703125" style="10" customWidth="1"/>
+    <col min="12296" max="12296" width="5.140625" style="10" customWidth="1"/>
+    <col min="12297" max="12297" width="5.42578125" style="10" customWidth="1"/>
+    <col min="12298" max="12298" width="9.140625" style="10"/>
+    <col min="12299" max="12299" width="17.140625" style="10" customWidth="1"/>
+    <col min="12300" max="12300" width="9.140625" style="10"/>
+    <col min="12301" max="12301" width="9" style="10" customWidth="1"/>
+    <col min="12302" max="12544" width="9.140625" style="10"/>
+    <col min="12545" max="12548" width="7.42578125" style="10" customWidth="1"/>
+    <col min="12549" max="12549" width="9.140625" style="10"/>
+    <col min="12550" max="12550" width="5.5703125" style="10" customWidth="1"/>
+    <col min="12551" max="12551" width="3.5703125" style="10" customWidth="1"/>
+    <col min="12552" max="12552" width="5.140625" style="10" customWidth="1"/>
+    <col min="12553" max="12553" width="5.42578125" style="10" customWidth="1"/>
+    <col min="12554" max="12554" width="9.140625" style="10"/>
+    <col min="12555" max="12555" width="17.140625" style="10" customWidth="1"/>
+    <col min="12556" max="12556" width="9.140625" style="10"/>
+    <col min="12557" max="12557" width="9" style="10" customWidth="1"/>
+    <col min="12558" max="12800" width="9.140625" style="10"/>
+    <col min="12801" max="12804" width="7.42578125" style="10" customWidth="1"/>
+    <col min="12805" max="12805" width="9.140625" style="10"/>
+    <col min="12806" max="12806" width="5.5703125" style="10" customWidth="1"/>
+    <col min="12807" max="12807" width="3.5703125" style="10" customWidth="1"/>
+    <col min="12808" max="12808" width="5.140625" style="10" customWidth="1"/>
+    <col min="12809" max="12809" width="5.42578125" style="10" customWidth="1"/>
+    <col min="12810" max="12810" width="9.140625" style="10"/>
+    <col min="12811" max="12811" width="17.140625" style="10" customWidth="1"/>
+    <col min="12812" max="12812" width="9.140625" style="10"/>
+    <col min="12813" max="12813" width="9" style="10" customWidth="1"/>
+    <col min="12814" max="13056" width="9.140625" style="10"/>
+    <col min="13057" max="13060" width="7.42578125" style="10" customWidth="1"/>
+    <col min="13061" max="13061" width="9.140625" style="10"/>
+    <col min="13062" max="13062" width="5.5703125" style="10" customWidth="1"/>
+    <col min="13063" max="13063" width="3.5703125" style="10" customWidth="1"/>
+    <col min="13064" max="13064" width="5.140625" style="10" customWidth="1"/>
+    <col min="13065" max="13065" width="5.42578125" style="10" customWidth="1"/>
+    <col min="13066" max="13066" width="9.140625" style="10"/>
+    <col min="13067" max="13067" width="17.140625" style="10" customWidth="1"/>
+    <col min="13068" max="13068" width="9.140625" style="10"/>
+    <col min="13069" max="13069" width="9" style="10" customWidth="1"/>
+    <col min="13070" max="13312" width="9.140625" style="10"/>
+    <col min="13313" max="13316" width="7.42578125" style="10" customWidth="1"/>
+    <col min="13317" max="13317" width="9.140625" style="10"/>
+    <col min="13318" max="13318" width="5.5703125" style="10" customWidth="1"/>
+    <col min="13319" max="13319" width="3.5703125" style="10" customWidth="1"/>
+    <col min="13320" max="13320" width="5.140625" style="10" customWidth="1"/>
+    <col min="13321" max="13321" width="5.42578125" style="10" customWidth="1"/>
+    <col min="13322" max="13322" width="9.140625" style="10"/>
+    <col min="13323" max="13323" width="17.140625" style="10" customWidth="1"/>
+    <col min="13324" max="13324" width="9.140625" style="10"/>
+    <col min="13325" max="13325" width="9" style="10" customWidth="1"/>
+    <col min="13326" max="13568" width="9.140625" style="10"/>
+    <col min="13569" max="13572" width="7.42578125" style="10" customWidth="1"/>
+    <col min="13573" max="13573" width="9.140625" style="10"/>
+    <col min="13574" max="13574" width="5.5703125" style="10" customWidth="1"/>
+    <col min="13575" max="13575" width="3.5703125" style="10" customWidth="1"/>
+    <col min="13576" max="13576" width="5.140625" style="10" customWidth="1"/>
+    <col min="13577" max="13577" width="5.42578125" style="10" customWidth="1"/>
+    <col min="13578" max="13578" width="9.140625" style="10"/>
+    <col min="13579" max="13579" width="17.140625" style="10" customWidth="1"/>
+    <col min="13580" max="13580" width="9.140625" style="10"/>
+    <col min="13581" max="13581" width="9" style="10" customWidth="1"/>
+    <col min="13582" max="13824" width="9.140625" style="10"/>
+    <col min="13825" max="13828" width="7.42578125" style="10" customWidth="1"/>
+    <col min="13829" max="13829" width="9.140625" style="10"/>
+    <col min="13830" max="13830" width="5.5703125" style="10" customWidth="1"/>
+    <col min="13831" max="13831" width="3.5703125" style="10" customWidth="1"/>
+    <col min="13832" max="13832" width="5.140625" style="10" customWidth="1"/>
+    <col min="13833" max="13833" width="5.42578125" style="10" customWidth="1"/>
+    <col min="13834" max="13834" width="9.140625" style="10"/>
+    <col min="13835" max="13835" width="17.140625" style="10" customWidth="1"/>
+    <col min="13836" max="13836" width="9.140625" style="10"/>
+    <col min="13837" max="13837" width="9" style="10" customWidth="1"/>
+    <col min="13838" max="14080" width="9.140625" style="10"/>
+    <col min="14081" max="14084" width="7.42578125" style="10" customWidth="1"/>
+    <col min="14085" max="14085" width="9.140625" style="10"/>
+    <col min="14086" max="14086" width="5.5703125" style="10" customWidth="1"/>
+    <col min="14087" max="14087" width="3.5703125" style="10" customWidth="1"/>
+    <col min="14088" max="14088" width="5.140625" style="10" customWidth="1"/>
+    <col min="14089" max="14089" width="5.42578125" style="10" customWidth="1"/>
+    <col min="14090" max="14090" width="9.140625" style="10"/>
+    <col min="14091" max="14091" width="17.140625" style="10" customWidth="1"/>
+    <col min="14092" max="14092" width="9.140625" style="10"/>
+    <col min="14093" max="14093" width="9" style="10" customWidth="1"/>
+    <col min="14094" max="14336" width="9.140625" style="10"/>
+    <col min="14337" max="14340" width="7.42578125" style="10" customWidth="1"/>
+    <col min="14341" max="14341" width="9.140625" style="10"/>
+    <col min="14342" max="14342" width="5.5703125" style="10" customWidth="1"/>
+    <col min="14343" max="14343" width="3.5703125" style="10" customWidth="1"/>
+    <col min="14344" max="14344" width="5.140625" style="10" customWidth="1"/>
+    <col min="14345" max="14345" width="5.42578125" style="10" customWidth="1"/>
+    <col min="14346" max="14346" width="9.140625" style="10"/>
+    <col min="14347" max="14347" width="17.140625" style="10" customWidth="1"/>
+    <col min="14348" max="14348" width="9.140625" style="10"/>
+    <col min="14349" max="14349" width="9" style="10" customWidth="1"/>
+    <col min="14350" max="14592" width="9.140625" style="10"/>
+    <col min="14593" max="14596" width="7.42578125" style="10" customWidth="1"/>
+    <col min="14597" max="14597" width="9.140625" style="10"/>
+    <col min="14598" max="14598" width="5.5703125" style="10" customWidth="1"/>
+    <col min="14599" max="14599" width="3.5703125" style="10" customWidth="1"/>
+    <col min="14600" max="14600" width="5.140625" style="10" customWidth="1"/>
+    <col min="14601" max="14601" width="5.42578125" style="10" customWidth="1"/>
+    <col min="14602" max="14602" width="9.140625" style="10"/>
+    <col min="14603" max="14603" width="17.140625" style="10" customWidth="1"/>
+    <col min="14604" max="14604" width="9.140625" style="10"/>
+    <col min="14605" max="14605" width="9" style="10" customWidth="1"/>
+    <col min="14606" max="14848" width="9.140625" style="10"/>
+    <col min="14849" max="14852" width="7.42578125" style="10" customWidth="1"/>
+    <col min="14853" max="14853" width="9.140625" style="10"/>
+    <col min="14854" max="14854" width="5.5703125" style="10" customWidth="1"/>
+    <col min="14855" max="14855" width="3.5703125" style="10" customWidth="1"/>
+    <col min="14856" max="14856" width="5.140625" style="10" customWidth="1"/>
+    <col min="14857" max="14857" width="5.42578125" style="10" customWidth="1"/>
+    <col min="14858" max="14858" width="9.140625" style="10"/>
+    <col min="14859" max="14859" width="17.140625" style="10" customWidth="1"/>
+    <col min="14860" max="14860" width="9.140625" style="10"/>
+    <col min="14861" max="14861" width="9" style="10" customWidth="1"/>
+    <col min="14862" max="15104" width="9.140625" style="10"/>
+    <col min="15105" max="15108" width="7.42578125" style="10" customWidth="1"/>
+    <col min="15109" max="15109" width="9.140625" style="10"/>
+    <col min="15110" max="15110" width="5.5703125" style="10" customWidth="1"/>
+    <col min="15111" max="15111" width="3.5703125" style="10" customWidth="1"/>
+    <col min="15112" max="15112" width="5.140625" style="10" customWidth="1"/>
+    <col min="15113" max="15113" width="5.42578125" style="10" customWidth="1"/>
+    <col min="15114" max="15114" width="9.140625" style="10"/>
+    <col min="15115" max="15115" width="17.140625" style="10" customWidth="1"/>
+    <col min="15116" max="15116" width="9.140625" style="10"/>
+    <col min="15117" max="15117" width="9" style="10" customWidth="1"/>
+    <col min="15118" max="15360" width="9.140625" style="10"/>
+    <col min="15361" max="15364" width="7.42578125" style="10" customWidth="1"/>
+    <col min="15365" max="15365" width="9.140625" style="10"/>
+    <col min="15366" max="15366" width="5.5703125" style="10" customWidth="1"/>
+    <col min="15367" max="15367" width="3.5703125" style="10" customWidth="1"/>
+    <col min="15368" max="15368" width="5.140625" style="10" customWidth="1"/>
+    <col min="15369" max="15369" width="5.42578125" style="10" customWidth="1"/>
+    <col min="15370" max="15370" width="9.140625" style="10"/>
+    <col min="15371" max="15371" width="17.140625" style="10" customWidth="1"/>
+    <col min="15372" max="15372" width="9.140625" style="10"/>
+    <col min="15373" max="15373" width="9" style="10" customWidth="1"/>
+    <col min="15374" max="15616" width="9.140625" style="10"/>
+    <col min="15617" max="15620" width="7.42578125" style="10" customWidth="1"/>
+    <col min="15621" max="15621" width="9.140625" style="10"/>
+    <col min="15622" max="15622" width="5.5703125" style="10" customWidth="1"/>
+    <col min="15623" max="15623" width="3.5703125" style="10" customWidth="1"/>
+    <col min="15624" max="15624" width="5.140625" style="10" customWidth="1"/>
+    <col min="15625" max="15625" width="5.42578125" style="10" customWidth="1"/>
+    <col min="15626" max="15626" width="9.140625" style="10"/>
+    <col min="15627" max="15627" width="17.140625" style="10" customWidth="1"/>
+    <col min="15628" max="15628" width="9.140625" style="10"/>
+    <col min="15629" max="15629" width="9" style="10" customWidth="1"/>
+    <col min="15630" max="15872" width="9.140625" style="10"/>
+    <col min="15873" max="15876" width="7.42578125" style="10" customWidth="1"/>
+    <col min="15877" max="15877" width="9.140625" style="10"/>
+    <col min="15878" max="15878" width="5.5703125" style="10" customWidth="1"/>
+    <col min="15879" max="15879" width="3.5703125" style="10" customWidth="1"/>
+    <col min="15880" max="15880" width="5.140625" style="10" customWidth="1"/>
+    <col min="15881" max="15881" width="5.42578125" style="10" customWidth="1"/>
+    <col min="15882" max="15882" width="9.140625" style="10"/>
+    <col min="15883" max="15883" width="17.140625" style="10" customWidth="1"/>
+    <col min="15884" max="15884" width="9.140625" style="10"/>
+    <col min="15885" max="15885" width="9" style="10" customWidth="1"/>
+    <col min="15886" max="16128" width="9.140625" style="10"/>
+    <col min="16129" max="16132" width="7.42578125" style="10" customWidth="1"/>
+    <col min="16133" max="16133" width="9.140625" style="10"/>
+    <col min="16134" max="16134" width="5.5703125" style="10" customWidth="1"/>
+    <col min="16135" max="16135" width="3.5703125" style="10" customWidth="1"/>
+    <col min="16136" max="16136" width="5.140625" style="10" customWidth="1"/>
+    <col min="16137" max="16137" width="5.42578125" style="10" customWidth="1"/>
+    <col min="16138" max="16138" width="9.140625" style="10"/>
+    <col min="16139" max="16139" width="17.140625" style="10" customWidth="1"/>
+    <col min="16140" max="16140" width="9.140625" style="10"/>
+    <col min="16141" max="16141" width="9" style="10" customWidth="1"/>
+    <col min="16142" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="383" t="s">
+      <c r="A1" s="343" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="384"/>
-      <c r="C1" s="380" t="s">
+      <c r="B1" s="344"/>
+      <c r="C1" s="340" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="381"/>
-      <c r="E1" s="381"/>
-      <c r="F1" s="381"/>
-      <c r="G1" s="381"/>
-      <c r="H1" s="381"/>
-      <c r="I1" s="381"/>
-      <c r="J1" s="381"/>
-      <c r="K1" s="382"/>
-      <c r="L1" s="385" t="s">
+      <c r="D1" s="341"/>
+      <c r="E1" s="341"/>
+      <c r="F1" s="341"/>
+      <c r="G1" s="341"/>
+      <c r="H1" s="341"/>
+      <c r="I1" s="341"/>
+      <c r="J1" s="341"/>
+      <c r="K1" s="342"/>
+      <c r="L1" s="345" t="s">
         <v>61</v>
       </c>
-      <c r="M1" s="386"/>
+      <c r="M1" s="346"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="207" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="378"/>
-      <c r="C2" s="378"/>
-      <c r="D2" s="378"/>
-      <c r="E2" s="378"/>
-      <c r="F2" s="378"/>
-      <c r="G2" s="378"/>
-      <c r="H2" s="249"/>
-      <c r="I2" s="227" t="s">
+      <c r="B2" s="338"/>
+      <c r="C2" s="338"/>
+      <c r="D2" s="338"/>
+      <c r="E2" s="338"/>
+      <c r="F2" s="338"/>
+      <c r="G2" s="338"/>
+      <c r="H2" s="209"/>
+      <c r="I2" s="187" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="379"/>
-      <c r="K2" s="379"/>
-      <c r="L2" s="379"/>
-      <c r="M2" s="229"/>
+      <c r="J2" s="339"/>
+      <c r="K2" s="339"/>
+      <c r="L2" s="339"/>
+      <c r="M2" s="189"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="212" t="s">
+      <c r="A3" s="172" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="213"/>
-      <c r="C3" s="213"/>
-      <c r="D3" s="213"/>
-      <c r="E3" s="213"/>
-      <c r="F3" s="213"/>
-      <c r="G3" s="213"/>
-      <c r="H3" s="214"/>
-      <c r="I3" s="227"/>
-      <c r="J3" s="228"/>
-      <c r="K3" s="228"/>
-      <c r="L3" s="228"/>
-      <c r="M3" s="229"/>
+      <c r="B3" s="173"/>
+      <c r="C3" s="173"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="173"/>
+      <c r="F3" s="173"/>
+      <c r="G3" s="173"/>
+      <c r="H3" s="174"/>
+      <c r="I3" s="187"/>
+      <c r="J3" s="188"/>
+      <c r="K3" s="188"/>
+      <c r="L3" s="188"/>
+      <c r="M3" s="189"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="212" t="s">
+      <c r="A4" s="172" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="213"/>
-      <c r="C4" s="213"/>
-      <c r="D4" s="213"/>
-      <c r="E4" s="213"/>
-      <c r="F4" s="213"/>
-      <c r="G4" s="213"/>
-      <c r="H4" s="214"/>
-      <c r="I4" s="215"/>
-      <c r="J4" s="216"/>
-      <c r="K4" s="216"/>
-      <c r="L4" s="216"/>
-      <c r="M4" s="217"/>
+      <c r="B4" s="173"/>
+      <c r="C4" s="173"/>
+      <c r="D4" s="173"/>
+      <c r="E4" s="173"/>
+      <c r="F4" s="173"/>
+      <c r="G4" s="173"/>
+      <c r="H4" s="174"/>
+      <c r="I4" s="175"/>
+      <c r="J4" s="176"/>
+      <c r="K4" s="176"/>
+      <c r="L4" s="176"/>
+      <c r="M4" s="177"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="212" t="s">
+      <c r="A5" s="172" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="213"/>
-      <c r="C5" s="213"/>
-      <c r="D5" s="213"/>
-      <c r="E5" s="213"/>
-      <c r="F5" s="213"/>
-      <c r="G5" s="213"/>
-      <c r="H5" s="214"/>
-      <c r="I5" s="215"/>
-      <c r="J5" s="216"/>
-      <c r="K5" s="216"/>
-      <c r="L5" s="216"/>
-      <c r="M5" s="217"/>
+      <c r="B5" s="173"/>
+      <c r="C5" s="173"/>
+      <c r="D5" s="173"/>
+      <c r="E5" s="173"/>
+      <c r="F5" s="173"/>
+      <c r="G5" s="173"/>
+      <c r="H5" s="174"/>
+      <c r="I5" s="175"/>
+      <c r="J5" s="176"/>
+      <c r="K5" s="176"/>
+      <c r="L5" s="176"/>
+      <c r="M5" s="177"/>
     </row>
     <row r="6" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="221" t="s">
+      <c r="A6" s="181" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="222"/>
-      <c r="C6" s="222"/>
-      <c r="D6" s="222"/>
-      <c r="E6" s="222"/>
-      <c r="F6" s="223" t="s">
+      <c r="B6" s="182"/>
+      <c r="C6" s="182"/>
+      <c r="D6" s="182"/>
+      <c r="E6" s="182"/>
+      <c r="F6" s="183" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="223"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="218"/>
-      <c r="J6" s="219"/>
-      <c r="K6" s="219"/>
-      <c r="L6" s="219"/>
-      <c r="M6" s="220"/>
+      <c r="G6" s="183"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="178"/>
+      <c r="J6" s="179"/>
+      <c r="K6" s="179"/>
+      <c r="L6" s="179"/>
+      <c r="M6" s="180"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="224" t="s">
+      <c r="A7" s="184" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="225"/>
-      <c r="C7" s="225"/>
-      <c r="D7" s="225"/>
-      <c r="E7" s="225"/>
-      <c r="F7" s="225"/>
-      <c r="G7" s="225"/>
-      <c r="H7" s="226"/>
-      <c r="I7" s="62" t="s">
+      <c r="B7" s="185"/>
+      <c r="C7" s="185"/>
+      <c r="D7" s="185"/>
+      <c r="E7" s="185"/>
+      <c r="F7" s="185"/>
+      <c r="G7" s="185"/>
+      <c r="H7" s="186"/>
+      <c r="I7" s="55" t="s">
         <v>77</v>
       </c>
-      <c r="J7" s="63"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="63"/>
-      <c r="M7" s="65"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="57"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="58"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="242" t="s">
+      <c r="A8" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="243"/>
-      <c r="C8" s="243"/>
-      <c r="D8" s="243"/>
-      <c r="E8" s="244" t="s">
+      <c r="B8" s="203"/>
+      <c r="C8" s="203"/>
+      <c r="D8" s="203"/>
+      <c r="E8" s="204" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="244"/>
-      <c r="G8" s="244"/>
-      <c r="H8" s="245"/>
-      <c r="I8" s="242" t="s">
+      <c r="F8" s="204"/>
+      <c r="G8" s="204"/>
+      <c r="H8" s="205"/>
+      <c r="I8" s="202" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="243"/>
-      <c r="K8" s="243"/>
-      <c r="L8" s="243"/>
-      <c r="M8" s="246"/>
+      <c r="J8" s="203"/>
+      <c r="K8" s="203"/>
+      <c r="L8" s="203"/>
+      <c r="M8" s="206"/>
     </row>
     <row r="9" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="242" t="s">
+      <c r="A9" s="202" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="243"/>
-      <c r="C9" s="243"/>
-      <c r="D9" s="243"/>
-      <c r="E9" s="243"/>
-      <c r="F9" s="243"/>
-      <c r="G9" s="243"/>
-      <c r="H9" s="246"/>
-      <c r="I9" s="66" t="s">
+      <c r="B9" s="203"/>
+      <c r="C9" s="203"/>
+      <c r="D9" s="203"/>
+      <c r="E9" s="203"/>
+      <c r="F9" s="203"/>
+      <c r="G9" s="203"/>
+      <c r="H9" s="206"/>
+      <c r="I9" s="59" t="s">
         <v>71</v>
       </c>
-      <c r="J9" s="67"/>
-      <c r="K9" s="67"/>
-      <c r="L9" s="67"/>
-      <c r="M9" s="61"/>
+      <c r="J9" s="60"/>
+      <c r="K9" s="60"/>
+      <c r="L9" s="60"/>
+      <c r="M9" s="54"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="242" t="s">
+      <c r="A10" s="202" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="243"/>
-      <c r="C10" s="243"/>
-      <c r="D10" s="243"/>
-      <c r="E10" s="243"/>
-      <c r="F10" s="243"/>
-      <c r="G10" s="243"/>
-      <c r="H10" s="246"/>
-      <c r="I10" s="68" t="s">
+      <c r="B10" s="203"/>
+      <c r="C10" s="203"/>
+      <c r="D10" s="203"/>
+      <c r="E10" s="203"/>
+      <c r="F10" s="203"/>
+      <c r="G10" s="203"/>
+      <c r="H10" s="206"/>
+      <c r="I10" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="J10" s="69"/>
-      <c r="K10" s="69"/>
-      <c r="L10" s="69"/>
-      <c r="M10" s="70"/>
+      <c r="J10" s="62"/>
+      <c r="K10" s="62"/>
+      <c r="L10" s="62"/>
+      <c r="M10" s="63"/>
     </row>
     <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="230" t="s">
+      <c r="A11" s="190" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="231"/>
-      <c r="C11" s="231"/>
-      <c r="D11" s="231"/>
-      <c r="E11" s="231"/>
-      <c r="F11" s="232" t="s">
+      <c r="B11" s="191"/>
+      <c r="C11" s="191"/>
+      <c r="D11" s="191"/>
+      <c r="E11" s="191"/>
+      <c r="F11" s="192" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="232"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="71" t="s">
+      <c r="G11" s="192"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="J11" s="72"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="72"/>
-      <c r="M11" s="73"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="65"/>
+      <c r="L11" s="65"/>
+      <c r="M11" s="66"/>
     </row>
     <row r="12" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="224" t="s">
+      <c r="A12" s="184" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="225"/>
-      <c r="C12" s="225"/>
-      <c r="D12" s="225"/>
-      <c r="E12" s="225"/>
-      <c r="F12" s="225"/>
-      <c r="G12" s="225"/>
-      <c r="H12" s="226"/>
-      <c r="I12" s="233"/>
-      <c r="J12" s="234"/>
-      <c r="K12" s="234"/>
-      <c r="L12" s="234"/>
-      <c r="M12" s="235"/>
+      <c r="B12" s="185"/>
+      <c r="C12" s="185"/>
+      <c r="D12" s="185"/>
+      <c r="E12" s="185"/>
+      <c r="F12" s="185"/>
+      <c r="G12" s="185"/>
+      <c r="H12" s="186"/>
+      <c r="I12" s="193"/>
+      <c r="J12" s="194"/>
+      <c r="K12" s="194"/>
+      <c r="L12" s="194"/>
+      <c r="M12" s="195"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="239" t="s">
+      <c r="A13" s="199" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="240"/>
-      <c r="C13" s="240"/>
-      <c r="D13" s="240"/>
-      <c r="E13" s="240"/>
-      <c r="F13" s="240"/>
-      <c r="G13" s="240"/>
-      <c r="H13" s="241"/>
-      <c r="I13" s="233"/>
-      <c r="J13" s="234"/>
-      <c r="K13" s="234"/>
-      <c r="L13" s="234"/>
-      <c r="M13" s="235"/>
+      <c r="B13" s="200"/>
+      <c r="C13" s="200"/>
+      <c r="D13" s="200"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="200"/>
+      <c r="G13" s="200"/>
+      <c r="H13" s="201"/>
+      <c r="I13" s="193"/>
+      <c r="J13" s="194"/>
+      <c r="K13" s="194"/>
+      <c r="L13" s="194"/>
+      <c r="M13" s="195"/>
     </row>
     <row r="14" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="212" t="s">
+      <c r="A14" s="172" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="213"/>
-      <c r="C14" s="213"/>
-      <c r="D14" s="213"/>
-      <c r="E14" s="213"/>
-      <c r="F14" s="213"/>
-      <c r="G14" s="213"/>
-      <c r="H14" s="214"/>
-      <c r="I14" s="236"/>
-      <c r="J14" s="237"/>
-      <c r="K14" s="237"/>
-      <c r="L14" s="237"/>
-      <c r="M14" s="238"/>
+      <c r="B14" s="173"/>
+      <c r="C14" s="173"/>
+      <c r="D14" s="173"/>
+      <c r="E14" s="173"/>
+      <c r="F14" s="173"/>
+      <c r="G14" s="173"/>
+      <c r="H14" s="174"/>
+      <c r="I14" s="196"/>
+      <c r="J14" s="197"/>
+      <c r="K14" s="197"/>
+      <c r="L14" s="197"/>
+      <c r="M14" s="198"/>
     </row>
     <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="262" t="s">
+      <c r="A15" s="222" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="263"/>
-      <c r="C15" s="263"/>
-      <c r="D15" s="263"/>
-      <c r="E15" s="263"/>
-      <c r="F15" s="263"/>
-      <c r="G15" s="263"/>
-      <c r="H15" s="263"/>
-      <c r="I15" s="264" t="s">
+      <c r="B15" s="223"/>
+      <c r="C15" s="223"/>
+      <c r="D15" s="223"/>
+      <c r="E15" s="223"/>
+      <c r="F15" s="223"/>
+      <c r="G15" s="223"/>
+      <c r="H15" s="223"/>
+      <c r="I15" s="224" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="265"/>
-      <c r="K15" s="265"/>
-      <c r="L15" s="265"/>
-      <c r="M15" s="266"/>
+      <c r="J15" s="225"/>
+      <c r="K15" s="225"/>
+      <c r="L15" s="225"/>
+      <c r="M15" s="226"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="74" t="s">
+      <c r="A16" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="75"/>
-      <c r="C16" s="75"/>
-      <c r="D16" s="75"/>
-      <c r="E16" s="75"/>
-      <c r="F16" s="315"/>
-      <c r="G16" s="315"/>
-      <c r="H16" s="316"/>
-      <c r="I16" s="267" t="s">
+      <c r="B16" s="68"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="275"/>
+      <c r="G16" s="275"/>
+      <c r="H16" s="276"/>
+      <c r="I16" s="227" t="s">
         <v>81</v>
       </c>
-      <c r="J16" s="268"/>
-      <c r="K16" s="268"/>
-      <c r="L16" s="268"/>
-      <c r="M16" s="269"/>
+      <c r="J16" s="228"/>
+      <c r="K16" s="228"/>
+      <c r="L16" s="228"/>
+      <c r="M16" s="229"/>
     </row>
     <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="76"/>
-      <c r="B17" s="77"/>
-      <c r="C17" s="77"/>
-      <c r="D17" s="77"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="270"/>
-      <c r="J17" s="244"/>
-      <c r="K17" s="271" t="s">
+      <c r="A17" s="69"/>
+      <c r="B17" s="70"/>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="230"/>
+      <c r="J17" s="204"/>
+      <c r="K17" s="231" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="271"/>
-      <c r="M17" s="272"/>
+      <c r="L17" s="231"/>
+      <c r="M17" s="232"/>
     </row>
     <row r="18" spans="1:13" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="76"/>
-      <c r="B18" s="77"/>
-      <c r="C18" s="77"/>
-      <c r="D18" s="77"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="77"/>
-      <c r="G18" s="77"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="275" t="s">
+      <c r="A18" s="69"/>
+      <c r="B18" s="70"/>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="235" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="276"/>
-      <c r="K18" s="273"/>
-      <c r="L18" s="273"/>
-      <c r="M18" s="274"/>
+      <c r="J18" s="236"/>
+      <c r="K18" s="233"/>
+      <c r="L18" s="233"/>
+      <c r="M18" s="234"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="247" t="s">
+      <c r="A19" s="207" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="248"/>
-      <c r="C19" s="248"/>
-      <c r="D19" s="248"/>
-      <c r="E19" s="248"/>
-      <c r="F19" s="248"/>
-      <c r="G19" s="248"/>
-      <c r="H19" s="248"/>
-      <c r="I19" s="248"/>
-      <c r="J19" s="248"/>
-      <c r="K19" s="248"/>
-      <c r="L19" s="248"/>
-      <c r="M19" s="249"/>
+      <c r="B19" s="208"/>
+      <c r="C19" s="208"/>
+      <c r="D19" s="208"/>
+      <c r="E19" s="208"/>
+      <c r="F19" s="208"/>
+      <c r="G19" s="208"/>
+      <c r="H19" s="208"/>
+      <c r="I19" s="208"/>
+      <c r="J19" s="208"/>
+      <c r="K19" s="208"/>
+      <c r="L19" s="208"/>
+      <c r="M19" s="209"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="250" t="s">
+      <c r="A20" s="210" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="251"/>
-      <c r="C20" s="251"/>
-      <c r="D20" s="251"/>
-      <c r="E20" s="251" t="s">
+      <c r="B20" s="211"/>
+      <c r="C20" s="211"/>
+      <c r="D20" s="211"/>
+      <c r="E20" s="211" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="251" t="s">
+      <c r="F20" s="211" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="251"/>
-      <c r="H20" s="252" t="s">
+      <c r="G20" s="211"/>
+      <c r="H20" s="212" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="253"/>
-      <c r="J20" s="254" t="s">
+      <c r="I20" s="213"/>
+      <c r="J20" s="214" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="255"/>
-      <c r="L20" s="255"/>
-      <c r="M20" s="256"/>
+      <c r="K20" s="215"/>
+      <c r="L20" s="215"/>
+      <c r="M20" s="216"/>
     </row>
     <row r="21" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="250"/>
-      <c r="B21" s="251"/>
-      <c r="C21" s="251"/>
-      <c r="D21" s="251"/>
-      <c r="E21" s="251"/>
-      <c r="F21" s="251"/>
-      <c r="G21" s="251"/>
-      <c r="H21" s="260" t="s">
+      <c r="A21" s="210"/>
+      <c r="B21" s="211"/>
+      <c r="C21" s="211"/>
+      <c r="D21" s="211"/>
+      <c r="E21" s="211"/>
+      <c r="F21" s="211"/>
+      <c r="G21" s="211"/>
+      <c r="H21" s="220" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="261"/>
-      <c r="J21" s="257"/>
-      <c r="K21" s="258"/>
-      <c r="L21" s="258"/>
-      <c r="M21" s="259"/>
+      <c r="I21" s="221"/>
+      <c r="J21" s="217"/>
+      <c r="K21" s="218"/>
+      <c r="L21" s="218"/>
+      <c r="M21" s="219"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="277"/>
-      <c r="B22" s="277"/>
-      <c r="C22" s="277"/>
-      <c r="D22" s="278"/>
-      <c r="E22" s="79"/>
-      <c r="F22" s="279"/>
-      <c r="G22" s="279"/>
-      <c r="H22" s="80" t="s">
+      <c r="A22" s="237"/>
+      <c r="B22" s="237"/>
+      <c r="C22" s="237"/>
+      <c r="D22" s="238"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="239"/>
+      <c r="G22" s="239"/>
+      <c r="H22" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I22" s="80" t="s">
+      <c r="I22" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="280"/>
-      <c r="K22" s="280"/>
-      <c r="L22" s="280"/>
-      <c r="M22" s="281"/>
+      <c r="J22" s="240"/>
+      <c r="K22" s="240"/>
+      <c r="L22" s="240"/>
+      <c r="M22" s="241"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="277"/>
-      <c r="B23" s="277"/>
-      <c r="C23" s="277"/>
-      <c r="D23" s="278"/>
-      <c r="E23" s="79"/>
-      <c r="F23" s="279"/>
-      <c r="G23" s="279"/>
-      <c r="H23" s="80" t="s">
+      <c r="A23" s="237"/>
+      <c r="B23" s="237"/>
+      <c r="C23" s="237"/>
+      <c r="D23" s="238"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="239"/>
+      <c r="G23" s="239"/>
+      <c r="H23" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I23" s="80" t="s">
+      <c r="I23" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="280"/>
-      <c r="K23" s="280"/>
-      <c r="L23" s="280"/>
-      <c r="M23" s="281"/>
+      <c r="J23" s="240"/>
+      <c r="K23" s="240"/>
+      <c r="L23" s="240"/>
+      <c r="M23" s="241"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="277"/>
-      <c r="B24" s="277"/>
-      <c r="C24" s="277"/>
-      <c r="D24" s="278"/>
-      <c r="E24" s="79"/>
-      <c r="F24" s="279"/>
-      <c r="G24" s="279"/>
-      <c r="H24" s="80" t="s">
+      <c r="A24" s="237"/>
+      <c r="B24" s="237"/>
+      <c r="C24" s="237"/>
+      <c r="D24" s="238"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="239"/>
+      <c r="G24" s="239"/>
+      <c r="H24" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I24" s="80" t="s">
+      <c r="I24" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="280"/>
-      <c r="K24" s="280"/>
-      <c r="L24" s="280"/>
-      <c r="M24" s="281"/>
+      <c r="J24" s="240"/>
+      <c r="K24" s="240"/>
+      <c r="L24" s="240"/>
+      <c r="M24" s="241"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="277"/>
-      <c r="B25" s="277"/>
-      <c r="C25" s="277"/>
-      <c r="D25" s="278"/>
-      <c r="E25" s="79"/>
-      <c r="F25" s="279"/>
-      <c r="G25" s="279"/>
-      <c r="H25" s="80" t="s">
+      <c r="A25" s="237"/>
+      <c r="B25" s="237"/>
+      <c r="C25" s="237"/>
+      <c r="D25" s="238"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="239"/>
+      <c r="G25" s="239"/>
+      <c r="H25" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I25" s="80" t="s">
+      <c r="I25" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="280"/>
-      <c r="K25" s="280"/>
-      <c r="L25" s="280"/>
-      <c r="M25" s="281"/>
+      <c r="J25" s="240"/>
+      <c r="K25" s="240"/>
+      <c r="L25" s="240"/>
+      <c r="M25" s="241"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="277"/>
-      <c r="B26" s="277"/>
-      <c r="C26" s="277"/>
-      <c r="D26" s="278"/>
-      <c r="E26" s="79"/>
-      <c r="F26" s="279"/>
-      <c r="G26" s="279"/>
-      <c r="H26" s="80" t="s">
+      <c r="A26" s="237"/>
+      <c r="B26" s="237"/>
+      <c r="C26" s="237"/>
+      <c r="D26" s="238"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="239"/>
+      <c r="G26" s="239"/>
+      <c r="H26" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I26" s="80" t="s">
+      <c r="I26" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="280"/>
-      <c r="K26" s="280"/>
-      <c r="L26" s="280"/>
-      <c r="M26" s="281"/>
+      <c r="J26" s="240"/>
+      <c r="K26" s="240"/>
+      <c r="L26" s="240"/>
+      <c r="M26" s="241"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="277"/>
-      <c r="B27" s="277"/>
-      <c r="C27" s="277"/>
-      <c r="D27" s="278"/>
-      <c r="E27" s="79"/>
-      <c r="F27" s="279"/>
-      <c r="G27" s="279"/>
-      <c r="H27" s="80" t="s">
+      <c r="A27" s="237"/>
+      <c r="B27" s="237"/>
+      <c r="C27" s="237"/>
+      <c r="D27" s="238"/>
+      <c r="E27" s="72"/>
+      <c r="F27" s="239"/>
+      <c r="G27" s="239"/>
+      <c r="H27" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I27" s="80" t="s">
+      <c r="I27" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J27" s="280"/>
-      <c r="K27" s="280"/>
-      <c r="L27" s="280"/>
-      <c r="M27" s="281"/>
+      <c r="J27" s="240"/>
+      <c r="K27" s="240"/>
+      <c r="L27" s="240"/>
+      <c r="M27" s="241"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="277"/>
-      <c r="B28" s="277"/>
-      <c r="C28" s="277"/>
-      <c r="D28" s="278"/>
-      <c r="E28" s="79"/>
-      <c r="F28" s="279"/>
-      <c r="G28" s="279"/>
-      <c r="H28" s="80" t="s">
+      <c r="A28" s="237"/>
+      <c r="B28" s="237"/>
+      <c r="C28" s="237"/>
+      <c r="D28" s="238"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="239"/>
+      <c r="G28" s="239"/>
+      <c r="H28" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="80" t="s">
+      <c r="I28" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J28" s="280"/>
-      <c r="K28" s="280"/>
-      <c r="L28" s="280"/>
-      <c r="M28" s="281"/>
+      <c r="J28" s="240"/>
+      <c r="K28" s="240"/>
+      <c r="L28" s="240"/>
+      <c r="M28" s="241"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="277"/>
-      <c r="B29" s="277"/>
-      <c r="C29" s="277"/>
-      <c r="D29" s="278"/>
-      <c r="E29" s="79"/>
-      <c r="F29" s="279"/>
-      <c r="G29" s="279"/>
-      <c r="H29" s="80" t="s">
+      <c r="A29" s="237"/>
+      <c r="B29" s="237"/>
+      <c r="C29" s="237"/>
+      <c r="D29" s="238"/>
+      <c r="E29" s="72"/>
+      <c r="F29" s="239"/>
+      <c r="G29" s="239"/>
+      <c r="H29" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I29" s="80" t="s">
+      <c r="I29" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J29" s="280"/>
-      <c r="K29" s="280"/>
-      <c r="L29" s="280"/>
-      <c r="M29" s="281"/>
+      <c r="J29" s="240"/>
+      <c r="K29" s="240"/>
+      <c r="L29" s="240"/>
+      <c r="M29" s="241"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="287" t="s">
+      <c r="A30" s="247" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="288"/>
-      <c r="C30" s="288"/>
-      <c r="D30" s="288"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="289"/>
-      <c r="G30" s="280"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="290"/>
-      <c r="K30" s="290"/>
-      <c r="L30" s="290"/>
-      <c r="M30" s="291"/>
+      <c r="B30" s="248"/>
+      <c r="C30" s="248"/>
+      <c r="D30" s="248"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="249"/>
+      <c r="G30" s="240"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="250"/>
+      <c r="K30" s="250"/>
+      <c r="L30" s="250"/>
+      <c r="M30" s="251"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="247" t="s">
+      <c r="A31" s="207" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="248"/>
-      <c r="C31" s="248"/>
-      <c r="D31" s="248"/>
-      <c r="E31" s="248"/>
-      <c r="F31" s="248"/>
-      <c r="G31" s="248"/>
-      <c r="H31" s="248"/>
-      <c r="I31" s="248"/>
-      <c r="J31" s="248"/>
-      <c r="K31" s="248"/>
-      <c r="L31" s="248"/>
-      <c r="M31" s="249"/>
+      <c r="B31" s="208"/>
+      <c r="C31" s="208"/>
+      <c r="D31" s="208"/>
+      <c r="E31" s="208"/>
+      <c r="F31" s="208"/>
+      <c r="G31" s="208"/>
+      <c r="H31" s="208"/>
+      <c r="I31" s="208"/>
+      <c r="J31" s="208"/>
+      <c r="K31" s="208"/>
+      <c r="L31" s="208"/>
+      <c r="M31" s="209"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="292" t="s">
+      <c r="A32" s="252" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="293"/>
-      <c r="C32" s="293" t="s">
+      <c r="B32" s="253"/>
+      <c r="C32" s="253" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="293"/>
-      <c r="E32" s="294" t="s">
+      <c r="D32" s="253"/>
+      <c r="E32" s="254" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="295" t="s">
+      <c r="F32" s="255" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="296" t="s">
+      <c r="G32" s="256" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="296"/>
-      <c r="I32" s="296"/>
-      <c r="J32" s="296"/>
-      <c r="K32" s="296"/>
-      <c r="L32" s="293" t="s">
+      <c r="H32" s="256"/>
+      <c r="I32" s="256"/>
+      <c r="J32" s="256"/>
+      <c r="K32" s="256"/>
+      <c r="L32" s="253" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="297"/>
+      <c r="M32" s="257"/>
     </row>
     <row r="33" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="294"/>
-      <c r="F33" s="295"/>
-      <c r="G33" s="282" t="s">
+      <c r="E33" s="254"/>
+      <c r="F33" s="255"/>
+      <c r="G33" s="242" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="282"/>
-      <c r="I33" s="282"/>
-      <c r="J33" s="282"/>
-      <c r="K33" s="282"/>
-      <c r="L33" s="18" t="s">
+      <c r="H33" s="242"/>
+      <c r="I33" s="242"/>
+      <c r="J33" s="242"/>
+      <c r="K33" s="242"/>
+      <c r="L33" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="M33" s="19" t="s">
+      <c r="M33" s="18" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="83"/>
-      <c r="B34" s="80"/>
-      <c r="C34" s="81"/>
-      <c r="D34" s="80" t="s">
+      <c r="A34" s="76"/>
+      <c r="B34" s="73"/>
+      <c r="C34" s="74"/>
+      <c r="D34" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="E34" s="81"/>
-      <c r="F34" s="80"/>
-      <c r="G34" s="283"/>
-      <c r="H34" s="284"/>
-      <c r="I34" s="284"/>
-      <c r="J34" s="284"/>
-      <c r="K34" s="285"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="21"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="73"/>
+      <c r="G34" s="243"/>
+      <c r="H34" s="244"/>
+      <c r="I34" s="244"/>
+      <c r="J34" s="244"/>
+      <c r="K34" s="245"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="20"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" s="83"/>
-      <c r="B35" s="80"/>
-      <c r="C35" s="80"/>
-      <c r="D35" s="80"/>
-      <c r="E35" s="80"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="283"/>
-      <c r="H35" s="284"/>
-      <c r="I35" s="284"/>
-      <c r="J35" s="284"/>
-      <c r="K35" s="285"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="21"/>
+      <c r="A35" s="76"/>
+      <c r="B35" s="73"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="243"/>
+      <c r="H35" s="244"/>
+      <c r="I35" s="244"/>
+      <c r="J35" s="244"/>
+      <c r="K35" s="245"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="20"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" s="83"/>
-      <c r="B36" s="80"/>
-      <c r="C36" s="80"/>
-      <c r="D36" s="80"/>
-      <c r="E36" s="80"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="283"/>
-      <c r="H36" s="284"/>
-      <c r="I36" s="284"/>
-      <c r="J36" s="284"/>
-      <c r="K36" s="285"/>
-      <c r="L36" s="20"/>
-      <c r="M36" s="21"/>
+      <c r="A36" s="76"/>
+      <c r="B36" s="73"/>
+      <c r="C36" s="73"/>
+      <c r="D36" s="73"/>
+      <c r="E36" s="73"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="243"/>
+      <c r="H36" s="244"/>
+      <c r="I36" s="244"/>
+      <c r="J36" s="244"/>
+      <c r="K36" s="245"/>
+      <c r="L36" s="19"/>
+      <c r="M36" s="20"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A37" s="83"/>
-      <c r="B37" s="80"/>
-      <c r="C37" s="80"/>
-      <c r="D37" s="80"/>
-      <c r="E37" s="80"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="283"/>
-      <c r="H37" s="284"/>
-      <c r="I37" s="284"/>
-      <c r="J37" s="284"/>
-      <c r="K37" s="285"/>
-      <c r="L37" s="20"/>
-      <c r="M37" s="21"/>
-      <c r="Q37" s="286"/>
-      <c r="R37" s="286"/>
-      <c r="S37" s="22"/>
-      <c r="T37" s="310"/>
-      <c r="U37" s="310"/>
-      <c r="V37" s="310"/>
+      <c r="A37" s="76"/>
+      <c r="B37" s="73"/>
+      <c r="C37" s="73"/>
+      <c r="D37" s="73"/>
+      <c r="E37" s="73"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="243"/>
+      <c r="H37" s="244"/>
+      <c r="I37" s="244"/>
+      <c r="J37" s="244"/>
+      <c r="K37" s="245"/>
+      <c r="L37" s="19"/>
+      <c r="M37" s="20"/>
+      <c r="Q37" s="246"/>
+      <c r="R37" s="246"/>
+      <c r="S37" s="21"/>
+      <c r="T37" s="270"/>
+      <c r="U37" s="270"/>
+      <c r="V37" s="270"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A38" s="83"/>
-      <c r="B38" s="80"/>
-      <c r="C38" s="80"/>
-      <c r="D38" s="80"/>
-      <c r="E38" s="80"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="283"/>
-      <c r="H38" s="284"/>
-      <c r="I38" s="284"/>
-      <c r="J38" s="284"/>
-      <c r="K38" s="285"/>
-      <c r="L38" s="20"/>
-      <c r="M38" s="24"/>
-      <c r="Q38" s="286"/>
-      <c r="R38" s="286"/>
-      <c r="S38" s="22"/>
-      <c r="T38" s="310"/>
-      <c r="U38" s="310"/>
-      <c r="V38" s="310"/>
+      <c r="A38" s="76"/>
+      <c r="B38" s="73"/>
+      <c r="C38" s="73"/>
+      <c r="D38" s="73"/>
+      <c r="E38" s="73"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="243"/>
+      <c r="H38" s="244"/>
+      <c r="I38" s="244"/>
+      <c r="J38" s="244"/>
+      <c r="K38" s="245"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="23"/>
+      <c r="Q38" s="246"/>
+      <c r="R38" s="246"/>
+      <c r="S38" s="21"/>
+      <c r="T38" s="270"/>
+      <c r="U38" s="270"/>
+      <c r="V38" s="270"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A39" s="83"/>
-      <c r="B39" s="80"/>
-      <c r="C39" s="80"/>
-      <c r="D39" s="80"/>
-      <c r="E39" s="80"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="283"/>
-      <c r="H39" s="284"/>
-      <c r="I39" s="284"/>
-      <c r="J39" s="284"/>
-      <c r="K39" s="285"/>
-      <c r="L39" s="20"/>
-      <c r="M39" s="24"/>
-      <c r="Q39" s="25"/>
-      <c r="R39" s="25"/>
-      <c r="S39" s="311"/>
-      <c r="T39" s="310"/>
-      <c r="U39" s="310"/>
-      <c r="V39" s="310"/>
+      <c r="A39" s="76"/>
+      <c r="B39" s="73"/>
+      <c r="C39" s="73"/>
+      <c r="D39" s="73"/>
+      <c r="E39" s="73"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="243"/>
+      <c r="H39" s="244"/>
+      <c r="I39" s="244"/>
+      <c r="J39" s="244"/>
+      <c r="K39" s="245"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="23"/>
+      <c r="Q39" s="24"/>
+      <c r="R39" s="24"/>
+      <c r="S39" s="271"/>
+      <c r="T39" s="270"/>
+      <c r="U39" s="270"/>
+      <c r="V39" s="270"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A40" s="83"/>
-      <c r="B40" s="80"/>
-      <c r="C40" s="80"/>
-      <c r="D40" s="80"/>
-      <c r="E40" s="80"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="283"/>
-      <c r="H40" s="284"/>
-      <c r="I40" s="284"/>
-      <c r="J40" s="284"/>
-      <c r="K40" s="285"/>
-      <c r="L40" s="20"/>
-      <c r="M40" s="21"/>
-      <c r="Q40" s="25"/>
-      <c r="R40" s="25"/>
-      <c r="S40" s="311"/>
-      <c r="T40" s="310"/>
-      <c r="U40" s="310"/>
-      <c r="V40" s="310"/>
+      <c r="A40" s="76"/>
+      <c r="B40" s="73"/>
+      <c r="C40" s="73"/>
+      <c r="D40" s="73"/>
+      <c r="E40" s="73"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="243"/>
+      <c r="H40" s="244"/>
+      <c r="I40" s="244"/>
+      <c r="J40" s="244"/>
+      <c r="K40" s="245"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="20"/>
+      <c r="Q40" s="24"/>
+      <c r="R40" s="24"/>
+      <c r="S40" s="271"/>
+      <c r="T40" s="270"/>
+      <c r="U40" s="270"/>
+      <c r="V40" s="270"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A41" s="83"/>
-      <c r="B41" s="80"/>
-      <c r="C41" s="80"/>
-      <c r="D41" s="80"/>
-      <c r="E41" s="80"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="283"/>
-      <c r="H41" s="284"/>
-      <c r="I41" s="284"/>
-      <c r="J41" s="284"/>
-      <c r="K41" s="285"/>
-      <c r="L41" s="20"/>
-      <c r="M41" s="21"/>
+      <c r="A41" s="76"/>
+      <c r="B41" s="73"/>
+      <c r="C41" s="73"/>
+      <c r="D41" s="73"/>
+      <c r="E41" s="73"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="243"/>
+      <c r="H41" s="244"/>
+      <c r="I41" s="244"/>
+      <c r="J41" s="244"/>
+      <c r="K41" s="245"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="20"/>
     </row>
     <row r="42" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="84"/>
-      <c r="B42" s="85"/>
-      <c r="C42" s="86"/>
-      <c r="D42" s="85"/>
-      <c r="E42" s="86"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="350" t="s">
+      <c r="A42" s="77"/>
+      <c r="B42" s="78"/>
+      <c r="C42" s="79"/>
+      <c r="D42" s="78"/>
+      <c r="E42" s="79"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="310" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="351"/>
-      <c r="I42" s="351"/>
-      <c r="J42" s="351"/>
-      <c r="K42" s="352"/>
-      <c r="L42" s="26"/>
-      <c r="M42" s="27"/>
+      <c r="H42" s="311"/>
+      <c r="I42" s="311"/>
+      <c r="J42" s="311"/>
+      <c r="K42" s="312"/>
+      <c r="L42" s="25"/>
+      <c r="M42" s="26"/>
     </row>
     <row r="43" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="330" t="s">
+      <c r="A43" s="290" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="331"/>
-      <c r="C43" s="331"/>
-      <c r="D43" s="331"/>
-      <c r="E43" s="331"/>
-      <c r="F43" s="331"/>
-      <c r="G43" s="331"/>
-      <c r="H43" s="332"/>
-      <c r="I43" s="353" t="s">
+      <c r="B43" s="291"/>
+      <c r="C43" s="291"/>
+      <c r="D43" s="291"/>
+      <c r="E43" s="291"/>
+      <c r="F43" s="291"/>
+      <c r="G43" s="291"/>
+      <c r="H43" s="292"/>
+      <c r="I43" s="313" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="354"/>
-      <c r="K43" s="354"/>
-      <c r="L43" s="354"/>
-      <c r="M43" s="355"/>
+      <c r="J43" s="314"/>
+      <c r="K43" s="314"/>
+      <c r="L43" s="314"/>
+      <c r="M43" s="315"/>
     </row>
     <row r="44" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="333"/>
-      <c r="B44" s="334"/>
-      <c r="C44" s="334"/>
-      <c r="D44" s="334"/>
-      <c r="E44" s="334"/>
-      <c r="F44" s="334"/>
-      <c r="G44" s="334"/>
-      <c r="H44" s="335"/>
-      <c r="I44" s="356"/>
-      <c r="J44" s="357"/>
-      <c r="K44" s="357"/>
-      <c r="L44" s="357"/>
-      <c r="M44" s="358"/>
+      <c r="A44" s="293"/>
+      <c r="B44" s="294"/>
+      <c r="C44" s="294"/>
+      <c r="D44" s="294"/>
+      <c r="E44" s="294"/>
+      <c r="F44" s="294"/>
+      <c r="G44" s="294"/>
+      <c r="H44" s="295"/>
+      <c r="I44" s="316"/>
+      <c r="J44" s="317"/>
+      <c r="K44" s="317"/>
+      <c r="L44" s="317"/>
+      <c r="M44" s="318"/>
     </row>
     <row r="45" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="298" t="s">
+      <c r="A45" s="258" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="299"/>
-      <c r="C45" s="299"/>
-      <c r="D45" s="299"/>
-      <c r="E45" s="299"/>
-      <c r="F45" s="299"/>
-      <c r="G45" s="299"/>
-      <c r="H45" s="300"/>
-      <c r="I45" s="301" t="s">
+      <c r="B45" s="259"/>
+      <c r="C45" s="259"/>
+      <c r="D45" s="259"/>
+      <c r="E45" s="259"/>
+      <c r="F45" s="259"/>
+      <c r="G45" s="259"/>
+      <c r="H45" s="260"/>
+      <c r="I45" s="261" t="s">
         <v>36</v>
       </c>
-      <c r="J45" s="302"/>
-      <c r="K45" s="302"/>
-      <c r="L45" s="302"/>
-      <c r="M45" s="303"/>
+      <c r="J45" s="262"/>
+      <c r="K45" s="262"/>
+      <c r="L45" s="262"/>
+      <c r="M45" s="263"/>
     </row>
     <row r="46" spans="1:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="298" t="s">
+      <c r="A46" s="258" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="299"/>
-      <c r="C46" s="299"/>
-      <c r="D46" s="299"/>
-      <c r="E46" s="299"/>
-      <c r="F46" s="299"/>
-      <c r="G46" s="299"/>
-      <c r="H46" s="300"/>
-      <c r="I46" s="301"/>
-      <c r="J46" s="302"/>
-      <c r="K46" s="302"/>
-      <c r="L46" s="302"/>
-      <c r="M46" s="303"/>
+      <c r="B46" s="259"/>
+      <c r="C46" s="259"/>
+      <c r="D46" s="259"/>
+      <c r="E46" s="259"/>
+      <c r="F46" s="259"/>
+      <c r="G46" s="259"/>
+      <c r="H46" s="260"/>
+      <c r="I46" s="261"/>
+      <c r="J46" s="262"/>
+      <c r="K46" s="262"/>
+      <c r="L46" s="262"/>
+      <c r="M46" s="263"/>
     </row>
     <row r="47" spans="1:22" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="304"/>
-      <c r="B47" s="305"/>
-      <c r="C47" s="305"/>
-      <c r="D47" s="305"/>
-      <c r="E47" s="305"/>
-      <c r="F47" s="305"/>
-      <c r="G47" s="305"/>
-      <c r="H47" s="306"/>
-      <c r="I47" s="307" t="s">
+      <c r="A47" s="264"/>
+      <c r="B47" s="265"/>
+      <c r="C47" s="265"/>
+      <c r="D47" s="265"/>
+      <c r="E47" s="265"/>
+      <c r="F47" s="265"/>
+      <c r="G47" s="265"/>
+      <c r="H47" s="266"/>
+      <c r="I47" s="267" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="308"/>
-      <c r="K47" s="308"/>
-      <c r="L47" s="308"/>
-      <c r="M47" s="309"/>
+      <c r="J47" s="268"/>
+      <c r="K47" s="268"/>
+      <c r="L47" s="268"/>
+      <c r="M47" s="269"/>
     </row>
     <row r="48" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="327" t="s">
+      <c r="A48" s="287" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="328"/>
-      <c r="C48" s="328"/>
-      <c r="D48" s="328"/>
-      <c r="E48" s="328"/>
-      <c r="F48" s="328"/>
-      <c r="G48" s="328"/>
-      <c r="H48" s="328"/>
-      <c r="I48" s="328"/>
-      <c r="J48" s="328"/>
-      <c r="K48" s="328"/>
-      <c r="L48" s="328"/>
-      <c r="M48" s="329"/>
+      <c r="B48" s="288"/>
+      <c r="C48" s="288"/>
+      <c r="D48" s="288"/>
+      <c r="E48" s="288"/>
+      <c r="F48" s="288"/>
+      <c r="G48" s="288"/>
+      <c r="H48" s="288"/>
+      <c r="I48" s="288"/>
+      <c r="J48" s="288"/>
+      <c r="K48" s="288"/>
+      <c r="L48" s="288"/>
+      <c r="M48" s="289"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="330" t="s">
+      <c r="A49" s="290" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="331"/>
-      <c r="C49" s="331"/>
-      <c r="D49" s="331"/>
-      <c r="E49" s="331"/>
-      <c r="F49" s="331"/>
-      <c r="G49" s="331"/>
-      <c r="H49" s="332"/>
-      <c r="I49" s="338" t="s">
+      <c r="B49" s="291"/>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="291"/>
+      <c r="G49" s="291"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="298" t="s">
         <v>40</v>
       </c>
-      <c r="J49" s="339"/>
-      <c r="K49" s="339"/>
-      <c r="L49" s="339"/>
-      <c r="M49" s="340"/>
+      <c r="J49" s="299"/>
+      <c r="K49" s="299"/>
+      <c r="L49" s="299"/>
+      <c r="M49" s="300"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="333"/>
-      <c r="B50" s="334"/>
-      <c r="C50" s="334"/>
-      <c r="D50" s="334"/>
-      <c r="E50" s="334"/>
-      <c r="F50" s="334"/>
-      <c r="G50" s="334"/>
-      <c r="H50" s="335"/>
-      <c r="I50" s="341"/>
-      <c r="J50" s="342"/>
-      <c r="K50" s="342"/>
-      <c r="L50" s="342"/>
-      <c r="M50" s="343"/>
+      <c r="A50" s="293"/>
+      <c r="B50" s="294"/>
+      <c r="C50" s="294"/>
+      <c r="D50" s="294"/>
+      <c r="E50" s="294"/>
+      <c r="F50" s="294"/>
+      <c r="G50" s="294"/>
+      <c r="H50" s="295"/>
+      <c r="I50" s="301"/>
+      <c r="J50" s="302"/>
+      <c r="K50" s="302"/>
+      <c r="L50" s="302"/>
+      <c r="M50" s="303"/>
     </row>
     <row r="51" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="336"/>
-      <c r="B51" s="337"/>
-      <c r="C51" s="337"/>
-      <c r="D51" s="337"/>
-      <c r="E51" s="334"/>
-      <c r="F51" s="334"/>
-      <c r="G51" s="334"/>
-      <c r="H51" s="335"/>
-      <c r="I51" s="344" t="s">
+      <c r="A51" s="296"/>
+      <c r="B51" s="297"/>
+      <c r="C51" s="297"/>
+      <c r="D51" s="297"/>
+      <c r="E51" s="294"/>
+      <c r="F51" s="294"/>
+      <c r="G51" s="294"/>
+      <c r="H51" s="295"/>
+      <c r="I51" s="304" t="s">
         <v>41</v>
       </c>
-      <c r="J51" s="345"/>
-      <c r="K51" s="346"/>
-      <c r="L51" s="346"/>
-      <c r="M51" s="347"/>
+      <c r="J51" s="305"/>
+      <c r="K51" s="306"/>
+      <c r="L51" s="306"/>
+      <c r="M51" s="307"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="327" t="s">
+      <c r="A52" s="287" t="s">
         <v>42</v>
       </c>
-      <c r="B52" s="328"/>
-      <c r="C52" s="328"/>
-      <c r="D52" s="328"/>
-      <c r="E52" s="87" t="s">
+      <c r="B52" s="288"/>
+      <c r="C52" s="288"/>
+      <c r="D52" s="288"/>
+      <c r="E52" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="F52" s="88"/>
-      <c r="G52" s="348" t="s">
+      <c r="F52" s="81"/>
+      <c r="G52" s="308" t="s">
         <v>45</v>
       </c>
-      <c r="H52" s="348"/>
-      <c r="I52" s="348"/>
-      <c r="J52" s="349"/>
-      <c r="K52" s="328" t="s">
+      <c r="H52" s="308"/>
+      <c r="I52" s="308"/>
+      <c r="J52" s="309"/>
+      <c r="K52" s="288" t="s">
         <v>50</v>
       </c>
-      <c r="L52" s="328"/>
-      <c r="M52" s="329"/>
+      <c r="L52" s="288"/>
+      <c r="M52" s="289"/>
     </row>
     <row r="53" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="317" t="s">
+      <c r="A53" s="277" t="s">
         <v>43</v>
       </c>
-      <c r="B53" s="318"/>
-      <c r="C53" s="318"/>
-      <c r="D53" s="318"/>
-      <c r="E53" s="89"/>
-      <c r="F53" s="82"/>
-      <c r="G53" s="82"/>
-      <c r="H53" s="82"/>
-      <c r="I53" s="82"/>
-      <c r="J53" s="90"/>
-      <c r="K53" s="318" t="s">
+      <c r="B53" s="278"/>
+      <c r="C53" s="278"/>
+      <c r="D53" s="278"/>
+      <c r="E53" s="82"/>
+      <c r="F53" s="75"/>
+      <c r="G53" s="75"/>
+      <c r="H53" s="75"/>
+      <c r="I53" s="75"/>
+      <c r="J53" s="83"/>
+      <c r="K53" s="278" t="s">
         <v>52</v>
       </c>
-      <c r="L53" s="318"/>
-      <c r="M53" s="319"/>
+      <c r="L53" s="278"/>
+      <c r="M53" s="279"/>
     </row>
     <row r="54" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="317"/>
-      <c r="B54" s="318"/>
-      <c r="C54" s="318"/>
-      <c r="D54" s="318"/>
-      <c r="E54" s="320" t="s">
+      <c r="A54" s="277"/>
+      <c r="B54" s="278"/>
+      <c r="C54" s="278"/>
+      <c r="D54" s="278"/>
+      <c r="E54" s="280" t="s">
         <v>46</v>
       </c>
-      <c r="F54" s="321"/>
-      <c r="G54" s="91"/>
-      <c r="H54" s="312" t="s">
+      <c r="F54" s="281"/>
+      <c r="G54" s="84"/>
+      <c r="H54" s="272" t="s">
         <v>46</v>
       </c>
-      <c r="I54" s="312"/>
-      <c r="J54" s="313"/>
-      <c r="K54" s="318"/>
-      <c r="L54" s="318"/>
-      <c r="M54" s="319"/>
+      <c r="I54" s="272"/>
+      <c r="J54" s="273"/>
+      <c r="K54" s="278"/>
+      <c r="L54" s="278"/>
+      <c r="M54" s="279"/>
     </row>
     <row r="55" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="317"/>
-      <c r="B55" s="318"/>
-      <c r="C55" s="318"/>
-      <c r="D55" s="318"/>
-      <c r="E55" s="320" t="s">
+      <c r="A55" s="277"/>
+      <c r="B55" s="278"/>
+      <c r="C55" s="278"/>
+      <c r="D55" s="278"/>
+      <c r="E55" s="280" t="s">
         <v>47</v>
       </c>
-      <c r="F55" s="321"/>
-      <c r="G55" s="321"/>
-      <c r="H55" s="312" t="s">
+      <c r="F55" s="281"/>
+      <c r="G55" s="281"/>
+      <c r="H55" s="272" t="s">
         <v>48</v>
       </c>
-      <c r="I55" s="312"/>
-      <c r="J55" s="313"/>
-      <c r="K55" s="318"/>
-      <c r="L55" s="318"/>
-      <c r="M55" s="319"/>
+      <c r="I55" s="272"/>
+      <c r="J55" s="273"/>
+      <c r="K55" s="278"/>
+      <c r="L55" s="278"/>
+      <c r="M55" s="279"/>
     </row>
     <row r="56" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="270"/>
-      <c r="B56" s="244"/>
-      <c r="C56" s="244"/>
-      <c r="D56" s="245"/>
-      <c r="E56" s="320"/>
-      <c r="F56" s="321"/>
-      <c r="G56" s="321"/>
-      <c r="H56" s="312"/>
-      <c r="I56" s="312"/>
-      <c r="J56" s="313"/>
-      <c r="K56" s="325" t="s">
+      <c r="A56" s="230"/>
+      <c r="B56" s="204"/>
+      <c r="C56" s="204"/>
+      <c r="D56" s="205"/>
+      <c r="E56" s="280"/>
+      <c r="F56" s="281"/>
+      <c r="G56" s="281"/>
+      <c r="H56" s="272"/>
+      <c r="I56" s="272"/>
+      <c r="J56" s="273"/>
+      <c r="K56" s="285" t="s">
         <v>51</v>
       </c>
-      <c r="L56" s="325"/>
-      <c r="M56" s="326"/>
+      <c r="L56" s="285"/>
+      <c r="M56" s="286"/>
     </row>
     <row r="57" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="270"/>
-      <c r="B57" s="244"/>
-      <c r="C57" s="244"/>
-      <c r="D57" s="245"/>
-      <c r="E57" s="320"/>
-      <c r="F57" s="321"/>
-      <c r="G57" s="91"/>
-      <c r="H57" s="312" t="s">
+      <c r="A57" s="230"/>
+      <c r="B57" s="204"/>
+      <c r="C57" s="204"/>
+      <c r="D57" s="205"/>
+      <c r="E57" s="280"/>
+      <c r="F57" s="281"/>
+      <c r="G57" s="84"/>
+      <c r="H57" s="272" t="s">
         <v>49</v>
       </c>
-      <c r="I57" s="312"/>
-      <c r="J57" s="313"/>
-      <c r="K57" s="92"/>
-      <c r="L57" s="93"/>
-      <c r="M57" s="94"/>
+      <c r="I57" s="272"/>
+      <c r="J57" s="273"/>
+      <c r="K57" s="85"/>
+      <c r="L57" s="86"/>
+      <c r="M57" s="87"/>
     </row>
     <row r="58" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="322"/>
-      <c r="B58" s="323"/>
-      <c r="C58" s="323"/>
-      <c r="D58" s="324"/>
-      <c r="E58" s="275"/>
-      <c r="F58" s="276"/>
-      <c r="G58" s="276"/>
-      <c r="H58" s="276"/>
-      <c r="I58" s="276"/>
-      <c r="J58" s="314"/>
-      <c r="K58" s="95"/>
-      <c r="L58" s="96"/>
-      <c r="M58" s="97"/>
+      <c r="A58" s="282"/>
+      <c r="B58" s="283"/>
+      <c r="C58" s="283"/>
+      <c r="D58" s="284"/>
+      <c r="E58" s="235"/>
+      <c r="F58" s="236"/>
+      <c r="G58" s="236"/>
+      <c r="H58" s="236"/>
+      <c r="I58" s="236"/>
+      <c r="J58" s="274"/>
+      <c r="K58" s="88"/>
+      <c r="L58" s="89"/>
+      <c r="M58" s="90"/>
     </row>
     <row r="59" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="28"/>
-      <c r="B59" s="28"/>
-      <c r="C59" s="28"/>
-      <c r="D59" s="28"/>
-      <c r="E59" s="25"/>
-      <c r="F59" s="25"/>
-      <c r="G59" s="25"/>
-      <c r="H59" s="23"/>
-      <c r="I59" s="23"/>
-      <c r="J59" s="23"/>
+      <c r="A59" s="27"/>
+      <c r="B59" s="27"/>
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="24"/>
+      <c r="G59" s="24"/>
+      <c r="H59" s="22"/>
+      <c r="I59" s="22"/>
+      <c r="J59" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="111">
@@ -5649,1731 +5678,1731 @@
   <dimension ref="A1:M61"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="4" width="7.42578125" style="11" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="11"/>
-    <col min="6" max="6" width="5.5703125" style="11" customWidth="1"/>
-    <col min="7" max="7" width="3.5703125" style="11" customWidth="1"/>
-    <col min="8" max="8" width="5.140625" style="11" customWidth="1"/>
-    <col min="9" max="9" width="5.42578125" style="11" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="11"/>
-    <col min="11" max="11" width="17.140625" style="11" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" style="11"/>
-    <col min="13" max="13" width="9" style="11" customWidth="1"/>
-    <col min="14" max="256" width="9.140625" style="11"/>
-    <col min="257" max="260" width="7.42578125" style="11" customWidth="1"/>
-    <col min="261" max="261" width="9.140625" style="11"/>
-    <col min="262" max="262" width="5.5703125" style="11" customWidth="1"/>
-    <col min="263" max="263" width="3.5703125" style="11" customWidth="1"/>
-    <col min="264" max="264" width="5.140625" style="11" customWidth="1"/>
-    <col min="265" max="265" width="5.42578125" style="11" customWidth="1"/>
-    <col min="266" max="266" width="9.140625" style="11"/>
-    <col min="267" max="267" width="17.140625" style="11" customWidth="1"/>
-    <col min="268" max="268" width="9.140625" style="11"/>
-    <col min="269" max="269" width="9" style="11" customWidth="1"/>
-    <col min="270" max="512" width="9.140625" style="11"/>
-    <col min="513" max="516" width="7.42578125" style="11" customWidth="1"/>
-    <col min="517" max="517" width="9.140625" style="11"/>
-    <col min="518" max="518" width="5.5703125" style="11" customWidth="1"/>
-    <col min="519" max="519" width="3.5703125" style="11" customWidth="1"/>
-    <col min="520" max="520" width="5.140625" style="11" customWidth="1"/>
-    <col min="521" max="521" width="5.42578125" style="11" customWidth="1"/>
-    <col min="522" max="522" width="9.140625" style="11"/>
-    <col min="523" max="523" width="17.140625" style="11" customWidth="1"/>
-    <col min="524" max="524" width="9.140625" style="11"/>
-    <col min="525" max="525" width="9" style="11" customWidth="1"/>
-    <col min="526" max="768" width="9.140625" style="11"/>
-    <col min="769" max="772" width="7.42578125" style="11" customWidth="1"/>
-    <col min="773" max="773" width="9.140625" style="11"/>
-    <col min="774" max="774" width="5.5703125" style="11" customWidth="1"/>
-    <col min="775" max="775" width="3.5703125" style="11" customWidth="1"/>
-    <col min="776" max="776" width="5.140625" style="11" customWidth="1"/>
-    <col min="777" max="777" width="5.42578125" style="11" customWidth="1"/>
-    <col min="778" max="778" width="9.140625" style="11"/>
-    <col min="779" max="779" width="17.140625" style="11" customWidth="1"/>
-    <col min="780" max="780" width="9.140625" style="11"/>
-    <col min="781" max="781" width="9" style="11" customWidth="1"/>
-    <col min="782" max="1024" width="9.140625" style="11"/>
-    <col min="1025" max="1028" width="7.42578125" style="11" customWidth="1"/>
-    <col min="1029" max="1029" width="9.140625" style="11"/>
-    <col min="1030" max="1030" width="5.5703125" style="11" customWidth="1"/>
-    <col min="1031" max="1031" width="3.5703125" style="11" customWidth="1"/>
-    <col min="1032" max="1032" width="5.140625" style="11" customWidth="1"/>
-    <col min="1033" max="1033" width="5.42578125" style="11" customWidth="1"/>
-    <col min="1034" max="1034" width="9.140625" style="11"/>
-    <col min="1035" max="1035" width="17.140625" style="11" customWidth="1"/>
-    <col min="1036" max="1036" width="9.140625" style="11"/>
-    <col min="1037" max="1037" width="9" style="11" customWidth="1"/>
-    <col min="1038" max="1280" width="9.140625" style="11"/>
-    <col min="1281" max="1284" width="7.42578125" style="11" customWidth="1"/>
-    <col min="1285" max="1285" width="9.140625" style="11"/>
-    <col min="1286" max="1286" width="5.5703125" style="11" customWidth="1"/>
-    <col min="1287" max="1287" width="3.5703125" style="11" customWidth="1"/>
-    <col min="1288" max="1288" width="5.140625" style="11" customWidth="1"/>
-    <col min="1289" max="1289" width="5.42578125" style="11" customWidth="1"/>
-    <col min="1290" max="1290" width="9.140625" style="11"/>
-    <col min="1291" max="1291" width="17.140625" style="11" customWidth="1"/>
-    <col min="1292" max="1292" width="9.140625" style="11"/>
-    <col min="1293" max="1293" width="9" style="11" customWidth="1"/>
-    <col min="1294" max="1536" width="9.140625" style="11"/>
-    <col min="1537" max="1540" width="7.42578125" style="11" customWidth="1"/>
-    <col min="1541" max="1541" width="9.140625" style="11"/>
-    <col min="1542" max="1542" width="5.5703125" style="11" customWidth="1"/>
-    <col min="1543" max="1543" width="3.5703125" style="11" customWidth="1"/>
-    <col min="1544" max="1544" width="5.140625" style="11" customWidth="1"/>
-    <col min="1545" max="1545" width="5.42578125" style="11" customWidth="1"/>
-    <col min="1546" max="1546" width="9.140625" style="11"/>
-    <col min="1547" max="1547" width="17.140625" style="11" customWidth="1"/>
-    <col min="1548" max="1548" width="9.140625" style="11"/>
-    <col min="1549" max="1549" width="9" style="11" customWidth="1"/>
-    <col min="1550" max="1792" width="9.140625" style="11"/>
-    <col min="1793" max="1796" width="7.42578125" style="11" customWidth="1"/>
-    <col min="1797" max="1797" width="9.140625" style="11"/>
-    <col min="1798" max="1798" width="5.5703125" style="11" customWidth="1"/>
-    <col min="1799" max="1799" width="3.5703125" style="11" customWidth="1"/>
-    <col min="1800" max="1800" width="5.140625" style="11" customWidth="1"/>
-    <col min="1801" max="1801" width="5.42578125" style="11" customWidth="1"/>
-    <col min="1802" max="1802" width="9.140625" style="11"/>
-    <col min="1803" max="1803" width="17.140625" style="11" customWidth="1"/>
-    <col min="1804" max="1804" width="9.140625" style="11"/>
-    <col min="1805" max="1805" width="9" style="11" customWidth="1"/>
-    <col min="1806" max="2048" width="9.140625" style="11"/>
-    <col min="2049" max="2052" width="7.42578125" style="11" customWidth="1"/>
-    <col min="2053" max="2053" width="9.140625" style="11"/>
-    <col min="2054" max="2054" width="5.5703125" style="11" customWidth="1"/>
-    <col min="2055" max="2055" width="3.5703125" style="11" customWidth="1"/>
-    <col min="2056" max="2056" width="5.140625" style="11" customWidth="1"/>
-    <col min="2057" max="2057" width="5.42578125" style="11" customWidth="1"/>
-    <col min="2058" max="2058" width="9.140625" style="11"/>
-    <col min="2059" max="2059" width="17.140625" style="11" customWidth="1"/>
-    <col min="2060" max="2060" width="9.140625" style="11"/>
-    <col min="2061" max="2061" width="9" style="11" customWidth="1"/>
-    <col min="2062" max="2304" width="9.140625" style="11"/>
-    <col min="2305" max="2308" width="7.42578125" style="11" customWidth="1"/>
-    <col min="2309" max="2309" width="9.140625" style="11"/>
-    <col min="2310" max="2310" width="5.5703125" style="11" customWidth="1"/>
-    <col min="2311" max="2311" width="3.5703125" style="11" customWidth="1"/>
-    <col min="2312" max="2312" width="5.140625" style="11" customWidth="1"/>
-    <col min="2313" max="2313" width="5.42578125" style="11" customWidth="1"/>
-    <col min="2314" max="2314" width="9.140625" style="11"/>
-    <col min="2315" max="2315" width="17.140625" style="11" customWidth="1"/>
-    <col min="2316" max="2316" width="9.140625" style="11"/>
-    <col min="2317" max="2317" width="9" style="11" customWidth="1"/>
-    <col min="2318" max="2560" width="9.140625" style="11"/>
-    <col min="2561" max="2564" width="7.42578125" style="11" customWidth="1"/>
-    <col min="2565" max="2565" width="9.140625" style="11"/>
-    <col min="2566" max="2566" width="5.5703125" style="11" customWidth="1"/>
-    <col min="2567" max="2567" width="3.5703125" style="11" customWidth="1"/>
-    <col min="2568" max="2568" width="5.140625" style="11" customWidth="1"/>
-    <col min="2569" max="2569" width="5.42578125" style="11" customWidth="1"/>
-    <col min="2570" max="2570" width="9.140625" style="11"/>
-    <col min="2571" max="2571" width="17.140625" style="11" customWidth="1"/>
-    <col min="2572" max="2572" width="9.140625" style="11"/>
-    <col min="2573" max="2573" width="9" style="11" customWidth="1"/>
-    <col min="2574" max="2816" width="9.140625" style="11"/>
-    <col min="2817" max="2820" width="7.42578125" style="11" customWidth="1"/>
-    <col min="2821" max="2821" width="9.140625" style="11"/>
-    <col min="2822" max="2822" width="5.5703125" style="11" customWidth="1"/>
-    <col min="2823" max="2823" width="3.5703125" style="11" customWidth="1"/>
-    <col min="2824" max="2824" width="5.140625" style="11" customWidth="1"/>
-    <col min="2825" max="2825" width="5.42578125" style="11" customWidth="1"/>
-    <col min="2826" max="2826" width="9.140625" style="11"/>
-    <col min="2827" max="2827" width="17.140625" style="11" customWidth="1"/>
-    <col min="2828" max="2828" width="9.140625" style="11"/>
-    <col min="2829" max="2829" width="9" style="11" customWidth="1"/>
-    <col min="2830" max="3072" width="9.140625" style="11"/>
-    <col min="3073" max="3076" width="7.42578125" style="11" customWidth="1"/>
-    <col min="3077" max="3077" width="9.140625" style="11"/>
-    <col min="3078" max="3078" width="5.5703125" style="11" customWidth="1"/>
-    <col min="3079" max="3079" width="3.5703125" style="11" customWidth="1"/>
-    <col min="3080" max="3080" width="5.140625" style="11" customWidth="1"/>
-    <col min="3081" max="3081" width="5.42578125" style="11" customWidth="1"/>
-    <col min="3082" max="3082" width="9.140625" style="11"/>
-    <col min="3083" max="3083" width="17.140625" style="11" customWidth="1"/>
-    <col min="3084" max="3084" width="9.140625" style="11"/>
-    <col min="3085" max="3085" width="9" style="11" customWidth="1"/>
-    <col min="3086" max="3328" width="9.140625" style="11"/>
-    <col min="3329" max="3332" width="7.42578125" style="11" customWidth="1"/>
-    <col min="3333" max="3333" width="9.140625" style="11"/>
-    <col min="3334" max="3334" width="5.5703125" style="11" customWidth="1"/>
-    <col min="3335" max="3335" width="3.5703125" style="11" customWidth="1"/>
-    <col min="3336" max="3336" width="5.140625" style="11" customWidth="1"/>
-    <col min="3337" max="3337" width="5.42578125" style="11" customWidth="1"/>
-    <col min="3338" max="3338" width="9.140625" style="11"/>
-    <col min="3339" max="3339" width="17.140625" style="11" customWidth="1"/>
-    <col min="3340" max="3340" width="9.140625" style="11"/>
-    <col min="3341" max="3341" width="9" style="11" customWidth="1"/>
-    <col min="3342" max="3584" width="9.140625" style="11"/>
-    <col min="3585" max="3588" width="7.42578125" style="11" customWidth="1"/>
-    <col min="3589" max="3589" width="9.140625" style="11"/>
-    <col min="3590" max="3590" width="5.5703125" style="11" customWidth="1"/>
-    <col min="3591" max="3591" width="3.5703125" style="11" customWidth="1"/>
-    <col min="3592" max="3592" width="5.140625" style="11" customWidth="1"/>
-    <col min="3593" max="3593" width="5.42578125" style="11" customWidth="1"/>
-    <col min="3594" max="3594" width="9.140625" style="11"/>
-    <col min="3595" max="3595" width="17.140625" style="11" customWidth="1"/>
-    <col min="3596" max="3596" width="9.140625" style="11"/>
-    <col min="3597" max="3597" width="9" style="11" customWidth="1"/>
-    <col min="3598" max="3840" width="9.140625" style="11"/>
-    <col min="3841" max="3844" width="7.42578125" style="11" customWidth="1"/>
-    <col min="3845" max="3845" width="9.140625" style="11"/>
-    <col min="3846" max="3846" width="5.5703125" style="11" customWidth="1"/>
-    <col min="3847" max="3847" width="3.5703125" style="11" customWidth="1"/>
-    <col min="3848" max="3848" width="5.140625" style="11" customWidth="1"/>
-    <col min="3849" max="3849" width="5.42578125" style="11" customWidth="1"/>
-    <col min="3850" max="3850" width="9.140625" style="11"/>
-    <col min="3851" max="3851" width="17.140625" style="11" customWidth="1"/>
-    <col min="3852" max="3852" width="9.140625" style="11"/>
-    <col min="3853" max="3853" width="9" style="11" customWidth="1"/>
-    <col min="3854" max="4096" width="9.140625" style="11"/>
-    <col min="4097" max="4100" width="7.42578125" style="11" customWidth="1"/>
-    <col min="4101" max="4101" width="9.140625" style="11"/>
-    <col min="4102" max="4102" width="5.5703125" style="11" customWidth="1"/>
-    <col min="4103" max="4103" width="3.5703125" style="11" customWidth="1"/>
-    <col min="4104" max="4104" width="5.140625" style="11" customWidth="1"/>
-    <col min="4105" max="4105" width="5.42578125" style="11" customWidth="1"/>
-    <col min="4106" max="4106" width="9.140625" style="11"/>
-    <col min="4107" max="4107" width="17.140625" style="11" customWidth="1"/>
-    <col min="4108" max="4108" width="9.140625" style="11"/>
-    <col min="4109" max="4109" width="9" style="11" customWidth="1"/>
-    <col min="4110" max="4352" width="9.140625" style="11"/>
-    <col min="4353" max="4356" width="7.42578125" style="11" customWidth="1"/>
-    <col min="4357" max="4357" width="9.140625" style="11"/>
-    <col min="4358" max="4358" width="5.5703125" style="11" customWidth="1"/>
-    <col min="4359" max="4359" width="3.5703125" style="11" customWidth="1"/>
-    <col min="4360" max="4360" width="5.140625" style="11" customWidth="1"/>
-    <col min="4361" max="4361" width="5.42578125" style="11" customWidth="1"/>
-    <col min="4362" max="4362" width="9.140625" style="11"/>
-    <col min="4363" max="4363" width="17.140625" style="11" customWidth="1"/>
-    <col min="4364" max="4364" width="9.140625" style="11"/>
-    <col min="4365" max="4365" width="9" style="11" customWidth="1"/>
-    <col min="4366" max="4608" width="9.140625" style="11"/>
-    <col min="4609" max="4612" width="7.42578125" style="11" customWidth="1"/>
-    <col min="4613" max="4613" width="9.140625" style="11"/>
-    <col min="4614" max="4614" width="5.5703125" style="11" customWidth="1"/>
-    <col min="4615" max="4615" width="3.5703125" style="11" customWidth="1"/>
-    <col min="4616" max="4616" width="5.140625" style="11" customWidth="1"/>
-    <col min="4617" max="4617" width="5.42578125" style="11" customWidth="1"/>
-    <col min="4618" max="4618" width="9.140625" style="11"/>
-    <col min="4619" max="4619" width="17.140625" style="11" customWidth="1"/>
-    <col min="4620" max="4620" width="9.140625" style="11"/>
-    <col min="4621" max="4621" width="9" style="11" customWidth="1"/>
-    <col min="4622" max="4864" width="9.140625" style="11"/>
-    <col min="4865" max="4868" width="7.42578125" style="11" customWidth="1"/>
-    <col min="4869" max="4869" width="9.140625" style="11"/>
-    <col min="4870" max="4870" width="5.5703125" style="11" customWidth="1"/>
-    <col min="4871" max="4871" width="3.5703125" style="11" customWidth="1"/>
-    <col min="4872" max="4872" width="5.140625" style="11" customWidth="1"/>
-    <col min="4873" max="4873" width="5.42578125" style="11" customWidth="1"/>
-    <col min="4874" max="4874" width="9.140625" style="11"/>
-    <col min="4875" max="4875" width="17.140625" style="11" customWidth="1"/>
-    <col min="4876" max="4876" width="9.140625" style="11"/>
-    <col min="4877" max="4877" width="9" style="11" customWidth="1"/>
-    <col min="4878" max="5120" width="9.140625" style="11"/>
-    <col min="5121" max="5124" width="7.42578125" style="11" customWidth="1"/>
-    <col min="5125" max="5125" width="9.140625" style="11"/>
-    <col min="5126" max="5126" width="5.5703125" style="11" customWidth="1"/>
-    <col min="5127" max="5127" width="3.5703125" style="11" customWidth="1"/>
-    <col min="5128" max="5128" width="5.140625" style="11" customWidth="1"/>
-    <col min="5129" max="5129" width="5.42578125" style="11" customWidth="1"/>
-    <col min="5130" max="5130" width="9.140625" style="11"/>
-    <col min="5131" max="5131" width="17.140625" style="11" customWidth="1"/>
-    <col min="5132" max="5132" width="9.140625" style="11"/>
-    <col min="5133" max="5133" width="9" style="11" customWidth="1"/>
-    <col min="5134" max="5376" width="9.140625" style="11"/>
-    <col min="5377" max="5380" width="7.42578125" style="11" customWidth="1"/>
-    <col min="5381" max="5381" width="9.140625" style="11"/>
-    <col min="5382" max="5382" width="5.5703125" style="11" customWidth="1"/>
-    <col min="5383" max="5383" width="3.5703125" style="11" customWidth="1"/>
-    <col min="5384" max="5384" width="5.140625" style="11" customWidth="1"/>
-    <col min="5385" max="5385" width="5.42578125" style="11" customWidth="1"/>
-    <col min="5386" max="5386" width="9.140625" style="11"/>
-    <col min="5387" max="5387" width="17.140625" style="11" customWidth="1"/>
-    <col min="5388" max="5388" width="9.140625" style="11"/>
-    <col min="5389" max="5389" width="9" style="11" customWidth="1"/>
-    <col min="5390" max="5632" width="9.140625" style="11"/>
-    <col min="5633" max="5636" width="7.42578125" style="11" customWidth="1"/>
-    <col min="5637" max="5637" width="9.140625" style="11"/>
-    <col min="5638" max="5638" width="5.5703125" style="11" customWidth="1"/>
-    <col min="5639" max="5639" width="3.5703125" style="11" customWidth="1"/>
-    <col min="5640" max="5640" width="5.140625" style="11" customWidth="1"/>
-    <col min="5641" max="5641" width="5.42578125" style="11" customWidth="1"/>
-    <col min="5642" max="5642" width="9.140625" style="11"/>
-    <col min="5643" max="5643" width="17.140625" style="11" customWidth="1"/>
-    <col min="5644" max="5644" width="9.140625" style="11"/>
-    <col min="5645" max="5645" width="9" style="11" customWidth="1"/>
-    <col min="5646" max="5888" width="9.140625" style="11"/>
-    <col min="5889" max="5892" width="7.42578125" style="11" customWidth="1"/>
-    <col min="5893" max="5893" width="9.140625" style="11"/>
-    <col min="5894" max="5894" width="5.5703125" style="11" customWidth="1"/>
-    <col min="5895" max="5895" width="3.5703125" style="11" customWidth="1"/>
-    <col min="5896" max="5896" width="5.140625" style="11" customWidth="1"/>
-    <col min="5897" max="5897" width="5.42578125" style="11" customWidth="1"/>
-    <col min="5898" max="5898" width="9.140625" style="11"/>
-    <col min="5899" max="5899" width="17.140625" style="11" customWidth="1"/>
-    <col min="5900" max="5900" width="9.140625" style="11"/>
-    <col min="5901" max="5901" width="9" style="11" customWidth="1"/>
-    <col min="5902" max="6144" width="9.140625" style="11"/>
-    <col min="6145" max="6148" width="7.42578125" style="11" customWidth="1"/>
-    <col min="6149" max="6149" width="9.140625" style="11"/>
-    <col min="6150" max="6150" width="5.5703125" style="11" customWidth="1"/>
-    <col min="6151" max="6151" width="3.5703125" style="11" customWidth="1"/>
-    <col min="6152" max="6152" width="5.140625" style="11" customWidth="1"/>
-    <col min="6153" max="6153" width="5.42578125" style="11" customWidth="1"/>
-    <col min="6154" max="6154" width="9.140625" style="11"/>
-    <col min="6155" max="6155" width="17.140625" style="11" customWidth="1"/>
-    <col min="6156" max="6156" width="9.140625" style="11"/>
-    <col min="6157" max="6157" width="9" style="11" customWidth="1"/>
-    <col min="6158" max="6400" width="9.140625" style="11"/>
-    <col min="6401" max="6404" width="7.42578125" style="11" customWidth="1"/>
-    <col min="6405" max="6405" width="9.140625" style="11"/>
-    <col min="6406" max="6406" width="5.5703125" style="11" customWidth="1"/>
-    <col min="6407" max="6407" width="3.5703125" style="11" customWidth="1"/>
-    <col min="6408" max="6408" width="5.140625" style="11" customWidth="1"/>
-    <col min="6409" max="6409" width="5.42578125" style="11" customWidth="1"/>
-    <col min="6410" max="6410" width="9.140625" style="11"/>
-    <col min="6411" max="6411" width="17.140625" style="11" customWidth="1"/>
-    <col min="6412" max="6412" width="9.140625" style="11"/>
-    <col min="6413" max="6413" width="9" style="11" customWidth="1"/>
-    <col min="6414" max="6656" width="9.140625" style="11"/>
-    <col min="6657" max="6660" width="7.42578125" style="11" customWidth="1"/>
-    <col min="6661" max="6661" width="9.140625" style="11"/>
-    <col min="6662" max="6662" width="5.5703125" style="11" customWidth="1"/>
-    <col min="6663" max="6663" width="3.5703125" style="11" customWidth="1"/>
-    <col min="6664" max="6664" width="5.140625" style="11" customWidth="1"/>
-    <col min="6665" max="6665" width="5.42578125" style="11" customWidth="1"/>
-    <col min="6666" max="6666" width="9.140625" style="11"/>
-    <col min="6667" max="6667" width="17.140625" style="11" customWidth="1"/>
-    <col min="6668" max="6668" width="9.140625" style="11"/>
-    <col min="6669" max="6669" width="9" style="11" customWidth="1"/>
-    <col min="6670" max="6912" width="9.140625" style="11"/>
-    <col min="6913" max="6916" width="7.42578125" style="11" customWidth="1"/>
-    <col min="6917" max="6917" width="9.140625" style="11"/>
-    <col min="6918" max="6918" width="5.5703125" style="11" customWidth="1"/>
-    <col min="6919" max="6919" width="3.5703125" style="11" customWidth="1"/>
-    <col min="6920" max="6920" width="5.140625" style="11" customWidth="1"/>
-    <col min="6921" max="6921" width="5.42578125" style="11" customWidth="1"/>
-    <col min="6922" max="6922" width="9.140625" style="11"/>
-    <col min="6923" max="6923" width="17.140625" style="11" customWidth="1"/>
-    <col min="6924" max="6924" width="9.140625" style="11"/>
-    <col min="6925" max="6925" width="9" style="11" customWidth="1"/>
-    <col min="6926" max="7168" width="9.140625" style="11"/>
-    <col min="7169" max="7172" width="7.42578125" style="11" customWidth="1"/>
-    <col min="7173" max="7173" width="9.140625" style="11"/>
-    <col min="7174" max="7174" width="5.5703125" style="11" customWidth="1"/>
-    <col min="7175" max="7175" width="3.5703125" style="11" customWidth="1"/>
-    <col min="7176" max="7176" width="5.140625" style="11" customWidth="1"/>
-    <col min="7177" max="7177" width="5.42578125" style="11" customWidth="1"/>
-    <col min="7178" max="7178" width="9.140625" style="11"/>
-    <col min="7179" max="7179" width="17.140625" style="11" customWidth="1"/>
-    <col min="7180" max="7180" width="9.140625" style="11"/>
-    <col min="7181" max="7181" width="9" style="11" customWidth="1"/>
-    <col min="7182" max="7424" width="9.140625" style="11"/>
-    <col min="7425" max="7428" width="7.42578125" style="11" customWidth="1"/>
-    <col min="7429" max="7429" width="9.140625" style="11"/>
-    <col min="7430" max="7430" width="5.5703125" style="11" customWidth="1"/>
-    <col min="7431" max="7431" width="3.5703125" style="11" customWidth="1"/>
-    <col min="7432" max="7432" width="5.140625" style="11" customWidth="1"/>
-    <col min="7433" max="7433" width="5.42578125" style="11" customWidth="1"/>
-    <col min="7434" max="7434" width="9.140625" style="11"/>
-    <col min="7435" max="7435" width="17.140625" style="11" customWidth="1"/>
-    <col min="7436" max="7436" width="9.140625" style="11"/>
-    <col min="7437" max="7437" width="9" style="11" customWidth="1"/>
-    <col min="7438" max="7680" width="9.140625" style="11"/>
-    <col min="7681" max="7684" width="7.42578125" style="11" customWidth="1"/>
-    <col min="7685" max="7685" width="9.140625" style="11"/>
-    <col min="7686" max="7686" width="5.5703125" style="11" customWidth="1"/>
-    <col min="7687" max="7687" width="3.5703125" style="11" customWidth="1"/>
-    <col min="7688" max="7688" width="5.140625" style="11" customWidth="1"/>
-    <col min="7689" max="7689" width="5.42578125" style="11" customWidth="1"/>
-    <col min="7690" max="7690" width="9.140625" style="11"/>
-    <col min="7691" max="7691" width="17.140625" style="11" customWidth="1"/>
-    <col min="7692" max="7692" width="9.140625" style="11"/>
-    <col min="7693" max="7693" width="9" style="11" customWidth="1"/>
-    <col min="7694" max="7936" width="9.140625" style="11"/>
-    <col min="7937" max="7940" width="7.42578125" style="11" customWidth="1"/>
-    <col min="7941" max="7941" width="9.140625" style="11"/>
-    <col min="7942" max="7942" width="5.5703125" style="11" customWidth="1"/>
-    <col min="7943" max="7943" width="3.5703125" style="11" customWidth="1"/>
-    <col min="7944" max="7944" width="5.140625" style="11" customWidth="1"/>
-    <col min="7945" max="7945" width="5.42578125" style="11" customWidth="1"/>
-    <col min="7946" max="7946" width="9.140625" style="11"/>
-    <col min="7947" max="7947" width="17.140625" style="11" customWidth="1"/>
-    <col min="7948" max="7948" width="9.140625" style="11"/>
-    <col min="7949" max="7949" width="9" style="11" customWidth="1"/>
-    <col min="7950" max="8192" width="9.140625" style="11"/>
-    <col min="8193" max="8196" width="7.42578125" style="11" customWidth="1"/>
-    <col min="8197" max="8197" width="9.140625" style="11"/>
-    <col min="8198" max="8198" width="5.5703125" style="11" customWidth="1"/>
-    <col min="8199" max="8199" width="3.5703125" style="11" customWidth="1"/>
-    <col min="8200" max="8200" width="5.140625" style="11" customWidth="1"/>
-    <col min="8201" max="8201" width="5.42578125" style="11" customWidth="1"/>
-    <col min="8202" max="8202" width="9.140625" style="11"/>
-    <col min="8203" max="8203" width="17.140625" style="11" customWidth="1"/>
-    <col min="8204" max="8204" width="9.140625" style="11"/>
-    <col min="8205" max="8205" width="9" style="11" customWidth="1"/>
-    <col min="8206" max="8448" width="9.140625" style="11"/>
-    <col min="8449" max="8452" width="7.42578125" style="11" customWidth="1"/>
-    <col min="8453" max="8453" width="9.140625" style="11"/>
-    <col min="8454" max="8454" width="5.5703125" style="11" customWidth="1"/>
-    <col min="8455" max="8455" width="3.5703125" style="11" customWidth="1"/>
-    <col min="8456" max="8456" width="5.140625" style="11" customWidth="1"/>
-    <col min="8457" max="8457" width="5.42578125" style="11" customWidth="1"/>
-    <col min="8458" max="8458" width="9.140625" style="11"/>
-    <col min="8459" max="8459" width="17.140625" style="11" customWidth="1"/>
-    <col min="8460" max="8460" width="9.140625" style="11"/>
-    <col min="8461" max="8461" width="9" style="11" customWidth="1"/>
-    <col min="8462" max="8704" width="9.140625" style="11"/>
-    <col min="8705" max="8708" width="7.42578125" style="11" customWidth="1"/>
-    <col min="8709" max="8709" width="9.140625" style="11"/>
-    <col min="8710" max="8710" width="5.5703125" style="11" customWidth="1"/>
-    <col min="8711" max="8711" width="3.5703125" style="11" customWidth="1"/>
-    <col min="8712" max="8712" width="5.140625" style="11" customWidth="1"/>
-    <col min="8713" max="8713" width="5.42578125" style="11" customWidth="1"/>
-    <col min="8714" max="8714" width="9.140625" style="11"/>
-    <col min="8715" max="8715" width="17.140625" style="11" customWidth="1"/>
-    <col min="8716" max="8716" width="9.140625" style="11"/>
-    <col min="8717" max="8717" width="9" style="11" customWidth="1"/>
-    <col min="8718" max="8960" width="9.140625" style="11"/>
-    <col min="8961" max="8964" width="7.42578125" style="11" customWidth="1"/>
-    <col min="8965" max="8965" width="9.140625" style="11"/>
-    <col min="8966" max="8966" width="5.5703125" style="11" customWidth="1"/>
-    <col min="8967" max="8967" width="3.5703125" style="11" customWidth="1"/>
-    <col min="8968" max="8968" width="5.140625" style="11" customWidth="1"/>
-    <col min="8969" max="8969" width="5.42578125" style="11" customWidth="1"/>
-    <col min="8970" max="8970" width="9.140625" style="11"/>
-    <col min="8971" max="8971" width="17.140625" style="11" customWidth="1"/>
-    <col min="8972" max="8972" width="9.140625" style="11"/>
-    <col min="8973" max="8973" width="9" style="11" customWidth="1"/>
-    <col min="8974" max="9216" width="9.140625" style="11"/>
-    <col min="9217" max="9220" width="7.42578125" style="11" customWidth="1"/>
-    <col min="9221" max="9221" width="9.140625" style="11"/>
-    <col min="9222" max="9222" width="5.5703125" style="11" customWidth="1"/>
-    <col min="9223" max="9223" width="3.5703125" style="11" customWidth="1"/>
-    <col min="9224" max="9224" width="5.140625" style="11" customWidth="1"/>
-    <col min="9225" max="9225" width="5.42578125" style="11" customWidth="1"/>
-    <col min="9226" max="9226" width="9.140625" style="11"/>
-    <col min="9227" max="9227" width="17.140625" style="11" customWidth="1"/>
-    <col min="9228" max="9228" width="9.140625" style="11"/>
-    <col min="9229" max="9229" width="9" style="11" customWidth="1"/>
-    <col min="9230" max="9472" width="9.140625" style="11"/>
-    <col min="9473" max="9476" width="7.42578125" style="11" customWidth="1"/>
-    <col min="9477" max="9477" width="9.140625" style="11"/>
-    <col min="9478" max="9478" width="5.5703125" style="11" customWidth="1"/>
-    <col min="9479" max="9479" width="3.5703125" style="11" customWidth="1"/>
-    <col min="9480" max="9480" width="5.140625" style="11" customWidth="1"/>
-    <col min="9481" max="9481" width="5.42578125" style="11" customWidth="1"/>
-    <col min="9482" max="9482" width="9.140625" style="11"/>
-    <col min="9483" max="9483" width="17.140625" style="11" customWidth="1"/>
-    <col min="9484" max="9484" width="9.140625" style="11"/>
-    <col min="9485" max="9485" width="9" style="11" customWidth="1"/>
-    <col min="9486" max="9728" width="9.140625" style="11"/>
-    <col min="9729" max="9732" width="7.42578125" style="11" customWidth="1"/>
-    <col min="9733" max="9733" width="9.140625" style="11"/>
-    <col min="9734" max="9734" width="5.5703125" style="11" customWidth="1"/>
-    <col min="9735" max="9735" width="3.5703125" style="11" customWidth="1"/>
-    <col min="9736" max="9736" width="5.140625" style="11" customWidth="1"/>
-    <col min="9737" max="9737" width="5.42578125" style="11" customWidth="1"/>
-    <col min="9738" max="9738" width="9.140625" style="11"/>
-    <col min="9739" max="9739" width="17.140625" style="11" customWidth="1"/>
-    <col min="9740" max="9740" width="9.140625" style="11"/>
-    <col min="9741" max="9741" width="9" style="11" customWidth="1"/>
-    <col min="9742" max="9984" width="9.140625" style="11"/>
-    <col min="9985" max="9988" width="7.42578125" style="11" customWidth="1"/>
-    <col min="9989" max="9989" width="9.140625" style="11"/>
-    <col min="9990" max="9990" width="5.5703125" style="11" customWidth="1"/>
-    <col min="9991" max="9991" width="3.5703125" style="11" customWidth="1"/>
-    <col min="9992" max="9992" width="5.140625" style="11" customWidth="1"/>
-    <col min="9993" max="9993" width="5.42578125" style="11" customWidth="1"/>
-    <col min="9994" max="9994" width="9.140625" style="11"/>
-    <col min="9995" max="9995" width="17.140625" style="11" customWidth="1"/>
-    <col min="9996" max="9996" width="9.140625" style="11"/>
-    <col min="9997" max="9997" width="9" style="11" customWidth="1"/>
-    <col min="9998" max="10240" width="9.140625" style="11"/>
-    <col min="10241" max="10244" width="7.42578125" style="11" customWidth="1"/>
-    <col min="10245" max="10245" width="9.140625" style="11"/>
-    <col min="10246" max="10246" width="5.5703125" style="11" customWidth="1"/>
-    <col min="10247" max="10247" width="3.5703125" style="11" customWidth="1"/>
-    <col min="10248" max="10248" width="5.140625" style="11" customWidth="1"/>
-    <col min="10249" max="10249" width="5.42578125" style="11" customWidth="1"/>
-    <col min="10250" max="10250" width="9.140625" style="11"/>
-    <col min="10251" max="10251" width="17.140625" style="11" customWidth="1"/>
-    <col min="10252" max="10252" width="9.140625" style="11"/>
-    <col min="10253" max="10253" width="9" style="11" customWidth="1"/>
-    <col min="10254" max="10496" width="9.140625" style="11"/>
-    <col min="10497" max="10500" width="7.42578125" style="11" customWidth="1"/>
-    <col min="10501" max="10501" width="9.140625" style="11"/>
-    <col min="10502" max="10502" width="5.5703125" style="11" customWidth="1"/>
-    <col min="10503" max="10503" width="3.5703125" style="11" customWidth="1"/>
-    <col min="10504" max="10504" width="5.140625" style="11" customWidth="1"/>
-    <col min="10505" max="10505" width="5.42578125" style="11" customWidth="1"/>
-    <col min="10506" max="10506" width="9.140625" style="11"/>
-    <col min="10507" max="10507" width="17.140625" style="11" customWidth="1"/>
-    <col min="10508" max="10508" width="9.140625" style="11"/>
-    <col min="10509" max="10509" width="9" style="11" customWidth="1"/>
-    <col min="10510" max="10752" width="9.140625" style="11"/>
-    <col min="10753" max="10756" width="7.42578125" style="11" customWidth="1"/>
-    <col min="10757" max="10757" width="9.140625" style="11"/>
-    <col min="10758" max="10758" width="5.5703125" style="11" customWidth="1"/>
-    <col min="10759" max="10759" width="3.5703125" style="11" customWidth="1"/>
-    <col min="10760" max="10760" width="5.140625" style="11" customWidth="1"/>
-    <col min="10761" max="10761" width="5.42578125" style="11" customWidth="1"/>
-    <col min="10762" max="10762" width="9.140625" style="11"/>
-    <col min="10763" max="10763" width="17.140625" style="11" customWidth="1"/>
-    <col min="10764" max="10764" width="9.140625" style="11"/>
-    <col min="10765" max="10765" width="9" style="11" customWidth="1"/>
-    <col min="10766" max="11008" width="9.140625" style="11"/>
-    <col min="11009" max="11012" width="7.42578125" style="11" customWidth="1"/>
-    <col min="11013" max="11013" width="9.140625" style="11"/>
-    <col min="11014" max="11014" width="5.5703125" style="11" customWidth="1"/>
-    <col min="11015" max="11015" width="3.5703125" style="11" customWidth="1"/>
-    <col min="11016" max="11016" width="5.140625" style="11" customWidth="1"/>
-    <col min="11017" max="11017" width="5.42578125" style="11" customWidth="1"/>
-    <col min="11018" max="11018" width="9.140625" style="11"/>
-    <col min="11019" max="11019" width="17.140625" style="11" customWidth="1"/>
-    <col min="11020" max="11020" width="9.140625" style="11"/>
-    <col min="11021" max="11021" width="9" style="11" customWidth="1"/>
-    <col min="11022" max="11264" width="9.140625" style="11"/>
-    <col min="11265" max="11268" width="7.42578125" style="11" customWidth="1"/>
-    <col min="11269" max="11269" width="9.140625" style="11"/>
-    <col min="11270" max="11270" width="5.5703125" style="11" customWidth="1"/>
-    <col min="11271" max="11271" width="3.5703125" style="11" customWidth="1"/>
-    <col min="11272" max="11272" width="5.140625" style="11" customWidth="1"/>
-    <col min="11273" max="11273" width="5.42578125" style="11" customWidth="1"/>
-    <col min="11274" max="11274" width="9.140625" style="11"/>
-    <col min="11275" max="11275" width="17.140625" style="11" customWidth="1"/>
-    <col min="11276" max="11276" width="9.140625" style="11"/>
-    <col min="11277" max="11277" width="9" style="11" customWidth="1"/>
-    <col min="11278" max="11520" width="9.140625" style="11"/>
-    <col min="11521" max="11524" width="7.42578125" style="11" customWidth="1"/>
-    <col min="11525" max="11525" width="9.140625" style="11"/>
-    <col min="11526" max="11526" width="5.5703125" style="11" customWidth="1"/>
-    <col min="11527" max="11527" width="3.5703125" style="11" customWidth="1"/>
-    <col min="11528" max="11528" width="5.140625" style="11" customWidth="1"/>
-    <col min="11529" max="11529" width="5.42578125" style="11" customWidth="1"/>
-    <col min="11530" max="11530" width="9.140625" style="11"/>
-    <col min="11531" max="11531" width="17.140625" style="11" customWidth="1"/>
-    <col min="11532" max="11532" width="9.140625" style="11"/>
-    <col min="11533" max="11533" width="9" style="11" customWidth="1"/>
-    <col min="11534" max="11776" width="9.140625" style="11"/>
-    <col min="11777" max="11780" width="7.42578125" style="11" customWidth="1"/>
-    <col min="11781" max="11781" width="9.140625" style="11"/>
-    <col min="11782" max="11782" width="5.5703125" style="11" customWidth="1"/>
-    <col min="11783" max="11783" width="3.5703125" style="11" customWidth="1"/>
-    <col min="11784" max="11784" width="5.140625" style="11" customWidth="1"/>
-    <col min="11785" max="11785" width="5.42578125" style="11" customWidth="1"/>
-    <col min="11786" max="11786" width="9.140625" style="11"/>
-    <col min="11787" max="11787" width="17.140625" style="11" customWidth="1"/>
-    <col min="11788" max="11788" width="9.140625" style="11"/>
-    <col min="11789" max="11789" width="9" style="11" customWidth="1"/>
-    <col min="11790" max="12032" width="9.140625" style="11"/>
-    <col min="12033" max="12036" width="7.42578125" style="11" customWidth="1"/>
-    <col min="12037" max="12037" width="9.140625" style="11"/>
-    <col min="12038" max="12038" width="5.5703125" style="11" customWidth="1"/>
-    <col min="12039" max="12039" width="3.5703125" style="11" customWidth="1"/>
-    <col min="12040" max="12040" width="5.140625" style="11" customWidth="1"/>
-    <col min="12041" max="12041" width="5.42578125" style="11" customWidth="1"/>
-    <col min="12042" max="12042" width="9.140625" style="11"/>
-    <col min="12043" max="12043" width="17.140625" style="11" customWidth="1"/>
-    <col min="12044" max="12044" width="9.140625" style="11"/>
-    <col min="12045" max="12045" width="9" style="11" customWidth="1"/>
-    <col min="12046" max="12288" width="9.140625" style="11"/>
-    <col min="12289" max="12292" width="7.42578125" style="11" customWidth="1"/>
-    <col min="12293" max="12293" width="9.140625" style="11"/>
-    <col min="12294" max="12294" width="5.5703125" style="11" customWidth="1"/>
-    <col min="12295" max="12295" width="3.5703125" style="11" customWidth="1"/>
-    <col min="12296" max="12296" width="5.140625" style="11" customWidth="1"/>
-    <col min="12297" max="12297" width="5.42578125" style="11" customWidth="1"/>
-    <col min="12298" max="12298" width="9.140625" style="11"/>
-    <col min="12299" max="12299" width="17.140625" style="11" customWidth="1"/>
-    <col min="12300" max="12300" width="9.140625" style="11"/>
-    <col min="12301" max="12301" width="9" style="11" customWidth="1"/>
-    <col min="12302" max="12544" width="9.140625" style="11"/>
-    <col min="12545" max="12548" width="7.42578125" style="11" customWidth="1"/>
-    <col min="12549" max="12549" width="9.140625" style="11"/>
-    <col min="12550" max="12550" width="5.5703125" style="11" customWidth="1"/>
-    <col min="12551" max="12551" width="3.5703125" style="11" customWidth="1"/>
-    <col min="12552" max="12552" width="5.140625" style="11" customWidth="1"/>
-    <col min="12553" max="12553" width="5.42578125" style="11" customWidth="1"/>
-    <col min="12554" max="12554" width="9.140625" style="11"/>
-    <col min="12555" max="12555" width="17.140625" style="11" customWidth="1"/>
-    <col min="12556" max="12556" width="9.140625" style="11"/>
-    <col min="12557" max="12557" width="9" style="11" customWidth="1"/>
-    <col min="12558" max="12800" width="9.140625" style="11"/>
-    <col min="12801" max="12804" width="7.42578125" style="11" customWidth="1"/>
-    <col min="12805" max="12805" width="9.140625" style="11"/>
-    <col min="12806" max="12806" width="5.5703125" style="11" customWidth="1"/>
-    <col min="12807" max="12807" width="3.5703125" style="11" customWidth="1"/>
-    <col min="12808" max="12808" width="5.140625" style="11" customWidth="1"/>
-    <col min="12809" max="12809" width="5.42578125" style="11" customWidth="1"/>
-    <col min="12810" max="12810" width="9.140625" style="11"/>
-    <col min="12811" max="12811" width="17.140625" style="11" customWidth="1"/>
-    <col min="12812" max="12812" width="9.140625" style="11"/>
-    <col min="12813" max="12813" width="9" style="11" customWidth="1"/>
-    <col min="12814" max="13056" width="9.140625" style="11"/>
-    <col min="13057" max="13060" width="7.42578125" style="11" customWidth="1"/>
-    <col min="13061" max="13061" width="9.140625" style="11"/>
-    <col min="13062" max="13062" width="5.5703125" style="11" customWidth="1"/>
-    <col min="13063" max="13063" width="3.5703125" style="11" customWidth="1"/>
-    <col min="13064" max="13064" width="5.140625" style="11" customWidth="1"/>
-    <col min="13065" max="13065" width="5.42578125" style="11" customWidth="1"/>
-    <col min="13066" max="13066" width="9.140625" style="11"/>
-    <col min="13067" max="13067" width="17.140625" style="11" customWidth="1"/>
-    <col min="13068" max="13068" width="9.140625" style="11"/>
-    <col min="13069" max="13069" width="9" style="11" customWidth="1"/>
-    <col min="13070" max="13312" width="9.140625" style="11"/>
-    <col min="13313" max="13316" width="7.42578125" style="11" customWidth="1"/>
-    <col min="13317" max="13317" width="9.140625" style="11"/>
-    <col min="13318" max="13318" width="5.5703125" style="11" customWidth="1"/>
-    <col min="13319" max="13319" width="3.5703125" style="11" customWidth="1"/>
-    <col min="13320" max="13320" width="5.140625" style="11" customWidth="1"/>
-    <col min="13321" max="13321" width="5.42578125" style="11" customWidth="1"/>
-    <col min="13322" max="13322" width="9.140625" style="11"/>
-    <col min="13323" max="13323" width="17.140625" style="11" customWidth="1"/>
-    <col min="13324" max="13324" width="9.140625" style="11"/>
-    <col min="13325" max="13325" width="9" style="11" customWidth="1"/>
-    <col min="13326" max="13568" width="9.140625" style="11"/>
-    <col min="13569" max="13572" width="7.42578125" style="11" customWidth="1"/>
-    <col min="13573" max="13573" width="9.140625" style="11"/>
-    <col min="13574" max="13574" width="5.5703125" style="11" customWidth="1"/>
-    <col min="13575" max="13575" width="3.5703125" style="11" customWidth="1"/>
-    <col min="13576" max="13576" width="5.140625" style="11" customWidth="1"/>
-    <col min="13577" max="13577" width="5.42578125" style="11" customWidth="1"/>
-    <col min="13578" max="13578" width="9.140625" style="11"/>
-    <col min="13579" max="13579" width="17.140625" style="11" customWidth="1"/>
-    <col min="13580" max="13580" width="9.140625" style="11"/>
-    <col min="13581" max="13581" width="9" style="11" customWidth="1"/>
-    <col min="13582" max="13824" width="9.140625" style="11"/>
-    <col min="13825" max="13828" width="7.42578125" style="11" customWidth="1"/>
-    <col min="13829" max="13829" width="9.140625" style="11"/>
-    <col min="13830" max="13830" width="5.5703125" style="11" customWidth="1"/>
-    <col min="13831" max="13831" width="3.5703125" style="11" customWidth="1"/>
-    <col min="13832" max="13832" width="5.140625" style="11" customWidth="1"/>
-    <col min="13833" max="13833" width="5.42578125" style="11" customWidth="1"/>
-    <col min="13834" max="13834" width="9.140625" style="11"/>
-    <col min="13835" max="13835" width="17.140625" style="11" customWidth="1"/>
-    <col min="13836" max="13836" width="9.140625" style="11"/>
-    <col min="13837" max="13837" width="9" style="11" customWidth="1"/>
-    <col min="13838" max="14080" width="9.140625" style="11"/>
-    <col min="14081" max="14084" width="7.42578125" style="11" customWidth="1"/>
-    <col min="14085" max="14085" width="9.140625" style="11"/>
-    <col min="14086" max="14086" width="5.5703125" style="11" customWidth="1"/>
-    <col min="14087" max="14087" width="3.5703125" style="11" customWidth="1"/>
-    <col min="14088" max="14088" width="5.140625" style="11" customWidth="1"/>
-    <col min="14089" max="14089" width="5.42578125" style="11" customWidth="1"/>
-    <col min="14090" max="14090" width="9.140625" style="11"/>
-    <col min="14091" max="14091" width="17.140625" style="11" customWidth="1"/>
-    <col min="14092" max="14092" width="9.140625" style="11"/>
-    <col min="14093" max="14093" width="9" style="11" customWidth="1"/>
-    <col min="14094" max="14336" width="9.140625" style="11"/>
-    <col min="14337" max="14340" width="7.42578125" style="11" customWidth="1"/>
-    <col min="14341" max="14341" width="9.140625" style="11"/>
-    <col min="14342" max="14342" width="5.5703125" style="11" customWidth="1"/>
-    <col min="14343" max="14343" width="3.5703125" style="11" customWidth="1"/>
-    <col min="14344" max="14344" width="5.140625" style="11" customWidth="1"/>
-    <col min="14345" max="14345" width="5.42578125" style="11" customWidth="1"/>
-    <col min="14346" max="14346" width="9.140625" style="11"/>
-    <col min="14347" max="14347" width="17.140625" style="11" customWidth="1"/>
-    <col min="14348" max="14348" width="9.140625" style="11"/>
-    <col min="14349" max="14349" width="9" style="11" customWidth="1"/>
-    <col min="14350" max="14592" width="9.140625" style="11"/>
-    <col min="14593" max="14596" width="7.42578125" style="11" customWidth="1"/>
-    <col min="14597" max="14597" width="9.140625" style="11"/>
-    <col min="14598" max="14598" width="5.5703125" style="11" customWidth="1"/>
-    <col min="14599" max="14599" width="3.5703125" style="11" customWidth="1"/>
-    <col min="14600" max="14600" width="5.140625" style="11" customWidth="1"/>
-    <col min="14601" max="14601" width="5.42578125" style="11" customWidth="1"/>
-    <col min="14602" max="14602" width="9.140625" style="11"/>
-    <col min="14603" max="14603" width="17.140625" style="11" customWidth="1"/>
-    <col min="14604" max="14604" width="9.140625" style="11"/>
-    <col min="14605" max="14605" width="9" style="11" customWidth="1"/>
-    <col min="14606" max="14848" width="9.140625" style="11"/>
-    <col min="14849" max="14852" width="7.42578125" style="11" customWidth="1"/>
-    <col min="14853" max="14853" width="9.140625" style="11"/>
-    <col min="14854" max="14854" width="5.5703125" style="11" customWidth="1"/>
-    <col min="14855" max="14855" width="3.5703125" style="11" customWidth="1"/>
-    <col min="14856" max="14856" width="5.140625" style="11" customWidth="1"/>
-    <col min="14857" max="14857" width="5.42578125" style="11" customWidth="1"/>
-    <col min="14858" max="14858" width="9.140625" style="11"/>
-    <col min="14859" max="14859" width="17.140625" style="11" customWidth="1"/>
-    <col min="14860" max="14860" width="9.140625" style="11"/>
-    <col min="14861" max="14861" width="9" style="11" customWidth="1"/>
-    <col min="14862" max="15104" width="9.140625" style="11"/>
-    <col min="15105" max="15108" width="7.42578125" style="11" customWidth="1"/>
-    <col min="15109" max="15109" width="9.140625" style="11"/>
-    <col min="15110" max="15110" width="5.5703125" style="11" customWidth="1"/>
-    <col min="15111" max="15111" width="3.5703125" style="11" customWidth="1"/>
-    <col min="15112" max="15112" width="5.140625" style="11" customWidth="1"/>
-    <col min="15113" max="15113" width="5.42578125" style="11" customWidth="1"/>
-    <col min="15114" max="15114" width="9.140625" style="11"/>
-    <col min="15115" max="15115" width="17.140625" style="11" customWidth="1"/>
-    <col min="15116" max="15116" width="9.140625" style="11"/>
-    <col min="15117" max="15117" width="9" style="11" customWidth="1"/>
-    <col min="15118" max="15360" width="9.140625" style="11"/>
-    <col min="15361" max="15364" width="7.42578125" style="11" customWidth="1"/>
-    <col min="15365" max="15365" width="9.140625" style="11"/>
-    <col min="15366" max="15366" width="5.5703125" style="11" customWidth="1"/>
-    <col min="15367" max="15367" width="3.5703125" style="11" customWidth="1"/>
-    <col min="15368" max="15368" width="5.140625" style="11" customWidth="1"/>
-    <col min="15369" max="15369" width="5.42578125" style="11" customWidth="1"/>
-    <col min="15370" max="15370" width="9.140625" style="11"/>
-    <col min="15371" max="15371" width="17.140625" style="11" customWidth="1"/>
-    <col min="15372" max="15372" width="9.140625" style="11"/>
-    <col min="15373" max="15373" width="9" style="11" customWidth="1"/>
-    <col min="15374" max="15616" width="9.140625" style="11"/>
-    <col min="15617" max="15620" width="7.42578125" style="11" customWidth="1"/>
-    <col min="15621" max="15621" width="9.140625" style="11"/>
-    <col min="15622" max="15622" width="5.5703125" style="11" customWidth="1"/>
-    <col min="15623" max="15623" width="3.5703125" style="11" customWidth="1"/>
-    <col min="15624" max="15624" width="5.140625" style="11" customWidth="1"/>
-    <col min="15625" max="15625" width="5.42578125" style="11" customWidth="1"/>
-    <col min="15626" max="15626" width="9.140625" style="11"/>
-    <col min="15627" max="15627" width="17.140625" style="11" customWidth="1"/>
-    <col min="15628" max="15628" width="9.140625" style="11"/>
-    <col min="15629" max="15629" width="9" style="11" customWidth="1"/>
-    <col min="15630" max="15872" width="9.140625" style="11"/>
-    <col min="15873" max="15876" width="7.42578125" style="11" customWidth="1"/>
-    <col min="15877" max="15877" width="9.140625" style="11"/>
-    <col min="15878" max="15878" width="5.5703125" style="11" customWidth="1"/>
-    <col min="15879" max="15879" width="3.5703125" style="11" customWidth="1"/>
-    <col min="15880" max="15880" width="5.140625" style="11" customWidth="1"/>
-    <col min="15881" max="15881" width="5.42578125" style="11" customWidth="1"/>
-    <col min="15882" max="15882" width="9.140625" style="11"/>
-    <col min="15883" max="15883" width="17.140625" style="11" customWidth="1"/>
-    <col min="15884" max="15884" width="9.140625" style="11"/>
-    <col min="15885" max="15885" width="9" style="11" customWidth="1"/>
-    <col min="15886" max="16128" width="9.140625" style="11"/>
-    <col min="16129" max="16132" width="7.42578125" style="11" customWidth="1"/>
-    <col min="16133" max="16133" width="9.140625" style="11"/>
-    <col min="16134" max="16134" width="5.5703125" style="11" customWidth="1"/>
-    <col min="16135" max="16135" width="3.5703125" style="11" customWidth="1"/>
-    <col min="16136" max="16136" width="5.140625" style="11" customWidth="1"/>
-    <col min="16137" max="16137" width="5.42578125" style="11" customWidth="1"/>
-    <col min="16138" max="16138" width="9.140625" style="11"/>
-    <col min="16139" max="16139" width="17.140625" style="11" customWidth="1"/>
-    <col min="16140" max="16140" width="9.140625" style="11"/>
-    <col min="16141" max="16141" width="9" style="11" customWidth="1"/>
-    <col min="16142" max="16384" width="9.140625" style="11"/>
+    <col min="1" max="4" width="7.42578125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="10"/>
+    <col min="6" max="6" width="5.5703125" style="10" customWidth="1"/>
+    <col min="7" max="7" width="3.5703125" style="10" customWidth="1"/>
+    <col min="8" max="8" width="5.140625" style="10" customWidth="1"/>
+    <col min="9" max="9" width="5.42578125" style="10" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="10"/>
+    <col min="11" max="11" width="17.140625" style="10" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="10"/>
+    <col min="13" max="13" width="9" style="10" customWidth="1"/>
+    <col min="14" max="256" width="9.140625" style="10"/>
+    <col min="257" max="260" width="7.42578125" style="10" customWidth="1"/>
+    <col min="261" max="261" width="9.140625" style="10"/>
+    <col min="262" max="262" width="5.5703125" style="10" customWidth="1"/>
+    <col min="263" max="263" width="3.5703125" style="10" customWidth="1"/>
+    <col min="264" max="264" width="5.140625" style="10" customWidth="1"/>
+    <col min="265" max="265" width="5.42578125" style="10" customWidth="1"/>
+    <col min="266" max="266" width="9.140625" style="10"/>
+    <col min="267" max="267" width="17.140625" style="10" customWidth="1"/>
+    <col min="268" max="268" width="9.140625" style="10"/>
+    <col min="269" max="269" width="9" style="10" customWidth="1"/>
+    <col min="270" max="512" width="9.140625" style="10"/>
+    <col min="513" max="516" width="7.42578125" style="10" customWidth="1"/>
+    <col min="517" max="517" width="9.140625" style="10"/>
+    <col min="518" max="518" width="5.5703125" style="10" customWidth="1"/>
+    <col min="519" max="519" width="3.5703125" style="10" customWidth="1"/>
+    <col min="520" max="520" width="5.140625" style="10" customWidth="1"/>
+    <col min="521" max="521" width="5.42578125" style="10" customWidth="1"/>
+    <col min="522" max="522" width="9.140625" style="10"/>
+    <col min="523" max="523" width="17.140625" style="10" customWidth="1"/>
+    <col min="524" max="524" width="9.140625" style="10"/>
+    <col min="525" max="525" width="9" style="10" customWidth="1"/>
+    <col min="526" max="768" width="9.140625" style="10"/>
+    <col min="769" max="772" width="7.42578125" style="10" customWidth="1"/>
+    <col min="773" max="773" width="9.140625" style="10"/>
+    <col min="774" max="774" width="5.5703125" style="10" customWidth="1"/>
+    <col min="775" max="775" width="3.5703125" style="10" customWidth="1"/>
+    <col min="776" max="776" width="5.140625" style="10" customWidth="1"/>
+    <col min="777" max="777" width="5.42578125" style="10" customWidth="1"/>
+    <col min="778" max="778" width="9.140625" style="10"/>
+    <col min="779" max="779" width="17.140625" style="10" customWidth="1"/>
+    <col min="780" max="780" width="9.140625" style="10"/>
+    <col min="781" max="781" width="9" style="10" customWidth="1"/>
+    <col min="782" max="1024" width="9.140625" style="10"/>
+    <col min="1025" max="1028" width="7.42578125" style="10" customWidth="1"/>
+    <col min="1029" max="1029" width="9.140625" style="10"/>
+    <col min="1030" max="1030" width="5.5703125" style="10" customWidth="1"/>
+    <col min="1031" max="1031" width="3.5703125" style="10" customWidth="1"/>
+    <col min="1032" max="1032" width="5.140625" style="10" customWidth="1"/>
+    <col min="1033" max="1033" width="5.42578125" style="10" customWidth="1"/>
+    <col min="1034" max="1034" width="9.140625" style="10"/>
+    <col min="1035" max="1035" width="17.140625" style="10" customWidth="1"/>
+    <col min="1036" max="1036" width="9.140625" style="10"/>
+    <col min="1037" max="1037" width="9" style="10" customWidth="1"/>
+    <col min="1038" max="1280" width="9.140625" style="10"/>
+    <col min="1281" max="1284" width="7.42578125" style="10" customWidth="1"/>
+    <col min="1285" max="1285" width="9.140625" style="10"/>
+    <col min="1286" max="1286" width="5.5703125" style="10" customWidth="1"/>
+    <col min="1287" max="1287" width="3.5703125" style="10" customWidth="1"/>
+    <col min="1288" max="1288" width="5.140625" style="10" customWidth="1"/>
+    <col min="1289" max="1289" width="5.42578125" style="10" customWidth="1"/>
+    <col min="1290" max="1290" width="9.140625" style="10"/>
+    <col min="1291" max="1291" width="17.140625" style="10" customWidth="1"/>
+    <col min="1292" max="1292" width="9.140625" style="10"/>
+    <col min="1293" max="1293" width="9" style="10" customWidth="1"/>
+    <col min="1294" max="1536" width="9.140625" style="10"/>
+    <col min="1537" max="1540" width="7.42578125" style="10" customWidth="1"/>
+    <col min="1541" max="1541" width="9.140625" style="10"/>
+    <col min="1542" max="1542" width="5.5703125" style="10" customWidth="1"/>
+    <col min="1543" max="1543" width="3.5703125" style="10" customWidth="1"/>
+    <col min="1544" max="1544" width="5.140625" style="10" customWidth="1"/>
+    <col min="1545" max="1545" width="5.42578125" style="10" customWidth="1"/>
+    <col min="1546" max="1546" width="9.140625" style="10"/>
+    <col min="1547" max="1547" width="17.140625" style="10" customWidth="1"/>
+    <col min="1548" max="1548" width="9.140625" style="10"/>
+    <col min="1549" max="1549" width="9" style="10" customWidth="1"/>
+    <col min="1550" max="1792" width="9.140625" style="10"/>
+    <col min="1793" max="1796" width="7.42578125" style="10" customWidth="1"/>
+    <col min="1797" max="1797" width="9.140625" style="10"/>
+    <col min="1798" max="1798" width="5.5703125" style="10" customWidth="1"/>
+    <col min="1799" max="1799" width="3.5703125" style="10" customWidth="1"/>
+    <col min="1800" max="1800" width="5.140625" style="10" customWidth="1"/>
+    <col min="1801" max="1801" width="5.42578125" style="10" customWidth="1"/>
+    <col min="1802" max="1802" width="9.140625" style="10"/>
+    <col min="1803" max="1803" width="17.140625" style="10" customWidth="1"/>
+    <col min="1804" max="1804" width="9.140625" style="10"/>
+    <col min="1805" max="1805" width="9" style="10" customWidth="1"/>
+    <col min="1806" max="2048" width="9.140625" style="10"/>
+    <col min="2049" max="2052" width="7.42578125" style="10" customWidth="1"/>
+    <col min="2053" max="2053" width="9.140625" style="10"/>
+    <col min="2054" max="2054" width="5.5703125" style="10" customWidth="1"/>
+    <col min="2055" max="2055" width="3.5703125" style="10" customWidth="1"/>
+    <col min="2056" max="2056" width="5.140625" style="10" customWidth="1"/>
+    <col min="2057" max="2057" width="5.42578125" style="10" customWidth="1"/>
+    <col min="2058" max="2058" width="9.140625" style="10"/>
+    <col min="2059" max="2059" width="17.140625" style="10" customWidth="1"/>
+    <col min="2060" max="2060" width="9.140625" style="10"/>
+    <col min="2061" max="2061" width="9" style="10" customWidth="1"/>
+    <col min="2062" max="2304" width="9.140625" style="10"/>
+    <col min="2305" max="2308" width="7.42578125" style="10" customWidth="1"/>
+    <col min="2309" max="2309" width="9.140625" style="10"/>
+    <col min="2310" max="2310" width="5.5703125" style="10" customWidth="1"/>
+    <col min="2311" max="2311" width="3.5703125" style="10" customWidth="1"/>
+    <col min="2312" max="2312" width="5.140625" style="10" customWidth="1"/>
+    <col min="2313" max="2313" width="5.42578125" style="10" customWidth="1"/>
+    <col min="2314" max="2314" width="9.140625" style="10"/>
+    <col min="2315" max="2315" width="17.140625" style="10" customWidth="1"/>
+    <col min="2316" max="2316" width="9.140625" style="10"/>
+    <col min="2317" max="2317" width="9" style="10" customWidth="1"/>
+    <col min="2318" max="2560" width="9.140625" style="10"/>
+    <col min="2561" max="2564" width="7.42578125" style="10" customWidth="1"/>
+    <col min="2565" max="2565" width="9.140625" style="10"/>
+    <col min="2566" max="2566" width="5.5703125" style="10" customWidth="1"/>
+    <col min="2567" max="2567" width="3.5703125" style="10" customWidth="1"/>
+    <col min="2568" max="2568" width="5.140625" style="10" customWidth="1"/>
+    <col min="2569" max="2569" width="5.42578125" style="10" customWidth="1"/>
+    <col min="2570" max="2570" width="9.140625" style="10"/>
+    <col min="2571" max="2571" width="17.140625" style="10" customWidth="1"/>
+    <col min="2572" max="2572" width="9.140625" style="10"/>
+    <col min="2573" max="2573" width="9" style="10" customWidth="1"/>
+    <col min="2574" max="2816" width="9.140625" style="10"/>
+    <col min="2817" max="2820" width="7.42578125" style="10" customWidth="1"/>
+    <col min="2821" max="2821" width="9.140625" style="10"/>
+    <col min="2822" max="2822" width="5.5703125" style="10" customWidth="1"/>
+    <col min="2823" max="2823" width="3.5703125" style="10" customWidth="1"/>
+    <col min="2824" max="2824" width="5.140625" style="10" customWidth="1"/>
+    <col min="2825" max="2825" width="5.42578125" style="10" customWidth="1"/>
+    <col min="2826" max="2826" width="9.140625" style="10"/>
+    <col min="2827" max="2827" width="17.140625" style="10" customWidth="1"/>
+    <col min="2828" max="2828" width="9.140625" style="10"/>
+    <col min="2829" max="2829" width="9" style="10" customWidth="1"/>
+    <col min="2830" max="3072" width="9.140625" style="10"/>
+    <col min="3073" max="3076" width="7.42578125" style="10" customWidth="1"/>
+    <col min="3077" max="3077" width="9.140625" style="10"/>
+    <col min="3078" max="3078" width="5.5703125" style="10" customWidth="1"/>
+    <col min="3079" max="3079" width="3.5703125" style="10" customWidth="1"/>
+    <col min="3080" max="3080" width="5.140625" style="10" customWidth="1"/>
+    <col min="3081" max="3081" width="5.42578125" style="10" customWidth="1"/>
+    <col min="3082" max="3082" width="9.140625" style="10"/>
+    <col min="3083" max="3083" width="17.140625" style="10" customWidth="1"/>
+    <col min="3084" max="3084" width="9.140625" style="10"/>
+    <col min="3085" max="3085" width="9" style="10" customWidth="1"/>
+    <col min="3086" max="3328" width="9.140625" style="10"/>
+    <col min="3329" max="3332" width="7.42578125" style="10" customWidth="1"/>
+    <col min="3333" max="3333" width="9.140625" style="10"/>
+    <col min="3334" max="3334" width="5.5703125" style="10" customWidth="1"/>
+    <col min="3335" max="3335" width="3.5703125" style="10" customWidth="1"/>
+    <col min="3336" max="3336" width="5.140625" style="10" customWidth="1"/>
+    <col min="3337" max="3337" width="5.42578125" style="10" customWidth="1"/>
+    <col min="3338" max="3338" width="9.140625" style="10"/>
+    <col min="3339" max="3339" width="17.140625" style="10" customWidth="1"/>
+    <col min="3340" max="3340" width="9.140625" style="10"/>
+    <col min="3341" max="3341" width="9" style="10" customWidth="1"/>
+    <col min="3342" max="3584" width="9.140625" style="10"/>
+    <col min="3585" max="3588" width="7.42578125" style="10" customWidth="1"/>
+    <col min="3589" max="3589" width="9.140625" style="10"/>
+    <col min="3590" max="3590" width="5.5703125" style="10" customWidth="1"/>
+    <col min="3591" max="3591" width="3.5703125" style="10" customWidth="1"/>
+    <col min="3592" max="3592" width="5.140625" style="10" customWidth="1"/>
+    <col min="3593" max="3593" width="5.42578125" style="10" customWidth="1"/>
+    <col min="3594" max="3594" width="9.140625" style="10"/>
+    <col min="3595" max="3595" width="17.140625" style="10" customWidth="1"/>
+    <col min="3596" max="3596" width="9.140625" style="10"/>
+    <col min="3597" max="3597" width="9" style="10" customWidth="1"/>
+    <col min="3598" max="3840" width="9.140625" style="10"/>
+    <col min="3841" max="3844" width="7.42578125" style="10" customWidth="1"/>
+    <col min="3845" max="3845" width="9.140625" style="10"/>
+    <col min="3846" max="3846" width="5.5703125" style="10" customWidth="1"/>
+    <col min="3847" max="3847" width="3.5703125" style="10" customWidth="1"/>
+    <col min="3848" max="3848" width="5.140625" style="10" customWidth="1"/>
+    <col min="3849" max="3849" width="5.42578125" style="10" customWidth="1"/>
+    <col min="3850" max="3850" width="9.140625" style="10"/>
+    <col min="3851" max="3851" width="17.140625" style="10" customWidth="1"/>
+    <col min="3852" max="3852" width="9.140625" style="10"/>
+    <col min="3853" max="3853" width="9" style="10" customWidth="1"/>
+    <col min="3854" max="4096" width="9.140625" style="10"/>
+    <col min="4097" max="4100" width="7.42578125" style="10" customWidth="1"/>
+    <col min="4101" max="4101" width="9.140625" style="10"/>
+    <col min="4102" max="4102" width="5.5703125" style="10" customWidth="1"/>
+    <col min="4103" max="4103" width="3.5703125" style="10" customWidth="1"/>
+    <col min="4104" max="4104" width="5.140625" style="10" customWidth="1"/>
+    <col min="4105" max="4105" width="5.42578125" style="10" customWidth="1"/>
+    <col min="4106" max="4106" width="9.140625" style="10"/>
+    <col min="4107" max="4107" width="17.140625" style="10" customWidth="1"/>
+    <col min="4108" max="4108" width="9.140625" style="10"/>
+    <col min="4109" max="4109" width="9" style="10" customWidth="1"/>
+    <col min="4110" max="4352" width="9.140625" style="10"/>
+    <col min="4353" max="4356" width="7.42578125" style="10" customWidth="1"/>
+    <col min="4357" max="4357" width="9.140625" style="10"/>
+    <col min="4358" max="4358" width="5.5703125" style="10" customWidth="1"/>
+    <col min="4359" max="4359" width="3.5703125" style="10" customWidth="1"/>
+    <col min="4360" max="4360" width="5.140625" style="10" customWidth="1"/>
+    <col min="4361" max="4361" width="5.42578125" style="10" customWidth="1"/>
+    <col min="4362" max="4362" width="9.140625" style="10"/>
+    <col min="4363" max="4363" width="17.140625" style="10" customWidth="1"/>
+    <col min="4364" max="4364" width="9.140625" style="10"/>
+    <col min="4365" max="4365" width="9" style="10" customWidth="1"/>
+    <col min="4366" max="4608" width="9.140625" style="10"/>
+    <col min="4609" max="4612" width="7.42578125" style="10" customWidth="1"/>
+    <col min="4613" max="4613" width="9.140625" style="10"/>
+    <col min="4614" max="4614" width="5.5703125" style="10" customWidth="1"/>
+    <col min="4615" max="4615" width="3.5703125" style="10" customWidth="1"/>
+    <col min="4616" max="4616" width="5.140625" style="10" customWidth="1"/>
+    <col min="4617" max="4617" width="5.42578125" style="10" customWidth="1"/>
+    <col min="4618" max="4618" width="9.140625" style="10"/>
+    <col min="4619" max="4619" width="17.140625" style="10" customWidth="1"/>
+    <col min="4620" max="4620" width="9.140625" style="10"/>
+    <col min="4621" max="4621" width="9" style="10" customWidth="1"/>
+    <col min="4622" max="4864" width="9.140625" style="10"/>
+    <col min="4865" max="4868" width="7.42578125" style="10" customWidth="1"/>
+    <col min="4869" max="4869" width="9.140625" style="10"/>
+    <col min="4870" max="4870" width="5.5703125" style="10" customWidth="1"/>
+    <col min="4871" max="4871" width="3.5703125" style="10" customWidth="1"/>
+    <col min="4872" max="4872" width="5.140625" style="10" customWidth="1"/>
+    <col min="4873" max="4873" width="5.42578125" style="10" customWidth="1"/>
+    <col min="4874" max="4874" width="9.140625" style="10"/>
+    <col min="4875" max="4875" width="17.140625" style="10" customWidth="1"/>
+    <col min="4876" max="4876" width="9.140625" style="10"/>
+    <col min="4877" max="4877" width="9" style="10" customWidth="1"/>
+    <col min="4878" max="5120" width="9.140625" style="10"/>
+    <col min="5121" max="5124" width="7.42578125" style="10" customWidth="1"/>
+    <col min="5125" max="5125" width="9.140625" style="10"/>
+    <col min="5126" max="5126" width="5.5703125" style="10" customWidth="1"/>
+    <col min="5127" max="5127" width="3.5703125" style="10" customWidth="1"/>
+    <col min="5128" max="5128" width="5.140625" style="10" customWidth="1"/>
+    <col min="5129" max="5129" width="5.42578125" style="10" customWidth="1"/>
+    <col min="5130" max="5130" width="9.140625" style="10"/>
+    <col min="5131" max="5131" width="17.140625" style="10" customWidth="1"/>
+    <col min="5132" max="5132" width="9.140625" style="10"/>
+    <col min="5133" max="5133" width="9" style="10" customWidth="1"/>
+    <col min="5134" max="5376" width="9.140625" style="10"/>
+    <col min="5377" max="5380" width="7.42578125" style="10" customWidth="1"/>
+    <col min="5381" max="5381" width="9.140625" style="10"/>
+    <col min="5382" max="5382" width="5.5703125" style="10" customWidth="1"/>
+    <col min="5383" max="5383" width="3.5703125" style="10" customWidth="1"/>
+    <col min="5384" max="5384" width="5.140625" style="10" customWidth="1"/>
+    <col min="5385" max="5385" width="5.42578125" style="10" customWidth="1"/>
+    <col min="5386" max="5386" width="9.140625" style="10"/>
+    <col min="5387" max="5387" width="17.140625" style="10" customWidth="1"/>
+    <col min="5388" max="5388" width="9.140625" style="10"/>
+    <col min="5389" max="5389" width="9" style="10" customWidth="1"/>
+    <col min="5390" max="5632" width="9.140625" style="10"/>
+    <col min="5633" max="5636" width="7.42578125" style="10" customWidth="1"/>
+    <col min="5637" max="5637" width="9.140625" style="10"/>
+    <col min="5638" max="5638" width="5.5703125" style="10" customWidth="1"/>
+    <col min="5639" max="5639" width="3.5703125" style="10" customWidth="1"/>
+    <col min="5640" max="5640" width="5.140625" style="10" customWidth="1"/>
+    <col min="5641" max="5641" width="5.42578125" style="10" customWidth="1"/>
+    <col min="5642" max="5642" width="9.140625" style="10"/>
+    <col min="5643" max="5643" width="17.140625" style="10" customWidth="1"/>
+    <col min="5644" max="5644" width="9.140625" style="10"/>
+    <col min="5645" max="5645" width="9" style="10" customWidth="1"/>
+    <col min="5646" max="5888" width="9.140625" style="10"/>
+    <col min="5889" max="5892" width="7.42578125" style="10" customWidth="1"/>
+    <col min="5893" max="5893" width="9.140625" style="10"/>
+    <col min="5894" max="5894" width="5.5703125" style="10" customWidth="1"/>
+    <col min="5895" max="5895" width="3.5703125" style="10" customWidth="1"/>
+    <col min="5896" max="5896" width="5.140625" style="10" customWidth="1"/>
+    <col min="5897" max="5897" width="5.42578125" style="10" customWidth="1"/>
+    <col min="5898" max="5898" width="9.140625" style="10"/>
+    <col min="5899" max="5899" width="17.140625" style="10" customWidth="1"/>
+    <col min="5900" max="5900" width="9.140625" style="10"/>
+    <col min="5901" max="5901" width="9" style="10" customWidth="1"/>
+    <col min="5902" max="6144" width="9.140625" style="10"/>
+    <col min="6145" max="6148" width="7.42578125" style="10" customWidth="1"/>
+    <col min="6149" max="6149" width="9.140625" style="10"/>
+    <col min="6150" max="6150" width="5.5703125" style="10" customWidth="1"/>
+    <col min="6151" max="6151" width="3.5703125" style="10" customWidth="1"/>
+    <col min="6152" max="6152" width="5.140625" style="10" customWidth="1"/>
+    <col min="6153" max="6153" width="5.42578125" style="10" customWidth="1"/>
+    <col min="6154" max="6154" width="9.140625" style="10"/>
+    <col min="6155" max="6155" width="17.140625" style="10" customWidth="1"/>
+    <col min="6156" max="6156" width="9.140625" style="10"/>
+    <col min="6157" max="6157" width="9" style="10" customWidth="1"/>
+    <col min="6158" max="6400" width="9.140625" style="10"/>
+    <col min="6401" max="6404" width="7.42578125" style="10" customWidth="1"/>
+    <col min="6405" max="6405" width="9.140625" style="10"/>
+    <col min="6406" max="6406" width="5.5703125" style="10" customWidth="1"/>
+    <col min="6407" max="6407" width="3.5703125" style="10" customWidth="1"/>
+    <col min="6408" max="6408" width="5.140625" style="10" customWidth="1"/>
+    <col min="6409" max="6409" width="5.42578125" style="10" customWidth="1"/>
+    <col min="6410" max="6410" width="9.140625" style="10"/>
+    <col min="6411" max="6411" width="17.140625" style="10" customWidth="1"/>
+    <col min="6412" max="6412" width="9.140625" style="10"/>
+    <col min="6413" max="6413" width="9" style="10" customWidth="1"/>
+    <col min="6414" max="6656" width="9.140625" style="10"/>
+    <col min="6657" max="6660" width="7.42578125" style="10" customWidth="1"/>
+    <col min="6661" max="6661" width="9.140625" style="10"/>
+    <col min="6662" max="6662" width="5.5703125" style="10" customWidth="1"/>
+    <col min="6663" max="6663" width="3.5703125" style="10" customWidth="1"/>
+    <col min="6664" max="6664" width="5.140625" style="10" customWidth="1"/>
+    <col min="6665" max="6665" width="5.42578125" style="10" customWidth="1"/>
+    <col min="6666" max="6666" width="9.140625" style="10"/>
+    <col min="6667" max="6667" width="17.140625" style="10" customWidth="1"/>
+    <col min="6668" max="6668" width="9.140625" style="10"/>
+    <col min="6669" max="6669" width="9" style="10" customWidth="1"/>
+    <col min="6670" max="6912" width="9.140625" style="10"/>
+    <col min="6913" max="6916" width="7.42578125" style="10" customWidth="1"/>
+    <col min="6917" max="6917" width="9.140625" style="10"/>
+    <col min="6918" max="6918" width="5.5703125" style="10" customWidth="1"/>
+    <col min="6919" max="6919" width="3.5703125" style="10" customWidth="1"/>
+    <col min="6920" max="6920" width="5.140625" style="10" customWidth="1"/>
+    <col min="6921" max="6921" width="5.42578125" style="10" customWidth="1"/>
+    <col min="6922" max="6922" width="9.140625" style="10"/>
+    <col min="6923" max="6923" width="17.140625" style="10" customWidth="1"/>
+    <col min="6924" max="6924" width="9.140625" style="10"/>
+    <col min="6925" max="6925" width="9" style="10" customWidth="1"/>
+    <col min="6926" max="7168" width="9.140625" style="10"/>
+    <col min="7169" max="7172" width="7.42578125" style="10" customWidth="1"/>
+    <col min="7173" max="7173" width="9.140625" style="10"/>
+    <col min="7174" max="7174" width="5.5703125" style="10" customWidth="1"/>
+    <col min="7175" max="7175" width="3.5703125" style="10" customWidth="1"/>
+    <col min="7176" max="7176" width="5.140625" style="10" customWidth="1"/>
+    <col min="7177" max="7177" width="5.42578125" style="10" customWidth="1"/>
+    <col min="7178" max="7178" width="9.140625" style="10"/>
+    <col min="7179" max="7179" width="17.140625" style="10" customWidth="1"/>
+    <col min="7180" max="7180" width="9.140625" style="10"/>
+    <col min="7181" max="7181" width="9" style="10" customWidth="1"/>
+    <col min="7182" max="7424" width="9.140625" style="10"/>
+    <col min="7425" max="7428" width="7.42578125" style="10" customWidth="1"/>
+    <col min="7429" max="7429" width="9.140625" style="10"/>
+    <col min="7430" max="7430" width="5.5703125" style="10" customWidth="1"/>
+    <col min="7431" max="7431" width="3.5703125" style="10" customWidth="1"/>
+    <col min="7432" max="7432" width="5.140625" style="10" customWidth="1"/>
+    <col min="7433" max="7433" width="5.42578125" style="10" customWidth="1"/>
+    <col min="7434" max="7434" width="9.140625" style="10"/>
+    <col min="7435" max="7435" width="17.140625" style="10" customWidth="1"/>
+    <col min="7436" max="7436" width="9.140625" style="10"/>
+    <col min="7437" max="7437" width="9" style="10" customWidth="1"/>
+    <col min="7438" max="7680" width="9.140625" style="10"/>
+    <col min="7681" max="7684" width="7.42578125" style="10" customWidth="1"/>
+    <col min="7685" max="7685" width="9.140625" style="10"/>
+    <col min="7686" max="7686" width="5.5703125" style="10" customWidth="1"/>
+    <col min="7687" max="7687" width="3.5703125" style="10" customWidth="1"/>
+    <col min="7688" max="7688" width="5.140625" style="10" customWidth="1"/>
+    <col min="7689" max="7689" width="5.42578125" style="10" customWidth="1"/>
+    <col min="7690" max="7690" width="9.140625" style="10"/>
+    <col min="7691" max="7691" width="17.140625" style="10" customWidth="1"/>
+    <col min="7692" max="7692" width="9.140625" style="10"/>
+    <col min="7693" max="7693" width="9" style="10" customWidth="1"/>
+    <col min="7694" max="7936" width="9.140625" style="10"/>
+    <col min="7937" max="7940" width="7.42578125" style="10" customWidth="1"/>
+    <col min="7941" max="7941" width="9.140625" style="10"/>
+    <col min="7942" max="7942" width="5.5703125" style="10" customWidth="1"/>
+    <col min="7943" max="7943" width="3.5703125" style="10" customWidth="1"/>
+    <col min="7944" max="7944" width="5.140625" style="10" customWidth="1"/>
+    <col min="7945" max="7945" width="5.42578125" style="10" customWidth="1"/>
+    <col min="7946" max="7946" width="9.140625" style="10"/>
+    <col min="7947" max="7947" width="17.140625" style="10" customWidth="1"/>
+    <col min="7948" max="7948" width="9.140625" style="10"/>
+    <col min="7949" max="7949" width="9" style="10" customWidth="1"/>
+    <col min="7950" max="8192" width="9.140625" style="10"/>
+    <col min="8193" max="8196" width="7.42578125" style="10" customWidth="1"/>
+    <col min="8197" max="8197" width="9.140625" style="10"/>
+    <col min="8198" max="8198" width="5.5703125" style="10" customWidth="1"/>
+    <col min="8199" max="8199" width="3.5703125" style="10" customWidth="1"/>
+    <col min="8200" max="8200" width="5.140625" style="10" customWidth="1"/>
+    <col min="8201" max="8201" width="5.42578125" style="10" customWidth="1"/>
+    <col min="8202" max="8202" width="9.140625" style="10"/>
+    <col min="8203" max="8203" width="17.140625" style="10" customWidth="1"/>
+    <col min="8204" max="8204" width="9.140625" style="10"/>
+    <col min="8205" max="8205" width="9" style="10" customWidth="1"/>
+    <col min="8206" max="8448" width="9.140625" style="10"/>
+    <col min="8449" max="8452" width="7.42578125" style="10" customWidth="1"/>
+    <col min="8453" max="8453" width="9.140625" style="10"/>
+    <col min="8454" max="8454" width="5.5703125" style="10" customWidth="1"/>
+    <col min="8455" max="8455" width="3.5703125" style="10" customWidth="1"/>
+    <col min="8456" max="8456" width="5.140625" style="10" customWidth="1"/>
+    <col min="8457" max="8457" width="5.42578125" style="10" customWidth="1"/>
+    <col min="8458" max="8458" width="9.140625" style="10"/>
+    <col min="8459" max="8459" width="17.140625" style="10" customWidth="1"/>
+    <col min="8460" max="8460" width="9.140625" style="10"/>
+    <col min="8461" max="8461" width="9" style="10" customWidth="1"/>
+    <col min="8462" max="8704" width="9.140625" style="10"/>
+    <col min="8705" max="8708" width="7.42578125" style="10" customWidth="1"/>
+    <col min="8709" max="8709" width="9.140625" style="10"/>
+    <col min="8710" max="8710" width="5.5703125" style="10" customWidth="1"/>
+    <col min="8711" max="8711" width="3.5703125" style="10" customWidth="1"/>
+    <col min="8712" max="8712" width="5.140625" style="10" customWidth="1"/>
+    <col min="8713" max="8713" width="5.42578125" style="10" customWidth="1"/>
+    <col min="8714" max="8714" width="9.140625" style="10"/>
+    <col min="8715" max="8715" width="17.140625" style="10" customWidth="1"/>
+    <col min="8716" max="8716" width="9.140625" style="10"/>
+    <col min="8717" max="8717" width="9" style="10" customWidth="1"/>
+    <col min="8718" max="8960" width="9.140625" style="10"/>
+    <col min="8961" max="8964" width="7.42578125" style="10" customWidth="1"/>
+    <col min="8965" max="8965" width="9.140625" style="10"/>
+    <col min="8966" max="8966" width="5.5703125" style="10" customWidth="1"/>
+    <col min="8967" max="8967" width="3.5703125" style="10" customWidth="1"/>
+    <col min="8968" max="8968" width="5.140625" style="10" customWidth="1"/>
+    <col min="8969" max="8969" width="5.42578125" style="10" customWidth="1"/>
+    <col min="8970" max="8970" width="9.140625" style="10"/>
+    <col min="8971" max="8971" width="17.140625" style="10" customWidth="1"/>
+    <col min="8972" max="8972" width="9.140625" style="10"/>
+    <col min="8973" max="8973" width="9" style="10" customWidth="1"/>
+    <col min="8974" max="9216" width="9.140625" style="10"/>
+    <col min="9217" max="9220" width="7.42578125" style="10" customWidth="1"/>
+    <col min="9221" max="9221" width="9.140625" style="10"/>
+    <col min="9222" max="9222" width="5.5703125" style="10" customWidth="1"/>
+    <col min="9223" max="9223" width="3.5703125" style="10" customWidth="1"/>
+    <col min="9224" max="9224" width="5.140625" style="10" customWidth="1"/>
+    <col min="9225" max="9225" width="5.42578125" style="10" customWidth="1"/>
+    <col min="9226" max="9226" width="9.140625" style="10"/>
+    <col min="9227" max="9227" width="17.140625" style="10" customWidth="1"/>
+    <col min="9228" max="9228" width="9.140625" style="10"/>
+    <col min="9229" max="9229" width="9" style="10" customWidth="1"/>
+    <col min="9230" max="9472" width="9.140625" style="10"/>
+    <col min="9473" max="9476" width="7.42578125" style="10" customWidth="1"/>
+    <col min="9477" max="9477" width="9.140625" style="10"/>
+    <col min="9478" max="9478" width="5.5703125" style="10" customWidth="1"/>
+    <col min="9479" max="9479" width="3.5703125" style="10" customWidth="1"/>
+    <col min="9480" max="9480" width="5.140625" style="10" customWidth="1"/>
+    <col min="9481" max="9481" width="5.42578125" style="10" customWidth="1"/>
+    <col min="9482" max="9482" width="9.140625" style="10"/>
+    <col min="9483" max="9483" width="17.140625" style="10" customWidth="1"/>
+    <col min="9484" max="9484" width="9.140625" style="10"/>
+    <col min="9485" max="9485" width="9" style="10" customWidth="1"/>
+    <col min="9486" max="9728" width="9.140625" style="10"/>
+    <col min="9729" max="9732" width="7.42578125" style="10" customWidth="1"/>
+    <col min="9733" max="9733" width="9.140625" style="10"/>
+    <col min="9734" max="9734" width="5.5703125" style="10" customWidth="1"/>
+    <col min="9735" max="9735" width="3.5703125" style="10" customWidth="1"/>
+    <col min="9736" max="9736" width="5.140625" style="10" customWidth="1"/>
+    <col min="9737" max="9737" width="5.42578125" style="10" customWidth="1"/>
+    <col min="9738" max="9738" width="9.140625" style="10"/>
+    <col min="9739" max="9739" width="17.140625" style="10" customWidth="1"/>
+    <col min="9740" max="9740" width="9.140625" style="10"/>
+    <col min="9741" max="9741" width="9" style="10" customWidth="1"/>
+    <col min="9742" max="9984" width="9.140625" style="10"/>
+    <col min="9985" max="9988" width="7.42578125" style="10" customWidth="1"/>
+    <col min="9989" max="9989" width="9.140625" style="10"/>
+    <col min="9990" max="9990" width="5.5703125" style="10" customWidth="1"/>
+    <col min="9991" max="9991" width="3.5703125" style="10" customWidth="1"/>
+    <col min="9992" max="9992" width="5.140625" style="10" customWidth="1"/>
+    <col min="9993" max="9993" width="5.42578125" style="10" customWidth="1"/>
+    <col min="9994" max="9994" width="9.140625" style="10"/>
+    <col min="9995" max="9995" width="17.140625" style="10" customWidth="1"/>
+    <col min="9996" max="9996" width="9.140625" style="10"/>
+    <col min="9997" max="9997" width="9" style="10" customWidth="1"/>
+    <col min="9998" max="10240" width="9.140625" style="10"/>
+    <col min="10241" max="10244" width="7.42578125" style="10" customWidth="1"/>
+    <col min="10245" max="10245" width="9.140625" style="10"/>
+    <col min="10246" max="10246" width="5.5703125" style="10" customWidth="1"/>
+    <col min="10247" max="10247" width="3.5703125" style="10" customWidth="1"/>
+    <col min="10248" max="10248" width="5.140625" style="10" customWidth="1"/>
+    <col min="10249" max="10249" width="5.42578125" style="10" customWidth="1"/>
+    <col min="10250" max="10250" width="9.140625" style="10"/>
+    <col min="10251" max="10251" width="17.140625" style="10" customWidth="1"/>
+    <col min="10252" max="10252" width="9.140625" style="10"/>
+    <col min="10253" max="10253" width="9" style="10" customWidth="1"/>
+    <col min="10254" max="10496" width="9.140625" style="10"/>
+    <col min="10497" max="10500" width="7.42578125" style="10" customWidth="1"/>
+    <col min="10501" max="10501" width="9.140625" style="10"/>
+    <col min="10502" max="10502" width="5.5703125" style="10" customWidth="1"/>
+    <col min="10503" max="10503" width="3.5703125" style="10" customWidth="1"/>
+    <col min="10504" max="10504" width="5.140625" style="10" customWidth="1"/>
+    <col min="10505" max="10505" width="5.42578125" style="10" customWidth="1"/>
+    <col min="10506" max="10506" width="9.140625" style="10"/>
+    <col min="10507" max="10507" width="17.140625" style="10" customWidth="1"/>
+    <col min="10508" max="10508" width="9.140625" style="10"/>
+    <col min="10509" max="10509" width="9" style="10" customWidth="1"/>
+    <col min="10510" max="10752" width="9.140625" style="10"/>
+    <col min="10753" max="10756" width="7.42578125" style="10" customWidth="1"/>
+    <col min="10757" max="10757" width="9.140625" style="10"/>
+    <col min="10758" max="10758" width="5.5703125" style="10" customWidth="1"/>
+    <col min="10759" max="10759" width="3.5703125" style="10" customWidth="1"/>
+    <col min="10760" max="10760" width="5.140625" style="10" customWidth="1"/>
+    <col min="10761" max="10761" width="5.42578125" style="10" customWidth="1"/>
+    <col min="10762" max="10762" width="9.140625" style="10"/>
+    <col min="10763" max="10763" width="17.140625" style="10" customWidth="1"/>
+    <col min="10764" max="10764" width="9.140625" style="10"/>
+    <col min="10765" max="10765" width="9" style="10" customWidth="1"/>
+    <col min="10766" max="11008" width="9.140625" style="10"/>
+    <col min="11009" max="11012" width="7.42578125" style="10" customWidth="1"/>
+    <col min="11013" max="11013" width="9.140625" style="10"/>
+    <col min="11014" max="11014" width="5.5703125" style="10" customWidth="1"/>
+    <col min="11015" max="11015" width="3.5703125" style="10" customWidth="1"/>
+    <col min="11016" max="11016" width="5.140625" style="10" customWidth="1"/>
+    <col min="11017" max="11017" width="5.42578125" style="10" customWidth="1"/>
+    <col min="11018" max="11018" width="9.140625" style="10"/>
+    <col min="11019" max="11019" width="17.140625" style="10" customWidth="1"/>
+    <col min="11020" max="11020" width="9.140625" style="10"/>
+    <col min="11021" max="11021" width="9" style="10" customWidth="1"/>
+    <col min="11022" max="11264" width="9.140625" style="10"/>
+    <col min="11265" max="11268" width="7.42578125" style="10" customWidth="1"/>
+    <col min="11269" max="11269" width="9.140625" style="10"/>
+    <col min="11270" max="11270" width="5.5703125" style="10" customWidth="1"/>
+    <col min="11271" max="11271" width="3.5703125" style="10" customWidth="1"/>
+    <col min="11272" max="11272" width="5.140625" style="10" customWidth="1"/>
+    <col min="11273" max="11273" width="5.42578125" style="10" customWidth="1"/>
+    <col min="11274" max="11274" width="9.140625" style="10"/>
+    <col min="11275" max="11275" width="17.140625" style="10" customWidth="1"/>
+    <col min="11276" max="11276" width="9.140625" style="10"/>
+    <col min="11277" max="11277" width="9" style="10" customWidth="1"/>
+    <col min="11278" max="11520" width="9.140625" style="10"/>
+    <col min="11521" max="11524" width="7.42578125" style="10" customWidth="1"/>
+    <col min="11525" max="11525" width="9.140625" style="10"/>
+    <col min="11526" max="11526" width="5.5703125" style="10" customWidth="1"/>
+    <col min="11527" max="11527" width="3.5703125" style="10" customWidth="1"/>
+    <col min="11528" max="11528" width="5.140625" style="10" customWidth="1"/>
+    <col min="11529" max="11529" width="5.42578125" style="10" customWidth="1"/>
+    <col min="11530" max="11530" width="9.140625" style="10"/>
+    <col min="11531" max="11531" width="17.140625" style="10" customWidth="1"/>
+    <col min="11532" max="11532" width="9.140625" style="10"/>
+    <col min="11533" max="11533" width="9" style="10" customWidth="1"/>
+    <col min="11534" max="11776" width="9.140625" style="10"/>
+    <col min="11777" max="11780" width="7.42578125" style="10" customWidth="1"/>
+    <col min="11781" max="11781" width="9.140625" style="10"/>
+    <col min="11782" max="11782" width="5.5703125" style="10" customWidth="1"/>
+    <col min="11783" max="11783" width="3.5703125" style="10" customWidth="1"/>
+    <col min="11784" max="11784" width="5.140625" style="10" customWidth="1"/>
+    <col min="11785" max="11785" width="5.42578125" style="10" customWidth="1"/>
+    <col min="11786" max="11786" width="9.140625" style="10"/>
+    <col min="11787" max="11787" width="17.140625" style="10" customWidth="1"/>
+    <col min="11788" max="11788" width="9.140625" style="10"/>
+    <col min="11789" max="11789" width="9" style="10" customWidth="1"/>
+    <col min="11790" max="12032" width="9.140625" style="10"/>
+    <col min="12033" max="12036" width="7.42578125" style="10" customWidth="1"/>
+    <col min="12037" max="12037" width="9.140625" style="10"/>
+    <col min="12038" max="12038" width="5.5703125" style="10" customWidth="1"/>
+    <col min="12039" max="12039" width="3.5703125" style="10" customWidth="1"/>
+    <col min="12040" max="12040" width="5.140625" style="10" customWidth="1"/>
+    <col min="12041" max="12041" width="5.42578125" style="10" customWidth="1"/>
+    <col min="12042" max="12042" width="9.140625" style="10"/>
+    <col min="12043" max="12043" width="17.140625" style="10" customWidth="1"/>
+    <col min="12044" max="12044" width="9.140625" style="10"/>
+    <col min="12045" max="12045" width="9" style="10" customWidth="1"/>
+    <col min="12046" max="12288" width="9.140625" style="10"/>
+    <col min="12289" max="12292" width="7.42578125" style="10" customWidth="1"/>
+    <col min="12293" max="12293" width="9.140625" style="10"/>
+    <col min="12294" max="12294" width="5.5703125" style="10" customWidth="1"/>
+    <col min="12295" max="12295" width="3.5703125" style="10" customWidth="1"/>
+    <col min="12296" max="12296" width="5.140625" style="10" customWidth="1"/>
+    <col min="12297" max="12297" width="5.42578125" style="10" customWidth="1"/>
+    <col min="12298" max="12298" width="9.140625" style="10"/>
+    <col min="12299" max="12299" width="17.140625" style="10" customWidth="1"/>
+    <col min="12300" max="12300" width="9.140625" style="10"/>
+    <col min="12301" max="12301" width="9" style="10" customWidth="1"/>
+    <col min="12302" max="12544" width="9.140625" style="10"/>
+    <col min="12545" max="12548" width="7.42578125" style="10" customWidth="1"/>
+    <col min="12549" max="12549" width="9.140625" style="10"/>
+    <col min="12550" max="12550" width="5.5703125" style="10" customWidth="1"/>
+    <col min="12551" max="12551" width="3.5703125" style="10" customWidth="1"/>
+    <col min="12552" max="12552" width="5.140625" style="10" customWidth="1"/>
+    <col min="12553" max="12553" width="5.42578125" style="10" customWidth="1"/>
+    <col min="12554" max="12554" width="9.140625" style="10"/>
+    <col min="12555" max="12555" width="17.140625" style="10" customWidth="1"/>
+    <col min="12556" max="12556" width="9.140625" style="10"/>
+    <col min="12557" max="12557" width="9" style="10" customWidth="1"/>
+    <col min="12558" max="12800" width="9.140625" style="10"/>
+    <col min="12801" max="12804" width="7.42578125" style="10" customWidth="1"/>
+    <col min="12805" max="12805" width="9.140625" style="10"/>
+    <col min="12806" max="12806" width="5.5703125" style="10" customWidth="1"/>
+    <col min="12807" max="12807" width="3.5703125" style="10" customWidth="1"/>
+    <col min="12808" max="12808" width="5.140625" style="10" customWidth="1"/>
+    <col min="12809" max="12809" width="5.42578125" style="10" customWidth="1"/>
+    <col min="12810" max="12810" width="9.140625" style="10"/>
+    <col min="12811" max="12811" width="17.140625" style="10" customWidth="1"/>
+    <col min="12812" max="12812" width="9.140625" style="10"/>
+    <col min="12813" max="12813" width="9" style="10" customWidth="1"/>
+    <col min="12814" max="13056" width="9.140625" style="10"/>
+    <col min="13057" max="13060" width="7.42578125" style="10" customWidth="1"/>
+    <col min="13061" max="13061" width="9.140625" style="10"/>
+    <col min="13062" max="13062" width="5.5703125" style="10" customWidth="1"/>
+    <col min="13063" max="13063" width="3.5703125" style="10" customWidth="1"/>
+    <col min="13064" max="13064" width="5.140625" style="10" customWidth="1"/>
+    <col min="13065" max="13065" width="5.42578125" style="10" customWidth="1"/>
+    <col min="13066" max="13066" width="9.140625" style="10"/>
+    <col min="13067" max="13067" width="17.140625" style="10" customWidth="1"/>
+    <col min="13068" max="13068" width="9.140625" style="10"/>
+    <col min="13069" max="13069" width="9" style="10" customWidth="1"/>
+    <col min="13070" max="13312" width="9.140625" style="10"/>
+    <col min="13313" max="13316" width="7.42578125" style="10" customWidth="1"/>
+    <col min="13317" max="13317" width="9.140625" style="10"/>
+    <col min="13318" max="13318" width="5.5703125" style="10" customWidth="1"/>
+    <col min="13319" max="13319" width="3.5703125" style="10" customWidth="1"/>
+    <col min="13320" max="13320" width="5.140625" style="10" customWidth="1"/>
+    <col min="13321" max="13321" width="5.42578125" style="10" customWidth="1"/>
+    <col min="13322" max="13322" width="9.140625" style="10"/>
+    <col min="13323" max="13323" width="17.140625" style="10" customWidth="1"/>
+    <col min="13324" max="13324" width="9.140625" style="10"/>
+    <col min="13325" max="13325" width="9" style="10" customWidth="1"/>
+    <col min="13326" max="13568" width="9.140625" style="10"/>
+    <col min="13569" max="13572" width="7.42578125" style="10" customWidth="1"/>
+    <col min="13573" max="13573" width="9.140625" style="10"/>
+    <col min="13574" max="13574" width="5.5703125" style="10" customWidth="1"/>
+    <col min="13575" max="13575" width="3.5703125" style="10" customWidth="1"/>
+    <col min="13576" max="13576" width="5.140625" style="10" customWidth="1"/>
+    <col min="13577" max="13577" width="5.42578125" style="10" customWidth="1"/>
+    <col min="13578" max="13578" width="9.140625" style="10"/>
+    <col min="13579" max="13579" width="17.140625" style="10" customWidth="1"/>
+    <col min="13580" max="13580" width="9.140625" style="10"/>
+    <col min="13581" max="13581" width="9" style="10" customWidth="1"/>
+    <col min="13582" max="13824" width="9.140625" style="10"/>
+    <col min="13825" max="13828" width="7.42578125" style="10" customWidth="1"/>
+    <col min="13829" max="13829" width="9.140625" style="10"/>
+    <col min="13830" max="13830" width="5.5703125" style="10" customWidth="1"/>
+    <col min="13831" max="13831" width="3.5703125" style="10" customWidth="1"/>
+    <col min="13832" max="13832" width="5.140625" style="10" customWidth="1"/>
+    <col min="13833" max="13833" width="5.42578125" style="10" customWidth="1"/>
+    <col min="13834" max="13834" width="9.140625" style="10"/>
+    <col min="13835" max="13835" width="17.140625" style="10" customWidth="1"/>
+    <col min="13836" max="13836" width="9.140625" style="10"/>
+    <col min="13837" max="13837" width="9" style="10" customWidth="1"/>
+    <col min="13838" max="14080" width="9.140625" style="10"/>
+    <col min="14081" max="14084" width="7.42578125" style="10" customWidth="1"/>
+    <col min="14085" max="14085" width="9.140625" style="10"/>
+    <col min="14086" max="14086" width="5.5703125" style="10" customWidth="1"/>
+    <col min="14087" max="14087" width="3.5703125" style="10" customWidth="1"/>
+    <col min="14088" max="14088" width="5.140625" style="10" customWidth="1"/>
+    <col min="14089" max="14089" width="5.42578125" style="10" customWidth="1"/>
+    <col min="14090" max="14090" width="9.140625" style="10"/>
+    <col min="14091" max="14091" width="17.140625" style="10" customWidth="1"/>
+    <col min="14092" max="14092" width="9.140625" style="10"/>
+    <col min="14093" max="14093" width="9" style="10" customWidth="1"/>
+    <col min="14094" max="14336" width="9.140625" style="10"/>
+    <col min="14337" max="14340" width="7.42578125" style="10" customWidth="1"/>
+    <col min="14341" max="14341" width="9.140625" style="10"/>
+    <col min="14342" max="14342" width="5.5703125" style="10" customWidth="1"/>
+    <col min="14343" max="14343" width="3.5703125" style="10" customWidth="1"/>
+    <col min="14344" max="14344" width="5.140625" style="10" customWidth="1"/>
+    <col min="14345" max="14345" width="5.42578125" style="10" customWidth="1"/>
+    <col min="14346" max="14346" width="9.140625" style="10"/>
+    <col min="14347" max="14347" width="17.140625" style="10" customWidth="1"/>
+    <col min="14348" max="14348" width="9.140625" style="10"/>
+    <col min="14349" max="14349" width="9" style="10" customWidth="1"/>
+    <col min="14350" max="14592" width="9.140625" style="10"/>
+    <col min="14593" max="14596" width="7.42578125" style="10" customWidth="1"/>
+    <col min="14597" max="14597" width="9.140625" style="10"/>
+    <col min="14598" max="14598" width="5.5703125" style="10" customWidth="1"/>
+    <col min="14599" max="14599" width="3.5703125" style="10" customWidth="1"/>
+    <col min="14600" max="14600" width="5.140625" style="10" customWidth="1"/>
+    <col min="14601" max="14601" width="5.42578125" style="10" customWidth="1"/>
+    <col min="14602" max="14602" width="9.140625" style="10"/>
+    <col min="14603" max="14603" width="17.140625" style="10" customWidth="1"/>
+    <col min="14604" max="14604" width="9.140625" style="10"/>
+    <col min="14605" max="14605" width="9" style="10" customWidth="1"/>
+    <col min="14606" max="14848" width="9.140625" style="10"/>
+    <col min="14849" max="14852" width="7.42578125" style="10" customWidth="1"/>
+    <col min="14853" max="14853" width="9.140625" style="10"/>
+    <col min="14854" max="14854" width="5.5703125" style="10" customWidth="1"/>
+    <col min="14855" max="14855" width="3.5703125" style="10" customWidth="1"/>
+    <col min="14856" max="14856" width="5.140625" style="10" customWidth="1"/>
+    <col min="14857" max="14857" width="5.42578125" style="10" customWidth="1"/>
+    <col min="14858" max="14858" width="9.140625" style="10"/>
+    <col min="14859" max="14859" width="17.140625" style="10" customWidth="1"/>
+    <col min="14860" max="14860" width="9.140625" style="10"/>
+    <col min="14861" max="14861" width="9" style="10" customWidth="1"/>
+    <col min="14862" max="15104" width="9.140625" style="10"/>
+    <col min="15105" max="15108" width="7.42578125" style="10" customWidth="1"/>
+    <col min="15109" max="15109" width="9.140625" style="10"/>
+    <col min="15110" max="15110" width="5.5703125" style="10" customWidth="1"/>
+    <col min="15111" max="15111" width="3.5703125" style="10" customWidth="1"/>
+    <col min="15112" max="15112" width="5.140625" style="10" customWidth="1"/>
+    <col min="15113" max="15113" width="5.42578125" style="10" customWidth="1"/>
+    <col min="15114" max="15114" width="9.140625" style="10"/>
+    <col min="15115" max="15115" width="17.140625" style="10" customWidth="1"/>
+    <col min="15116" max="15116" width="9.140625" style="10"/>
+    <col min="15117" max="15117" width="9" style="10" customWidth="1"/>
+    <col min="15118" max="15360" width="9.140625" style="10"/>
+    <col min="15361" max="15364" width="7.42578125" style="10" customWidth="1"/>
+    <col min="15365" max="15365" width="9.140625" style="10"/>
+    <col min="15366" max="15366" width="5.5703125" style="10" customWidth="1"/>
+    <col min="15367" max="15367" width="3.5703125" style="10" customWidth="1"/>
+    <col min="15368" max="15368" width="5.140625" style="10" customWidth="1"/>
+    <col min="15369" max="15369" width="5.42578125" style="10" customWidth="1"/>
+    <col min="15370" max="15370" width="9.140625" style="10"/>
+    <col min="15371" max="15371" width="17.140625" style="10" customWidth="1"/>
+    <col min="15372" max="15372" width="9.140625" style="10"/>
+    <col min="15373" max="15373" width="9" style="10" customWidth="1"/>
+    <col min="15374" max="15616" width="9.140625" style="10"/>
+    <col min="15617" max="15620" width="7.42578125" style="10" customWidth="1"/>
+    <col min="15621" max="15621" width="9.140625" style="10"/>
+    <col min="15622" max="15622" width="5.5703125" style="10" customWidth="1"/>
+    <col min="15623" max="15623" width="3.5703125" style="10" customWidth="1"/>
+    <col min="15624" max="15624" width="5.140625" style="10" customWidth="1"/>
+    <col min="15625" max="15625" width="5.42578125" style="10" customWidth="1"/>
+    <col min="15626" max="15626" width="9.140625" style="10"/>
+    <col min="15627" max="15627" width="17.140625" style="10" customWidth="1"/>
+    <col min="15628" max="15628" width="9.140625" style="10"/>
+    <col min="15629" max="15629" width="9" style="10" customWidth="1"/>
+    <col min="15630" max="15872" width="9.140625" style="10"/>
+    <col min="15873" max="15876" width="7.42578125" style="10" customWidth="1"/>
+    <col min="15877" max="15877" width="9.140625" style="10"/>
+    <col min="15878" max="15878" width="5.5703125" style="10" customWidth="1"/>
+    <col min="15879" max="15879" width="3.5703125" style="10" customWidth="1"/>
+    <col min="15880" max="15880" width="5.140625" style="10" customWidth="1"/>
+    <col min="15881" max="15881" width="5.42578125" style="10" customWidth="1"/>
+    <col min="15882" max="15882" width="9.140625" style="10"/>
+    <col min="15883" max="15883" width="17.140625" style="10" customWidth="1"/>
+    <col min="15884" max="15884" width="9.140625" style="10"/>
+    <col min="15885" max="15885" width="9" style="10" customWidth="1"/>
+    <col min="15886" max="16128" width="9.140625" style="10"/>
+    <col min="16129" max="16132" width="7.42578125" style="10" customWidth="1"/>
+    <col min="16133" max="16133" width="9.140625" style="10"/>
+    <col min="16134" max="16134" width="5.5703125" style="10" customWidth="1"/>
+    <col min="16135" max="16135" width="3.5703125" style="10" customWidth="1"/>
+    <col min="16136" max="16136" width="5.140625" style="10" customWidth="1"/>
+    <col min="16137" max="16137" width="5.42578125" style="10" customWidth="1"/>
+    <col min="16138" max="16138" width="9.140625" style="10"/>
+    <col min="16139" max="16139" width="17.140625" style="10" customWidth="1"/>
+    <col min="16140" max="16140" width="9.140625" style="10"/>
+    <col min="16141" max="16141" width="9" style="10" customWidth="1"/>
+    <col min="16142" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="383" t="s">
+      <c r="A1" s="343" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="384"/>
-      <c r="C1" s="381" t="s">
+      <c r="B1" s="344"/>
+      <c r="C1" s="341" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="381"/>
-      <c r="E1" s="381"/>
-      <c r="F1" s="381"/>
-      <c r="G1" s="381"/>
-      <c r="H1" s="381"/>
-      <c r="I1" s="381"/>
-      <c r="J1" s="381"/>
-      <c r="K1" s="381"/>
-      <c r="L1" s="385" t="s">
+      <c r="D1" s="341"/>
+      <c r="E1" s="341"/>
+      <c r="F1" s="341"/>
+      <c r="G1" s="341"/>
+      <c r="H1" s="341"/>
+      <c r="I1" s="341"/>
+      <c r="J1" s="341"/>
+      <c r="K1" s="341"/>
+      <c r="L1" s="345" t="s">
         <v>62</v>
       </c>
-      <c r="M1" s="386"/>
+      <c r="M1" s="346"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="207" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="248"/>
-      <c r="C2" s="248"/>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="248"/>
-      <c r="H2" s="248"/>
-      <c r="I2" s="248"/>
-      <c r="J2" s="248"/>
-      <c r="K2" s="248"/>
-      <c r="L2" s="248"/>
-      <c r="M2" s="249"/>
+      <c r="B2" s="208"/>
+      <c r="C2" s="208"/>
+      <c r="D2" s="208"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="208"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
+      <c r="M2" s="209"/>
     </row>
     <row r="3" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="250" t="s">
+      <c r="A3" s="210" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="251"/>
-      <c r="C3" s="251"/>
-      <c r="D3" s="251"/>
-      <c r="E3" s="251" t="s">
+      <c r="B3" s="211"/>
+      <c r="C3" s="211"/>
+      <c r="D3" s="211"/>
+      <c r="E3" s="211" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="251" t="s">
+      <c r="F3" s="211" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="251"/>
-      <c r="H3" s="252" t="s">
+      <c r="G3" s="211"/>
+      <c r="H3" s="212" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="253"/>
-      <c r="J3" s="254" t="s">
+      <c r="I3" s="213"/>
+      <c r="J3" s="214" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="255"/>
-      <c r="L3" s="255"/>
-      <c r="M3" s="256"/>
+      <c r="K3" s="215"/>
+      <c r="L3" s="215"/>
+      <c r="M3" s="216"/>
     </row>
     <row r="4" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="250"/>
-      <c r="B4" s="251"/>
-      <c r="C4" s="251"/>
-      <c r="D4" s="251"/>
-      <c r="E4" s="251"/>
-      <c r="F4" s="251"/>
-      <c r="G4" s="251"/>
-      <c r="H4" s="260" t="s">
+      <c r="A4" s="210"/>
+      <c r="B4" s="211"/>
+      <c r="C4" s="211"/>
+      <c r="D4" s="211"/>
+      <c r="E4" s="211"/>
+      <c r="F4" s="211"/>
+      <c r="G4" s="211"/>
+      <c r="H4" s="220" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="261"/>
-      <c r="J4" s="257"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
-      <c r="M4" s="259"/>
+      <c r="I4" s="221"/>
+      <c r="J4" s="217"/>
+      <c r="K4" s="218"/>
+      <c r="L4" s="218"/>
+      <c r="M4" s="219"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="359"/>
-      <c r="B5" s="277"/>
-      <c r="C5" s="277"/>
-      <c r="D5" s="277"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="137"/>
-      <c r="G5" s="139"/>
-      <c r="H5" s="80" t="s">
+      <c r="A5" s="319"/>
+      <c r="B5" s="237"/>
+      <c r="C5" s="237"/>
+      <c r="D5" s="237"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I5" s="80" t="s">
+      <c r="I5" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J5" s="280"/>
-      <c r="K5" s="280"/>
-      <c r="L5" s="280"/>
-      <c r="M5" s="281"/>
+      <c r="J5" s="240"/>
+      <c r="K5" s="240"/>
+      <c r="L5" s="240"/>
+      <c r="M5" s="241"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="359"/>
-      <c r="B6" s="277"/>
-      <c r="C6" s="277"/>
-      <c r="D6" s="277"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="137"/>
-      <c r="G6" s="139"/>
-      <c r="H6" s="80" t="s">
+      <c r="A6" s="319"/>
+      <c r="B6" s="237"/>
+      <c r="C6" s="237"/>
+      <c r="D6" s="237"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="120"/>
+      <c r="H6" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I6" s="80" t="s">
+      <c r="I6" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J6" s="280"/>
-      <c r="K6" s="280"/>
-      <c r="L6" s="280"/>
-      <c r="M6" s="281"/>
+      <c r="J6" s="240"/>
+      <c r="K6" s="240"/>
+      <c r="L6" s="240"/>
+      <c r="M6" s="241"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="359"/>
-      <c r="B7" s="277"/>
-      <c r="C7" s="277"/>
-      <c r="D7" s="277"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="137"/>
-      <c r="G7" s="139"/>
-      <c r="H7" s="80" t="s">
+      <c r="A7" s="319"/>
+      <c r="B7" s="237"/>
+      <c r="C7" s="237"/>
+      <c r="D7" s="237"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="120"/>
+      <c r="H7" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="80" t="s">
+      <c r="I7" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J7" s="280"/>
-      <c r="K7" s="280"/>
-      <c r="L7" s="280"/>
-      <c r="M7" s="281"/>
+      <c r="J7" s="240"/>
+      <c r="K7" s="240"/>
+      <c r="L7" s="240"/>
+      <c r="M7" s="241"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="359"/>
-      <c r="B8" s="277"/>
-      <c r="C8" s="277"/>
-      <c r="D8" s="277"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="137"/>
-      <c r="G8" s="139"/>
-      <c r="H8" s="80" t="s">
+      <c r="A8" s="319"/>
+      <c r="B8" s="237"/>
+      <c r="C8" s="237"/>
+      <c r="D8" s="237"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="118"/>
+      <c r="G8" s="120"/>
+      <c r="H8" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="80" t="s">
+      <c r="I8" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J8" s="280"/>
-      <c r="K8" s="280"/>
-      <c r="L8" s="280"/>
-      <c r="M8" s="281"/>
+      <c r="J8" s="240"/>
+      <c r="K8" s="240"/>
+      <c r="L8" s="240"/>
+      <c r="M8" s="241"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="359"/>
-      <c r="B9" s="277"/>
-      <c r="C9" s="277"/>
-      <c r="D9" s="277"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="137"/>
-      <c r="G9" s="139"/>
-      <c r="H9" s="80" t="s">
+      <c r="A9" s="319"/>
+      <c r="B9" s="237"/>
+      <c r="C9" s="237"/>
+      <c r="D9" s="237"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="118"/>
+      <c r="G9" s="120"/>
+      <c r="H9" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="80" t="s">
+      <c r="I9" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J9" s="280"/>
-      <c r="K9" s="280"/>
-      <c r="L9" s="280"/>
-      <c r="M9" s="281"/>
+      <c r="J9" s="240"/>
+      <c r="K9" s="240"/>
+      <c r="L9" s="240"/>
+      <c r="M9" s="241"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="359"/>
-      <c r="B10" s="277"/>
-      <c r="C10" s="277"/>
-      <c r="D10" s="277"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="137"/>
-      <c r="G10" s="139"/>
-      <c r="H10" s="80" t="s">
+      <c r="A10" s="319"/>
+      <c r="B10" s="237"/>
+      <c r="C10" s="237"/>
+      <c r="D10" s="237"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="118"/>
+      <c r="G10" s="120"/>
+      <c r="H10" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="80" t="s">
+      <c r="I10" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="280"/>
-      <c r="K10" s="280"/>
-      <c r="L10" s="280"/>
-      <c r="M10" s="281"/>
+      <c r="J10" s="240"/>
+      <c r="K10" s="240"/>
+      <c r="L10" s="240"/>
+      <c r="M10" s="241"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="359"/>
-      <c r="B11" s="277"/>
-      <c r="C11" s="277"/>
-      <c r="D11" s="277"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="137"/>
-      <c r="G11" s="139"/>
-      <c r="H11" s="80" t="s">
+      <c r="A11" s="319"/>
+      <c r="B11" s="237"/>
+      <c r="C11" s="237"/>
+      <c r="D11" s="237"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="118"/>
+      <c r="G11" s="120"/>
+      <c r="H11" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="80" t="s">
+      <c r="I11" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J11" s="280"/>
-      <c r="K11" s="280"/>
-      <c r="L11" s="280"/>
-      <c r="M11" s="281"/>
+      <c r="J11" s="240"/>
+      <c r="K11" s="240"/>
+      <c r="L11" s="240"/>
+      <c r="M11" s="241"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="359"/>
-      <c r="B12" s="277"/>
-      <c r="C12" s="277"/>
-      <c r="D12" s="277"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="137"/>
-      <c r="G12" s="139"/>
-      <c r="H12" s="80" t="s">
+      <c r="A12" s="319"/>
+      <c r="B12" s="237"/>
+      <c r="C12" s="237"/>
+      <c r="D12" s="237"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="118"/>
+      <c r="G12" s="120"/>
+      <c r="H12" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I12" s="80" t="s">
+      <c r="I12" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J12" s="280"/>
-      <c r="K12" s="280"/>
-      <c r="L12" s="280"/>
-      <c r="M12" s="281"/>
+      <c r="J12" s="240"/>
+      <c r="K12" s="240"/>
+      <c r="L12" s="240"/>
+      <c r="M12" s="241"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="359"/>
-      <c r="B13" s="277"/>
-      <c r="C13" s="277"/>
-      <c r="D13" s="277"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="139"/>
-      <c r="H13" s="80" t="s">
+      <c r="A13" s="319"/>
+      <c r="B13" s="237"/>
+      <c r="C13" s="237"/>
+      <c r="D13" s="237"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="118"/>
+      <c r="G13" s="120"/>
+      <c r="H13" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I13" s="80" t="s">
+      <c r="I13" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J13" s="280"/>
-      <c r="K13" s="280"/>
-      <c r="L13" s="280"/>
-      <c r="M13" s="281"/>
+      <c r="J13" s="240"/>
+      <c r="K13" s="240"/>
+      <c r="L13" s="240"/>
+      <c r="M13" s="241"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="359"/>
-      <c r="B14" s="277"/>
-      <c r="C14" s="277"/>
-      <c r="D14" s="277"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="137"/>
-      <c r="G14" s="139"/>
-      <c r="H14" s="80" t="s">
+      <c r="A14" s="319"/>
+      <c r="B14" s="237"/>
+      <c r="C14" s="237"/>
+      <c r="D14" s="237"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="118"/>
+      <c r="G14" s="120"/>
+      <c r="H14" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I14" s="80" t="s">
+      <c r="I14" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J14" s="280"/>
-      <c r="K14" s="280"/>
-      <c r="L14" s="280"/>
-      <c r="M14" s="281"/>
+      <c r="J14" s="240"/>
+      <c r="K14" s="240"/>
+      <c r="L14" s="240"/>
+      <c r="M14" s="241"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="359"/>
-      <c r="B15" s="277"/>
-      <c r="C15" s="277"/>
-      <c r="D15" s="277"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="137"/>
-      <c r="G15" s="139"/>
-      <c r="H15" s="80" t="s">
+      <c r="A15" s="319"/>
+      <c r="B15" s="237"/>
+      <c r="C15" s="237"/>
+      <c r="D15" s="237"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="118"/>
+      <c r="G15" s="120"/>
+      <c r="H15" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I15" s="80" t="s">
+      <c r="I15" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J15" s="280"/>
-      <c r="K15" s="280"/>
-      <c r="L15" s="280"/>
-      <c r="M15" s="281"/>
+      <c r="J15" s="240"/>
+      <c r="K15" s="240"/>
+      <c r="L15" s="240"/>
+      <c r="M15" s="241"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="359"/>
-      <c r="B16" s="277"/>
-      <c r="C16" s="277"/>
-      <c r="D16" s="277"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="137"/>
-      <c r="G16" s="139"/>
-      <c r="H16" s="80" t="s">
+      <c r="A16" s="319"/>
+      <c r="B16" s="237"/>
+      <c r="C16" s="237"/>
+      <c r="D16" s="237"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="118"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I16" s="80" t="s">
+      <c r="I16" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J16" s="280"/>
-      <c r="K16" s="280"/>
-      <c r="L16" s="280"/>
-      <c r="M16" s="281"/>
+      <c r="J16" s="240"/>
+      <c r="K16" s="240"/>
+      <c r="L16" s="240"/>
+      <c r="M16" s="241"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="359"/>
-      <c r="B17" s="277"/>
-      <c r="C17" s="277"/>
-      <c r="D17" s="277"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="137"/>
-      <c r="G17" s="139"/>
-      <c r="H17" s="80" t="s">
+      <c r="A17" s="319"/>
+      <c r="B17" s="237"/>
+      <c r="C17" s="237"/>
+      <c r="D17" s="237"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="120"/>
+      <c r="H17" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I17" s="80" t="s">
+      <c r="I17" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J17" s="280"/>
-      <c r="K17" s="280"/>
-      <c r="L17" s="280"/>
-      <c r="M17" s="281"/>
+      <c r="J17" s="240"/>
+      <c r="K17" s="240"/>
+      <c r="L17" s="240"/>
+      <c r="M17" s="241"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="359"/>
-      <c r="B18" s="277"/>
-      <c r="C18" s="277"/>
-      <c r="D18" s="277"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="137"/>
-      <c r="G18" s="139"/>
-      <c r="H18" s="80" t="s">
+      <c r="A18" s="319"/>
+      <c r="B18" s="237"/>
+      <c r="C18" s="237"/>
+      <c r="D18" s="237"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="120"/>
+      <c r="H18" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I18" s="80" t="s">
+      <c r="I18" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J18" s="280"/>
-      <c r="K18" s="280"/>
-      <c r="L18" s="280"/>
-      <c r="M18" s="281"/>
+      <c r="J18" s="240"/>
+      <c r="K18" s="240"/>
+      <c r="L18" s="240"/>
+      <c r="M18" s="241"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="359"/>
-      <c r="B19" s="277"/>
-      <c r="C19" s="277"/>
-      <c r="D19" s="277"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="137"/>
-      <c r="G19" s="139"/>
-      <c r="H19" s="80" t="s">
+      <c r="A19" s="319"/>
+      <c r="B19" s="237"/>
+      <c r="C19" s="237"/>
+      <c r="D19" s="237"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="118"/>
+      <c r="G19" s="120"/>
+      <c r="H19" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I19" s="80" t="s">
+      <c r="I19" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J19" s="280"/>
-      <c r="K19" s="280"/>
-      <c r="L19" s="280"/>
-      <c r="M19" s="281"/>
+      <c r="J19" s="240"/>
+      <c r="K19" s="240"/>
+      <c r="L19" s="240"/>
+      <c r="M19" s="241"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="359"/>
-      <c r="B20" s="277"/>
-      <c r="C20" s="277"/>
-      <c r="D20" s="277"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="137"/>
-      <c r="G20" s="139"/>
-      <c r="H20" s="80" t="s">
+      <c r="A20" s="319"/>
+      <c r="B20" s="237"/>
+      <c r="C20" s="237"/>
+      <c r="D20" s="237"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="118"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I20" s="80" t="s">
+      <c r="I20" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J20" s="280"/>
-      <c r="K20" s="280"/>
-      <c r="L20" s="280"/>
-      <c r="M20" s="281"/>
+      <c r="J20" s="240"/>
+      <c r="K20" s="240"/>
+      <c r="L20" s="240"/>
+      <c r="M20" s="241"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="359"/>
-      <c r="B21" s="277"/>
-      <c r="C21" s="277"/>
-      <c r="D21" s="277"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="137"/>
-      <c r="G21" s="139"/>
-      <c r="H21" s="80" t="s">
+      <c r="A21" s="319"/>
+      <c r="B21" s="237"/>
+      <c r="C21" s="237"/>
+      <c r="D21" s="237"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="118"/>
+      <c r="G21" s="120"/>
+      <c r="H21" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I21" s="80" t="s">
+      <c r="I21" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J21" s="280"/>
-      <c r="K21" s="280"/>
-      <c r="L21" s="280"/>
-      <c r="M21" s="281"/>
+      <c r="J21" s="240"/>
+      <c r="K21" s="240"/>
+      <c r="L21" s="240"/>
+      <c r="M21" s="241"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="359"/>
-      <c r="B22" s="277"/>
-      <c r="C22" s="277"/>
-      <c r="D22" s="277"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="137"/>
-      <c r="G22" s="139"/>
-      <c r="H22" s="80" t="s">
+      <c r="A22" s="319"/>
+      <c r="B22" s="237"/>
+      <c r="C22" s="237"/>
+      <c r="D22" s="237"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="120"/>
+      <c r="H22" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I22" s="80" t="s">
+      <c r="I22" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="280"/>
-      <c r="K22" s="280"/>
-      <c r="L22" s="280"/>
-      <c r="M22" s="281"/>
+      <c r="J22" s="240"/>
+      <c r="K22" s="240"/>
+      <c r="L22" s="240"/>
+      <c r="M22" s="241"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="359"/>
-      <c r="B23" s="277"/>
-      <c r="C23" s="277"/>
-      <c r="D23" s="277"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="137"/>
-      <c r="G23" s="139"/>
-      <c r="H23" s="80" t="s">
+      <c r="A23" s="319"/>
+      <c r="B23" s="237"/>
+      <c r="C23" s="237"/>
+      <c r="D23" s="237"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="120"/>
+      <c r="H23" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I23" s="80" t="s">
+      <c r="I23" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="280"/>
-      <c r="K23" s="280"/>
-      <c r="L23" s="280"/>
-      <c r="M23" s="281"/>
+      <c r="J23" s="240"/>
+      <c r="K23" s="240"/>
+      <c r="L23" s="240"/>
+      <c r="M23" s="241"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="359"/>
-      <c r="B24" s="277"/>
-      <c r="C24" s="277"/>
-      <c r="D24" s="277"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="137"/>
-      <c r="G24" s="139"/>
-      <c r="H24" s="80" t="s">
+      <c r="A24" s="319"/>
+      <c r="B24" s="237"/>
+      <c r="C24" s="237"/>
+      <c r="D24" s="237"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="118"/>
+      <c r="G24" s="120"/>
+      <c r="H24" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I24" s="80" t="s">
+      <c r="I24" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="280"/>
-      <c r="K24" s="280"/>
-      <c r="L24" s="280"/>
-      <c r="M24" s="281"/>
+      <c r="J24" s="240"/>
+      <c r="K24" s="240"/>
+      <c r="L24" s="240"/>
+      <c r="M24" s="241"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="359"/>
-      <c r="B25" s="277"/>
-      <c r="C25" s="277"/>
-      <c r="D25" s="277"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="137"/>
-      <c r="G25" s="139"/>
-      <c r="H25" s="80" t="s">
+      <c r="A25" s="319"/>
+      <c r="B25" s="237"/>
+      <c r="C25" s="237"/>
+      <c r="D25" s="237"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="118"/>
+      <c r="G25" s="120"/>
+      <c r="H25" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="I25" s="80" t="s">
+      <c r="I25" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="280"/>
-      <c r="K25" s="280"/>
-      <c r="L25" s="280"/>
-      <c r="M25" s="281"/>
+      <c r="J25" s="240"/>
+      <c r="K25" s="240"/>
+      <c r="L25" s="240"/>
+      <c r="M25" s="241"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="360"/>
-      <c r="B26" s="361"/>
-      <c r="C26" s="361"/>
-      <c r="D26" s="361"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="280"/>
-      <c r="G26" s="280"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="280"/>
-      <c r="K26" s="280"/>
-      <c r="L26" s="280"/>
-      <c r="M26" s="281"/>
+      <c r="A26" s="320"/>
+      <c r="B26" s="321"/>
+      <c r="C26" s="321"/>
+      <c r="D26" s="321"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="240"/>
+      <c r="G26" s="240"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="240"/>
+      <c r="K26" s="240"/>
+      <c r="L26" s="240"/>
+      <c r="M26" s="241"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="360"/>
-      <c r="B27" s="361"/>
-      <c r="C27" s="361"/>
-      <c r="D27" s="361"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="280"/>
-      <c r="G27" s="280"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="280"/>
-      <c r="K27" s="280"/>
-      <c r="L27" s="280"/>
-      <c r="M27" s="281"/>
+      <c r="A27" s="320"/>
+      <c r="B27" s="321"/>
+      <c r="C27" s="321"/>
+      <c r="D27" s="321"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="240"/>
+      <c r="G27" s="240"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="240"/>
+      <c r="K27" s="240"/>
+      <c r="L27" s="240"/>
+      <c r="M27" s="241"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="360"/>
-      <c r="B28" s="361"/>
-      <c r="C28" s="361"/>
-      <c r="D28" s="361"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="280"/>
-      <c r="G28" s="280"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="280"/>
-      <c r="K28" s="280"/>
-      <c r="L28" s="280"/>
-      <c r="M28" s="281"/>
+      <c r="A28" s="320"/>
+      <c r="B28" s="321"/>
+      <c r="C28" s="321"/>
+      <c r="D28" s="321"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="240"/>
+      <c r="G28" s="240"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="240"/>
+      <c r="K28" s="240"/>
+      <c r="L28" s="240"/>
+      <c r="M28" s="241"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="360"/>
-      <c r="B29" s="361"/>
-      <c r="C29" s="361"/>
-      <c r="D29" s="361"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="280"/>
-      <c r="G29" s="280"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="280"/>
-      <c r="K29" s="280"/>
-      <c r="L29" s="280"/>
-      <c r="M29" s="281"/>
+      <c r="A29" s="320"/>
+      <c r="B29" s="321"/>
+      <c r="C29" s="321"/>
+      <c r="D29" s="321"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="240"/>
+      <c r="G29" s="240"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="240"/>
+      <c r="K29" s="240"/>
+      <c r="L29" s="240"/>
+      <c r="M29" s="241"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="360"/>
-      <c r="B30" s="361"/>
-      <c r="C30" s="361"/>
-      <c r="D30" s="361"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="280"/>
-      <c r="G30" s="280"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="280"/>
-      <c r="K30" s="280"/>
-      <c r="L30" s="280"/>
-      <c r="M30" s="281"/>
+      <c r="A30" s="320"/>
+      <c r="B30" s="321"/>
+      <c r="C30" s="321"/>
+      <c r="D30" s="321"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="240"/>
+      <c r="G30" s="240"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="240"/>
+      <c r="K30" s="240"/>
+      <c r="L30" s="240"/>
+      <c r="M30" s="241"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="360"/>
-      <c r="B31" s="361"/>
-      <c r="C31" s="361"/>
-      <c r="D31" s="361"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="280"/>
-      <c r="G31" s="280"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="280"/>
-      <c r="K31" s="280"/>
-      <c r="L31" s="280"/>
-      <c r="M31" s="281"/>
+      <c r="A31" s="320"/>
+      <c r="B31" s="321"/>
+      <c r="C31" s="321"/>
+      <c r="D31" s="321"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="240"/>
+      <c r="G31" s="240"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="240"/>
+      <c r="K31" s="240"/>
+      <c r="L31" s="240"/>
+      <c r="M31" s="241"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="360"/>
-      <c r="B32" s="361"/>
-      <c r="C32" s="361"/>
-      <c r="D32" s="361"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="280"/>
-      <c r="G32" s="280"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="280"/>
-      <c r="K32" s="280"/>
-      <c r="L32" s="280"/>
-      <c r="M32" s="281"/>
+      <c r="A32" s="320"/>
+      <c r="B32" s="321"/>
+      <c r="C32" s="321"/>
+      <c r="D32" s="321"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="240"/>
+      <c r="G32" s="240"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="240"/>
+      <c r="K32" s="240"/>
+      <c r="L32" s="240"/>
+      <c r="M32" s="241"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A33" s="360"/>
-      <c r="B33" s="361"/>
-      <c r="C33" s="361"/>
-      <c r="D33" s="361"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="280"/>
-      <c r="G33" s="280"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="280"/>
-      <c r="K33" s="280"/>
-      <c r="L33" s="280"/>
-      <c r="M33" s="281"/>
+      <c r="A33" s="320"/>
+      <c r="B33" s="321"/>
+      <c r="C33" s="321"/>
+      <c r="D33" s="321"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="240"/>
+      <c r="G33" s="240"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="240"/>
+      <c r="K33" s="240"/>
+      <c r="L33" s="240"/>
+      <c r="M33" s="241"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A34" s="360"/>
-      <c r="B34" s="361"/>
-      <c r="C34" s="361"/>
-      <c r="D34" s="361"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="280"/>
-      <c r="G34" s="280"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="280"/>
-      <c r="K34" s="280"/>
-      <c r="L34" s="280"/>
-      <c r="M34" s="281"/>
+      <c r="A34" s="320"/>
+      <c r="B34" s="321"/>
+      <c r="C34" s="321"/>
+      <c r="D34" s="321"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="240"/>
+      <c r="G34" s="240"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="240"/>
+      <c r="K34" s="240"/>
+      <c r="L34" s="240"/>
+      <c r="M34" s="241"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35" s="360"/>
-      <c r="B35" s="361"/>
-      <c r="C35" s="361"/>
-      <c r="D35" s="361"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="280"/>
-      <c r="G35" s="280"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="280"/>
-      <c r="K35" s="280"/>
-      <c r="L35" s="280"/>
-      <c r="M35" s="281"/>
+      <c r="A35" s="320"/>
+      <c r="B35" s="321"/>
+      <c r="C35" s="321"/>
+      <c r="D35" s="321"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="240"/>
+      <c r="G35" s="240"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="240"/>
+      <c r="K35" s="240"/>
+      <c r="L35" s="240"/>
+      <c r="M35" s="241"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A36" s="360"/>
-      <c r="B36" s="361"/>
-      <c r="C36" s="361"/>
-      <c r="D36" s="361"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="280"/>
-      <c r="G36" s="280"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="280"/>
-      <c r="K36" s="280"/>
-      <c r="L36" s="280"/>
-      <c r="M36" s="281"/>
+      <c r="A36" s="320"/>
+      <c r="B36" s="321"/>
+      <c r="C36" s="321"/>
+      <c r="D36" s="321"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="240"/>
+      <c r="G36" s="240"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="240"/>
+      <c r="K36" s="240"/>
+      <c r="L36" s="240"/>
+      <c r="M36" s="241"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A37" s="360"/>
-      <c r="B37" s="361"/>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="280"/>
-      <c r="G37" s="280"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="280"/>
-      <c r="K37" s="280"/>
-      <c r="L37" s="280"/>
-      <c r="M37" s="281"/>
+      <c r="A37" s="320"/>
+      <c r="B37" s="321"/>
+      <c r="C37" s="321"/>
+      <c r="D37" s="321"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="240"/>
+      <c r="G37" s="240"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="240"/>
+      <c r="K37" s="240"/>
+      <c r="L37" s="240"/>
+      <c r="M37" s="241"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A38" s="360"/>
-      <c r="B38" s="361"/>
-      <c r="C38" s="361"/>
-      <c r="D38" s="361"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="280"/>
-      <c r="G38" s="280"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="280"/>
-      <c r="K38" s="280"/>
-      <c r="L38" s="280"/>
-      <c r="M38" s="281"/>
+      <c r="A38" s="320"/>
+      <c r="B38" s="321"/>
+      <c r="C38" s="321"/>
+      <c r="D38" s="321"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="240"/>
+      <c r="G38" s="240"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="240"/>
+      <c r="K38" s="240"/>
+      <c r="L38" s="240"/>
+      <c r="M38" s="241"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A39" s="360"/>
-      <c r="B39" s="361"/>
-      <c r="C39" s="361"/>
-      <c r="D39" s="361"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="280"/>
-      <c r="G39" s="280"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="280"/>
-      <c r="K39" s="280"/>
-      <c r="L39" s="280"/>
-      <c r="M39" s="281"/>
+      <c r="A39" s="320"/>
+      <c r="B39" s="321"/>
+      <c r="C39" s="321"/>
+      <c r="D39" s="321"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="240"/>
+      <c r="G39" s="240"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="240"/>
+      <c r="K39" s="240"/>
+      <c r="L39" s="240"/>
+      <c r="M39" s="241"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A40" s="360"/>
-      <c r="B40" s="361"/>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="280"/>
-      <c r="G40" s="280"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="280"/>
-      <c r="K40" s="280"/>
-      <c r="L40" s="280"/>
-      <c r="M40" s="281"/>
+      <c r="A40" s="320"/>
+      <c r="B40" s="321"/>
+      <c r="C40" s="321"/>
+      <c r="D40" s="321"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="240"/>
+      <c r="G40" s="240"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="240"/>
+      <c r="K40" s="240"/>
+      <c r="L40" s="240"/>
+      <c r="M40" s="241"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A41" s="360"/>
-      <c r="B41" s="361"/>
-      <c r="C41" s="361"/>
-      <c r="D41" s="361"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="280"/>
-      <c r="G41" s="280"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="280"/>
-      <c r="K41" s="280"/>
-      <c r="L41" s="280"/>
-      <c r="M41" s="281"/>
+      <c r="A41" s="320"/>
+      <c r="B41" s="321"/>
+      <c r="C41" s="321"/>
+      <c r="D41" s="321"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="240"/>
+      <c r="G41" s="240"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="240"/>
+      <c r="K41" s="240"/>
+      <c r="L41" s="240"/>
+      <c r="M41" s="241"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A42" s="360"/>
-      <c r="B42" s="361"/>
-      <c r="C42" s="361"/>
-      <c r="D42" s="361"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="280"/>
-      <c r="G42" s="280"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="13"/>
-      <c r="J42" s="280"/>
-      <c r="K42" s="280"/>
-      <c r="L42" s="280"/>
-      <c r="M42" s="281"/>
+      <c r="A42" s="320"/>
+      <c r="B42" s="321"/>
+      <c r="C42" s="321"/>
+      <c r="D42" s="321"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="240"/>
+      <c r="G42" s="240"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="240"/>
+      <c r="K42" s="240"/>
+      <c r="L42" s="240"/>
+      <c r="M42" s="241"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A43" s="360"/>
-      <c r="B43" s="361"/>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="280"/>
-      <c r="G43" s="280"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="280"/>
-      <c r="K43" s="280"/>
-      <c r="L43" s="280"/>
-      <c r="M43" s="281"/>
+      <c r="A43" s="320"/>
+      <c r="B43" s="321"/>
+      <c r="C43" s="321"/>
+      <c r="D43" s="321"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="240"/>
+      <c r="G43" s="240"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="240"/>
+      <c r="K43" s="240"/>
+      <c r="L43" s="240"/>
+      <c r="M43" s="241"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A44" s="360"/>
-      <c r="B44" s="361"/>
-      <c r="C44" s="361"/>
-      <c r="D44" s="361"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="280"/>
-      <c r="G44" s="280"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="280"/>
-      <c r="K44" s="280"/>
-      <c r="L44" s="280"/>
-      <c r="M44" s="281"/>
+      <c r="A44" s="320"/>
+      <c r="B44" s="321"/>
+      <c r="C44" s="321"/>
+      <c r="D44" s="321"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="240"/>
+      <c r="G44" s="240"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="240"/>
+      <c r="K44" s="240"/>
+      <c r="L44" s="240"/>
+      <c r="M44" s="241"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A45" s="360"/>
-      <c r="B45" s="361"/>
-      <c r="C45" s="361"/>
-      <c r="D45" s="361"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="280"/>
-      <c r="G45" s="280"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="280"/>
-      <c r="K45" s="280"/>
-      <c r="L45" s="280"/>
-      <c r="M45" s="281"/>
+      <c r="A45" s="320"/>
+      <c r="B45" s="321"/>
+      <c r="C45" s="321"/>
+      <c r="D45" s="321"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="240"/>
+      <c r="G45" s="240"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="240"/>
+      <c r="K45" s="240"/>
+      <c r="L45" s="240"/>
+      <c r="M45" s="241"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A46" s="360"/>
-      <c r="B46" s="361"/>
-      <c r="C46" s="361"/>
-      <c r="D46" s="361"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="280"/>
-      <c r="G46" s="280"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
-      <c r="J46" s="280"/>
-      <c r="K46" s="280"/>
-      <c r="L46" s="280"/>
-      <c r="M46" s="281"/>
+      <c r="A46" s="320"/>
+      <c r="B46" s="321"/>
+      <c r="C46" s="321"/>
+      <c r="D46" s="321"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="240"/>
+      <c r="G46" s="240"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="240"/>
+      <c r="K46" s="240"/>
+      <c r="L46" s="240"/>
+      <c r="M46" s="241"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A47" s="360"/>
-      <c r="B47" s="361"/>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="280"/>
-      <c r="G47" s="280"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="13"/>
-      <c r="J47" s="280"/>
-      <c r="K47" s="280"/>
-      <c r="L47" s="280"/>
-      <c r="M47" s="281"/>
+      <c r="A47" s="320"/>
+      <c r="B47" s="321"/>
+      <c r="C47" s="321"/>
+      <c r="D47" s="321"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="240"/>
+      <c r="G47" s="240"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="240"/>
+      <c r="K47" s="240"/>
+      <c r="L47" s="240"/>
+      <c r="M47" s="241"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A48" s="360"/>
-      <c r="B48" s="361"/>
-      <c r="C48" s="361"/>
-      <c r="D48" s="361"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="280"/>
-      <c r="G48" s="280"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="280"/>
-      <c r="K48" s="280"/>
-      <c r="L48" s="280"/>
-      <c r="M48" s="281"/>
+      <c r="A48" s="320"/>
+      <c r="B48" s="321"/>
+      <c r="C48" s="321"/>
+      <c r="D48" s="321"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="240"/>
+      <c r="G48" s="240"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="240"/>
+      <c r="K48" s="240"/>
+      <c r="L48" s="240"/>
+      <c r="M48" s="241"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A49" s="360"/>
-      <c r="B49" s="361"/>
-      <c r="C49" s="361"/>
-      <c r="D49" s="361"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="280"/>
-      <c r="G49" s="280"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="13"/>
-      <c r="J49" s="280"/>
-      <c r="K49" s="280"/>
-      <c r="L49" s="280"/>
-      <c r="M49" s="281"/>
+      <c r="A49" s="320"/>
+      <c r="B49" s="321"/>
+      <c r="C49" s="321"/>
+      <c r="D49" s="321"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="240"/>
+      <c r="G49" s="240"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="240"/>
+      <c r="K49" s="240"/>
+      <c r="L49" s="240"/>
+      <c r="M49" s="241"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="287" t="s">
+      <c r="A50" s="247" t="s">
         <v>22</v>
       </c>
-      <c r="B50" s="288"/>
-      <c r="C50" s="288"/>
-      <c r="D50" s="288"/>
-      <c r="E50" s="81"/>
-      <c r="F50" s="374"/>
-      <c r="G50" s="375"/>
-      <c r="H50" s="29"/>
-      <c r="I50" s="30"/>
-      <c r="J50" s="376"/>
-      <c r="K50" s="376"/>
-      <c r="L50" s="376"/>
-      <c r="M50" s="377"/>
+      <c r="B50" s="248"/>
+      <c r="C50" s="248"/>
+      <c r="D50" s="248"/>
+      <c r="E50" s="74"/>
+      <c r="F50" s="334"/>
+      <c r="G50" s="335"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="29"/>
+      <c r="J50" s="336"/>
+      <c r="K50" s="336"/>
+      <c r="L50" s="336"/>
+      <c r="M50" s="337"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A51" s="362" t="s">
+      <c r="A51" s="322" t="s">
         <v>58</v>
       </c>
-      <c r="B51" s="363"/>
-      <c r="C51" s="363"/>
-      <c r="D51" s="363"/>
-      <c r="E51" s="363"/>
-      <c r="F51" s="363"/>
-      <c r="G51" s="363"/>
-      <c r="H51" s="363"/>
-      <c r="I51" s="363"/>
-      <c r="J51" s="363"/>
-      <c r="K51" s="363"/>
-      <c r="L51" s="363"/>
-      <c r="M51" s="364"/>
+      <c r="B51" s="323"/>
+      <c r="C51" s="323"/>
+      <c r="D51" s="323"/>
+      <c r="E51" s="323"/>
+      <c r="F51" s="323"/>
+      <c r="G51" s="323"/>
+      <c r="H51" s="323"/>
+      <c r="I51" s="323"/>
+      <c r="J51" s="323"/>
+      <c r="K51" s="323"/>
+      <c r="L51" s="323"/>
+      <c r="M51" s="324"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="365"/>
-      <c r="B52" s="366"/>
-      <c r="C52" s="366"/>
-      <c r="D52" s="366"/>
-      <c r="E52" s="366"/>
-      <c r="F52" s="366"/>
-      <c r="G52" s="366"/>
-      <c r="H52" s="366"/>
-      <c r="I52" s="366"/>
-      <c r="J52" s="366"/>
-      <c r="K52" s="366"/>
-      <c r="L52" s="366"/>
-      <c r="M52" s="367"/>
+      <c r="A52" s="325"/>
+      <c r="B52" s="326"/>
+      <c r="C52" s="326"/>
+      <c r="D52" s="326"/>
+      <c r="E52" s="326"/>
+      <c r="F52" s="326"/>
+      <c r="G52" s="326"/>
+      <c r="H52" s="326"/>
+      <c r="I52" s="326"/>
+      <c r="J52" s="326"/>
+      <c r="K52" s="326"/>
+      <c r="L52" s="326"/>
+      <c r="M52" s="327"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A53" s="368"/>
-      <c r="B53" s="369"/>
-      <c r="C53" s="369"/>
-      <c r="D53" s="369"/>
-      <c r="E53" s="369"/>
-      <c r="F53" s="369"/>
-      <c r="G53" s="369"/>
-      <c r="H53" s="369"/>
-      <c r="I53" s="369"/>
-      <c r="J53" s="369"/>
-      <c r="K53" s="369"/>
-      <c r="L53" s="369"/>
-      <c r="M53" s="370"/>
+      <c r="A53" s="328"/>
+      <c r="B53" s="329"/>
+      <c r="C53" s="329"/>
+      <c r="D53" s="329"/>
+      <c r="E53" s="329"/>
+      <c r="F53" s="329"/>
+      <c r="G53" s="329"/>
+      <c r="H53" s="329"/>
+      <c r="I53" s="329"/>
+      <c r="J53" s="329"/>
+      <c r="K53" s="329"/>
+      <c r="L53" s="329"/>
+      <c r="M53" s="330"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A54" s="368"/>
-      <c r="B54" s="369"/>
-      <c r="C54" s="369"/>
-      <c r="D54" s="369"/>
-      <c r="E54" s="369"/>
-      <c r="F54" s="369"/>
-      <c r="G54" s="369"/>
-      <c r="H54" s="369"/>
-      <c r="I54" s="369"/>
-      <c r="J54" s="369"/>
-      <c r="K54" s="369"/>
-      <c r="L54" s="369"/>
-      <c r="M54" s="370"/>
+      <c r="A54" s="328"/>
+      <c r="B54" s="329"/>
+      <c r="C54" s="329"/>
+      <c r="D54" s="329"/>
+      <c r="E54" s="329"/>
+      <c r="F54" s="329"/>
+      <c r="G54" s="329"/>
+      <c r="H54" s="329"/>
+      <c r="I54" s="329"/>
+      <c r="J54" s="329"/>
+      <c r="K54" s="329"/>
+      <c r="L54" s="329"/>
+      <c r="M54" s="330"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A55" s="368"/>
-      <c r="B55" s="369"/>
-      <c r="C55" s="369"/>
-      <c r="D55" s="369"/>
-      <c r="E55" s="369"/>
-      <c r="F55" s="369"/>
-      <c r="G55" s="369"/>
-      <c r="H55" s="369"/>
-      <c r="I55" s="369"/>
-      <c r="J55" s="369"/>
-      <c r="K55" s="369"/>
-      <c r="L55" s="369"/>
-      <c r="M55" s="370"/>
+      <c r="A55" s="328"/>
+      <c r="B55" s="329"/>
+      <c r="C55" s="329"/>
+      <c r="D55" s="329"/>
+      <c r="E55" s="329"/>
+      <c r="F55" s="329"/>
+      <c r="G55" s="329"/>
+      <c r="H55" s="329"/>
+      <c r="I55" s="329"/>
+      <c r="J55" s="329"/>
+      <c r="K55" s="329"/>
+      <c r="L55" s="329"/>
+      <c r="M55" s="330"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A56" s="368"/>
-      <c r="B56" s="369"/>
-      <c r="C56" s="369"/>
-      <c r="D56" s="369"/>
-      <c r="E56" s="369"/>
-      <c r="F56" s="369"/>
-      <c r="G56" s="369"/>
-      <c r="H56" s="369"/>
-      <c r="I56" s="369"/>
-      <c r="J56" s="369"/>
-      <c r="K56" s="369"/>
-      <c r="L56" s="369"/>
-      <c r="M56" s="370"/>
+      <c r="A56" s="328"/>
+      <c r="B56" s="329"/>
+      <c r="C56" s="329"/>
+      <c r="D56" s="329"/>
+      <c r="E56" s="329"/>
+      <c r="F56" s="329"/>
+      <c r="G56" s="329"/>
+      <c r="H56" s="329"/>
+      <c r="I56" s="329"/>
+      <c r="J56" s="329"/>
+      <c r="K56" s="329"/>
+      <c r="L56" s="329"/>
+      <c r="M56" s="330"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A57" s="368"/>
-      <c r="B57" s="369"/>
-      <c r="C57" s="369"/>
-      <c r="D57" s="369"/>
-      <c r="E57" s="369"/>
-      <c r="F57" s="369"/>
-      <c r="G57" s="369"/>
-      <c r="H57" s="369"/>
-      <c r="I57" s="369"/>
-      <c r="J57" s="369"/>
-      <c r="K57" s="369"/>
-      <c r="L57" s="369"/>
-      <c r="M57" s="370"/>
+      <c r="A57" s="328"/>
+      <c r="B57" s="329"/>
+      <c r="C57" s="329"/>
+      <c r="D57" s="329"/>
+      <c r="E57" s="329"/>
+      <c r="F57" s="329"/>
+      <c r="G57" s="329"/>
+      <c r="H57" s="329"/>
+      <c r="I57" s="329"/>
+      <c r="J57" s="329"/>
+      <c r="K57" s="329"/>
+      <c r="L57" s="329"/>
+      <c r="M57" s="330"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A58" s="368"/>
-      <c r="B58" s="369"/>
-      <c r="C58" s="369"/>
-      <c r="D58" s="369"/>
-      <c r="E58" s="369"/>
-      <c r="F58" s="369"/>
-      <c r="G58" s="369"/>
-      <c r="H58" s="369"/>
-      <c r="I58" s="369"/>
-      <c r="J58" s="369"/>
-      <c r="K58" s="369"/>
-      <c r="L58" s="369"/>
-      <c r="M58" s="370"/>
+      <c r="A58" s="328"/>
+      <c r="B58" s="329"/>
+      <c r="C58" s="329"/>
+      <c r="D58" s="329"/>
+      <c r="E58" s="329"/>
+      <c r="F58" s="329"/>
+      <c r="G58" s="329"/>
+      <c r="H58" s="329"/>
+      <c r="I58" s="329"/>
+      <c r="J58" s="329"/>
+      <c r="K58" s="329"/>
+      <c r="L58" s="329"/>
+      <c r="M58" s="330"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A59" s="368"/>
-      <c r="B59" s="369"/>
-      <c r="C59" s="369"/>
-      <c r="D59" s="369"/>
-      <c r="E59" s="369"/>
-      <c r="F59" s="369"/>
-      <c r="G59" s="369"/>
-      <c r="H59" s="369"/>
-      <c r="I59" s="369"/>
-      <c r="J59" s="369"/>
-      <c r="K59" s="369"/>
-      <c r="L59" s="369"/>
-      <c r="M59" s="370"/>
+      <c r="A59" s="328"/>
+      <c r="B59" s="329"/>
+      <c r="C59" s="329"/>
+      <c r="D59" s="329"/>
+      <c r="E59" s="329"/>
+      <c r="F59" s="329"/>
+      <c r="G59" s="329"/>
+      <c r="H59" s="329"/>
+      <c r="I59" s="329"/>
+      <c r="J59" s="329"/>
+      <c r="K59" s="329"/>
+      <c r="L59" s="329"/>
+      <c r="M59" s="330"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A60" s="371"/>
-      <c r="B60" s="372"/>
-      <c r="C60" s="372"/>
-      <c r="D60" s="372"/>
-      <c r="E60" s="372"/>
-      <c r="F60" s="372"/>
-      <c r="G60" s="372"/>
-      <c r="H60" s="372"/>
-      <c r="I60" s="372"/>
-      <c r="J60" s="372"/>
-      <c r="K60" s="372"/>
-      <c r="L60" s="372"/>
-      <c r="M60" s="373"/>
+      <c r="A60" s="331"/>
+      <c r="B60" s="332"/>
+      <c r="C60" s="332"/>
+      <c r="D60" s="332"/>
+      <c r="E60" s="332"/>
+      <c r="F60" s="332"/>
+      <c r="G60" s="332"/>
+      <c r="H60" s="332"/>
+      <c r="I60" s="332"/>
+      <c r="J60" s="332"/>
+      <c r="K60" s="332"/>
+      <c r="L60" s="332"/>
+      <c r="M60" s="333"/>
     </row>
     <row r="61" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="28"/>
-      <c r="B61" s="28"/>
-      <c r="C61" s="28"/>
-      <c r="D61" s="28"/>
-      <c r="E61" s="25"/>
-      <c r="F61" s="25"/>
-      <c r="G61" s="25"/>
-      <c r="H61" s="23"/>
-      <c r="I61" s="23"/>
-      <c r="J61" s="23"/>
+      <c r="A61" s="27"/>
+      <c r="B61" s="27"/>
+      <c r="C61" s="27"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="22"/>
+      <c r="I61" s="22"/>
+      <c r="J61" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="149">
@@ -7536,7 +7565,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D273127C-4D82-451E-94BD-40B506A25824}">
-  <dimension ref="A1:V59"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="7.42578125" customWidth="1"/>
@@ -7545,607 +7574,648 @@
     <col min="8" max="8" width="5.140625" customWidth="1"/>
     <col min="9" max="9" width="6.7109375" customWidth="1"/>
     <col min="11" max="11" width="17.140625" customWidth="1"/>
-    <col min="13" max="13" width="9" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" customWidth="1"/>
+    <col min="13" max="13" width="8" style="407" customWidth="1"/>
+    <col min="14" max="14" width="0.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="390" t="s">
+    <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="350" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="391"/>
-      <c r="C1" s="391"/>
-      <c r="D1" s="392"/>
-      <c r="E1" s="392"/>
-      <c r="F1" s="393"/>
-      <c r="G1" s="393" t="s">
+      <c r="B1" s="351"/>
+      <c r="C1" s="351"/>
+      <c r="D1" s="352"/>
+      <c r="E1" s="352"/>
+      <c r="F1" s="353"/>
+      <c r="G1" s="353" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="393"/>
-      <c r="I1" s="393"/>
-      <c r="J1" s="393"/>
-      <c r="K1" s="393"/>
-      <c r="L1" s="394" t="s">
+      <c r="H1" s="353"/>
+      <c r="I1" s="353"/>
+      <c r="J1" s="353"/>
+      <c r="K1" s="353"/>
+      <c r="L1" s="354" t="s">
         <v>69</v>
       </c>
-      <c r="M1" s="395"/>
-    </row>
-    <row r="2" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="387" t="s">
+      <c r="M1" s="355"/>
+      <c r="N1" s="403"/>
+    </row>
+    <row r="2" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="347" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="388"/>
-      <c r="C2" s="388"/>
-      <c r="D2" s="388"/>
-      <c r="E2" s="388"/>
-      <c r="F2" s="388"/>
-      <c r="G2" s="388"/>
-      <c r="H2" s="388"/>
-      <c r="I2" s="412"/>
-      <c r="J2" s="413"/>
-      <c r="K2" s="413"/>
-      <c r="L2" s="413"/>
-      <c r="M2" s="414"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="183" t="s">
+      <c r="B2" s="348"/>
+      <c r="C2" s="348"/>
+      <c r="D2" s="348"/>
+      <c r="E2" s="348"/>
+      <c r="F2" s="348"/>
+      <c r="G2" s="348"/>
+      <c r="H2" s="348"/>
+      <c r="I2" s="372"/>
+      <c r="J2" s="373"/>
+      <c r="K2" s="373"/>
+      <c r="L2" s="373"/>
+      <c r="M2" s="374"/>
+      <c r="N2" s="403"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" s="152" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="184"/>
-      <c r="C3" s="184"/>
-      <c r="D3" s="184"/>
-      <c r="E3" s="184"/>
-      <c r="F3" s="184"/>
-      <c r="G3" s="184"/>
-      <c r="H3" s="400"/>
-      <c r="I3" s="415" t="s">
+      <c r="B3" s="360"/>
+      <c r="C3" s="360"/>
+      <c r="D3" s="360"/>
+      <c r="E3" s="360"/>
+      <c r="F3" s="360"/>
+      <c r="G3" s="360"/>
+      <c r="H3" s="360"/>
+      <c r="I3" s="375" t="s">
         <v>75</v>
       </c>
-      <c r="J3" s="389"/>
-      <c r="K3" s="416"/>
-      <c r="L3" s="389"/>
-      <c r="M3" s="417"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="183" t="s">
+      <c r="J3" s="349"/>
+      <c r="K3" s="376"/>
+      <c r="L3" s="349"/>
+      <c r="M3" s="377"/>
+      <c r="N3" s="403"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" s="152" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
-      <c r="G4" s="184"/>
-      <c r="H4" s="400"/>
-      <c r="I4" s="418"/>
-      <c r="J4" s="396"/>
-      <c r="K4" s="396"/>
-      <c r="L4" s="396"/>
-      <c r="M4" s="409"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="183" t="s">
+      <c r="B4" s="360"/>
+      <c r="C4" s="360"/>
+      <c r="D4" s="360"/>
+      <c r="E4" s="360"/>
+      <c r="F4" s="360"/>
+      <c r="G4" s="360"/>
+      <c r="H4" s="360"/>
+      <c r="I4" s="378"/>
+      <c r="J4" s="356"/>
+      <c r="K4" s="356"/>
+      <c r="L4" s="356"/>
+      <c r="M4" s="369"/>
+      <c r="N4" s="403"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" s="152" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="184"/>
-      <c r="C5" s="184"/>
-      <c r="D5" s="184"/>
-      <c r="E5" s="184"/>
-      <c r="F5" s="184"/>
-      <c r="G5" s="184"/>
-      <c r="H5" s="400"/>
-      <c r="I5" s="418"/>
-      <c r="J5" s="396"/>
-      <c r="K5" s="396"/>
-      <c r="L5" s="396"/>
-      <c r="M5" s="409"/>
-    </row>
-    <row r="6" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="206" t="s">
+      <c r="B5" s="360"/>
+      <c r="C5" s="360"/>
+      <c r="D5" s="360"/>
+      <c r="E5" s="360"/>
+      <c r="F5" s="360"/>
+      <c r="G5" s="360"/>
+      <c r="H5" s="360"/>
+      <c r="I5" s="378"/>
+      <c r="J5" s="356"/>
+      <c r="K5" s="356"/>
+      <c r="L5" s="356"/>
+      <c r="M5" s="369"/>
+      <c r="N5" s="403"/>
+    </row>
+    <row r="6" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="166" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="182"/>
-      <c r="C6" s="182"/>
-      <c r="D6" s="182"/>
-      <c r="E6" s="182"/>
-      <c r="F6" s="207" t="s">
+      <c r="B6" s="151"/>
+      <c r="C6" s="151"/>
+      <c r="D6" s="151"/>
+      <c r="E6" s="151"/>
+      <c r="F6" s="167" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="207"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="419"/>
-      <c r="J6" s="420"/>
-      <c r="K6" s="420"/>
-      <c r="L6" s="420"/>
-      <c r="M6" s="421"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="208" t="s">
+      <c r="G6" s="167"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="379"/>
+      <c r="J6" s="380"/>
+      <c r="K6" s="380"/>
+      <c r="L6" s="380"/>
+      <c r="M6" s="381"/>
+      <c r="N6" s="403"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" s="168" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="209"/>
-      <c r="C7" s="209"/>
-      <c r="D7" s="209"/>
-      <c r="E7" s="209"/>
-      <c r="F7" s="209"/>
-      <c r="G7" s="209"/>
-      <c r="H7" s="209"/>
-      <c r="I7" s="423" t="s">
+      <c r="B7" s="169"/>
+      <c r="C7" s="169"/>
+      <c r="D7" s="169"/>
+      <c r="E7" s="169"/>
+      <c r="F7" s="169"/>
+      <c r="G7" s="169"/>
+      <c r="H7" s="169"/>
+      <c r="I7" s="383" t="s">
         <v>77</v>
       </c>
-      <c r="J7" s="424"/>
-      <c r="K7" s="425"/>
-      <c r="L7" s="424"/>
-      <c r="M7" s="426"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="35" t="s">
+      <c r="J7" s="384"/>
+      <c r="K7" s="385"/>
+      <c r="L7" s="384"/>
+      <c r="M7" s="386"/>
+      <c r="N7" s="403"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="98"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="198" t="s">
+      <c r="B8" s="91"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="364" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="198"/>
-      <c r="G8" s="198"/>
-      <c r="H8" s="404"/>
-      <c r="I8" s="427" t="s">
+      <c r="F8" s="364"/>
+      <c r="G8" s="364"/>
+      <c r="H8" s="364"/>
+      <c r="I8" s="387" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="400"/>
-      <c r="K8" s="400"/>
-      <c r="L8" s="400"/>
-      <c r="M8" s="401"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="37" t="s">
+      <c r="J8" s="360"/>
+      <c r="K8" s="360"/>
+      <c r="L8" s="360"/>
+      <c r="M8" s="361"/>
+      <c r="N8" s="403"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="H9" s="422"/>
-      <c r="I9" s="428" t="s">
+      <c r="B9" s="382"/>
+      <c r="C9" s="382"/>
+      <c r="D9" s="382"/>
+      <c r="E9" s="382"/>
+      <c r="F9" s="382"/>
+      <c r="G9" s="382"/>
+      <c r="H9" s="382"/>
+      <c r="I9" s="388" t="s">
         <v>71</v>
       </c>
-      <c r="J9" s="429"/>
-      <c r="K9" s="429"/>
-      <c r="L9" s="429"/>
-      <c r="M9" s="430"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="40" t="s">
+      <c r="J9" s="389"/>
+      <c r="K9" s="389"/>
+      <c r="L9" s="389"/>
+      <c r="M9" s="390"/>
+      <c r="N9" s="403"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="204"/>
-      <c r="D10" s="204"/>
-      <c r="E10" s="204"/>
-      <c r="F10" s="204"/>
-      <c r="G10" s="204"/>
-      <c r="H10" s="422"/>
-      <c r="I10" s="412" t="s">
+      <c r="B10" s="382"/>
+      <c r="C10" s="440"/>
+      <c r="D10" s="440"/>
+      <c r="E10" s="440"/>
+      <c r="F10" s="440"/>
+      <c r="G10" s="440"/>
+      <c r="H10" s="382"/>
+      <c r="I10" s="372" t="s">
         <v>78</v>
       </c>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="433"/>
-    </row>
-    <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="181" t="s">
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="391"/>
+      <c r="N10" s="403"/>
+    </row>
+    <row r="11" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="150" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="182"/>
-      <c r="C11" s="182"/>
-      <c r="D11" s="182"/>
-      <c r="E11" s="182"/>
-      <c r="F11" s="207" t="s">
+      <c r="B11" s="151"/>
+      <c r="C11" s="151"/>
+      <c r="D11" s="151"/>
+      <c r="E11" s="151"/>
+      <c r="F11" s="167" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="207"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="434" t="s">
+      <c r="G11" s="167"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="392" t="s">
         <v>72</v>
       </c>
-      <c r="J11" s="435"/>
-      <c r="K11" s="436"/>
-      <c r="L11" s="436"/>
-      <c r="M11" s="437"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="151" t="s">
+      <c r="J11" s="393"/>
+      <c r="K11" s="394"/>
+      <c r="L11" s="394"/>
+      <c r="M11" s="395"/>
+      <c r="N11" s="403"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" s="129" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="152"/>
-      <c r="C12" s="152"/>
-      <c r="D12" s="152"/>
-      <c r="E12" s="152"/>
-      <c r="F12" s="152"/>
-      <c r="G12" s="152"/>
-      <c r="H12" s="152"/>
-      <c r="I12" s="418"/>
-      <c r="J12" s="396"/>
-      <c r="K12" s="396"/>
-      <c r="L12" s="396"/>
-      <c r="M12" s="409"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="397" t="s">
+      <c r="B12" s="130"/>
+      <c r="C12" s="130"/>
+      <c r="D12" s="130"/>
+      <c r="E12" s="130"/>
+      <c r="F12" s="130"/>
+      <c r="G12" s="130"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="378"/>
+      <c r="J12" s="356"/>
+      <c r="K12" s="356"/>
+      <c r="L12" s="356"/>
+      <c r="M12" s="369"/>
+      <c r="N12" s="403"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" s="357" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="398"/>
-      <c r="C13" s="398"/>
-      <c r="D13" s="398"/>
-      <c r="E13" s="398"/>
-      <c r="F13" s="398"/>
-      <c r="G13" s="398"/>
-      <c r="H13" s="398"/>
-      <c r="I13" s="418"/>
-      <c r="J13" s="396"/>
-      <c r="K13" s="396"/>
-      <c r="L13" s="396"/>
-      <c r="M13" s="409"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="399" t="s">
+      <c r="B13" s="358"/>
+      <c r="C13" s="358"/>
+      <c r="D13" s="358"/>
+      <c r="E13" s="358"/>
+      <c r="F13" s="358"/>
+      <c r="G13" s="358"/>
+      <c r="H13" s="358"/>
+      <c r="I13" s="378"/>
+      <c r="J13" s="356"/>
+      <c r="K13" s="356"/>
+      <c r="L13" s="356"/>
+      <c r="M13" s="369"/>
+      <c r="N13" s="403"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" s="359" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="400"/>
-      <c r="C14" s="400"/>
-      <c r="D14" s="400"/>
-      <c r="E14" s="400"/>
-      <c r="F14" s="400"/>
-      <c r="G14" s="400"/>
-      <c r="H14" s="400"/>
-      <c r="I14" s="419"/>
-      <c r="J14" s="420"/>
-      <c r="K14" s="420"/>
-      <c r="L14" s="420"/>
-      <c r="M14" s="421"/>
-    </row>
-    <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="402" t="s">
+      <c r="B14" s="360"/>
+      <c r="C14" s="360"/>
+      <c r="D14" s="360"/>
+      <c r="E14" s="360"/>
+      <c r="F14" s="360"/>
+      <c r="G14" s="360"/>
+      <c r="H14" s="360"/>
+      <c r="I14" s="379"/>
+      <c r="J14" s="380"/>
+      <c r="K14" s="380"/>
+      <c r="L14" s="380"/>
+      <c r="M14" s="381"/>
+      <c r="N14" s="403"/>
+    </row>
+    <row r="15" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="362" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="189"/>
-      <c r="C15" s="189"/>
-      <c r="D15" s="189"/>
-      <c r="E15" s="189"/>
-      <c r="F15" s="189"/>
-      <c r="G15" s="189"/>
-      <c r="H15" s="403"/>
-      <c r="I15" s="431" t="s">
+      <c r="B15" s="154"/>
+      <c r="C15" s="154"/>
+      <c r="D15" s="154"/>
+      <c r="E15" s="154"/>
+      <c r="F15" s="154"/>
+      <c r="G15" s="154"/>
+      <c r="H15" s="363"/>
+      <c r="I15" s="408" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="431"/>
-      <c r="K15" s="431"/>
-      <c r="L15" s="431"/>
-      <c r="M15" s="432"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="405"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="406"/>
-      <c r="I16" s="199" t="s">
+      <c r="J15" s="409"/>
+      <c r="K15" s="409"/>
+      <c r="L15" s="409"/>
+      <c r="M15" s="410"/>
+      <c r="N15" s="403"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" s="365"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="366"/>
+      <c r="I16" s="411" t="s">
         <v>81</v>
       </c>
-      <c r="J16" s="199"/>
-      <c r="K16" s="199"/>
-      <c r="L16" s="199"/>
-      <c r="M16" s="200"/>
-    </row>
-    <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="407" t="s">
+      <c r="J16" s="161"/>
+      <c r="K16" s="161"/>
+      <c r="L16" s="161"/>
+      <c r="M16" s="412"/>
+      <c r="N16" s="403"/>
+    </row>
+    <row r="17" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="367" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="408"/>
-      <c r="C17" s="408"/>
-      <c r="D17" s="408"/>
-      <c r="E17" s="408"/>
-      <c r="F17" s="396"/>
-      <c r="G17" s="396"/>
-      <c r="H17" s="409"/>
-      <c r="I17" s="404"/>
-      <c r="J17" s="198"/>
-      <c r="K17" s="185" t="s">
+      <c r="B17" s="368"/>
+      <c r="C17" s="368"/>
+      <c r="D17" s="368"/>
+      <c r="E17" s="368"/>
+      <c r="F17" s="356"/>
+      <c r="G17" s="356"/>
+      <c r="H17" s="369"/>
+      <c r="I17" s="364"/>
+      <c r="J17" s="364"/>
+      <c r="K17" s="413" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="185"/>
-      <c r="M17" s="186"/>
-    </row>
-    <row r="18" spans="1:13" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="410"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="411"/>
-      <c r="I18" s="100" t="s">
+      <c r="L17" s="413"/>
+      <c r="M17" s="414"/>
+      <c r="N17" s="403"/>
+    </row>
+    <row r="18" spans="1:14" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="370"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="371"/>
+      <c r="I18" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="100"/>
-      <c r="K18" s="187"/>
-      <c r="L18" s="187"/>
-      <c r="M18" s="188"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="154" t="s">
+      <c r="J18" s="93"/>
+      <c r="K18" s="153"/>
+      <c r="L18" s="153"/>
+      <c r="M18" s="415"/>
+      <c r="N18" s="403"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" s="416" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="155"/>
-      <c r="C19" s="155"/>
-      <c r="D19" s="155"/>
-      <c r="E19" s="155"/>
-      <c r="F19" s="155"/>
-      <c r="G19" s="155"/>
-      <c r="H19" s="155"/>
-      <c r="I19" s="155"/>
-      <c r="J19" s="155"/>
-      <c r="K19" s="155"/>
-      <c r="L19" s="155"/>
-      <c r="M19" s="156"/>
-    </row>
-    <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="201" t="s">
+      <c r="B19" s="417"/>
+      <c r="C19" s="417"/>
+      <c r="D19" s="417"/>
+      <c r="E19" s="417"/>
+      <c r="F19" s="417"/>
+      <c r="G19" s="417"/>
+      <c r="H19" s="417"/>
+      <c r="I19" s="417"/>
+      <c r="J19" s="417"/>
+      <c r="K19" s="417"/>
+      <c r="L19" s="417"/>
+      <c r="M19" s="418"/>
+      <c r="N19" s="403"/>
+    </row>
+    <row r="20" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="162" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="202"/>
-      <c r="C20" s="202"/>
-      <c r="D20" s="202"/>
-      <c r="E20" s="202" t="s">
+      <c r="B20" s="163"/>
+      <c r="C20" s="163"/>
+      <c r="D20" s="163"/>
+      <c r="E20" s="163" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="202" t="s">
+      <c r="F20" s="163" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="202"/>
-      <c r="H20" s="196" t="s">
+      <c r="G20" s="163"/>
+      <c r="H20" s="159" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="197"/>
-      <c r="J20" s="190" t="s">
+      <c r="I20" s="160"/>
+      <c r="J20" s="155" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="191"/>
-      <c r="L20" s="191"/>
-      <c r="M20" s="192"/>
-    </row>
-    <row r="21" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="201"/>
-      <c r="B21" s="202"/>
-      <c r="C21" s="202"/>
-      <c r="D21" s="202"/>
-      <c r="E21" s="202"/>
-      <c r="F21" s="202"/>
-      <c r="G21" s="202"/>
-      <c r="H21" s="210" t="s">
+      <c r="K20" s="156"/>
+      <c r="L20" s="156"/>
+      <c r="M20" s="419"/>
+      <c r="N20" s="403"/>
+    </row>
+    <row r="21" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="162"/>
+      <c r="B21" s="163"/>
+      <c r="C21" s="163"/>
+      <c r="D21" s="163"/>
+      <c r="E21" s="163"/>
+      <c r="F21" s="163"/>
+      <c r="G21" s="163"/>
+      <c r="H21" s="170" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="211"/>
-      <c r="J21" s="193"/>
-      <c r="K21" s="194"/>
-      <c r="L21" s="194"/>
-      <c r="M21" s="195"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="203"/>
-      <c r="B22" s="160"/>
-      <c r="C22" s="160"/>
-      <c r="D22" s="137"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="160"/>
-      <c r="G22" s="160"/>
-      <c r="H22" s="10" t="s">
+      <c r="I21" s="171"/>
+      <c r="J21" s="157"/>
+      <c r="K21" s="158"/>
+      <c r="L21" s="158"/>
+      <c r="M21" s="420"/>
+      <c r="N21" s="403"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" s="164"/>
+      <c r="B22" s="133"/>
+      <c r="C22" s="133"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="133"/>
+      <c r="G22" s="133"/>
+      <c r="H22" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I22" s="10" t="s">
+      <c r="I22" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="160"/>
-      <c r="K22" s="160"/>
-      <c r="L22" s="160"/>
-      <c r="M22" s="172"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="175"/>
-      <c r="B23" s="176"/>
-      <c r="C23" s="176"/>
-      <c r="D23" s="177"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="160"/>
-      <c r="G23" s="160"/>
-      <c r="H23" s="10" t="s">
+      <c r="J22" s="133"/>
+      <c r="K22" s="133"/>
+      <c r="L22" s="133"/>
+      <c r="M22" s="133"/>
+      <c r="N22" s="403"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" s="144"/>
+      <c r="B23" s="145"/>
+      <c r="C23" s="145"/>
+      <c r="D23" s="146"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="133"/>
+      <c r="G23" s="133"/>
+      <c r="H23" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I23" s="10" t="s">
+      <c r="I23" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="160"/>
-      <c r="K23" s="160"/>
-      <c r="L23" s="160"/>
-      <c r="M23" s="172"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="175"/>
-      <c r="B24" s="176"/>
-      <c r="C24" s="176"/>
-      <c r="D24" s="177"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="160"/>
-      <c r="G24" s="160"/>
-      <c r="H24" s="10" t="s">
+      <c r="J23" s="133"/>
+      <c r="K23" s="133"/>
+      <c r="L23" s="133"/>
+      <c r="M23" s="133"/>
+      <c r="N23" s="403"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" s="144"/>
+      <c r="B24" s="145"/>
+      <c r="C24" s="145"/>
+      <c r="D24" s="146"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="133"/>
+      <c r="H24" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I24" s="10" t="s">
+      <c r="I24" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="160"/>
-      <c r="K24" s="160"/>
-      <c r="L24" s="160"/>
-      <c r="M24" s="172"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="175"/>
-      <c r="B25" s="176"/>
-      <c r="C25" s="176"/>
-      <c r="D25" s="177"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="160"/>
-      <c r="G25" s="160"/>
-      <c r="H25" s="10" t="s">
+      <c r="J24" s="133"/>
+      <c r="K24" s="133"/>
+      <c r="L24" s="133"/>
+      <c r="M24" s="133"/>
+      <c r="N24" s="403"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" s="144"/>
+      <c r="B25" s="145"/>
+      <c r="C25" s="145"/>
+      <c r="D25" s="146"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="133"/>
+      <c r="G25" s="133"/>
+      <c r="H25" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I25" s="10" t="s">
+      <c r="I25" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="160"/>
-      <c r="K25" s="160"/>
-      <c r="L25" s="160"/>
-      <c r="M25" s="172"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="175"/>
-      <c r="B26" s="176"/>
-      <c r="C26" s="176"/>
-      <c r="D26" s="177"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="160"/>
-      <c r="G26" s="160"/>
-      <c r="H26" s="10" t="s">
+      <c r="J25" s="133"/>
+      <c r="K25" s="133"/>
+      <c r="L25" s="133"/>
+      <c r="M25" s="133"/>
+      <c r="N25" s="403"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" s="144"/>
+      <c r="B26" s="145"/>
+      <c r="C26" s="145"/>
+      <c r="D26" s="146"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="133"/>
+      <c r="G26" s="133"/>
+      <c r="H26" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I26" s="10" t="s">
+      <c r="I26" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="160"/>
-      <c r="K26" s="160"/>
-      <c r="L26" s="160"/>
-      <c r="M26" s="172"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="175"/>
-      <c r="B27" s="176"/>
-      <c r="C27" s="176"/>
-      <c r="D27" s="177"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="160"/>
-      <c r="G27" s="160"/>
-      <c r="H27" s="10" t="s">
+      <c r="J26" s="133"/>
+      <c r="K26" s="133"/>
+      <c r="L26" s="133"/>
+      <c r="M26" s="133"/>
+      <c r="N26" s="403"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" s="144"/>
+      <c r="B27" s="145"/>
+      <c r="C27" s="145"/>
+      <c r="D27" s="146"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I27" s="10" t="s">
+      <c r="I27" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="J27" s="160"/>
-      <c r="K27" s="160"/>
-      <c r="L27" s="160"/>
-      <c r="M27" s="172"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="175"/>
-      <c r="B28" s="176"/>
-      <c r="C28" s="176"/>
-      <c r="D28" s="177"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="160"/>
-      <c r="G28" s="160"/>
-      <c r="H28" s="10" t="s">
+      <c r="J27" s="133"/>
+      <c r="K27" s="133"/>
+      <c r="L27" s="133"/>
+      <c r="M27" s="133"/>
+      <c r="N27" s="403"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" s="144"/>
+      <c r="B28" s="145"/>
+      <c r="C28" s="145"/>
+      <c r="D28" s="146"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="133"/>
+      <c r="G28" s="133"/>
+      <c r="H28" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="10" t="s">
+      <c r="I28" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="J28" s="160"/>
-      <c r="K28" s="160"/>
-      <c r="L28" s="160"/>
-      <c r="M28" s="172"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="175"/>
-      <c r="B29" s="176"/>
-      <c r="C29" s="176"/>
-      <c r="D29" s="177"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="160"/>
-      <c r="G29" s="160"/>
-      <c r="H29" s="10" t="s">
+      <c r="J28" s="133"/>
+      <c r="K28" s="133"/>
+      <c r="L28" s="133"/>
+      <c r="M28" s="133"/>
+      <c r="N28" s="403"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" s="144"/>
+      <c r="B29" s="145"/>
+      <c r="C29" s="145"/>
+      <c r="D29" s="146"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="133"/>
+      <c r="G29" s="133"/>
+      <c r="H29" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I29" s="10" t="s">
+      <c r="I29" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="J29" s="160"/>
-      <c r="K29" s="160"/>
-      <c r="L29" s="160"/>
-      <c r="M29" s="172"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="173" t="s">
+      <c r="J29" s="133"/>
+      <c r="K29" s="133"/>
+      <c r="L29" s="133"/>
+      <c r="M29" s="133"/>
+      <c r="N29" s="403"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="174"/>
-      <c r="C30" s="174"/>
-      <c r="D30" s="174"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="161"/>
-      <c r="G30" s="160"/>
-      <c r="H30" s="178"/>
-      <c r="I30" s="180"/>
-      <c r="J30" s="178"/>
-      <c r="K30" s="179"/>
-      <c r="L30" s="179"/>
-      <c r="M30" s="180"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="162" t="s">
+      <c r="B30" s="143"/>
+      <c r="C30" s="143"/>
+      <c r="D30" s="143"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="134"/>
+      <c r="G30" s="133"/>
+      <c r="H30" s="147"/>
+      <c r="I30" s="149"/>
+      <c r="J30" s="147"/>
+      <c r="K30" s="148"/>
+      <c r="L30" s="148"/>
+      <c r="M30" s="149"/>
+      <c r="N30" s="403"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A31" s="135" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="163"/>
-      <c r="C31" s="163"/>
-      <c r="D31" s="163"/>
-      <c r="E31" s="163"/>
-      <c r="F31" s="163"/>
-      <c r="G31" s="163"/>
-      <c r="H31" s="163"/>
-      <c r="I31" s="163"/>
-      <c r="J31" s="163"/>
-      <c r="K31" s="163"/>
-      <c r="L31" s="163"/>
-      <c r="M31" s="164"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="169" t="s">
+      <c r="B31" s="397"/>
+      <c r="C31" s="397"/>
+      <c r="D31" s="397"/>
+      <c r="E31" s="397"/>
+      <c r="F31" s="397"/>
+      <c r="G31" s="397"/>
+      <c r="H31" s="397"/>
+      <c r="I31" s="397"/>
+      <c r="J31" s="397"/>
+      <c r="K31" s="397"/>
+      <c r="L31" s="397"/>
+      <c r="M31" s="421"/>
+      <c r="N31" s="403"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A32" s="139" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="167"/>
-      <c r="C32" s="167" t="s">
+      <c r="B32" s="138"/>
+      <c r="C32" s="138" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="167"/>
-      <c r="E32" s="170" t="s">
+      <c r="D32" s="138"/>
+      <c r="E32" s="140" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="171" t="s">
+      <c r="F32" s="141" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="165" t="s">
+      <c r="G32" s="136" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="165"/>
-      <c r="I32" s="165"/>
-      <c r="J32" s="165"/>
-      <c r="K32" s="165"/>
-      <c r="L32" s="167" t="s">
+      <c r="H32" s="136"/>
+      <c r="I32" s="136"/>
+      <c r="J32" s="136"/>
+      <c r="K32" s="136"/>
+      <c r="L32" s="138" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="168"/>
-    </row>
-    <row r="33" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M32" s="138"/>
+      <c r="N32" s="403"/>
+    </row>
+    <row r="33" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>7</v>
       </c>
@@ -8158,476 +8228,510 @@
       <c r="D33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="170"/>
-      <c r="F33" s="171"/>
-      <c r="G33" s="166" t="s">
+      <c r="E33" s="140"/>
+      <c r="F33" s="141"/>
+      <c r="G33" s="137" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="166"/>
-      <c r="I33" s="166"/>
-      <c r="J33" s="166"/>
-      <c r="K33" s="166"/>
+      <c r="H33" s="137"/>
+      <c r="I33" s="137"/>
+      <c r="J33" s="137"/>
+      <c r="K33" s="137"/>
       <c r="L33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M33" s="5" t="s">
+      <c r="M33" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="42"/>
-      <c r="B34" s="10" t="s">
+      <c r="N33" s="403"/>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A34" s="41"/>
+      <c r="B34" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C34" s="9"/>
-      <c r="D34" s="41" t="s">
+      <c r="C34" s="8"/>
+      <c r="D34" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="E34" s="9"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="137" t="s">
+      <c r="E34" s="8"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="118" t="s">
         <v>74</v>
       </c>
-      <c r="H34" s="138"/>
-      <c r="I34" s="138"/>
-      <c r="J34" s="138"/>
-      <c r="K34" s="139"/>
-      <c r="L34" s="43"/>
-      <c r="M34" s="44"/>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" s="45"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="137"/>
-      <c r="H35" s="138"/>
-      <c r="I35" s="138"/>
-      <c r="J35" s="138"/>
-      <c r="K35" s="139"/>
-      <c r="L35" s="43"/>
-      <c r="M35" s="44"/>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" s="45"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="137"/>
-      <c r="H36" s="138"/>
-      <c r="I36" s="138"/>
-      <c r="J36" s="138"/>
-      <c r="K36" s="139"/>
-      <c r="L36" s="43"/>
-      <c r="M36" s="44"/>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A37" s="45"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="137"/>
-      <c r="H37" s="138"/>
-      <c r="I37" s="138"/>
-      <c r="J37" s="138"/>
-      <c r="K37" s="139"/>
-      <c r="L37" s="43"/>
-      <c r="M37" s="44"/>
-      <c r="Q37" s="128"/>
-      <c r="R37" s="128"/>
-      <c r="S37" s="7"/>
-      <c r="T37" s="105"/>
-      <c r="U37" s="105"/>
-      <c r="V37" s="105"/>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A38" s="45"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="137"/>
-      <c r="H38" s="138"/>
-      <c r="I38" s="138"/>
-      <c r="J38" s="138"/>
-      <c r="K38" s="139"/>
-      <c r="L38" s="43"/>
-      <c r="M38" s="46"/>
-      <c r="Q38" s="128"/>
-      <c r="R38" s="128"/>
-      <c r="S38" s="7"/>
-      <c r="T38" s="105"/>
-      <c r="U38" s="105"/>
-      <c r="V38" s="105"/>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A39" s="45"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="137"/>
-      <c r="H39" s="138"/>
-      <c r="I39" s="138"/>
-      <c r="J39" s="138"/>
-      <c r="K39" s="139"/>
-      <c r="L39" s="43"/>
-      <c r="M39" s="46"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="6"/>
-      <c r="S39" s="131"/>
-      <c r="T39" s="105"/>
-      <c r="U39" s="105"/>
-      <c r="V39" s="105"/>
-    </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A40" s="45"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="43"/>
-      <c r="G40" s="137"/>
-      <c r="H40" s="138"/>
-      <c r="I40" s="138"/>
-      <c r="J40" s="138"/>
-      <c r="K40" s="139"/>
-      <c r="L40" s="43"/>
-      <c r="M40" s="44"/>
-      <c r="Q40" s="6"/>
-      <c r="R40" s="6"/>
-      <c r="S40" s="131"/>
-      <c r="T40" s="105"/>
-      <c r="U40" s="105"/>
-      <c r="V40" s="105"/>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A41" s="45"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="137"/>
-      <c r="H41" s="138"/>
-      <c r="I41" s="138"/>
-      <c r="J41" s="138"/>
-      <c r="K41" s="139"/>
-      <c r="L41" s="43"/>
-      <c r="M41" s="44"/>
-    </row>
-    <row r="42" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="47"/>
-      <c r="B42" s="48"/>
-      <c r="C42" s="49"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="49"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="140" t="s">
+      <c r="H34" s="119"/>
+      <c r="I34" s="119"/>
+      <c r="J34" s="119"/>
+      <c r="K34" s="120"/>
+      <c r="L34" s="42"/>
+      <c r="M34" s="42"/>
+      <c r="N34" s="403"/>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A35" s="43"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="118"/>
+      <c r="H35" s="119"/>
+      <c r="I35" s="119"/>
+      <c r="J35" s="119"/>
+      <c r="K35" s="120"/>
+      <c r="L35" s="42"/>
+      <c r="M35" s="42"/>
+      <c r="N35" s="403"/>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A36" s="43"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="118"/>
+      <c r="H36" s="119"/>
+      <c r="I36" s="119"/>
+      <c r="J36" s="119"/>
+      <c r="K36" s="120"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="403"/>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A37" s="43"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="118"/>
+      <c r="H37" s="119"/>
+      <c r="I37" s="119"/>
+      <c r="J37" s="119"/>
+      <c r="K37" s="120"/>
+      <c r="L37" s="42"/>
+      <c r="M37" s="42"/>
+      <c r="N37" s="403"/>
+      <c r="P37" s="114"/>
+      <c r="Q37" s="114"/>
+      <c r="R37" s="6"/>
+      <c r="S37" s="97"/>
+      <c r="T37" s="97"/>
+      <c r="U37" s="97"/>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A38" s="43"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="118"/>
+      <c r="H38" s="119"/>
+      <c r="I38" s="119"/>
+      <c r="J38" s="119"/>
+      <c r="K38" s="120"/>
+      <c r="L38" s="42"/>
+      <c r="M38" s="404"/>
+      <c r="N38" s="403"/>
+      <c r="P38" s="114"/>
+      <c r="Q38" s="114"/>
+      <c r="R38" s="6"/>
+      <c r="S38" s="97"/>
+      <c r="T38" s="97"/>
+      <c r="U38" s="97"/>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A39" s="43"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="118"/>
+      <c r="H39" s="119"/>
+      <c r="I39" s="119"/>
+      <c r="J39" s="119"/>
+      <c r="K39" s="120"/>
+      <c r="L39" s="42"/>
+      <c r="M39" s="404"/>
+      <c r="N39" s="403"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="117"/>
+      <c r="S39" s="97"/>
+      <c r="T39" s="97"/>
+      <c r="U39" s="97"/>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A40" s="43"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="118"/>
+      <c r="H40" s="119"/>
+      <c r="I40" s="119"/>
+      <c r="J40" s="119"/>
+      <c r="K40" s="120"/>
+      <c r="L40" s="42"/>
+      <c r="M40" s="42"/>
+      <c r="N40" s="403"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="117"/>
+      <c r="S40" s="97"/>
+      <c r="T40" s="97"/>
+      <c r="U40" s="97"/>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A41" s="43"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="118"/>
+      <c r="H41" s="119"/>
+      <c r="I41" s="119"/>
+      <c r="J41" s="119"/>
+      <c r="K41" s="120"/>
+      <c r="L41" s="42"/>
+      <c r="M41" s="42"/>
+      <c r="N41" s="403"/>
+    </row>
+    <row r="42" spans="1:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="44"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="46"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="141"/>
-      <c r="I42" s="141"/>
-      <c r="J42" s="141"/>
-      <c r="K42" s="142"/>
-      <c r="L42" s="50"/>
-      <c r="M42" s="51"/>
-    </row>
-    <row r="43" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="107" t="s">
+      <c r="H42" s="122"/>
+      <c r="I42" s="122"/>
+      <c r="J42" s="122"/>
+      <c r="K42" s="123"/>
+      <c r="L42" s="47"/>
+      <c r="M42" s="47"/>
+      <c r="N42" s="403"/>
+    </row>
+    <row r="43" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="108"/>
-      <c r="C43" s="108"/>
-      <c r="D43" s="108"/>
-      <c r="E43" s="108"/>
-      <c r="F43" s="108"/>
-      <c r="G43" s="108"/>
-      <c r="H43" s="109"/>
-      <c r="I43" s="151" t="s">
+      <c r="B43" s="100"/>
+      <c r="C43" s="100"/>
+      <c r="D43" s="100"/>
+      <c r="E43" s="100"/>
+      <c r="F43" s="100"/>
+      <c r="G43" s="100"/>
+      <c r="H43" s="101"/>
+      <c r="I43" s="129" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="152"/>
-      <c r="K43" s="152"/>
-      <c r="L43" s="152"/>
-      <c r="M43" s="153"/>
-    </row>
-    <row r="44" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="110"/>
-      <c r="B44" s="111"/>
-      <c r="C44" s="111"/>
-      <c r="D44" s="111"/>
-      <c r="E44" s="111"/>
-      <c r="F44" s="111"/>
-      <c r="G44" s="111"/>
-      <c r="H44" s="112"/>
-      <c r="I44" s="154"/>
-      <c r="J44" s="155"/>
-      <c r="K44" s="155"/>
-      <c r="L44" s="155"/>
-      <c r="M44" s="156"/>
-    </row>
-    <row r="45" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="113" t="s">
+      <c r="J43" s="130"/>
+      <c r="K43" s="130"/>
+      <c r="L43" s="130"/>
+      <c r="M43" s="422"/>
+      <c r="N43" s="403"/>
+    </row>
+    <row r="44" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="102"/>
+      <c r="B44" s="423"/>
+      <c r="C44" s="423"/>
+      <c r="D44" s="423"/>
+      <c r="E44" s="423"/>
+      <c r="F44" s="423"/>
+      <c r="G44" s="423"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="131"/>
+      <c r="J44" s="396"/>
+      <c r="K44" s="396"/>
+      <c r="L44" s="396"/>
+      <c r="M44" s="424"/>
+      <c r="N44" s="403"/>
+    </row>
+    <row r="45" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="114"/>
-      <c r="C45" s="114"/>
-      <c r="D45" s="114"/>
-      <c r="E45" s="114"/>
-      <c r="F45" s="114"/>
-      <c r="G45" s="114"/>
-      <c r="H45" s="115"/>
-      <c r="I45" s="157" t="s">
+      <c r="B45" s="425"/>
+      <c r="C45" s="425"/>
+      <c r="D45" s="425"/>
+      <c r="E45" s="425"/>
+      <c r="F45" s="425"/>
+      <c r="G45" s="425"/>
+      <c r="H45" s="105"/>
+      <c r="I45" s="132" t="s">
         <v>36</v>
       </c>
-      <c r="J45" s="158"/>
-      <c r="K45" s="158"/>
-      <c r="L45" s="158"/>
-      <c r="M45" s="159"/>
-    </row>
-    <row r="46" spans="1:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="113" t="s">
+      <c r="J45" s="398"/>
+      <c r="K45" s="398"/>
+      <c r="L45" s="398"/>
+      <c r="M45" s="426"/>
+      <c r="N45" s="403"/>
+    </row>
+    <row r="46" spans="1:21" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="114"/>
-      <c r="C46" s="114"/>
-      <c r="D46" s="114"/>
-      <c r="E46" s="114"/>
-      <c r="F46" s="114"/>
-      <c r="G46" s="114"/>
-      <c r="H46" s="115"/>
-      <c r="I46" s="157"/>
-      <c r="J46" s="158"/>
-      <c r="K46" s="158"/>
-      <c r="L46" s="158"/>
-      <c r="M46" s="159"/>
-    </row>
-    <row r="47" spans="1:22" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="116"/>
-      <c r="B47" s="117"/>
-      <c r="C47" s="117"/>
-      <c r="D47" s="117"/>
-      <c r="E47" s="117"/>
-      <c r="F47" s="117"/>
-      <c r="G47" s="117"/>
-      <c r="H47" s="118"/>
-      <c r="I47" s="102" t="s">
+      <c r="B46" s="425"/>
+      <c r="C46" s="425"/>
+      <c r="D46" s="425"/>
+      <c r="E46" s="425"/>
+      <c r="F46" s="425"/>
+      <c r="G46" s="425"/>
+      <c r="H46" s="105"/>
+      <c r="I46" s="132"/>
+      <c r="J46" s="398"/>
+      <c r="K46" s="398"/>
+      <c r="L46" s="398"/>
+      <c r="M46" s="426"/>
+      <c r="N46" s="403"/>
+    </row>
+    <row r="47" spans="1:21" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="106"/>
+      <c r="B47" s="107"/>
+      <c r="C47" s="107"/>
+      <c r="D47" s="107"/>
+      <c r="E47" s="107"/>
+      <c r="F47" s="107"/>
+      <c r="G47" s="107"/>
+      <c r="H47" s="108"/>
+      <c r="I47" s="95" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="103"/>
-      <c r="K47" s="103"/>
-      <c r="L47" s="103"/>
-      <c r="M47" s="104"/>
-    </row>
-    <row r="48" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="123" t="s">
+      <c r="J47" s="96"/>
+      <c r="K47" s="96"/>
+      <c r="L47" s="96"/>
+      <c r="M47" s="427"/>
+      <c r="N47" s="403"/>
+    </row>
+    <row r="48" spans="1:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="110" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="124"/>
-      <c r="C48" s="124"/>
-      <c r="D48" s="124"/>
-      <c r="E48" s="124"/>
-      <c r="F48" s="124"/>
-      <c r="G48" s="124"/>
-      <c r="H48" s="124"/>
-      <c r="I48" s="124"/>
-      <c r="J48" s="124"/>
-      <c r="K48" s="124"/>
-      <c r="L48" s="124"/>
-      <c r="M48" s="132"/>
-    </row>
-    <row r="49" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="107" t="s">
+      <c r="B48" s="111"/>
+      <c r="C48" s="111"/>
+      <c r="D48" s="111"/>
+      <c r="E48" s="111"/>
+      <c r="F48" s="111"/>
+      <c r="G48" s="111"/>
+      <c r="H48" s="111"/>
+      <c r="I48" s="111"/>
+      <c r="J48" s="111"/>
+      <c r="K48" s="111"/>
+      <c r="L48" s="111"/>
+      <c r="M48" s="428"/>
+      <c r="N48" s="403"/>
+    </row>
+    <row r="49" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="108"/>
-      <c r="C49" s="108"/>
-      <c r="D49" s="108"/>
-      <c r="E49" s="108"/>
-      <c r="F49" s="108"/>
-      <c r="G49" s="108"/>
-      <c r="H49" s="109"/>
-      <c r="I49" s="143" t="s">
+      <c r="B49" s="100"/>
+      <c r="C49" s="100"/>
+      <c r="D49" s="100"/>
+      <c r="E49" s="100"/>
+      <c r="F49" s="100"/>
+      <c r="G49" s="100"/>
+      <c r="H49" s="101"/>
+      <c r="I49" s="124" t="s">
         <v>40</v>
       </c>
-      <c r="J49" s="144"/>
-      <c r="K49" s="144"/>
-      <c r="L49" s="144"/>
-      <c r="M49" s="145"/>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="110"/>
-      <c r="B50" s="111"/>
-      <c r="C50" s="111"/>
-      <c r="D50" s="111"/>
-      <c r="E50" s="111"/>
-      <c r="F50" s="111"/>
-      <c r="G50" s="111"/>
-      <c r="H50" s="112"/>
-      <c r="I50" s="146"/>
-      <c r="J50" s="147"/>
-      <c r="K50" s="147"/>
-      <c r="L50" s="147"/>
-      <c r="M50" s="148"/>
-    </row>
-    <row r="51" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="149"/>
-      <c r="B51" s="150"/>
-      <c r="C51" s="150"/>
-      <c r="D51" s="150"/>
-      <c r="E51" s="111"/>
-      <c r="F51" s="111"/>
-      <c r="G51" s="111"/>
-      <c r="H51" s="112"/>
-      <c r="I51" s="119" t="s">
+      <c r="J49" s="125"/>
+      <c r="K49" s="125"/>
+      <c r="L49" s="125"/>
+      <c r="M49" s="429"/>
+      <c r="N49" s="403"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A50" s="102"/>
+      <c r="B50" s="423"/>
+      <c r="C50" s="423"/>
+      <c r="D50" s="423"/>
+      <c r="E50" s="423"/>
+      <c r="F50" s="423"/>
+      <c r="G50" s="423"/>
+      <c r="H50" s="103"/>
+      <c r="I50" s="126"/>
+      <c r="J50" s="399"/>
+      <c r="K50" s="399"/>
+      <c r="L50" s="399"/>
+      <c r="M50" s="430"/>
+      <c r="N50" s="403"/>
+    </row>
+    <row r="51" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="127"/>
+      <c r="B51" s="128"/>
+      <c r="C51" s="128"/>
+      <c r="D51" s="128"/>
+      <c r="E51" s="128"/>
+      <c r="F51" s="128"/>
+      <c r="G51" s="128"/>
+      <c r="H51" s="431"/>
+      <c r="I51" s="432" t="s">
         <v>41</v>
       </c>
-      <c r="J51" s="120"/>
-      <c r="K51" s="121"/>
-      <c r="L51" s="121"/>
-      <c r="M51" s="122"/>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="123" t="s">
+      <c r="J51" s="109"/>
+      <c r="K51" s="109"/>
+      <c r="L51" s="109"/>
+      <c r="M51" s="433"/>
+      <c r="N51" s="403"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A52" s="110" t="s">
         <v>42</v>
       </c>
-      <c r="B52" s="124"/>
-      <c r="C52" s="124"/>
-      <c r="D52" s="124"/>
-      <c r="E52" s="52" t="s">
+      <c r="B52" s="111"/>
+      <c r="C52" s="111"/>
+      <c r="D52" s="111"/>
+      <c r="E52" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="F52" s="53"/>
-      <c r="G52" s="129" t="s">
+      <c r="F52" s="49"/>
+      <c r="G52" s="115" t="s">
         <v>45</v>
       </c>
-      <c r="H52" s="129"/>
-      <c r="I52" s="129"/>
-      <c r="J52" s="130"/>
-      <c r="K52" s="124" t="s">
+      <c r="H52" s="115"/>
+      <c r="I52" s="115"/>
+      <c r="J52" s="116"/>
+      <c r="K52" s="111" t="s">
         <v>50</v>
       </c>
-      <c r="L52" s="124"/>
-      <c r="M52" s="132"/>
-    </row>
-    <row r="53" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="125" t="s">
+      <c r="L52" s="111"/>
+      <c r="M52" s="428"/>
+      <c r="N52" s="403"/>
+    </row>
+    <row r="53" spans="1:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="B53" s="126"/>
-      <c r="C53" s="126"/>
-      <c r="D53" s="126"/>
-      <c r="E53" s="40"/>
-      <c r="J53" s="38"/>
-      <c r="K53" s="133" t="s">
+      <c r="B53" s="434"/>
+      <c r="C53" s="434"/>
+      <c r="D53" s="434"/>
+      <c r="E53" s="39"/>
+      <c r="F53" s="382"/>
+      <c r="G53" s="382"/>
+      <c r="H53" s="382"/>
+      <c r="I53" s="382"/>
+      <c r="J53" s="37"/>
+      <c r="K53" s="400" t="s">
         <v>52</v>
       </c>
-      <c r="L53" s="133"/>
-      <c r="M53" s="134"/>
-    </row>
-    <row r="54" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="125"/>
-      <c r="B54" s="126"/>
-      <c r="C54" s="126"/>
-      <c r="D54" s="126"/>
-      <c r="E54" s="127" t="s">
+      <c r="L53" s="400"/>
+      <c r="M53" s="435"/>
+      <c r="N53" s="403"/>
+    </row>
+    <row r="54" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="112"/>
+      <c r="B54" s="434"/>
+      <c r="C54" s="434"/>
+      <c r="D54" s="434"/>
+      <c r="E54" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="F54" s="128"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="105" t="s">
+      <c r="F54" s="436"/>
+      <c r="G54" s="437"/>
+      <c r="H54" s="438" t="s">
         <v>46</v>
       </c>
-      <c r="I54" s="105"/>
-      <c r="J54" s="106"/>
-      <c r="K54" s="133"/>
-      <c r="L54" s="133"/>
-      <c r="M54" s="134"/>
-    </row>
-    <row r="55" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="125"/>
-      <c r="B55" s="126"/>
-      <c r="C55" s="126"/>
-      <c r="D55" s="126"/>
-      <c r="E55" s="127" t="s">
+      <c r="I54" s="438"/>
+      <c r="J54" s="98"/>
+      <c r="K54" s="400"/>
+      <c r="L54" s="400"/>
+      <c r="M54" s="435"/>
+      <c r="N54" s="403"/>
+    </row>
+    <row r="55" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="112"/>
+      <c r="B55" s="434"/>
+      <c r="C55" s="434"/>
+      <c r="D55" s="434"/>
+      <c r="E55" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="F55" s="128"/>
-      <c r="G55" s="128"/>
-      <c r="H55" s="105" t="s">
+      <c r="F55" s="436"/>
+      <c r="G55" s="436"/>
+      <c r="H55" s="438" t="s">
         <v>48</v>
       </c>
-      <c r="I55" s="105"/>
-      <c r="J55" s="106"/>
-      <c r="K55" s="133"/>
-      <c r="L55" s="133"/>
-      <c r="M55" s="134"/>
-    </row>
-    <row r="56" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="40"/>
-      <c r="D56" s="38"/>
-      <c r="E56" s="127"/>
-      <c r="F56" s="128"/>
-      <c r="G56" s="128"/>
-      <c r="H56" s="105"/>
-      <c r="I56" s="105"/>
-      <c r="J56" s="106"/>
-      <c r="K56" s="135" t="s">
+      <c r="I55" s="438"/>
+      <c r="J55" s="98"/>
+      <c r="K55" s="400"/>
+      <c r="L55" s="400"/>
+      <c r="M55" s="435"/>
+      <c r="N55" s="403"/>
+    </row>
+    <row r="56" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="39"/>
+      <c r="B56" s="382"/>
+      <c r="C56" s="382"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="113"/>
+      <c r="F56" s="436"/>
+      <c r="G56" s="436"/>
+      <c r="H56" s="438"/>
+      <c r="I56" s="438"/>
+      <c r="J56" s="98"/>
+      <c r="K56" s="401" t="s">
         <v>51</v>
       </c>
-      <c r="L56" s="135"/>
-      <c r="M56" s="136"/>
-    </row>
-    <row r="57" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="40"/>
-      <c r="D57" s="38"/>
-      <c r="E57" s="127"/>
-      <c r="F57" s="128"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="105" t="s">
+      <c r="L56" s="401"/>
+      <c r="M56" s="439"/>
+      <c r="N56" s="403"/>
+    </row>
+    <row r="57" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="39"/>
+      <c r="B57" s="382"/>
+      <c r="C57" s="382"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="113"/>
+      <c r="F57" s="436"/>
+      <c r="G57" s="437"/>
+      <c r="H57" s="438" t="s">
         <v>49</v>
       </c>
-      <c r="I57" s="105"/>
-      <c r="J57" s="106"/>
-      <c r="K57" s="54"/>
-      <c r="L57" s="55"/>
-      <c r="M57" s="56"/>
-    </row>
-    <row r="58" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="57"/>
-      <c r="B58" s="205"/>
-      <c r="C58" s="205"/>
-      <c r="D58" s="34"/>
-      <c r="E58" s="99"/>
-      <c r="F58" s="100"/>
-      <c r="G58" s="100"/>
-      <c r="H58" s="100"/>
-      <c r="I58" s="100"/>
-      <c r="J58" s="101"/>
-      <c r="K58" s="58"/>
-      <c r="L58" s="59"/>
-      <c r="M58" s="60"/>
-    </row>
-    <row r="59" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I57" s="438"/>
+      <c r="J57" s="98"/>
+      <c r="K57" s="50"/>
+      <c r="L57" s="402"/>
+      <c r="M57" s="405"/>
+      <c r="N57" s="403"/>
+    </row>
+    <row r="58" spans="1:14" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="51"/>
+      <c r="B58" s="165"/>
+      <c r="C58" s="165"/>
+      <c r="D58" s="33"/>
+      <c r="E58" s="92"/>
+      <c r="F58" s="93"/>
+      <c r="G58" s="93"/>
+      <c r="H58" s="93"/>
+      <c r="I58" s="93"/>
+      <c r="J58" s="94"/>
+      <c r="K58" s="52"/>
+      <c r="L58" s="53"/>
+      <c r="M58" s="406"/>
+      <c r="N58" s="403"/>
+    </row>
+    <row r="59" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="8"/>
-      <c r="I59" s="8"/>
-      <c r="J59" s="8"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="110">
@@ -8705,12 +8809,12 @@
     <mergeCell ref="J27:M27"/>
     <mergeCell ref="A30:D30"/>
     <mergeCell ref="G34:K34"/>
-    <mergeCell ref="T37:V37"/>
-    <mergeCell ref="T38:V38"/>
-    <mergeCell ref="T39:V40"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="S39:S40"/>
+    <mergeCell ref="S37:U37"/>
+    <mergeCell ref="S38:U38"/>
+    <mergeCell ref="S39:U40"/>
+    <mergeCell ref="P37:Q37"/>
+    <mergeCell ref="P38:Q38"/>
+    <mergeCell ref="R39:R40"/>
     <mergeCell ref="K52:M52"/>
     <mergeCell ref="K53:M55"/>
     <mergeCell ref="K56:M56"/>

--- a/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
+++ b/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Procomm\Documents\GitHub\Acumatica_Customizations_and_Packages\Istar_Development\Projects\BOL_Generation\Code\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD7B902-8E2A-4842-BE44-38E79A69FF1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93E07A3-DE6F-4B55-8D62-0B059AD9C45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="28800" windowHeight="15345" xr2:uid="{888CA347-7849-4038-B8EE-FAC87BA1B844}"/>
+    <workbookView xWindow="2640" yWindow="2640" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{888CA347-7849-4038-B8EE-FAC87BA1B844}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterBOL" sheetId="3" r:id="rId1"/>
@@ -1018,7 +1018,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="419">
+  <cellXfs count="415">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1079,12 +1079,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1200,22 +1194,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2139,6 +2117,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3415,614 +3405,614 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="387" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="379" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="388"/>
-      <c r="E1" s="388"/>
-      <c r="F1" s="388"/>
-      <c r="G1" s="388"/>
-      <c r="H1" s="388"/>
-      <c r="I1" s="388"/>
-      <c r="J1" s="388"/>
-      <c r="K1" s="389"/>
-      <c r="L1" s="390" t="s">
+      <c r="D1" s="380"/>
+      <c r="E1" s="380"/>
+      <c r="F1" s="380"/>
+      <c r="G1" s="380"/>
+      <c r="H1" s="380"/>
+      <c r="I1" s="380"/>
+      <c r="J1" s="380"/>
+      <c r="K1" s="381"/>
+      <c r="L1" s="382" t="s">
         <v>58</v>
       </c>
-      <c r="M1" s="391"/>
+      <c r="M1" s="383"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="320" t="s">
+      <c r="A2" s="312" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="321"/>
-      <c r="C2" s="321"/>
-      <c r="D2" s="321"/>
-      <c r="E2" s="321"/>
-      <c r="F2" s="321"/>
-      <c r="G2" s="321"/>
-      <c r="H2" s="322"/>
-      <c r="I2" s="392" t="s">
+      <c r="B2" s="313"/>
+      <c r="C2" s="313"/>
+      <c r="D2" s="313"/>
+      <c r="E2" s="313"/>
+      <c r="F2" s="313"/>
+      <c r="G2" s="313"/>
+      <c r="H2" s="314"/>
+      <c r="I2" s="384" t="s">
         <v>73</v>
       </c>
-      <c r="J2" s="393"/>
-      <c r="K2" s="393"/>
-      <c r="L2" s="393"/>
-      <c r="M2" s="394"/>
+      <c r="J2" s="385"/>
+      <c r="K2" s="385"/>
+      <c r="L2" s="385"/>
+      <c r="M2" s="386"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="372" t="s">
+      <c r="A3" s="364" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="373"/>
-      <c r="C3" s="373"/>
-      <c r="D3" s="373"/>
-      <c r="E3" s="373"/>
-      <c r="F3" s="373"/>
-      <c r="G3" s="373"/>
-      <c r="H3" s="374"/>
-      <c r="I3" s="392"/>
-      <c r="J3" s="393"/>
-      <c r="K3" s="393"/>
-      <c r="L3" s="393"/>
-      <c r="M3" s="394"/>
+      <c r="B3" s="365"/>
+      <c r="C3" s="365"/>
+      <c r="D3" s="365"/>
+      <c r="E3" s="365"/>
+      <c r="F3" s="365"/>
+      <c r="G3" s="365"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="384"/>
+      <c r="J3" s="385"/>
+      <c r="K3" s="385"/>
+      <c r="L3" s="385"/>
+      <c r="M3" s="386"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="372" t="s">
+      <c r="A4" s="364" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="373"/>
-      <c r="C4" s="373"/>
-      <c r="D4" s="373"/>
-      <c r="E4" s="373"/>
-      <c r="F4" s="373"/>
-      <c r="G4" s="373"/>
-      <c r="H4" s="374"/>
-      <c r="I4" s="378"/>
-      <c r="J4" s="379"/>
-      <c r="K4" s="379"/>
-      <c r="L4" s="379"/>
-      <c r="M4" s="380"/>
+      <c r="B4" s="365"/>
+      <c r="C4" s="365"/>
+      <c r="D4" s="365"/>
+      <c r="E4" s="365"/>
+      <c r="F4" s="365"/>
+      <c r="G4" s="365"/>
+      <c r="H4" s="366"/>
+      <c r="I4" s="370"/>
+      <c r="J4" s="371"/>
+      <c r="K4" s="371"/>
+      <c r="L4" s="371"/>
+      <c r="M4" s="372"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="372" t="s">
+      <c r="A5" s="364" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="373"/>
-      <c r="C5" s="373"/>
-      <c r="D5" s="373"/>
-      <c r="E5" s="373"/>
-      <c r="F5" s="373"/>
-      <c r="G5" s="373"/>
-      <c r="H5" s="374"/>
-      <c r="I5" s="378"/>
-      <c r="J5" s="379"/>
-      <c r="K5" s="379"/>
-      <c r="L5" s="379"/>
-      <c r="M5" s="380"/>
+      <c r="B5" s="365"/>
+      <c r="C5" s="365"/>
+      <c r="D5" s="365"/>
+      <c r="E5" s="365"/>
+      <c r="F5" s="365"/>
+      <c r="G5" s="365"/>
+      <c r="H5" s="366"/>
+      <c r="I5" s="370"/>
+      <c r="J5" s="371"/>
+      <c r="K5" s="371"/>
+      <c r="L5" s="371"/>
+      <c r="M5" s="372"/>
     </row>
     <row r="6" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="384" t="s">
+      <c r="A6" s="376" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="385"/>
-      <c r="C6" s="385"/>
-      <c r="D6" s="385"/>
-      <c r="E6" s="385"/>
-      <c r="F6" s="386" t="s">
+      <c r="B6" s="377"/>
+      <c r="C6" s="377"/>
+      <c r="D6" s="377"/>
+      <c r="E6" s="377"/>
+      <c r="F6" s="378" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="386"/>
-      <c r="H6" s="418" t="s">
+      <c r="G6" s="378"/>
+      <c r="H6" s="410" t="s">
         <v>80</v>
       </c>
-      <c r="I6" s="381"/>
-      <c r="J6" s="382"/>
-      <c r="K6" s="382"/>
-      <c r="L6" s="382"/>
-      <c r="M6" s="383"/>
+      <c r="I6" s="373"/>
+      <c r="J6" s="374"/>
+      <c r="K6" s="374"/>
+      <c r="L6" s="374"/>
+      <c r="M6" s="375"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="360" t="s">
+      <c r="A7" s="352" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="361"/>
-      <c r="C7" s="361"/>
-      <c r="D7" s="361"/>
-      <c r="E7" s="361"/>
-      <c r="F7" s="361"/>
-      <c r="G7" s="361"/>
-      <c r="H7" s="362"/>
-      <c r="I7" s="51" t="s">
+      <c r="B7" s="353"/>
+      <c r="C7" s="353"/>
+      <c r="D7" s="353"/>
+      <c r="E7" s="353"/>
+      <c r="F7" s="353"/>
+      <c r="G7" s="353"/>
+      <c r="H7" s="354"/>
+      <c r="I7" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="J7" s="52"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="52"/>
-      <c r="M7" s="54"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="50"/>
+      <c r="M7" s="52"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="375" t="s">
+      <c r="A8" s="367" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="376"/>
-      <c r="C8" s="376"/>
-      <c r="D8" s="376"/>
-      <c r="E8" s="256" t="s">
+      <c r="B8" s="368"/>
+      <c r="C8" s="368"/>
+      <c r="D8" s="368"/>
+      <c r="E8" s="248" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="256"/>
-      <c r="G8" s="256"/>
-      <c r="H8" s="257"/>
-      <c r="I8" s="375" t="s">
+      <c r="F8" s="248"/>
+      <c r="G8" s="248"/>
+      <c r="H8" s="249"/>
+      <c r="I8" s="367" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="376"/>
-      <c r="K8" s="376"/>
-      <c r="L8" s="376"/>
-      <c r="M8" s="377"/>
+      <c r="J8" s="368"/>
+      <c r="K8" s="368"/>
+      <c r="L8" s="368"/>
+      <c r="M8" s="369"/>
     </row>
     <row r="9" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="375" t="s">
+      <c r="A9" s="367" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="376"/>
-      <c r="C9" s="376"/>
-      <c r="D9" s="376"/>
-      <c r="E9" s="376"/>
-      <c r="F9" s="376"/>
-      <c r="G9" s="376"/>
-      <c r="H9" s="377"/>
-      <c r="I9" s="55" t="s">
+      <c r="B9" s="368"/>
+      <c r="C9" s="368"/>
+      <c r="D9" s="368"/>
+      <c r="E9" s="368"/>
+      <c r="F9" s="368"/>
+      <c r="G9" s="368"/>
+      <c r="H9" s="369"/>
+      <c r="I9" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="J9" s="56"/>
-      <c r="K9" s="56"/>
-      <c r="L9" s="56"/>
-      <c r="M9" s="50"/>
+      <c r="J9" s="54"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="54"/>
+      <c r="M9" s="48"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="375" t="s">
+      <c r="A10" s="367" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="376"/>
-      <c r="C10" s="376"/>
-      <c r="D10" s="376"/>
-      <c r="E10" s="376"/>
-      <c r="F10" s="376"/>
-      <c r="G10" s="376"/>
-      <c r="H10" s="377"/>
-      <c r="I10" s="57" t="s">
+      <c r="B10" s="368"/>
+      <c r="C10" s="368"/>
+      <c r="D10" s="368"/>
+      <c r="E10" s="368"/>
+      <c r="F10" s="368"/>
+      <c r="G10" s="368"/>
+      <c r="H10" s="369"/>
+      <c r="I10" s="55" t="s">
         <v>75</v>
       </c>
-      <c r="J10" s="58"/>
-      <c r="K10" s="58"/>
-      <c r="L10" s="58"/>
-      <c r="M10" s="59"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="56"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="57"/>
     </row>
     <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="357" t="s">
+      <c r="A11" s="349" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="358"/>
-      <c r="C11" s="358"/>
-      <c r="D11" s="358"/>
-      <c r="E11" s="358"/>
-      <c r="F11" s="359" t="s">
+      <c r="B11" s="350"/>
+      <c r="C11" s="350"/>
+      <c r="D11" s="350"/>
+      <c r="E11" s="350"/>
+      <c r="F11" s="351" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="359"/>
-      <c r="H11" s="418" t="s">
+      <c r="G11" s="351"/>
+      <c r="H11" s="410" t="s">
         <v>80</v>
       </c>
-      <c r="I11" s="60" t="s">
+      <c r="I11" s="58" t="s">
         <v>76</v>
       </c>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
-      <c r="L11" s="61"/>
-      <c r="M11" s="62"/>
+      <c r="J11" s="59"/>
+      <c r="K11" s="59"/>
+      <c r="L11" s="59"/>
+      <c r="M11" s="60"/>
     </row>
     <row r="12" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="360" t="s">
+      <c r="A12" s="352" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="361"/>
-      <c r="C12" s="361"/>
-      <c r="D12" s="361"/>
-      <c r="E12" s="361"/>
-      <c r="F12" s="361"/>
-      <c r="G12" s="361"/>
-      <c r="H12" s="362"/>
-      <c r="I12" s="363"/>
-      <c r="J12" s="364"/>
-      <c r="K12" s="364"/>
-      <c r="L12" s="364"/>
-      <c r="M12" s="365"/>
+      <c r="B12" s="353"/>
+      <c r="C12" s="353"/>
+      <c r="D12" s="353"/>
+      <c r="E12" s="353"/>
+      <c r="F12" s="353"/>
+      <c r="G12" s="353"/>
+      <c r="H12" s="354"/>
+      <c r="I12" s="355"/>
+      <c r="J12" s="356"/>
+      <c r="K12" s="356"/>
+      <c r="L12" s="356"/>
+      <c r="M12" s="357"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="369" t="s">
+      <c r="A13" s="361" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="370"/>
-      <c r="C13" s="370"/>
-      <c r="D13" s="370"/>
-      <c r="E13" s="370"/>
-      <c r="F13" s="370"/>
-      <c r="G13" s="370"/>
-      <c r="H13" s="371"/>
-      <c r="I13" s="363"/>
-      <c r="J13" s="364"/>
-      <c r="K13" s="364"/>
-      <c r="L13" s="364"/>
-      <c r="M13" s="365"/>
+      <c r="B13" s="362"/>
+      <c r="C13" s="362"/>
+      <c r="D13" s="362"/>
+      <c r="E13" s="362"/>
+      <c r="F13" s="362"/>
+      <c r="G13" s="362"/>
+      <c r="H13" s="363"/>
+      <c r="I13" s="355"/>
+      <c r="J13" s="356"/>
+      <c r="K13" s="356"/>
+      <c r="L13" s="356"/>
+      <c r="M13" s="357"/>
     </row>
     <row r="14" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="372" t="s">
+      <c r="A14" s="364" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="373"/>
-      <c r="C14" s="373"/>
-      <c r="D14" s="373"/>
-      <c r="E14" s="373"/>
-      <c r="F14" s="373"/>
-      <c r="G14" s="373"/>
-      <c r="H14" s="374"/>
-      <c r="I14" s="366"/>
-      <c r="J14" s="367"/>
-      <c r="K14" s="367"/>
-      <c r="L14" s="367"/>
-      <c r="M14" s="368"/>
+      <c r="B14" s="365"/>
+      <c r="C14" s="365"/>
+      <c r="D14" s="365"/>
+      <c r="E14" s="365"/>
+      <c r="F14" s="365"/>
+      <c r="G14" s="365"/>
+      <c r="H14" s="366"/>
+      <c r="I14" s="358"/>
+      <c r="J14" s="359"/>
+      <c r="K14" s="359"/>
+      <c r="L14" s="359"/>
+      <c r="M14" s="360"/>
     </row>
     <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="345" t="s">
+      <c r="A15" s="337" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="346"/>
-      <c r="C15" s="346"/>
-      <c r="D15" s="346"/>
-      <c r="E15" s="346"/>
-      <c r="F15" s="346"/>
-      <c r="G15" s="346"/>
-      <c r="H15" s="346"/>
-      <c r="I15" s="347" t="s">
+      <c r="B15" s="338"/>
+      <c r="C15" s="338"/>
+      <c r="D15" s="338"/>
+      <c r="E15" s="338"/>
+      <c r="F15" s="338"/>
+      <c r="G15" s="338"/>
+      <c r="H15" s="338"/>
+      <c r="I15" s="339" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="348"/>
-      <c r="K15" s="348"/>
-      <c r="L15" s="348"/>
-      <c r="M15" s="349"/>
+      <c r="J15" s="340"/>
+      <c r="K15" s="340"/>
+      <c r="L15" s="340"/>
+      <c r="M15" s="341"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="63" t="s">
+      <c r="A16" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="64"/>
-      <c r="D16" s="64"/>
-      <c r="E16" s="64"/>
-      <c r="F16" s="248"/>
-      <c r="G16" s="248"/>
-      <c r="H16" s="249"/>
-      <c r="I16" s="350" t="s">
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="240"/>
+      <c r="G16" s="240"/>
+      <c r="H16" s="241"/>
+      <c r="I16" s="342" t="s">
         <v>78</v>
       </c>
-      <c r="J16" s="351"/>
-      <c r="K16" s="351"/>
-      <c r="L16" s="351"/>
-      <c r="M16" s="352"/>
+      <c r="J16" s="343"/>
+      <c r="K16" s="343"/>
+      <c r="L16" s="343"/>
+      <c r="M16" s="344"/>
     </row>
     <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="65"/>
-      <c r="B17" s="66"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="66"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="66"/>
-      <c r="G17" s="66"/>
-      <c r="H17" s="67"/>
-      <c r="I17" s="416" t="s">
+      <c r="A17" s="63"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="64"/>
+      <c r="G17" s="64"/>
+      <c r="H17" s="65"/>
+      <c r="I17" s="408" t="s">
         <v>80</v>
       </c>
-      <c r="J17" s="417"/>
-      <c r="K17" s="353" t="s">
+      <c r="J17" s="409"/>
+      <c r="K17" s="345" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="353"/>
-      <c r="M17" s="354"/>
+      <c r="L17" s="345"/>
+      <c r="M17" s="346"/>
     </row>
     <row r="18" spans="1:13" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="65"/>
-      <c r="B18" s="66"/>
-      <c r="C18" s="66"/>
-      <c r="D18" s="66"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="66"/>
-      <c r="G18" s="66"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="245" t="s">
+      <c r="A18" s="63"/>
+      <c r="B18" s="64"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="64"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="237" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="246"/>
-      <c r="K18" s="355"/>
-      <c r="L18" s="355"/>
-      <c r="M18" s="356"/>
+      <c r="J18" s="238"/>
+      <c r="K18" s="347"/>
+      <c r="L18" s="347"/>
+      <c r="M18" s="348"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="320" t="s">
+      <c r="A19" s="312" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="321"/>
-      <c r="C19" s="321"/>
-      <c r="D19" s="321"/>
-      <c r="E19" s="321"/>
-      <c r="F19" s="321"/>
-      <c r="G19" s="321"/>
-      <c r="H19" s="321"/>
-      <c r="I19" s="321"/>
-      <c r="J19" s="321"/>
-      <c r="K19" s="321"/>
-      <c r="L19" s="321"/>
-      <c r="M19" s="322"/>
+      <c r="B19" s="313"/>
+      <c r="C19" s="313"/>
+      <c r="D19" s="313"/>
+      <c r="E19" s="313"/>
+      <c r="F19" s="313"/>
+      <c r="G19" s="313"/>
+      <c r="H19" s="313"/>
+      <c r="I19" s="313"/>
+      <c r="J19" s="313"/>
+      <c r="K19" s="313"/>
+      <c r="L19" s="313"/>
+      <c r="M19" s="314"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="333" t="s">
+      <c r="A20" s="325" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="334"/>
-      <c r="C20" s="334"/>
-      <c r="D20" s="334"/>
-      <c r="E20" s="334" t="s">
+      <c r="B20" s="326"/>
+      <c r="C20" s="326"/>
+      <c r="D20" s="326"/>
+      <c r="E20" s="326" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="334" t="s">
+      <c r="F20" s="326" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="334"/>
-      <c r="H20" s="335" t="s">
+      <c r="G20" s="326"/>
+      <c r="H20" s="327" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="336"/>
-      <c r="J20" s="337" t="s">
+      <c r="I20" s="328"/>
+      <c r="J20" s="329" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="338"/>
-      <c r="L20" s="338"/>
-      <c r="M20" s="339"/>
+      <c r="K20" s="330"/>
+      <c r="L20" s="330"/>
+      <c r="M20" s="331"/>
     </row>
     <row r="21" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="333"/>
-      <c r="B21" s="334"/>
-      <c r="C21" s="334"/>
-      <c r="D21" s="334"/>
-      <c r="E21" s="334"/>
-      <c r="F21" s="334"/>
-      <c r="G21" s="334"/>
-      <c r="H21" s="343" t="s">
+      <c r="A21" s="325"/>
+      <c r="B21" s="326"/>
+      <c r="C21" s="326"/>
+      <c r="D21" s="326"/>
+      <c r="E21" s="326"/>
+      <c r="F21" s="326"/>
+      <c r="G21" s="326"/>
+      <c r="H21" s="335" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="344"/>
-      <c r="J21" s="340"/>
-      <c r="K21" s="341"/>
-      <c r="L21" s="341"/>
-      <c r="M21" s="342"/>
+      <c r="I21" s="336"/>
+      <c r="J21" s="332"/>
+      <c r="K21" s="333"/>
+      <c r="L21" s="333"/>
+      <c r="M21" s="334"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="329"/>
-      <c r="B22" s="329"/>
-      <c r="C22" s="329"/>
-      <c r="D22" s="330"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="331"/>
-      <c r="G22" s="331"/>
-      <c r="H22" s="69" t="s">
+      <c r="A22" s="321"/>
+      <c r="B22" s="321"/>
+      <c r="C22" s="321"/>
+      <c r="D22" s="322"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="323"/>
+      <c r="G22" s="323"/>
+      <c r="H22" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="69" t="s">
+      <c r="I22" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="317"/>
-      <c r="K22" s="317"/>
-      <c r="L22" s="317"/>
-      <c r="M22" s="332"/>
+      <c r="J22" s="309"/>
+      <c r="K22" s="309"/>
+      <c r="L22" s="309"/>
+      <c r="M22" s="324"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="329"/>
-      <c r="B23" s="329"/>
-      <c r="C23" s="329"/>
-      <c r="D23" s="330"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="331"/>
-      <c r="G23" s="331"/>
-      <c r="H23" s="69" t="s">
+      <c r="A23" s="321"/>
+      <c r="B23" s="321"/>
+      <c r="C23" s="321"/>
+      <c r="D23" s="322"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="323"/>
+      <c r="G23" s="323"/>
+      <c r="H23" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="69" t="s">
+      <c r="I23" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J23" s="317"/>
-      <c r="K23" s="317"/>
-      <c r="L23" s="317"/>
-      <c r="M23" s="332"/>
+      <c r="J23" s="309"/>
+      <c r="K23" s="309"/>
+      <c r="L23" s="309"/>
+      <c r="M23" s="324"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="329"/>
-      <c r="B24" s="329"/>
-      <c r="C24" s="329"/>
-      <c r="D24" s="330"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="331"/>
-      <c r="G24" s="331"/>
-      <c r="H24" s="69" t="s">
+      <c r="A24" s="321"/>
+      <c r="B24" s="321"/>
+      <c r="C24" s="321"/>
+      <c r="D24" s="322"/>
+      <c r="E24" s="66"/>
+      <c r="F24" s="323"/>
+      <c r="G24" s="323"/>
+      <c r="H24" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I24" s="69" t="s">
+      <c r="I24" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J24" s="317"/>
-      <c r="K24" s="317"/>
-      <c r="L24" s="317"/>
-      <c r="M24" s="332"/>
+      <c r="J24" s="309"/>
+      <c r="K24" s="309"/>
+      <c r="L24" s="309"/>
+      <c r="M24" s="324"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="329"/>
-      <c r="B25" s="329"/>
-      <c r="C25" s="329"/>
-      <c r="D25" s="330"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="331"/>
-      <c r="G25" s="331"/>
-      <c r="H25" s="69" t="s">
+      <c r="A25" s="321"/>
+      <c r="B25" s="321"/>
+      <c r="C25" s="321"/>
+      <c r="D25" s="322"/>
+      <c r="E25" s="66"/>
+      <c r="F25" s="323"/>
+      <c r="G25" s="323"/>
+      <c r="H25" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I25" s="69" t="s">
+      <c r="I25" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J25" s="317"/>
-      <c r="K25" s="317"/>
-      <c r="L25" s="317"/>
-      <c r="M25" s="332"/>
+      <c r="J25" s="309"/>
+      <c r="K25" s="309"/>
+      <c r="L25" s="309"/>
+      <c r="M25" s="324"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="329"/>
-      <c r="B26" s="329"/>
-      <c r="C26" s="329"/>
-      <c r="D26" s="330"/>
-      <c r="E26" s="68"/>
-      <c r="F26" s="331"/>
-      <c r="G26" s="331"/>
-      <c r="H26" s="69" t="s">
+      <c r="A26" s="321"/>
+      <c r="B26" s="321"/>
+      <c r="C26" s="321"/>
+      <c r="D26" s="322"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="323"/>
+      <c r="G26" s="323"/>
+      <c r="H26" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I26" s="69" t="s">
+      <c r="I26" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J26" s="317"/>
-      <c r="K26" s="317"/>
-      <c r="L26" s="317"/>
-      <c r="M26" s="332"/>
+      <c r="J26" s="309"/>
+      <c r="K26" s="309"/>
+      <c r="L26" s="309"/>
+      <c r="M26" s="324"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="329"/>
-      <c r="B27" s="329"/>
-      <c r="C27" s="329"/>
-      <c r="D27" s="330"/>
-      <c r="E27" s="68"/>
-      <c r="F27" s="331"/>
-      <c r="G27" s="331"/>
-      <c r="H27" s="69" t="s">
+      <c r="A27" s="321"/>
+      <c r="B27" s="321"/>
+      <c r="C27" s="321"/>
+      <c r="D27" s="322"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="323"/>
+      <c r="G27" s="323"/>
+      <c r="H27" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I27" s="69" t="s">
+      <c r="I27" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="317"/>
-      <c r="K27" s="317"/>
-      <c r="L27" s="317"/>
-      <c r="M27" s="332"/>
+      <c r="J27" s="309"/>
+      <c r="K27" s="309"/>
+      <c r="L27" s="309"/>
+      <c r="M27" s="324"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="329"/>
-      <c r="B28" s="329"/>
-      <c r="C28" s="329"/>
-      <c r="D28" s="330"/>
-      <c r="E28" s="68"/>
-      <c r="F28" s="331"/>
-      <c r="G28" s="331"/>
-      <c r="H28" s="69" t="s">
+      <c r="A28" s="321"/>
+      <c r="B28" s="321"/>
+      <c r="C28" s="321"/>
+      <c r="D28" s="322"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="323"/>
+      <c r="G28" s="323"/>
+      <c r="H28" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I28" s="69" t="s">
+      <c r="I28" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J28" s="317"/>
-      <c r="K28" s="317"/>
-      <c r="L28" s="317"/>
-      <c r="M28" s="332"/>
+      <c r="J28" s="309"/>
+      <c r="K28" s="309"/>
+      <c r="L28" s="309"/>
+      <c r="M28" s="324"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="329"/>
-      <c r="B29" s="329"/>
-      <c r="C29" s="329"/>
-      <c r="D29" s="330"/>
-      <c r="E29" s="68"/>
-      <c r="F29" s="331"/>
-      <c r="G29" s="331"/>
-      <c r="H29" s="69" t="s">
+      <c r="A29" s="321"/>
+      <c r="B29" s="321"/>
+      <c r="C29" s="321"/>
+      <c r="D29" s="322"/>
+      <c r="E29" s="66"/>
+      <c r="F29" s="323"/>
+      <c r="G29" s="323"/>
+      <c r="H29" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I29" s="69" t="s">
+      <c r="I29" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J29" s="317"/>
-      <c r="K29" s="317"/>
-      <c r="L29" s="317"/>
-      <c r="M29" s="332"/>
+      <c r="J29" s="309"/>
+      <c r="K29" s="309"/>
+      <c r="L29" s="309"/>
+      <c r="M29" s="324"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="314" t="s">
+      <c r="A30" s="306" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="315"/>
-      <c r="C30" s="315"/>
-      <c r="D30" s="315"/>
+      <c r="B30" s="307"/>
+      <c r="C30" s="307"/>
+      <c r="D30" s="307"/>
       <c r="E30" s="12"/>
-      <c r="F30" s="316"/>
-      <c r="G30" s="317"/>
+      <c r="F30" s="308"/>
+      <c r="G30" s="309"/>
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
-      <c r="J30" s="318"/>
-      <c r="K30" s="318"/>
-      <c r="L30" s="318"/>
-      <c r="M30" s="319"/>
+      <c r="J30" s="310"/>
+      <c r="K30" s="310"/>
+      <c r="L30" s="310"/>
+      <c r="M30" s="311"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="320" t="s">
+      <c r="A31" s="312" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="321"/>
-      <c r="C31" s="321"/>
-      <c r="D31" s="321"/>
-      <c r="E31" s="321"/>
-      <c r="F31" s="321"/>
-      <c r="G31" s="321"/>
-      <c r="H31" s="321"/>
-      <c r="I31" s="321"/>
-      <c r="J31" s="321"/>
-      <c r="K31" s="321"/>
-      <c r="L31" s="321"/>
-      <c r="M31" s="322"/>
+      <c r="B31" s="313"/>
+      <c r="C31" s="313"/>
+      <c r="D31" s="313"/>
+      <c r="E31" s="313"/>
+      <c r="F31" s="313"/>
+      <c r="G31" s="313"/>
+      <c r="H31" s="313"/>
+      <c r="I31" s="313"/>
+      <c r="J31" s="313"/>
+      <c r="K31" s="313"/>
+      <c r="L31" s="313"/>
+      <c r="M31" s="314"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="323" t="s">
+      <c r="A32" s="315" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="324"/>
-      <c r="C32" s="324" t="s">
+      <c r="B32" s="316"/>
+      <c r="C32" s="316" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="324"/>
-      <c r="E32" s="325" t="s">
+      <c r="D32" s="316"/>
+      <c r="E32" s="317" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="326" t="s">
+      <c r="F32" s="318" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="327" t="s">
+      <c r="G32" s="319" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="327"/>
-      <c r="I32" s="327"/>
-      <c r="J32" s="327"/>
-      <c r="K32" s="327"/>
-      <c r="L32" s="324" t="s">
+      <c r="H32" s="319"/>
+      <c r="I32" s="319"/>
+      <c r="J32" s="319"/>
+      <c r="K32" s="319"/>
+      <c r="L32" s="316" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="328"/>
+      <c r="M32" s="320"/>
     </row>
     <row r="33" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="14" t="s">
@@ -4037,15 +4027,15 @@
       <c r="D33" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="325"/>
-      <c r="F33" s="326"/>
-      <c r="G33" s="313" t="s">
+      <c r="E33" s="317"/>
+      <c r="F33" s="318"/>
+      <c r="G33" s="305" t="s">
         <v>50</v>
       </c>
-      <c r="H33" s="313"/>
-      <c r="I33" s="313"/>
-      <c r="J33" s="313"/>
-      <c r="K33" s="313"/>
+      <c r="H33" s="305"/>
+      <c r="I33" s="305"/>
+      <c r="J33" s="305"/>
+      <c r="K33" s="305"/>
       <c r="L33" s="16" t="s">
         <v>14</v>
       </c>
@@ -4054,457 +4044,457 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="72"/>
-      <c r="B34" s="69"/>
-      <c r="C34" s="70"/>
-      <c r="D34" s="69" t="s">
+      <c r="A34" s="70"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="68"/>
+      <c r="D34" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="E34" s="70"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="286"/>
-      <c r="H34" s="287"/>
-      <c r="I34" s="287"/>
-      <c r="J34" s="287"/>
-      <c r="K34" s="288"/>
+      <c r="E34" s="68"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="278"/>
+      <c r="H34" s="279"/>
+      <c r="I34" s="279"/>
+      <c r="J34" s="279"/>
+      <c r="K34" s="280"/>
       <c r="L34" s="18"/>
       <c r="M34" s="19"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" s="72"/>
-      <c r="B35" s="69"/>
-      <c r="C35" s="69"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
+      <c r="A35" s="70"/>
+      <c r="B35" s="67"/>
+      <c r="C35" s="67"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
       <c r="F35" s="18"/>
-      <c r="G35" s="286"/>
-      <c r="H35" s="287"/>
-      <c r="I35" s="287"/>
-      <c r="J35" s="287"/>
-      <c r="K35" s="288"/>
+      <c r="G35" s="278"/>
+      <c r="H35" s="279"/>
+      <c r="I35" s="279"/>
+      <c r="J35" s="279"/>
+      <c r="K35" s="280"/>
       <c r="L35" s="18"/>
       <c r="M35" s="19"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" s="72"/>
-      <c r="B36" s="69"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="69"/>
-      <c r="E36" s="69"/>
+      <c r="A36" s="70"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="67"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
       <c r="F36" s="18"/>
-      <c r="G36" s="286"/>
-      <c r="H36" s="287"/>
-      <c r="I36" s="287"/>
-      <c r="J36" s="287"/>
-      <c r="K36" s="288"/>
+      <c r="G36" s="278"/>
+      <c r="H36" s="279"/>
+      <c r="I36" s="279"/>
+      <c r="J36" s="279"/>
+      <c r="K36" s="280"/>
       <c r="L36" s="18"/>
       <c r="M36" s="19"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A37" s="72"/>
-      <c r="B37" s="69"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
+      <c r="A37" s="70"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="67"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
       <c r="F37" s="18"/>
-      <c r="G37" s="286"/>
-      <c r="H37" s="287"/>
-      <c r="I37" s="287"/>
-      <c r="J37" s="287"/>
-      <c r="K37" s="288"/>
+      <c r="G37" s="278"/>
+      <c r="H37" s="279"/>
+      <c r="I37" s="279"/>
+      <c r="J37" s="279"/>
+      <c r="K37" s="280"/>
       <c r="L37" s="18"/>
       <c r="M37" s="19"/>
-      <c r="Q37" s="311"/>
-      <c r="R37" s="311"/>
+      <c r="Q37" s="303"/>
+      <c r="R37" s="303"/>
       <c r="S37" s="20"/>
-      <c r="T37" s="310"/>
-      <c r="U37" s="310"/>
-      <c r="V37" s="310"/>
+      <c r="T37" s="302"/>
+      <c r="U37" s="302"/>
+      <c r="V37" s="302"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A38" s="72"/>
-      <c r="B38" s="69"/>
-      <c r="C38" s="69"/>
-      <c r="D38" s="69"/>
-      <c r="E38" s="69"/>
+      <c r="A38" s="70"/>
+      <c r="B38" s="67"/>
+      <c r="C38" s="67"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
       <c r="F38" s="18"/>
-      <c r="G38" s="286"/>
-      <c r="H38" s="287"/>
-      <c r="I38" s="287"/>
-      <c r="J38" s="287"/>
-      <c r="K38" s="288"/>
+      <c r="G38" s="278"/>
+      <c r="H38" s="279"/>
+      <c r="I38" s="279"/>
+      <c r="J38" s="279"/>
+      <c r="K38" s="280"/>
       <c r="L38" s="18"/>
       <c r="M38" s="22"/>
-      <c r="Q38" s="311"/>
-      <c r="R38" s="311"/>
+      <c r="Q38" s="303"/>
+      <c r="R38" s="303"/>
       <c r="S38" s="20"/>
-      <c r="T38" s="310"/>
-      <c r="U38" s="310"/>
-      <c r="V38" s="310"/>
+      <c r="T38" s="302"/>
+      <c r="U38" s="302"/>
+      <c r="V38" s="302"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A39" s="72"/>
-      <c r="B39" s="69"/>
-      <c r="C39" s="69"/>
-      <c r="D39" s="69"/>
-      <c r="E39" s="69"/>
+      <c r="A39" s="70"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="67"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
       <c r="F39" s="18"/>
-      <c r="G39" s="286"/>
-      <c r="H39" s="287"/>
-      <c r="I39" s="287"/>
-      <c r="J39" s="287"/>
-      <c r="K39" s="288"/>
+      <c r="G39" s="278"/>
+      <c r="H39" s="279"/>
+      <c r="I39" s="279"/>
+      <c r="J39" s="279"/>
+      <c r="K39" s="280"/>
       <c r="L39" s="18"/>
       <c r="M39" s="22"/>
       <c r="Q39" s="23"/>
       <c r="R39" s="23"/>
-      <c r="S39" s="312"/>
-      <c r="T39" s="310"/>
-      <c r="U39" s="310"/>
-      <c r="V39" s="310"/>
+      <c r="S39" s="304"/>
+      <c r="T39" s="302"/>
+      <c r="U39" s="302"/>
+      <c r="V39" s="302"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A40" s="72"/>
-      <c r="B40" s="69"/>
-      <c r="C40" s="69"/>
-      <c r="D40" s="69"/>
-      <c r="E40" s="69"/>
+      <c r="A40" s="70"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="67"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
       <c r="F40" s="18"/>
-      <c r="G40" s="286"/>
-      <c r="H40" s="287"/>
-      <c r="I40" s="287"/>
-      <c r="J40" s="287"/>
-      <c r="K40" s="288"/>
+      <c r="G40" s="278"/>
+      <c r="H40" s="279"/>
+      <c r="I40" s="279"/>
+      <c r="J40" s="279"/>
+      <c r="K40" s="280"/>
       <c r="L40" s="18"/>
       <c r="M40" s="19"/>
       <c r="Q40" s="23"/>
       <c r="R40" s="23"/>
-      <c r="S40" s="312"/>
-      <c r="T40" s="310"/>
-      <c r="U40" s="310"/>
-      <c r="V40" s="310"/>
+      <c r="S40" s="304"/>
+      <c r="T40" s="302"/>
+      <c r="U40" s="302"/>
+      <c r="V40" s="302"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A41" s="72"/>
-      <c r="B41" s="69"/>
-      <c r="C41" s="69"/>
-      <c r="D41" s="69"/>
-      <c r="E41" s="69"/>
+      <c r="A41" s="70"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="67"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
       <c r="F41" s="18"/>
-      <c r="G41" s="286"/>
-      <c r="H41" s="287"/>
-      <c r="I41" s="287"/>
-      <c r="J41" s="287"/>
-      <c r="K41" s="288"/>
+      <c r="G41" s="278"/>
+      <c r="H41" s="279"/>
+      <c r="I41" s="279"/>
+      <c r="J41" s="279"/>
+      <c r="K41" s="280"/>
       <c r="L41" s="18"/>
       <c r="M41" s="19"/>
     </row>
     <row r="42" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="73"/>
-      <c r="B42" s="74"/>
-      <c r="C42" s="75"/>
-      <c r="D42" s="74"/>
-      <c r="E42" s="75"/>
+      <c r="A42" s="71"/>
+      <c r="B42" s="72"/>
+      <c r="C42" s="73"/>
+      <c r="D42" s="72"/>
+      <c r="E42" s="73"/>
       <c r="F42" s="24"/>
-      <c r="G42" s="289" t="s">
+      <c r="G42" s="281" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="290"/>
-      <c r="I42" s="290"/>
-      <c r="J42" s="290"/>
-      <c r="K42" s="291"/>
+      <c r="H42" s="282"/>
+      <c r="I42" s="282"/>
+      <c r="J42" s="282"/>
+      <c r="K42" s="283"/>
       <c r="L42" s="24"/>
       <c r="M42" s="25"/>
     </row>
     <row r="43" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="266" t="s">
+      <c r="A43" s="258" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="267"/>
-      <c r="C43" s="267"/>
-      <c r="D43" s="267"/>
-      <c r="E43" s="267"/>
-      <c r="F43" s="267"/>
-      <c r="G43" s="267"/>
-      <c r="H43" s="268"/>
-      <c r="I43" s="292" t="s">
+      <c r="B43" s="259"/>
+      <c r="C43" s="259"/>
+      <c r="D43" s="259"/>
+      <c r="E43" s="259"/>
+      <c r="F43" s="259"/>
+      <c r="G43" s="259"/>
+      <c r="H43" s="260"/>
+      <c r="I43" s="284" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="293"/>
-      <c r="K43" s="293"/>
-      <c r="L43" s="293"/>
-      <c r="M43" s="294"/>
+      <c r="J43" s="285"/>
+      <c r="K43" s="285"/>
+      <c r="L43" s="285"/>
+      <c r="M43" s="286"/>
     </row>
     <row r="44" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="269"/>
-      <c r="B44" s="270"/>
-      <c r="C44" s="270"/>
-      <c r="D44" s="270"/>
-      <c r="E44" s="270"/>
-      <c r="F44" s="270"/>
-      <c r="G44" s="270"/>
-      <c r="H44" s="271"/>
-      <c r="I44" s="295"/>
-      <c r="J44" s="296"/>
-      <c r="K44" s="296"/>
-      <c r="L44" s="296"/>
-      <c r="M44" s="297"/>
+      <c r="A44" s="261"/>
+      <c r="B44" s="262"/>
+      <c r="C44" s="262"/>
+      <c r="D44" s="262"/>
+      <c r="E44" s="262"/>
+      <c r="F44" s="262"/>
+      <c r="G44" s="262"/>
+      <c r="H44" s="263"/>
+      <c r="I44" s="287"/>
+      <c r="J44" s="288"/>
+      <c r="K44" s="288"/>
+      <c r="L44" s="288"/>
+      <c r="M44" s="289"/>
     </row>
     <row r="45" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="298" t="s">
+      <c r="A45" s="290" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="299"/>
-      <c r="C45" s="299"/>
-      <c r="D45" s="299"/>
-      <c r="E45" s="299"/>
-      <c r="F45" s="299"/>
-      <c r="G45" s="299"/>
-      <c r="H45" s="300"/>
-      <c r="I45" s="301" t="s">
+      <c r="B45" s="291"/>
+      <c r="C45" s="291"/>
+      <c r="D45" s="291"/>
+      <c r="E45" s="291"/>
+      <c r="F45" s="291"/>
+      <c r="G45" s="291"/>
+      <c r="H45" s="292"/>
+      <c r="I45" s="293" t="s">
         <v>83</v>
       </c>
-      <c r="J45" s="302"/>
-      <c r="K45" s="302"/>
-      <c r="L45" s="302"/>
-      <c r="M45" s="303"/>
+      <c r="J45" s="294"/>
+      <c r="K45" s="294"/>
+      <c r="L45" s="294"/>
+      <c r="M45" s="295"/>
     </row>
     <row r="46" spans="1:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="298" t="s">
+      <c r="A46" s="290" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="299"/>
-      <c r="C46" s="299"/>
-      <c r="D46" s="299"/>
-      <c r="E46" s="299"/>
-      <c r="F46" s="299"/>
-      <c r="G46" s="299"/>
-      <c r="H46" s="300"/>
-      <c r="I46" s="301"/>
-      <c r="J46" s="302"/>
-      <c r="K46" s="302"/>
-      <c r="L46" s="302"/>
-      <c r="M46" s="303"/>
+      <c r="B46" s="291"/>
+      <c r="C46" s="291"/>
+      <c r="D46" s="291"/>
+      <c r="E46" s="291"/>
+      <c r="F46" s="291"/>
+      <c r="G46" s="291"/>
+      <c r="H46" s="292"/>
+      <c r="I46" s="293"/>
+      <c r="J46" s="294"/>
+      <c r="K46" s="294"/>
+      <c r="L46" s="294"/>
+      <c r="M46" s="295"/>
     </row>
     <row r="47" spans="1:22" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="304"/>
-      <c r="B47" s="305"/>
-      <c r="C47" s="305"/>
-      <c r="D47" s="305"/>
-      <c r="E47" s="305"/>
-      <c r="F47" s="305"/>
-      <c r="G47" s="305"/>
-      <c r="H47" s="306"/>
-      <c r="I47" s="307" t="s">
+      <c r="A47" s="296"/>
+      <c r="B47" s="297"/>
+      <c r="C47" s="297"/>
+      <c r="D47" s="297"/>
+      <c r="E47" s="297"/>
+      <c r="F47" s="297"/>
+      <c r="G47" s="297"/>
+      <c r="H47" s="298"/>
+      <c r="I47" s="299" t="s">
         <v>84</v>
       </c>
-      <c r="J47" s="308"/>
-      <c r="K47" s="308"/>
-      <c r="L47" s="308"/>
-      <c r="M47" s="309"/>
+      <c r="J47" s="300"/>
+      <c r="K47" s="300"/>
+      <c r="L47" s="300"/>
+      <c r="M47" s="301"/>
     </row>
     <row r="48" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="263" t="s">
+      <c r="A48" s="255" t="s">
         <v>36</v>
       </c>
-      <c r="B48" s="264"/>
-      <c r="C48" s="264"/>
-      <c r="D48" s="264"/>
-      <c r="E48" s="264"/>
-      <c r="F48" s="264"/>
-      <c r="G48" s="264"/>
-      <c r="H48" s="264"/>
-      <c r="I48" s="264"/>
-      <c r="J48" s="264"/>
-      <c r="K48" s="264"/>
-      <c r="L48" s="264"/>
-      <c r="M48" s="265"/>
+      <c r="B48" s="256"/>
+      <c r="C48" s="256"/>
+      <c r="D48" s="256"/>
+      <c r="E48" s="256"/>
+      <c r="F48" s="256"/>
+      <c r="G48" s="256"/>
+      <c r="H48" s="256"/>
+      <c r="I48" s="256"/>
+      <c r="J48" s="256"/>
+      <c r="K48" s="256"/>
+      <c r="L48" s="256"/>
+      <c r="M48" s="257"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="266" t="s">
+      <c r="A49" s="258" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="267"/>
-      <c r="C49" s="267"/>
-      <c r="D49" s="267"/>
-      <c r="E49" s="267"/>
-      <c r="F49" s="267"/>
-      <c r="G49" s="267"/>
-      <c r="H49" s="268"/>
-      <c r="I49" s="274" t="s">
+      <c r="B49" s="259"/>
+      <c r="C49" s="259"/>
+      <c r="D49" s="259"/>
+      <c r="E49" s="259"/>
+      <c r="F49" s="259"/>
+      <c r="G49" s="259"/>
+      <c r="H49" s="260"/>
+      <c r="I49" s="266" t="s">
         <v>38</v>
       </c>
-      <c r="J49" s="275"/>
-      <c r="K49" s="275"/>
-      <c r="L49" s="275"/>
-      <c r="M49" s="276"/>
+      <c r="J49" s="267"/>
+      <c r="K49" s="267"/>
+      <c r="L49" s="267"/>
+      <c r="M49" s="268"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="269"/>
-      <c r="B50" s="270"/>
-      <c r="C50" s="270"/>
-      <c r="D50" s="270"/>
-      <c r="E50" s="270"/>
-      <c r="F50" s="270"/>
-      <c r="G50" s="270"/>
-      <c r="H50" s="271"/>
-      <c r="I50" s="277"/>
-      <c r="J50" s="278"/>
-      <c r="K50" s="278"/>
-      <c r="L50" s="278"/>
-      <c r="M50" s="279"/>
+      <c r="A50" s="261"/>
+      <c r="B50" s="262"/>
+      <c r="C50" s="262"/>
+      <c r="D50" s="262"/>
+      <c r="E50" s="262"/>
+      <c r="F50" s="262"/>
+      <c r="G50" s="262"/>
+      <c r="H50" s="263"/>
+      <c r="I50" s="269"/>
+      <c r="J50" s="270"/>
+      <c r="K50" s="270"/>
+      <c r="L50" s="270"/>
+      <c r="M50" s="271"/>
     </row>
     <row r="51" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="272"/>
-      <c r="B51" s="273"/>
-      <c r="C51" s="273"/>
-      <c r="D51" s="273"/>
-      <c r="E51" s="270"/>
-      <c r="F51" s="270"/>
-      <c r="G51" s="270"/>
-      <c r="H51" s="271"/>
-      <c r="I51" s="280" t="s">
+      <c r="A51" s="264"/>
+      <c r="B51" s="265"/>
+      <c r="C51" s="265"/>
+      <c r="D51" s="265"/>
+      <c r="E51" s="262"/>
+      <c r="F51" s="262"/>
+      <c r="G51" s="262"/>
+      <c r="H51" s="263"/>
+      <c r="I51" s="272" t="s">
         <v>39</v>
       </c>
-      <c r="J51" s="281"/>
-      <c r="K51" s="282"/>
-      <c r="L51" s="282"/>
-      <c r="M51" s="283"/>
+      <c r="J51" s="273"/>
+      <c r="K51" s="274"/>
+      <c r="L51" s="274"/>
+      <c r="M51" s="275"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="263" t="s">
+      <c r="A52" s="255" t="s">
         <v>40</v>
       </c>
-      <c r="B52" s="264"/>
-      <c r="C52" s="264"/>
-      <c r="D52" s="264"/>
-      <c r="E52" s="76" t="s">
+      <c r="B52" s="256"/>
+      <c r="C52" s="256"/>
+      <c r="D52" s="256"/>
+      <c r="E52" s="74" t="s">
         <v>42</v>
       </c>
-      <c r="F52" s="77"/>
-      <c r="G52" s="284" t="s">
+      <c r="F52" s="75"/>
+      <c r="G52" s="276" t="s">
         <v>43</v>
       </c>
-      <c r="H52" s="284"/>
-      <c r="I52" s="284"/>
-      <c r="J52" s="285"/>
-      <c r="K52" s="264" t="s">
+      <c r="H52" s="276"/>
+      <c r="I52" s="276"/>
+      <c r="J52" s="277"/>
+      <c r="K52" s="256" t="s">
         <v>47</v>
       </c>
-      <c r="L52" s="264"/>
-      <c r="M52" s="265"/>
+      <c r="L52" s="256"/>
+      <c r="M52" s="257"/>
     </row>
     <row r="53" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="250" t="s">
+      <c r="A53" s="242" t="s">
         <v>41</v>
       </c>
-      <c r="B53" s="251"/>
-      <c r="C53" s="251"/>
-      <c r="D53" s="251"/>
-      <c r="E53" s="78"/>
-      <c r="F53" s="71"/>
-      <c r="G53" s="71"/>
-      <c r="H53" s="71"/>
-      <c r="I53" s="71"/>
-      <c r="J53" s="79"/>
-      <c r="K53" s="251" t="s">
+      <c r="B53" s="243"/>
+      <c r="C53" s="243"/>
+      <c r="D53" s="243"/>
+      <c r="E53" s="76"/>
+      <c r="F53" s="69"/>
+      <c r="G53" s="69"/>
+      <c r="H53" s="69"/>
+      <c r="I53" s="69"/>
+      <c r="J53" s="77"/>
+      <c r="K53" s="243" t="s">
         <v>49</v>
       </c>
-      <c r="L53" s="251"/>
-      <c r="M53" s="252"/>
+      <c r="L53" s="243"/>
+      <c r="M53" s="244"/>
     </row>
     <row r="54" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="250"/>
-      <c r="B54" s="251"/>
-      <c r="C54" s="251"/>
-      <c r="D54" s="251"/>
-      <c r="E54" s="253" t="s">
+      <c r="A54" s="242"/>
+      <c r="B54" s="243"/>
+      <c r="C54" s="243"/>
+      <c r="D54" s="243"/>
+      <c r="E54" s="245" t="s">
         <v>81</v>
       </c>
-      <c r="F54" s="254"/>
-      <c r="G54" s="414" t="s">
+      <c r="F54" s="246"/>
+      <c r="G54" s="406" t="s">
         <v>80</v>
       </c>
-      <c r="H54" s="243" t="s">
+      <c r="H54" s="235" t="s">
         <v>44</v>
       </c>
-      <c r="I54" s="243"/>
-      <c r="J54" s="244"/>
-      <c r="K54" s="251"/>
-      <c r="L54" s="251"/>
-      <c r="M54" s="252"/>
+      <c r="I54" s="235"/>
+      <c r="J54" s="236"/>
+      <c r="K54" s="243"/>
+      <c r="L54" s="243"/>
+      <c r="M54" s="244"/>
     </row>
     <row r="55" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="250"/>
-      <c r="B55" s="251"/>
-      <c r="C55" s="251"/>
-      <c r="D55" s="251"/>
-      <c r="E55" s="253" t="s">
+      <c r="A55" s="242"/>
+      <c r="B55" s="243"/>
+      <c r="C55" s="243"/>
+      <c r="D55" s="243"/>
+      <c r="E55" s="245" t="s">
         <v>82</v>
       </c>
-      <c r="F55" s="254"/>
-      <c r="G55" s="415" t="s">
+      <c r="F55" s="246"/>
+      <c r="G55" s="407" t="s">
         <v>80</v>
       </c>
-      <c r="H55" s="243" t="s">
+      <c r="H55" s="235" t="s">
         <v>45</v>
       </c>
-      <c r="I55" s="243"/>
-      <c r="J55" s="244"/>
-      <c r="K55" s="251"/>
-      <c r="L55" s="251"/>
-      <c r="M55" s="252"/>
+      <c r="I55" s="235"/>
+      <c r="J55" s="236"/>
+      <c r="K55" s="243"/>
+      <c r="L55" s="243"/>
+      <c r="M55" s="244"/>
     </row>
     <row r="56" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="255"/>
-      <c r="B56" s="256"/>
-      <c r="C56" s="256"/>
-      <c r="D56" s="257"/>
-      <c r="E56" s="253"/>
-      <c r="F56" s="254"/>
-      <c r="G56" s="415"/>
-      <c r="H56" s="243"/>
-      <c r="I56" s="243"/>
-      <c r="J56" s="244"/>
-      <c r="K56" s="261" t="s">
+      <c r="A56" s="247"/>
+      <c r="B56" s="248"/>
+      <c r="C56" s="248"/>
+      <c r="D56" s="249"/>
+      <c r="E56" s="245"/>
+      <c r="F56" s="246"/>
+      <c r="G56" s="407"/>
+      <c r="H56" s="235"/>
+      <c r="I56" s="235"/>
+      <c r="J56" s="236"/>
+      <c r="K56" s="253" t="s">
         <v>48</v>
       </c>
-      <c r="L56" s="261"/>
-      <c r="M56" s="262"/>
+      <c r="L56" s="253"/>
+      <c r="M56" s="254"/>
     </row>
     <row r="57" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="255"/>
-      <c r="B57" s="256"/>
-      <c r="C57" s="256"/>
-      <c r="D57" s="257"/>
-      <c r="E57" s="253"/>
-      <c r="F57" s="254"/>
-      <c r="G57" s="414" t="s">
+      <c r="A57" s="247"/>
+      <c r="B57" s="248"/>
+      <c r="C57" s="248"/>
+      <c r="D57" s="249"/>
+      <c r="E57" s="245"/>
+      <c r="F57" s="246"/>
+      <c r="G57" s="406" t="s">
         <v>80</v>
       </c>
-      <c r="H57" s="243" t="s">
+      <c r="H57" s="235" t="s">
         <v>46</v>
       </c>
-      <c r="I57" s="243"/>
-      <c r="J57" s="244"/>
-      <c r="K57" s="80"/>
-      <c r="L57" s="81"/>
-      <c r="M57" s="82"/>
+      <c r="I57" s="235"/>
+      <c r="J57" s="236"/>
+      <c r="K57" s="78"/>
+      <c r="L57" s="79"/>
+      <c r="M57" s="80"/>
     </row>
     <row r="58" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="258"/>
-      <c r="B58" s="259"/>
-      <c r="C58" s="259"/>
-      <c r="D58" s="260"/>
-      <c r="E58" s="245"/>
-      <c r="F58" s="246"/>
-      <c r="G58" s="246"/>
-      <c r="H58" s="246"/>
-      <c r="I58" s="246"/>
-      <c r="J58" s="247"/>
-      <c r="K58" s="83"/>
-      <c r="L58" s="84"/>
-      <c r="M58" s="85"/>
+      <c r="A58" s="250"/>
+      <c r="B58" s="251"/>
+      <c r="C58" s="251"/>
+      <c r="D58" s="252"/>
+      <c r="E58" s="237"/>
+      <c r="F58" s="238"/>
+      <c r="G58" s="238"/>
+      <c r="H58" s="238"/>
+      <c r="I58" s="238"/>
+      <c r="J58" s="239"/>
+      <c r="K58" s="81"/>
+      <c r="L58" s="82"/>
+      <c r="M58" s="83"/>
     </row>
     <row r="59" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="26"/>
@@ -5351,1012 +5341,1012 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="85" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="388" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="380" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="388"/>
-      <c r="E1" s="388"/>
-      <c r="F1" s="388"/>
-      <c r="G1" s="388"/>
-      <c r="H1" s="388"/>
-      <c r="I1" s="388"/>
-      <c r="J1" s="388"/>
-      <c r="K1" s="388"/>
-      <c r="L1" s="390" t="s">
+      <c r="D1" s="380"/>
+      <c r="E1" s="380"/>
+      <c r="F1" s="380"/>
+      <c r="G1" s="380"/>
+      <c r="H1" s="380"/>
+      <c r="I1" s="380"/>
+      <c r="J1" s="380"/>
+      <c r="K1" s="380"/>
+      <c r="L1" s="382" t="s">
         <v>59</v>
       </c>
-      <c r="M1" s="391"/>
+      <c r="M1" s="383"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="320" t="s">
+      <c r="A2" s="312" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="321"/>
-      <c r="C2" s="321"/>
-      <c r="D2" s="321"/>
-      <c r="E2" s="321"/>
-      <c r="F2" s="321"/>
-      <c r="G2" s="321"/>
-      <c r="H2" s="321"/>
-      <c r="I2" s="321"/>
-      <c r="J2" s="321"/>
-      <c r="K2" s="321"/>
-      <c r="L2" s="321"/>
-      <c r="M2" s="322"/>
+      <c r="B2" s="313"/>
+      <c r="C2" s="313"/>
+      <c r="D2" s="313"/>
+      <c r="E2" s="313"/>
+      <c r="F2" s="313"/>
+      <c r="G2" s="313"/>
+      <c r="H2" s="313"/>
+      <c r="I2" s="313"/>
+      <c r="J2" s="313"/>
+      <c r="K2" s="313"/>
+      <c r="L2" s="313"/>
+      <c r="M2" s="314"/>
     </row>
     <row r="3" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="333" t="s">
+      <c r="A3" s="325" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="334"/>
-      <c r="C3" s="334"/>
-      <c r="D3" s="334"/>
-      <c r="E3" s="334" t="s">
+      <c r="B3" s="326"/>
+      <c r="C3" s="326"/>
+      <c r="D3" s="326"/>
+      <c r="E3" s="326" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="334" t="s">
+      <c r="F3" s="326" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="334"/>
-      <c r="H3" s="335" t="s">
+      <c r="G3" s="326"/>
+      <c r="H3" s="327" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="336"/>
-      <c r="J3" s="337" t="s">
+      <c r="I3" s="328"/>
+      <c r="J3" s="329" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="338"/>
-      <c r="L3" s="338"/>
-      <c r="M3" s="339"/>
+      <c r="K3" s="330"/>
+      <c r="L3" s="330"/>
+      <c r="M3" s="331"/>
     </row>
     <row r="4" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="333"/>
-      <c r="B4" s="334"/>
-      <c r="C4" s="334"/>
-      <c r="D4" s="334"/>
-      <c r="E4" s="334"/>
-      <c r="F4" s="334"/>
-      <c r="G4" s="334"/>
-      <c r="H4" s="343" t="s">
+      <c r="A4" s="325"/>
+      <c r="B4" s="326"/>
+      <c r="C4" s="326"/>
+      <c r="D4" s="326"/>
+      <c r="E4" s="326"/>
+      <c r="F4" s="326"/>
+      <c r="G4" s="326"/>
+      <c r="H4" s="335" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="344"/>
-      <c r="J4" s="340"/>
-      <c r="K4" s="341"/>
-      <c r="L4" s="341"/>
-      <c r="M4" s="342"/>
+      <c r="I4" s="336"/>
+      <c r="J4" s="332"/>
+      <c r="K4" s="333"/>
+      <c r="L4" s="333"/>
+      <c r="M4" s="334"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="413"/>
-      <c r="B5" s="329"/>
-      <c r="C5" s="329"/>
-      <c r="D5" s="329"/>
+      <c r="A5" s="405"/>
+      <c r="B5" s="321"/>
+      <c r="C5" s="321"/>
+      <c r="D5" s="321"/>
       <c r="E5" s="9"/>
-      <c r="F5" s="187"/>
-      <c r="G5" s="191"/>
-      <c r="H5" s="69" t="s">
+      <c r="F5" s="179"/>
+      <c r="G5" s="183"/>
+      <c r="H5" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="69" t="s">
+      <c r="I5" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="317"/>
-      <c r="K5" s="317"/>
-      <c r="L5" s="317"/>
-      <c r="M5" s="332"/>
+      <c r="J5" s="309"/>
+      <c r="K5" s="309"/>
+      <c r="L5" s="309"/>
+      <c r="M5" s="324"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="413"/>
-      <c r="B6" s="329"/>
-      <c r="C6" s="329"/>
-      <c r="D6" s="329"/>
+      <c r="A6" s="405"/>
+      <c r="B6" s="321"/>
+      <c r="C6" s="321"/>
+      <c r="D6" s="321"/>
       <c r="E6" s="9"/>
-      <c r="F6" s="187"/>
-      <c r="G6" s="191"/>
-      <c r="H6" s="69" t="s">
+      <c r="F6" s="179"/>
+      <c r="G6" s="183"/>
+      <c r="H6" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="69" t="s">
+      <c r="I6" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="317"/>
-      <c r="K6" s="317"/>
-      <c r="L6" s="317"/>
-      <c r="M6" s="332"/>
+      <c r="J6" s="309"/>
+      <c r="K6" s="309"/>
+      <c r="L6" s="309"/>
+      <c r="M6" s="324"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="413"/>
-      <c r="B7" s="329"/>
-      <c r="C7" s="329"/>
-      <c r="D7" s="329"/>
+      <c r="A7" s="405"/>
+      <c r="B7" s="321"/>
+      <c r="C7" s="321"/>
+      <c r="D7" s="321"/>
       <c r="E7" s="9"/>
-      <c r="F7" s="187"/>
-      <c r="G7" s="191"/>
-      <c r="H7" s="69" t="s">
+      <c r="F7" s="179"/>
+      <c r="G7" s="183"/>
+      <c r="H7" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="69" t="s">
+      <c r="I7" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="317"/>
-      <c r="K7" s="317"/>
-      <c r="L7" s="317"/>
-      <c r="M7" s="332"/>
+      <c r="J7" s="309"/>
+      <c r="K7" s="309"/>
+      <c r="L7" s="309"/>
+      <c r="M7" s="324"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="413"/>
-      <c r="B8" s="329"/>
-      <c r="C8" s="329"/>
-      <c r="D8" s="329"/>
+      <c r="A8" s="405"/>
+      <c r="B8" s="321"/>
+      <c r="C8" s="321"/>
+      <c r="D8" s="321"/>
       <c r="E8" s="9"/>
-      <c r="F8" s="187"/>
-      <c r="G8" s="191"/>
-      <c r="H8" s="69" t="s">
+      <c r="F8" s="179"/>
+      <c r="G8" s="183"/>
+      <c r="H8" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I8" s="69" t="s">
+      <c r="I8" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="317"/>
-      <c r="K8" s="317"/>
-      <c r="L8" s="317"/>
-      <c r="M8" s="332"/>
+      <c r="J8" s="309"/>
+      <c r="K8" s="309"/>
+      <c r="L8" s="309"/>
+      <c r="M8" s="324"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="413"/>
-      <c r="B9" s="329"/>
-      <c r="C9" s="329"/>
-      <c r="D9" s="329"/>
+      <c r="A9" s="405"/>
+      <c r="B9" s="321"/>
+      <c r="C9" s="321"/>
+      <c r="D9" s="321"/>
       <c r="E9" s="9"/>
-      <c r="F9" s="187"/>
-      <c r="G9" s="191"/>
-      <c r="H9" s="69" t="s">
+      <c r="F9" s="179"/>
+      <c r="G9" s="183"/>
+      <c r="H9" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="69" t="s">
+      <c r="I9" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="317"/>
-      <c r="K9" s="317"/>
-      <c r="L9" s="317"/>
-      <c r="M9" s="332"/>
+      <c r="J9" s="309"/>
+      <c r="K9" s="309"/>
+      <c r="L9" s="309"/>
+      <c r="M9" s="324"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="413"/>
-      <c r="B10" s="329"/>
-      <c r="C10" s="329"/>
-      <c r="D10" s="329"/>
+      <c r="A10" s="405"/>
+      <c r="B10" s="321"/>
+      <c r="C10" s="321"/>
+      <c r="D10" s="321"/>
       <c r="E10" s="9"/>
-      <c r="F10" s="187"/>
-      <c r="G10" s="191"/>
-      <c r="H10" s="69" t="s">
+      <c r="F10" s="179"/>
+      <c r="G10" s="183"/>
+      <c r="H10" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="69" t="s">
+      <c r="I10" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="317"/>
-      <c r="K10" s="317"/>
-      <c r="L10" s="317"/>
-      <c r="M10" s="332"/>
+      <c r="J10" s="309"/>
+      <c r="K10" s="309"/>
+      <c r="L10" s="309"/>
+      <c r="M10" s="324"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="413"/>
-      <c r="B11" s="329"/>
-      <c r="C11" s="329"/>
-      <c r="D11" s="329"/>
+      <c r="A11" s="405"/>
+      <c r="B11" s="321"/>
+      <c r="C11" s="321"/>
+      <c r="D11" s="321"/>
       <c r="E11" s="9"/>
-      <c r="F11" s="187"/>
-      <c r="G11" s="191"/>
-      <c r="H11" s="69" t="s">
+      <c r="F11" s="179"/>
+      <c r="G11" s="183"/>
+      <c r="H11" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I11" s="69" t="s">
+      <c r="I11" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J11" s="317"/>
-      <c r="K11" s="317"/>
-      <c r="L11" s="317"/>
-      <c r="M11" s="332"/>
+      <c r="J11" s="309"/>
+      <c r="K11" s="309"/>
+      <c r="L11" s="309"/>
+      <c r="M11" s="324"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="413"/>
-      <c r="B12" s="329"/>
-      <c r="C12" s="329"/>
-      <c r="D12" s="329"/>
+      <c r="A12" s="405"/>
+      <c r="B12" s="321"/>
+      <c r="C12" s="321"/>
+      <c r="D12" s="321"/>
       <c r="E12" s="9"/>
-      <c r="F12" s="187"/>
-      <c r="G12" s="191"/>
-      <c r="H12" s="69" t="s">
+      <c r="F12" s="179"/>
+      <c r="G12" s="183"/>
+      <c r="H12" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I12" s="69" t="s">
+      <c r="I12" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J12" s="317"/>
-      <c r="K12" s="317"/>
-      <c r="L12" s="317"/>
-      <c r="M12" s="332"/>
+      <c r="J12" s="309"/>
+      <c r="K12" s="309"/>
+      <c r="L12" s="309"/>
+      <c r="M12" s="324"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="413"/>
-      <c r="B13" s="329"/>
-      <c r="C13" s="329"/>
-      <c r="D13" s="329"/>
+      <c r="A13" s="405"/>
+      <c r="B13" s="321"/>
+      <c r="C13" s="321"/>
+      <c r="D13" s="321"/>
       <c r="E13" s="9"/>
-      <c r="F13" s="187"/>
-      <c r="G13" s="191"/>
-      <c r="H13" s="69" t="s">
+      <c r="F13" s="179"/>
+      <c r="G13" s="183"/>
+      <c r="H13" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I13" s="69" t="s">
+      <c r="I13" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J13" s="317"/>
-      <c r="K13" s="317"/>
-      <c r="L13" s="317"/>
-      <c r="M13" s="332"/>
+      <c r="J13" s="309"/>
+      <c r="K13" s="309"/>
+      <c r="L13" s="309"/>
+      <c r="M13" s="324"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="413"/>
-      <c r="B14" s="329"/>
-      <c r="C14" s="329"/>
-      <c r="D14" s="329"/>
+      <c r="A14" s="405"/>
+      <c r="B14" s="321"/>
+      <c r="C14" s="321"/>
+      <c r="D14" s="321"/>
       <c r="E14" s="9"/>
-      <c r="F14" s="187"/>
-      <c r="G14" s="191"/>
-      <c r="H14" s="69" t="s">
+      <c r="F14" s="179"/>
+      <c r="G14" s="183"/>
+      <c r="H14" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I14" s="69" t="s">
+      <c r="I14" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J14" s="317"/>
-      <c r="K14" s="317"/>
-      <c r="L14" s="317"/>
-      <c r="M14" s="332"/>
+      <c r="J14" s="309"/>
+      <c r="K14" s="309"/>
+      <c r="L14" s="309"/>
+      <c r="M14" s="324"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="413"/>
-      <c r="B15" s="329"/>
-      <c r="C15" s="329"/>
-      <c r="D15" s="329"/>
+      <c r="A15" s="405"/>
+      <c r="B15" s="321"/>
+      <c r="C15" s="321"/>
+      <c r="D15" s="321"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="187"/>
-      <c r="G15" s="191"/>
-      <c r="H15" s="69" t="s">
+      <c r="F15" s="179"/>
+      <c r="G15" s="183"/>
+      <c r="H15" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="69" t="s">
+      <c r="I15" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J15" s="317"/>
-      <c r="K15" s="317"/>
-      <c r="L15" s="317"/>
-      <c r="M15" s="332"/>
+      <c r="J15" s="309"/>
+      <c r="K15" s="309"/>
+      <c r="L15" s="309"/>
+      <c r="M15" s="324"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="413"/>
-      <c r="B16" s="329"/>
-      <c r="C16" s="329"/>
-      <c r="D16" s="329"/>
+      <c r="A16" s="405"/>
+      <c r="B16" s="321"/>
+      <c r="C16" s="321"/>
+      <c r="D16" s="321"/>
       <c r="E16" s="9"/>
-      <c r="F16" s="187"/>
-      <c r="G16" s="191"/>
-      <c r="H16" s="69" t="s">
+      <c r="F16" s="179"/>
+      <c r="G16" s="183"/>
+      <c r="H16" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I16" s="69" t="s">
+      <c r="I16" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J16" s="317"/>
-      <c r="K16" s="317"/>
-      <c r="L16" s="317"/>
-      <c r="M16" s="332"/>
+      <c r="J16" s="309"/>
+      <c r="K16" s="309"/>
+      <c r="L16" s="309"/>
+      <c r="M16" s="324"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="413"/>
-      <c r="B17" s="329"/>
-      <c r="C17" s="329"/>
-      <c r="D17" s="329"/>
+      <c r="A17" s="405"/>
+      <c r="B17" s="321"/>
+      <c r="C17" s="321"/>
+      <c r="D17" s="321"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="187"/>
-      <c r="G17" s="191"/>
-      <c r="H17" s="69" t="s">
+      <c r="F17" s="179"/>
+      <c r="G17" s="183"/>
+      <c r="H17" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="69" t="s">
+      <c r="I17" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J17" s="317"/>
-      <c r="K17" s="317"/>
-      <c r="L17" s="317"/>
-      <c r="M17" s="332"/>
+      <c r="J17" s="309"/>
+      <c r="K17" s="309"/>
+      <c r="L17" s="309"/>
+      <c r="M17" s="324"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="413"/>
-      <c r="B18" s="329"/>
-      <c r="C18" s="329"/>
-      <c r="D18" s="329"/>
+      <c r="A18" s="405"/>
+      <c r="B18" s="321"/>
+      <c r="C18" s="321"/>
+      <c r="D18" s="321"/>
       <c r="E18" s="9"/>
-      <c r="F18" s="187"/>
-      <c r="G18" s="191"/>
-      <c r="H18" s="69" t="s">
+      <c r="F18" s="179"/>
+      <c r="G18" s="183"/>
+      <c r="H18" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I18" s="69" t="s">
+      <c r="I18" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J18" s="317"/>
-      <c r="K18" s="317"/>
-      <c r="L18" s="317"/>
-      <c r="M18" s="332"/>
+      <c r="J18" s="309"/>
+      <c r="K18" s="309"/>
+      <c r="L18" s="309"/>
+      <c r="M18" s="324"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="413"/>
-      <c r="B19" s="329"/>
-      <c r="C19" s="329"/>
-      <c r="D19" s="329"/>
+      <c r="A19" s="405"/>
+      <c r="B19" s="321"/>
+      <c r="C19" s="321"/>
+      <c r="D19" s="321"/>
       <c r="E19" s="9"/>
-      <c r="F19" s="187"/>
-      <c r="G19" s="191"/>
-      <c r="H19" s="69" t="s">
+      <c r="F19" s="179"/>
+      <c r="G19" s="183"/>
+      <c r="H19" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I19" s="69" t="s">
+      <c r="I19" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J19" s="317"/>
-      <c r="K19" s="317"/>
-      <c r="L19" s="317"/>
-      <c r="M19" s="332"/>
+      <c r="J19" s="309"/>
+      <c r="K19" s="309"/>
+      <c r="L19" s="309"/>
+      <c r="M19" s="324"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="413"/>
-      <c r="B20" s="329"/>
-      <c r="C20" s="329"/>
-      <c r="D20" s="329"/>
+      <c r="A20" s="405"/>
+      <c r="B20" s="321"/>
+      <c r="C20" s="321"/>
+      <c r="D20" s="321"/>
       <c r="E20" s="9"/>
-      <c r="F20" s="187"/>
-      <c r="G20" s="191"/>
-      <c r="H20" s="69" t="s">
+      <c r="F20" s="179"/>
+      <c r="G20" s="183"/>
+      <c r="H20" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I20" s="69" t="s">
+      <c r="I20" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J20" s="317"/>
-      <c r="K20" s="317"/>
-      <c r="L20" s="317"/>
-      <c r="M20" s="332"/>
+      <c r="J20" s="309"/>
+      <c r="K20" s="309"/>
+      <c r="L20" s="309"/>
+      <c r="M20" s="324"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="413"/>
-      <c r="B21" s="329"/>
-      <c r="C21" s="329"/>
-      <c r="D21" s="329"/>
+      <c r="A21" s="405"/>
+      <c r="B21" s="321"/>
+      <c r="C21" s="321"/>
+      <c r="D21" s="321"/>
       <c r="E21" s="9"/>
-      <c r="F21" s="187"/>
-      <c r="G21" s="191"/>
-      <c r="H21" s="69" t="s">
+      <c r="F21" s="179"/>
+      <c r="G21" s="183"/>
+      <c r="H21" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I21" s="69" t="s">
+      <c r="I21" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J21" s="317"/>
-      <c r="K21" s="317"/>
-      <c r="L21" s="317"/>
-      <c r="M21" s="332"/>
+      <c r="J21" s="309"/>
+      <c r="K21" s="309"/>
+      <c r="L21" s="309"/>
+      <c r="M21" s="324"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="413"/>
-      <c r="B22" s="329"/>
-      <c r="C22" s="329"/>
-      <c r="D22" s="329"/>
+      <c r="A22" s="405"/>
+      <c r="B22" s="321"/>
+      <c r="C22" s="321"/>
+      <c r="D22" s="321"/>
       <c r="E22" s="9"/>
-      <c r="F22" s="187"/>
-      <c r="G22" s="191"/>
-      <c r="H22" s="69" t="s">
+      <c r="F22" s="179"/>
+      <c r="G22" s="183"/>
+      <c r="H22" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="69" t="s">
+      <c r="I22" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="317"/>
-      <c r="K22" s="317"/>
-      <c r="L22" s="317"/>
-      <c r="M22" s="332"/>
+      <c r="J22" s="309"/>
+      <c r="K22" s="309"/>
+      <c r="L22" s="309"/>
+      <c r="M22" s="324"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="413"/>
-      <c r="B23" s="329"/>
-      <c r="C23" s="329"/>
-      <c r="D23" s="329"/>
+      <c r="A23" s="405"/>
+      <c r="B23" s="321"/>
+      <c r="C23" s="321"/>
+      <c r="D23" s="321"/>
       <c r="E23" s="9"/>
-      <c r="F23" s="187"/>
-      <c r="G23" s="191"/>
-      <c r="H23" s="69" t="s">
+      <c r="F23" s="179"/>
+      <c r="G23" s="183"/>
+      <c r="H23" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="69" t="s">
+      <c r="I23" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J23" s="317"/>
-      <c r="K23" s="317"/>
-      <c r="L23" s="317"/>
-      <c r="M23" s="332"/>
+      <c r="J23" s="309"/>
+      <c r="K23" s="309"/>
+      <c r="L23" s="309"/>
+      <c r="M23" s="324"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="413"/>
-      <c r="B24" s="329"/>
-      <c r="C24" s="329"/>
-      <c r="D24" s="329"/>
+      <c r="A24" s="405"/>
+      <c r="B24" s="321"/>
+      <c r="C24" s="321"/>
+      <c r="D24" s="321"/>
       <c r="E24" s="9"/>
-      <c r="F24" s="187"/>
-      <c r="G24" s="191"/>
-      <c r="H24" s="69" t="s">
+      <c r="F24" s="179"/>
+      <c r="G24" s="183"/>
+      <c r="H24" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I24" s="69" t="s">
+      <c r="I24" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J24" s="317"/>
-      <c r="K24" s="317"/>
-      <c r="L24" s="317"/>
-      <c r="M24" s="332"/>
+      <c r="J24" s="309"/>
+      <c r="K24" s="309"/>
+      <c r="L24" s="309"/>
+      <c r="M24" s="324"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="413"/>
-      <c r="B25" s="329"/>
-      <c r="C25" s="329"/>
-      <c r="D25" s="329"/>
+      <c r="A25" s="405"/>
+      <c r="B25" s="321"/>
+      <c r="C25" s="321"/>
+      <c r="D25" s="321"/>
       <c r="E25" s="9"/>
-      <c r="F25" s="187"/>
-      <c r="G25" s="191"/>
-      <c r="H25" s="69" t="s">
+      <c r="F25" s="179"/>
+      <c r="G25" s="183"/>
+      <c r="H25" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="I25" s="69" t="s">
+      <c r="I25" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J25" s="317"/>
-      <c r="K25" s="317"/>
-      <c r="L25" s="317"/>
-      <c r="M25" s="332"/>
+      <c r="J25" s="309"/>
+      <c r="K25" s="309"/>
+      <c r="L25" s="309"/>
+      <c r="M25" s="324"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="407"/>
-      <c r="B26" s="408"/>
-      <c r="C26" s="408"/>
-      <c r="D26" s="408"/>
+      <c r="A26" s="399"/>
+      <c r="B26" s="400"/>
+      <c r="C26" s="400"/>
+      <c r="D26" s="400"/>
       <c r="E26" s="11"/>
-      <c r="F26" s="317"/>
-      <c r="G26" s="317"/>
+      <c r="F26" s="309"/>
+      <c r="G26" s="309"/>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
-      <c r="J26" s="317"/>
-      <c r="K26" s="317"/>
-      <c r="L26" s="317"/>
-      <c r="M26" s="332"/>
+      <c r="J26" s="309"/>
+      <c r="K26" s="309"/>
+      <c r="L26" s="309"/>
+      <c r="M26" s="324"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="407"/>
-      <c r="B27" s="408"/>
-      <c r="C27" s="408"/>
-      <c r="D27" s="408"/>
+      <c r="A27" s="399"/>
+      <c r="B27" s="400"/>
+      <c r="C27" s="400"/>
+      <c r="D27" s="400"/>
       <c r="E27" s="11"/>
-      <c r="F27" s="317"/>
-      <c r="G27" s="317"/>
+      <c r="F27" s="309"/>
+      <c r="G27" s="309"/>
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
-      <c r="J27" s="317"/>
-      <c r="K27" s="317"/>
-      <c r="L27" s="317"/>
-      <c r="M27" s="332"/>
+      <c r="J27" s="309"/>
+      <c r="K27" s="309"/>
+      <c r="L27" s="309"/>
+      <c r="M27" s="324"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="407"/>
-      <c r="B28" s="408"/>
-      <c r="C28" s="408"/>
-      <c r="D28" s="408"/>
+      <c r="A28" s="399"/>
+      <c r="B28" s="400"/>
+      <c r="C28" s="400"/>
+      <c r="D28" s="400"/>
       <c r="E28" s="11"/>
-      <c r="F28" s="317"/>
-      <c r="G28" s="317"/>
+      <c r="F28" s="309"/>
+      <c r="G28" s="309"/>
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
-      <c r="J28" s="317"/>
-      <c r="K28" s="317"/>
-      <c r="L28" s="317"/>
-      <c r="M28" s="332"/>
+      <c r="J28" s="309"/>
+      <c r="K28" s="309"/>
+      <c r="L28" s="309"/>
+      <c r="M28" s="324"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="407"/>
-      <c r="B29" s="408"/>
-      <c r="C29" s="408"/>
-      <c r="D29" s="408"/>
+      <c r="A29" s="399"/>
+      <c r="B29" s="400"/>
+      <c r="C29" s="400"/>
+      <c r="D29" s="400"/>
       <c r="E29" s="11"/>
-      <c r="F29" s="317"/>
-      <c r="G29" s="317"/>
+      <c r="F29" s="309"/>
+      <c r="G29" s="309"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
-      <c r="J29" s="317"/>
-      <c r="K29" s="317"/>
-      <c r="L29" s="317"/>
-      <c r="M29" s="332"/>
+      <c r="J29" s="309"/>
+      <c r="K29" s="309"/>
+      <c r="L29" s="309"/>
+      <c r="M29" s="324"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="407"/>
-      <c r="B30" s="408"/>
-      <c r="C30" s="408"/>
-      <c r="D30" s="408"/>
+      <c r="A30" s="399"/>
+      <c r="B30" s="400"/>
+      <c r="C30" s="400"/>
+      <c r="D30" s="400"/>
       <c r="E30" s="11"/>
-      <c r="F30" s="317"/>
-      <c r="G30" s="317"/>
+      <c r="F30" s="309"/>
+      <c r="G30" s="309"/>
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
-      <c r="J30" s="317"/>
-      <c r="K30" s="317"/>
-      <c r="L30" s="317"/>
-      <c r="M30" s="332"/>
+      <c r="J30" s="309"/>
+      <c r="K30" s="309"/>
+      <c r="L30" s="309"/>
+      <c r="M30" s="324"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="407"/>
-      <c r="B31" s="408"/>
-      <c r="C31" s="408"/>
-      <c r="D31" s="408"/>
+      <c r="A31" s="399"/>
+      <c r="B31" s="400"/>
+      <c r="C31" s="400"/>
+      <c r="D31" s="400"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="317"/>
-      <c r="G31" s="317"/>
+      <c r="F31" s="309"/>
+      <c r="G31" s="309"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
-      <c r="J31" s="317"/>
-      <c r="K31" s="317"/>
-      <c r="L31" s="317"/>
-      <c r="M31" s="332"/>
+      <c r="J31" s="309"/>
+      <c r="K31" s="309"/>
+      <c r="L31" s="309"/>
+      <c r="M31" s="324"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="407"/>
-      <c r="B32" s="408"/>
-      <c r="C32" s="408"/>
-      <c r="D32" s="408"/>
+      <c r="A32" s="399"/>
+      <c r="B32" s="400"/>
+      <c r="C32" s="400"/>
+      <c r="D32" s="400"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="317"/>
-      <c r="G32" s="317"/>
+      <c r="F32" s="309"/>
+      <c r="G32" s="309"/>
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
-      <c r="J32" s="317"/>
-      <c r="K32" s="317"/>
-      <c r="L32" s="317"/>
-      <c r="M32" s="332"/>
+      <c r="J32" s="309"/>
+      <c r="K32" s="309"/>
+      <c r="L32" s="309"/>
+      <c r="M32" s="324"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A33" s="407"/>
-      <c r="B33" s="408"/>
-      <c r="C33" s="408"/>
-      <c r="D33" s="408"/>
+      <c r="A33" s="399"/>
+      <c r="B33" s="400"/>
+      <c r="C33" s="400"/>
+      <c r="D33" s="400"/>
       <c r="E33" s="11"/>
-      <c r="F33" s="317"/>
-      <c r="G33" s="317"/>
+      <c r="F33" s="309"/>
+      <c r="G33" s="309"/>
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
-      <c r="J33" s="317"/>
-      <c r="K33" s="317"/>
-      <c r="L33" s="317"/>
-      <c r="M33" s="332"/>
+      <c r="J33" s="309"/>
+      <c r="K33" s="309"/>
+      <c r="L33" s="309"/>
+      <c r="M33" s="324"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A34" s="407"/>
-      <c r="B34" s="408"/>
-      <c r="C34" s="408"/>
-      <c r="D34" s="408"/>
+      <c r="A34" s="399"/>
+      <c r="B34" s="400"/>
+      <c r="C34" s="400"/>
+      <c r="D34" s="400"/>
       <c r="E34" s="11"/>
-      <c r="F34" s="317"/>
-      <c r="G34" s="317"/>
+      <c r="F34" s="309"/>
+      <c r="G34" s="309"/>
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
-      <c r="J34" s="317"/>
-      <c r="K34" s="317"/>
-      <c r="L34" s="317"/>
-      <c r="M34" s="332"/>
+      <c r="J34" s="309"/>
+      <c r="K34" s="309"/>
+      <c r="L34" s="309"/>
+      <c r="M34" s="324"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35" s="407"/>
-      <c r="B35" s="408"/>
-      <c r="C35" s="408"/>
-      <c r="D35" s="408"/>
+      <c r="A35" s="399"/>
+      <c r="B35" s="400"/>
+      <c r="C35" s="400"/>
+      <c r="D35" s="400"/>
       <c r="E35" s="11"/>
-      <c r="F35" s="317"/>
-      <c r="G35" s="317"/>
+      <c r="F35" s="309"/>
+      <c r="G35" s="309"/>
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
-      <c r="J35" s="317"/>
-      <c r="K35" s="317"/>
-      <c r="L35" s="317"/>
-      <c r="M35" s="332"/>
+      <c r="J35" s="309"/>
+      <c r="K35" s="309"/>
+      <c r="L35" s="309"/>
+      <c r="M35" s="324"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A36" s="407"/>
-      <c r="B36" s="408"/>
-      <c r="C36" s="408"/>
-      <c r="D36" s="408"/>
+      <c r="A36" s="399"/>
+      <c r="B36" s="400"/>
+      <c r="C36" s="400"/>
+      <c r="D36" s="400"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="317"/>
-      <c r="G36" s="317"/>
+      <c r="F36" s="309"/>
+      <c r="G36" s="309"/>
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
-      <c r="J36" s="317"/>
-      <c r="K36" s="317"/>
-      <c r="L36" s="317"/>
-      <c r="M36" s="332"/>
+      <c r="J36" s="309"/>
+      <c r="K36" s="309"/>
+      <c r="L36" s="309"/>
+      <c r="M36" s="324"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A37" s="407"/>
-      <c r="B37" s="408"/>
-      <c r="C37" s="408"/>
-      <c r="D37" s="408"/>
+      <c r="A37" s="399"/>
+      <c r="B37" s="400"/>
+      <c r="C37" s="400"/>
+      <c r="D37" s="400"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="317"/>
-      <c r="G37" s="317"/>
+      <c r="F37" s="309"/>
+      <c r="G37" s="309"/>
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
-      <c r="J37" s="317"/>
-      <c r="K37" s="317"/>
-      <c r="L37" s="317"/>
-      <c r="M37" s="332"/>
+      <c r="J37" s="309"/>
+      <c r="K37" s="309"/>
+      <c r="L37" s="309"/>
+      <c r="M37" s="324"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A38" s="407"/>
-      <c r="B38" s="408"/>
-      <c r="C38" s="408"/>
-      <c r="D38" s="408"/>
+      <c r="A38" s="399"/>
+      <c r="B38" s="400"/>
+      <c r="C38" s="400"/>
+      <c r="D38" s="400"/>
       <c r="E38" s="11"/>
-      <c r="F38" s="317"/>
-      <c r="G38" s="317"/>
+      <c r="F38" s="309"/>
+      <c r="G38" s="309"/>
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
-      <c r="J38" s="317"/>
-      <c r="K38" s="317"/>
-      <c r="L38" s="317"/>
-      <c r="M38" s="332"/>
+      <c r="J38" s="309"/>
+      <c r="K38" s="309"/>
+      <c r="L38" s="309"/>
+      <c r="M38" s="324"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A39" s="407"/>
-      <c r="B39" s="408"/>
-      <c r="C39" s="408"/>
-      <c r="D39" s="408"/>
+      <c r="A39" s="399"/>
+      <c r="B39" s="400"/>
+      <c r="C39" s="400"/>
+      <c r="D39" s="400"/>
       <c r="E39" s="11"/>
-      <c r="F39" s="317"/>
-      <c r="G39" s="317"/>
+      <c r="F39" s="309"/>
+      <c r="G39" s="309"/>
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
-      <c r="J39" s="317"/>
-      <c r="K39" s="317"/>
-      <c r="L39" s="317"/>
-      <c r="M39" s="332"/>
+      <c r="J39" s="309"/>
+      <c r="K39" s="309"/>
+      <c r="L39" s="309"/>
+      <c r="M39" s="324"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A40" s="407"/>
-      <c r="B40" s="408"/>
-      <c r="C40" s="408"/>
-      <c r="D40" s="408"/>
+      <c r="A40" s="399"/>
+      <c r="B40" s="400"/>
+      <c r="C40" s="400"/>
+      <c r="D40" s="400"/>
       <c r="E40" s="11"/>
-      <c r="F40" s="317"/>
-      <c r="G40" s="317"/>
+      <c r="F40" s="309"/>
+      <c r="G40" s="309"/>
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
-      <c r="J40" s="317"/>
-      <c r="K40" s="317"/>
-      <c r="L40" s="317"/>
-      <c r="M40" s="332"/>
+      <c r="J40" s="309"/>
+      <c r="K40" s="309"/>
+      <c r="L40" s="309"/>
+      <c r="M40" s="324"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A41" s="407"/>
-      <c r="B41" s="408"/>
-      <c r="C41" s="408"/>
-      <c r="D41" s="408"/>
+      <c r="A41" s="399"/>
+      <c r="B41" s="400"/>
+      <c r="C41" s="400"/>
+      <c r="D41" s="400"/>
       <c r="E41" s="11"/>
-      <c r="F41" s="317"/>
-      <c r="G41" s="317"/>
+      <c r="F41" s="309"/>
+      <c r="G41" s="309"/>
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
-      <c r="J41" s="317"/>
-      <c r="K41" s="317"/>
-      <c r="L41" s="317"/>
-      <c r="M41" s="332"/>
+      <c r="J41" s="309"/>
+      <c r="K41" s="309"/>
+      <c r="L41" s="309"/>
+      <c r="M41" s="324"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A42" s="407"/>
-      <c r="B42" s="408"/>
-      <c r="C42" s="408"/>
-      <c r="D42" s="408"/>
+      <c r="A42" s="399"/>
+      <c r="B42" s="400"/>
+      <c r="C42" s="400"/>
+      <c r="D42" s="400"/>
       <c r="E42" s="11"/>
-      <c r="F42" s="317"/>
-      <c r="G42" s="317"/>
+      <c r="F42" s="309"/>
+      <c r="G42" s="309"/>
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
-      <c r="J42" s="317"/>
-      <c r="K42" s="317"/>
-      <c r="L42" s="317"/>
-      <c r="M42" s="332"/>
+      <c r="J42" s="309"/>
+      <c r="K42" s="309"/>
+      <c r="L42" s="309"/>
+      <c r="M42" s="324"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A43" s="407"/>
-      <c r="B43" s="408"/>
-      <c r="C43" s="408"/>
-      <c r="D43" s="408"/>
+      <c r="A43" s="399"/>
+      <c r="B43" s="400"/>
+      <c r="C43" s="400"/>
+      <c r="D43" s="400"/>
       <c r="E43" s="11"/>
-      <c r="F43" s="317"/>
-      <c r="G43" s="317"/>
+      <c r="F43" s="309"/>
+      <c r="G43" s="309"/>
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
-      <c r="J43" s="317"/>
-      <c r="K43" s="317"/>
-      <c r="L43" s="317"/>
-      <c r="M43" s="332"/>
+      <c r="J43" s="309"/>
+      <c r="K43" s="309"/>
+      <c r="L43" s="309"/>
+      <c r="M43" s="324"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A44" s="407"/>
-      <c r="B44" s="408"/>
-      <c r="C44" s="408"/>
-      <c r="D44" s="408"/>
+      <c r="A44" s="399"/>
+      <c r="B44" s="400"/>
+      <c r="C44" s="400"/>
+      <c r="D44" s="400"/>
       <c r="E44" s="11"/>
-      <c r="F44" s="317"/>
-      <c r="G44" s="317"/>
+      <c r="F44" s="309"/>
+      <c r="G44" s="309"/>
       <c r="H44" s="11"/>
       <c r="I44" s="11"/>
-      <c r="J44" s="317"/>
-      <c r="K44" s="317"/>
-      <c r="L44" s="317"/>
-      <c r="M44" s="332"/>
+      <c r="J44" s="309"/>
+      <c r="K44" s="309"/>
+      <c r="L44" s="309"/>
+      <c r="M44" s="324"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A45" s="407"/>
-      <c r="B45" s="408"/>
-      <c r="C45" s="408"/>
-      <c r="D45" s="408"/>
+      <c r="A45" s="399"/>
+      <c r="B45" s="400"/>
+      <c r="C45" s="400"/>
+      <c r="D45" s="400"/>
       <c r="E45" s="11"/>
-      <c r="F45" s="317"/>
-      <c r="G45" s="317"/>
+      <c r="F45" s="309"/>
+      <c r="G45" s="309"/>
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
-      <c r="J45" s="317"/>
-      <c r="K45" s="317"/>
-      <c r="L45" s="317"/>
-      <c r="M45" s="332"/>
+      <c r="J45" s="309"/>
+      <c r="K45" s="309"/>
+      <c r="L45" s="309"/>
+      <c r="M45" s="324"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A46" s="407"/>
-      <c r="B46" s="408"/>
-      <c r="C46" s="408"/>
-      <c r="D46" s="408"/>
+      <c r="A46" s="399"/>
+      <c r="B46" s="400"/>
+      <c r="C46" s="400"/>
+      <c r="D46" s="400"/>
       <c r="E46" s="11"/>
-      <c r="F46" s="317"/>
-      <c r="G46" s="317"/>
+      <c r="F46" s="309"/>
+      <c r="G46" s="309"/>
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
-      <c r="J46" s="317"/>
-      <c r="K46" s="317"/>
-      <c r="L46" s="317"/>
-      <c r="M46" s="332"/>
+      <c r="J46" s="309"/>
+      <c r="K46" s="309"/>
+      <c r="L46" s="309"/>
+      <c r="M46" s="324"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A47" s="407"/>
-      <c r="B47" s="408"/>
-      <c r="C47" s="408"/>
-      <c r="D47" s="408"/>
+      <c r="A47" s="399"/>
+      <c r="B47" s="400"/>
+      <c r="C47" s="400"/>
+      <c r="D47" s="400"/>
       <c r="E47" s="11"/>
-      <c r="F47" s="317"/>
-      <c r="G47" s="317"/>
+      <c r="F47" s="309"/>
+      <c r="G47" s="309"/>
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
-      <c r="J47" s="317"/>
-      <c r="K47" s="317"/>
-      <c r="L47" s="317"/>
-      <c r="M47" s="332"/>
+      <c r="J47" s="309"/>
+      <c r="K47" s="309"/>
+      <c r="L47" s="309"/>
+      <c r="M47" s="324"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A48" s="407"/>
-      <c r="B48" s="408"/>
-      <c r="C48" s="408"/>
-      <c r="D48" s="408"/>
+      <c r="A48" s="399"/>
+      <c r="B48" s="400"/>
+      <c r="C48" s="400"/>
+      <c r="D48" s="400"/>
       <c r="E48" s="11"/>
-      <c r="F48" s="317"/>
-      <c r="G48" s="317"/>
+      <c r="F48" s="309"/>
+      <c r="G48" s="309"/>
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
-      <c r="J48" s="317"/>
-      <c r="K48" s="317"/>
-      <c r="L48" s="317"/>
-      <c r="M48" s="332"/>
+      <c r="J48" s="309"/>
+      <c r="K48" s="309"/>
+      <c r="L48" s="309"/>
+      <c r="M48" s="324"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A49" s="407"/>
-      <c r="B49" s="408"/>
-      <c r="C49" s="408"/>
-      <c r="D49" s="408"/>
+      <c r="A49" s="399"/>
+      <c r="B49" s="400"/>
+      <c r="C49" s="400"/>
+      <c r="D49" s="400"/>
       <c r="E49" s="11"/>
-      <c r="F49" s="317"/>
-      <c r="G49" s="317"/>
+      <c r="F49" s="309"/>
+      <c r="G49" s="309"/>
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
-      <c r="J49" s="317"/>
-      <c r="K49" s="317"/>
-      <c r="L49" s="317"/>
-      <c r="M49" s="332"/>
+      <c r="J49" s="309"/>
+      <c r="K49" s="309"/>
+      <c r="L49" s="309"/>
+      <c r="M49" s="324"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="314" t="s">
+      <c r="A50" s="306" t="s">
         <v>22</v>
       </c>
-      <c r="B50" s="315"/>
-      <c r="C50" s="315"/>
-      <c r="D50" s="315"/>
-      <c r="E50" s="70"/>
-      <c r="F50" s="409"/>
-      <c r="G50" s="410"/>
+      <c r="B50" s="307"/>
+      <c r="C50" s="307"/>
+      <c r="D50" s="307"/>
+      <c r="E50" s="68"/>
+      <c r="F50" s="401"/>
+      <c r="G50" s="402"/>
       <c r="H50" s="27"/>
       <c r="I50" s="28"/>
-      <c r="J50" s="411"/>
-      <c r="K50" s="411"/>
-      <c r="L50" s="411"/>
-      <c r="M50" s="412"/>
+      <c r="J50" s="403"/>
+      <c r="K50" s="403"/>
+      <c r="L50" s="403"/>
+      <c r="M50" s="404"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A51" s="395" t="s">
+      <c r="A51" s="387" t="s">
         <v>55</v>
       </c>
-      <c r="B51" s="396"/>
-      <c r="C51" s="396"/>
-      <c r="D51" s="396"/>
-      <c r="E51" s="396"/>
-      <c r="F51" s="396"/>
-      <c r="G51" s="396"/>
-      <c r="H51" s="396"/>
-      <c r="I51" s="396"/>
-      <c r="J51" s="396"/>
-      <c r="K51" s="396"/>
-      <c r="L51" s="396"/>
-      <c r="M51" s="397"/>
+      <c r="B51" s="388"/>
+      <c r="C51" s="388"/>
+      <c r="D51" s="388"/>
+      <c r="E51" s="388"/>
+      <c r="F51" s="388"/>
+      <c r="G51" s="388"/>
+      <c r="H51" s="388"/>
+      <c r="I51" s="388"/>
+      <c r="J51" s="388"/>
+      <c r="K51" s="388"/>
+      <c r="L51" s="388"/>
+      <c r="M51" s="389"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="398"/>
-      <c r="B52" s="399"/>
-      <c r="C52" s="399"/>
-      <c r="D52" s="399"/>
-      <c r="E52" s="399"/>
-      <c r="F52" s="399"/>
-      <c r="G52" s="399"/>
-      <c r="H52" s="399"/>
-      <c r="I52" s="399"/>
-      <c r="J52" s="399"/>
-      <c r="K52" s="399"/>
-      <c r="L52" s="399"/>
-      <c r="M52" s="400"/>
+      <c r="A52" s="390"/>
+      <c r="B52" s="391"/>
+      <c r="C52" s="391"/>
+      <c r="D52" s="391"/>
+      <c r="E52" s="391"/>
+      <c r="F52" s="391"/>
+      <c r="G52" s="391"/>
+      <c r="H52" s="391"/>
+      <c r="I52" s="391"/>
+      <c r="J52" s="391"/>
+      <c r="K52" s="391"/>
+      <c r="L52" s="391"/>
+      <c r="M52" s="392"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A53" s="401"/>
-      <c r="B53" s="402"/>
-      <c r="C53" s="402"/>
-      <c r="D53" s="402"/>
-      <c r="E53" s="402"/>
-      <c r="F53" s="402"/>
-      <c r="G53" s="402"/>
-      <c r="H53" s="402"/>
-      <c r="I53" s="402"/>
-      <c r="J53" s="402"/>
-      <c r="K53" s="402"/>
-      <c r="L53" s="402"/>
-      <c r="M53" s="403"/>
+      <c r="A53" s="393"/>
+      <c r="B53" s="394"/>
+      <c r="C53" s="394"/>
+      <c r="D53" s="394"/>
+      <c r="E53" s="394"/>
+      <c r="F53" s="394"/>
+      <c r="G53" s="394"/>
+      <c r="H53" s="394"/>
+      <c r="I53" s="394"/>
+      <c r="J53" s="394"/>
+      <c r="K53" s="394"/>
+      <c r="L53" s="394"/>
+      <c r="M53" s="395"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A54" s="401"/>
-      <c r="B54" s="402"/>
-      <c r="C54" s="402"/>
-      <c r="D54" s="402"/>
-      <c r="E54" s="402"/>
-      <c r="F54" s="402"/>
-      <c r="G54" s="402"/>
-      <c r="H54" s="402"/>
-      <c r="I54" s="402"/>
-      <c r="J54" s="402"/>
-      <c r="K54" s="402"/>
-      <c r="L54" s="402"/>
-      <c r="M54" s="403"/>
+      <c r="A54" s="393"/>
+      <c r="B54" s="394"/>
+      <c r="C54" s="394"/>
+      <c r="D54" s="394"/>
+      <c r="E54" s="394"/>
+      <c r="F54" s="394"/>
+      <c r="G54" s="394"/>
+      <c r="H54" s="394"/>
+      <c r="I54" s="394"/>
+      <c r="J54" s="394"/>
+      <c r="K54" s="394"/>
+      <c r="L54" s="394"/>
+      <c r="M54" s="395"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A55" s="401"/>
-      <c r="B55" s="402"/>
-      <c r="C55" s="402"/>
-      <c r="D55" s="402"/>
-      <c r="E55" s="402"/>
-      <c r="F55" s="402"/>
-      <c r="G55" s="402"/>
-      <c r="H55" s="402"/>
-      <c r="I55" s="402"/>
-      <c r="J55" s="402"/>
-      <c r="K55" s="402"/>
-      <c r="L55" s="402"/>
-      <c r="M55" s="403"/>
+      <c r="A55" s="393"/>
+      <c r="B55" s="394"/>
+      <c r="C55" s="394"/>
+      <c r="D55" s="394"/>
+      <c r="E55" s="394"/>
+      <c r="F55" s="394"/>
+      <c r="G55" s="394"/>
+      <c r="H55" s="394"/>
+      <c r="I55" s="394"/>
+      <c r="J55" s="394"/>
+      <c r="K55" s="394"/>
+      <c r="L55" s="394"/>
+      <c r="M55" s="395"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A56" s="401"/>
-      <c r="B56" s="402"/>
-      <c r="C56" s="402"/>
-      <c r="D56" s="402"/>
-      <c r="E56" s="402"/>
-      <c r="F56" s="402"/>
-      <c r="G56" s="402"/>
-      <c r="H56" s="402"/>
-      <c r="I56" s="402"/>
-      <c r="J56" s="402"/>
-      <c r="K56" s="402"/>
-      <c r="L56" s="402"/>
-      <c r="M56" s="403"/>
+      <c r="A56" s="393"/>
+      <c r="B56" s="394"/>
+      <c r="C56" s="394"/>
+      <c r="D56" s="394"/>
+      <c r="E56" s="394"/>
+      <c r="F56" s="394"/>
+      <c r="G56" s="394"/>
+      <c r="H56" s="394"/>
+      <c r="I56" s="394"/>
+      <c r="J56" s="394"/>
+      <c r="K56" s="394"/>
+      <c r="L56" s="394"/>
+      <c r="M56" s="395"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A57" s="401"/>
-      <c r="B57" s="402"/>
-      <c r="C57" s="402"/>
-      <c r="D57" s="402"/>
-      <c r="E57" s="402"/>
-      <c r="F57" s="402"/>
-      <c r="G57" s="402"/>
-      <c r="H57" s="402"/>
-      <c r="I57" s="402"/>
-      <c r="J57" s="402"/>
-      <c r="K57" s="402"/>
-      <c r="L57" s="402"/>
-      <c r="M57" s="403"/>
+      <c r="A57" s="393"/>
+      <c r="B57" s="394"/>
+      <c r="C57" s="394"/>
+      <c r="D57" s="394"/>
+      <c r="E57" s="394"/>
+      <c r="F57" s="394"/>
+      <c r="G57" s="394"/>
+      <c r="H57" s="394"/>
+      <c r="I57" s="394"/>
+      <c r="J57" s="394"/>
+      <c r="K57" s="394"/>
+      <c r="L57" s="394"/>
+      <c r="M57" s="395"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A58" s="401"/>
-      <c r="B58" s="402"/>
-      <c r="C58" s="402"/>
-      <c r="D58" s="402"/>
-      <c r="E58" s="402"/>
-      <c r="F58" s="402"/>
-      <c r="G58" s="402"/>
-      <c r="H58" s="402"/>
-      <c r="I58" s="402"/>
-      <c r="J58" s="402"/>
-      <c r="K58" s="402"/>
-      <c r="L58" s="402"/>
-      <c r="M58" s="403"/>
+      <c r="A58" s="393"/>
+      <c r="B58" s="394"/>
+      <c r="C58" s="394"/>
+      <c r="D58" s="394"/>
+      <c r="E58" s="394"/>
+      <c r="F58" s="394"/>
+      <c r="G58" s="394"/>
+      <c r="H58" s="394"/>
+      <c r="I58" s="394"/>
+      <c r="J58" s="394"/>
+      <c r="K58" s="394"/>
+      <c r="L58" s="394"/>
+      <c r="M58" s="395"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A59" s="401"/>
-      <c r="B59" s="402"/>
-      <c r="C59" s="402"/>
-      <c r="D59" s="402"/>
-      <c r="E59" s="402"/>
-      <c r="F59" s="402"/>
-      <c r="G59" s="402"/>
-      <c r="H59" s="402"/>
-      <c r="I59" s="402"/>
-      <c r="J59" s="402"/>
-      <c r="K59" s="402"/>
-      <c r="L59" s="402"/>
-      <c r="M59" s="403"/>
+      <c r="A59" s="393"/>
+      <c r="B59" s="394"/>
+      <c r="C59" s="394"/>
+      <c r="D59" s="394"/>
+      <c r="E59" s="394"/>
+      <c r="F59" s="394"/>
+      <c r="G59" s="394"/>
+      <c r="H59" s="394"/>
+      <c r="I59" s="394"/>
+      <c r="J59" s="394"/>
+      <c r="K59" s="394"/>
+      <c r="L59" s="394"/>
+      <c r="M59" s="395"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A60" s="404"/>
-      <c r="B60" s="405"/>
-      <c r="C60" s="405"/>
-      <c r="D60" s="405"/>
-      <c r="E60" s="405"/>
-      <c r="F60" s="405"/>
-      <c r="G60" s="405"/>
-      <c r="H60" s="405"/>
-      <c r="I60" s="405"/>
-      <c r="J60" s="405"/>
-      <c r="K60" s="405"/>
-      <c r="L60" s="405"/>
-      <c r="M60" s="406"/>
+      <c r="A60" s="396"/>
+      <c r="B60" s="397"/>
+      <c r="C60" s="397"/>
+      <c r="D60" s="397"/>
+      <c r="E60" s="397"/>
+      <c r="F60" s="397"/>
+      <c r="G60" s="397"/>
+      <c r="H60" s="397"/>
+      <c r="I60" s="397"/>
+      <c r="J60" s="397"/>
+      <c r="K60" s="397"/>
+      <c r="L60" s="397"/>
+      <c r="M60" s="398"/>
     </row>
     <row r="61" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="26"/>
@@ -6541,642 +6531,642 @@
     <col min="9" max="9" width="6.7109375" customWidth="1"/>
     <col min="11" max="11" width="17.140625" customWidth="1"/>
     <col min="12" max="12" width="8.42578125" customWidth="1"/>
-    <col min="13" max="13" width="8" style="120" customWidth="1"/>
+    <col min="13" max="13" width="8" style="112" customWidth="1"/>
     <col min="14" max="14" width="0.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="88" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92" t="s">
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="131" t="s">
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="90"/>
+      <c r="K1" s="90"/>
+      <c r="L1" s="123" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="132"/>
-      <c r="N1" s="116"/>
+      <c r="M1" s="124"/>
+      <c r="N1" s="108"/>
     </row>
     <row r="2" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="129" t="s">
+      <c r="A2" s="121" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="116"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="122"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="93"/>
+      <c r="N2" s="108"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="137" t="s">
+      <c r="A3" s="129" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="138"/>
-      <c r="C3" s="138"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="138"/>
-      <c r="F3" s="138"/>
-      <c r="G3" s="138"/>
-      <c r="H3" s="138"/>
-      <c r="I3" s="102" t="s">
+      <c r="B3" s="130"/>
+      <c r="C3" s="130"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="130"/>
+      <c r="F3" s="130"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="J3" s="89"/>
-      <c r="K3" s="103"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="104"/>
-      <c r="N3" s="116"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="95"/>
+      <c r="L3" s="87"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="108"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="137" t="s">
+      <c r="A4" s="129" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="138"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="138"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="138"/>
-      <c r="I4" s="140"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121"/>
-      <c r="M4" s="122"/>
-      <c r="N4" s="116"/>
+      <c r="B4" s="130"/>
+      <c r="C4" s="130"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="130"/>
+      <c r="I4" s="132"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113"/>
+      <c r="M4" s="114"/>
+      <c r="N4" s="108"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="137" t="s">
+      <c r="A5" s="129" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="138"/>
-      <c r="C5" s="138"/>
-      <c r="D5" s="138"/>
-      <c r="E5" s="138"/>
-      <c r="F5" s="138"/>
-      <c r="G5" s="138"/>
-      <c r="H5" s="138"/>
-      <c r="I5" s="140"/>
-      <c r="J5" s="121"/>
-      <c r="K5" s="121"/>
-      <c r="L5" s="121"/>
-      <c r="M5" s="122"/>
-      <c r="N5" s="116"/>
+      <c r="B5" s="130"/>
+      <c r="C5" s="130"/>
+      <c r="D5" s="130"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="130"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="132"/>
+      <c r="J5" s="113"/>
+      <c r="K5" s="113"/>
+      <c r="L5" s="113"/>
+      <c r="M5" s="114"/>
+      <c r="N5" s="108"/>
     </row>
     <row r="6" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="135" t="s">
+      <c r="A6" s="127" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="136"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="136"/>
-      <c r="E6" s="136"/>
-      <c r="F6" s="139" t="s">
+      <c r="B6" s="128"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="128"/>
+      <c r="E6" s="128"/>
+      <c r="F6" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="139"/>
-      <c r="H6" s="418" t="s">
+      <c r="G6" s="131"/>
+      <c r="H6" s="410" t="s">
         <v>80</v>
       </c>
-      <c r="I6" s="141"/>
-      <c r="J6" s="142"/>
-      <c r="K6" s="142"/>
-      <c r="L6" s="142"/>
-      <c r="M6" s="143"/>
-      <c r="N6" s="116"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="134"/>
+      <c r="K6" s="134"/>
+      <c r="L6" s="134"/>
+      <c r="M6" s="135"/>
+      <c r="N6" s="108"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="152" t="s">
+      <c r="A7" s="144" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="153"/>
-      <c r="C7" s="153"/>
-      <c r="D7" s="153"/>
-      <c r="E7" s="153"/>
-      <c r="F7" s="153"/>
-      <c r="G7" s="153"/>
-      <c r="H7" s="153"/>
-      <c r="I7" s="105" t="s">
+      <c r="B7" s="145"/>
+      <c r="C7" s="145"/>
+      <c r="D7" s="145"/>
+      <c r="E7" s="145"/>
+      <c r="F7" s="145"/>
+      <c r="G7" s="145"/>
+      <c r="H7" s="145"/>
+      <c r="I7" s="97" t="s">
         <v>74</v>
       </c>
-      <c r="J7" s="106"/>
-      <c r="K7" s="107"/>
-      <c r="L7" s="106"/>
-      <c r="M7" s="108"/>
-      <c r="N7" s="116"/>
+      <c r="J7" s="98"/>
+      <c r="K7" s="99"/>
+      <c r="L7" s="98"/>
+      <c r="M7" s="100"/>
+      <c r="N7" s="108"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="86"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="157" t="s">
+      <c r="B8" s="84"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="149" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="157"/>
-      <c r="G8" s="157"/>
-      <c r="H8" s="157"/>
-      <c r="I8" s="144" t="s">
+      <c r="F8" s="149"/>
+      <c r="G8" s="149"/>
+      <c r="H8" s="149"/>
+      <c r="I8" s="136" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="138"/>
-      <c r="K8" s="138"/>
-      <c r="L8" s="138"/>
-      <c r="M8" s="145"/>
-      <c r="N8" s="116"/>
+      <c r="J8" s="130"/>
+      <c r="K8" s="130"/>
+      <c r="L8" s="130"/>
+      <c r="M8" s="137"/>
+      <c r="N8" s="108"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="109" t="s">
+      <c r="I9" s="101" t="s">
         <v>68</v>
       </c>
-      <c r="J9" s="110"/>
-      <c r="K9" s="110"/>
-      <c r="L9" s="110"/>
-      <c r="M9" s="111"/>
-      <c r="N9" s="116"/>
+      <c r="J9" s="102"/>
+      <c r="K9" s="102"/>
+      <c r="L9" s="102"/>
+      <c r="M9" s="103"/>
+      <c r="N9" s="108"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="188"/>
-      <c r="D10" s="188"/>
-      <c r="E10" s="188"/>
-      <c r="F10" s="188"/>
-      <c r="G10" s="188"/>
-      <c r="I10" s="99" t="s">
+      <c r="C10" s="180"/>
+      <c r="D10" s="180"/>
+      <c r="E10" s="180"/>
+      <c r="F10" s="180"/>
+      <c r="G10" s="180"/>
+      <c r="I10" s="91" t="s">
         <v>75</v>
       </c>
       <c r="J10" s="29"/>
       <c r="K10" s="29"/>
       <c r="L10" s="29"/>
-      <c r="M10" s="112"/>
-      <c r="N10" s="116"/>
+      <c r="M10" s="104"/>
+      <c r="N10" s="108"/>
     </row>
     <row r="11" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="158" t="s">
+      <c r="A11" s="150" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="136"/>
-      <c r="C11" s="136"/>
-      <c r="D11" s="136"/>
-      <c r="E11" s="136"/>
-      <c r="F11" s="139" t="s">
+      <c r="B11" s="128"/>
+      <c r="C11" s="128"/>
+      <c r="D11" s="128"/>
+      <c r="E11" s="128"/>
+      <c r="F11" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="139"/>
-      <c r="H11" s="418" t="s">
+      <c r="G11" s="131"/>
+      <c r="H11" s="410" t="s">
         <v>80</v>
       </c>
-      <c r="I11" s="123" t="s">
+      <c r="I11" s="115" t="s">
         <v>69</v>
       </c>
-      <c r="J11" s="124"/>
-      <c r="K11" s="113"/>
-      <c r="L11" s="113"/>
-      <c r="M11" s="114"/>
-      <c r="N11" s="116"/>
+      <c r="J11" s="116"/>
+      <c r="K11" s="105"/>
+      <c r="L11" s="105"/>
+      <c r="M11" s="106"/>
+      <c r="N11" s="108"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="146" t="s">
+      <c r="A12" s="138" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="147"/>
-      <c r="C12" s="147"/>
-      <c r="D12" s="147"/>
-      <c r="E12" s="147"/>
-      <c r="F12" s="147"/>
-      <c r="G12" s="147"/>
-      <c r="H12" s="147"/>
-      <c r="I12" s="140"/>
-      <c r="J12" s="121"/>
-      <c r="K12" s="121"/>
-      <c r="L12" s="121"/>
-      <c r="M12" s="122"/>
-      <c r="N12" s="116"/>
+      <c r="B12" s="139"/>
+      <c r="C12" s="139"/>
+      <c r="D12" s="139"/>
+      <c r="E12" s="139"/>
+      <c r="F12" s="139"/>
+      <c r="G12" s="139"/>
+      <c r="H12" s="139"/>
+      <c r="I12" s="132"/>
+      <c r="J12" s="113"/>
+      <c r="K12" s="113"/>
+      <c r="L12" s="113"/>
+      <c r="M12" s="114"/>
+      <c r="N12" s="108"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="133" t="s">
+      <c r="A13" s="125" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="134"/>
-      <c r="C13" s="134"/>
-      <c r="D13" s="134"/>
-      <c r="E13" s="134"/>
-      <c r="F13" s="134"/>
-      <c r="G13" s="134"/>
-      <c r="H13" s="134"/>
-      <c r="I13" s="140"/>
-      <c r="J13" s="121"/>
-      <c r="K13" s="121"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="122"/>
-      <c r="N13" s="116"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="132"/>
+      <c r="J13" s="113"/>
+      <c r="K13" s="113"/>
+      <c r="L13" s="113"/>
+      <c r="M13" s="114"/>
+      <c r="N13" s="108"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="156" t="s">
+      <c r="A14" s="148" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="138"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="141"/>
-      <c r="J14" s="142"/>
-      <c r="K14" s="142"/>
-      <c r="L14" s="142"/>
-      <c r="M14" s="143"/>
-      <c r="N14" s="116"/>
+      <c r="B14" s="130"/>
+      <c r="C14" s="130"/>
+      <c r="D14" s="130"/>
+      <c r="E14" s="130"/>
+      <c r="F14" s="130"/>
+      <c r="G14" s="130"/>
+      <c r="H14" s="130"/>
+      <c r="I14" s="133"/>
+      <c r="J14" s="134"/>
+      <c r="K14" s="134"/>
+      <c r="L14" s="134"/>
+      <c r="M14" s="135"/>
+      <c r="N14" s="108"/>
     </row>
     <row r="15" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="166" t="s">
+      <c r="A15" s="158" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="167"/>
-      <c r="C15" s="167"/>
-      <c r="D15" s="167"/>
-      <c r="E15" s="167"/>
-      <c r="F15" s="167"/>
-      <c r="G15" s="167"/>
-      <c r="H15" s="168"/>
-      <c r="I15" s="163" t="s">
+      <c r="B15" s="159"/>
+      <c r="C15" s="159"/>
+      <c r="D15" s="159"/>
+      <c r="E15" s="159"/>
+      <c r="F15" s="159"/>
+      <c r="G15" s="159"/>
+      <c r="H15" s="160"/>
+      <c r="I15" s="155" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="164"/>
-      <c r="K15" s="164"/>
-      <c r="L15" s="164"/>
-      <c r="M15" s="165"/>
-      <c r="N15" s="116"/>
+      <c r="J15" s="156"/>
+      <c r="K15" s="156"/>
+      <c r="L15" s="156"/>
+      <c r="M15" s="157"/>
+      <c r="N15" s="108"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="93"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="94"/>
-      <c r="I16" s="178" t="s">
+      <c r="A16" s="61" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="240"/>
+      <c r="G16" s="240"/>
+      <c r="H16" s="241"/>
+      <c r="I16" s="170" t="s">
         <v>78</v>
       </c>
-      <c r="J16" s="179"/>
-      <c r="K16" s="179"/>
-      <c r="L16" s="179"/>
-      <c r="M16" s="180"/>
-      <c r="N16" s="116"/>
+      <c r="J16" s="171"/>
+      <c r="K16" s="171"/>
+      <c r="L16" s="171"/>
+      <c r="M16" s="172"/>
+      <c r="N16" s="108"/>
     </row>
     <row r="17" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="95" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="96"/>
-      <c r="C17" s="96"/>
-      <c r="D17" s="96"/>
-      <c r="E17" s="96"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="416" t="s">
+      <c r="A17" s="411"/>
+      <c r="B17" s="412"/>
+      <c r="C17" s="412"/>
+      <c r="D17" s="412"/>
+      <c r="E17" s="412"/>
+      <c r="F17" s="412"/>
+      <c r="G17" s="412"/>
+      <c r="H17" s="412"/>
+      <c r="I17" s="408" t="s">
         <v>80</v>
       </c>
-      <c r="J17" s="417"/>
-      <c r="K17" s="159" t="s">
+      <c r="J17" s="409"/>
+      <c r="K17" s="151" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="159"/>
-      <c r="M17" s="160"/>
-      <c r="N17" s="116"/>
+      <c r="L17" s="151"/>
+      <c r="M17" s="152"/>
+      <c r="N17" s="108"/>
     </row>
     <row r="18" spans="1:14" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="97"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="98"/>
-      <c r="I18" s="177" t="s">
+      <c r="A18" s="413"/>
+      <c r="B18" s="414"/>
+      <c r="C18" s="414"/>
+      <c r="D18" s="414"/>
+      <c r="E18" s="414"/>
+      <c r="F18" s="414"/>
+      <c r="G18" s="414"/>
+      <c r="H18" s="414"/>
+      <c r="I18" s="169" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="177"/>
-      <c r="K18" s="161"/>
-      <c r="L18" s="161"/>
-      <c r="M18" s="162"/>
-      <c r="N18" s="116"/>
+      <c r="J18" s="169"/>
+      <c r="K18" s="153"/>
+      <c r="L18" s="153"/>
+      <c r="M18" s="154"/>
+      <c r="N18" s="108"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="181" t="s">
+      <c r="A19" s="173" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="182"/>
-      <c r="C19" s="182"/>
-      <c r="D19" s="182"/>
-      <c r="E19" s="182"/>
-      <c r="F19" s="182"/>
-      <c r="G19" s="182"/>
-      <c r="H19" s="182"/>
-      <c r="I19" s="182"/>
-      <c r="J19" s="182"/>
-      <c r="K19" s="182"/>
-      <c r="L19" s="182"/>
-      <c r="M19" s="183"/>
-      <c r="N19" s="116"/>
+      <c r="B19" s="174"/>
+      <c r="C19" s="174"/>
+      <c r="D19" s="174"/>
+      <c r="E19" s="174"/>
+      <c r="F19" s="174"/>
+      <c r="G19" s="174"/>
+      <c r="H19" s="174"/>
+      <c r="I19" s="174"/>
+      <c r="J19" s="174"/>
+      <c r="K19" s="174"/>
+      <c r="L19" s="174"/>
+      <c r="M19" s="175"/>
+      <c r="N19" s="108"/>
     </row>
     <row r="20" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="184" t="s">
+      <c r="A20" s="176" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="185"/>
-      <c r="C20" s="185"/>
-      <c r="D20" s="185"/>
-      <c r="E20" s="185" t="s">
+      <c r="B20" s="177"/>
+      <c r="C20" s="177"/>
+      <c r="D20" s="177"/>
+      <c r="E20" s="177" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="185" t="s">
+      <c r="F20" s="177" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="185"/>
-      <c r="H20" s="175" t="s">
+      <c r="G20" s="177"/>
+      <c r="H20" s="167" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="176"/>
-      <c r="J20" s="169" t="s">
+      <c r="I20" s="168"/>
+      <c r="J20" s="161" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="170"/>
-      <c r="L20" s="170"/>
-      <c r="M20" s="171"/>
-      <c r="N20" s="116"/>
+      <c r="K20" s="162"/>
+      <c r="L20" s="162"/>
+      <c r="M20" s="163"/>
+      <c r="N20" s="108"/>
     </row>
     <row r="21" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="184"/>
-      <c r="B21" s="185"/>
-      <c r="C21" s="185"/>
-      <c r="D21" s="185"/>
-      <c r="E21" s="185"/>
-      <c r="F21" s="185"/>
-      <c r="G21" s="185"/>
-      <c r="H21" s="154" t="s">
+      <c r="A21" s="176"/>
+      <c r="B21" s="177"/>
+      <c r="C21" s="177"/>
+      <c r="D21" s="177"/>
+      <c r="E21" s="177"/>
+      <c r="F21" s="177"/>
+      <c r="G21" s="177"/>
+      <c r="H21" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="155"/>
-      <c r="J21" s="172"/>
-      <c r="K21" s="173"/>
-      <c r="L21" s="173"/>
-      <c r="M21" s="174"/>
-      <c r="N21" s="116"/>
+      <c r="I21" s="147"/>
+      <c r="J21" s="164"/>
+      <c r="K21" s="165"/>
+      <c r="L21" s="165"/>
+      <c r="M21" s="166"/>
+      <c r="N21" s="108"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" s="186"/>
-      <c r="B22" s="151"/>
-      <c r="C22" s="151"/>
-      <c r="D22" s="187"/>
+      <c r="A22" s="178"/>
+      <c r="B22" s="143"/>
+      <c r="C22" s="143"/>
+      <c r="D22" s="179"/>
       <c r="E22" s="9"/>
-      <c r="F22" s="151"/>
-      <c r="G22" s="151"/>
+      <c r="F22" s="143"/>
+      <c r="G22" s="143"/>
       <c r="H22" s="9" t="s">
         <v>51</v>
       </c>
       <c r="I22" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="151"/>
-      <c r="K22" s="151"/>
-      <c r="L22" s="151"/>
-      <c r="M22" s="151"/>
-      <c r="N22" s="116"/>
+      <c r="J22" s="143"/>
+      <c r="K22" s="143"/>
+      <c r="L22" s="143"/>
+      <c r="M22" s="143"/>
+      <c r="N22" s="108"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="148"/>
-      <c r="B23" s="149"/>
-      <c r="C23" s="149"/>
-      <c r="D23" s="150"/>
+      <c r="A23" s="140"/>
+      <c r="B23" s="141"/>
+      <c r="C23" s="141"/>
+      <c r="D23" s="142"/>
       <c r="E23" s="9"/>
-      <c r="F23" s="151"/>
-      <c r="G23" s="151"/>
+      <c r="F23" s="143"/>
+      <c r="G23" s="143"/>
       <c r="H23" s="9" t="s">
         <v>51</v>
       </c>
       <c r="I23" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J23" s="151"/>
-      <c r="K23" s="151"/>
-      <c r="L23" s="151"/>
-      <c r="M23" s="151"/>
-      <c r="N23" s="116"/>
+      <c r="J23" s="143"/>
+      <c r="K23" s="143"/>
+      <c r="L23" s="143"/>
+      <c r="M23" s="143"/>
+      <c r="N23" s="108"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="148"/>
-      <c r="B24" s="149"/>
-      <c r="C24" s="149"/>
-      <c r="D24" s="150"/>
+      <c r="A24" s="140"/>
+      <c r="B24" s="141"/>
+      <c r="C24" s="141"/>
+      <c r="D24" s="142"/>
       <c r="E24" s="9"/>
-      <c r="F24" s="151"/>
-      <c r="G24" s="151"/>
+      <c r="F24" s="143"/>
+      <c r="G24" s="143"/>
       <c r="H24" s="9" t="s">
         <v>51</v>
       </c>
       <c r="I24" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J24" s="151"/>
-      <c r="K24" s="151"/>
-      <c r="L24" s="151"/>
-      <c r="M24" s="151"/>
-      <c r="N24" s="116"/>
+      <c r="J24" s="143"/>
+      <c r="K24" s="143"/>
+      <c r="L24" s="143"/>
+      <c r="M24" s="143"/>
+      <c r="N24" s="108"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="148"/>
-      <c r="B25" s="149"/>
-      <c r="C25" s="149"/>
-      <c r="D25" s="150"/>
+      <c r="A25" s="140"/>
+      <c r="B25" s="141"/>
+      <c r="C25" s="141"/>
+      <c r="D25" s="142"/>
       <c r="E25" s="9"/>
-      <c r="F25" s="151"/>
-      <c r="G25" s="151"/>
+      <c r="F25" s="143"/>
+      <c r="G25" s="143"/>
       <c r="H25" s="9" t="s">
         <v>51</v>
       </c>
       <c r="I25" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J25" s="151"/>
-      <c r="K25" s="151"/>
-      <c r="L25" s="151"/>
-      <c r="M25" s="151"/>
-      <c r="N25" s="116"/>
+      <c r="J25" s="143"/>
+      <c r="K25" s="143"/>
+      <c r="L25" s="143"/>
+      <c r="M25" s="143"/>
+      <c r="N25" s="108"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="148"/>
-      <c r="B26" s="149"/>
-      <c r="C26" s="149"/>
-      <c r="D26" s="150"/>
+      <c r="A26" s="140"/>
+      <c r="B26" s="141"/>
+      <c r="C26" s="141"/>
+      <c r="D26" s="142"/>
       <c r="E26" s="9"/>
-      <c r="F26" s="151"/>
-      <c r="G26" s="151"/>
+      <c r="F26" s="143"/>
+      <c r="G26" s="143"/>
       <c r="H26" s="9" t="s">
         <v>51</v>
       </c>
       <c r="I26" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J26" s="151"/>
-      <c r="K26" s="151"/>
-      <c r="L26" s="151"/>
-      <c r="M26" s="151"/>
-      <c r="N26" s="116"/>
+      <c r="J26" s="143"/>
+      <c r="K26" s="143"/>
+      <c r="L26" s="143"/>
+      <c r="M26" s="143"/>
+      <c r="N26" s="108"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="148"/>
-      <c r="B27" s="149"/>
-      <c r="C27" s="149"/>
-      <c r="D27" s="150"/>
+      <c r="A27" s="140"/>
+      <c r="B27" s="141"/>
+      <c r="C27" s="141"/>
+      <c r="D27" s="142"/>
       <c r="E27" s="9"/>
-      <c r="F27" s="151"/>
-      <c r="G27" s="151"/>
+      <c r="F27" s="143"/>
+      <c r="G27" s="143"/>
       <c r="H27" s="9" t="s">
         <v>51</v>
       </c>
       <c r="I27" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="151"/>
-      <c r="K27" s="151"/>
-      <c r="L27" s="151"/>
-      <c r="M27" s="151"/>
-      <c r="N27" s="116"/>
+      <c r="J27" s="143"/>
+      <c r="K27" s="143"/>
+      <c r="L27" s="143"/>
+      <c r="M27" s="143"/>
+      <c r="N27" s="108"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="148"/>
-      <c r="B28" s="149"/>
-      <c r="C28" s="149"/>
-      <c r="D28" s="150"/>
+      <c r="A28" s="140"/>
+      <c r="B28" s="141"/>
+      <c r="C28" s="141"/>
+      <c r="D28" s="142"/>
       <c r="E28" s="9"/>
-      <c r="F28" s="151"/>
-      <c r="G28" s="151"/>
+      <c r="F28" s="143"/>
+      <c r="G28" s="143"/>
       <c r="H28" s="9" t="s">
         <v>51</v>
       </c>
       <c r="I28" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J28" s="151"/>
-      <c r="K28" s="151"/>
-      <c r="L28" s="151"/>
-      <c r="M28" s="151"/>
-      <c r="N28" s="116"/>
+      <c r="J28" s="143"/>
+      <c r="K28" s="143"/>
+      <c r="L28" s="143"/>
+      <c r="M28" s="143"/>
+      <c r="N28" s="108"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="148"/>
-      <c r="B29" s="149"/>
-      <c r="C29" s="149"/>
-      <c r="D29" s="150"/>
+      <c r="A29" s="140"/>
+      <c r="B29" s="141"/>
+      <c r="C29" s="141"/>
+      <c r="D29" s="142"/>
       <c r="E29" s="9"/>
-      <c r="F29" s="151"/>
-      <c r="G29" s="151"/>
+      <c r="F29" s="143"/>
+      <c r="G29" s="143"/>
       <c r="H29" s="9" t="s">
         <v>51</v>
       </c>
       <c r="I29" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J29" s="151"/>
-      <c r="K29" s="151"/>
-      <c r="L29" s="151"/>
-      <c r="M29" s="151"/>
-      <c r="N29" s="116"/>
+      <c r="J29" s="143"/>
+      <c r="K29" s="143"/>
+      <c r="L29" s="143"/>
+      <c r="M29" s="143"/>
+      <c r="N29" s="108"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" s="202" t="s">
+      <c r="A30" s="194" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="203"/>
-      <c r="C30" s="203"/>
-      <c r="D30" s="203"/>
+      <c r="B30" s="195"/>
+      <c r="C30" s="195"/>
+      <c r="D30" s="195"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="192"/>
-      <c r="G30" s="151"/>
-      <c r="H30" s="127"/>
-      <c r="I30" s="128"/>
-      <c r="J30" s="127"/>
-      <c r="K30" s="189"/>
-      <c r="L30" s="189"/>
-      <c r="M30" s="128"/>
-      <c r="N30" s="116"/>
+      <c r="F30" s="184"/>
+      <c r="G30" s="143"/>
+      <c r="H30" s="119"/>
+      <c r="I30" s="120"/>
+      <c r="J30" s="119"/>
+      <c r="K30" s="181"/>
+      <c r="L30" s="181"/>
+      <c r="M30" s="120"/>
+      <c r="N30" s="108"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A31" s="193" t="s">
+      <c r="A31" s="185" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="194"/>
-      <c r="C31" s="194"/>
-      <c r="D31" s="194"/>
-      <c r="E31" s="194"/>
-      <c r="F31" s="194"/>
-      <c r="G31" s="194"/>
-      <c r="H31" s="194"/>
-      <c r="I31" s="194"/>
-      <c r="J31" s="194"/>
-      <c r="K31" s="194"/>
-      <c r="L31" s="194"/>
-      <c r="M31" s="195"/>
-      <c r="N31" s="116"/>
+      <c r="B31" s="186"/>
+      <c r="C31" s="186"/>
+      <c r="D31" s="186"/>
+      <c r="E31" s="186"/>
+      <c r="F31" s="186"/>
+      <c r="G31" s="186"/>
+      <c r="H31" s="186"/>
+      <c r="I31" s="186"/>
+      <c r="J31" s="186"/>
+      <c r="K31" s="186"/>
+      <c r="L31" s="186"/>
+      <c r="M31" s="187"/>
+      <c r="N31" s="108"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A32" s="199" t="s">
+      <c r="A32" s="191" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="198"/>
-      <c r="C32" s="198" t="s">
+      <c r="B32" s="190"/>
+      <c r="C32" s="190" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="198"/>
-      <c r="E32" s="200" t="s">
+      <c r="D32" s="190"/>
+      <c r="E32" s="192" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="201" t="s">
+      <c r="F32" s="193" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="196" t="s">
+      <c r="G32" s="188" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="196"/>
-      <c r="I32" s="196"/>
-      <c r="J32" s="196"/>
-      <c r="K32" s="196"/>
-      <c r="L32" s="198" t="s">
+      <c r="H32" s="188"/>
+      <c r="I32" s="188"/>
+      <c r="J32" s="188"/>
+      <c r="K32" s="188"/>
+      <c r="L32" s="190" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="198"/>
-      <c r="N32" s="116"/>
+      <c r="M32" s="190"/>
+      <c r="N32" s="108"/>
     </row>
     <row r="33" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
@@ -7191,500 +7181,500 @@
       <c r="D33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="200"/>
-      <c r="F33" s="201"/>
-      <c r="G33" s="197" t="s">
+      <c r="E33" s="192"/>
+      <c r="F33" s="193"/>
+      <c r="G33" s="189" t="s">
         <v>50</v>
       </c>
-      <c r="H33" s="197"/>
-      <c r="I33" s="197"/>
-      <c r="J33" s="197"/>
-      <c r="K33" s="197"/>
+      <c r="H33" s="189"/>
+      <c r="I33" s="189"/>
+      <c r="J33" s="189"/>
+      <c r="K33" s="189"/>
       <c r="L33" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="N33" s="116"/>
+      <c r="N33" s="108"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A34" s="39"/>
+      <c r="A34" s="37"/>
       <c r="B34" s="9" t="s">
         <v>57</v>
       </c>
       <c r="C34" s="8"/>
-      <c r="D34" s="38" t="s">
+      <c r="D34" s="36" t="s">
         <v>57</v>
       </c>
       <c r="E34" s="8"/>
       <c r="F34" s="9"/>
-      <c r="G34" s="187" t="s">
+      <c r="G34" s="179" t="s">
         <v>71</v>
       </c>
-      <c r="H34" s="190"/>
-      <c r="I34" s="190"/>
-      <c r="J34" s="190"/>
-      <c r="K34" s="191"/>
-      <c r="L34" s="40"/>
-      <c r="M34" s="40"/>
-      <c r="N34" s="116"/>
+      <c r="H34" s="182"/>
+      <c r="I34" s="182"/>
+      <c r="J34" s="182"/>
+      <c r="K34" s="183"/>
+      <c r="L34" s="38"/>
+      <c r="M34" s="38"/>
+      <c r="N34" s="108"/>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A35" s="41"/>
+      <c r="A35" s="39"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="187"/>
-      <c r="H35" s="190"/>
-      <c r="I35" s="190"/>
-      <c r="J35" s="190"/>
-      <c r="K35" s="191"/>
-      <c r="L35" s="40"/>
-      <c r="M35" s="40"/>
-      <c r="N35" s="116"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="179"/>
+      <c r="H35" s="182"/>
+      <c r="I35" s="182"/>
+      <c r="J35" s="182"/>
+      <c r="K35" s="183"/>
+      <c r="L35" s="38"/>
+      <c r="M35" s="38"/>
+      <c r="N35" s="108"/>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A36" s="41"/>
+      <c r="A36" s="39"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="187"/>
-      <c r="H36" s="190"/>
-      <c r="I36" s="190"/>
-      <c r="J36" s="190"/>
-      <c r="K36" s="191"/>
-      <c r="L36" s="40"/>
-      <c r="M36" s="40"/>
-      <c r="N36" s="116"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="179"/>
+      <c r="H36" s="182"/>
+      <c r="I36" s="182"/>
+      <c r="J36" s="182"/>
+      <c r="K36" s="183"/>
+      <c r="L36" s="38"/>
+      <c r="M36" s="38"/>
+      <c r="N36" s="108"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A37" s="41"/>
+      <c r="A37" s="39"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="187"/>
-      <c r="H37" s="190"/>
-      <c r="I37" s="190"/>
-      <c r="J37" s="190"/>
-      <c r="K37" s="191"/>
-      <c r="L37" s="40"/>
-      <c r="M37" s="40"/>
-      <c r="N37" s="116"/>
-      <c r="P37" s="205"/>
-      <c r="Q37" s="205"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="179"/>
+      <c r="H37" s="182"/>
+      <c r="I37" s="182"/>
+      <c r="J37" s="182"/>
+      <c r="K37" s="183"/>
+      <c r="L37" s="38"/>
+      <c r="M37" s="38"/>
+      <c r="N37" s="108"/>
+      <c r="P37" s="197"/>
+      <c r="Q37" s="197"/>
       <c r="R37" s="6"/>
-      <c r="S37" s="204"/>
-      <c r="T37" s="204"/>
-      <c r="U37" s="204"/>
+      <c r="S37" s="196"/>
+      <c r="T37" s="196"/>
+      <c r="U37" s="196"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A38" s="41"/>
+      <c r="A38" s="39"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="187"/>
-      <c r="H38" s="190"/>
-      <c r="I38" s="190"/>
-      <c r="J38" s="190"/>
-      <c r="K38" s="191"/>
-      <c r="L38" s="40"/>
-      <c r="M38" s="117"/>
-      <c r="N38" s="116"/>
-      <c r="P38" s="205"/>
-      <c r="Q38" s="205"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="179"/>
+      <c r="H38" s="182"/>
+      <c r="I38" s="182"/>
+      <c r="J38" s="182"/>
+      <c r="K38" s="183"/>
+      <c r="L38" s="38"/>
+      <c r="M38" s="109"/>
+      <c r="N38" s="108"/>
+      <c r="P38" s="197"/>
+      <c r="Q38" s="197"/>
       <c r="R38" s="6"/>
-      <c r="S38" s="204"/>
-      <c r="T38" s="204"/>
-      <c r="U38" s="204"/>
+      <c r="S38" s="196"/>
+      <c r="T38" s="196"/>
+      <c r="U38" s="196"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A39" s="41"/>
+      <c r="A39" s="39"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
-      <c r="F39" s="40"/>
-      <c r="G39" s="187"/>
-      <c r="H39" s="190"/>
-      <c r="I39" s="190"/>
-      <c r="J39" s="190"/>
-      <c r="K39" s="191"/>
-      <c r="L39" s="40"/>
-      <c r="M39" s="117"/>
-      <c r="N39" s="116"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="179"/>
+      <c r="H39" s="182"/>
+      <c r="I39" s="182"/>
+      <c r="J39" s="182"/>
+      <c r="K39" s="183"/>
+      <c r="L39" s="38"/>
+      <c r="M39" s="109"/>
+      <c r="N39" s="108"/>
       <c r="P39" s="5"/>
       <c r="Q39" s="5"/>
-      <c r="R39" s="206"/>
-      <c r="S39" s="204"/>
-      <c r="T39" s="204"/>
-      <c r="U39" s="204"/>
+      <c r="R39" s="198"/>
+      <c r="S39" s="196"/>
+      <c r="T39" s="196"/>
+      <c r="U39" s="196"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A40" s="41"/>
+      <c r="A40" s="39"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
-      <c r="F40" s="40"/>
-      <c r="G40" s="187"/>
-      <c r="H40" s="190"/>
-      <c r="I40" s="190"/>
-      <c r="J40" s="190"/>
-      <c r="K40" s="191"/>
-      <c r="L40" s="40"/>
-      <c r="M40" s="40"/>
-      <c r="N40" s="116"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="179"/>
+      <c r="H40" s="182"/>
+      <c r="I40" s="182"/>
+      <c r="J40" s="182"/>
+      <c r="K40" s="183"/>
+      <c r="L40" s="38"/>
+      <c r="M40" s="38"/>
+      <c r="N40" s="108"/>
       <c r="P40" s="5"/>
       <c r="Q40" s="5"/>
-      <c r="R40" s="206"/>
-      <c r="S40" s="204"/>
-      <c r="T40" s="204"/>
-      <c r="U40" s="204"/>
+      <c r="R40" s="198"/>
+      <c r="S40" s="196"/>
+      <c r="T40" s="196"/>
+      <c r="U40" s="196"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A41" s="41"/>
+      <c r="A41" s="39"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
-      <c r="F41" s="40"/>
-      <c r="G41" s="187"/>
-      <c r="H41" s="190"/>
-      <c r="I41" s="190"/>
-      <c r="J41" s="190"/>
-      <c r="K41" s="191"/>
-      <c r="L41" s="40"/>
-      <c r="M41" s="40"/>
-      <c r="N41" s="116"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="179"/>
+      <c r="H41" s="182"/>
+      <c r="I41" s="182"/>
+      <c r="J41" s="182"/>
+      <c r="K41" s="183"/>
+      <c r="L41" s="38"/>
+      <c r="M41" s="38"/>
+      <c r="N41" s="108"/>
     </row>
     <row r="42" spans="1:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="42"/>
-      <c r="B42" s="43"/>
-      <c r="C42" s="44"/>
-      <c r="D42" s="43"/>
-      <c r="E42" s="44"/>
-      <c r="F42" s="45"/>
-      <c r="G42" s="213" t="s">
+      <c r="A42" s="40"/>
+      <c r="B42" s="41"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="205" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="214"/>
-      <c r="I42" s="214"/>
-      <c r="J42" s="214"/>
-      <c r="K42" s="215"/>
-      <c r="L42" s="45"/>
-      <c r="M42" s="45"/>
-      <c r="N42" s="116"/>
+      <c r="H42" s="206"/>
+      <c r="I42" s="206"/>
+      <c r="J42" s="206"/>
+      <c r="K42" s="207"/>
+      <c r="L42" s="43"/>
+      <c r="M42" s="43"/>
+      <c r="N42" s="108"/>
     </row>
     <row r="43" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="223" t="s">
+      <c r="A43" s="215" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="224"/>
-      <c r="C43" s="224"/>
-      <c r="D43" s="224"/>
-      <c r="E43" s="224"/>
-      <c r="F43" s="224"/>
-      <c r="G43" s="224"/>
-      <c r="H43" s="225"/>
-      <c r="I43" s="292" t="s">
+      <c r="B43" s="216"/>
+      <c r="C43" s="216"/>
+      <c r="D43" s="216"/>
+      <c r="E43" s="216"/>
+      <c r="F43" s="216"/>
+      <c r="G43" s="216"/>
+      <c r="H43" s="217"/>
+      <c r="I43" s="284" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="293"/>
-      <c r="K43" s="293"/>
-      <c r="L43" s="293"/>
-      <c r="M43" s="294"/>
-      <c r="N43" s="116"/>
+      <c r="J43" s="285"/>
+      <c r="K43" s="285"/>
+      <c r="L43" s="285"/>
+      <c r="M43" s="286"/>
+      <c r="N43" s="108"/>
     </row>
     <row r="44" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="226"/>
-      <c r="B44" s="227"/>
-      <c r="C44" s="227"/>
-      <c r="D44" s="227"/>
-      <c r="E44" s="227"/>
-      <c r="F44" s="227"/>
-      <c r="G44" s="227"/>
-      <c r="H44" s="228"/>
-      <c r="I44" s="295"/>
-      <c r="J44" s="296"/>
-      <c r="K44" s="296"/>
-      <c r="L44" s="296"/>
-      <c r="M44" s="297"/>
-      <c r="N44" s="116"/>
+      <c r="A44" s="218"/>
+      <c r="B44" s="219"/>
+      <c r="C44" s="219"/>
+      <c r="D44" s="219"/>
+      <c r="E44" s="219"/>
+      <c r="F44" s="219"/>
+      <c r="G44" s="219"/>
+      <c r="H44" s="220"/>
+      <c r="I44" s="287"/>
+      <c r="J44" s="288"/>
+      <c r="K44" s="288"/>
+      <c r="L44" s="288"/>
+      <c r="M44" s="289"/>
+      <c r="N44" s="108"/>
     </row>
     <row r="45" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="232" t="s">
+      <c r="A45" s="224" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="233"/>
-      <c r="C45" s="233"/>
-      <c r="D45" s="233"/>
-      <c r="E45" s="233"/>
-      <c r="F45" s="233"/>
-      <c r="G45" s="233"/>
-      <c r="H45" s="234"/>
-      <c r="I45" s="301" t="s">
+      <c r="B45" s="225"/>
+      <c r="C45" s="225"/>
+      <c r="D45" s="225"/>
+      <c r="E45" s="225"/>
+      <c r="F45" s="225"/>
+      <c r="G45" s="225"/>
+      <c r="H45" s="226"/>
+      <c r="I45" s="293" t="s">
         <v>83</v>
       </c>
-      <c r="J45" s="302"/>
-      <c r="K45" s="302"/>
-      <c r="L45" s="302"/>
-      <c r="M45" s="303"/>
-      <c r="N45" s="116"/>
+      <c r="J45" s="294"/>
+      <c r="K45" s="294"/>
+      <c r="L45" s="294"/>
+      <c r="M45" s="295"/>
+      <c r="N45" s="108"/>
     </row>
     <row r="46" spans="1:21" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="232" t="s">
+      <c r="A46" s="224" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="233"/>
-      <c r="C46" s="233"/>
-      <c r="D46" s="233"/>
-      <c r="E46" s="233"/>
-      <c r="F46" s="233"/>
-      <c r="G46" s="233"/>
-      <c r="H46" s="234"/>
-      <c r="I46" s="301"/>
-      <c r="J46" s="302"/>
-      <c r="K46" s="302"/>
-      <c r="L46" s="302"/>
-      <c r="M46" s="303"/>
-      <c r="N46" s="116"/>
+      <c r="B46" s="225"/>
+      <c r="C46" s="225"/>
+      <c r="D46" s="225"/>
+      <c r="E46" s="225"/>
+      <c r="F46" s="225"/>
+      <c r="G46" s="225"/>
+      <c r="H46" s="226"/>
+      <c r="I46" s="293"/>
+      <c r="J46" s="294"/>
+      <c r="K46" s="294"/>
+      <c r="L46" s="294"/>
+      <c r="M46" s="295"/>
+      <c r="N46" s="108"/>
     </row>
     <row r="47" spans="1:21" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="235"/>
-      <c r="B47" s="236"/>
-      <c r="C47" s="236"/>
-      <c r="D47" s="236"/>
-      <c r="E47" s="236"/>
-      <c r="F47" s="236"/>
-      <c r="G47" s="236"/>
-      <c r="H47" s="237"/>
-      <c r="I47" s="307" t="s">
+      <c r="A47" s="227"/>
+      <c r="B47" s="228"/>
+      <c r="C47" s="228"/>
+      <c r="D47" s="228"/>
+      <c r="E47" s="228"/>
+      <c r="F47" s="228"/>
+      <c r="G47" s="228"/>
+      <c r="H47" s="229"/>
+      <c r="I47" s="299" t="s">
         <v>84</v>
       </c>
-      <c r="J47" s="308"/>
-      <c r="K47" s="308"/>
-      <c r="L47" s="308"/>
-      <c r="M47" s="309"/>
-      <c r="N47" s="116"/>
+      <c r="J47" s="300"/>
+      <c r="K47" s="300"/>
+      <c r="L47" s="300"/>
+      <c r="M47" s="301"/>
+      <c r="N47" s="108"/>
     </row>
     <row r="48" spans="1:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="216" t="s">
+      <c r="A48" s="208" t="s">
         <v>36</v>
       </c>
-      <c r="B48" s="207"/>
-      <c r="C48" s="207"/>
-      <c r="D48" s="207"/>
-      <c r="E48" s="207"/>
-      <c r="F48" s="207"/>
-      <c r="G48" s="207"/>
-      <c r="H48" s="207"/>
-      <c r="I48" s="207"/>
-      <c r="J48" s="207"/>
-      <c r="K48" s="207"/>
-      <c r="L48" s="207"/>
-      <c r="M48" s="208"/>
-      <c r="N48" s="116"/>
+      <c r="B48" s="199"/>
+      <c r="C48" s="199"/>
+      <c r="D48" s="199"/>
+      <c r="E48" s="199"/>
+      <c r="F48" s="199"/>
+      <c r="G48" s="199"/>
+      <c r="H48" s="199"/>
+      <c r="I48" s="199"/>
+      <c r="J48" s="199"/>
+      <c r="K48" s="199"/>
+      <c r="L48" s="199"/>
+      <c r="M48" s="200"/>
+      <c r="N48" s="108"/>
     </row>
     <row r="49" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="223" t="s">
+      <c r="A49" s="215" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="224"/>
-      <c r="C49" s="224"/>
-      <c r="D49" s="224"/>
-      <c r="E49" s="224"/>
-      <c r="F49" s="224"/>
-      <c r="G49" s="224"/>
-      <c r="H49" s="225"/>
-      <c r="I49" s="217" t="s">
+      <c r="B49" s="216"/>
+      <c r="C49" s="216"/>
+      <c r="D49" s="216"/>
+      <c r="E49" s="216"/>
+      <c r="F49" s="216"/>
+      <c r="G49" s="216"/>
+      <c r="H49" s="217"/>
+      <c r="I49" s="209" t="s">
         <v>38</v>
       </c>
-      <c r="J49" s="218"/>
-      <c r="K49" s="218"/>
-      <c r="L49" s="218"/>
-      <c r="M49" s="219"/>
-      <c r="N49" s="116"/>
+      <c r="J49" s="210"/>
+      <c r="K49" s="210"/>
+      <c r="L49" s="210"/>
+      <c r="M49" s="211"/>
+      <c r="N49" s="108"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A50" s="226"/>
-      <c r="B50" s="227"/>
-      <c r="C50" s="227"/>
-      <c r="D50" s="227"/>
-      <c r="E50" s="227"/>
-      <c r="F50" s="227"/>
-      <c r="G50" s="227"/>
-      <c r="H50" s="228"/>
-      <c r="I50" s="220"/>
-      <c r="J50" s="221"/>
-      <c r="K50" s="221"/>
-      <c r="L50" s="221"/>
-      <c r="M50" s="222"/>
-      <c r="N50" s="116"/>
+      <c r="A50" s="218"/>
+      <c r="B50" s="219"/>
+      <c r="C50" s="219"/>
+      <c r="D50" s="219"/>
+      <c r="E50" s="219"/>
+      <c r="F50" s="219"/>
+      <c r="G50" s="219"/>
+      <c r="H50" s="220"/>
+      <c r="I50" s="212"/>
+      <c r="J50" s="213"/>
+      <c r="K50" s="213"/>
+      <c r="L50" s="213"/>
+      <c r="M50" s="214"/>
+      <c r="N50" s="108"/>
     </row>
     <row r="51" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="229"/>
-      <c r="B51" s="230"/>
-      <c r="C51" s="230"/>
-      <c r="D51" s="230"/>
-      <c r="E51" s="230"/>
-      <c r="F51" s="230"/>
-      <c r="G51" s="230"/>
-      <c r="H51" s="231"/>
-      <c r="I51" s="238" t="s">
+      <c r="A51" s="221"/>
+      <c r="B51" s="222"/>
+      <c r="C51" s="222"/>
+      <c r="D51" s="222"/>
+      <c r="E51" s="222"/>
+      <c r="F51" s="222"/>
+      <c r="G51" s="222"/>
+      <c r="H51" s="223"/>
+      <c r="I51" s="230" t="s">
         <v>39</v>
       </c>
-      <c r="J51" s="239"/>
-      <c r="K51" s="239"/>
-      <c r="L51" s="239"/>
-      <c r="M51" s="240"/>
-      <c r="N51" s="116"/>
+      <c r="J51" s="231"/>
+      <c r="K51" s="231"/>
+      <c r="L51" s="231"/>
+      <c r="M51" s="232"/>
+      <c r="N51" s="108"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A52" s="216" t="s">
+      <c r="A52" s="208" t="s">
         <v>40</v>
       </c>
-      <c r="B52" s="207"/>
-      <c r="C52" s="207"/>
-      <c r="D52" s="207"/>
-      <c r="E52" s="76" t="s">
+      <c r="B52" s="199"/>
+      <c r="C52" s="199"/>
+      <c r="D52" s="199"/>
+      <c r="E52" s="74" t="s">
         <v>42</v>
       </c>
-      <c r="F52" s="77"/>
-      <c r="G52" s="284" t="s">
+      <c r="F52" s="75"/>
+      <c r="G52" s="276" t="s">
         <v>43</v>
       </c>
-      <c r="H52" s="284"/>
-      <c r="I52" s="284"/>
-      <c r="J52" s="285"/>
-      <c r="K52" s="207" t="s">
+      <c r="H52" s="276"/>
+      <c r="I52" s="276"/>
+      <c r="J52" s="277"/>
+      <c r="K52" s="199" t="s">
         <v>47</v>
       </c>
-      <c r="L52" s="207"/>
-      <c r="M52" s="208"/>
-      <c r="N52" s="116"/>
+      <c r="L52" s="199"/>
+      <c r="M52" s="200"/>
+      <c r="N52" s="108"/>
     </row>
     <row r="53" spans="1:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="241" t="s">
+      <c r="A53" s="233" t="s">
         <v>41</v>
       </c>
-      <c r="B53" s="242"/>
-      <c r="C53" s="242"/>
-      <c r="D53" s="242"/>
-      <c r="E53" s="78"/>
-      <c r="F53" s="71"/>
-      <c r="G53" s="71"/>
-      <c r="H53" s="71"/>
-      <c r="I53" s="71"/>
-      <c r="J53" s="79"/>
-      <c r="K53" s="209" t="s">
+      <c r="B53" s="234"/>
+      <c r="C53" s="234"/>
+      <c r="D53" s="234"/>
+      <c r="E53" s="76"/>
+      <c r="F53" s="69"/>
+      <c r="G53" s="69"/>
+      <c r="H53" s="69"/>
+      <c r="I53" s="69"/>
+      <c r="J53" s="77"/>
+      <c r="K53" s="201" t="s">
         <v>49</v>
       </c>
-      <c r="L53" s="209"/>
-      <c r="M53" s="210"/>
-      <c r="N53" s="116"/>
+      <c r="L53" s="201"/>
+      <c r="M53" s="202"/>
+      <c r="N53" s="108"/>
     </row>
     <row r="54" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="241"/>
-      <c r="B54" s="242"/>
-      <c r="C54" s="242"/>
-      <c r="D54" s="242"/>
-      <c r="E54" s="253" t="s">
+      <c r="A54" s="233"/>
+      <c r="B54" s="234"/>
+      <c r="C54" s="234"/>
+      <c r="D54" s="234"/>
+      <c r="E54" s="245" t="s">
         <v>81</v>
       </c>
-      <c r="F54" s="254"/>
-      <c r="G54" s="414" t="s">
+      <c r="F54" s="246"/>
+      <c r="G54" s="406" t="s">
         <v>80</v>
       </c>
-      <c r="H54" s="243" t="s">
+      <c r="H54" s="235" t="s">
         <v>44</v>
       </c>
-      <c r="I54" s="243"/>
-      <c r="J54" s="244"/>
-      <c r="K54" s="209"/>
-      <c r="L54" s="209"/>
-      <c r="M54" s="210"/>
-      <c r="N54" s="116"/>
+      <c r="I54" s="235"/>
+      <c r="J54" s="236"/>
+      <c r="K54" s="201"/>
+      <c r="L54" s="201"/>
+      <c r="M54" s="202"/>
+      <c r="N54" s="108"/>
     </row>
     <row r="55" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="241"/>
-      <c r="B55" s="242"/>
-      <c r="C55" s="242"/>
-      <c r="D55" s="242"/>
-      <c r="E55" s="253" t="s">
+      <c r="A55" s="233"/>
+      <c r="B55" s="234"/>
+      <c r="C55" s="234"/>
+      <c r="D55" s="234"/>
+      <c r="E55" s="245" t="s">
         <v>82</v>
       </c>
-      <c r="F55" s="254"/>
-      <c r="G55" s="415" t="s">
+      <c r="F55" s="246"/>
+      <c r="G55" s="407" t="s">
         <v>80</v>
       </c>
-      <c r="H55" s="243" t="s">
+      <c r="H55" s="235" t="s">
         <v>45</v>
       </c>
-      <c r="I55" s="243"/>
-      <c r="J55" s="244"/>
-      <c r="K55" s="209"/>
-      <c r="L55" s="209"/>
-      <c r="M55" s="210"/>
-      <c r="N55" s="116"/>
+      <c r="I55" s="235"/>
+      <c r="J55" s="236"/>
+      <c r="K55" s="201"/>
+      <c r="L55" s="201"/>
+      <c r="M55" s="202"/>
+      <c r="N55" s="108"/>
     </row>
     <row r="56" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="37"/>
-      <c r="D56" s="36"/>
-      <c r="E56" s="253"/>
-      <c r="F56" s="254"/>
-      <c r="G56" s="415"/>
-      <c r="H56" s="243"/>
-      <c r="I56" s="243"/>
-      <c r="J56" s="244"/>
-      <c r="K56" s="211" t="s">
+      <c r="A56" s="35"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="245"/>
+      <c r="F56" s="246"/>
+      <c r="G56" s="407"/>
+      <c r="H56" s="235"/>
+      <c r="I56" s="235"/>
+      <c r="J56" s="236"/>
+      <c r="K56" s="203" t="s">
         <v>48</v>
       </c>
-      <c r="L56" s="211"/>
-      <c r="M56" s="212"/>
-      <c r="N56" s="116"/>
+      <c r="L56" s="203"/>
+      <c r="M56" s="204"/>
+      <c r="N56" s="108"/>
     </row>
     <row r="57" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="37"/>
-      <c r="D57" s="36"/>
-      <c r="E57" s="253"/>
-      <c r="F57" s="254"/>
-      <c r="G57" s="414" t="s">
+      <c r="A57" s="35"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="245"/>
+      <c r="F57" s="246"/>
+      <c r="G57" s="406" t="s">
         <v>80</v>
       </c>
-      <c r="H57" s="243" t="s">
+      <c r="H57" s="235" t="s">
         <v>46</v>
       </c>
-      <c r="I57" s="243"/>
-      <c r="J57" s="244"/>
-      <c r="K57" s="46"/>
-      <c r="L57" s="115"/>
-      <c r="M57" s="118"/>
-      <c r="N57" s="116"/>
+      <c r="I57" s="235"/>
+      <c r="J57" s="236"/>
+      <c r="K57" s="44"/>
+      <c r="L57" s="107"/>
+      <c r="M57" s="110"/>
+      <c r="N57" s="108"/>
     </row>
     <row r="58" spans="1:14" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="47"/>
-      <c r="B58" s="126"/>
-      <c r="C58" s="126"/>
-      <c r="D58" s="32"/>
-      <c r="E58" s="245"/>
-      <c r="F58" s="246"/>
-      <c r="G58" s="246"/>
-      <c r="H58" s="246"/>
-      <c r="I58" s="246"/>
-      <c r="J58" s="247"/>
-      <c r="K58" s="48"/>
-      <c r="L58" s="49"/>
-      <c r="M58" s="119"/>
-      <c r="N58" s="116"/>
+      <c r="A58" s="45"/>
+      <c r="B58" s="118"/>
+      <c r="C58" s="118"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="237"/>
+      <c r="F58" s="238"/>
+      <c r="G58" s="238"/>
+      <c r="H58" s="238"/>
+      <c r="I58" s="238"/>
+      <c r="J58" s="239"/>
+      <c r="K58" s="46"/>
+      <c r="L58" s="47"/>
+      <c r="M58" s="111"/>
+      <c r="N58" s="108"/>
     </row>
     <row r="59" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3"/>
@@ -7699,7 +7689,9 @@
       <c r="J59" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="110">
+  <mergeCells count="111">
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="A17:H18"/>
     <mergeCell ref="E58:J58"/>
     <mergeCell ref="I47:M47"/>
     <mergeCell ref="H55:J56"/>
@@ -7786,7 +7778,6 @@
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F17:H17"/>
     <mergeCell ref="I11:J11"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B58:C58"/>

--- a/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
+++ b/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Procomm\Documents\GitHub\Acumatica_Customizations_and_Packages\Istar_Development\Projects\BOL_Generation\Code\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93E07A3-DE6F-4B55-8D62-0B059AD9C45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7014F9B9-38B0-48A2-B7A1-405CAF8EE714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{888CA347-7849-4038-B8EE-FAC87BA1B844}"/>
+    <workbookView xWindow="2640" yWindow="2640" windowWidth="28800" windowHeight="15345" xr2:uid="{888CA347-7849-4038-B8EE-FAC87BA1B844}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterBOL" sheetId="3" r:id="rId1"/>
@@ -1018,7 +1018,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="415">
+  <cellXfs count="417">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1189,7 +1189,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -2129,6 +2128,13 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3408,125 +3414,125 @@
       <c r="A1" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="379" t="s">
+      <c r="B1" s="415"/>
+      <c r="C1" s="416"/>
+      <c r="D1" s="378" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="380"/>
-      <c r="E1" s="380"/>
-      <c r="F1" s="380"/>
-      <c r="G1" s="380"/>
-      <c r="H1" s="380"/>
-      <c r="I1" s="380"/>
-      <c r="J1" s="380"/>
-      <c r="K1" s="381"/>
-      <c r="L1" s="382" t="s">
+      <c r="E1" s="379"/>
+      <c r="F1" s="379"/>
+      <c r="G1" s="379"/>
+      <c r="H1" s="379"/>
+      <c r="I1" s="379"/>
+      <c r="J1" s="379"/>
+      <c r="K1" s="380"/>
+      <c r="L1" s="381" t="s">
         <v>58</v>
       </c>
-      <c r="M1" s="383"/>
+      <c r="M1" s="382"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="312" t="s">
+      <c r="A2" s="311" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="313"/>
-      <c r="C2" s="313"/>
-      <c r="D2" s="313"/>
-      <c r="E2" s="313"/>
-      <c r="F2" s="313"/>
-      <c r="G2" s="313"/>
-      <c r="H2" s="314"/>
-      <c r="I2" s="384" t="s">
+      <c r="B2" s="312"/>
+      <c r="C2" s="312"/>
+      <c r="D2" s="312"/>
+      <c r="E2" s="312"/>
+      <c r="F2" s="312"/>
+      <c r="G2" s="312"/>
+      <c r="H2" s="313"/>
+      <c r="I2" s="383" t="s">
         <v>73</v>
       </c>
-      <c r="J2" s="385"/>
-      <c r="K2" s="385"/>
-      <c r="L2" s="385"/>
-      <c r="M2" s="386"/>
+      <c r="J2" s="384"/>
+      <c r="K2" s="384"/>
+      <c r="L2" s="384"/>
+      <c r="M2" s="385"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="364" t="s">
+      <c r="A3" s="363" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="365"/>
-      <c r="C3" s="365"/>
-      <c r="D3" s="365"/>
-      <c r="E3" s="365"/>
-      <c r="F3" s="365"/>
-      <c r="G3" s="365"/>
-      <c r="H3" s="366"/>
-      <c r="I3" s="384"/>
-      <c r="J3" s="385"/>
-      <c r="K3" s="385"/>
-      <c r="L3" s="385"/>
-      <c r="M3" s="386"/>
+      <c r="B3" s="364"/>
+      <c r="C3" s="364"/>
+      <c r="D3" s="364"/>
+      <c r="E3" s="364"/>
+      <c r="F3" s="364"/>
+      <c r="G3" s="364"/>
+      <c r="H3" s="365"/>
+      <c r="I3" s="383"/>
+      <c r="J3" s="384"/>
+      <c r="K3" s="384"/>
+      <c r="L3" s="384"/>
+      <c r="M3" s="385"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="364" t="s">
+      <c r="A4" s="363" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="365"/>
-      <c r="C4" s="365"/>
-      <c r="D4" s="365"/>
-      <c r="E4" s="365"/>
-      <c r="F4" s="365"/>
-      <c r="G4" s="365"/>
-      <c r="H4" s="366"/>
-      <c r="I4" s="370"/>
-      <c r="J4" s="371"/>
-      <c r="K4" s="371"/>
-      <c r="L4" s="371"/>
-      <c r="M4" s="372"/>
+      <c r="B4" s="364"/>
+      <c r="C4" s="364"/>
+      <c r="D4" s="364"/>
+      <c r="E4" s="364"/>
+      <c r="F4" s="364"/>
+      <c r="G4" s="364"/>
+      <c r="H4" s="365"/>
+      <c r="I4" s="369"/>
+      <c r="J4" s="370"/>
+      <c r="K4" s="370"/>
+      <c r="L4" s="370"/>
+      <c r="M4" s="371"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="364" t="s">
+      <c r="A5" s="363" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="365"/>
-      <c r="C5" s="365"/>
-      <c r="D5" s="365"/>
-      <c r="E5" s="365"/>
-      <c r="F5" s="365"/>
-      <c r="G5" s="365"/>
-      <c r="H5" s="366"/>
-      <c r="I5" s="370"/>
-      <c r="J5" s="371"/>
-      <c r="K5" s="371"/>
-      <c r="L5" s="371"/>
-      <c r="M5" s="372"/>
+      <c r="B5" s="364"/>
+      <c r="C5" s="364"/>
+      <c r="D5" s="364"/>
+      <c r="E5" s="364"/>
+      <c r="F5" s="364"/>
+      <c r="G5" s="364"/>
+      <c r="H5" s="365"/>
+      <c r="I5" s="369"/>
+      <c r="J5" s="370"/>
+      <c r="K5" s="370"/>
+      <c r="L5" s="370"/>
+      <c r="M5" s="371"/>
     </row>
     <row r="6" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="376" t="s">
+      <c r="A6" s="375" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="377"/>
-      <c r="C6" s="377"/>
-      <c r="D6" s="377"/>
-      <c r="E6" s="377"/>
-      <c r="F6" s="378" t="s">
+      <c r="B6" s="376"/>
+      <c r="C6" s="376"/>
+      <c r="D6" s="376"/>
+      <c r="E6" s="376"/>
+      <c r="F6" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="378"/>
-      <c r="H6" s="410" t="s">
+      <c r="G6" s="377"/>
+      <c r="H6" s="409" t="s">
         <v>80</v>
       </c>
-      <c r="I6" s="373"/>
-      <c r="J6" s="374"/>
-      <c r="K6" s="374"/>
-      <c r="L6" s="374"/>
-      <c r="M6" s="375"/>
+      <c r="I6" s="372"/>
+      <c r="J6" s="373"/>
+      <c r="K6" s="373"/>
+      <c r="L6" s="373"/>
+      <c r="M6" s="374"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="352" t="s">
+      <c r="A7" s="351" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="353"/>
-      <c r="C7" s="353"/>
-      <c r="D7" s="353"/>
-      <c r="E7" s="353"/>
-      <c r="F7" s="353"/>
-      <c r="G7" s="353"/>
-      <c r="H7" s="354"/>
+      <c r="B7" s="352"/>
+      <c r="C7" s="352"/>
+      <c r="D7" s="352"/>
+      <c r="E7" s="352"/>
+      <c r="F7" s="352"/>
+      <c r="G7" s="352"/>
+      <c r="H7" s="353"/>
       <c r="I7" s="49" t="s">
         <v>74</v>
       </c>
@@ -3536,37 +3542,37 @@
       <c r="M7" s="52"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="367" t="s">
+      <c r="A8" s="366" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="368"/>
-      <c r="C8" s="368"/>
-      <c r="D8" s="368"/>
-      <c r="E8" s="248" t="s">
+      <c r="B8" s="367"/>
+      <c r="C8" s="367"/>
+      <c r="D8" s="367"/>
+      <c r="E8" s="247" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="248"/>
-      <c r="G8" s="248"/>
-      <c r="H8" s="249"/>
-      <c r="I8" s="367" t="s">
+      <c r="F8" s="247"/>
+      <c r="G8" s="247"/>
+      <c r="H8" s="248"/>
+      <c r="I8" s="366" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="368"/>
-      <c r="K8" s="368"/>
-      <c r="L8" s="368"/>
-      <c r="M8" s="369"/>
+      <c r="J8" s="367"/>
+      <c r="K8" s="367"/>
+      <c r="L8" s="367"/>
+      <c r="M8" s="368"/>
     </row>
     <row r="9" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="367" t="s">
+      <c r="A9" s="366" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="368"/>
-      <c r="C9" s="368"/>
-      <c r="D9" s="368"/>
-      <c r="E9" s="368"/>
-      <c r="F9" s="368"/>
-      <c r="G9" s="368"/>
-      <c r="H9" s="369"/>
+      <c r="B9" s="367"/>
+      <c r="C9" s="367"/>
+      <c r="D9" s="367"/>
+      <c r="E9" s="367"/>
+      <c r="F9" s="367"/>
+      <c r="G9" s="367"/>
+      <c r="H9" s="368"/>
       <c r="I9" s="53" t="s">
         <v>68</v>
       </c>
@@ -3576,16 +3582,16 @@
       <c r="M9" s="48"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="367" t="s">
+      <c r="A10" s="366" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="368"/>
-      <c r="C10" s="368"/>
-      <c r="D10" s="368"/>
-      <c r="E10" s="368"/>
-      <c r="F10" s="368"/>
-      <c r="G10" s="368"/>
-      <c r="H10" s="369"/>
+      <c r="B10" s="367"/>
+      <c r="C10" s="367"/>
+      <c r="D10" s="367"/>
+      <c r="E10" s="367"/>
+      <c r="F10" s="367"/>
+      <c r="G10" s="367"/>
+      <c r="H10" s="368"/>
       <c r="I10" s="55" t="s">
         <v>75</v>
       </c>
@@ -3595,18 +3601,18 @@
       <c r="M10" s="57"/>
     </row>
     <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="349" t="s">
+      <c r="A11" s="348" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="350"/>
-      <c r="C11" s="350"/>
-      <c r="D11" s="350"/>
-      <c r="E11" s="350"/>
-      <c r="F11" s="351" t="s">
+      <c r="B11" s="349"/>
+      <c r="C11" s="349"/>
+      <c r="D11" s="349"/>
+      <c r="E11" s="349"/>
+      <c r="F11" s="350" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="351"/>
-      <c r="H11" s="410" t="s">
+      <c r="G11" s="350"/>
+      <c r="H11" s="409" t="s">
         <v>80</v>
       </c>
       <c r="I11" s="58" t="s">
@@ -3618,74 +3624,74 @@
       <c r="M11" s="60"/>
     </row>
     <row r="12" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="352" t="s">
+      <c r="A12" s="351" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="353"/>
-      <c r="C12" s="353"/>
-      <c r="D12" s="353"/>
-      <c r="E12" s="353"/>
-      <c r="F12" s="353"/>
-      <c r="G12" s="353"/>
-      <c r="H12" s="354"/>
-      <c r="I12" s="355"/>
-      <c r="J12" s="356"/>
-      <c r="K12" s="356"/>
-      <c r="L12" s="356"/>
-      <c r="M12" s="357"/>
+      <c r="B12" s="352"/>
+      <c r="C12" s="352"/>
+      <c r="D12" s="352"/>
+      <c r="E12" s="352"/>
+      <c r="F12" s="352"/>
+      <c r="G12" s="352"/>
+      <c r="H12" s="353"/>
+      <c r="I12" s="354"/>
+      <c r="J12" s="355"/>
+      <c r="K12" s="355"/>
+      <c r="L12" s="355"/>
+      <c r="M12" s="356"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="361" t="s">
+      <c r="A13" s="360" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="362"/>
-      <c r="C13" s="362"/>
-      <c r="D13" s="362"/>
-      <c r="E13" s="362"/>
-      <c r="F13" s="362"/>
-      <c r="G13" s="362"/>
-      <c r="H13" s="363"/>
-      <c r="I13" s="355"/>
-      <c r="J13" s="356"/>
-      <c r="K13" s="356"/>
-      <c r="L13" s="356"/>
-      <c r="M13" s="357"/>
+      <c r="B13" s="361"/>
+      <c r="C13" s="361"/>
+      <c r="D13" s="361"/>
+      <c r="E13" s="361"/>
+      <c r="F13" s="361"/>
+      <c r="G13" s="361"/>
+      <c r="H13" s="362"/>
+      <c r="I13" s="354"/>
+      <c r="J13" s="355"/>
+      <c r="K13" s="355"/>
+      <c r="L13" s="355"/>
+      <c r="M13" s="356"/>
     </row>
     <row r="14" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="364" t="s">
+      <c r="A14" s="363" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="365"/>
-      <c r="C14" s="365"/>
-      <c r="D14" s="365"/>
-      <c r="E14" s="365"/>
-      <c r="F14" s="365"/>
-      <c r="G14" s="365"/>
-      <c r="H14" s="366"/>
-      <c r="I14" s="358"/>
-      <c r="J14" s="359"/>
-      <c r="K14" s="359"/>
-      <c r="L14" s="359"/>
-      <c r="M14" s="360"/>
+      <c r="B14" s="364"/>
+      <c r="C14" s="364"/>
+      <c r="D14" s="364"/>
+      <c r="E14" s="364"/>
+      <c r="F14" s="364"/>
+      <c r="G14" s="364"/>
+      <c r="H14" s="365"/>
+      <c r="I14" s="357"/>
+      <c r="J14" s="358"/>
+      <c r="K14" s="358"/>
+      <c r="L14" s="358"/>
+      <c r="M14" s="359"/>
     </row>
     <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="337" t="s">
+      <c r="A15" s="336" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="338"/>
-      <c r="C15" s="338"/>
-      <c r="D15" s="338"/>
-      <c r="E15" s="338"/>
-      <c r="F15" s="338"/>
-      <c r="G15" s="338"/>
-      <c r="H15" s="338"/>
-      <c r="I15" s="339" t="s">
+      <c r="B15" s="337"/>
+      <c r="C15" s="337"/>
+      <c r="D15" s="337"/>
+      <c r="E15" s="337"/>
+      <c r="F15" s="337"/>
+      <c r="G15" s="337"/>
+      <c r="H15" s="337"/>
+      <c r="I15" s="338" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="340"/>
-      <c r="K15" s="340"/>
-      <c r="L15" s="340"/>
-      <c r="M15" s="341"/>
+      <c r="J15" s="339"/>
+      <c r="K15" s="339"/>
+      <c r="L15" s="339"/>
+      <c r="M15" s="340"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="61" t="s">
@@ -3695,16 +3701,16 @@
       <c r="C16" s="62"/>
       <c r="D16" s="62"/>
       <c r="E16" s="62"/>
-      <c r="F16" s="240"/>
-      <c r="G16" s="240"/>
-      <c r="H16" s="241"/>
-      <c r="I16" s="342" t="s">
+      <c r="F16" s="239"/>
+      <c r="G16" s="239"/>
+      <c r="H16" s="240"/>
+      <c r="I16" s="341" t="s">
         <v>78</v>
       </c>
-      <c r="J16" s="343"/>
-      <c r="K16" s="343"/>
-      <c r="L16" s="343"/>
-      <c r="M16" s="344"/>
+      <c r="J16" s="342"/>
+      <c r="K16" s="342"/>
+      <c r="L16" s="342"/>
+      <c r="M16" s="343"/>
     </row>
     <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="63"/>
@@ -3715,15 +3721,15 @@
       <c r="F17" s="64"/>
       <c r="G17" s="64"/>
       <c r="H17" s="65"/>
-      <c r="I17" s="408" t="s">
+      <c r="I17" s="407" t="s">
         <v>80</v>
       </c>
-      <c r="J17" s="409"/>
-      <c r="K17" s="345" t="s">
+      <c r="J17" s="408"/>
+      <c r="K17" s="344" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="345"/>
-      <c r="M17" s="346"/>
+      <c r="L17" s="344"/>
+      <c r="M17" s="345"/>
     </row>
     <row r="18" spans="1:13" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="63"/>
@@ -3734,285 +3740,285 @@
       <c r="F18" s="64"/>
       <c r="G18" s="64"/>
       <c r="H18" s="65"/>
-      <c r="I18" s="237" t="s">
+      <c r="I18" s="236" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="238"/>
-      <c r="K18" s="347"/>
-      <c r="L18" s="347"/>
-      <c r="M18" s="348"/>
+      <c r="J18" s="237"/>
+      <c r="K18" s="346"/>
+      <c r="L18" s="346"/>
+      <c r="M18" s="347"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="312" t="s">
+      <c r="A19" s="311" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="313"/>
-      <c r="C19" s="313"/>
-      <c r="D19" s="313"/>
-      <c r="E19" s="313"/>
-      <c r="F19" s="313"/>
-      <c r="G19" s="313"/>
-      <c r="H19" s="313"/>
-      <c r="I19" s="313"/>
-      <c r="J19" s="313"/>
-      <c r="K19" s="313"/>
-      <c r="L19" s="313"/>
-      <c r="M19" s="314"/>
+      <c r="B19" s="312"/>
+      <c r="C19" s="312"/>
+      <c r="D19" s="312"/>
+      <c r="E19" s="312"/>
+      <c r="F19" s="312"/>
+      <c r="G19" s="312"/>
+      <c r="H19" s="312"/>
+      <c r="I19" s="312"/>
+      <c r="J19" s="312"/>
+      <c r="K19" s="312"/>
+      <c r="L19" s="312"/>
+      <c r="M19" s="313"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="325" t="s">
+      <c r="A20" s="324" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="326"/>
-      <c r="C20" s="326"/>
-      <c r="D20" s="326"/>
-      <c r="E20" s="326" t="s">
+      <c r="B20" s="325"/>
+      <c r="C20" s="325"/>
+      <c r="D20" s="325"/>
+      <c r="E20" s="325" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="326" t="s">
+      <c r="F20" s="325" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="326"/>
-      <c r="H20" s="327" t="s">
+      <c r="G20" s="325"/>
+      <c r="H20" s="326" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="328"/>
-      <c r="J20" s="329" t="s">
+      <c r="I20" s="327"/>
+      <c r="J20" s="328" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="330"/>
-      <c r="L20" s="330"/>
-      <c r="M20" s="331"/>
+      <c r="K20" s="329"/>
+      <c r="L20" s="329"/>
+      <c r="M20" s="330"/>
     </row>
     <row r="21" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="325"/>
-      <c r="B21" s="326"/>
-      <c r="C21" s="326"/>
-      <c r="D21" s="326"/>
-      <c r="E21" s="326"/>
-      <c r="F21" s="326"/>
-      <c r="G21" s="326"/>
-      <c r="H21" s="335" t="s">
+      <c r="A21" s="324"/>
+      <c r="B21" s="325"/>
+      <c r="C21" s="325"/>
+      <c r="D21" s="325"/>
+      <c r="E21" s="325"/>
+      <c r="F21" s="325"/>
+      <c r="G21" s="325"/>
+      <c r="H21" s="334" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="336"/>
-      <c r="J21" s="332"/>
-      <c r="K21" s="333"/>
-      <c r="L21" s="333"/>
-      <c r="M21" s="334"/>
+      <c r="I21" s="335"/>
+      <c r="J21" s="331"/>
+      <c r="K21" s="332"/>
+      <c r="L21" s="332"/>
+      <c r="M21" s="333"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="321"/>
-      <c r="B22" s="321"/>
-      <c r="C22" s="321"/>
-      <c r="D22" s="322"/>
+      <c r="A22" s="320"/>
+      <c r="B22" s="320"/>
+      <c r="C22" s="320"/>
+      <c r="D22" s="321"/>
       <c r="E22" s="66"/>
-      <c r="F22" s="323"/>
-      <c r="G22" s="323"/>
+      <c r="F22" s="322"/>
+      <c r="G22" s="322"/>
       <c r="H22" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I22" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="309"/>
-      <c r="K22" s="309"/>
-      <c r="L22" s="309"/>
-      <c r="M22" s="324"/>
+      <c r="J22" s="308"/>
+      <c r="K22" s="308"/>
+      <c r="L22" s="308"/>
+      <c r="M22" s="323"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="321"/>
-      <c r="B23" s="321"/>
-      <c r="C23" s="321"/>
-      <c r="D23" s="322"/>
+      <c r="A23" s="320"/>
+      <c r="B23" s="320"/>
+      <c r="C23" s="320"/>
+      <c r="D23" s="321"/>
       <c r="E23" s="66"/>
-      <c r="F23" s="323"/>
-      <c r="G23" s="323"/>
+      <c r="F23" s="322"/>
+      <c r="G23" s="322"/>
       <c r="H23" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I23" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J23" s="309"/>
-      <c r="K23" s="309"/>
-      <c r="L23" s="309"/>
-      <c r="M23" s="324"/>
+      <c r="J23" s="308"/>
+      <c r="K23" s="308"/>
+      <c r="L23" s="308"/>
+      <c r="M23" s="323"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="321"/>
-      <c r="B24" s="321"/>
-      <c r="C24" s="321"/>
-      <c r="D24" s="322"/>
+      <c r="A24" s="320"/>
+      <c r="B24" s="320"/>
+      <c r="C24" s="320"/>
+      <c r="D24" s="321"/>
       <c r="E24" s="66"/>
-      <c r="F24" s="323"/>
-      <c r="G24" s="323"/>
+      <c r="F24" s="322"/>
+      <c r="G24" s="322"/>
       <c r="H24" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I24" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J24" s="309"/>
-      <c r="K24" s="309"/>
-      <c r="L24" s="309"/>
-      <c r="M24" s="324"/>
+      <c r="J24" s="308"/>
+      <c r="K24" s="308"/>
+      <c r="L24" s="308"/>
+      <c r="M24" s="323"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="321"/>
-      <c r="B25" s="321"/>
-      <c r="C25" s="321"/>
-      <c r="D25" s="322"/>
+      <c r="A25" s="320"/>
+      <c r="B25" s="320"/>
+      <c r="C25" s="320"/>
+      <c r="D25" s="321"/>
       <c r="E25" s="66"/>
-      <c r="F25" s="323"/>
-      <c r="G25" s="323"/>
+      <c r="F25" s="322"/>
+      <c r="G25" s="322"/>
       <c r="H25" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I25" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J25" s="309"/>
-      <c r="K25" s="309"/>
-      <c r="L25" s="309"/>
-      <c r="M25" s="324"/>
+      <c r="J25" s="308"/>
+      <c r="K25" s="308"/>
+      <c r="L25" s="308"/>
+      <c r="M25" s="323"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="321"/>
-      <c r="B26" s="321"/>
-      <c r="C26" s="321"/>
-      <c r="D26" s="322"/>
+      <c r="A26" s="320"/>
+      <c r="B26" s="320"/>
+      <c r="C26" s="320"/>
+      <c r="D26" s="321"/>
       <c r="E26" s="66"/>
-      <c r="F26" s="323"/>
-      <c r="G26" s="323"/>
+      <c r="F26" s="322"/>
+      <c r="G26" s="322"/>
       <c r="H26" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I26" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J26" s="309"/>
-      <c r="K26" s="309"/>
-      <c r="L26" s="309"/>
-      <c r="M26" s="324"/>
+      <c r="J26" s="308"/>
+      <c r="K26" s="308"/>
+      <c r="L26" s="308"/>
+      <c r="M26" s="323"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="321"/>
-      <c r="B27" s="321"/>
-      <c r="C27" s="321"/>
-      <c r="D27" s="322"/>
+      <c r="A27" s="320"/>
+      <c r="B27" s="320"/>
+      <c r="C27" s="320"/>
+      <c r="D27" s="321"/>
       <c r="E27" s="66"/>
-      <c r="F27" s="323"/>
-      <c r="G27" s="323"/>
+      <c r="F27" s="322"/>
+      <c r="G27" s="322"/>
       <c r="H27" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I27" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="309"/>
-      <c r="K27" s="309"/>
-      <c r="L27" s="309"/>
-      <c r="M27" s="324"/>
+      <c r="J27" s="308"/>
+      <c r="K27" s="308"/>
+      <c r="L27" s="308"/>
+      <c r="M27" s="323"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="321"/>
-      <c r="B28" s="321"/>
-      <c r="C28" s="321"/>
-      <c r="D28" s="322"/>
+      <c r="A28" s="320"/>
+      <c r="B28" s="320"/>
+      <c r="C28" s="320"/>
+      <c r="D28" s="321"/>
       <c r="E28" s="66"/>
-      <c r="F28" s="323"/>
-      <c r="G28" s="323"/>
+      <c r="F28" s="322"/>
+      <c r="G28" s="322"/>
       <c r="H28" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I28" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J28" s="309"/>
-      <c r="K28" s="309"/>
-      <c r="L28" s="309"/>
-      <c r="M28" s="324"/>
+      <c r="J28" s="308"/>
+      <c r="K28" s="308"/>
+      <c r="L28" s="308"/>
+      <c r="M28" s="323"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="321"/>
-      <c r="B29" s="321"/>
-      <c r="C29" s="321"/>
-      <c r="D29" s="322"/>
+      <c r="A29" s="320"/>
+      <c r="B29" s="320"/>
+      <c r="C29" s="320"/>
+      <c r="D29" s="321"/>
       <c r="E29" s="66"/>
-      <c r="F29" s="323"/>
-      <c r="G29" s="323"/>
+      <c r="F29" s="322"/>
+      <c r="G29" s="322"/>
       <c r="H29" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I29" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J29" s="309"/>
-      <c r="K29" s="309"/>
-      <c r="L29" s="309"/>
-      <c r="M29" s="324"/>
+      <c r="J29" s="308"/>
+      <c r="K29" s="308"/>
+      <c r="L29" s="308"/>
+      <c r="M29" s="323"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="306" t="s">
+      <c r="A30" s="305" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="307"/>
-      <c r="C30" s="307"/>
-      <c r="D30" s="307"/>
+      <c r="B30" s="306"/>
+      <c r="C30" s="306"/>
+      <c r="D30" s="306"/>
       <c r="E30" s="12"/>
-      <c r="F30" s="308"/>
-      <c r="G30" s="309"/>
+      <c r="F30" s="307"/>
+      <c r="G30" s="308"/>
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
-      <c r="J30" s="310"/>
-      <c r="K30" s="310"/>
-      <c r="L30" s="310"/>
-      <c r="M30" s="311"/>
+      <c r="J30" s="309"/>
+      <c r="K30" s="309"/>
+      <c r="L30" s="309"/>
+      <c r="M30" s="310"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="312" t="s">
+      <c r="A31" s="311" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="313"/>
-      <c r="C31" s="313"/>
-      <c r="D31" s="313"/>
-      <c r="E31" s="313"/>
-      <c r="F31" s="313"/>
-      <c r="G31" s="313"/>
-      <c r="H31" s="313"/>
-      <c r="I31" s="313"/>
-      <c r="J31" s="313"/>
-      <c r="K31" s="313"/>
-      <c r="L31" s="313"/>
-      <c r="M31" s="314"/>
+      <c r="B31" s="312"/>
+      <c r="C31" s="312"/>
+      <c r="D31" s="312"/>
+      <c r="E31" s="312"/>
+      <c r="F31" s="312"/>
+      <c r="G31" s="312"/>
+      <c r="H31" s="312"/>
+      <c r="I31" s="312"/>
+      <c r="J31" s="312"/>
+      <c r="K31" s="312"/>
+      <c r="L31" s="312"/>
+      <c r="M31" s="313"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="315" t="s">
+      <c r="A32" s="314" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="316"/>
-      <c r="C32" s="316" t="s">
+      <c r="B32" s="315"/>
+      <c r="C32" s="315" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="316"/>
-      <c r="E32" s="317" t="s">
+      <c r="D32" s="315"/>
+      <c r="E32" s="316" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="318" t="s">
+      <c r="F32" s="317" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="319" t="s">
+      <c r="G32" s="318" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="319"/>
-      <c r="I32" s="319"/>
-      <c r="J32" s="319"/>
-      <c r="K32" s="319"/>
-      <c r="L32" s="316" t="s">
+      <c r="H32" s="318"/>
+      <c r="I32" s="318"/>
+      <c r="J32" s="318"/>
+      <c r="K32" s="318"/>
+      <c r="L32" s="315" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="320"/>
+      <c r="M32" s="319"/>
     </row>
     <row r="33" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="14" t="s">
@@ -4027,15 +4033,15 @@
       <c r="D33" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="317"/>
-      <c r="F33" s="318"/>
-      <c r="G33" s="305" t="s">
+      <c r="E33" s="316"/>
+      <c r="F33" s="317"/>
+      <c r="G33" s="304" t="s">
         <v>50</v>
       </c>
-      <c r="H33" s="305"/>
-      <c r="I33" s="305"/>
-      <c r="J33" s="305"/>
-      <c r="K33" s="305"/>
+      <c r="H33" s="304"/>
+      <c r="I33" s="304"/>
+      <c r="J33" s="304"/>
+      <c r="K33" s="304"/>
       <c r="L33" s="16" t="s">
         <v>14</v>
       </c>
@@ -4052,11 +4058,11 @@
       </c>
       <c r="E34" s="68"/>
       <c r="F34" s="67"/>
-      <c r="G34" s="278"/>
-      <c r="H34" s="279"/>
-      <c r="I34" s="279"/>
-      <c r="J34" s="279"/>
-      <c r="K34" s="280"/>
+      <c r="G34" s="277"/>
+      <c r="H34" s="278"/>
+      <c r="I34" s="278"/>
+      <c r="J34" s="278"/>
+      <c r="K34" s="279"/>
       <c r="L34" s="18"/>
       <c r="M34" s="19"/>
     </row>
@@ -4067,11 +4073,11 @@
       <c r="D35" s="67"/>
       <c r="E35" s="67"/>
       <c r="F35" s="18"/>
-      <c r="G35" s="278"/>
-      <c r="H35" s="279"/>
-      <c r="I35" s="279"/>
-      <c r="J35" s="279"/>
-      <c r="K35" s="280"/>
+      <c r="G35" s="277"/>
+      <c r="H35" s="278"/>
+      <c r="I35" s="278"/>
+      <c r="J35" s="278"/>
+      <c r="K35" s="279"/>
       <c r="L35" s="18"/>
       <c r="M35" s="19"/>
     </row>
@@ -4082,11 +4088,11 @@
       <c r="D36" s="67"/>
       <c r="E36" s="67"/>
       <c r="F36" s="18"/>
-      <c r="G36" s="278"/>
-      <c r="H36" s="279"/>
-      <c r="I36" s="279"/>
-      <c r="J36" s="279"/>
-      <c r="K36" s="280"/>
+      <c r="G36" s="277"/>
+      <c r="H36" s="278"/>
+      <c r="I36" s="278"/>
+      <c r="J36" s="278"/>
+      <c r="K36" s="279"/>
       <c r="L36" s="18"/>
       <c r="M36" s="19"/>
     </row>
@@ -4097,19 +4103,19 @@
       <c r="D37" s="67"/>
       <c r="E37" s="67"/>
       <c r="F37" s="18"/>
-      <c r="G37" s="278"/>
-      <c r="H37" s="279"/>
-      <c r="I37" s="279"/>
-      <c r="J37" s="279"/>
-      <c r="K37" s="280"/>
+      <c r="G37" s="277"/>
+      <c r="H37" s="278"/>
+      <c r="I37" s="278"/>
+      <c r="J37" s="278"/>
+      <c r="K37" s="279"/>
       <c r="L37" s="18"/>
       <c r="M37" s="19"/>
-      <c r="Q37" s="303"/>
-      <c r="R37" s="303"/>
+      <c r="Q37" s="302"/>
+      <c r="R37" s="302"/>
       <c r="S37" s="20"/>
-      <c r="T37" s="302"/>
-      <c r="U37" s="302"/>
-      <c r="V37" s="302"/>
+      <c r="T37" s="301"/>
+      <c r="U37" s="301"/>
+      <c r="V37" s="301"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A38" s="70"/>
@@ -4118,19 +4124,19 @@
       <c r="D38" s="67"/>
       <c r="E38" s="67"/>
       <c r="F38" s="18"/>
-      <c r="G38" s="278"/>
-      <c r="H38" s="279"/>
-      <c r="I38" s="279"/>
-      <c r="J38" s="279"/>
-      <c r="K38" s="280"/>
+      <c r="G38" s="277"/>
+      <c r="H38" s="278"/>
+      <c r="I38" s="278"/>
+      <c r="J38" s="278"/>
+      <c r="K38" s="279"/>
       <c r="L38" s="18"/>
       <c r="M38" s="22"/>
-      <c r="Q38" s="303"/>
-      <c r="R38" s="303"/>
+      <c r="Q38" s="302"/>
+      <c r="R38" s="302"/>
       <c r="S38" s="20"/>
-      <c r="T38" s="302"/>
-      <c r="U38" s="302"/>
-      <c r="V38" s="302"/>
+      <c r="T38" s="301"/>
+      <c r="U38" s="301"/>
+      <c r="V38" s="301"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A39" s="70"/>
@@ -4139,19 +4145,19 @@
       <c r="D39" s="67"/>
       <c r="E39" s="67"/>
       <c r="F39" s="18"/>
-      <c r="G39" s="278"/>
-      <c r="H39" s="279"/>
-      <c r="I39" s="279"/>
-      <c r="J39" s="279"/>
-      <c r="K39" s="280"/>
+      <c r="G39" s="277"/>
+      <c r="H39" s="278"/>
+      <c r="I39" s="278"/>
+      <c r="J39" s="278"/>
+      <c r="K39" s="279"/>
       <c r="L39" s="18"/>
       <c r="M39" s="22"/>
       <c r="Q39" s="23"/>
       <c r="R39" s="23"/>
-      <c r="S39" s="304"/>
-      <c r="T39" s="302"/>
-      <c r="U39" s="302"/>
-      <c r="V39" s="302"/>
+      <c r="S39" s="303"/>
+      <c r="T39" s="301"/>
+      <c r="U39" s="301"/>
+      <c r="V39" s="301"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A40" s="70"/>
@@ -4160,19 +4166,19 @@
       <c r="D40" s="67"/>
       <c r="E40" s="67"/>
       <c r="F40" s="18"/>
-      <c r="G40" s="278"/>
-      <c r="H40" s="279"/>
-      <c r="I40" s="279"/>
-      <c r="J40" s="279"/>
-      <c r="K40" s="280"/>
+      <c r="G40" s="277"/>
+      <c r="H40" s="278"/>
+      <c r="I40" s="278"/>
+      <c r="J40" s="278"/>
+      <c r="K40" s="279"/>
       <c r="L40" s="18"/>
       <c r="M40" s="19"/>
       <c r="Q40" s="23"/>
       <c r="R40" s="23"/>
-      <c r="S40" s="304"/>
-      <c r="T40" s="302"/>
-      <c r="U40" s="302"/>
-      <c r="V40" s="302"/>
+      <c r="S40" s="303"/>
+      <c r="T40" s="301"/>
+      <c r="U40" s="301"/>
+      <c r="V40" s="301"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A41" s="70"/>
@@ -4181,11 +4187,11 @@
       <c r="D41" s="67"/>
       <c r="E41" s="67"/>
       <c r="F41" s="18"/>
-      <c r="G41" s="278"/>
-      <c r="H41" s="279"/>
-      <c r="I41" s="279"/>
-      <c r="J41" s="279"/>
-      <c r="K41" s="280"/>
+      <c r="G41" s="277"/>
+      <c r="H41" s="278"/>
+      <c r="I41" s="278"/>
+      <c r="J41" s="278"/>
+      <c r="K41" s="279"/>
       <c r="L41" s="18"/>
       <c r="M41" s="19"/>
     </row>
@@ -4196,302 +4202,302 @@
       <c r="D42" s="72"/>
       <c r="E42" s="73"/>
       <c r="F42" s="24"/>
-      <c r="G42" s="281" t="s">
+      <c r="G42" s="280" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="282"/>
-      <c r="I42" s="282"/>
-      <c r="J42" s="282"/>
-      <c r="K42" s="283"/>
+      <c r="H42" s="281"/>
+      <c r="I42" s="281"/>
+      <c r="J42" s="281"/>
+      <c r="K42" s="282"/>
       <c r="L42" s="24"/>
       <c r="M42" s="25"/>
     </row>
     <row r="43" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="258" t="s">
+      <c r="A43" s="257" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="259"/>
-      <c r="C43" s="259"/>
-      <c r="D43" s="259"/>
-      <c r="E43" s="259"/>
-      <c r="F43" s="259"/>
-      <c r="G43" s="259"/>
-      <c r="H43" s="260"/>
-      <c r="I43" s="284" t="s">
+      <c r="B43" s="258"/>
+      <c r="C43" s="258"/>
+      <c r="D43" s="258"/>
+      <c r="E43" s="258"/>
+      <c r="F43" s="258"/>
+      <c r="G43" s="258"/>
+      <c r="H43" s="259"/>
+      <c r="I43" s="283" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="285"/>
-      <c r="K43" s="285"/>
-      <c r="L43" s="285"/>
-      <c r="M43" s="286"/>
+      <c r="J43" s="284"/>
+      <c r="K43" s="284"/>
+      <c r="L43" s="284"/>
+      <c r="M43" s="285"/>
     </row>
     <row r="44" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="261"/>
-      <c r="B44" s="262"/>
-      <c r="C44" s="262"/>
-      <c r="D44" s="262"/>
-      <c r="E44" s="262"/>
-      <c r="F44" s="262"/>
-      <c r="G44" s="262"/>
-      <c r="H44" s="263"/>
-      <c r="I44" s="287"/>
-      <c r="J44" s="288"/>
-      <c r="K44" s="288"/>
-      <c r="L44" s="288"/>
-      <c r="M44" s="289"/>
+      <c r="A44" s="260"/>
+      <c r="B44" s="261"/>
+      <c r="C44" s="261"/>
+      <c r="D44" s="261"/>
+      <c r="E44" s="261"/>
+      <c r="F44" s="261"/>
+      <c r="G44" s="261"/>
+      <c r="H44" s="262"/>
+      <c r="I44" s="286"/>
+      <c r="J44" s="287"/>
+      <c r="K44" s="287"/>
+      <c r="L44" s="287"/>
+      <c r="M44" s="288"/>
     </row>
     <row r="45" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="290" t="s">
+      <c r="A45" s="289" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="291"/>
-      <c r="C45" s="291"/>
-      <c r="D45" s="291"/>
-      <c r="E45" s="291"/>
-      <c r="F45" s="291"/>
-      <c r="G45" s="291"/>
-      <c r="H45" s="292"/>
-      <c r="I45" s="293" t="s">
+      <c r="B45" s="290"/>
+      <c r="C45" s="290"/>
+      <c r="D45" s="290"/>
+      <c r="E45" s="290"/>
+      <c r="F45" s="290"/>
+      <c r="G45" s="290"/>
+      <c r="H45" s="291"/>
+      <c r="I45" s="292" t="s">
         <v>83</v>
       </c>
-      <c r="J45" s="294"/>
-      <c r="K45" s="294"/>
-      <c r="L45" s="294"/>
-      <c r="M45" s="295"/>
+      <c r="J45" s="293"/>
+      <c r="K45" s="293"/>
+      <c r="L45" s="293"/>
+      <c r="M45" s="294"/>
     </row>
     <row r="46" spans="1:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="290" t="s">
+      <c r="A46" s="289" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="291"/>
-      <c r="C46" s="291"/>
-      <c r="D46" s="291"/>
-      <c r="E46" s="291"/>
-      <c r="F46" s="291"/>
-      <c r="G46" s="291"/>
-      <c r="H46" s="292"/>
-      <c r="I46" s="293"/>
-      <c r="J46" s="294"/>
-      <c r="K46" s="294"/>
-      <c r="L46" s="294"/>
-      <c r="M46" s="295"/>
+      <c r="B46" s="290"/>
+      <c r="C46" s="290"/>
+      <c r="D46" s="290"/>
+      <c r="E46" s="290"/>
+      <c r="F46" s="290"/>
+      <c r="G46" s="290"/>
+      <c r="H46" s="291"/>
+      <c r="I46" s="292"/>
+      <c r="J46" s="293"/>
+      <c r="K46" s="293"/>
+      <c r="L46" s="293"/>
+      <c r="M46" s="294"/>
     </row>
     <row r="47" spans="1:22" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="296"/>
-      <c r="B47" s="297"/>
-      <c r="C47" s="297"/>
-      <c r="D47" s="297"/>
-      <c r="E47" s="297"/>
-      <c r="F47" s="297"/>
-      <c r="G47" s="297"/>
-      <c r="H47" s="298"/>
-      <c r="I47" s="299" t="s">
+      <c r="A47" s="295"/>
+      <c r="B47" s="296"/>
+      <c r="C47" s="296"/>
+      <c r="D47" s="296"/>
+      <c r="E47" s="296"/>
+      <c r="F47" s="296"/>
+      <c r="G47" s="296"/>
+      <c r="H47" s="297"/>
+      <c r="I47" s="298" t="s">
         <v>84</v>
       </c>
-      <c r="J47" s="300"/>
-      <c r="K47" s="300"/>
-      <c r="L47" s="300"/>
-      <c r="M47" s="301"/>
+      <c r="J47" s="299"/>
+      <c r="K47" s="299"/>
+      <c r="L47" s="299"/>
+      <c r="M47" s="300"/>
     </row>
     <row r="48" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="255" t="s">
+      <c r="A48" s="254" t="s">
         <v>36</v>
       </c>
-      <c r="B48" s="256"/>
-      <c r="C48" s="256"/>
-      <c r="D48" s="256"/>
-      <c r="E48" s="256"/>
-      <c r="F48" s="256"/>
-      <c r="G48" s="256"/>
-      <c r="H48" s="256"/>
-      <c r="I48" s="256"/>
-      <c r="J48" s="256"/>
-      <c r="K48" s="256"/>
-      <c r="L48" s="256"/>
-      <c r="M48" s="257"/>
+      <c r="B48" s="255"/>
+      <c r="C48" s="255"/>
+      <c r="D48" s="255"/>
+      <c r="E48" s="255"/>
+      <c r="F48" s="255"/>
+      <c r="G48" s="255"/>
+      <c r="H48" s="255"/>
+      <c r="I48" s="255"/>
+      <c r="J48" s="255"/>
+      <c r="K48" s="255"/>
+      <c r="L48" s="255"/>
+      <c r="M48" s="256"/>
     </row>
     <row r="49" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="258" t="s">
+      <c r="A49" s="257" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="259"/>
-      <c r="C49" s="259"/>
-      <c r="D49" s="259"/>
-      <c r="E49" s="259"/>
-      <c r="F49" s="259"/>
-      <c r="G49" s="259"/>
-      <c r="H49" s="260"/>
-      <c r="I49" s="266" t="s">
+      <c r="B49" s="258"/>
+      <c r="C49" s="258"/>
+      <c r="D49" s="258"/>
+      <c r="E49" s="258"/>
+      <c r="F49" s="258"/>
+      <c r="G49" s="258"/>
+      <c r="H49" s="259"/>
+      <c r="I49" s="265" t="s">
         <v>38</v>
       </c>
-      <c r="J49" s="267"/>
-      <c r="K49" s="267"/>
-      <c r="L49" s="267"/>
-      <c r="M49" s="268"/>
+      <c r="J49" s="266"/>
+      <c r="K49" s="266"/>
+      <c r="L49" s="266"/>
+      <c r="M49" s="267"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="261"/>
-      <c r="B50" s="262"/>
-      <c r="C50" s="262"/>
-      <c r="D50" s="262"/>
-      <c r="E50" s="262"/>
-      <c r="F50" s="262"/>
-      <c r="G50" s="262"/>
-      <c r="H50" s="263"/>
-      <c r="I50" s="269"/>
-      <c r="J50" s="270"/>
-      <c r="K50" s="270"/>
-      <c r="L50" s="270"/>
-      <c r="M50" s="271"/>
+      <c r="A50" s="260"/>
+      <c r="B50" s="261"/>
+      <c r="C50" s="261"/>
+      <c r="D50" s="261"/>
+      <c r="E50" s="261"/>
+      <c r="F50" s="261"/>
+      <c r="G50" s="261"/>
+      <c r="H50" s="262"/>
+      <c r="I50" s="268"/>
+      <c r="J50" s="269"/>
+      <c r="K50" s="269"/>
+      <c r="L50" s="269"/>
+      <c r="M50" s="270"/>
     </row>
     <row r="51" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="264"/>
-      <c r="B51" s="265"/>
-      <c r="C51" s="265"/>
-      <c r="D51" s="265"/>
-      <c r="E51" s="262"/>
-      <c r="F51" s="262"/>
-      <c r="G51" s="262"/>
-      <c r="H51" s="263"/>
-      <c r="I51" s="272" t="s">
+      <c r="A51" s="263"/>
+      <c r="B51" s="264"/>
+      <c r="C51" s="264"/>
+      <c r="D51" s="264"/>
+      <c r="E51" s="261"/>
+      <c r="F51" s="261"/>
+      <c r="G51" s="261"/>
+      <c r="H51" s="262"/>
+      <c r="I51" s="271" t="s">
         <v>39</v>
       </c>
-      <c r="J51" s="273"/>
-      <c r="K51" s="274"/>
-      <c r="L51" s="274"/>
-      <c r="M51" s="275"/>
+      <c r="J51" s="272"/>
+      <c r="K51" s="273"/>
+      <c r="L51" s="273"/>
+      <c r="M51" s="274"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="255" t="s">
+      <c r="A52" s="254" t="s">
         <v>40</v>
       </c>
-      <c r="B52" s="256"/>
-      <c r="C52" s="256"/>
-      <c r="D52" s="256"/>
+      <c r="B52" s="255"/>
+      <c r="C52" s="255"/>
+      <c r="D52" s="255"/>
       <c r="E52" s="74" t="s">
         <v>42</v>
       </c>
       <c r="F52" s="75"/>
-      <c r="G52" s="276" t="s">
+      <c r="G52" s="275" t="s">
         <v>43</v>
       </c>
-      <c r="H52" s="276"/>
-      <c r="I52" s="276"/>
-      <c r="J52" s="277"/>
-      <c r="K52" s="256" t="s">
+      <c r="H52" s="275"/>
+      <c r="I52" s="275"/>
+      <c r="J52" s="276"/>
+      <c r="K52" s="255" t="s">
         <v>47</v>
       </c>
-      <c r="L52" s="256"/>
-      <c r="M52" s="257"/>
+      <c r="L52" s="255"/>
+      <c r="M52" s="256"/>
     </row>
     <row r="53" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="242" t="s">
+      <c r="A53" s="241" t="s">
         <v>41</v>
       </c>
-      <c r="B53" s="243"/>
-      <c r="C53" s="243"/>
-      <c r="D53" s="243"/>
+      <c r="B53" s="242"/>
+      <c r="C53" s="242"/>
+      <c r="D53" s="242"/>
       <c r="E53" s="76"/>
       <c r="F53" s="69"/>
       <c r="G53" s="69"/>
       <c r="H53" s="69"/>
       <c r="I53" s="69"/>
       <c r="J53" s="77"/>
-      <c r="K53" s="243" t="s">
+      <c r="K53" s="242" t="s">
         <v>49</v>
       </c>
-      <c r="L53" s="243"/>
-      <c r="M53" s="244"/>
+      <c r="L53" s="242"/>
+      <c r="M53" s="243"/>
     </row>
     <row r="54" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="242"/>
-      <c r="B54" s="243"/>
-      <c r="C54" s="243"/>
-      <c r="D54" s="243"/>
-      <c r="E54" s="245" t="s">
+      <c r="A54" s="241"/>
+      <c r="B54" s="242"/>
+      <c r="C54" s="242"/>
+      <c r="D54" s="242"/>
+      <c r="E54" s="244" t="s">
         <v>81</v>
       </c>
-      <c r="F54" s="246"/>
-      <c r="G54" s="406" t="s">
+      <c r="F54" s="245"/>
+      <c r="G54" s="405" t="s">
         <v>80</v>
       </c>
-      <c r="H54" s="235" t="s">
+      <c r="H54" s="234" t="s">
         <v>44</v>
       </c>
-      <c r="I54" s="235"/>
-      <c r="J54" s="236"/>
-      <c r="K54" s="243"/>
-      <c r="L54" s="243"/>
-      <c r="M54" s="244"/>
+      <c r="I54" s="234"/>
+      <c r="J54" s="235"/>
+      <c r="K54" s="242"/>
+      <c r="L54" s="242"/>
+      <c r="M54" s="243"/>
     </row>
     <row r="55" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="242"/>
-      <c r="B55" s="243"/>
-      <c r="C55" s="243"/>
-      <c r="D55" s="243"/>
-      <c r="E55" s="245" t="s">
+      <c r="A55" s="241"/>
+      <c r="B55" s="242"/>
+      <c r="C55" s="242"/>
+      <c r="D55" s="242"/>
+      <c r="E55" s="244" t="s">
         <v>82</v>
       </c>
-      <c r="F55" s="246"/>
-      <c r="G55" s="407" t="s">
+      <c r="F55" s="245"/>
+      <c r="G55" s="406" t="s">
         <v>80</v>
       </c>
-      <c r="H55" s="235" t="s">
+      <c r="H55" s="234" t="s">
         <v>45</v>
       </c>
-      <c r="I55" s="235"/>
-      <c r="J55" s="236"/>
-      <c r="K55" s="243"/>
-      <c r="L55" s="243"/>
-      <c r="M55" s="244"/>
+      <c r="I55" s="234"/>
+      <c r="J55" s="235"/>
+      <c r="K55" s="242"/>
+      <c r="L55" s="242"/>
+      <c r="M55" s="243"/>
     </row>
     <row r="56" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="247"/>
-      <c r="B56" s="248"/>
-      <c r="C56" s="248"/>
-      <c r="D56" s="249"/>
-      <c r="E56" s="245"/>
-      <c r="F56" s="246"/>
-      <c r="G56" s="407"/>
-      <c r="H56" s="235"/>
-      <c r="I56" s="235"/>
-      <c r="J56" s="236"/>
-      <c r="K56" s="253" t="s">
+      <c r="A56" s="246"/>
+      <c r="B56" s="247"/>
+      <c r="C56" s="247"/>
+      <c r="D56" s="248"/>
+      <c r="E56" s="244"/>
+      <c r="F56" s="245"/>
+      <c r="G56" s="406"/>
+      <c r="H56" s="234"/>
+      <c r="I56" s="234"/>
+      <c r="J56" s="235"/>
+      <c r="K56" s="252" t="s">
         <v>48</v>
       </c>
-      <c r="L56" s="253"/>
-      <c r="M56" s="254"/>
+      <c r="L56" s="252"/>
+      <c r="M56" s="253"/>
     </row>
     <row r="57" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="247"/>
-      <c r="B57" s="248"/>
-      <c r="C57" s="248"/>
-      <c r="D57" s="249"/>
-      <c r="E57" s="245"/>
-      <c r="F57" s="246"/>
-      <c r="G57" s="406" t="s">
+      <c r="A57" s="246"/>
+      <c r="B57" s="247"/>
+      <c r="C57" s="247"/>
+      <c r="D57" s="248"/>
+      <c r="E57" s="244"/>
+      <c r="F57" s="245"/>
+      <c r="G57" s="405" t="s">
         <v>80</v>
       </c>
-      <c r="H57" s="235" t="s">
+      <c r="H57" s="234" t="s">
         <v>46</v>
       </c>
-      <c r="I57" s="235"/>
-      <c r="J57" s="236"/>
+      <c r="I57" s="234"/>
+      <c r="J57" s="235"/>
       <c r="K57" s="78"/>
       <c r="L57" s="79"/>
       <c r="M57" s="80"/>
     </row>
     <row r="58" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="250"/>
-      <c r="B58" s="251"/>
-      <c r="C58" s="251"/>
-      <c r="D58" s="252"/>
-      <c r="E58" s="237"/>
-      <c r="F58" s="238"/>
-      <c r="G58" s="238"/>
-      <c r="H58" s="238"/>
-      <c r="I58" s="238"/>
-      <c r="J58" s="239"/>
+      <c r="A58" s="249"/>
+      <c r="B58" s="250"/>
+      <c r="C58" s="250"/>
+      <c r="D58" s="251"/>
+      <c r="E58" s="236"/>
+      <c r="F58" s="237"/>
+      <c r="G58" s="237"/>
+      <c r="H58" s="237"/>
+      <c r="I58" s="237"/>
+      <c r="J58" s="238"/>
       <c r="K58" s="81"/>
       <c r="L58" s="82"/>
       <c r="M58" s="83"/>
@@ -4509,18 +4515,19 @@
       <c r="J59" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="111">
+  <mergeCells count="112">
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="I4:M6"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="C1:K1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:M3"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:K1"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="A12:H12"/>
@@ -4631,7 +4638,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{193EDE3F-A5B1-4510-8EA4-93E70B2B66C7}">
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:P61"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="7.42578125" style="10" customWidth="1"/>
@@ -5340,1013 +5347,1014 @@
     <col min="16142" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="85" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="380" t="s">
+      <c r="B1" s="415"/>
+      <c r="C1" s="415"/>
+      <c r="D1" s="379" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="380"/>
-      <c r="E1" s="380"/>
-      <c r="F1" s="380"/>
-      <c r="G1" s="380"/>
-      <c r="H1" s="380"/>
-      <c r="I1" s="380"/>
-      <c r="J1" s="380"/>
-      <c r="K1" s="380"/>
-      <c r="L1" s="382" t="s">
+      <c r="E1" s="379"/>
+      <c r="F1" s="379"/>
+      <c r="G1" s="379"/>
+      <c r="H1" s="379"/>
+      <c r="I1" s="379"/>
+      <c r="J1" s="379"/>
+      <c r="K1" s="379"/>
+      <c r="L1" s="381" t="s">
         <v>59</v>
       </c>
-      <c r="M1" s="383"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="312" t="s">
+      <c r="M1" s="382"/>
+      <c r="P1" s="414"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" s="311" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="313"/>
-      <c r="C2" s="313"/>
-      <c r="D2" s="313"/>
-      <c r="E2" s="313"/>
-      <c r="F2" s="313"/>
-      <c r="G2" s="313"/>
-      <c r="H2" s="313"/>
-      <c r="I2" s="313"/>
-      <c r="J2" s="313"/>
-      <c r="K2" s="313"/>
-      <c r="L2" s="313"/>
-      <c r="M2" s="314"/>
-    </row>
-    <row r="3" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="325" t="s">
+      <c r="B2" s="312"/>
+      <c r="C2" s="312"/>
+      <c r="D2" s="312"/>
+      <c r="E2" s="312"/>
+      <c r="F2" s="312"/>
+      <c r="G2" s="312"/>
+      <c r="H2" s="312"/>
+      <c r="I2" s="312"/>
+      <c r="J2" s="312"/>
+      <c r="K2" s="312"/>
+      <c r="L2" s="312"/>
+      <c r="M2" s="313"/>
+    </row>
+    <row r="3" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="324" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="326"/>
-      <c r="C3" s="326"/>
-      <c r="D3" s="326"/>
-      <c r="E3" s="326" t="s">
+      <c r="B3" s="325"/>
+      <c r="C3" s="325"/>
+      <c r="D3" s="325"/>
+      <c r="E3" s="325" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="326" t="s">
+      <c r="F3" s="325" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="326"/>
-      <c r="H3" s="327" t="s">
+      <c r="G3" s="325"/>
+      <c r="H3" s="326" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="328"/>
-      <c r="J3" s="329" t="s">
+      <c r="I3" s="327"/>
+      <c r="J3" s="328" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="330"/>
-      <c r="L3" s="330"/>
-      <c r="M3" s="331"/>
-    </row>
-    <row r="4" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="325"/>
-      <c r="B4" s="326"/>
-      <c r="C4" s="326"/>
-      <c r="D4" s="326"/>
-      <c r="E4" s="326"/>
-      <c r="F4" s="326"/>
-      <c r="G4" s="326"/>
-      <c r="H4" s="335" t="s">
+      <c r="K3" s="329"/>
+      <c r="L3" s="329"/>
+      <c r="M3" s="330"/>
+    </row>
+    <row r="4" spans="1:16" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="324"/>
+      <c r="B4" s="325"/>
+      <c r="C4" s="325"/>
+      <c r="D4" s="325"/>
+      <c r="E4" s="325"/>
+      <c r="F4" s="325"/>
+      <c r="G4" s="325"/>
+      <c r="H4" s="334" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="336"/>
-      <c r="J4" s="332"/>
-      <c r="K4" s="333"/>
-      <c r="L4" s="333"/>
-      <c r="M4" s="334"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="405"/>
-      <c r="B5" s="321"/>
-      <c r="C5" s="321"/>
-      <c r="D5" s="321"/>
+      <c r="I4" s="335"/>
+      <c r="J4" s="331"/>
+      <c r="K4" s="332"/>
+      <c r="L4" s="332"/>
+      <c r="M4" s="333"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A5" s="404"/>
+      <c r="B5" s="320"/>
+      <c r="C5" s="320"/>
+      <c r="D5" s="320"/>
       <c r="E5" s="9"/>
-      <c r="F5" s="179"/>
-      <c r="G5" s="183"/>
+      <c r="F5" s="178"/>
+      <c r="G5" s="182"/>
       <c r="H5" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I5" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="309"/>
-      <c r="K5" s="309"/>
-      <c r="L5" s="309"/>
-      <c r="M5" s="324"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="405"/>
-      <c r="B6" s="321"/>
-      <c r="C6" s="321"/>
-      <c r="D6" s="321"/>
+      <c r="J5" s="308"/>
+      <c r="K5" s="308"/>
+      <c r="L5" s="308"/>
+      <c r="M5" s="323"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A6" s="404"/>
+      <c r="B6" s="320"/>
+      <c r="C6" s="320"/>
+      <c r="D6" s="320"/>
       <c r="E6" s="9"/>
-      <c r="F6" s="179"/>
-      <c r="G6" s="183"/>
+      <c r="F6" s="178"/>
+      <c r="G6" s="182"/>
       <c r="H6" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I6" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="309"/>
-      <c r="K6" s="309"/>
-      <c r="L6" s="309"/>
-      <c r="M6" s="324"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="405"/>
-      <c r="B7" s="321"/>
-      <c r="C7" s="321"/>
-      <c r="D7" s="321"/>
+      <c r="J6" s="308"/>
+      <c r="K6" s="308"/>
+      <c r="L6" s="308"/>
+      <c r="M6" s="323"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A7" s="404"/>
+      <c r="B7" s="320"/>
+      <c r="C7" s="320"/>
+      <c r="D7" s="320"/>
       <c r="E7" s="9"/>
-      <c r="F7" s="179"/>
-      <c r="G7" s="183"/>
+      <c r="F7" s="178"/>
+      <c r="G7" s="182"/>
       <c r="H7" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I7" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="309"/>
-      <c r="K7" s="309"/>
-      <c r="L7" s="309"/>
-      <c r="M7" s="324"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="405"/>
-      <c r="B8" s="321"/>
-      <c r="C8" s="321"/>
-      <c r="D8" s="321"/>
+      <c r="J7" s="308"/>
+      <c r="K7" s="308"/>
+      <c r="L7" s="308"/>
+      <c r="M7" s="323"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A8" s="404"/>
+      <c r="B8" s="320"/>
+      <c r="C8" s="320"/>
+      <c r="D8" s="320"/>
       <c r="E8" s="9"/>
-      <c r="F8" s="179"/>
-      <c r="G8" s="183"/>
+      <c r="F8" s="178"/>
+      <c r="G8" s="182"/>
       <c r="H8" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I8" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="309"/>
-      <c r="K8" s="309"/>
-      <c r="L8" s="309"/>
-      <c r="M8" s="324"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="405"/>
-      <c r="B9" s="321"/>
-      <c r="C9" s="321"/>
-      <c r="D9" s="321"/>
+      <c r="J8" s="308"/>
+      <c r="K8" s="308"/>
+      <c r="L8" s="308"/>
+      <c r="M8" s="323"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A9" s="404"/>
+      <c r="B9" s="320"/>
+      <c r="C9" s="320"/>
+      <c r="D9" s="320"/>
       <c r="E9" s="9"/>
-      <c r="F9" s="179"/>
-      <c r="G9" s="183"/>
+      <c r="F9" s="178"/>
+      <c r="G9" s="182"/>
       <c r="H9" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I9" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="309"/>
-      <c r="K9" s="309"/>
-      <c r="L9" s="309"/>
-      <c r="M9" s="324"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="405"/>
-      <c r="B10" s="321"/>
-      <c r="C10" s="321"/>
-      <c r="D10" s="321"/>
+      <c r="J9" s="308"/>
+      <c r="K9" s="308"/>
+      <c r="L9" s="308"/>
+      <c r="M9" s="323"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A10" s="404"/>
+      <c r="B10" s="320"/>
+      <c r="C10" s="320"/>
+      <c r="D10" s="320"/>
       <c r="E10" s="9"/>
-      <c r="F10" s="179"/>
-      <c r="G10" s="183"/>
+      <c r="F10" s="178"/>
+      <c r="G10" s="182"/>
       <c r="H10" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I10" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="309"/>
-      <c r="K10" s="309"/>
-      <c r="L10" s="309"/>
-      <c r="M10" s="324"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="405"/>
-      <c r="B11" s="321"/>
-      <c r="C11" s="321"/>
-      <c r="D11" s="321"/>
+      <c r="J10" s="308"/>
+      <c r="K10" s="308"/>
+      <c r="L10" s="308"/>
+      <c r="M10" s="323"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A11" s="404"/>
+      <c r="B11" s="320"/>
+      <c r="C11" s="320"/>
+      <c r="D11" s="320"/>
       <c r="E11" s="9"/>
-      <c r="F11" s="179"/>
-      <c r="G11" s="183"/>
+      <c r="F11" s="178"/>
+      <c r="G11" s="182"/>
       <c r="H11" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I11" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J11" s="309"/>
-      <c r="K11" s="309"/>
-      <c r="L11" s="309"/>
-      <c r="M11" s="324"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="405"/>
-      <c r="B12" s="321"/>
-      <c r="C12" s="321"/>
-      <c r="D12" s="321"/>
+      <c r="J11" s="308"/>
+      <c r="K11" s="308"/>
+      <c r="L11" s="308"/>
+      <c r="M11" s="323"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A12" s="404"/>
+      <c r="B12" s="320"/>
+      <c r="C12" s="320"/>
+      <c r="D12" s="320"/>
       <c r="E12" s="9"/>
-      <c r="F12" s="179"/>
-      <c r="G12" s="183"/>
+      <c r="F12" s="178"/>
+      <c r="G12" s="182"/>
       <c r="H12" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I12" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J12" s="309"/>
-      <c r="K12" s="309"/>
-      <c r="L12" s="309"/>
-      <c r="M12" s="324"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="405"/>
-      <c r="B13" s="321"/>
-      <c r="C13" s="321"/>
-      <c r="D13" s="321"/>
+      <c r="J12" s="308"/>
+      <c r="K12" s="308"/>
+      <c r="L12" s="308"/>
+      <c r="M12" s="323"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A13" s="404"/>
+      <c r="B13" s="320"/>
+      <c r="C13" s="320"/>
+      <c r="D13" s="320"/>
       <c r="E13" s="9"/>
-      <c r="F13" s="179"/>
-      <c r="G13" s="183"/>
+      <c r="F13" s="178"/>
+      <c r="G13" s="182"/>
       <c r="H13" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I13" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J13" s="309"/>
-      <c r="K13" s="309"/>
-      <c r="L13" s="309"/>
-      <c r="M13" s="324"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="405"/>
-      <c r="B14" s="321"/>
-      <c r="C14" s="321"/>
-      <c r="D14" s="321"/>
+      <c r="J13" s="308"/>
+      <c r="K13" s="308"/>
+      <c r="L13" s="308"/>
+      <c r="M13" s="323"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A14" s="404"/>
+      <c r="B14" s="320"/>
+      <c r="C14" s="320"/>
+      <c r="D14" s="320"/>
       <c r="E14" s="9"/>
-      <c r="F14" s="179"/>
-      <c r="G14" s="183"/>
+      <c r="F14" s="178"/>
+      <c r="G14" s="182"/>
       <c r="H14" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I14" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J14" s="309"/>
-      <c r="K14" s="309"/>
-      <c r="L14" s="309"/>
-      <c r="M14" s="324"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="405"/>
-      <c r="B15" s="321"/>
-      <c r="C15" s="321"/>
-      <c r="D15" s="321"/>
+      <c r="J14" s="308"/>
+      <c r="K14" s="308"/>
+      <c r="L14" s="308"/>
+      <c r="M14" s="323"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A15" s="404"/>
+      <c r="B15" s="320"/>
+      <c r="C15" s="320"/>
+      <c r="D15" s="320"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="179"/>
-      <c r="G15" s="183"/>
+      <c r="F15" s="178"/>
+      <c r="G15" s="182"/>
       <c r="H15" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I15" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J15" s="309"/>
-      <c r="K15" s="309"/>
-      <c r="L15" s="309"/>
-      <c r="M15" s="324"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="405"/>
-      <c r="B16" s="321"/>
-      <c r="C16" s="321"/>
-      <c r="D16" s="321"/>
+      <c r="J15" s="308"/>
+      <c r="K15" s="308"/>
+      <c r="L15" s="308"/>
+      <c r="M15" s="323"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A16" s="404"/>
+      <c r="B16" s="320"/>
+      <c r="C16" s="320"/>
+      <c r="D16" s="320"/>
       <c r="E16" s="9"/>
-      <c r="F16" s="179"/>
-      <c r="G16" s="183"/>
+      <c r="F16" s="178"/>
+      <c r="G16" s="182"/>
       <c r="H16" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I16" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J16" s="309"/>
-      <c r="K16" s="309"/>
-      <c r="L16" s="309"/>
-      <c r="M16" s="324"/>
+      <c r="J16" s="308"/>
+      <c r="K16" s="308"/>
+      <c r="L16" s="308"/>
+      <c r="M16" s="323"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="405"/>
-      <c r="B17" s="321"/>
-      <c r="C17" s="321"/>
-      <c r="D17" s="321"/>
+      <c r="A17" s="404"/>
+      <c r="B17" s="320"/>
+      <c r="C17" s="320"/>
+      <c r="D17" s="320"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="179"/>
-      <c r="G17" s="183"/>
+      <c r="F17" s="178"/>
+      <c r="G17" s="182"/>
       <c r="H17" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I17" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J17" s="309"/>
-      <c r="K17" s="309"/>
-      <c r="L17" s="309"/>
-      <c r="M17" s="324"/>
+      <c r="J17" s="308"/>
+      <c r="K17" s="308"/>
+      <c r="L17" s="308"/>
+      <c r="M17" s="323"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="405"/>
-      <c r="B18" s="321"/>
-      <c r="C18" s="321"/>
-      <c r="D18" s="321"/>
+      <c r="A18" s="404"/>
+      <c r="B18" s="320"/>
+      <c r="C18" s="320"/>
+      <c r="D18" s="320"/>
       <c r="E18" s="9"/>
-      <c r="F18" s="179"/>
-      <c r="G18" s="183"/>
+      <c r="F18" s="178"/>
+      <c r="G18" s="182"/>
       <c r="H18" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I18" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J18" s="309"/>
-      <c r="K18" s="309"/>
-      <c r="L18" s="309"/>
-      <c r="M18" s="324"/>
+      <c r="J18" s="308"/>
+      <c r="K18" s="308"/>
+      <c r="L18" s="308"/>
+      <c r="M18" s="323"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="405"/>
-      <c r="B19" s="321"/>
-      <c r="C19" s="321"/>
-      <c r="D19" s="321"/>
+      <c r="A19" s="404"/>
+      <c r="B19" s="320"/>
+      <c r="C19" s="320"/>
+      <c r="D19" s="320"/>
       <c r="E19" s="9"/>
-      <c r="F19" s="179"/>
-      <c r="G19" s="183"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="182"/>
       <c r="H19" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I19" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J19" s="309"/>
-      <c r="K19" s="309"/>
-      <c r="L19" s="309"/>
-      <c r="M19" s="324"/>
+      <c r="J19" s="308"/>
+      <c r="K19" s="308"/>
+      <c r="L19" s="308"/>
+      <c r="M19" s="323"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="405"/>
-      <c r="B20" s="321"/>
-      <c r="C20" s="321"/>
-      <c r="D20" s="321"/>
+      <c r="A20" s="404"/>
+      <c r="B20" s="320"/>
+      <c r="C20" s="320"/>
+      <c r="D20" s="320"/>
       <c r="E20" s="9"/>
-      <c r="F20" s="179"/>
-      <c r="G20" s="183"/>
+      <c r="F20" s="178"/>
+      <c r="G20" s="182"/>
       <c r="H20" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I20" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J20" s="309"/>
-      <c r="K20" s="309"/>
-      <c r="L20" s="309"/>
-      <c r="M20" s="324"/>
+      <c r="J20" s="308"/>
+      <c r="K20" s="308"/>
+      <c r="L20" s="308"/>
+      <c r="M20" s="323"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="405"/>
-      <c r="B21" s="321"/>
-      <c r="C21" s="321"/>
-      <c r="D21" s="321"/>
+      <c r="A21" s="404"/>
+      <c r="B21" s="320"/>
+      <c r="C21" s="320"/>
+      <c r="D21" s="320"/>
       <c r="E21" s="9"/>
-      <c r="F21" s="179"/>
-      <c r="G21" s="183"/>
+      <c r="F21" s="178"/>
+      <c r="G21" s="182"/>
       <c r="H21" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I21" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J21" s="309"/>
-      <c r="K21" s="309"/>
-      <c r="L21" s="309"/>
-      <c r="M21" s="324"/>
+      <c r="J21" s="308"/>
+      <c r="K21" s="308"/>
+      <c r="L21" s="308"/>
+      <c r="M21" s="323"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="405"/>
-      <c r="B22" s="321"/>
-      <c r="C22" s="321"/>
-      <c r="D22" s="321"/>
+      <c r="A22" s="404"/>
+      <c r="B22" s="320"/>
+      <c r="C22" s="320"/>
+      <c r="D22" s="320"/>
       <c r="E22" s="9"/>
-      <c r="F22" s="179"/>
-      <c r="G22" s="183"/>
+      <c r="F22" s="178"/>
+      <c r="G22" s="182"/>
       <c r="H22" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I22" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="309"/>
-      <c r="K22" s="309"/>
-      <c r="L22" s="309"/>
-      <c r="M22" s="324"/>
+      <c r="J22" s="308"/>
+      <c r="K22" s="308"/>
+      <c r="L22" s="308"/>
+      <c r="M22" s="323"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="405"/>
-      <c r="B23" s="321"/>
-      <c r="C23" s="321"/>
-      <c r="D23" s="321"/>
+      <c r="A23" s="404"/>
+      <c r="B23" s="320"/>
+      <c r="C23" s="320"/>
+      <c r="D23" s="320"/>
       <c r="E23" s="9"/>
-      <c r="F23" s="179"/>
-      <c r="G23" s="183"/>
+      <c r="F23" s="178"/>
+      <c r="G23" s="182"/>
       <c r="H23" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I23" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J23" s="309"/>
-      <c r="K23" s="309"/>
-      <c r="L23" s="309"/>
-      <c r="M23" s="324"/>
+      <c r="J23" s="308"/>
+      <c r="K23" s="308"/>
+      <c r="L23" s="308"/>
+      <c r="M23" s="323"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="405"/>
-      <c r="B24" s="321"/>
-      <c r="C24" s="321"/>
-      <c r="D24" s="321"/>
+      <c r="A24" s="404"/>
+      <c r="B24" s="320"/>
+      <c r="C24" s="320"/>
+      <c r="D24" s="320"/>
       <c r="E24" s="9"/>
-      <c r="F24" s="179"/>
-      <c r="G24" s="183"/>
+      <c r="F24" s="178"/>
+      <c r="G24" s="182"/>
       <c r="H24" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I24" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J24" s="309"/>
-      <c r="K24" s="309"/>
-      <c r="L24" s="309"/>
-      <c r="M24" s="324"/>
+      <c r="J24" s="308"/>
+      <c r="K24" s="308"/>
+      <c r="L24" s="308"/>
+      <c r="M24" s="323"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="405"/>
-      <c r="B25" s="321"/>
-      <c r="C25" s="321"/>
-      <c r="D25" s="321"/>
+      <c r="A25" s="404"/>
+      <c r="B25" s="320"/>
+      <c r="C25" s="320"/>
+      <c r="D25" s="320"/>
       <c r="E25" s="9"/>
-      <c r="F25" s="179"/>
-      <c r="G25" s="183"/>
+      <c r="F25" s="178"/>
+      <c r="G25" s="182"/>
       <c r="H25" s="67" t="s">
         <v>51</v>
       </c>
       <c r="I25" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="J25" s="309"/>
-      <c r="K25" s="309"/>
-      <c r="L25" s="309"/>
-      <c r="M25" s="324"/>
+      <c r="J25" s="308"/>
+      <c r="K25" s="308"/>
+      <c r="L25" s="308"/>
+      <c r="M25" s="323"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="399"/>
-      <c r="B26" s="400"/>
-      <c r="C26" s="400"/>
-      <c r="D26" s="400"/>
+      <c r="A26" s="398"/>
+      <c r="B26" s="399"/>
+      <c r="C26" s="399"/>
+      <c r="D26" s="399"/>
       <c r="E26" s="11"/>
-      <c r="F26" s="309"/>
-      <c r="G26" s="309"/>
+      <c r="F26" s="308"/>
+      <c r="G26" s="308"/>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
-      <c r="J26" s="309"/>
-      <c r="K26" s="309"/>
-      <c r="L26" s="309"/>
-      <c r="M26" s="324"/>
+      <c r="J26" s="308"/>
+      <c r="K26" s="308"/>
+      <c r="L26" s="308"/>
+      <c r="M26" s="323"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="399"/>
-      <c r="B27" s="400"/>
-      <c r="C27" s="400"/>
-      <c r="D27" s="400"/>
+      <c r="A27" s="398"/>
+      <c r="B27" s="399"/>
+      <c r="C27" s="399"/>
+      <c r="D27" s="399"/>
       <c r="E27" s="11"/>
-      <c r="F27" s="309"/>
-      <c r="G27" s="309"/>
+      <c r="F27" s="308"/>
+      <c r="G27" s="308"/>
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
-      <c r="J27" s="309"/>
-      <c r="K27" s="309"/>
-      <c r="L27" s="309"/>
-      <c r="M27" s="324"/>
+      <c r="J27" s="308"/>
+      <c r="K27" s="308"/>
+      <c r="L27" s="308"/>
+      <c r="M27" s="323"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="399"/>
-      <c r="B28" s="400"/>
-      <c r="C28" s="400"/>
-      <c r="D28" s="400"/>
+      <c r="A28" s="398"/>
+      <c r="B28" s="399"/>
+      <c r="C28" s="399"/>
+      <c r="D28" s="399"/>
       <c r="E28" s="11"/>
-      <c r="F28" s="309"/>
-      <c r="G28" s="309"/>
+      <c r="F28" s="308"/>
+      <c r="G28" s="308"/>
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
-      <c r="J28" s="309"/>
-      <c r="K28" s="309"/>
-      <c r="L28" s="309"/>
-      <c r="M28" s="324"/>
+      <c r="J28" s="308"/>
+      <c r="K28" s="308"/>
+      <c r="L28" s="308"/>
+      <c r="M28" s="323"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="399"/>
-      <c r="B29" s="400"/>
-      <c r="C29" s="400"/>
-      <c r="D29" s="400"/>
+      <c r="A29" s="398"/>
+      <c r="B29" s="399"/>
+      <c r="C29" s="399"/>
+      <c r="D29" s="399"/>
       <c r="E29" s="11"/>
-      <c r="F29" s="309"/>
-      <c r="G29" s="309"/>
+      <c r="F29" s="308"/>
+      <c r="G29" s="308"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
-      <c r="J29" s="309"/>
-      <c r="K29" s="309"/>
-      <c r="L29" s="309"/>
-      <c r="M29" s="324"/>
+      <c r="J29" s="308"/>
+      <c r="K29" s="308"/>
+      <c r="L29" s="308"/>
+      <c r="M29" s="323"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="399"/>
-      <c r="B30" s="400"/>
-      <c r="C30" s="400"/>
-      <c r="D30" s="400"/>
+      <c r="A30" s="398"/>
+      <c r="B30" s="399"/>
+      <c r="C30" s="399"/>
+      <c r="D30" s="399"/>
       <c r="E30" s="11"/>
-      <c r="F30" s="309"/>
-      <c r="G30" s="309"/>
+      <c r="F30" s="308"/>
+      <c r="G30" s="308"/>
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
-      <c r="J30" s="309"/>
-      <c r="K30" s="309"/>
-      <c r="L30" s="309"/>
-      <c r="M30" s="324"/>
+      <c r="J30" s="308"/>
+      <c r="K30" s="308"/>
+      <c r="L30" s="308"/>
+      <c r="M30" s="323"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="399"/>
-      <c r="B31" s="400"/>
-      <c r="C31" s="400"/>
-      <c r="D31" s="400"/>
+      <c r="A31" s="398"/>
+      <c r="B31" s="399"/>
+      <c r="C31" s="399"/>
+      <c r="D31" s="399"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="309"/>
-      <c r="G31" s="309"/>
+      <c r="F31" s="308"/>
+      <c r="G31" s="308"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
-      <c r="J31" s="309"/>
-      <c r="K31" s="309"/>
-      <c r="L31" s="309"/>
-      <c r="M31" s="324"/>
+      <c r="J31" s="308"/>
+      <c r="K31" s="308"/>
+      <c r="L31" s="308"/>
+      <c r="M31" s="323"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="399"/>
-      <c r="B32" s="400"/>
-      <c r="C32" s="400"/>
-      <c r="D32" s="400"/>
+      <c r="A32" s="398"/>
+      <c r="B32" s="399"/>
+      <c r="C32" s="399"/>
+      <c r="D32" s="399"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="309"/>
-      <c r="G32" s="309"/>
+      <c r="F32" s="308"/>
+      <c r="G32" s="308"/>
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
-      <c r="J32" s="309"/>
-      <c r="K32" s="309"/>
-      <c r="L32" s="309"/>
-      <c r="M32" s="324"/>
+      <c r="J32" s="308"/>
+      <c r="K32" s="308"/>
+      <c r="L32" s="308"/>
+      <c r="M32" s="323"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A33" s="399"/>
-      <c r="B33" s="400"/>
-      <c r="C33" s="400"/>
-      <c r="D33" s="400"/>
+      <c r="A33" s="398"/>
+      <c r="B33" s="399"/>
+      <c r="C33" s="399"/>
+      <c r="D33" s="399"/>
       <c r="E33" s="11"/>
-      <c r="F33" s="309"/>
-      <c r="G33" s="309"/>
+      <c r="F33" s="308"/>
+      <c r="G33" s="308"/>
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
-      <c r="J33" s="309"/>
-      <c r="K33" s="309"/>
-      <c r="L33" s="309"/>
-      <c r="M33" s="324"/>
+      <c r="J33" s="308"/>
+      <c r="K33" s="308"/>
+      <c r="L33" s="308"/>
+      <c r="M33" s="323"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A34" s="399"/>
-      <c r="B34" s="400"/>
-      <c r="C34" s="400"/>
-      <c r="D34" s="400"/>
+      <c r="A34" s="398"/>
+      <c r="B34" s="399"/>
+      <c r="C34" s="399"/>
+      <c r="D34" s="399"/>
       <c r="E34" s="11"/>
-      <c r="F34" s="309"/>
-      <c r="G34" s="309"/>
+      <c r="F34" s="308"/>
+      <c r="G34" s="308"/>
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
-      <c r="J34" s="309"/>
-      <c r="K34" s="309"/>
-      <c r="L34" s="309"/>
-      <c r="M34" s="324"/>
+      <c r="J34" s="308"/>
+      <c r="K34" s="308"/>
+      <c r="L34" s="308"/>
+      <c r="M34" s="323"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35" s="399"/>
-      <c r="B35" s="400"/>
-      <c r="C35" s="400"/>
-      <c r="D35" s="400"/>
+      <c r="A35" s="398"/>
+      <c r="B35" s="399"/>
+      <c r="C35" s="399"/>
+      <c r="D35" s="399"/>
       <c r="E35" s="11"/>
-      <c r="F35" s="309"/>
-      <c r="G35" s="309"/>
+      <c r="F35" s="308"/>
+      <c r="G35" s="308"/>
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
-      <c r="J35" s="309"/>
-      <c r="K35" s="309"/>
-      <c r="L35" s="309"/>
-      <c r="M35" s="324"/>
+      <c r="J35" s="308"/>
+      <c r="K35" s="308"/>
+      <c r="L35" s="308"/>
+      <c r="M35" s="323"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A36" s="399"/>
-      <c r="B36" s="400"/>
-      <c r="C36" s="400"/>
-      <c r="D36" s="400"/>
+      <c r="A36" s="398"/>
+      <c r="B36" s="399"/>
+      <c r="C36" s="399"/>
+      <c r="D36" s="399"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="309"/>
-      <c r="G36" s="309"/>
+      <c r="F36" s="308"/>
+      <c r="G36" s="308"/>
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
-      <c r="J36" s="309"/>
-      <c r="K36" s="309"/>
-      <c r="L36" s="309"/>
-      <c r="M36" s="324"/>
+      <c r="J36" s="308"/>
+      <c r="K36" s="308"/>
+      <c r="L36" s="308"/>
+      <c r="M36" s="323"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A37" s="399"/>
-      <c r="B37" s="400"/>
-      <c r="C37" s="400"/>
-      <c r="D37" s="400"/>
+      <c r="A37" s="398"/>
+      <c r="B37" s="399"/>
+      <c r="C37" s="399"/>
+      <c r="D37" s="399"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="309"/>
-      <c r="G37" s="309"/>
+      <c r="F37" s="308"/>
+      <c r="G37" s="308"/>
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
-      <c r="J37" s="309"/>
-      <c r="K37" s="309"/>
-      <c r="L37" s="309"/>
-      <c r="M37" s="324"/>
+      <c r="J37" s="308"/>
+      <c r="K37" s="308"/>
+      <c r="L37" s="308"/>
+      <c r="M37" s="323"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A38" s="399"/>
-      <c r="B38" s="400"/>
-      <c r="C38" s="400"/>
-      <c r="D38" s="400"/>
+      <c r="A38" s="398"/>
+      <c r="B38" s="399"/>
+      <c r="C38" s="399"/>
+      <c r="D38" s="399"/>
       <c r="E38" s="11"/>
-      <c r="F38" s="309"/>
-      <c r="G38" s="309"/>
+      <c r="F38" s="308"/>
+      <c r="G38" s="308"/>
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
-      <c r="J38" s="309"/>
-      <c r="K38" s="309"/>
-      <c r="L38" s="309"/>
-      <c r="M38" s="324"/>
+      <c r="J38" s="308"/>
+      <c r="K38" s="308"/>
+      <c r="L38" s="308"/>
+      <c r="M38" s="323"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A39" s="399"/>
-      <c r="B39" s="400"/>
-      <c r="C39" s="400"/>
-      <c r="D39" s="400"/>
+      <c r="A39" s="398"/>
+      <c r="B39" s="399"/>
+      <c r="C39" s="399"/>
+      <c r="D39" s="399"/>
       <c r="E39" s="11"/>
-      <c r="F39" s="309"/>
-      <c r="G39" s="309"/>
+      <c r="F39" s="308"/>
+      <c r="G39" s="308"/>
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
-      <c r="J39" s="309"/>
-      <c r="K39" s="309"/>
-      <c r="L39" s="309"/>
-      <c r="M39" s="324"/>
+      <c r="J39" s="308"/>
+      <c r="K39" s="308"/>
+      <c r="L39" s="308"/>
+      <c r="M39" s="323"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A40" s="399"/>
-      <c r="B40" s="400"/>
-      <c r="C40" s="400"/>
-      <c r="D40" s="400"/>
+      <c r="A40" s="398"/>
+      <c r="B40" s="399"/>
+      <c r="C40" s="399"/>
+      <c r="D40" s="399"/>
       <c r="E40" s="11"/>
-      <c r="F40" s="309"/>
-      <c r="G40" s="309"/>
+      <c r="F40" s="308"/>
+      <c r="G40" s="308"/>
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
-      <c r="J40" s="309"/>
-      <c r="K40" s="309"/>
-      <c r="L40" s="309"/>
-      <c r="M40" s="324"/>
+      <c r="J40" s="308"/>
+      <c r="K40" s="308"/>
+      <c r="L40" s="308"/>
+      <c r="M40" s="323"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A41" s="399"/>
-      <c r="B41" s="400"/>
-      <c r="C41" s="400"/>
-      <c r="D41" s="400"/>
+      <c r="A41" s="398"/>
+      <c r="B41" s="399"/>
+      <c r="C41" s="399"/>
+      <c r="D41" s="399"/>
       <c r="E41" s="11"/>
-      <c r="F41" s="309"/>
-      <c r="G41" s="309"/>
+      <c r="F41" s="308"/>
+      <c r="G41" s="308"/>
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
-      <c r="J41" s="309"/>
-      <c r="K41" s="309"/>
-      <c r="L41" s="309"/>
-      <c r="M41" s="324"/>
+      <c r="J41" s="308"/>
+      <c r="K41" s="308"/>
+      <c r="L41" s="308"/>
+      <c r="M41" s="323"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A42" s="399"/>
-      <c r="B42" s="400"/>
-      <c r="C42" s="400"/>
-      <c r="D42" s="400"/>
+      <c r="A42" s="398"/>
+      <c r="B42" s="399"/>
+      <c r="C42" s="399"/>
+      <c r="D42" s="399"/>
       <c r="E42" s="11"/>
-      <c r="F42" s="309"/>
-      <c r="G42" s="309"/>
+      <c r="F42" s="308"/>
+      <c r="G42" s="308"/>
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
-      <c r="J42" s="309"/>
-      <c r="K42" s="309"/>
-      <c r="L42" s="309"/>
-      <c r="M42" s="324"/>
+      <c r="J42" s="308"/>
+      <c r="K42" s="308"/>
+      <c r="L42" s="308"/>
+      <c r="M42" s="323"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A43" s="399"/>
-      <c r="B43" s="400"/>
-      <c r="C43" s="400"/>
-      <c r="D43" s="400"/>
+      <c r="A43" s="398"/>
+      <c r="B43" s="399"/>
+      <c r="C43" s="399"/>
+      <c r="D43" s="399"/>
       <c r="E43" s="11"/>
-      <c r="F43" s="309"/>
-      <c r="G43" s="309"/>
+      <c r="F43" s="308"/>
+      <c r="G43" s="308"/>
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
-      <c r="J43" s="309"/>
-      <c r="K43" s="309"/>
-      <c r="L43" s="309"/>
-      <c r="M43" s="324"/>
+      <c r="J43" s="308"/>
+      <c r="K43" s="308"/>
+      <c r="L43" s="308"/>
+      <c r="M43" s="323"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A44" s="399"/>
-      <c r="B44" s="400"/>
-      <c r="C44" s="400"/>
-      <c r="D44" s="400"/>
+      <c r="A44" s="398"/>
+      <c r="B44" s="399"/>
+      <c r="C44" s="399"/>
+      <c r="D44" s="399"/>
       <c r="E44" s="11"/>
-      <c r="F44" s="309"/>
-      <c r="G44" s="309"/>
+      <c r="F44" s="308"/>
+      <c r="G44" s="308"/>
       <c r="H44" s="11"/>
       <c r="I44" s="11"/>
-      <c r="J44" s="309"/>
-      <c r="K44" s="309"/>
-      <c r="L44" s="309"/>
-      <c r="M44" s="324"/>
+      <c r="J44" s="308"/>
+      <c r="K44" s="308"/>
+      <c r="L44" s="308"/>
+      <c r="M44" s="323"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A45" s="399"/>
-      <c r="B45" s="400"/>
-      <c r="C45" s="400"/>
-      <c r="D45" s="400"/>
+      <c r="A45" s="398"/>
+      <c r="B45" s="399"/>
+      <c r="C45" s="399"/>
+      <c r="D45" s="399"/>
       <c r="E45" s="11"/>
-      <c r="F45" s="309"/>
-      <c r="G45" s="309"/>
+      <c r="F45" s="308"/>
+      <c r="G45" s="308"/>
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
-      <c r="J45" s="309"/>
-      <c r="K45" s="309"/>
-      <c r="L45" s="309"/>
-      <c r="M45" s="324"/>
+      <c r="J45" s="308"/>
+      <c r="K45" s="308"/>
+      <c r="L45" s="308"/>
+      <c r="M45" s="323"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A46" s="399"/>
-      <c r="B46" s="400"/>
-      <c r="C46" s="400"/>
-      <c r="D46" s="400"/>
+      <c r="A46" s="398"/>
+      <c r="B46" s="399"/>
+      <c r="C46" s="399"/>
+      <c r="D46" s="399"/>
       <c r="E46" s="11"/>
-      <c r="F46" s="309"/>
-      <c r="G46" s="309"/>
+      <c r="F46" s="308"/>
+      <c r="G46" s="308"/>
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
-      <c r="J46" s="309"/>
-      <c r="K46" s="309"/>
-      <c r="L46" s="309"/>
-      <c r="M46" s="324"/>
+      <c r="J46" s="308"/>
+      <c r="K46" s="308"/>
+      <c r="L46" s="308"/>
+      <c r="M46" s="323"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A47" s="399"/>
-      <c r="B47" s="400"/>
-      <c r="C47" s="400"/>
-      <c r="D47" s="400"/>
+      <c r="A47" s="398"/>
+      <c r="B47" s="399"/>
+      <c r="C47" s="399"/>
+      <c r="D47" s="399"/>
       <c r="E47" s="11"/>
-      <c r="F47" s="309"/>
-      <c r="G47" s="309"/>
+      <c r="F47" s="308"/>
+      <c r="G47" s="308"/>
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
-      <c r="J47" s="309"/>
-      <c r="K47" s="309"/>
-      <c r="L47" s="309"/>
-      <c r="M47" s="324"/>
+      <c r="J47" s="308"/>
+      <c r="K47" s="308"/>
+      <c r="L47" s="308"/>
+      <c r="M47" s="323"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A48" s="399"/>
-      <c r="B48" s="400"/>
-      <c r="C48" s="400"/>
-      <c r="D48" s="400"/>
+      <c r="A48" s="398"/>
+      <c r="B48" s="399"/>
+      <c r="C48" s="399"/>
+      <c r="D48" s="399"/>
       <c r="E48" s="11"/>
-      <c r="F48" s="309"/>
-      <c r="G48" s="309"/>
+      <c r="F48" s="308"/>
+      <c r="G48" s="308"/>
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
-      <c r="J48" s="309"/>
-      <c r="K48" s="309"/>
-      <c r="L48" s="309"/>
-      <c r="M48" s="324"/>
+      <c r="J48" s="308"/>
+      <c r="K48" s="308"/>
+      <c r="L48" s="308"/>
+      <c r="M48" s="323"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A49" s="399"/>
-      <c r="B49" s="400"/>
-      <c r="C49" s="400"/>
-      <c r="D49" s="400"/>
+      <c r="A49" s="398"/>
+      <c r="B49" s="399"/>
+      <c r="C49" s="399"/>
+      <c r="D49" s="399"/>
       <c r="E49" s="11"/>
-      <c r="F49" s="309"/>
-      <c r="G49" s="309"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
-      <c r="J49" s="309"/>
-      <c r="K49" s="309"/>
-      <c r="L49" s="309"/>
-      <c r="M49" s="324"/>
+      <c r="J49" s="308"/>
+      <c r="K49" s="308"/>
+      <c r="L49" s="308"/>
+      <c r="M49" s="323"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="306" t="s">
+      <c r="A50" s="305" t="s">
         <v>22</v>
       </c>
-      <c r="B50" s="307"/>
-      <c r="C50" s="307"/>
-      <c r="D50" s="307"/>
+      <c r="B50" s="306"/>
+      <c r="C50" s="306"/>
+      <c r="D50" s="306"/>
       <c r="E50" s="68"/>
-      <c r="F50" s="401"/>
-      <c r="G50" s="402"/>
+      <c r="F50" s="400"/>
+      <c r="G50" s="401"/>
       <c r="H50" s="27"/>
       <c r="I50" s="28"/>
-      <c r="J50" s="403"/>
-      <c r="K50" s="403"/>
-      <c r="L50" s="403"/>
-      <c r="M50" s="404"/>
+      <c r="J50" s="402"/>
+      <c r="K50" s="402"/>
+      <c r="L50" s="402"/>
+      <c r="M50" s="403"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A51" s="387" t="s">
+      <c r="A51" s="386" t="s">
         <v>55</v>
       </c>
-      <c r="B51" s="388"/>
-      <c r="C51" s="388"/>
-      <c r="D51" s="388"/>
-      <c r="E51" s="388"/>
-      <c r="F51" s="388"/>
-      <c r="G51" s="388"/>
-      <c r="H51" s="388"/>
-      <c r="I51" s="388"/>
-      <c r="J51" s="388"/>
-      <c r="K51" s="388"/>
-      <c r="L51" s="388"/>
-      <c r="M51" s="389"/>
+      <c r="B51" s="387"/>
+      <c r="C51" s="387"/>
+      <c r="D51" s="387"/>
+      <c r="E51" s="387"/>
+      <c r="F51" s="387"/>
+      <c r="G51" s="387"/>
+      <c r="H51" s="387"/>
+      <c r="I51" s="387"/>
+      <c r="J51" s="387"/>
+      <c r="K51" s="387"/>
+      <c r="L51" s="387"/>
+      <c r="M51" s="388"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="390"/>
-      <c r="B52" s="391"/>
-      <c r="C52" s="391"/>
-      <c r="D52" s="391"/>
-      <c r="E52" s="391"/>
-      <c r="F52" s="391"/>
-      <c r="G52" s="391"/>
-      <c r="H52" s="391"/>
-      <c r="I52" s="391"/>
-      <c r="J52" s="391"/>
-      <c r="K52" s="391"/>
-      <c r="L52" s="391"/>
-      <c r="M52" s="392"/>
+      <c r="A52" s="389"/>
+      <c r="B52" s="390"/>
+      <c r="C52" s="390"/>
+      <c r="D52" s="390"/>
+      <c r="E52" s="390"/>
+      <c r="F52" s="390"/>
+      <c r="G52" s="390"/>
+      <c r="H52" s="390"/>
+      <c r="I52" s="390"/>
+      <c r="J52" s="390"/>
+      <c r="K52" s="390"/>
+      <c r="L52" s="390"/>
+      <c r="M52" s="391"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A53" s="393"/>
-      <c r="B53" s="394"/>
-      <c r="C53" s="394"/>
-      <c r="D53" s="394"/>
-      <c r="E53" s="394"/>
-      <c r="F53" s="394"/>
-      <c r="G53" s="394"/>
-      <c r="H53" s="394"/>
-      <c r="I53" s="394"/>
-      <c r="J53" s="394"/>
-      <c r="K53" s="394"/>
-      <c r="L53" s="394"/>
-      <c r="M53" s="395"/>
+      <c r="A53" s="392"/>
+      <c r="B53" s="393"/>
+      <c r="C53" s="393"/>
+      <c r="D53" s="393"/>
+      <c r="E53" s="393"/>
+      <c r="F53" s="393"/>
+      <c r="G53" s="393"/>
+      <c r="H53" s="393"/>
+      <c r="I53" s="393"/>
+      <c r="J53" s="393"/>
+      <c r="K53" s="393"/>
+      <c r="L53" s="393"/>
+      <c r="M53" s="394"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A54" s="393"/>
-      <c r="B54" s="394"/>
-      <c r="C54" s="394"/>
-      <c r="D54" s="394"/>
-      <c r="E54" s="394"/>
-      <c r="F54" s="394"/>
-      <c r="G54" s="394"/>
-      <c r="H54" s="394"/>
-      <c r="I54" s="394"/>
-      <c r="J54" s="394"/>
-      <c r="K54" s="394"/>
-      <c r="L54" s="394"/>
-      <c r="M54" s="395"/>
+      <c r="A54" s="392"/>
+      <c r="B54" s="393"/>
+      <c r="C54" s="393"/>
+      <c r="D54" s="393"/>
+      <c r="E54" s="393"/>
+      <c r="F54" s="393"/>
+      <c r="G54" s="393"/>
+      <c r="H54" s="393"/>
+      <c r="I54" s="393"/>
+      <c r="J54" s="393"/>
+      <c r="K54" s="393"/>
+      <c r="L54" s="393"/>
+      <c r="M54" s="394"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A55" s="393"/>
-      <c r="B55" s="394"/>
-      <c r="C55" s="394"/>
-      <c r="D55" s="394"/>
-      <c r="E55" s="394"/>
-      <c r="F55" s="394"/>
-      <c r="G55" s="394"/>
-      <c r="H55" s="394"/>
-      <c r="I55" s="394"/>
-      <c r="J55" s="394"/>
-      <c r="K55" s="394"/>
-      <c r="L55" s="394"/>
-      <c r="M55" s="395"/>
+      <c r="A55" s="392"/>
+      <c r="B55" s="393"/>
+      <c r="C55" s="393"/>
+      <c r="D55" s="393"/>
+      <c r="E55" s="393"/>
+      <c r="F55" s="393"/>
+      <c r="G55" s="393"/>
+      <c r="H55" s="393"/>
+      <c r="I55" s="393"/>
+      <c r="J55" s="393"/>
+      <c r="K55" s="393"/>
+      <c r="L55" s="393"/>
+      <c r="M55" s="394"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A56" s="393"/>
-      <c r="B56" s="394"/>
-      <c r="C56" s="394"/>
-      <c r="D56" s="394"/>
-      <c r="E56" s="394"/>
-      <c r="F56" s="394"/>
-      <c r="G56" s="394"/>
-      <c r="H56" s="394"/>
-      <c r="I56" s="394"/>
-      <c r="J56" s="394"/>
-      <c r="K56" s="394"/>
-      <c r="L56" s="394"/>
-      <c r="M56" s="395"/>
+      <c r="A56" s="392"/>
+      <c r="B56" s="393"/>
+      <c r="C56" s="393"/>
+      <c r="D56" s="393"/>
+      <c r="E56" s="393"/>
+      <c r="F56" s="393"/>
+      <c r="G56" s="393"/>
+      <c r="H56" s="393"/>
+      <c r="I56" s="393"/>
+      <c r="J56" s="393"/>
+      <c r="K56" s="393"/>
+      <c r="L56" s="393"/>
+      <c r="M56" s="394"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A57" s="393"/>
-      <c r="B57" s="394"/>
-      <c r="C57" s="394"/>
-      <c r="D57" s="394"/>
-      <c r="E57" s="394"/>
-      <c r="F57" s="394"/>
-      <c r="G57" s="394"/>
-      <c r="H57" s="394"/>
-      <c r="I57" s="394"/>
-      <c r="J57" s="394"/>
-      <c r="K57" s="394"/>
-      <c r="L57" s="394"/>
-      <c r="M57" s="395"/>
+      <c r="A57" s="392"/>
+      <c r="B57" s="393"/>
+      <c r="C57" s="393"/>
+      <c r="D57" s="393"/>
+      <c r="E57" s="393"/>
+      <c r="F57" s="393"/>
+      <c r="G57" s="393"/>
+      <c r="H57" s="393"/>
+      <c r="I57" s="393"/>
+      <c r="J57" s="393"/>
+      <c r="K57" s="393"/>
+      <c r="L57" s="393"/>
+      <c r="M57" s="394"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A58" s="393"/>
-      <c r="B58" s="394"/>
-      <c r="C58" s="394"/>
-      <c r="D58" s="394"/>
-      <c r="E58" s="394"/>
-      <c r="F58" s="394"/>
-      <c r="G58" s="394"/>
-      <c r="H58" s="394"/>
-      <c r="I58" s="394"/>
-      <c r="J58" s="394"/>
-      <c r="K58" s="394"/>
-      <c r="L58" s="394"/>
-      <c r="M58" s="395"/>
+      <c r="A58" s="392"/>
+      <c r="B58" s="393"/>
+      <c r="C58" s="393"/>
+      <c r="D58" s="393"/>
+      <c r="E58" s="393"/>
+      <c r="F58" s="393"/>
+      <c r="G58" s="393"/>
+      <c r="H58" s="393"/>
+      <c r="I58" s="393"/>
+      <c r="J58" s="393"/>
+      <c r="K58" s="393"/>
+      <c r="L58" s="393"/>
+      <c r="M58" s="394"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A59" s="393"/>
-      <c r="B59" s="394"/>
-      <c r="C59" s="394"/>
-      <c r="D59" s="394"/>
-      <c r="E59" s="394"/>
-      <c r="F59" s="394"/>
-      <c r="G59" s="394"/>
-      <c r="H59" s="394"/>
-      <c r="I59" s="394"/>
-      <c r="J59" s="394"/>
-      <c r="K59" s="394"/>
-      <c r="L59" s="394"/>
-      <c r="M59" s="395"/>
+      <c r="A59" s="392"/>
+      <c r="B59" s="393"/>
+      <c r="C59" s="393"/>
+      <c r="D59" s="393"/>
+      <c r="E59" s="393"/>
+      <c r="F59" s="393"/>
+      <c r="G59" s="393"/>
+      <c r="H59" s="393"/>
+      <c r="I59" s="393"/>
+      <c r="J59" s="393"/>
+      <c r="K59" s="393"/>
+      <c r="L59" s="393"/>
+      <c r="M59" s="394"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A60" s="396"/>
-      <c r="B60" s="397"/>
-      <c r="C60" s="397"/>
-      <c r="D60" s="397"/>
-      <c r="E60" s="397"/>
-      <c r="F60" s="397"/>
-      <c r="G60" s="397"/>
-      <c r="H60" s="397"/>
-      <c r="I60" s="397"/>
-      <c r="J60" s="397"/>
-      <c r="K60" s="397"/>
-      <c r="L60" s="397"/>
-      <c r="M60" s="398"/>
+      <c r="A60" s="395"/>
+      <c r="B60" s="396"/>
+      <c r="C60" s="396"/>
+      <c r="D60" s="396"/>
+      <c r="E60" s="396"/>
+      <c r="F60" s="396"/>
+      <c r="G60" s="396"/>
+      <c r="H60" s="396"/>
+      <c r="I60" s="396"/>
+      <c r="J60" s="396"/>
+      <c r="K60" s="396"/>
+      <c r="L60" s="396"/>
+      <c r="M60" s="397"/>
     </row>
     <row r="61" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="26"/>
@@ -6361,14 +6369,13 @@
       <c r="J61" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="149">
+  <mergeCells count="150">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="J5:M5"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="J6:M6"/>
-    <mergeCell ref="C1:K1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A3:D4"/>
@@ -6377,6 +6384,8 @@
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="J3:M4"/>
     <mergeCell ref="H4:I4"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:K1"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="J9:M9"/>
@@ -6531,147 +6540,147 @@
     <col min="9" max="9" width="6.7109375" customWidth="1"/>
     <col min="11" max="11" width="17.140625" customWidth="1"/>
     <col min="12" max="12" width="8.42578125" customWidth="1"/>
-    <col min="13" max="13" width="8" style="112" customWidth="1"/>
+    <col min="13" max="13" width="8" style="111" customWidth="1"/>
     <col min="14" max="14" width="0.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90" t="s">
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="90"/>
-      <c r="K1" s="90"/>
-      <c r="L1" s="123" t="s">
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="122" t="s">
         <v>66</v>
       </c>
-      <c r="M1" s="124"/>
-      <c r="N1" s="108"/>
+      <c r="M1" s="123"/>
+      <c r="N1" s="107"/>
     </row>
     <row r="2" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="120" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="122"/>
-      <c r="C2" s="122"/>
-      <c r="D2" s="122"/>
-      <c r="E2" s="122"/>
-      <c r="F2" s="122"/>
-      <c r="G2" s="122"/>
-      <c r="H2" s="122"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="108"/>
+      <c r="B2" s="121"/>
+      <c r="C2" s="121"/>
+      <c r="D2" s="121"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="107"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="129" t="s">
+      <c r="A3" s="128" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="130"/>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="94" t="s">
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="93" t="s">
         <v>72</v>
       </c>
-      <c r="J3" s="87"/>
-      <c r="K3" s="95"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="96"/>
-      <c r="N3" s="108"/>
+      <c r="J3" s="86"/>
+      <c r="K3" s="94"/>
+      <c r="L3" s="86"/>
+      <c r="M3" s="95"/>
+      <c r="N3" s="107"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="129" t="s">
+      <c r="A4" s="128" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="130"/>
-      <c r="C4" s="130"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="130"/>
-      <c r="F4" s="130"/>
-      <c r="G4" s="130"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="132"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113"/>
-      <c r="M4" s="114"/>
-      <c r="N4" s="108"/>
+      <c r="B4" s="129"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="129"/>
+      <c r="I4" s="131"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="112"/>
+      <c r="M4" s="113"/>
+      <c r="N4" s="107"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="129" t="s">
+      <c r="A5" s="128" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="130"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="130"/>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="132"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="113"/>
-      <c r="L5" s="113"/>
-      <c r="M5" s="114"/>
-      <c r="N5" s="108"/>
+      <c r="B5" s="129"/>
+      <c r="C5" s="129"/>
+      <c r="D5" s="129"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="129"/>
+      <c r="G5" s="129"/>
+      <c r="H5" s="129"/>
+      <c r="I5" s="131"/>
+      <c r="J5" s="112"/>
+      <c r="K5" s="112"/>
+      <c r="L5" s="112"/>
+      <c r="M5" s="113"/>
+      <c r="N5" s="107"/>
     </row>
     <row r="6" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="127" t="s">
+      <c r="A6" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="128"/>
-      <c r="C6" s="128"/>
-      <c r="D6" s="128"/>
-      <c r="E6" s="128"/>
-      <c r="F6" s="131" t="s">
+      <c r="B6" s="127"/>
+      <c r="C6" s="127"/>
+      <c r="D6" s="127"/>
+      <c r="E6" s="127"/>
+      <c r="F6" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="131"/>
-      <c r="H6" s="410" t="s">
+      <c r="G6" s="130"/>
+      <c r="H6" s="409" t="s">
         <v>80</v>
       </c>
-      <c r="I6" s="133"/>
-      <c r="J6" s="134"/>
-      <c r="K6" s="134"/>
-      <c r="L6" s="134"/>
-      <c r="M6" s="135"/>
-      <c r="N6" s="108"/>
+      <c r="I6" s="132"/>
+      <c r="J6" s="133"/>
+      <c r="K6" s="133"/>
+      <c r="L6" s="133"/>
+      <c r="M6" s="134"/>
+      <c r="N6" s="107"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="144" t="s">
+      <c r="A7" s="143" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="145"/>
-      <c r="C7" s="145"/>
-      <c r="D7" s="145"/>
-      <c r="E7" s="145"/>
-      <c r="F7" s="145"/>
-      <c r="G7" s="145"/>
-      <c r="H7" s="145"/>
-      <c r="I7" s="97" t="s">
+      <c r="B7" s="144"/>
+      <c r="C7" s="144"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="144"/>
+      <c r="F7" s="144"/>
+      <c r="G7" s="144"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="96" t="s">
         <v>74</v>
       </c>
-      <c r="J7" s="98"/>
-      <c r="K7" s="99"/>
-      <c r="L7" s="98"/>
-      <c r="M7" s="100"/>
-      <c r="N7" s="108"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="98"/>
+      <c r="L7" s="97"/>
+      <c r="M7" s="99"/>
+      <c r="N7" s="107"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="31" t="s">
@@ -6680,149 +6689,149 @@
       <c r="B8" s="84"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
-      <c r="E8" s="149" t="s">
+      <c r="E8" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="149"/>
-      <c r="G8" s="149"/>
-      <c r="H8" s="149"/>
-      <c r="I8" s="136" t="s">
+      <c r="F8" s="148"/>
+      <c r="G8" s="148"/>
+      <c r="H8" s="148"/>
+      <c r="I8" s="135" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="130"/>
-      <c r="K8" s="130"/>
-      <c r="L8" s="130"/>
-      <c r="M8" s="137"/>
-      <c r="N8" s="108"/>
+      <c r="J8" s="129"/>
+      <c r="K8" s="129"/>
+      <c r="L8" s="129"/>
+      <c r="M8" s="136"/>
+      <c r="N8" s="107"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="101" t="s">
+      <c r="I9" s="100" t="s">
         <v>68</v>
       </c>
-      <c r="J9" s="102"/>
-      <c r="K9" s="102"/>
-      <c r="L9" s="102"/>
-      <c r="M9" s="103"/>
-      <c r="N9" s="108"/>
+      <c r="J9" s="101"/>
+      <c r="K9" s="101"/>
+      <c r="L9" s="101"/>
+      <c r="M9" s="102"/>
+      <c r="N9" s="107"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="180"/>
-      <c r="D10" s="180"/>
-      <c r="E10" s="180"/>
-      <c r="F10" s="180"/>
-      <c r="G10" s="180"/>
-      <c r="I10" s="91" t="s">
+      <c r="C10" s="179"/>
+      <c r="D10" s="179"/>
+      <c r="E10" s="179"/>
+      <c r="F10" s="179"/>
+      <c r="G10" s="179"/>
+      <c r="I10" s="90" t="s">
         <v>75</v>
       </c>
       <c r="J10" s="29"/>
       <c r="K10" s="29"/>
       <c r="L10" s="29"/>
-      <c r="M10" s="104"/>
-      <c r="N10" s="108"/>
+      <c r="M10" s="103"/>
+      <c r="N10" s="107"/>
     </row>
     <row r="11" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="150" t="s">
+      <c r="A11" s="149" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="128"/>
-      <c r="C11" s="128"/>
-      <c r="D11" s="128"/>
-      <c r="E11" s="128"/>
-      <c r="F11" s="131" t="s">
+      <c r="B11" s="127"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="131"/>
-      <c r="H11" s="410" t="s">
+      <c r="G11" s="130"/>
+      <c r="H11" s="409" t="s">
         <v>80</v>
       </c>
-      <c r="I11" s="115" t="s">
+      <c r="I11" s="114" t="s">
         <v>69</v>
       </c>
-      <c r="J11" s="116"/>
-      <c r="K11" s="105"/>
-      <c r="L11" s="105"/>
-      <c r="M11" s="106"/>
-      <c r="N11" s="108"/>
+      <c r="J11" s="115"/>
+      <c r="K11" s="104"/>
+      <c r="L11" s="104"/>
+      <c r="M11" s="105"/>
+      <c r="N11" s="107"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="138" t="s">
+      <c r="A12" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="139"/>
-      <c r="C12" s="139"/>
-      <c r="D12" s="139"/>
-      <c r="E12" s="139"/>
-      <c r="F12" s="139"/>
-      <c r="G12" s="139"/>
-      <c r="H12" s="139"/>
-      <c r="I12" s="132"/>
-      <c r="J12" s="113"/>
-      <c r="K12" s="113"/>
-      <c r="L12" s="113"/>
-      <c r="M12" s="114"/>
-      <c r="N12" s="108"/>
+      <c r="B12" s="138"/>
+      <c r="C12" s="138"/>
+      <c r="D12" s="138"/>
+      <c r="E12" s="138"/>
+      <c r="F12" s="138"/>
+      <c r="G12" s="138"/>
+      <c r="H12" s="138"/>
+      <c r="I12" s="131"/>
+      <c r="J12" s="112"/>
+      <c r="K12" s="112"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="113"/>
+      <c r="N12" s="107"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="125" t="s">
+      <c r="A13" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="126"/>
-      <c r="C13" s="126"/>
-      <c r="D13" s="126"/>
-      <c r="E13" s="126"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="126"/>
-      <c r="H13" s="126"/>
-      <c r="I13" s="132"/>
-      <c r="J13" s="113"/>
-      <c r="K13" s="113"/>
-      <c r="L13" s="113"/>
-      <c r="M13" s="114"/>
-      <c r="N13" s="108"/>
+      <c r="B13" s="125"/>
+      <c r="C13" s="125"/>
+      <c r="D13" s="125"/>
+      <c r="E13" s="125"/>
+      <c r="F13" s="125"/>
+      <c r="G13" s="125"/>
+      <c r="H13" s="125"/>
+      <c r="I13" s="131"/>
+      <c r="J13" s="112"/>
+      <c r="K13" s="112"/>
+      <c r="L13" s="112"/>
+      <c r="M13" s="113"/>
+      <c r="N13" s="107"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="148" t="s">
+      <c r="A14" s="147" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="130"/>
-      <c r="C14" s="130"/>
-      <c r="D14" s="130"/>
-      <c r="E14" s="130"/>
-      <c r="F14" s="130"/>
-      <c r="G14" s="130"/>
-      <c r="H14" s="130"/>
-      <c r="I14" s="133"/>
-      <c r="J14" s="134"/>
-      <c r="K14" s="134"/>
-      <c r="L14" s="134"/>
-      <c r="M14" s="135"/>
-      <c r="N14" s="108"/>
+      <c r="B14" s="129"/>
+      <c r="C14" s="129"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="129"/>
+      <c r="F14" s="129"/>
+      <c r="G14" s="129"/>
+      <c r="H14" s="129"/>
+      <c r="I14" s="132"/>
+      <c r="J14" s="133"/>
+      <c r="K14" s="133"/>
+      <c r="L14" s="133"/>
+      <c r="M14" s="134"/>
+      <c r="N14" s="107"/>
     </row>
     <row r="15" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="158" t="s">
+      <c r="A15" s="157" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="159"/>
-      <c r="C15" s="159"/>
-      <c r="D15" s="159"/>
-      <c r="E15" s="159"/>
-      <c r="F15" s="159"/>
-      <c r="G15" s="159"/>
-      <c r="H15" s="160"/>
-      <c r="I15" s="155" t="s">
+      <c r="B15" s="158"/>
+      <c r="C15" s="158"/>
+      <c r="D15" s="158"/>
+      <c r="E15" s="158"/>
+      <c r="F15" s="158"/>
+      <c r="G15" s="158"/>
+      <c r="H15" s="159"/>
+      <c r="I15" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="156"/>
-      <c r="K15" s="156"/>
-      <c r="L15" s="156"/>
-      <c r="M15" s="157"/>
-      <c r="N15" s="108"/>
+      <c r="J15" s="155"/>
+      <c r="K15" s="155"/>
+      <c r="L15" s="155"/>
+      <c r="M15" s="156"/>
+      <c r="N15" s="107"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="61" t="s">
@@ -6832,341 +6841,341 @@
       <c r="C16" s="62"/>
       <c r="D16" s="62"/>
       <c r="E16" s="62"/>
-      <c r="F16" s="240"/>
-      <c r="G16" s="240"/>
-      <c r="H16" s="241"/>
-      <c r="I16" s="170" t="s">
+      <c r="F16" s="239"/>
+      <c r="G16" s="239"/>
+      <c r="H16" s="240"/>
+      <c r="I16" s="169" t="s">
         <v>78</v>
       </c>
-      <c r="J16" s="171"/>
-      <c r="K16" s="171"/>
-      <c r="L16" s="171"/>
-      <c r="M16" s="172"/>
-      <c r="N16" s="108"/>
+      <c r="J16" s="170"/>
+      <c r="K16" s="170"/>
+      <c r="L16" s="170"/>
+      <c r="M16" s="171"/>
+      <c r="N16" s="107"/>
     </row>
     <row r="17" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="411"/>
-      <c r="B17" s="412"/>
-      <c r="C17" s="412"/>
-      <c r="D17" s="412"/>
-      <c r="E17" s="412"/>
-      <c r="F17" s="412"/>
-      <c r="G17" s="412"/>
-      <c r="H17" s="412"/>
-      <c r="I17" s="408" t="s">
+      <c r="A17" s="410"/>
+      <c r="B17" s="411"/>
+      <c r="C17" s="411"/>
+      <c r="D17" s="411"/>
+      <c r="E17" s="411"/>
+      <c r="F17" s="411"/>
+      <c r="G17" s="411"/>
+      <c r="H17" s="411"/>
+      <c r="I17" s="407" t="s">
         <v>80</v>
       </c>
-      <c r="J17" s="409"/>
-      <c r="K17" s="151" t="s">
+      <c r="J17" s="408"/>
+      <c r="K17" s="150" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="151"/>
-      <c r="M17" s="152"/>
-      <c r="N17" s="108"/>
+      <c r="L17" s="150"/>
+      <c r="M17" s="151"/>
+      <c r="N17" s="107"/>
     </row>
     <row r="18" spans="1:14" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="413"/>
-      <c r="B18" s="414"/>
-      <c r="C18" s="414"/>
-      <c r="D18" s="414"/>
-      <c r="E18" s="414"/>
-      <c r="F18" s="414"/>
-      <c r="G18" s="414"/>
-      <c r="H18" s="414"/>
-      <c r="I18" s="169" t="s">
+      <c r="A18" s="412"/>
+      <c r="B18" s="413"/>
+      <c r="C18" s="413"/>
+      <c r="D18" s="413"/>
+      <c r="E18" s="413"/>
+      <c r="F18" s="413"/>
+      <c r="G18" s="413"/>
+      <c r="H18" s="413"/>
+      <c r="I18" s="168" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="169"/>
-      <c r="K18" s="153"/>
-      <c r="L18" s="153"/>
-      <c r="M18" s="154"/>
-      <c r="N18" s="108"/>
+      <c r="J18" s="168"/>
+      <c r="K18" s="152"/>
+      <c r="L18" s="152"/>
+      <c r="M18" s="153"/>
+      <c r="N18" s="107"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="173" t="s">
+      <c r="A19" s="172" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="174"/>
-      <c r="C19" s="174"/>
-      <c r="D19" s="174"/>
-      <c r="E19" s="174"/>
-      <c r="F19" s="174"/>
-      <c r="G19" s="174"/>
-      <c r="H19" s="174"/>
-      <c r="I19" s="174"/>
-      <c r="J19" s="174"/>
-      <c r="K19" s="174"/>
-      <c r="L19" s="174"/>
-      <c r="M19" s="175"/>
-      <c r="N19" s="108"/>
+      <c r="B19" s="173"/>
+      <c r="C19" s="173"/>
+      <c r="D19" s="173"/>
+      <c r="E19" s="173"/>
+      <c r="F19" s="173"/>
+      <c r="G19" s="173"/>
+      <c r="H19" s="173"/>
+      <c r="I19" s="173"/>
+      <c r="J19" s="173"/>
+      <c r="K19" s="173"/>
+      <c r="L19" s="173"/>
+      <c r="M19" s="174"/>
+      <c r="N19" s="107"/>
     </row>
     <row r="20" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="176" t="s">
+      <c r="A20" s="175" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="177"/>
-      <c r="C20" s="177"/>
-      <c r="D20" s="177"/>
-      <c r="E20" s="177" t="s">
+      <c r="B20" s="176"/>
+      <c r="C20" s="176"/>
+      <c r="D20" s="176"/>
+      <c r="E20" s="176" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="177" t="s">
+      <c r="F20" s="176" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="177"/>
-      <c r="H20" s="167" t="s">
+      <c r="G20" s="176"/>
+      <c r="H20" s="166" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="168"/>
-      <c r="J20" s="161" t="s">
+      <c r="I20" s="167"/>
+      <c r="J20" s="160" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="162"/>
-      <c r="L20" s="162"/>
-      <c r="M20" s="163"/>
-      <c r="N20" s="108"/>
+      <c r="K20" s="161"/>
+      <c r="L20" s="161"/>
+      <c r="M20" s="162"/>
+      <c r="N20" s="107"/>
     </row>
     <row r="21" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="176"/>
-      <c r="B21" s="177"/>
-      <c r="C21" s="177"/>
-      <c r="D21" s="177"/>
-      <c r="E21" s="177"/>
-      <c r="F21" s="177"/>
-      <c r="G21" s="177"/>
-      <c r="H21" s="146" t="s">
+      <c r="A21" s="175"/>
+      <c r="B21" s="176"/>
+      <c r="C21" s="176"/>
+      <c r="D21" s="176"/>
+      <c r="E21" s="176"/>
+      <c r="F21" s="176"/>
+      <c r="G21" s="176"/>
+      <c r="H21" s="145" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="147"/>
-      <c r="J21" s="164"/>
-      <c r="K21" s="165"/>
-      <c r="L21" s="165"/>
-      <c r="M21" s="166"/>
-      <c r="N21" s="108"/>
+      <c r="I21" s="146"/>
+      <c r="J21" s="163"/>
+      <c r="K21" s="164"/>
+      <c r="L21" s="164"/>
+      <c r="M21" s="165"/>
+      <c r="N21" s="107"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" s="178"/>
-      <c r="B22" s="143"/>
-      <c r="C22" s="143"/>
-      <c r="D22" s="179"/>
+      <c r="A22" s="177"/>
+      <c r="B22" s="142"/>
+      <c r="C22" s="142"/>
+      <c r="D22" s="178"/>
       <c r="E22" s="9"/>
-      <c r="F22" s="143"/>
-      <c r="G22" s="143"/>
+      <c r="F22" s="142"/>
+      <c r="G22" s="142"/>
       <c r="H22" s="9" t="s">
         <v>51</v>
       </c>
       <c r="I22" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="143"/>
-      <c r="K22" s="143"/>
-      <c r="L22" s="143"/>
-      <c r="M22" s="143"/>
-      <c r="N22" s="108"/>
+      <c r="J22" s="142"/>
+      <c r="K22" s="142"/>
+      <c r="L22" s="142"/>
+      <c r="M22" s="142"/>
+      <c r="N22" s="107"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="140"/>
-      <c r="B23" s="141"/>
-      <c r="C23" s="141"/>
-      <c r="D23" s="142"/>
+      <c r="A23" s="139"/>
+      <c r="B23" s="140"/>
+      <c r="C23" s="140"/>
+      <c r="D23" s="141"/>
       <c r="E23" s="9"/>
-      <c r="F23" s="143"/>
-      <c r="G23" s="143"/>
+      <c r="F23" s="142"/>
+      <c r="G23" s="142"/>
       <c r="H23" s="9" t="s">
         <v>51</v>
       </c>
       <c r="I23" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J23" s="143"/>
-      <c r="K23" s="143"/>
-      <c r="L23" s="143"/>
-      <c r="M23" s="143"/>
-      <c r="N23" s="108"/>
+      <c r="J23" s="142"/>
+      <c r="K23" s="142"/>
+      <c r="L23" s="142"/>
+      <c r="M23" s="142"/>
+      <c r="N23" s="107"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="140"/>
-      <c r="B24" s="141"/>
-      <c r="C24" s="141"/>
-      <c r="D24" s="142"/>
+      <c r="A24" s="139"/>
+      <c r="B24" s="140"/>
+      <c r="C24" s="140"/>
+      <c r="D24" s="141"/>
       <c r="E24" s="9"/>
-      <c r="F24" s="143"/>
-      <c r="G24" s="143"/>
+      <c r="F24" s="142"/>
+      <c r="G24" s="142"/>
       <c r="H24" s="9" t="s">
         <v>51</v>
       </c>
       <c r="I24" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J24" s="143"/>
-      <c r="K24" s="143"/>
-      <c r="L24" s="143"/>
-      <c r="M24" s="143"/>
-      <c r="N24" s="108"/>
+      <c r="J24" s="142"/>
+      <c r="K24" s="142"/>
+      <c r="L24" s="142"/>
+      <c r="M24" s="142"/>
+      <c r="N24" s="107"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="140"/>
-      <c r="B25" s="141"/>
-      <c r="C25" s="141"/>
-      <c r="D25" s="142"/>
+      <c r="A25" s="139"/>
+      <c r="B25" s="140"/>
+      <c r="C25" s="140"/>
+      <c r="D25" s="141"/>
       <c r="E25" s="9"/>
-      <c r="F25" s="143"/>
-      <c r="G25" s="143"/>
+      <c r="F25" s="142"/>
+      <c r="G25" s="142"/>
       <c r="H25" s="9" t="s">
         <v>51</v>
       </c>
       <c r="I25" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J25" s="143"/>
-      <c r="K25" s="143"/>
-      <c r="L25" s="143"/>
-      <c r="M25" s="143"/>
-      <c r="N25" s="108"/>
+      <c r="J25" s="142"/>
+      <c r="K25" s="142"/>
+      <c r="L25" s="142"/>
+      <c r="M25" s="142"/>
+      <c r="N25" s="107"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="140"/>
-      <c r="B26" s="141"/>
-      <c r="C26" s="141"/>
-      <c r="D26" s="142"/>
+      <c r="A26" s="139"/>
+      <c r="B26" s="140"/>
+      <c r="C26" s="140"/>
+      <c r="D26" s="141"/>
       <c r="E26" s="9"/>
-      <c r="F26" s="143"/>
-      <c r="G26" s="143"/>
+      <c r="F26" s="142"/>
+      <c r="G26" s="142"/>
       <c r="H26" s="9" t="s">
         <v>51</v>
       </c>
       <c r="I26" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J26" s="143"/>
-      <c r="K26" s="143"/>
-      <c r="L26" s="143"/>
-      <c r="M26" s="143"/>
-      <c r="N26" s="108"/>
+      <c r="J26" s="142"/>
+      <c r="K26" s="142"/>
+      <c r="L26" s="142"/>
+      <c r="M26" s="142"/>
+      <c r="N26" s="107"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="140"/>
-      <c r="B27" s="141"/>
-      <c r="C27" s="141"/>
-      <c r="D27" s="142"/>
+      <c r="A27" s="139"/>
+      <c r="B27" s="140"/>
+      <c r="C27" s="140"/>
+      <c r="D27" s="141"/>
       <c r="E27" s="9"/>
-      <c r="F27" s="143"/>
-      <c r="G27" s="143"/>
+      <c r="F27" s="142"/>
+      <c r="G27" s="142"/>
       <c r="H27" s="9" t="s">
         <v>51</v>
       </c>
       <c r="I27" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="143"/>
-      <c r="K27" s="143"/>
-      <c r="L27" s="143"/>
-      <c r="M27" s="143"/>
-      <c r="N27" s="108"/>
+      <c r="J27" s="142"/>
+      <c r="K27" s="142"/>
+      <c r="L27" s="142"/>
+      <c r="M27" s="142"/>
+      <c r="N27" s="107"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="140"/>
-      <c r="B28" s="141"/>
-      <c r="C28" s="141"/>
-      <c r="D28" s="142"/>
+      <c r="A28" s="139"/>
+      <c r="B28" s="140"/>
+      <c r="C28" s="140"/>
+      <c r="D28" s="141"/>
       <c r="E28" s="9"/>
-      <c r="F28" s="143"/>
-      <c r="G28" s="143"/>
+      <c r="F28" s="142"/>
+      <c r="G28" s="142"/>
       <c r="H28" s="9" t="s">
         <v>51</v>
       </c>
       <c r="I28" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J28" s="143"/>
-      <c r="K28" s="143"/>
-      <c r="L28" s="143"/>
-      <c r="M28" s="143"/>
-      <c r="N28" s="108"/>
+      <c r="J28" s="142"/>
+      <c r="K28" s="142"/>
+      <c r="L28" s="142"/>
+      <c r="M28" s="142"/>
+      <c r="N28" s="107"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="140"/>
-      <c r="B29" s="141"/>
-      <c r="C29" s="141"/>
-      <c r="D29" s="142"/>
+      <c r="A29" s="139"/>
+      <c r="B29" s="140"/>
+      <c r="C29" s="140"/>
+      <c r="D29" s="141"/>
       <c r="E29" s="9"/>
-      <c r="F29" s="143"/>
-      <c r="G29" s="143"/>
+      <c r="F29" s="142"/>
+      <c r="G29" s="142"/>
       <c r="H29" s="9" t="s">
         <v>51</v>
       </c>
       <c r="I29" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J29" s="143"/>
-      <c r="K29" s="143"/>
-      <c r="L29" s="143"/>
-      <c r="M29" s="143"/>
-      <c r="N29" s="108"/>
+      <c r="J29" s="142"/>
+      <c r="K29" s="142"/>
+      <c r="L29" s="142"/>
+      <c r="M29" s="142"/>
+      <c r="N29" s="107"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" s="194" t="s">
+      <c r="A30" s="193" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="195"/>
-      <c r="C30" s="195"/>
-      <c r="D30" s="195"/>
+      <c r="B30" s="194"/>
+      <c r="C30" s="194"/>
+      <c r="D30" s="194"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="184"/>
-      <c r="G30" s="143"/>
-      <c r="H30" s="119"/>
-      <c r="I30" s="120"/>
-      <c r="J30" s="119"/>
-      <c r="K30" s="181"/>
-      <c r="L30" s="181"/>
-      <c r="M30" s="120"/>
-      <c r="N30" s="108"/>
+      <c r="F30" s="183"/>
+      <c r="G30" s="142"/>
+      <c r="H30" s="118"/>
+      <c r="I30" s="119"/>
+      <c r="J30" s="118"/>
+      <c r="K30" s="180"/>
+      <c r="L30" s="180"/>
+      <c r="M30" s="119"/>
+      <c r="N30" s="107"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A31" s="185" t="s">
+      <c r="A31" s="184" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="186"/>
-      <c r="C31" s="186"/>
-      <c r="D31" s="186"/>
-      <c r="E31" s="186"/>
-      <c r="F31" s="186"/>
-      <c r="G31" s="186"/>
-      <c r="H31" s="186"/>
-      <c r="I31" s="186"/>
-      <c r="J31" s="186"/>
-      <c r="K31" s="186"/>
-      <c r="L31" s="186"/>
-      <c r="M31" s="187"/>
-      <c r="N31" s="108"/>
+      <c r="B31" s="185"/>
+      <c r="C31" s="185"/>
+      <c r="D31" s="185"/>
+      <c r="E31" s="185"/>
+      <c r="F31" s="185"/>
+      <c r="G31" s="185"/>
+      <c r="H31" s="185"/>
+      <c r="I31" s="185"/>
+      <c r="J31" s="185"/>
+      <c r="K31" s="185"/>
+      <c r="L31" s="185"/>
+      <c r="M31" s="186"/>
+      <c r="N31" s="107"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A32" s="191" t="s">
+      <c r="A32" s="190" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="190"/>
-      <c r="C32" s="190" t="s">
+      <c r="B32" s="189"/>
+      <c r="C32" s="189" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="190"/>
-      <c r="E32" s="192" t="s">
+      <c r="D32" s="189"/>
+      <c r="E32" s="191" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="193" t="s">
+      <c r="F32" s="192" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="188" t="s">
+      <c r="G32" s="187" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="188"/>
-      <c r="I32" s="188"/>
-      <c r="J32" s="188"/>
-      <c r="K32" s="188"/>
-      <c r="L32" s="190" t="s">
+      <c r="H32" s="187"/>
+      <c r="I32" s="187"/>
+      <c r="J32" s="187"/>
+      <c r="K32" s="187"/>
+      <c r="L32" s="189" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="190"/>
-      <c r="N32" s="108"/>
+      <c r="M32" s="189"/>
+      <c r="N32" s="107"/>
     </row>
     <row r="33" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
@@ -7181,22 +7190,22 @@
       <c r="D33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="192"/>
-      <c r="F33" s="193"/>
-      <c r="G33" s="189" t="s">
+      <c r="E33" s="191"/>
+      <c r="F33" s="192"/>
+      <c r="G33" s="188" t="s">
         <v>50</v>
       </c>
-      <c r="H33" s="189"/>
-      <c r="I33" s="189"/>
-      <c r="J33" s="189"/>
-      <c r="K33" s="189"/>
+      <c r="H33" s="188"/>
+      <c r="I33" s="188"/>
+      <c r="J33" s="188"/>
+      <c r="K33" s="188"/>
       <c r="L33" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="N33" s="108"/>
+      <c r="N33" s="107"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A34" s="37"/>
@@ -7209,16 +7218,16 @@
       </c>
       <c r="E34" s="8"/>
       <c r="F34" s="9"/>
-      <c r="G34" s="179" t="s">
+      <c r="G34" s="178" t="s">
         <v>71</v>
       </c>
-      <c r="H34" s="182"/>
-      <c r="I34" s="182"/>
-      <c r="J34" s="182"/>
-      <c r="K34" s="183"/>
+      <c r="H34" s="181"/>
+      <c r="I34" s="181"/>
+      <c r="J34" s="181"/>
+      <c r="K34" s="182"/>
       <c r="L34" s="38"/>
       <c r="M34" s="38"/>
-      <c r="N34" s="108"/>
+      <c r="N34" s="107"/>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A35" s="39"/>
@@ -7227,14 +7236,14 @@
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="38"/>
-      <c r="G35" s="179"/>
-      <c r="H35" s="182"/>
-      <c r="I35" s="182"/>
-      <c r="J35" s="182"/>
-      <c r="K35" s="183"/>
+      <c r="G35" s="178"/>
+      <c r="H35" s="181"/>
+      <c r="I35" s="181"/>
+      <c r="J35" s="181"/>
+      <c r="K35" s="182"/>
       <c r="L35" s="38"/>
       <c r="M35" s="38"/>
-      <c r="N35" s="108"/>
+      <c r="N35" s="107"/>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A36" s="39"/>
@@ -7243,14 +7252,14 @@
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="38"/>
-      <c r="G36" s="179"/>
-      <c r="H36" s="182"/>
-      <c r="I36" s="182"/>
-      <c r="J36" s="182"/>
-      <c r="K36" s="183"/>
+      <c r="G36" s="178"/>
+      <c r="H36" s="181"/>
+      <c r="I36" s="181"/>
+      <c r="J36" s="181"/>
+      <c r="K36" s="182"/>
       <c r="L36" s="38"/>
       <c r="M36" s="38"/>
-      <c r="N36" s="108"/>
+      <c r="N36" s="107"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A37" s="39"/>
@@ -7259,20 +7268,20 @@
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="38"/>
-      <c r="G37" s="179"/>
-      <c r="H37" s="182"/>
-      <c r="I37" s="182"/>
-      <c r="J37" s="182"/>
-      <c r="K37" s="183"/>
+      <c r="G37" s="178"/>
+      <c r="H37" s="181"/>
+      <c r="I37" s="181"/>
+      <c r="J37" s="181"/>
+      <c r="K37" s="182"/>
       <c r="L37" s="38"/>
       <c r="M37" s="38"/>
-      <c r="N37" s="108"/>
-      <c r="P37" s="197"/>
-      <c r="Q37" s="197"/>
+      <c r="N37" s="107"/>
+      <c r="P37" s="196"/>
+      <c r="Q37" s="196"/>
       <c r="R37" s="6"/>
-      <c r="S37" s="196"/>
-      <c r="T37" s="196"/>
-      <c r="U37" s="196"/>
+      <c r="S37" s="195"/>
+      <c r="T37" s="195"/>
+      <c r="U37" s="195"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A38" s="39"/>
@@ -7281,20 +7290,20 @@
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="38"/>
-      <c r="G38" s="179"/>
-      <c r="H38" s="182"/>
-      <c r="I38" s="182"/>
-      <c r="J38" s="182"/>
-      <c r="K38" s="183"/>
+      <c r="G38" s="178"/>
+      <c r="H38" s="181"/>
+      <c r="I38" s="181"/>
+      <c r="J38" s="181"/>
+      <c r="K38" s="182"/>
       <c r="L38" s="38"/>
-      <c r="M38" s="109"/>
-      <c r="N38" s="108"/>
-      <c r="P38" s="197"/>
-      <c r="Q38" s="197"/>
+      <c r="M38" s="108"/>
+      <c r="N38" s="107"/>
+      <c r="P38" s="196"/>
+      <c r="Q38" s="196"/>
       <c r="R38" s="6"/>
-      <c r="S38" s="196"/>
-      <c r="T38" s="196"/>
-      <c r="U38" s="196"/>
+      <c r="S38" s="195"/>
+      <c r="T38" s="195"/>
+      <c r="U38" s="195"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A39" s="39"/>
@@ -7303,20 +7312,20 @@
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="38"/>
-      <c r="G39" s="179"/>
-      <c r="H39" s="182"/>
-      <c r="I39" s="182"/>
-      <c r="J39" s="182"/>
-      <c r="K39" s="183"/>
+      <c r="G39" s="178"/>
+      <c r="H39" s="181"/>
+      <c r="I39" s="181"/>
+      <c r="J39" s="181"/>
+      <c r="K39" s="182"/>
       <c r="L39" s="38"/>
-      <c r="M39" s="109"/>
-      <c r="N39" s="108"/>
+      <c r="M39" s="108"/>
+      <c r="N39" s="107"/>
       <c r="P39" s="5"/>
       <c r="Q39" s="5"/>
-      <c r="R39" s="198"/>
-      <c r="S39" s="196"/>
-      <c r="T39" s="196"/>
-      <c r="U39" s="196"/>
+      <c r="R39" s="197"/>
+      <c r="S39" s="195"/>
+      <c r="T39" s="195"/>
+      <c r="U39" s="195"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A40" s="39"/>
@@ -7325,20 +7334,20 @@
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="38"/>
-      <c r="G40" s="179"/>
-      <c r="H40" s="182"/>
-      <c r="I40" s="182"/>
-      <c r="J40" s="182"/>
-      <c r="K40" s="183"/>
+      <c r="G40" s="178"/>
+      <c r="H40" s="181"/>
+      <c r="I40" s="181"/>
+      <c r="J40" s="181"/>
+      <c r="K40" s="182"/>
       <c r="L40" s="38"/>
       <c r="M40" s="38"/>
-      <c r="N40" s="108"/>
+      <c r="N40" s="107"/>
       <c r="P40" s="5"/>
       <c r="Q40" s="5"/>
-      <c r="R40" s="198"/>
-      <c r="S40" s="196"/>
-      <c r="T40" s="196"/>
-      <c r="U40" s="196"/>
+      <c r="R40" s="197"/>
+      <c r="S40" s="195"/>
+      <c r="T40" s="195"/>
+      <c r="U40" s="195"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A41" s="39"/>
@@ -7347,14 +7356,14 @@
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="38"/>
-      <c r="G41" s="179"/>
-      <c r="H41" s="182"/>
-      <c r="I41" s="182"/>
-      <c r="J41" s="182"/>
-      <c r="K41" s="183"/>
+      <c r="G41" s="178"/>
+      <c r="H41" s="181"/>
+      <c r="I41" s="181"/>
+      <c r="J41" s="181"/>
+      <c r="K41" s="182"/>
       <c r="L41" s="38"/>
       <c r="M41" s="38"/>
-      <c r="N41" s="108"/>
+      <c r="N41" s="107"/>
     </row>
     <row r="42" spans="1:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="40"/>
@@ -7363,318 +7372,318 @@
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
       <c r="F42" s="43"/>
-      <c r="G42" s="205" t="s">
+      <c r="G42" s="204" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="206"/>
-      <c r="I42" s="206"/>
-      <c r="J42" s="206"/>
-      <c r="K42" s="207"/>
+      <c r="H42" s="205"/>
+      <c r="I42" s="205"/>
+      <c r="J42" s="205"/>
+      <c r="K42" s="206"/>
       <c r="L42" s="43"/>
       <c r="M42" s="43"/>
-      <c r="N42" s="108"/>
+      <c r="N42" s="107"/>
     </row>
     <row r="43" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="215" t="s">
+      <c r="A43" s="214" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="216"/>
-      <c r="C43" s="216"/>
-      <c r="D43" s="216"/>
-      <c r="E43" s="216"/>
-      <c r="F43" s="216"/>
-      <c r="G43" s="216"/>
-      <c r="H43" s="217"/>
-      <c r="I43" s="284" t="s">
+      <c r="B43" s="215"/>
+      <c r="C43" s="215"/>
+      <c r="D43" s="215"/>
+      <c r="E43" s="215"/>
+      <c r="F43" s="215"/>
+      <c r="G43" s="215"/>
+      <c r="H43" s="216"/>
+      <c r="I43" s="283" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="285"/>
-      <c r="K43" s="285"/>
-      <c r="L43" s="285"/>
-      <c r="M43" s="286"/>
-      <c r="N43" s="108"/>
+      <c r="J43" s="284"/>
+      <c r="K43" s="284"/>
+      <c r="L43" s="284"/>
+      <c r="M43" s="285"/>
+      <c r="N43" s="107"/>
     </row>
     <row r="44" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="218"/>
-      <c r="B44" s="219"/>
-      <c r="C44" s="219"/>
-      <c r="D44" s="219"/>
-      <c r="E44" s="219"/>
-      <c r="F44" s="219"/>
-      <c r="G44" s="219"/>
-      <c r="H44" s="220"/>
-      <c r="I44" s="287"/>
-      <c r="J44" s="288"/>
-      <c r="K44" s="288"/>
-      <c r="L44" s="288"/>
-      <c r="M44" s="289"/>
-      <c r="N44" s="108"/>
+      <c r="A44" s="217"/>
+      <c r="B44" s="218"/>
+      <c r="C44" s="218"/>
+      <c r="D44" s="218"/>
+      <c r="E44" s="218"/>
+      <c r="F44" s="218"/>
+      <c r="G44" s="218"/>
+      <c r="H44" s="219"/>
+      <c r="I44" s="286"/>
+      <c r="J44" s="287"/>
+      <c r="K44" s="287"/>
+      <c r="L44" s="287"/>
+      <c r="M44" s="288"/>
+      <c r="N44" s="107"/>
     </row>
     <row r="45" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="224" t="s">
+      <c r="A45" s="223" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="225"/>
-      <c r="C45" s="225"/>
-      <c r="D45" s="225"/>
-      <c r="E45" s="225"/>
-      <c r="F45" s="225"/>
-      <c r="G45" s="225"/>
-      <c r="H45" s="226"/>
-      <c r="I45" s="293" t="s">
+      <c r="B45" s="224"/>
+      <c r="C45" s="224"/>
+      <c r="D45" s="224"/>
+      <c r="E45" s="224"/>
+      <c r="F45" s="224"/>
+      <c r="G45" s="224"/>
+      <c r="H45" s="225"/>
+      <c r="I45" s="292" t="s">
         <v>83</v>
       </c>
-      <c r="J45" s="294"/>
-      <c r="K45" s="294"/>
-      <c r="L45" s="294"/>
-      <c r="M45" s="295"/>
-      <c r="N45" s="108"/>
+      <c r="J45" s="293"/>
+      <c r="K45" s="293"/>
+      <c r="L45" s="293"/>
+      <c r="M45" s="294"/>
+      <c r="N45" s="107"/>
     </row>
     <row r="46" spans="1:21" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="224" t="s">
+      <c r="A46" s="223" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="225"/>
-      <c r="C46" s="225"/>
-      <c r="D46" s="225"/>
-      <c r="E46" s="225"/>
-      <c r="F46" s="225"/>
-      <c r="G46" s="225"/>
-      <c r="H46" s="226"/>
-      <c r="I46" s="293"/>
-      <c r="J46" s="294"/>
-      <c r="K46" s="294"/>
-      <c r="L46" s="294"/>
-      <c r="M46" s="295"/>
-      <c r="N46" s="108"/>
+      <c r="B46" s="224"/>
+      <c r="C46" s="224"/>
+      <c r="D46" s="224"/>
+      <c r="E46" s="224"/>
+      <c r="F46" s="224"/>
+      <c r="G46" s="224"/>
+      <c r="H46" s="225"/>
+      <c r="I46" s="292"/>
+      <c r="J46" s="293"/>
+      <c r="K46" s="293"/>
+      <c r="L46" s="293"/>
+      <c r="M46" s="294"/>
+      <c r="N46" s="107"/>
     </row>
     <row r="47" spans="1:21" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="227"/>
-      <c r="B47" s="228"/>
-      <c r="C47" s="228"/>
-      <c r="D47" s="228"/>
-      <c r="E47" s="228"/>
-      <c r="F47" s="228"/>
-      <c r="G47" s="228"/>
-      <c r="H47" s="229"/>
-      <c r="I47" s="299" t="s">
+      <c r="A47" s="226"/>
+      <c r="B47" s="227"/>
+      <c r="C47" s="227"/>
+      <c r="D47" s="227"/>
+      <c r="E47" s="227"/>
+      <c r="F47" s="227"/>
+      <c r="G47" s="227"/>
+      <c r="H47" s="228"/>
+      <c r="I47" s="298" t="s">
         <v>84</v>
       </c>
-      <c r="J47" s="300"/>
-      <c r="K47" s="300"/>
-      <c r="L47" s="300"/>
-      <c r="M47" s="301"/>
-      <c r="N47" s="108"/>
+      <c r="J47" s="299"/>
+      <c r="K47" s="299"/>
+      <c r="L47" s="299"/>
+      <c r="M47" s="300"/>
+      <c r="N47" s="107"/>
     </row>
     <row r="48" spans="1:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="208" t="s">
+      <c r="A48" s="207" t="s">
         <v>36</v>
       </c>
-      <c r="B48" s="199"/>
-      <c r="C48" s="199"/>
-      <c r="D48" s="199"/>
-      <c r="E48" s="199"/>
-      <c r="F48" s="199"/>
-      <c r="G48" s="199"/>
-      <c r="H48" s="199"/>
-      <c r="I48" s="199"/>
-      <c r="J48" s="199"/>
-      <c r="K48" s="199"/>
-      <c r="L48" s="199"/>
-      <c r="M48" s="200"/>
-      <c r="N48" s="108"/>
+      <c r="B48" s="198"/>
+      <c r="C48" s="198"/>
+      <c r="D48" s="198"/>
+      <c r="E48" s="198"/>
+      <c r="F48" s="198"/>
+      <c r="G48" s="198"/>
+      <c r="H48" s="198"/>
+      <c r="I48" s="198"/>
+      <c r="J48" s="198"/>
+      <c r="K48" s="198"/>
+      <c r="L48" s="198"/>
+      <c r="M48" s="199"/>
+      <c r="N48" s="107"/>
     </row>
     <row r="49" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="215" t="s">
+      <c r="A49" s="214" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="216"/>
-      <c r="C49" s="216"/>
-      <c r="D49" s="216"/>
-      <c r="E49" s="216"/>
-      <c r="F49" s="216"/>
-      <c r="G49" s="216"/>
-      <c r="H49" s="217"/>
-      <c r="I49" s="209" t="s">
+      <c r="B49" s="215"/>
+      <c r="C49" s="215"/>
+      <c r="D49" s="215"/>
+      <c r="E49" s="215"/>
+      <c r="F49" s="215"/>
+      <c r="G49" s="215"/>
+      <c r="H49" s="216"/>
+      <c r="I49" s="208" t="s">
         <v>38</v>
       </c>
-      <c r="J49" s="210"/>
-      <c r="K49" s="210"/>
-      <c r="L49" s="210"/>
-      <c r="M49" s="211"/>
-      <c r="N49" s="108"/>
+      <c r="J49" s="209"/>
+      <c r="K49" s="209"/>
+      <c r="L49" s="209"/>
+      <c r="M49" s="210"/>
+      <c r="N49" s="107"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A50" s="218"/>
-      <c r="B50" s="219"/>
-      <c r="C50" s="219"/>
-      <c r="D50" s="219"/>
-      <c r="E50" s="219"/>
-      <c r="F50" s="219"/>
-      <c r="G50" s="219"/>
-      <c r="H50" s="220"/>
-      <c r="I50" s="212"/>
-      <c r="J50" s="213"/>
-      <c r="K50" s="213"/>
-      <c r="L50" s="213"/>
-      <c r="M50" s="214"/>
-      <c r="N50" s="108"/>
+      <c r="A50" s="217"/>
+      <c r="B50" s="218"/>
+      <c r="C50" s="218"/>
+      <c r="D50" s="218"/>
+      <c r="E50" s="218"/>
+      <c r="F50" s="218"/>
+      <c r="G50" s="218"/>
+      <c r="H50" s="219"/>
+      <c r="I50" s="211"/>
+      <c r="J50" s="212"/>
+      <c r="K50" s="212"/>
+      <c r="L50" s="212"/>
+      <c r="M50" s="213"/>
+      <c r="N50" s="107"/>
     </row>
     <row r="51" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="221"/>
-      <c r="B51" s="222"/>
-      <c r="C51" s="222"/>
-      <c r="D51" s="222"/>
-      <c r="E51" s="222"/>
-      <c r="F51" s="222"/>
-      <c r="G51" s="222"/>
-      <c r="H51" s="223"/>
-      <c r="I51" s="230" t="s">
+      <c r="A51" s="220"/>
+      <c r="B51" s="221"/>
+      <c r="C51" s="221"/>
+      <c r="D51" s="221"/>
+      <c r="E51" s="221"/>
+      <c r="F51" s="221"/>
+      <c r="G51" s="221"/>
+      <c r="H51" s="222"/>
+      <c r="I51" s="229" t="s">
         <v>39</v>
       </c>
-      <c r="J51" s="231"/>
-      <c r="K51" s="231"/>
-      <c r="L51" s="231"/>
-      <c r="M51" s="232"/>
-      <c r="N51" s="108"/>
+      <c r="J51" s="230"/>
+      <c r="K51" s="230"/>
+      <c r="L51" s="230"/>
+      <c r="M51" s="231"/>
+      <c r="N51" s="107"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A52" s="208" t="s">
+      <c r="A52" s="207" t="s">
         <v>40</v>
       </c>
-      <c r="B52" s="199"/>
-      <c r="C52" s="199"/>
-      <c r="D52" s="199"/>
+      <c r="B52" s="198"/>
+      <c r="C52" s="198"/>
+      <c r="D52" s="198"/>
       <c r="E52" s="74" t="s">
         <v>42</v>
       </c>
       <c r="F52" s="75"/>
-      <c r="G52" s="276" t="s">
+      <c r="G52" s="275" t="s">
         <v>43</v>
       </c>
-      <c r="H52" s="276"/>
-      <c r="I52" s="276"/>
-      <c r="J52" s="277"/>
-      <c r="K52" s="199" t="s">
+      <c r="H52" s="275"/>
+      <c r="I52" s="275"/>
+      <c r="J52" s="276"/>
+      <c r="K52" s="198" t="s">
         <v>47</v>
       </c>
-      <c r="L52" s="199"/>
-      <c r="M52" s="200"/>
-      <c r="N52" s="108"/>
+      <c r="L52" s="198"/>
+      <c r="M52" s="199"/>
+      <c r="N52" s="107"/>
     </row>
     <row r="53" spans="1:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="233" t="s">
+      <c r="A53" s="232" t="s">
         <v>41</v>
       </c>
-      <c r="B53" s="234"/>
-      <c r="C53" s="234"/>
-      <c r="D53" s="234"/>
+      <c r="B53" s="233"/>
+      <c r="C53" s="233"/>
+      <c r="D53" s="233"/>
       <c r="E53" s="76"/>
       <c r="F53" s="69"/>
       <c r="G53" s="69"/>
       <c r="H53" s="69"/>
       <c r="I53" s="69"/>
       <c r="J53" s="77"/>
-      <c r="K53" s="201" t="s">
+      <c r="K53" s="200" t="s">
         <v>49</v>
       </c>
-      <c r="L53" s="201"/>
-      <c r="M53" s="202"/>
-      <c r="N53" s="108"/>
+      <c r="L53" s="200"/>
+      <c r="M53" s="201"/>
+      <c r="N53" s="107"/>
     </row>
     <row r="54" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="233"/>
-      <c r="B54" s="234"/>
-      <c r="C54" s="234"/>
-      <c r="D54" s="234"/>
-      <c r="E54" s="245" t="s">
+      <c r="A54" s="232"/>
+      <c r="B54" s="233"/>
+      <c r="C54" s="233"/>
+      <c r="D54" s="233"/>
+      <c r="E54" s="244" t="s">
         <v>81</v>
       </c>
-      <c r="F54" s="246"/>
-      <c r="G54" s="406" t="s">
+      <c r="F54" s="245"/>
+      <c r="G54" s="405" t="s">
         <v>80</v>
       </c>
-      <c r="H54" s="235" t="s">
+      <c r="H54" s="234" t="s">
         <v>44</v>
       </c>
-      <c r="I54" s="235"/>
-      <c r="J54" s="236"/>
-      <c r="K54" s="201"/>
-      <c r="L54" s="201"/>
-      <c r="M54" s="202"/>
-      <c r="N54" s="108"/>
+      <c r="I54" s="234"/>
+      <c r="J54" s="235"/>
+      <c r="K54" s="200"/>
+      <c r="L54" s="200"/>
+      <c r="M54" s="201"/>
+      <c r="N54" s="107"/>
     </row>
     <row r="55" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="233"/>
-      <c r="B55" s="234"/>
-      <c r="C55" s="234"/>
-      <c r="D55" s="234"/>
-      <c r="E55" s="245" t="s">
+      <c r="A55" s="232"/>
+      <c r="B55" s="233"/>
+      <c r="C55" s="233"/>
+      <c r="D55" s="233"/>
+      <c r="E55" s="244" t="s">
         <v>82</v>
       </c>
-      <c r="F55" s="246"/>
-      <c r="G55" s="407" t="s">
+      <c r="F55" s="245"/>
+      <c r="G55" s="406" t="s">
         <v>80</v>
       </c>
-      <c r="H55" s="235" t="s">
+      <c r="H55" s="234" t="s">
         <v>45</v>
       </c>
-      <c r="I55" s="235"/>
-      <c r="J55" s="236"/>
-      <c r="K55" s="201"/>
-      <c r="L55" s="201"/>
-      <c r="M55" s="202"/>
-      <c r="N55" s="108"/>
+      <c r="I55" s="234"/>
+      <c r="J55" s="235"/>
+      <c r="K55" s="200"/>
+      <c r="L55" s="200"/>
+      <c r="M55" s="201"/>
+      <c r="N55" s="107"/>
     </row>
     <row r="56" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="35"/>
       <c r="D56" s="34"/>
-      <c r="E56" s="245"/>
-      <c r="F56" s="246"/>
-      <c r="G56" s="407"/>
-      <c r="H56" s="235"/>
-      <c r="I56" s="235"/>
-      <c r="J56" s="236"/>
-      <c r="K56" s="203" t="s">
+      <c r="E56" s="244"/>
+      <c r="F56" s="245"/>
+      <c r="G56" s="406"/>
+      <c r="H56" s="234"/>
+      <c r="I56" s="234"/>
+      <c r="J56" s="235"/>
+      <c r="K56" s="202" t="s">
         <v>48</v>
       </c>
-      <c r="L56" s="203"/>
-      <c r="M56" s="204"/>
-      <c r="N56" s="108"/>
+      <c r="L56" s="202"/>
+      <c r="M56" s="203"/>
+      <c r="N56" s="107"/>
     </row>
     <row r="57" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="35"/>
       <c r="D57" s="34"/>
-      <c r="E57" s="245"/>
-      <c r="F57" s="246"/>
-      <c r="G57" s="406" t="s">
+      <c r="E57" s="244"/>
+      <c r="F57" s="245"/>
+      <c r="G57" s="405" t="s">
         <v>80</v>
       </c>
-      <c r="H57" s="235" t="s">
+      <c r="H57" s="234" t="s">
         <v>46</v>
       </c>
-      <c r="I57" s="235"/>
-      <c r="J57" s="236"/>
+      <c r="I57" s="234"/>
+      <c r="J57" s="235"/>
       <c r="K57" s="44"/>
-      <c r="L57" s="107"/>
-      <c r="M57" s="110"/>
-      <c r="N57" s="108"/>
+      <c r="L57" s="106"/>
+      <c r="M57" s="109"/>
+      <c r="N57" s="107"/>
     </row>
     <row r="58" spans="1:14" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="45"/>
-      <c r="B58" s="118"/>
-      <c r="C58" s="118"/>
+      <c r="B58" s="117"/>
+      <c r="C58" s="117"/>
       <c r="D58" s="30"/>
-      <c r="E58" s="237"/>
-      <c r="F58" s="238"/>
-      <c r="G58" s="238"/>
-      <c r="H58" s="238"/>
-      <c r="I58" s="238"/>
-      <c r="J58" s="239"/>
+      <c r="E58" s="236"/>
+      <c r="F58" s="237"/>
+      <c r="G58" s="237"/>
+      <c r="H58" s="237"/>
+      <c r="I58" s="237"/>
+      <c r="J58" s="238"/>
       <c r="K58" s="46"/>
       <c r="L58" s="47"/>
-      <c r="M58" s="111"/>
-      <c r="N58" s="108"/>
+      <c r="M58" s="110"/>
+      <c r="N58" s="107"/>
     </row>
     <row r="59" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3"/>

--- a/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
+++ b/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Procomm\Documents\GitHub\Acumatica_Customizations_and_Packages\Istar_Development\Projects\BOL_Generation\Code\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7014F9B9-38B0-48A2-B7A1-405CAF8EE714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0689B93-5F4C-41BC-9FEE-95ABBBE7B28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2640" yWindow="2640" windowWidth="28800" windowHeight="15345" xr2:uid="{888CA347-7849-4038-B8EE-FAC87BA1B844}"/>
   </bookViews>
@@ -2130,10 +2130,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="29" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>

--- a/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
+++ b/Istar_Development/Projects/BOL_Generation/Code/templates/BOL_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Procomm\Documents\GitHub\Acumatica_Customizations_and_Packages\Istar_Development\Projects\BOL_Generation\Code\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0689B93-5F4C-41BC-9FEE-95ABBBE7B28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39292A6-02A7-4581-A07E-B08DD7A131F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="28800" windowHeight="15345" xr2:uid="{888CA347-7849-4038-B8EE-FAC87BA1B844}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{888CA347-7849-4038-B8EE-FAC87BA1B844}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterBOL" sheetId="3" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="84">
   <si>
     <t>SHIP FROM</t>
   </si>
@@ -143,15 +143,6 @@
   </si>
   <si>
     <t>ADDITIONAL SHIPPER INFO</t>
-  </si>
-  <si>
-    <t>Where the rate is dependent on value, shippers are required to state spacificly in writing the agreed or declared value of the property as follows:</t>
-  </si>
-  <si>
-    <t>"The agreed or declared value of the property is specifically stated by shipper to be not exceeding</t>
-  </si>
-  <si>
-    <t>_____________ per_____________."</t>
   </si>
   <si>
     <t>COD Amount: $___________________</t>
@@ -426,6 +417,12 @@
       </rPr>
       <t>☐</t>
     </r>
+  </si>
+  <si>
+    <t>Where the rate is dependent on value, shippers are required to state spacificly in writing the agreed or declared value of the property as follows: "The agreed or declared value of the property is specifically stated by shipper to be not exceeding  _____________ per_____________."</t>
+  </si>
+  <si>
+    <t>Mixed Pallets - Commodity as Jewelry</t>
   </si>
 </sst>
 </file>
@@ -578,7 +575,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -991,34 +988,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="417">
+  <cellXfs count="419">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1189,131 +1164,785 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="29" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1334,807 +1963,163 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="29" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3412,129 +3397,129 @@
   <sheetData>
     <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="85" t="s">
-        <v>79</v>
-      </c>
-      <c r="B1" s="415"/>
-      <c r="C1" s="416"/>
-      <c r="D1" s="378" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="379"/>
-      <c r="F1" s="379"/>
-      <c r="G1" s="379"/>
-      <c r="H1" s="379"/>
-      <c r="I1" s="379"/>
-      <c r="J1" s="379"/>
-      <c r="K1" s="380"/>
-      <c r="L1" s="381" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="119"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="121" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="123"/>
+      <c r="L1" s="114" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" s="115"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="244" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
+      <c r="M2" s="246"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="99" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="100"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="100"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="244"/>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
+      <c r="M3" s="246"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="99" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="100"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="100"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="103"/>
+      <c r="L4" s="103"/>
+      <c r="M4" s="104"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="99" t="s">
         <v>58</v>
       </c>
-      <c r="M1" s="382"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="311" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="312"/>
-      <c r="C2" s="312"/>
-      <c r="D2" s="312"/>
-      <c r="E2" s="312"/>
-      <c r="F2" s="312"/>
-      <c r="G2" s="312"/>
-      <c r="H2" s="313"/>
-      <c r="I2" s="383" t="s">
-        <v>73</v>
-      </c>
-      <c r="J2" s="384"/>
-      <c r="K2" s="384"/>
-      <c r="L2" s="384"/>
-      <c r="M2" s="385"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="363" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="364"/>
-      <c r="C3" s="364"/>
-      <c r="D3" s="364"/>
-      <c r="E3" s="364"/>
-      <c r="F3" s="364"/>
-      <c r="G3" s="364"/>
-      <c r="H3" s="365"/>
-      <c r="I3" s="383"/>
-      <c r="J3" s="384"/>
-      <c r="K3" s="384"/>
-      <c r="L3" s="384"/>
-      <c r="M3" s="385"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="363" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="364"/>
-      <c r="C4" s="364"/>
-      <c r="D4" s="364"/>
-      <c r="E4" s="364"/>
-      <c r="F4" s="364"/>
-      <c r="G4" s="364"/>
-      <c r="H4" s="365"/>
-      <c r="I4" s="369"/>
-      <c r="J4" s="370"/>
-      <c r="K4" s="370"/>
-      <c r="L4" s="370"/>
-      <c r="M4" s="371"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="363" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="364"/>
-      <c r="C5" s="364"/>
-      <c r="D5" s="364"/>
-      <c r="E5" s="364"/>
-      <c r="F5" s="364"/>
-      <c r="G5" s="364"/>
-      <c r="H5" s="365"/>
-      <c r="I5" s="369"/>
-      <c r="J5" s="370"/>
-      <c r="K5" s="370"/>
-      <c r="L5" s="370"/>
-      <c r="M5" s="371"/>
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="101"/>
+      <c r="I5" s="102"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
+      <c r="L5" s="103"/>
+      <c r="M5" s="104"/>
     </row>
     <row r="6" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="375" t="s">
+      <c r="A6" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="376"/>
-      <c r="C6" s="376"/>
-      <c r="D6" s="376"/>
-      <c r="E6" s="376"/>
-      <c r="F6" s="377" t="s">
+      <c r="B6" s="109"/>
+      <c r="C6" s="109"/>
+      <c r="D6" s="109"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="110" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="377"/>
-      <c r="H6" s="409" t="s">
-        <v>80</v>
-      </c>
-      <c r="I6" s="372"/>
-      <c r="J6" s="373"/>
-      <c r="K6" s="373"/>
-      <c r="L6" s="373"/>
-      <c r="M6" s="374"/>
+      <c r="G6" s="110"/>
+      <c r="H6" s="97" t="s">
+        <v>77</v>
+      </c>
+      <c r="I6" s="105"/>
+      <c r="J6" s="106"/>
+      <c r="K6" s="106"/>
+      <c r="L6" s="106"/>
+      <c r="M6" s="107"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="351" t="s">
+      <c r="A7" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="352"/>
-      <c r="C7" s="352"/>
-      <c r="D7" s="352"/>
-      <c r="E7" s="352"/>
-      <c r="F7" s="352"/>
-      <c r="G7" s="352"/>
-      <c r="H7" s="353"/>
+      <c r="B7" s="112"/>
+      <c r="C7" s="112"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="112"/>
+      <c r="F7" s="112"/>
+      <c r="G7" s="112"/>
+      <c r="H7" s="113"/>
       <c r="I7" s="49" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J7" s="50"/>
       <c r="K7" s="51"/>
@@ -3542,39 +3527,39 @@
       <c r="M7" s="52"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="366" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="367"/>
-      <c r="C8" s="367"/>
-      <c r="D8" s="367"/>
-      <c r="E8" s="247" t="s">
+      <c r="A8" s="136" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="137"/>
+      <c r="C8" s="137"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="138" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="247"/>
-      <c r="G8" s="247"/>
-      <c r="H8" s="248"/>
-      <c r="I8" s="366" t="s">
+      <c r="F8" s="138"/>
+      <c r="G8" s="138"/>
+      <c r="H8" s="139"/>
+      <c r="I8" s="136" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="367"/>
-      <c r="K8" s="367"/>
-      <c r="L8" s="367"/>
-      <c r="M8" s="368"/>
+      <c r="J8" s="137"/>
+      <c r="K8" s="137"/>
+      <c r="L8" s="137"/>
+      <c r="M8" s="140"/>
     </row>
     <row r="9" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="366" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="367"/>
-      <c r="C9" s="367"/>
-      <c r="D9" s="367"/>
-      <c r="E9" s="367"/>
-      <c r="F9" s="367"/>
-      <c r="G9" s="367"/>
-      <c r="H9" s="368"/>
+      <c r="A9" s="136" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="137"/>
+      <c r="C9" s="137"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="137"/>
+      <c r="F9" s="137"/>
+      <c r="G9" s="137"/>
+      <c r="H9" s="140"/>
       <c r="I9" s="53" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J9" s="54"/>
       <c r="K9" s="54"/>
@@ -3582,18 +3567,18 @@
       <c r="M9" s="48"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="366" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="367"/>
-      <c r="C10" s="367"/>
-      <c r="D10" s="367"/>
-      <c r="E10" s="367"/>
-      <c r="F10" s="367"/>
-      <c r="G10" s="367"/>
-      <c r="H10" s="368"/>
+      <c r="A10" s="136" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="137"/>
+      <c r="C10" s="137"/>
+      <c r="D10" s="137"/>
+      <c r="E10" s="137"/>
+      <c r="F10" s="137"/>
+      <c r="G10" s="137"/>
+      <c r="H10" s="140"/>
       <c r="I10" s="55" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J10" s="56"/>
       <c r="K10" s="56"/>
@@ -3601,22 +3586,22 @@
       <c r="M10" s="57"/>
     </row>
     <row r="11" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="348" t="s">
+      <c r="A11" s="124" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="349"/>
-      <c r="C11" s="349"/>
-      <c r="D11" s="349"/>
-      <c r="E11" s="349"/>
-      <c r="F11" s="350" t="s">
+      <c r="B11" s="125"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="126" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="350"/>
-      <c r="H11" s="409" t="s">
-        <v>80</v>
+      <c r="G11" s="126"/>
+      <c r="H11" s="97" t="s">
+        <v>77</v>
       </c>
       <c r="I11" s="58" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J11" s="59"/>
       <c r="K11" s="59"/>
@@ -3624,93 +3609,93 @@
       <c r="M11" s="60"/>
     </row>
     <row r="12" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="351" t="s">
+      <c r="A12" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="352"/>
-      <c r="C12" s="352"/>
-      <c r="D12" s="352"/>
-      <c r="E12" s="352"/>
-      <c r="F12" s="352"/>
-      <c r="G12" s="352"/>
-      <c r="H12" s="353"/>
-      <c r="I12" s="354"/>
-      <c r="J12" s="355"/>
-      <c r="K12" s="355"/>
-      <c r="L12" s="355"/>
-      <c r="M12" s="356"/>
+      <c r="B12" s="112"/>
+      <c r="C12" s="112"/>
+      <c r="D12" s="112"/>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="112"/>
+      <c r="H12" s="113"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="128"/>
+      <c r="K12" s="128"/>
+      <c r="L12" s="128"/>
+      <c r="M12" s="129"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="360" t="s">
+      <c r="A13" s="133" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="361"/>
-      <c r="C13" s="361"/>
-      <c r="D13" s="361"/>
-      <c r="E13" s="361"/>
-      <c r="F13" s="361"/>
-      <c r="G13" s="361"/>
-      <c r="H13" s="362"/>
-      <c r="I13" s="354"/>
-      <c r="J13" s="355"/>
-      <c r="K13" s="355"/>
-      <c r="L13" s="355"/>
-      <c r="M13" s="356"/>
+      <c r="B13" s="134"/>
+      <c r="C13" s="134"/>
+      <c r="D13" s="134"/>
+      <c r="E13" s="134"/>
+      <c r="F13" s="134"/>
+      <c r="G13" s="134"/>
+      <c r="H13" s="135"/>
+      <c r="I13" s="127"/>
+      <c r="J13" s="128"/>
+      <c r="K13" s="128"/>
+      <c r="L13" s="128"/>
+      <c r="M13" s="129"/>
     </row>
     <row r="14" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="363" t="s">
+      <c r="A14" s="99" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="364"/>
-      <c r="C14" s="364"/>
-      <c r="D14" s="364"/>
-      <c r="E14" s="364"/>
-      <c r="F14" s="364"/>
-      <c r="G14" s="364"/>
-      <c r="H14" s="365"/>
-      <c r="I14" s="357"/>
-      <c r="J14" s="358"/>
-      <c r="K14" s="358"/>
-      <c r="L14" s="358"/>
-      <c r="M14" s="359"/>
+      <c r="B14" s="100"/>
+      <c r="C14" s="100"/>
+      <c r="D14" s="100"/>
+      <c r="E14" s="100"/>
+      <c r="F14" s="100"/>
+      <c r="G14" s="100"/>
+      <c r="H14" s="101"/>
+      <c r="I14" s="130"/>
+      <c r="J14" s="131"/>
+      <c r="K14" s="131"/>
+      <c r="L14" s="131"/>
+      <c r="M14" s="132"/>
     </row>
     <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="336" t="s">
+      <c r="A15" s="153" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="337"/>
-      <c r="C15" s="337"/>
-      <c r="D15" s="337"/>
-      <c r="E15" s="337"/>
-      <c r="F15" s="337"/>
-      <c r="G15" s="337"/>
-      <c r="H15" s="337"/>
-      <c r="I15" s="338" t="s">
+      <c r="B15" s="154"/>
+      <c r="C15" s="154"/>
+      <c r="D15" s="154"/>
+      <c r="E15" s="154"/>
+      <c r="F15" s="154"/>
+      <c r="G15" s="154"/>
+      <c r="H15" s="154"/>
+      <c r="I15" s="155" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="339"/>
-      <c r="K15" s="339"/>
-      <c r="L15" s="339"/>
-      <c r="M15" s="340"/>
+      <c r="J15" s="156"/>
+      <c r="K15" s="156"/>
+      <c r="L15" s="156"/>
+      <c r="M15" s="157"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="61" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B16" s="62"/>
       <c r="C16" s="62"/>
       <c r="D16" s="62"/>
       <c r="E16" s="62"/>
-      <c r="F16" s="239"/>
-      <c r="G16" s="239"/>
-      <c r="H16" s="240"/>
-      <c r="I16" s="341" t="s">
-        <v>78</v>
-      </c>
-      <c r="J16" s="342"/>
-      <c r="K16" s="342"/>
-      <c r="L16" s="342"/>
-      <c r="M16" s="343"/>
+      <c r="F16" s="201"/>
+      <c r="G16" s="201"/>
+      <c r="H16" s="202"/>
+      <c r="I16" s="158" t="s">
+        <v>75</v>
+      </c>
+      <c r="J16" s="159"/>
+      <c r="K16" s="159"/>
+      <c r="L16" s="159"/>
+      <c r="M16" s="160"/>
     </row>
     <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="63"/>
@@ -3721,15 +3706,15 @@
       <c r="F17" s="64"/>
       <c r="G17" s="64"/>
       <c r="H17" s="65"/>
-      <c r="I17" s="407" t="s">
-        <v>80</v>
-      </c>
-      <c r="J17" s="408"/>
-      <c r="K17" s="344" t="s">
+      <c r="I17" s="161" t="s">
+        <v>77</v>
+      </c>
+      <c r="J17" s="162"/>
+      <c r="K17" s="163" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="344"/>
-      <c r="M17" s="345"/>
+      <c r="L17" s="163"/>
+      <c r="M17" s="164"/>
     </row>
     <row r="18" spans="1:13" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="63"/>
@@ -3740,285 +3725,285 @@
       <c r="F18" s="64"/>
       <c r="G18" s="64"/>
       <c r="H18" s="65"/>
-      <c r="I18" s="236" t="s">
+      <c r="I18" s="167" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="237"/>
-      <c r="K18" s="346"/>
-      <c r="L18" s="346"/>
-      <c r="M18" s="347"/>
+      <c r="J18" s="168"/>
+      <c r="K18" s="165"/>
+      <c r="L18" s="165"/>
+      <c r="M18" s="166"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="311" t="s">
+      <c r="A19" s="116" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="312"/>
-      <c r="C19" s="312"/>
-      <c r="D19" s="312"/>
-      <c r="E19" s="312"/>
-      <c r="F19" s="312"/>
-      <c r="G19" s="312"/>
-      <c r="H19" s="312"/>
-      <c r="I19" s="312"/>
-      <c r="J19" s="312"/>
-      <c r="K19" s="312"/>
-      <c r="L19" s="312"/>
-      <c r="M19" s="313"/>
+      <c r="B19" s="117"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="117"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="117"/>
+      <c r="G19" s="117"/>
+      <c r="H19" s="117"/>
+      <c r="I19" s="117"/>
+      <c r="J19" s="117"/>
+      <c r="K19" s="117"/>
+      <c r="L19" s="117"/>
+      <c r="M19" s="118"/>
     </row>
     <row r="20" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="324" t="s">
+      <c r="A20" s="141" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="325"/>
-      <c r="C20" s="325"/>
-      <c r="D20" s="325"/>
-      <c r="E20" s="325" t="s">
+      <c r="B20" s="142"/>
+      <c r="C20" s="142"/>
+      <c r="D20" s="142"/>
+      <c r="E20" s="142" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="325" t="s">
+      <c r="F20" s="142" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="325"/>
-      <c r="H20" s="326" t="s">
+      <c r="G20" s="142"/>
+      <c r="H20" s="143" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="327"/>
-      <c r="J20" s="328" t="s">
+      <c r="I20" s="144"/>
+      <c r="J20" s="145" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="329"/>
-      <c r="L20" s="329"/>
-      <c r="M20" s="330"/>
+      <c r="K20" s="146"/>
+      <c r="L20" s="146"/>
+      <c r="M20" s="147"/>
     </row>
     <row r="21" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="324"/>
-      <c r="B21" s="325"/>
-      <c r="C21" s="325"/>
-      <c r="D21" s="325"/>
-      <c r="E21" s="325"/>
-      <c r="F21" s="325"/>
-      <c r="G21" s="325"/>
-      <c r="H21" s="334" t="s">
+      <c r="A21" s="141"/>
+      <c r="B21" s="142"/>
+      <c r="C21" s="142"/>
+      <c r="D21" s="142"/>
+      <c r="E21" s="142"/>
+      <c r="F21" s="142"/>
+      <c r="G21" s="142"/>
+      <c r="H21" s="151" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="335"/>
-      <c r="J21" s="331"/>
-      <c r="K21" s="332"/>
-      <c r="L21" s="332"/>
-      <c r="M21" s="333"/>
+      <c r="I21" s="152"/>
+      <c r="J21" s="148"/>
+      <c r="K21" s="149"/>
+      <c r="L21" s="149"/>
+      <c r="M21" s="150"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="320"/>
-      <c r="B22" s="320"/>
-      <c r="C22" s="320"/>
-      <c r="D22" s="321"/>
+      <c r="A22" s="169"/>
+      <c r="B22" s="169"/>
+      <c r="C22" s="169"/>
+      <c r="D22" s="170"/>
       <c r="E22" s="66"/>
-      <c r="F22" s="322"/>
-      <c r="G22" s="322"/>
+      <c r="F22" s="171"/>
+      <c r="G22" s="171"/>
       <c r="H22" s="67" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I22" s="67" t="s">
-        <v>52</v>
-      </c>
-      <c r="J22" s="308"/>
-      <c r="K22" s="308"/>
-      <c r="L22" s="308"/>
-      <c r="M22" s="323"/>
+        <v>49</v>
+      </c>
+      <c r="J22" s="172"/>
+      <c r="K22" s="172"/>
+      <c r="L22" s="172"/>
+      <c r="M22" s="173"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="320"/>
-      <c r="B23" s="320"/>
-      <c r="C23" s="320"/>
-      <c r="D23" s="321"/>
+      <c r="A23" s="169"/>
+      <c r="B23" s="169"/>
+      <c r="C23" s="169"/>
+      <c r="D23" s="170"/>
       <c r="E23" s="66"/>
-      <c r="F23" s="322"/>
-      <c r="G23" s="322"/>
+      <c r="F23" s="171"/>
+      <c r="G23" s="171"/>
       <c r="H23" s="67" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I23" s="67" t="s">
-        <v>52</v>
-      </c>
-      <c r="J23" s="308"/>
-      <c r="K23" s="308"/>
-      <c r="L23" s="308"/>
-      <c r="M23" s="323"/>
+        <v>49</v>
+      </c>
+      <c r="J23" s="172"/>
+      <c r="K23" s="172"/>
+      <c r="L23" s="172"/>
+      <c r="M23" s="173"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="320"/>
-      <c r="B24" s="320"/>
-      <c r="C24" s="320"/>
-      <c r="D24" s="321"/>
+      <c r="A24" s="169"/>
+      <c r="B24" s="169"/>
+      <c r="C24" s="169"/>
+      <c r="D24" s="170"/>
       <c r="E24" s="66"/>
-      <c r="F24" s="322"/>
-      <c r="G24" s="322"/>
+      <c r="F24" s="171"/>
+      <c r="G24" s="171"/>
       <c r="H24" s="67" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I24" s="67" t="s">
-        <v>52</v>
-      </c>
-      <c r="J24" s="308"/>
-      <c r="K24" s="308"/>
-      <c r="L24" s="308"/>
-      <c r="M24" s="323"/>
+        <v>49</v>
+      </c>
+      <c r="J24" s="172"/>
+      <c r="K24" s="172"/>
+      <c r="L24" s="172"/>
+      <c r="M24" s="173"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="320"/>
-      <c r="B25" s="320"/>
-      <c r="C25" s="320"/>
-      <c r="D25" s="321"/>
+      <c r="A25" s="169"/>
+      <c r="B25" s="169"/>
+      <c r="C25" s="169"/>
+      <c r="D25" s="170"/>
       <c r="E25" s="66"/>
-      <c r="F25" s="322"/>
-      <c r="G25" s="322"/>
+      <c r="F25" s="171"/>
+      <c r="G25" s="171"/>
       <c r="H25" s="67" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I25" s="67" t="s">
-        <v>52</v>
-      </c>
-      <c r="J25" s="308"/>
-      <c r="K25" s="308"/>
-      <c r="L25" s="308"/>
-      <c r="M25" s="323"/>
+        <v>49</v>
+      </c>
+      <c r="J25" s="172"/>
+      <c r="K25" s="172"/>
+      <c r="L25" s="172"/>
+      <c r="M25" s="173"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="320"/>
-      <c r="B26" s="320"/>
-      <c r="C26" s="320"/>
-      <c r="D26" s="321"/>
+      <c r="A26" s="169"/>
+      <c r="B26" s="169"/>
+      <c r="C26" s="169"/>
+      <c r="D26" s="170"/>
       <c r="E26" s="66"/>
-      <c r="F26" s="322"/>
-      <c r="G26" s="322"/>
+      <c r="F26" s="171"/>
+      <c r="G26" s="171"/>
       <c r="H26" s="67" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I26" s="67" t="s">
-        <v>52</v>
-      </c>
-      <c r="J26" s="308"/>
-      <c r="K26" s="308"/>
-      <c r="L26" s="308"/>
-      <c r="M26" s="323"/>
+        <v>49</v>
+      </c>
+      <c r="J26" s="172"/>
+      <c r="K26" s="172"/>
+      <c r="L26" s="172"/>
+      <c r="M26" s="173"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="320"/>
-      <c r="B27" s="320"/>
-      <c r="C27" s="320"/>
-      <c r="D27" s="321"/>
+      <c r="A27" s="169"/>
+      <c r="B27" s="169"/>
+      <c r="C27" s="169"/>
+      <c r="D27" s="170"/>
       <c r="E27" s="66"/>
-      <c r="F27" s="322"/>
-      <c r="G27" s="322"/>
+      <c r="F27" s="171"/>
+      <c r="G27" s="171"/>
       <c r="H27" s="67" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I27" s="67" t="s">
-        <v>52</v>
-      </c>
-      <c r="J27" s="308"/>
-      <c r="K27" s="308"/>
-      <c r="L27" s="308"/>
-      <c r="M27" s="323"/>
+        <v>49</v>
+      </c>
+      <c r="J27" s="172"/>
+      <c r="K27" s="172"/>
+      <c r="L27" s="172"/>
+      <c r="M27" s="173"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="320"/>
-      <c r="B28" s="320"/>
-      <c r="C28" s="320"/>
-      <c r="D28" s="321"/>
+      <c r="A28" s="169"/>
+      <c r="B28" s="169"/>
+      <c r="C28" s="169"/>
+      <c r="D28" s="170"/>
       <c r="E28" s="66"/>
-      <c r="F28" s="322"/>
-      <c r="G28" s="322"/>
+      <c r="F28" s="171"/>
+      <c r="G28" s="171"/>
       <c r="H28" s="67" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I28" s="67" t="s">
-        <v>52</v>
-      </c>
-      <c r="J28" s="308"/>
-      <c r="K28" s="308"/>
-      <c r="L28" s="308"/>
-      <c r="M28" s="323"/>
+        <v>49</v>
+      </c>
+      <c r="J28" s="172"/>
+      <c r="K28" s="172"/>
+      <c r="L28" s="172"/>
+      <c r="M28" s="173"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="320"/>
-      <c r="B29" s="320"/>
-      <c r="C29" s="320"/>
-      <c r="D29" s="321"/>
+      <c r="A29" s="169"/>
+      <c r="B29" s="169"/>
+      <c r="C29" s="169"/>
+      <c r="D29" s="170"/>
       <c r="E29" s="66"/>
-      <c r="F29" s="322"/>
-      <c r="G29" s="322"/>
+      <c r="F29" s="171"/>
+      <c r="G29" s="171"/>
       <c r="H29" s="67" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I29" s="67" t="s">
-        <v>52</v>
-      </c>
-      <c r="J29" s="308"/>
-      <c r="K29" s="308"/>
-      <c r="L29" s="308"/>
-      <c r="M29" s="323"/>
+        <v>49</v>
+      </c>
+      <c r="J29" s="172"/>
+      <c r="K29" s="172"/>
+      <c r="L29" s="172"/>
+      <c r="M29" s="173"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="305" t="s">
+      <c r="A30" s="179" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="306"/>
-      <c r="C30" s="306"/>
-      <c r="D30" s="306"/>
+      <c r="B30" s="180"/>
+      <c r="C30" s="180"/>
+      <c r="D30" s="180"/>
       <c r="E30" s="12"/>
-      <c r="F30" s="307"/>
-      <c r="G30" s="308"/>
+      <c r="F30" s="181"/>
+      <c r="G30" s="172"/>
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
-      <c r="J30" s="309"/>
-      <c r="K30" s="309"/>
-      <c r="L30" s="309"/>
-      <c r="M30" s="310"/>
+      <c r="J30" s="182"/>
+      <c r="K30" s="182"/>
+      <c r="L30" s="182"/>
+      <c r="M30" s="183"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="311" t="s">
+      <c r="A31" s="116" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="312"/>
-      <c r="C31" s="312"/>
-      <c r="D31" s="312"/>
-      <c r="E31" s="312"/>
-      <c r="F31" s="312"/>
-      <c r="G31" s="312"/>
-      <c r="H31" s="312"/>
-      <c r="I31" s="312"/>
-      <c r="J31" s="312"/>
-      <c r="K31" s="312"/>
-      <c r="L31" s="312"/>
-      <c r="M31" s="313"/>
+      <c r="B31" s="117"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="117"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="117"/>
+      <c r="G31" s="117"/>
+      <c r="H31" s="117"/>
+      <c r="I31" s="117"/>
+      <c r="J31" s="117"/>
+      <c r="K31" s="117"/>
+      <c r="L31" s="117"/>
+      <c r="M31" s="118"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="314" t="s">
+      <c r="A32" s="184" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="315"/>
-      <c r="C32" s="315" t="s">
+      <c r="B32" s="185"/>
+      <c r="C32" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="315"/>
-      <c r="E32" s="316" t="s">
+      <c r="D32" s="185"/>
+      <c r="E32" s="186" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="317" t="s">
+      <c r="F32" s="187" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="318" t="s">
+      <c r="G32" s="188" t="s">
         <v>12</v>
       </c>
-      <c r="H32" s="318"/>
-      <c r="I32" s="318"/>
-      <c r="J32" s="318"/>
-      <c r="K32" s="318"/>
-      <c r="L32" s="315" t="s">
+      <c r="H32" s="188"/>
+      <c r="I32" s="188"/>
+      <c r="J32" s="188"/>
+      <c r="K32" s="188"/>
+      <c r="L32" s="185" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="319"/>
+      <c r="M32" s="189"/>
     </row>
     <row r="33" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="14" t="s">
@@ -4033,15 +4018,15 @@
       <c r="D33" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="316"/>
-      <c r="F33" s="317"/>
-      <c r="G33" s="304" t="s">
-        <v>50</v>
-      </c>
-      <c r="H33" s="304"/>
-      <c r="I33" s="304"/>
-      <c r="J33" s="304"/>
-      <c r="K33" s="304"/>
+      <c r="E33" s="186"/>
+      <c r="F33" s="187"/>
+      <c r="G33" s="174" t="s">
+        <v>47</v>
+      </c>
+      <c r="H33" s="174"/>
+      <c r="I33" s="174"/>
+      <c r="J33" s="174"/>
+      <c r="K33" s="174"/>
       <c r="L33" s="16" t="s">
         <v>14</v>
       </c>
@@ -4054,15 +4039,17 @@
       <c r="B34" s="67"/>
       <c r="C34" s="68"/>
       <c r="D34" s="67" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E34" s="68"/>
       <c r="F34" s="67"/>
-      <c r="G34" s="277"/>
-      <c r="H34" s="278"/>
-      <c r="I34" s="278"/>
-      <c r="J34" s="278"/>
-      <c r="K34" s="279"/>
+      <c r="G34" s="175" t="s">
+        <v>83</v>
+      </c>
+      <c r="H34" s="176"/>
+      <c r="I34" s="176"/>
+      <c r="J34" s="176"/>
+      <c r="K34" s="177"/>
       <c r="L34" s="18"/>
       <c r="M34" s="19"/>
     </row>
@@ -4073,11 +4060,11 @@
       <c r="D35" s="67"/>
       <c r="E35" s="67"/>
       <c r="F35" s="18"/>
-      <c r="G35" s="277"/>
-      <c r="H35" s="278"/>
-      <c r="I35" s="278"/>
-      <c r="J35" s="278"/>
-      <c r="K35" s="279"/>
+      <c r="G35" s="175"/>
+      <c r="H35" s="176"/>
+      <c r="I35" s="176"/>
+      <c r="J35" s="176"/>
+      <c r="K35" s="177"/>
       <c r="L35" s="18"/>
       <c r="M35" s="19"/>
     </row>
@@ -4088,11 +4075,11 @@
       <c r="D36" s="67"/>
       <c r="E36" s="67"/>
       <c r="F36" s="18"/>
-      <c r="G36" s="277"/>
-      <c r="H36" s="278"/>
-      <c r="I36" s="278"/>
-      <c r="J36" s="278"/>
-      <c r="K36" s="279"/>
+      <c r="G36" s="175"/>
+      <c r="H36" s="176"/>
+      <c r="I36" s="176"/>
+      <c r="J36" s="176"/>
+      <c r="K36" s="177"/>
       <c r="L36" s="18"/>
       <c r="M36" s="19"/>
     </row>
@@ -4103,19 +4090,19 @@
       <c r="D37" s="67"/>
       <c r="E37" s="67"/>
       <c r="F37" s="18"/>
-      <c r="G37" s="277"/>
-      <c r="H37" s="278"/>
-      <c r="I37" s="278"/>
-      <c r="J37" s="278"/>
-      <c r="K37" s="279"/>
+      <c r="G37" s="175"/>
+      <c r="H37" s="176"/>
+      <c r="I37" s="176"/>
+      <c r="J37" s="176"/>
+      <c r="K37" s="177"/>
       <c r="L37" s="18"/>
       <c r="M37" s="19"/>
-      <c r="Q37" s="302"/>
-      <c r="R37" s="302"/>
+      <c r="Q37" s="178"/>
+      <c r="R37" s="178"/>
       <c r="S37" s="20"/>
-      <c r="T37" s="301"/>
-      <c r="U37" s="301"/>
-      <c r="V37" s="301"/>
+      <c r="T37" s="196"/>
+      <c r="U37" s="196"/>
+      <c r="V37" s="196"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A38" s="70"/>
@@ -4124,19 +4111,19 @@
       <c r="D38" s="67"/>
       <c r="E38" s="67"/>
       <c r="F38" s="18"/>
-      <c r="G38" s="277"/>
-      <c r="H38" s="278"/>
-      <c r="I38" s="278"/>
-      <c r="J38" s="278"/>
-      <c r="K38" s="279"/>
+      <c r="G38" s="175"/>
+      <c r="H38" s="176"/>
+      <c r="I38" s="176"/>
+      <c r="J38" s="176"/>
+      <c r="K38" s="177"/>
       <c r="L38" s="18"/>
       <c r="M38" s="22"/>
-      <c r="Q38" s="302"/>
-      <c r="R38" s="302"/>
+      <c r="Q38" s="178"/>
+      <c r="R38" s="178"/>
       <c r="S38" s="20"/>
-      <c r="T38" s="301"/>
-      <c r="U38" s="301"/>
-      <c r="V38" s="301"/>
+      <c r="T38" s="196"/>
+      <c r="U38" s="196"/>
+      <c r="V38" s="196"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A39" s="70"/>
@@ -4145,19 +4132,19 @@
       <c r="D39" s="67"/>
       <c r="E39" s="67"/>
       <c r="F39" s="18"/>
-      <c r="G39" s="277"/>
-      <c r="H39" s="278"/>
-      <c r="I39" s="278"/>
-      <c r="J39" s="278"/>
-      <c r="K39" s="279"/>
+      <c r="G39" s="175"/>
+      <c r="H39" s="176"/>
+      <c r="I39" s="176"/>
+      <c r="J39" s="176"/>
+      <c r="K39" s="177"/>
       <c r="L39" s="18"/>
       <c r="M39" s="22"/>
       <c r="Q39" s="23"/>
       <c r="R39" s="23"/>
-      <c r="S39" s="303"/>
-      <c r="T39" s="301"/>
-      <c r="U39" s="301"/>
-      <c r="V39" s="301"/>
+      <c r="S39" s="197"/>
+      <c r="T39" s="196"/>
+      <c r="U39" s="196"/>
+      <c r="V39" s="196"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A40" s="70"/>
@@ -4166,19 +4153,19 @@
       <c r="D40" s="67"/>
       <c r="E40" s="67"/>
       <c r="F40" s="18"/>
-      <c r="G40" s="277"/>
-      <c r="H40" s="278"/>
-      <c r="I40" s="278"/>
-      <c r="J40" s="278"/>
-      <c r="K40" s="279"/>
+      <c r="G40" s="175"/>
+      <c r="H40" s="176"/>
+      <c r="I40" s="176"/>
+      <c r="J40" s="176"/>
+      <c r="K40" s="177"/>
       <c r="L40" s="18"/>
       <c r="M40" s="19"/>
       <c r="Q40" s="23"/>
       <c r="R40" s="23"/>
-      <c r="S40" s="303"/>
-      <c r="T40" s="301"/>
-      <c r="U40" s="301"/>
-      <c r="V40" s="301"/>
+      <c r="S40" s="197"/>
+      <c r="T40" s="196"/>
+      <c r="U40" s="196"/>
+      <c r="V40" s="196"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A41" s="70"/>
@@ -4187,11 +4174,11 @@
       <c r="D41" s="67"/>
       <c r="E41" s="67"/>
       <c r="F41" s="18"/>
-      <c r="G41" s="277"/>
-      <c r="H41" s="278"/>
-      <c r="I41" s="278"/>
-      <c r="J41" s="278"/>
-      <c r="K41" s="279"/>
+      <c r="G41" s="175"/>
+      <c r="H41" s="176"/>
+      <c r="I41" s="176"/>
+      <c r="J41" s="176"/>
+      <c r="K41" s="177"/>
       <c r="L41" s="18"/>
       <c r="M41" s="19"/>
     </row>
@@ -4202,302 +4189,298 @@
       <c r="D42" s="72"/>
       <c r="E42" s="73"/>
       <c r="F42" s="24"/>
-      <c r="G42" s="280" t="s">
+      <c r="G42" s="238" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="281"/>
-      <c r="I42" s="281"/>
-      <c r="J42" s="281"/>
-      <c r="K42" s="282"/>
+      <c r="H42" s="239"/>
+      <c r="I42" s="239"/>
+      <c r="J42" s="239"/>
+      <c r="K42" s="240"/>
       <c r="L42" s="24"/>
       <c r="M42" s="25"/>
     </row>
     <row r="43" spans="1:22" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="257" t="s">
+      <c r="A43" s="359" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="360"/>
+      <c r="C43" s="360"/>
+      <c r="D43" s="360"/>
+      <c r="E43" s="360"/>
+      <c r="F43" s="360"/>
+      <c r="G43" s="360"/>
+      <c r="H43" s="361"/>
+      <c r="I43" s="241" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="258"/>
-      <c r="C43" s="258"/>
-      <c r="D43" s="258"/>
-      <c r="E43" s="258"/>
-      <c r="F43" s="258"/>
-      <c r="G43" s="258"/>
-      <c r="H43" s="259"/>
-      <c r="I43" s="283" t="s">
+      <c r="J43" s="242"/>
+      <c r="K43" s="242"/>
+      <c r="L43" s="242"/>
+      <c r="M43" s="243"/>
+    </row>
+    <row r="44" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="362"/>
+      <c r="B44" s="363"/>
+      <c r="C44" s="363"/>
+      <c r="D44" s="363"/>
+      <c r="E44" s="363"/>
+      <c r="F44" s="363"/>
+      <c r="G44" s="363"/>
+      <c r="H44" s="364"/>
+      <c r="I44" s="244"/>
+      <c r="J44" s="245"/>
+      <c r="K44" s="245"/>
+      <c r="L44" s="245"/>
+      <c r="M44" s="246"/>
+    </row>
+    <row r="45" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="362"/>
+      <c r="B45" s="363"/>
+      <c r="C45" s="363"/>
+      <c r="D45" s="363"/>
+      <c r="E45" s="363"/>
+      <c r="F45" s="363"/>
+      <c r="G45" s="363"/>
+      <c r="H45" s="364"/>
+      <c r="I45" s="190" t="s">
+        <v>80</v>
+      </c>
+      <c r="J45" s="191"/>
+      <c r="K45" s="191"/>
+      <c r="L45" s="191"/>
+      <c r="M45" s="192"/>
+    </row>
+    <row r="46" spans="1:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="362"/>
+      <c r="B46" s="363"/>
+      <c r="C46" s="363"/>
+      <c r="D46" s="363"/>
+      <c r="E46" s="363"/>
+      <c r="F46" s="363"/>
+      <c r="G46" s="363"/>
+      <c r="H46" s="364"/>
+      <c r="I46" s="190"/>
+      <c r="J46" s="191"/>
+      <c r="K46" s="191"/>
+      <c r="L46" s="191"/>
+      <c r="M46" s="192"/>
+    </row>
+    <row r="47" spans="1:22" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="365"/>
+      <c r="B47" s="366"/>
+      <c r="C47" s="366"/>
+      <c r="D47" s="366"/>
+      <c r="E47" s="366"/>
+      <c r="F47" s="366"/>
+      <c r="G47" s="366"/>
+      <c r="H47" s="367"/>
+      <c r="I47" s="193" t="s">
+        <v>81</v>
+      </c>
+      <c r="J47" s="194"/>
+      <c r="K47" s="194"/>
+      <c r="L47" s="194"/>
+      <c r="M47" s="195"/>
+    </row>
+    <row r="48" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="215" t="s">
+        <v>33</v>
+      </c>
+      <c r="B48" s="216"/>
+      <c r="C48" s="216"/>
+      <c r="D48" s="216"/>
+      <c r="E48" s="216"/>
+      <c r="F48" s="216"/>
+      <c r="G48" s="216"/>
+      <c r="H48" s="216"/>
+      <c r="I48" s="216"/>
+      <c r="J48" s="216"/>
+      <c r="K48" s="216"/>
+      <c r="L48" s="216"/>
+      <c r="M48" s="217"/>
+    </row>
+    <row r="49" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="218" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" s="219"/>
+      <c r="C49" s="219"/>
+      <c r="D49" s="219"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="219"/>
+      <c r="G49" s="219"/>
+      <c r="H49" s="220"/>
+      <c r="I49" s="226" t="s">
         <v>35</v>
       </c>
-      <c r="J43" s="284"/>
-      <c r="K43" s="284"/>
-      <c r="L43" s="284"/>
-      <c r="M43" s="285"/>
-    </row>
-    <row r="44" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="260"/>
-      <c r="B44" s="261"/>
-      <c r="C44" s="261"/>
-      <c r="D44" s="261"/>
-      <c r="E44" s="261"/>
-      <c r="F44" s="261"/>
-      <c r="G44" s="261"/>
-      <c r="H44" s="262"/>
-      <c r="I44" s="286"/>
-      <c r="J44" s="287"/>
-      <c r="K44" s="287"/>
-      <c r="L44" s="287"/>
-      <c r="M44" s="288"/>
-    </row>
-    <row r="45" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="289" t="s">
-        <v>33</v>
-      </c>
-      <c r="B45" s="290"/>
-      <c r="C45" s="290"/>
-      <c r="D45" s="290"/>
-      <c r="E45" s="290"/>
-      <c r="F45" s="290"/>
-      <c r="G45" s="290"/>
-      <c r="H45" s="291"/>
-      <c r="I45" s="292" t="s">
-        <v>83</v>
-      </c>
-      <c r="J45" s="293"/>
-      <c r="K45" s="293"/>
-      <c r="L45" s="293"/>
-      <c r="M45" s="294"/>
-    </row>
-    <row r="46" spans="1:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="289" t="s">
-        <v>34</v>
-      </c>
-      <c r="B46" s="290"/>
-      <c r="C46" s="290"/>
-      <c r="D46" s="290"/>
-      <c r="E46" s="290"/>
-      <c r="F46" s="290"/>
-      <c r="G46" s="290"/>
-      <c r="H46" s="291"/>
-      <c r="I46" s="292"/>
-      <c r="J46" s="293"/>
-      <c r="K46" s="293"/>
-      <c r="L46" s="293"/>
-      <c r="M46" s="294"/>
-    </row>
-    <row r="47" spans="1:22" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="295"/>
-      <c r="B47" s="296"/>
-      <c r="C47" s="296"/>
-      <c r="D47" s="296"/>
-      <c r="E47" s="296"/>
-      <c r="F47" s="296"/>
-      <c r="G47" s="296"/>
-      <c r="H47" s="297"/>
-      <c r="I47" s="298" t="s">
-        <v>84</v>
-      </c>
-      <c r="J47" s="299"/>
-      <c r="K47" s="299"/>
-      <c r="L47" s="299"/>
-      <c r="M47" s="300"/>
-    </row>
-    <row r="48" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="254" t="s">
+      <c r="J49" s="227"/>
+      <c r="K49" s="227"/>
+      <c r="L49" s="227"/>
+      <c r="M49" s="228"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A50" s="221"/>
+      <c r="B50" s="222"/>
+      <c r="C50" s="222"/>
+      <c r="D50" s="222"/>
+      <c r="E50" s="222"/>
+      <c r="F50" s="222"/>
+      <c r="G50" s="222"/>
+      <c r="H50" s="223"/>
+      <c r="I50" s="229"/>
+      <c r="J50" s="230"/>
+      <c r="K50" s="230"/>
+      <c r="L50" s="230"/>
+      <c r="M50" s="231"/>
+    </row>
+    <row r="51" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="224"/>
+      <c r="B51" s="225"/>
+      <c r="C51" s="225"/>
+      <c r="D51" s="225"/>
+      <c r="E51" s="222"/>
+      <c r="F51" s="222"/>
+      <c r="G51" s="222"/>
+      <c r="H51" s="223"/>
+      <c r="I51" s="232" t="s">
         <v>36</v>
       </c>
-      <c r="B48" s="255"/>
-      <c r="C48" s="255"/>
-      <c r="D48" s="255"/>
-      <c r="E48" s="255"/>
-      <c r="F48" s="255"/>
-      <c r="G48" s="255"/>
-      <c r="H48" s="255"/>
-      <c r="I48" s="255"/>
-      <c r="J48" s="255"/>
-      <c r="K48" s="255"/>
-      <c r="L48" s="255"/>
-      <c r="M48" s="256"/>
-    </row>
-    <row r="49" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="257" t="s">
+      <c r="J51" s="233"/>
+      <c r="K51" s="234"/>
+      <c r="L51" s="234"/>
+      <c r="M51" s="235"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A52" s="215" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="258"/>
-      <c r="C49" s="258"/>
-      <c r="D49" s="258"/>
-      <c r="E49" s="258"/>
-      <c r="F49" s="258"/>
-      <c r="G49" s="258"/>
-      <c r="H49" s="259"/>
-      <c r="I49" s="265" t="s">
+      <c r="B52" s="216"/>
+      <c r="C52" s="216"/>
+      <c r="D52" s="216"/>
+      <c r="E52" s="74" t="s">
+        <v>39</v>
+      </c>
+      <c r="F52" s="75"/>
+      <c r="G52" s="236" t="s">
+        <v>40</v>
+      </c>
+      <c r="H52" s="236"/>
+      <c r="I52" s="236"/>
+      <c r="J52" s="237"/>
+      <c r="K52" s="216" t="s">
+        <v>44</v>
+      </c>
+      <c r="L52" s="216"/>
+      <c r="M52" s="217"/>
+    </row>
+    <row r="53" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="203" t="s">
         <v>38</v>
       </c>
-      <c r="J49" s="266"/>
-      <c r="K49" s="266"/>
-      <c r="L49" s="266"/>
-      <c r="M49" s="267"/>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="260"/>
-      <c r="B50" s="261"/>
-      <c r="C50" s="261"/>
-      <c r="D50" s="261"/>
-      <c r="E50" s="261"/>
-      <c r="F50" s="261"/>
-      <c r="G50" s="261"/>
-      <c r="H50" s="262"/>
-      <c r="I50" s="268"/>
-      <c r="J50" s="269"/>
-      <c r="K50" s="269"/>
-      <c r="L50" s="269"/>
-      <c r="M50" s="270"/>
-    </row>
-    <row r="51" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="263"/>
-      <c r="B51" s="264"/>
-      <c r="C51" s="264"/>
-      <c r="D51" s="264"/>
-      <c r="E51" s="261"/>
-      <c r="F51" s="261"/>
-      <c r="G51" s="261"/>
-      <c r="H51" s="262"/>
-      <c r="I51" s="271" t="s">
-        <v>39</v>
-      </c>
-      <c r="J51" s="272"/>
-      <c r="K51" s="273"/>
-      <c r="L51" s="273"/>
-      <c r="M51" s="274"/>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="254" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="255"/>
-      <c r="C52" s="255"/>
-      <c r="D52" s="255"/>
-      <c r="E52" s="74" t="s">
-        <v>42</v>
-      </c>
-      <c r="F52" s="75"/>
-      <c r="G52" s="275" t="s">
-        <v>43</v>
-      </c>
-      <c r="H52" s="275"/>
-      <c r="I52" s="275"/>
-      <c r="J52" s="276"/>
-      <c r="K52" s="255" t="s">
-        <v>47</v>
-      </c>
-      <c r="L52" s="255"/>
-      <c r="M52" s="256"/>
-    </row>
-    <row r="53" spans="1:13" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="241" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="242"/>
-      <c r="C53" s="242"/>
-      <c r="D53" s="242"/>
+      <c r="B53" s="204"/>
+      <c r="C53" s="204"/>
+      <c r="D53" s="204"/>
       <c r="E53" s="76"/>
       <c r="F53" s="69"/>
       <c r="G53" s="69"/>
       <c r="H53" s="69"/>
       <c r="I53" s="69"/>
       <c r="J53" s="77"/>
-      <c r="K53" s="242" t="s">
-        <v>49</v>
-      </c>
-      <c r="L53" s="242"/>
-      <c r="M53" s="243"/>
+      <c r="K53" s="204" t="s">
+        <v>46</v>
+      </c>
+      <c r="L53" s="204"/>
+      <c r="M53" s="205"/>
     </row>
     <row r="54" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="241"/>
-      <c r="B54" s="242"/>
-      <c r="C54" s="242"/>
-      <c r="D54" s="242"/>
-      <c r="E54" s="244" t="s">
-        <v>81</v>
-      </c>
-      <c r="F54" s="245"/>
-      <c r="G54" s="405" t="s">
-        <v>80</v>
-      </c>
-      <c r="H54" s="234" t="s">
-        <v>44</v>
-      </c>
-      <c r="I54" s="234"/>
-      <c r="J54" s="235"/>
-      <c r="K54" s="242"/>
-      <c r="L54" s="242"/>
-      <c r="M54" s="243"/>
+      <c r="A54" s="203"/>
+      <c r="B54" s="204"/>
+      <c r="C54" s="204"/>
+      <c r="D54" s="204"/>
+      <c r="E54" s="206" t="s">
+        <v>78</v>
+      </c>
+      <c r="F54" s="207"/>
+      <c r="G54" s="96" t="s">
+        <v>77</v>
+      </c>
+      <c r="H54" s="198" t="s">
+        <v>41</v>
+      </c>
+      <c r="I54" s="198"/>
+      <c r="J54" s="199"/>
+      <c r="K54" s="204"/>
+      <c r="L54" s="204"/>
+      <c r="M54" s="205"/>
     </row>
     <row r="55" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="241"/>
-      <c r="B55" s="242"/>
-      <c r="C55" s="242"/>
-      <c r="D55" s="242"/>
-      <c r="E55" s="244" t="s">
-        <v>82</v>
-      </c>
-      <c r="F55" s="245"/>
-      <c r="G55" s="406" t="s">
-        <v>80</v>
-      </c>
-      <c r="H55" s="234" t="s">
+      <c r="A55" s="203"/>
+      <c r="B55" s="204"/>
+      <c r="C55" s="204"/>
+      <c r="D55" s="204"/>
+      <c r="E55" s="206" t="s">
+        <v>79</v>
+      </c>
+      <c r="F55" s="207"/>
+      <c r="G55" s="208" t="s">
+        <v>77</v>
+      </c>
+      <c r="H55" s="198" t="s">
+        <v>42</v>
+      </c>
+      <c r="I55" s="198"/>
+      <c r="J55" s="199"/>
+      <c r="K55" s="204"/>
+      <c r="L55" s="204"/>
+      <c r="M55" s="205"/>
+    </row>
+    <row r="56" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="209"/>
+      <c r="B56" s="138"/>
+      <c r="C56" s="138"/>
+      <c r="D56" s="139"/>
+      <c r="E56" s="206"/>
+      <c r="F56" s="207"/>
+      <c r="G56" s="208"/>
+      <c r="H56" s="198"/>
+      <c r="I56" s="198"/>
+      <c r="J56" s="199"/>
+      <c r="K56" s="213" t="s">
         <v>45</v>
       </c>
-      <c r="I55" s="234"/>
-      <c r="J55" s="235"/>
-      <c r="K55" s="242"/>
-      <c r="L55" s="242"/>
-      <c r="M55" s="243"/>
-    </row>
-    <row r="56" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="246"/>
-      <c r="B56" s="247"/>
-      <c r="C56" s="247"/>
-      <c r="D56" s="248"/>
-      <c r="E56" s="244"/>
-      <c r="F56" s="245"/>
-      <c r="G56" s="406"/>
-      <c r="H56" s="234"/>
-      <c r="I56" s="234"/>
-      <c r="J56" s="235"/>
-      <c r="K56" s="252" t="s">
-        <v>48</v>
-      </c>
-      <c r="L56" s="252"/>
-      <c r="M56" s="253"/>
+      <c r="L56" s="213"/>
+      <c r="M56" s="214"/>
     </row>
     <row r="57" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="246"/>
-      <c r="B57" s="247"/>
-      <c r="C57" s="247"/>
-      <c r="D57" s="248"/>
-      <c r="E57" s="244"/>
-      <c r="F57" s="245"/>
-      <c r="G57" s="405" t="s">
-        <v>80</v>
-      </c>
-      <c r="H57" s="234" t="s">
-        <v>46</v>
-      </c>
-      <c r="I57" s="234"/>
-      <c r="J57" s="235"/>
+      <c r="A57" s="209"/>
+      <c r="B57" s="138"/>
+      <c r="C57" s="138"/>
+      <c r="D57" s="139"/>
+      <c r="E57" s="206"/>
+      <c r="F57" s="207"/>
+      <c r="G57" s="96" t="s">
+        <v>77</v>
+      </c>
+      <c r="H57" s="198" t="s">
+        <v>43</v>
+      </c>
+      <c r="I57" s="198"/>
+      <c r="J57" s="199"/>
       <c r="K57" s="78"/>
       <c r="L57" s="79"/>
       <c r="M57" s="80"/>
     </row>
     <row r="58" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="249"/>
-      <c r="B58" s="250"/>
-      <c r="C58" s="250"/>
-      <c r="D58" s="251"/>
-      <c r="E58" s="236"/>
-      <c r="F58" s="237"/>
-      <c r="G58" s="237"/>
-      <c r="H58" s="237"/>
-      <c r="I58" s="237"/>
-      <c r="J58" s="238"/>
+      <c r="A58" s="210"/>
+      <c r="B58" s="211"/>
+      <c r="C58" s="211"/>
+      <c r="D58" s="212"/>
+      <c r="E58" s="167"/>
+      <c r="F58" s="168"/>
+      <c r="G58" s="168"/>
+      <c r="H58" s="168"/>
+      <c r="I58" s="168"/>
+      <c r="J58" s="200"/>
       <c r="K58" s="81"/>
       <c r="L58" s="82"/>
       <c r="M58" s="83"/>
@@ -4515,95 +4498,7 @@
       <c r="J59" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="112">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="I4:M6"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:M3"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:K1"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="I12:M14"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="I8:M8"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="A20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:G21"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="J20:M21"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="I16:M16"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:M18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="G33:K33"/>
-    <mergeCell ref="G34:K34"/>
-    <mergeCell ref="G35:K35"/>
-    <mergeCell ref="G36:K36"/>
-    <mergeCell ref="G37:K37"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="A31:M31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="G32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="I45:M46"/>
-    <mergeCell ref="A46:H47"/>
-    <mergeCell ref="I47:M47"/>
-    <mergeCell ref="T37:V37"/>
-    <mergeCell ref="G38:K38"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="T38:V38"/>
-    <mergeCell ref="G39:K39"/>
-    <mergeCell ref="S39:S40"/>
-    <mergeCell ref="T39:V40"/>
-    <mergeCell ref="G40:K40"/>
+  <mergeCells count="110">
     <mergeCell ref="H57:J57"/>
     <mergeCell ref="E58:J58"/>
     <mergeCell ref="F16:H16"/>
@@ -4626,8 +4521,94 @@
     <mergeCell ref="K52:M52"/>
     <mergeCell ref="G41:K41"/>
     <mergeCell ref="G42:K42"/>
-    <mergeCell ref="A43:H44"/>
     <mergeCell ref="I43:M44"/>
+    <mergeCell ref="I45:M46"/>
+    <mergeCell ref="I47:M47"/>
+    <mergeCell ref="T37:V37"/>
+    <mergeCell ref="G38:K38"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="T38:V38"/>
+    <mergeCell ref="G39:K39"/>
+    <mergeCell ref="S39:S40"/>
+    <mergeCell ref="T39:V40"/>
+    <mergeCell ref="G40:K40"/>
+    <mergeCell ref="A43:H47"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="G34:K34"/>
+    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="G36:K36"/>
+    <mergeCell ref="G37:K37"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="A31:M31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="G32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:G21"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J20:M21"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="I15:M15"/>
+    <mergeCell ref="I16:M16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:M18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="I12:M14"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="I4:M6"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="I2:M3"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:K1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.26" top="0.52" bottom="0.56000000000000005" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5349,1012 +5330,1012 @@
   <sheetData>
     <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="85" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="415"/>
-      <c r="C1" s="415"/>
-      <c r="D1" s="379" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="379"/>
-      <c r="F1" s="379"/>
-      <c r="G1" s="379"/>
-      <c r="H1" s="379"/>
-      <c r="I1" s="379"/>
-      <c r="J1" s="379"/>
-      <c r="K1" s="379"/>
-      <c r="L1" s="381" t="s">
-        <v>59</v>
-      </c>
-      <c r="M1" s="382"/>
-      <c r="P1" s="414"/>
+        <v>74</v>
+      </c>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="122" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="114" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" s="115"/>
+      <c r="P1" s="98"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="311" t="s">
+      <c r="A2" s="116" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="312"/>
-      <c r="C2" s="312"/>
-      <c r="D2" s="312"/>
-      <c r="E2" s="312"/>
-      <c r="F2" s="312"/>
-      <c r="G2" s="312"/>
-      <c r="H2" s="312"/>
-      <c r="I2" s="312"/>
-      <c r="J2" s="312"/>
-      <c r="K2" s="312"/>
-      <c r="L2" s="312"/>
-      <c r="M2" s="313"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="118"/>
     </row>
     <row r="3" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="324" t="s">
+      <c r="A3" s="141" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="325"/>
-      <c r="C3" s="325"/>
-      <c r="D3" s="325"/>
-      <c r="E3" s="325" t="s">
+      <c r="B3" s="142"/>
+      <c r="C3" s="142"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="142" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="325" t="s">
+      <c r="F3" s="142" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="325"/>
-      <c r="H3" s="326" t="s">
+      <c r="G3" s="142"/>
+      <c r="H3" s="143" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="327"/>
-      <c r="J3" s="328" t="s">
+      <c r="I3" s="144"/>
+      <c r="J3" s="145" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="329"/>
-      <c r="L3" s="329"/>
-      <c r="M3" s="330"/>
+      <c r="K3" s="146"/>
+      <c r="L3" s="146"/>
+      <c r="M3" s="147"/>
     </row>
     <row r="4" spans="1:16" ht=